--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="2181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="2182">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528865814209</t>
+    <t xml:space="preserve">2.44528841972351</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">2.50193166732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40895104408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35658288002014</t>
+    <t xml:space="preserve">2.40895080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3565821647644</t>
   </si>
   <si>
     <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29780149459839</t>
+    <t xml:space="preserve">2.29780173301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.37261343002319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37795686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33413887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23474550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15458965301514</t>
+    <t xml:space="preserve">2.37795734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33413910865784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2347457408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15458989143372</t>
   </si>
   <si>
     <t xml:space="preserve">2.11183977127075</t>
@@ -80,241 +80,241 @@
     <t xml:space="preserve">1.9964154958725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06588411331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07977747917175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0348904132843</t>
+    <t xml:space="preserve">2.06588387489319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07977724075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03489017486572</t>
   </si>
   <si>
     <t xml:space="preserve">2.03168392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90343451499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00924062728882</t>
+    <t xml:space="preserve">2.02954697608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00924038887024</t>
   </si>
   <si>
     <t xml:space="preserve">1.93549692630768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84037899971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701653957367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349858760834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5315113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55822992324829</t>
+    <t xml:space="preserve">1.8403787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74953544139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701665878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792963981628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349882602692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151142597198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861711025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55823004245758</t>
   </si>
   <si>
     <t xml:space="preserve">1.60632359981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72922921180725</t>
+    <t xml:space="preserve">1.72922933101654</t>
   </si>
   <si>
     <t xml:space="preserve">1.67899823188782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7431229352951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350429534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69396078586578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419164657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70571672916412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296696662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533536911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82541656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82327878475189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88099110126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381587505341</t>
+    <t xml:space="preserve">1.74312305450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350405693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6939605474472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419188499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7057169675827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296708583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71533560752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82541596889496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8232786655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88099098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381611347198</t>
   </si>
   <si>
     <t xml:space="preserve">1.89488470554352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86602854728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404150485992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7655668258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82648491859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79976630210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92053425312042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442833423615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229067325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221530437469</t>
+    <t xml:space="preserve">1.86602878570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404162406921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82648456096649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79976642131805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92053461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93229055404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221566200256</t>
   </si>
   <si>
     <t xml:space="preserve">1.96435332298279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97183430194855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95580327510834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95259714126587</t>
+    <t xml:space="preserve">1.97183454036713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95580315589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95259702205658</t>
   </si>
   <si>
     <t xml:space="preserve">1.92374074459076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87564706802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88312828540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91198468208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90022826194763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89167857170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579732894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81793510913849</t>
+    <t xml:space="preserve">1.87564718723297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8831285238266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91198456287384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9002286195755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89167833328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579768657684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81793463230133</t>
   </si>
   <si>
     <t xml:space="preserve">1.80190396308899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87992238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465348720551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92587876319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92801570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91519093513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0177903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05626559257507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07443404197693</t>
+    <t xml:space="preserve">1.87992203235626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129721164703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587828636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92801594734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91519117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01779055595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05626487731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07443356513977</t>
   </si>
   <si>
     <t xml:space="preserve">2.06160879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07015872001648</t>
+    <t xml:space="preserve">2.07015895843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0551962852478</t>
+    <t xml:space="preserve">2.05519652366638</t>
   </si>
   <si>
     <t xml:space="preserve">2.05092144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99855291843414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214029312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95045924186707</t>
+    <t xml:space="preserve">1.99855279922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214053153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95045948028564</t>
   </si>
   <si>
     <t xml:space="preserve">1.93977212905884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84999716281891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7912163734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73884809017181</t>
+    <t xml:space="preserve">1.84999763965607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457871437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121661186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73884785175323</t>
   </si>
   <si>
     <t xml:space="preserve">1.72388565540314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69502937793732</t>
+    <t xml:space="preserve">1.69502949714661</t>
   </si>
   <si>
     <t xml:space="preserve">1.70678567886353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70785439014435</t>
+    <t xml:space="preserve">1.70785450935364</t>
   </si>
   <si>
     <t xml:space="preserve">1.76235246658325</t>
@@ -323,94 +323,94 @@
     <t xml:space="preserve">1.83700942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87773156166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87546896934509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279745101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90601027011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451826572418</t>
+    <t xml:space="preserve">1.87773132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87546908855438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279757022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90601050853729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451814651489</t>
   </si>
   <si>
     <t xml:space="preserve">1.80081224441528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80986166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81438601016998</t>
+    <t xml:space="preserve">1.80986154079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81438624858856</t>
   </si>
   <si>
     <t xml:space="preserve">1.80646812915802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75104069709778</t>
+    <t xml:space="preserve">1.75104117393494</t>
   </si>
   <si>
     <t xml:space="preserve">1.6311377286911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5429071187973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46711909770966</t>
+    <t xml:space="preserve">1.54290676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46711897850037</t>
   </si>
   <si>
     <t xml:space="preserve">1.47390592098236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42526578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51689028739929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6119077205658</t>
+    <t xml:space="preserve">1.42526590824127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190795898438</t>
   </si>
   <si>
     <t xml:space="preserve">1.6005961894989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57684183120728</t>
+    <t xml:space="preserve">1.57684195041656</t>
   </si>
   <si>
     <t xml:space="preserve">1.69900739192963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38341307640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2420175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27255868911743</t>
+    <t xml:space="preserve">1.38341295719147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24201774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27255892753601</t>
   </si>
   <si>
     <t xml:space="preserve">1.21373820304871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19111526012421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23636186122894</t>
+    <t xml:space="preserve">1.19111502170563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23636162281036</t>
   </si>
   <si>
     <t xml:space="preserve">1.18545937538147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14021277427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09949100017548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722864627838</t>
+    <t xml:space="preserve">1.14021289348602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0994907617569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722852706909</t>
   </si>
   <si>
     <t xml:space="preserve">1.23749279975891</t>
@@ -419,43 +419,43 @@
     <t xml:space="preserve">1.28726410865784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36870777606964</t>
+    <t xml:space="preserve">1.36870765686035</t>
   </si>
   <si>
     <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3935934305191</t>
+    <t xml:space="preserve">1.39359331130981</t>
   </si>
   <si>
     <t xml:space="preserve">1.38454413414001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40038049221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3698388338089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39811789989471</t>
+    <t xml:space="preserve">1.40038013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983895301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.398118019104</t>
   </si>
   <si>
     <t xml:space="preserve">1.37888836860657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37097001075745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37775695323944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42979085445404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4026426076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38567519187927</t>
+    <t xml:space="preserve">1.37097012996674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37775719165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42979061603546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40264272689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38567531108856</t>
   </si>
   <si>
     <t xml:space="preserve">1.26011598110199</t>
@@ -464,43 +464,43 @@
     <t xml:space="preserve">1.29631340503693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32232987880707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37549483776093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43657755851746</t>
+    <t xml:space="preserve">1.32233011722565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37549471855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43657743930817</t>
   </si>
   <si>
     <t xml:space="preserve">1.45354509353638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44788920879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47051227092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45015156269073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41961026191711</t>
+    <t xml:space="preserve">1.44788908958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47051239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45015144348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41961014270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.38001954555511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39698708057404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33137953281403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33251059055328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38228166103363</t>
+    <t xml:space="preserve">1.39698684215546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33137941360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33251070976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38228154182434</t>
   </si>
   <si>
     <t xml:space="preserve">1.36757659912109</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">1.33816623687744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35400283336639</t>
+    <t xml:space="preserve">1.35400259494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.32798588275909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41056072711945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40377378463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42413461208344</t>
+    <t xml:space="preserve">1.41056084632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40377402305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42413485050201</t>
   </si>
   <si>
     <t xml:space="preserve">1.43883979320526</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">1.477299451828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48747992515564</t>
+    <t xml:space="preserve">1.48748016357422</t>
   </si>
   <si>
     <t xml:space="preserve">1.48974239826202</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">1.36078953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41282308101654</t>
+    <t xml:space="preserve">1.41282320022583</t>
   </si>
   <si>
     <t xml:space="preserve">1.35513389110565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34947800636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34269118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821457386017</t>
+    <t xml:space="preserve">1.34947788715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34269094467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536258220673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821469306946</t>
   </si>
   <si>
     <t xml:space="preserve">1.31780540943146</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">1.28500175476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27934598922729</t>
+    <t xml:space="preserve">1.27934587001801</t>
   </si>
   <si>
     <t xml:space="preserve">1.35174036026001</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.358527302742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3721010684967</t>
+    <t xml:space="preserve">1.37210118770599</t>
   </si>
   <si>
     <t xml:space="preserve">1.39472460746765</t>
@@ -593,55 +593,55 @@
     <t xml:space="preserve">1.41621649265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44110238552094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49313580989838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52480852603912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53159534931183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51575887203217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54856276512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5655300617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61077690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63453137874603</t>
+    <t xml:space="preserve">1.44110214710236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4931355714798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52480828762054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53159511089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51575899124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54856264591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56553018093109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61077678203583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63453149795532</t>
   </si>
   <si>
     <t xml:space="preserve">1.59833407402039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57571089267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118594646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50444746017456</t>
+    <t xml:space="preserve">1.57571077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118618488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50444734096527</t>
   </si>
   <si>
     <t xml:space="preserve">1.51802134513855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47503733634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6571546792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69335198402405</t>
+    <t xml:space="preserve">1.47503697872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65715456008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69335186481476</t>
   </si>
   <si>
     <t xml:space="preserve">1.66733491420746</t>
@@ -650,94 +650,94 @@
     <t xml:space="preserve">1.66167891025543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905608654022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172724723816</t>
+    <t xml:space="preserve">1.63905596733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172736644745</t>
   </si>
   <si>
     <t xml:space="preserve">1.57457947731018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62661290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58476006984711</t>
+    <t xml:space="preserve">1.62661278247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5847601890564</t>
   </si>
   <si>
     <t xml:space="preserve">1.5610054731369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54064452648163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512101650238</t>
+    <t xml:space="preserve">1.54064464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512089729309</t>
   </si>
   <si>
     <t xml:space="preserve">1.64923632144928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6662038564682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62435078620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741847515106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284554958344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492778778076</t>
+    <t xml:space="preserve">1.66620397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62435066699982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049963474274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741871356964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284566879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492766857147</t>
   </si>
   <si>
     <t xml:space="preserve">1.83022248744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86302602291107</t>
+    <t xml:space="preserve">1.86302590370178</t>
   </si>
   <si>
     <t xml:space="preserve">1.85623931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91053509712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89922308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91166615486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92637121677399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94560098648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94447016716003</t>
+    <t xml:space="preserve">1.9105349779129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89922344684601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91166627407074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92637133598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94560134410858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446980953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.89696109294891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655204772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9806672334671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01347088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01573348045349</t>
+    <t xml:space="preserve">1.93655180931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066735267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0134711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781512260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01573300361633</t>
   </si>
   <si>
     <t xml:space="preserve">2.01912689208984</t>
@@ -746,76 +746,76 @@
     <t xml:space="preserve">1.96483087539673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99876570701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02025771141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727394104004</t>
+    <t xml:space="preserve">1.9987655878067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02025818824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727370262146</t>
   </si>
   <si>
     <t xml:space="preserve">2.01007747650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9716180562973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478634595871</t>
+    <t xml:space="preserve">1.97161793708801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94786369800568</t>
   </si>
   <si>
     <t xml:space="preserve">1.97953605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02252006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08247184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08699655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05079960823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193066596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542075157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9320273399353</t>
+    <t xml:space="preserve">2.0225203037262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99084770679474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247208595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08699679374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05079936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542087078094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202686309814</t>
   </si>
   <si>
     <t xml:space="preserve">1.96709322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894618034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940403938293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89130544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320649623871</t>
+    <t xml:space="preserve">2.00894641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940415859222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89130556583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87320697307587</t>
   </si>
   <si>
     <t xml:space="preserve">1.87999367713928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85510802268982</t>
+    <t xml:space="preserve">1.8551082611084</t>
   </si>
   <si>
     <t xml:space="preserve">1.96596217155457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03609395027161</t>
+    <t xml:space="preserve">2.03609418869019</t>
   </si>
   <si>
     <t xml:space="preserve">1.99424111843109</t>
@@ -824,85 +824,85 @@
     <t xml:space="preserve">2.00215911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329065322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478265762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01799535751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00442147254944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95465064048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02930736541748</t>
+    <t xml:space="preserve">2.00329041481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478241920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01799559593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00442171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9546502828598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02930760383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.02817606925964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09265208244324</t>
+    <t xml:space="preserve">2.09265232086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.13224315643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432503700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12093162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15939116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373539924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016103744507</t>
+    <t xml:space="preserve">2.12432527542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12093186378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15939092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016127586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.10848879814148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0756847858429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14921045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19332599639893</t>
+    <t xml:space="preserve">2.07568526268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14921069145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19332575798035</t>
   </si>
   <si>
     <t xml:space="preserve">2.1786208152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23291683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1955885887146</t>
+    <t xml:space="preserve">2.23291659355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558811187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.20803117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20576906204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18314552307129</t>
+    <t xml:space="preserve">2.20576858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18314504623413</t>
   </si>
   <si>
     <t xml:space="preserve">2.16617798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20350623130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19219470024109</t>
+    <t xml:space="preserve">2.2035059928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19219446182251</t>
   </si>
   <si>
     <t xml:space="preserve">2.15825986862183</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">2.20011305809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17522716522217</t>
+    <t xml:space="preserve">2.17522740364075</t>
   </si>
   <si>
     <t xml:space="preserve">2.17748975753784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15599751472473</t>
+    <t xml:space="preserve">2.15599727630615</t>
   </si>
   <si>
     <t xml:space="preserve">2.14129257202148</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">2.09378361701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07907819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08812785148621</t>
+    <t xml:space="preserve">2.07907867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08812761306763</t>
   </si>
   <si>
     <t xml:space="preserve">2.11188244819641</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">2.26232695579529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26006460189819</t>
+    <t xml:space="preserve">2.26006484031677</t>
   </si>
   <si>
     <t xml:space="preserve">2.2578022480011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31436038017273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33132815361023</t>
+    <t xml:space="preserve">2.31436014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33132791519165</t>
   </si>
   <si>
     <t xml:space="preserve">2.34716439247131</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">2.40032887458801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41164040565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43878817558289</t>
+    <t xml:space="preserve">2.41164064407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43878841400146</t>
   </si>
   <si>
     <t xml:space="preserve">2.44557523727417</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">2.38675475120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3630006313324</t>
+    <t xml:space="preserve">2.36300039291382</t>
   </si>
   <si>
     <t xml:space="preserve">2.33585262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25893330574036</t>
+    <t xml:space="preserve">2.25893354415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.24988412857056</t>
@@ -995,43 +995,43 @@
     <t xml:space="preserve">2.27137589454651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33769392967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.302166223526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36137866973877</t>
+    <t xml:space="preserve">2.33769369125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30216646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36137843132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.35072040557861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30808782577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453237533569</t>
+    <t xml:space="preserve">2.30808758735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453261375427</t>
   </si>
   <si>
     <t xml:space="preserve">2.21926951408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19558453559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2109797000885</t>
+    <t xml:space="preserve">2.19558501243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21097993850708</t>
   </si>
   <si>
     <t xml:space="preserve">2.18137407302856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1458466053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13637280464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10913515090942</t>
+    <t xml:space="preserve">2.14584684371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13637256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10913491249084</t>
   </si>
   <si>
     <t xml:space="preserve">2.14110946655273</t>
@@ -1040,34 +1040,34 @@
     <t xml:space="preserve">2.14229369163513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16360998153687</t>
+    <t xml:space="preserve">2.16361021995544</t>
   </si>
   <si>
     <t xml:space="preserve">2.18611073493958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13874101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11979293823242</t>
+    <t xml:space="preserve">2.13874077796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.119793176651</t>
   </si>
   <si>
     <t xml:space="preserve">2.1493992805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13755679130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1659791469574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15532088279724</t>
+    <t xml:space="preserve">2.13755702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16597890853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15532064437866</t>
   </si>
   <si>
     <t xml:space="preserve">2.20032167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18374228477478</t>
+    <t xml:space="preserve">2.1837420463562</t>
   </si>
   <si>
     <t xml:space="preserve">2.23821759223938</t>
@@ -1076,31 +1076,31 @@
     <t xml:space="preserve">2.27374458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39453744888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3838791847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34835171699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36848425865173</t>
+    <t xml:space="preserve">2.39453721046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38387942314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34835195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36848402023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.37322092056274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36966800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38032627105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38861608505249</t>
+    <t xml:space="preserve">2.36966824531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37203645706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38032650947571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38861632347107</t>
   </si>
   <si>
     <t xml:space="preserve">2.34361481666565</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">2.30927205085754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28913998603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29387664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058857917786</t>
+    <t xml:space="preserve">2.28913974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2938768863678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3305881023407</t>
   </si>
   <si>
     <t xml:space="preserve">2.34953618049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36019444465637</t>
+    <t xml:space="preserve">2.36019468307495</t>
   </si>
   <si>
     <t xml:space="preserve">2.31637740135193</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.31756162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34006190299988</t>
+    <t xml:space="preserve">2.34006214141846</t>
   </si>
   <si>
     <t xml:space="preserve">2.40401124954224</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">2.40993285179138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37914252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35545706748962</t>
+    <t xml:space="preserve">2.37914228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3554573059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.31045627593994</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.23111200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22163820266724</t>
+    <t xml:space="preserve">2.22163844108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.19676899909973</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">2.18847942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18492650985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163566589355</t>
+    <t xml:space="preserve">2.18492698669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163542747498</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005730628967</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">2.15058374404907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16834712028503</t>
+    <t xml:space="preserve">2.16834735870361</t>
   </si>
   <si>
     <t xml:space="preserve">2.13045144081116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12097764015198</t>
+    <t xml:space="preserve">2.1209774017334</t>
   </si>
   <si>
     <t xml:space="preserve">2.11031913757324</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.29624533653259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28795599937439</t>
+    <t xml:space="preserve">2.28795552253723</t>
   </si>
   <si>
     <t xml:space="preserve">2.25005984306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25834965705872</t>
+    <t xml:space="preserve">2.25834941864014</t>
   </si>
   <si>
     <t xml:space="preserve">2.24413871765137</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">2.22755932807922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22637486457825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23703336715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24769139289856</t>
+    <t xml:space="preserve">2.22637510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2370331287384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24769115447998</t>
   </si>
   <si>
     <t xml:space="preserve">2.2926926612854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3211145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25716543197632</t>
+    <t xml:space="preserve">2.32111430168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25716495513916</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137613296509</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">2.3187460899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27848172187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26663947105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28321862220764</t>
+    <t xml:space="preserve">2.27848148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2666392326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28321838378906</t>
   </si>
   <si>
     <t xml:space="preserve">2.32703566551208</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">2.34598350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30571913719177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27729773521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203186035156</t>
+    <t xml:space="preserve">2.30571937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27729749679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742726325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203233718872</t>
   </si>
   <si>
     <t xml:space="preserve">2.1482150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19795322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20979619026184</t>
+    <t xml:space="preserve">2.19795346260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20979571342468</t>
   </si>
   <si>
     <t xml:space="preserve">2.19913744926453</t>
@@ -1301,34 +1301,34 @@
     <t xml:space="preserve">2.23348069190979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23584890365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28085041046143</t>
+    <t xml:space="preserve">2.23584914207458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28085017204285</t>
   </si>
   <si>
     <t xml:space="preserve">2.26900768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24177026748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361275672913</t>
+    <t xml:space="preserve">2.27256083488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24177050590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361251831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.27019214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26308655738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677129745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032397270203</t>
+    <t xml:space="preserve">2.26308679580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677153587341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032421112061</t>
   </si>
   <si>
     <t xml:space="preserve">2.30098223686218</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">2.33177256584167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32821989059448</t>
+    <t xml:space="preserve">2.3282196521759</t>
   </si>
   <si>
     <t xml:space="preserve">2.31519317626953</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">2.41585350036621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41940665245056</t>
+    <t xml:space="preserve">2.41940641403198</t>
   </si>
   <si>
     <t xml:space="preserve">2.4371702671051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48098683357239</t>
+    <t xml:space="preserve">2.48098707199097</t>
   </si>
   <si>
     <t xml:space="preserve">2.53309345245361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5674364566803</t>
+    <t xml:space="preserve">2.56743693351746</t>
   </si>
   <si>
     <t xml:space="preserve">2.54612064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56151556968689</t>
+    <t xml:space="preserve">2.56151580810547</t>
   </si>
   <si>
     <t xml:space="preserve">2.57572650909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5686206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57691073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56980562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56625270843506</t>
+    <t xml:space="preserve">2.56862092018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57691097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56980538368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56625247001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.63967561721802</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">2.65743899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66691303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63671517372131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62960934638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58105564117432</t>
+    <t xml:space="preserve">2.66691327095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63671493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62960958480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58105540275574</t>
   </si>
   <si>
     <t xml:space="preserve">2.57158184051514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56921339035034</t>
+    <t xml:space="preserve">2.56921315193176</t>
   </si>
   <si>
     <t xml:space="preserve">2.48039507865906</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">2.53013300895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45611763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217105865479</t>
+    <t xml:space="preserve">2.45611786842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217153549194</t>
   </si>
   <si>
     <t xml:space="preserve">2.44605207443237</t>
@@ -1430,31 +1430,31 @@
     <t xml:space="preserve">2.42236709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4709210395813</t>
+    <t xml:space="preserve">2.47092080116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.45552563667297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44723629951477</t>
+    <t xml:space="preserve">2.44723653793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.46559166908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388124465942</t>
+    <t xml:space="preserve">2.47388172149658</t>
   </si>
   <si>
     <t xml:space="preserve">2.41881465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40934014320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43480181694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756392478943</t>
+    <t xml:space="preserve">2.40934038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43480157852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40756440162659</t>
   </si>
   <si>
     <t xml:space="preserve">2.3264434337616</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">2.35190439224243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39631366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37440514564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35782599449158</t>
+    <t xml:space="preserve">2.39631414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37440538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35782623291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38624787330627</t>
+    <t xml:space="preserve">2.36611580848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38624811172485</t>
   </si>
   <si>
     <t xml:space="preserve">2.39986658096313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32881236076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35249662399292</t>
+    <t xml:space="preserve">2.32881212234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35249710083008</t>
   </si>
   <si>
     <t xml:space="preserve">2.34302282333374</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39809012413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38565564155579</t>
+    <t xml:space="preserve">2.39809036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38565540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.4123010635376</t>
@@ -1514,61 +1514,61 @@
     <t xml:space="preserve">2.41822242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45078921318054</t>
+    <t xml:space="preserve">2.45078897476196</t>
   </si>
   <si>
     <t xml:space="preserve">2.51769852638245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51355361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54315972328186</t>
+    <t xml:space="preserve">2.51355385780334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315996170044</t>
   </si>
   <si>
     <t xml:space="preserve">2.54079127311707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54375219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756899833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61066150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58223938941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59408211708069</t>
+    <t xml:space="preserve">2.54375195503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61066126823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58223986625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59408235549927</t>
   </si>
   <si>
     <t xml:space="preserve">2.61480617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493847846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65803146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64204382896423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67164993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6752028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58638501167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60178017616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55855536460876</t>
+    <t xml:space="preserve">2.63493824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65803122520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64204406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67165017127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67520260810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58638477325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60177993774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55855512619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.57039761543274</t>
@@ -1580,70 +1580,70 @@
     <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51059341430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54967284202576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48868465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49672627449036</t>
+    <t xml:space="preserve">2.51059317588806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54967355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48868489265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49672651290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.48621010780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43548369407654</t>
+    <t xml:space="preserve">2.4354841709137</t>
   </si>
   <si>
     <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.387850522995</t>
+    <t xml:space="preserve">2.38785028457642</t>
   </si>
   <si>
     <t xml:space="preserve">2.3773341178894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25917863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176090240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361132621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33465003967285</t>
+    <t xml:space="preserve">2.25917840003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176114082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33464956283569</t>
   </si>
   <si>
     <t xml:space="preserve">2.28577923774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23752737045288</t>
+    <t xml:space="preserve">2.23752760887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.22577357292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23567175865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020083427429</t>
+    <t xml:space="preserve">2.23567128181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020035743713</t>
   </si>
   <si>
     <t xml:space="preserve">2.2498996257782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23196005821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23938274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371314048767</t>
+    <t xml:space="preserve">2.2319598197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23938298225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371361732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.20041036605835</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">2.20968961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22329902648926</t>
+    <t xml:space="preserve">2.22329926490784</t>
   </si>
   <si>
     <t xml:space="preserve">2.20721530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1552517414093</t>
+    <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298720359802</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">2.0587477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05379867553711</t>
+    <t xml:space="preserve">2.05379891395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843570709229</t>
@@ -1679,31 +1679,31 @@
     <t xml:space="preserve">2.04699397087097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04946851730347</t>
+    <t xml:space="preserve">2.04946875572205</t>
   </si>
   <si>
     <t xml:space="preserve">2.0921528339386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11689782142639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10143232345581</t>
+    <t xml:space="preserve">2.11689758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
     <t xml:space="preserve">2.1410231590271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11813473701477</t>
+    <t xml:space="preserve">2.11813497543335</t>
   </si>
   <si>
     <t xml:space="preserve">2.08906006813049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06864595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09091544151306</t>
+    <t xml:space="preserve">2.0686457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09091591835022</t>
   </si>
   <si>
     <t xml:space="preserve">2.10638093948364</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">2.14349770545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13793015480042</t>
+    <t xml:space="preserve">2.13793063163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.12122774124146</t>
@@ -1724,76 +1724,76 @@
     <t xml:space="preserve">2.09957647323608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11380457878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14473509788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18061470985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1651496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20102906227112</t>
+    <t xml:space="preserve">2.11380434036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14473533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18061494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16514921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20102882385254</t>
   </si>
   <si>
     <t xml:space="preserve">2.09029722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916754722595</t>
+    <t xml:space="preserve">2.1243212223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916778564453</t>
   </si>
   <si>
     <t xml:space="preserve">2.1199905872345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07730603218079</t>
+    <t xml:space="preserve">2.07730627059937</t>
   </si>
   <si>
     <t xml:space="preserve">2.07235717773438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11937212944031</t>
+    <t xml:space="preserve">2.11937236785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.20474052429199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28392338752747</t>
+    <t xml:space="preserve">2.28392314910889</t>
   </si>
   <si>
     <t xml:space="preserve">2.23319697380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19174981117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24309468269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26289081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2529923915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26969504356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711892127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25608587265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24185752868652</t>
+    <t xml:space="preserve">2.19174957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24309492111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26289057731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25299263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26969480514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25608563423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2418577671051</t>
   </si>
   <si>
     <t xml:space="preserve">2.19917321205139</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">2.22206211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27526259422302</t>
+    <t xml:space="preserve">2.2752628326416</t>
   </si>
   <si>
     <t xml:space="preserve">2.32846331596375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31485414505005</t>
+    <t xml:space="preserve">2.31485390663147</t>
   </si>
   <si>
     <t xml:space="preserve">2.3142352104187</t>
@@ -1820,85 +1820,85 @@
     <t xml:space="preserve">2.33712434768677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3383617401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33403134346008</t>
+    <t xml:space="preserve">2.33836150169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3340311050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.3600127696991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40145969390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4163064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41445088386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42063736915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45589804649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44352602958679</t>
+    <t xml:space="preserve">2.40146017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41630673408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41445112228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4206371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45589828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44352579116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.47012639045715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48682856559753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50600552558899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37300372123718</t>
+    <t xml:space="preserve">2.48682904243469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50600576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37300395965576</t>
   </si>
   <si>
     <t xml:space="preserve">2.367436170578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30743074417114</t>
+    <t xml:space="preserve">2.30743098258972</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795257568359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36496162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27093267440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28083038330078</t>
+    <t xml:space="preserve">2.36496186256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27093243598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808301448822</t>
   </si>
   <si>
     <t xml:space="preserve">2.19793581962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19855427742004</t>
+    <t xml:space="preserve">2.19855451583862</t>
   </si>
   <si>
     <t xml:space="preserve">2.20907115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18308925628662</t>
+    <t xml:space="preserve">2.1830894947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.17504715919495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19979190826416</t>
+    <t xml:space="preserve">2.19979166984558</t>
   </si>
   <si>
     <t xml:space="preserve">2.16824269294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15648889541626</t>
+    <t xml:space="preserve">2.15648865699768</t>
   </si>
   <si>
     <t xml:space="preserve">2.09772062301636</t>
@@ -1913,31 +1913,31 @@
     <t xml:space="preserve">2.1966986656189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17381000518799</t>
+    <t xml:space="preserve">2.17381024360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.21525716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24247622489929</t>
+    <t xml:space="preserve">2.24247646331787</t>
   </si>
   <si>
     <t xml:space="preserve">2.24433207511902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2474250793457</t>
+    <t xml:space="preserve">2.24742531776428</t>
   </si>
   <si>
     <t xml:space="preserve">2.25979733467102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33217525482178</t>
+    <t xml:space="preserve">2.33217549324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.34949636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26598381996155</t>
+    <t xml:space="preserve">2.26598358154297</t>
   </si>
   <si>
     <t xml:space="preserve">2.26227188110352</t>
@@ -1949,19 +1949,19 @@
     <t xml:space="preserve">2.22701096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20412182807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15834498405457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13731169700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443388938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22639226913452</t>
+    <t xml:space="preserve">2.2041220664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15834522247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1373119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2344343662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22639203071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949093818665</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">2.23381567001343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15277695655823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16947984695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15401434898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18556356430054</t>
+    <t xml:space="preserve">2.15277719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16947960853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15401458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18556380271912</t>
   </si>
   <si>
     <t xml:space="preserve">2.21278285980225</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17628479003906</t>
+    <t xml:space="preserve">2.1762843132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.14040470123291</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">2.27959299087524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3241331577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31794714927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35073375701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38846921920776</t>
+    <t xml:space="preserve">2.32413291931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31794691085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35073351860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846898078918</t>
   </si>
   <si>
     <t xml:space="preserve">2.41012048721313</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32227778434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37424087524414</t>
+    <t xml:space="preserve">2.32227754592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37424111366272</t>
   </si>
   <si>
     <t xml:space="preserve">2.41259503364563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43424654006958</t>
+    <t xml:space="preserve">2.43424677848816</t>
   </si>
   <si>
     <t xml:space="preserve">2.44971179962158</t>
@@ -2042,46 +2042,46 @@
     <t xml:space="preserve">2.45342350006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54930877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5511646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260588645935</t>
+    <t xml:space="preserve">2.54930853843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55116486549377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260612487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.47321915626526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136330604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50043845176697</t>
+    <t xml:space="preserve">2.47136354446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50043821334839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5152850151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52394533157349</t>
+    <t xml:space="preserve">2.52394556999207</t>
   </si>
   <si>
     <t xml:space="preserve">2.46208429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32908225059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36125016212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42620444297791</t>
+    <t xml:space="preserve">2.32908201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36124992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42620468139648</t>
   </si>
   <si>
     <t xml:space="preserve">2.4410514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609696388245</t>
+    <t xml:space="preserve">2.37609672546387</t>
   </si>
   <si>
     <t xml:space="preserve">2.45713520050049</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">2.45094919204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47507500648499</t>
+    <t xml:space="preserve">2.47507524490356</t>
   </si>
   <si>
     <t xml:space="preserve">2.46579599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47569346427917</t>
+    <t xml:space="preserve">2.47569370269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.49054050445557</t>
@@ -2105,52 +2105,52 @@
     <t xml:space="preserve">2.48188018798828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47878646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49548935890198</t>
+    <t xml:space="preserve">2.47878670692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49548959732056</t>
   </si>
   <si>
     <t xml:space="preserve">2.50662422180176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5288941860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53446221351624</t>
+    <t xml:space="preserve">2.52889442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53446197509766</t>
   </si>
   <si>
     <t xml:space="preserve">2.50786161422729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5530207157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601095199585</t>
+    <t xml:space="preserve">2.55302047729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601119041443</t>
   </si>
   <si>
     <t xml:space="preserve">2.58147668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64952445030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68292951583862</t>
+    <t xml:space="preserve">2.64952421188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6829297542572</t>
   </si>
   <si>
     <t xml:space="preserve">2.69901323318481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69220876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68231058120728</t>
+    <t xml:space="preserve">2.69220900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68231105804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.66870141029358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67179441452026</t>
+    <t xml:space="preserve">2.67179417610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.69282722473145</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">2.86109042167664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85057401657104</t>
+    <t xml:space="preserve">2.85057353973389</t>
   </si>
   <si>
     <t xml:space="preserve">2.79799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75716280937195</t>
+    <t xml:space="preserve">2.75716304779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.76025605201721</t>
@@ -2192,28 +2192,28 @@
     <t xml:space="preserve">2.78500056266785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78995013237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83943891525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8388204574585</t>
+    <t xml:space="preserve">2.78994965553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82088017463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83943867683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83881974220276</t>
   </si>
   <si>
     <t xml:space="preserve">2.79737305641174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81160092353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78685688972473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922866821289</t>
+    <t xml:space="preserve">2.81160116195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78685712814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922890663147</t>
   </si>
   <si>
     <t xml:space="preserve">2.80603361129761</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">2.81778717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79551720619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74417209625244</t>
+    <t xml:space="preserve">2.7955174446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74417233467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.65694761276245</t>
@@ -2237,28 +2237,28 @@
     <t xml:space="preserve">2.59137463569641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69097137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66560816764832</t>
+    <t xml:space="preserve">2.6909716129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66560792922974</t>
   </si>
   <si>
     <t xml:space="preserve">2.73056268692017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79984760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76334953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7504575252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75625872612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79106664657593</t>
+    <t xml:space="preserve">2.79984736442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76334929466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75045776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75625848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79106640815735</t>
   </si>
   <si>
     <t xml:space="preserve">2.68084192276001</t>
@@ -2270,46 +2270,46 @@
     <t xml:space="preserve">2.72596311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68148612976074</t>
+    <t xml:space="preserve">2.68148636817932</t>
   </si>
   <si>
     <t xml:space="preserve">2.62863063812256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65892577171326</t>
+    <t xml:space="preserve">2.65892601013184</t>
   </si>
   <si>
     <t xml:space="preserve">2.66279363632202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63443183898926</t>
+    <t xml:space="preserve">2.63443160057068</t>
   </si>
   <si>
     <t xml:space="preserve">2.68664336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66666126251221</t>
+    <t xml:space="preserve">2.66666102409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.65183544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68857717514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69437837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68986630439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72016143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69695663452148</t>
+    <t xml:space="preserve">2.66472744941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6885769367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72016167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69695687294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.65248012542725</t>
@@ -2318,178 +2318,178 @@
     <t xml:space="preserve">2.69953513145447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75303554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73563170433044</t>
+    <t xml:space="preserve">2.7530357837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73563194274902</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176455497742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76205968856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75883722305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79428958892822</t>
+    <t xml:space="preserve">2.76205992698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75883746147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7942898273468</t>
   </si>
   <si>
     <t xml:space="preserve">2.76077079772949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79944610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82007312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86197137832642</t>
+    <t xml:space="preserve">2.79944634437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.820072889328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86197113990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.91160464286804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90773677825928</t>
+    <t xml:space="preserve">2.90773725509644</t>
   </si>
   <si>
     <t xml:space="preserve">2.89162230491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89484548568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414710044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.974773645401</t>
+    <t xml:space="preserve">2.89484524726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414757728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97477388381958</t>
   </si>
   <si>
     <t xml:space="preserve">2.96832823753357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97541904449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98702120780945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96897268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735238075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91805028915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04181122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02118396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03665447235107</t>
+    <t xml:space="preserve">2.97541880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98702144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9689724445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735261917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91805005073547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04181146621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02118444442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0366542339325</t>
   </si>
   <si>
     <t xml:space="preserve">3.03923296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04825687408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829243659973</t>
+    <t xml:space="preserve">3.04825758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829267501831</t>
   </si>
   <si>
     <t xml:space="preserve">2.97155117988586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98895525932312</t>
+    <t xml:space="preserve">2.98895573616028</t>
   </si>
   <si>
     <t xml:space="preserve">2.90902614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86003756523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84263348579407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78655409812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76592755317688</t>
+    <t xml:space="preserve">2.86003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84263324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78655457496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76592707633972</t>
   </si>
   <si>
     <t xml:space="preserve">2.83812141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7343430519104</t>
+    <t xml:space="preserve">2.73434281349182</t>
   </si>
   <si>
     <t xml:space="preserve">2.78010869026184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84843492507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87421846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95608067512512</t>
+    <t xml:space="preserve">2.84843516349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87421822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95608115196228</t>
   </si>
   <si>
     <t xml:space="preserve">2.94770121574402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91869497299194</t>
+    <t xml:space="preserve">2.91869473457336</t>
   </si>
   <si>
     <t xml:space="preserve">2.91676139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94705700874329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91031527519226</t>
+    <t xml:space="preserve">2.94705677032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91031551361084</t>
   </si>
   <si>
     <t xml:space="preserve">2.9651050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94576811790466</t>
+    <t xml:space="preserve">2.9457676410675</t>
   </si>
   <si>
     <t xml:space="preserve">2.94125556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94383406639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97606325149536</t>
+    <t xml:space="preserve">2.94383382797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97606372833252</t>
   </si>
   <si>
     <t xml:space="preserve">2.9547917842865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801496505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98959946632385</t>
+    <t xml:space="preserve">2.95801448822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98959970474243</t>
   </si>
   <si>
     <t xml:space="preserve">3.05921506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11013746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10884809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.080486536026</t>
+    <t xml:space="preserve">3.11013770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10884833335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08048629760742</t>
   </si>
   <si>
     <t xml:space="preserve">3.11464953422546</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">3.10240268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09853506088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06372737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10175776481628</t>
+    <t xml:space="preserve">3.09853482246399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06372761726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10175800323486</t>
   </si>
   <si>
     <t xml:space="preserve">3.12431859970093</t>
@@ -2513,40 +2513,40 @@
     <t xml:space="preserve">3.1494574546814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661890983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05663704872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698588371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08757710456848</t>
+    <t xml:space="preserve">3.13592123985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05663681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696822166443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08757662773132</t>
   </si>
   <si>
     <t xml:space="preserve">3.12560796737671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19071078300476</t>
+    <t xml:space="preserve">3.19071102142334</t>
   </si>
   <si>
     <t xml:space="preserve">3.15396976470947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15010237693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17781925201416</t>
+    <t xml:space="preserve">3.15010190010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17781901359558</t>
   </si>
   <si>
     <t xml:space="preserve">3.20553660392761</t>
@@ -2558,64 +2558,64 @@
     <t xml:space="preserve">3.22165131568909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21262693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23325395584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001311302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21391582489014</t>
+    <t xml:space="preserve">3.21262717247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23325371742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21391677856445</t>
   </si>
   <si>
     <t xml:space="preserve">3.23969984054565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26548337936401</t>
+    <t xml:space="preserve">3.26548361778259</t>
   </si>
   <si>
     <t xml:space="preserve">3.24743485450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22229623794556</t>
+    <t xml:space="preserve">3.22229599952698</t>
   </si>
   <si>
     <t xml:space="preserve">3.25388050079346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28739905357361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447243690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185813903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3995578289032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4111602306366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43307590484619</t>
+    <t xml:space="preserve">3.28739953041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447219848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185790061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39955735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41116046905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43307638168335</t>
   </si>
   <si>
     <t xml:space="preserve">3.49108934402466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47304034233093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43823266029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45370292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311194419861</t>
+    <t xml:space="preserve">3.47304081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823313713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4537034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311170578003</t>
   </si>
   <si>
     <t xml:space="preserve">3.40600347518921</t>
@@ -2624,22 +2624,22 @@
     <t xml:space="preserve">3.41631722450256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4150276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.413738489151</t>
+    <t xml:space="preserve">3.41502785682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41373872756958</t>
   </si>
   <si>
     <t xml:space="preserve">3.44596815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40987086296082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34541249275208</t>
+    <t xml:space="preserve">3.40987062454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920851707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3454122543335</t>
   </si>
   <si>
     <t xml:space="preserve">3.32994246482849</t>
@@ -2648,16 +2648,16 @@
     <t xml:space="preserve">3.389244556427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38795518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34799075126648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29126715660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192902565002</t>
+    <t xml:space="preserve">3.38795495033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34799003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29126691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2719292640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.32865333557129</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">3.36861729621887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43049812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43694353103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42405152320862</t>
+    <t xml:space="preserve">3.43049764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43694376945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42405200004578</t>
   </si>
   <si>
     <t xml:space="preserve">3.42147350311279</t>
@@ -2684,58 +2684,58 @@
     <t xml:space="preserve">3.45499229431152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37635254859924</t>
+    <t xml:space="preserve">3.37635231018066</t>
   </si>
   <si>
     <t xml:space="preserve">3.29513430595398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032614707947</t>
+    <t xml:space="preserve">3.35572528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032662391663</t>
   </si>
   <si>
     <t xml:space="preserve">3.22938680648804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30544757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33252096176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576132774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841071128845</t>
+    <t xml:space="preserve">3.30544710159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3325207233429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576108932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841094970703</t>
   </si>
   <si>
     <t xml:space="preserve">3.1475236415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18490982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006657600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815066337585</t>
+    <t xml:space="preserve">3.18491005897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815042495728</t>
   </si>
   <si>
     <t xml:space="preserve">3.17395162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13205409049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09982466697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12238454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04890203475952</t>
+    <t xml:space="preserve">3.1320538520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09982419013977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12238478660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04890179634094</t>
   </si>
   <si>
     <t xml:space="preserve">3.11593890190125</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">3.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02182936668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96703934669495</t>
+    <t xml:space="preserve">3.02182912826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96703958511353</t>
   </si>
   <si>
     <t xml:space="preserve">3.00958204269409</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">3.04310059547424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09466743469238</t>
+    <t xml:space="preserve">3.09466767311096</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848183631897</t>
+    <t xml:space="preserve">3.15848159790039</t>
   </si>
   <si>
     <t xml:space="preserve">3.18297624588013</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">3.54394555091858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4756190776825</t>
+    <t xml:space="preserve">3.47561955451965</t>
   </si>
   <si>
     <t xml:space="preserve">3.39440107345581</t>
@@ -2786,61 +2786,61 @@
     <t xml:space="preserve">3.17459654808044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14236688613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01409387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88582110404968</t>
+    <t xml:space="preserve">3.1423671245575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01409411430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8858208656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.7427225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70017957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610536575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51969504356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24896788597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1593701839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17741870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646706581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88993239402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76617133617401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68817627429962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500655651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91313767433167</t>
+    <t xml:space="preserve">2.70017981529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610512733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51969480514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24896836280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17741847038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646694660187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88993215560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7661714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68817615509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62500643730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9131373167038</t>
   </si>
   <si>
     <t xml:space="preserve">1.77261734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83965444564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93827641010284</t>
+    <t xml:space="preserve">1.83965456485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93827664852142</t>
   </si>
   <si>
     <t xml:space="preserve">1.94149947166443</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">2.04141068458557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90669178962708</t>
+    <t xml:space="preserve">1.90669167041779</t>
   </si>
   <si>
     <t xml:space="preserve">1.94923460483551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02013921737671</t>
+    <t xml:space="preserve">2.02013897895813</t>
   </si>
   <si>
     <t xml:space="preserve">2.05236864089966</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">1.98662066459656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11295986175537</t>
+    <t xml:space="preserve">2.11296010017395</t>
   </si>
   <si>
     <t xml:space="preserve">2.12327313423157</t>
@@ -2873,28 +2873,28 @@
     <t xml:space="preserve">2.06912779808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04850101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09104371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92087256908417</t>
+    <t xml:space="preserve">2.04850077629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0910439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278872013092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92087268829346</t>
   </si>
   <si>
     <t xml:space="preserve">1.93892109394073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90282392501831</t>
+    <t xml:space="preserve">1.90282380580902</t>
   </si>
   <si>
     <t xml:space="preserve">1.83063018321991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89766752719879</t>
+    <t xml:space="preserve">1.89766728878021</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379990100861</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">1.99693393707275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06010365486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05623602867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0265851020813</t>
+    <t xml:space="preserve">2.06010389328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05623626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02658486366272</t>
   </si>
   <si>
     <t xml:space="preserve">2.02529573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04463315010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04721212387085</t>
+    <t xml:space="preserve">2.04463362693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04721188545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.05752515792847</t>
@@ -2927,22 +2927,22 @@
     <t xml:space="preserve">2.01627159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01756072044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97243988513947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32651400566101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22702980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21850228309631</t>
+    <t xml:space="preserve">2.01756048202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790991306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97243964672089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32651376724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22702956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
     <t xml:space="preserve">2.17018151283264</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">2.21992373466492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28387784957886</t>
+    <t xml:space="preserve">2.28387808799744</t>
   </si>
   <si>
     <t xml:space="preserve">2.27535057067871</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">2.24266290664673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25687527656555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39046859741211</t>
+    <t xml:space="preserve">2.25687503814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39046835899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.46863460540771</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63633704185486</t>
+    <t xml:space="preserve">2.63633728027344</t>
   </si>
   <si>
     <t xml:space="preserve">2.61644005775452</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">2.56669807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48995280265808</t>
+    <t xml:space="preserve">2.48995304107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.37909889221191</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">2.38336229324341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38762617111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47005605697632</t>
+    <t xml:space="preserve">2.38762593269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47005581855774</t>
   </si>
   <si>
     <t xml:space="preserve">2.44873809814453</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">2.44021081924438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40325951576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41889262199402</t>
+    <t xml:space="preserve">2.40325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4188928604126</t>
   </si>
   <si>
     <t xml:space="preserve">2.42457723617554</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">2.43310499191284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53258872032166</t>
+    <t xml:space="preserve">2.53258895874023</t>
   </si>
   <si>
     <t xml:space="preserve">2.53116798400879</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">2.55817079544067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57238268852234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58090996742249</t>
+    <t xml:space="preserve">2.57238292694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58091020584106</t>
   </si>
   <si>
     <t xml:space="preserve">2.51127076148987</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">2.53685259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56527662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60933423042297</t>
+    <t xml:space="preserve">2.5652768611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60933399200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.64202189445496</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">2.63207340240479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65481281280518</t>
+    <t xml:space="preserve">2.65481305122375</t>
   </si>
   <si>
     <t xml:space="preserve">2.67755198478699</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642457485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64770674705505</t>
+    <t xml:space="preserve">2.76424551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64770698547363</t>
   </si>
   <si>
     <t xml:space="preserve">2.61501908302307</t>
@@ -3089,37 +3089,37 @@
     <t xml:space="preserve">2.4572651386261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54680109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66049766540527</t>
+    <t xml:space="preserve">2.54680132865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186713218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66049742698669</t>
   </si>
   <si>
     <t xml:space="preserve">2.68465828895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7528760433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89073276519775</t>
+    <t xml:space="preserve">2.75287580490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89073300361633</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768430709839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89641809463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92199945449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86373019218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83388447761536</t>
+    <t xml:space="preserve">2.89641785621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92199969291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86373043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83388471603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.88931179046631</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">2.84951829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84099054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9177360534668</t>
+    <t xml:space="preserve">2.84099078178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91773581504822</t>
   </si>
   <si>
     <t xml:space="preserve">2.93479037284851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95895099639893</t>
+    <t xml:space="preserve">2.95895075798035</t>
   </si>
   <si>
     <t xml:space="preserve">2.94616007804871</t>
@@ -3149,22 +3149,22 @@
     <t xml:space="preserve">2.87083601951599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88789057731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8537814617157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81256651878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78556370735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90068125724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87794256210327</t>
+    <t xml:space="preserve">2.88789033889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85378122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81256628036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78556394577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90068101882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87794208526611</t>
   </si>
   <si>
     <t xml:space="preserve">2.94189620018005</t>
@@ -3173,31 +3173,31 @@
     <t xml:space="preserve">2.95184469223022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95753002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93621158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91489362716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85662412643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70313382148743</t>
+    <t xml:space="preserve">2.95752954483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93621134757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91489386558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85662436485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70313405990601</t>
   </si>
   <si>
     <t xml:space="preserve">2.74861216545105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6960277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70455479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6576554775238</t>
+    <t xml:space="preserve">2.69602799415588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70455503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65765523910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.72729420661926</t>
@@ -3212,10 +3212,10 @@
     <t xml:space="preserve">2.64912796020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.610755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68039464950562</t>
+    <t xml:space="preserve">2.61075520515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68039441108704</t>
   </si>
   <si>
     <t xml:space="preserve">2.62354612350464</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">2.50274395942688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48853182792664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49705862998962</t>
+    <t xml:space="preserve">2.48853158950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.52690410614014</t>
@@ -3251,19 +3251,19 @@
     <t xml:space="preserve">2.42741990089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39899587631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25403237342834</t>
+    <t xml:space="preserve">2.39899563789368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199282646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25403261184692</t>
   </si>
   <si>
     <t xml:space="preserve">2.23129343986511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276616096497</t>
+    <t xml:space="preserve">2.22276592254639</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">2.52264046669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52832531929016</t>
+    <t xml:space="preserve">2.52832508087158</t>
   </si>
   <si>
     <t xml:space="preserve">2.55532836914062</t>
@@ -3293,40 +3293,40 @@
     <t xml:space="preserve">2.76850914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74008512496948</t>
+    <t xml:space="preserve">2.74008464813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.84383296966553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83672738075256</t>
+    <t xml:space="preserve">2.83672714233398</t>
   </si>
   <si>
     <t xml:space="preserve">2.97174167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81967234611511</t>
+    <t xml:space="preserve">2.93052697181702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920853614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81967258453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.80972409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78840589523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78130006790161</t>
+    <t xml:space="preserve">2.78840613365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78129982948303</t>
   </si>
   <si>
     <t xml:space="preserve">2.78272128105164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77561521530151</t>
+    <t xml:space="preserve">2.77561497688293</t>
   </si>
   <si>
     <t xml:space="preserve">2.70597624778748</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">2.72871518135071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75429725646973</t>
+    <t xml:space="preserve">2.75429701805115</t>
   </si>
   <si>
     <t xml:space="preserve">2.75571823120117</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">2.79266977310181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77419424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77845764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7571394443512</t>
+    <t xml:space="preserve">2.77419400215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77845788002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75713920593262</t>
   </si>
   <si>
     <t xml:space="preserve">2.83246350288391</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">2.86088752746582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8594663143158</t>
+    <t xml:space="preserve">2.85946655273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.91347217559814</t>
@@ -3386,19 +3386,19 @@
     <t xml:space="preserve">2.84241199493408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76993036270142</t>
+    <t xml:space="preserve">2.76993012428284</t>
   </si>
   <si>
     <t xml:space="preserve">2.74719095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79551243782043</t>
+    <t xml:space="preserve">2.79551219940186</t>
   </si>
   <si>
     <t xml:space="preserve">2.67897343635559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68181586265564</t>
+    <t xml:space="preserve">2.68181562423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.745769739151</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">2.64344310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57522511482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.644864320755</t>
+    <t xml:space="preserve">2.57522535324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64486455917358</t>
   </si>
   <si>
     <t xml:space="preserve">2.80546045303345</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">2.94758105278015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13233780860901</t>
+    <t xml:space="preserve">3.13233804702759</t>
   </si>
   <si>
     <t xml:space="preserve">3.10533499717712</t>
@@ -3431,19 +3431,19 @@
     <t xml:space="preserve">3.18350124359131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1493923664093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13944387435913</t>
+    <t xml:space="preserve">3.14939284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13944435119629</t>
   </si>
   <si>
     <t xml:space="preserve">3.15791940689087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12665295600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03995966911316</t>
+    <t xml:space="preserve">3.12665343284607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.039959192276</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742652893066</t>
@@ -3461,22 +3461,22 @@
     <t xml:space="preserve">3.13375902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11812591552734</t>
+    <t xml:space="preserve">3.11812615394592</t>
   </si>
   <si>
     <t xml:space="preserve">3.0584352016449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19344997406006</t>
+    <t xml:space="preserve">3.19344973564148</t>
   </si>
   <si>
     <t xml:space="preserve">3.16928935050964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2119255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2517192363739</t>
+    <t xml:space="preserve">3.21192574501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25171899795532</t>
   </si>
   <si>
     <t xml:space="preserve">3.14797115325928</t>
@@ -3485,43 +3485,43 @@
     <t xml:space="preserve">3.30004024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28867030143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435539245605</t>
+    <t xml:space="preserve">3.2886700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435586929321</t>
   </si>
   <si>
     <t xml:space="preserve">3.30146145820618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32562160491943</t>
+    <t xml:space="preserve">3.32562184333801</t>
   </si>
   <si>
     <t xml:space="preserve">3.30572509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3526246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41942143440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36967968940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26450991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27587985992432</t>
+    <t xml:space="preserve">3.35262489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110090255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41942167282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36967921257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26450967788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27587962150574</t>
   </si>
   <si>
     <t xml:space="preserve">3.3085675239563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40947318077087</t>
+    <t xml:space="preserve">3.40947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.37962746620178</t>
@@ -3530,43 +3530,43 @@
     <t xml:space="preserve">3.38247036933899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40378832817078</t>
+    <t xml:space="preserve">3.40378785133362</t>
   </si>
   <si>
     <t xml:space="preserve">3.42013239860535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32846426963806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29790830612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272814750671</t>
+    <t xml:space="preserve">3.32846450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29790806770325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272790908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35902070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36683630943298</t>
+    <t xml:space="preserve">3.3668372631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.34978270530701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42723774909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500374794006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3220694065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28014373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29719734191895</t>
+    <t xml:space="preserve">3.42723822593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32206916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28014349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29719758033752</t>
   </si>
   <si>
     <t xml:space="preserve">3.31567335128784</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2844066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23679637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31212019920349</t>
+    <t xml:space="preserve">3.28440761566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23679661750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31212043762207</t>
   </si>
   <si>
     <t xml:space="preserve">3.27232670783997</t>
@@ -3596,31 +3596,31 @@
     <t xml:space="preserve">3.31283116340637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42226362228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48550796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47555923461914</t>
+    <t xml:space="preserve">3.42226433753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48550772666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47555899620056</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954559803009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48124432563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57575416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143901824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53027558326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49829864501953</t>
+    <t xml:space="preserve">3.48124408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57575392723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143877983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829840660095</t>
   </si>
   <si>
     <t xml:space="preserve">3.52459073066711</t>
@@ -3638,34 +3638,34 @@
     <t xml:space="preserve">3.43120431900024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41614198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44927930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4658477306366</t>
+    <t xml:space="preserve">3.41614151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44927883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48919415473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46584820747375</t>
   </si>
   <si>
     <t xml:space="preserve">3.47488474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831608772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844075202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46132874488831</t>
+    <t xml:space="preserve">3.45831632614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844122886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46132922172546</t>
   </si>
   <si>
     <t xml:space="preserve">3.4507851600647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44626688957214</t>
+    <t xml:space="preserve">3.44626641273499</t>
   </si>
   <si>
     <t xml:space="preserve">3.44099473953247</t>
@@ -3674,25 +3674,25 @@
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752388954163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36041116714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32501482963562</t>
+    <t xml:space="preserve">3.38752341270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36041069030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32501459121704</t>
   </si>
   <si>
     <t xml:space="preserve">3.24744319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27229619026184</t>
+    <t xml:space="preserve">3.27229642868042</t>
   </si>
   <si>
     <t xml:space="preserve">3.23765301704407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21129417419434</t>
+    <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
     <t xml:space="preserve">3.28359317779541</t>
@@ -3701,34 +3701,34 @@
     <t xml:space="preserve">3.21430635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24970269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279532432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062050819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37697958946228</t>
+    <t xml:space="preserve">3.24970293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279556274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37698006629944</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2948899269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2173182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30468058586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31673049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329916000366</t>
+    <t xml:space="preserve">3.29488968849182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21731901168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30468082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.316730260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329892158508</t>
   </si>
   <si>
     <t xml:space="preserve">3.32953333854675</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">3.28208637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14878535270691</t>
+    <t xml:space="preserve">3.14878511428833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19999718666077</t>
@@ -3758,52 +3758,52 @@
     <t xml:space="preserve">3.38601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37321448326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4221670627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40710425376892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38149833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42141389846802</t>
+    <t xml:space="preserve">3.37321400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42216682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4071044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38149809837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42141366004944</t>
   </si>
   <si>
     <t xml:space="preserve">3.37170791625977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36643576622009</t>
+    <t xml:space="preserve">3.36643600463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.39204216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48994731903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61797690391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60592770576477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6164710521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6533739566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981771469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078093528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63831114768982</t>
+    <t xml:space="preserve">3.48994755744934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61797738075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60592746734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65337371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63981795310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.72040152549744</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">3.6752142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66542410850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7505259513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010726928711</t>
+    <t xml:space="preserve">3.66542387008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75052618980408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010679244995</t>
   </si>
   <si>
     <t xml:space="preserve">3.77462601661682</t>
@@ -3833,55 +3833,55 @@
     <t xml:space="preserve">3.77613210678101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78215646743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76709461212158</t>
+    <t xml:space="preserve">3.78215670585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76709485054016</t>
   </si>
   <si>
     <t xml:space="preserve">3.78667569160461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73697018623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77763843536377</t>
+    <t xml:space="preserve">3.73696994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77763795852661</t>
   </si>
   <si>
     <t xml:space="preserve">3.71663570404053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71588277816772</t>
+    <t xml:space="preserve">3.71588253974915</t>
   </si>
   <si>
     <t xml:space="preserve">3.70533895492554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63755822181702</t>
+    <t xml:space="preserve">3.6375584602356</t>
   </si>
   <si>
     <t xml:space="preserve">3.68726420402527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994214057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638637542725</t>
+    <t xml:space="preserve">3.66994261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638613700867</t>
   </si>
   <si>
     <t xml:space="preserve">3.72567343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67144846916199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258104324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429177284241</t>
+    <t xml:space="preserve">3.67144894599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258080482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6413242816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429201126099</t>
   </si>
   <si>
     <t xml:space="preserve">3.75203204154968</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">3.80926918983459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74450159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625677108765</t>
+    <t xml:space="preserve">3.7445011138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8062572479248</t>
   </si>
   <si>
     <t xml:space="preserve">3.84541893005371</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">3.83939433097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717506408691</t>
+    <t xml:space="preserve">3.90717458724976</t>
   </si>
   <si>
     <t xml:space="preserve">3.88006234169006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9538676738739</t>
+    <t xml:space="preserve">3.95386815071106</t>
   </si>
   <si>
     <t xml:space="preserve">3.97947382926941</t>
@@ -3920,19 +3920,19 @@
     <t xml:space="preserve">3.94483017921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89060568809509</t>
+    <t xml:space="preserve">3.89060616493225</t>
   </si>
   <si>
     <t xml:space="preserve">3.88307476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92976784706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95682644844055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99502539634705</t>
+    <t xml:space="preserve">3.92976832389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95682597160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99502611160278</t>
   </si>
   <si>
     <t xml:space="preserve">4.01571655273438</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">3.96239686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95125555992126</t>
+    <t xml:space="preserve">3.95125532150269</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97910928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98388409614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95523428916931</t>
+    <t xml:space="preserve">3.97910904884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98388361930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95523452758789</t>
   </si>
   <si>
     <t xml:space="preserve">4.00457525253296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98070049285889</t>
+    <t xml:space="preserve">3.98070073127747</t>
   </si>
   <si>
     <t xml:space="preserve">4.0189003944397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97353863716125</t>
+    <t xml:space="preserve">3.9735381603241</t>
   </si>
   <si>
     <t xml:space="preserve">3.98706746101379</t>
@@ -3977,55 +3977,55 @@
     <t xml:space="preserve">3.92340135574341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98229265213013</t>
+    <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
     <t xml:space="preserve">4.04277467727661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98865914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9345428943634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97274255752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90907645225525</t>
+    <t xml:space="preserve">3.9886589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97274231910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90907692909241</t>
   </si>
   <si>
     <t xml:space="preserve">3.89952683448792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83984041213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66077995300293</t>
+    <t xml:space="preserve">3.83984017372131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66078019142151</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590093612671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66316771507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73638343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72524237632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70057129859924</t>
+    <t xml:space="preserve">3.66316843032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73638367652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72524189949036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70057153701782</t>
   </si>
   <si>
     <t xml:space="preserve">3.76821637153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84779834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77219486236572</t>
+    <t xml:space="preserve">3.84779858589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77219462394714</t>
   </si>
   <si>
     <t xml:space="preserve">3.76264595985413</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">3.77856230735779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74513721466064</t>
+    <t xml:space="preserve">3.74513697624207</t>
   </si>
   <si>
     <t xml:space="preserve">3.64565944671631</t>
@@ -4052,46 +4052,46 @@
     <t xml:space="preserve">3.74832081794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75150394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77697062492371</t>
+    <t xml:space="preserve">3.75150418281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77697014808655</t>
   </si>
   <si>
     <t xml:space="preserve">3.8326780796051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80641579627991</t>
+    <t xml:space="preserve">3.80641555786133</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85177755355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85973572731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93613457679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86212372779846</t>
+    <t xml:space="preserve">3.85177779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85973596572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93613481521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86212348937988</t>
   </si>
   <si>
     <t xml:space="preserve">3.87008142471313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89554786682129</t>
+    <t xml:space="preserve">3.89554762840271</t>
   </si>
   <si>
     <t xml:space="preserve">3.91146397590637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97115039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96398830413818</t>
+    <t xml:space="preserve">3.97115063667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96398854255676</t>
   </si>
   <si>
     <t xml:space="preserve">3.95443868637085</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">3.99980020523071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91942262649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76344132423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402803421021</t>
+    <t xml:space="preserve">3.91942238807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76344180107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402851104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.90748476982117</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">3.95603036880493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90430164337158</t>
+    <t xml:space="preserve">3.90430188179016</t>
   </si>
   <si>
     <t xml:space="preserve">3.94409275054932</t>
@@ -4124,16 +4124,16 @@
     <t xml:space="preserve">4.00775861740112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96796727180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8557562828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82710695266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03004169464111</t>
+    <t xml:space="preserve">3.96796822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85575675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82710719108582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03004121780396</t>
   </si>
   <si>
     <t xml:space="preserve">4.01253318786621</t>
@@ -4142,28 +4142,28 @@
     <t xml:space="preserve">4.00935029983521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99820828437805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91623878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8581440448761</t>
+    <t xml:space="preserve">3.99820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91623950004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85814428329468</t>
   </si>
   <si>
     <t xml:space="preserve">3.78094935417175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55414009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69261336326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60746002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42760491371155</t>
+    <t xml:space="preserve">3.55414032936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69261288642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60746026039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42760443687439</t>
   </si>
   <si>
     <t xml:space="preserve">3.40293383598328</t>
@@ -4181,49 +4181,49 @@
     <t xml:space="preserve">3.14429187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28913140296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39338445663452</t>
+    <t xml:space="preserve">3.28913164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39338421821594</t>
   </si>
   <si>
     <t xml:space="preserve">3.51912403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56846475601196</t>
+    <t xml:space="preserve">3.56846523284912</t>
   </si>
   <si>
     <t xml:space="preserve">3.73797488212585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69022560119629</t>
+    <t xml:space="preserve">3.69022607803345</t>
   </si>
   <si>
     <t xml:space="preserve">3.68385910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70852971076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74036192893982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90111827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90668916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92021894454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97194647789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319246292114</t>
+    <t xml:space="preserve">3.70852947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74036264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354600906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.901118516922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90668892860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92021822929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97194695472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319270133972</t>
   </si>
   <si>
     <t xml:space="preserve">3.93693065643311</t>
@@ -4235,19 +4235,19 @@
     <t xml:space="preserve">4.06346607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02845001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11758232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09848213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12235689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13349771499634</t>
+    <t xml:space="preserve">4.02844953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11758184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09848260879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12235736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1334981918335</t>
   </si>
   <si>
     <t xml:space="preserve">4.16055679321289</t>
@@ -4256,31 +4256,31 @@
     <t xml:space="preserve">4.16214799880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20193910598755</t>
+    <t xml:space="preserve">4.20193958282471</t>
   </si>
   <si>
     <t xml:space="preserve">4.21467256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716453552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13668155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14623212814331</t>
+    <t xml:space="preserve">4.1971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1541895866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599016189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13668203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14623117446899</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1939811706543</t>
+    <t xml:space="preserve">4.19398069381714</t>
   </si>
   <si>
     <t xml:space="preserve">4.17488145828247</t>
@@ -4289,43 +4289,43 @@
     <t xml:space="preserve">4.1255407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0650577545166</t>
+    <t xml:space="preserve">4.06505727767944</t>
   </si>
   <si>
     <t xml:space="preserve">4.1637396812439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26719617843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28470468521118</t>
+    <t xml:space="preserve">4.26719665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28470420837402</t>
   </si>
   <si>
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90509796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00298404693604</t>
+    <t xml:space="preserve">3.9050977230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00298357009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.00139188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12431621551514</t>
+    <t xml:space="preserve">4.12431669235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011207580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28597164154053</t>
+    <t xml:space="preserve">4.23011159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24703931808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28597116470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.25042390823364</t>
@@ -4340,13 +4340,13 @@
     <t xml:space="preserve">4.14124393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19202518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20810651779175</t>
+    <t xml:space="preserve">4.09723329544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19202566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20810604095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754560470581</t>
@@ -4355,10 +4355,10 @@
     <t xml:space="preserve">4.10738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77053785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383142471313</t>
+    <t xml:space="preserve">3.77053761482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383166313171</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4373,55 +4373,55 @@
     <t xml:space="preserve">3.71213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7730770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122760772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73075890541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65881776809692</t>
+    <t xml:space="preserve">3.77307677268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122736930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73075866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65881824493408</t>
   </si>
   <si>
     <t xml:space="preserve">3.80100655555725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70198249816895</t>
+    <t xml:space="preserve">3.70198225975037</t>
   </si>
   <si>
     <t xml:space="preserve">3.71467781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71044588088989</t>
+    <t xml:space="preserve">3.71044611930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.66982078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68082356452942</t>
+    <t xml:space="preserve">3.68082332611084</t>
   </si>
   <si>
     <t xml:space="preserve">3.69690442085266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47177243232727</t>
+    <t xml:space="preserve">3.47177267074585</t>
   </si>
   <si>
     <t xml:space="preserve">3.49123859405518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6063437461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62919545173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53355693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51324391365051</t>
+    <t xml:space="preserve">3.60634350776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62919569015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53355669975281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51324415206909</t>
   </si>
   <si>
     <t xml:space="preserve">3.48700666427612</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.33381533622742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38290452957153</t>
+    <t xml:space="preserve">3.38290429115295</t>
   </si>
   <si>
     <t xml:space="preserve">3.40406322479248</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">3.38713598251343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26356744766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25764298439026</t>
+    <t xml:space="preserve">3.26356720924377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25764274597168</t>
   </si>
   <si>
     <t xml:space="preserve">3.29657554626465</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">3.24325466156006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28134107589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005282402039</t>
+    <t xml:space="preserve">3.2813413143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005258560181</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415495872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860817909241</t>
+    <t xml:space="preserve">3.46415519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860794067383</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
@@ -4475,16 +4475,16 @@
     <t xml:space="preserve">3.56741118431091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66135716438293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64273691177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70875334739685</t>
+    <t xml:space="preserve">3.64358353614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66135692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64273715019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70875310897827</t>
   </si>
   <si>
     <t xml:space="preserve">3.70790696144104</t>
@@ -4496,34 +4496,34 @@
     <t xml:space="preserve">3.73922252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67659115791321</t>
+    <t xml:space="preserve">3.67659139633179</t>
   </si>
   <si>
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55979371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46838688850403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54625201225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50224137306213</t>
+    <t xml:space="preserve">3.5597939491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46838665008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54625225067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50224113464355</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50816559791565</t>
+    <t xml:space="preserve">3.50816583633423</t>
   </si>
   <si>
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709839820862</t>
+    <t xml:space="preserve">3.54709815979004</t>
   </si>
   <si>
     <t xml:space="preserve">3.61903882026672</t>
@@ -4532,31 +4532,31 @@
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4980092048645</t>
+    <t xml:space="preserve">3.49885582923889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800944328308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282888412476</t>
+    <t xml:space="preserve">3.70282864570618</t>
   </si>
   <si>
     <t xml:space="preserve">3.6791307926178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68336272239685</t>
+    <t xml:space="preserve">3.68336296081543</t>
   </si>
   <si>
     <t xml:space="preserve">3.69351863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70706033706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70029020309448</t>
+    <t xml:space="preserve">3.70706057548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7002899646759</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4568,16 +4568,16 @@
     <t xml:space="preserve">3.58010649681091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47515773773193</t>
+    <t xml:space="preserve">3.47515749931335</t>
   </si>
   <si>
     <t xml:space="preserve">3.44045686721802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38459730148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34735703468323</t>
+    <t xml:space="preserve">3.38459706306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34735727310181</t>
   </si>
   <si>
     <t xml:space="preserve">3.38036513328552</t>
@@ -4586,16 +4586,16 @@
     <t xml:space="preserve">3.40829515457153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52678537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4743115901947</t>
+    <t xml:space="preserve">3.52678561210632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
     <t xml:space="preserve">3.38205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34820342063904</t>
+    <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
     <t xml:space="preserve">3.3676700592041</t>
@@ -4610,25 +4610,25 @@
     <t xml:space="preserve">3.42014408111572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4243757724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43114686012268</t>
+    <t xml:space="preserve">3.42437601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43114709854126</t>
   </si>
   <si>
     <t xml:space="preserve">3.45315217971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50647306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48954606056213</t>
+    <t xml:space="preserve">3.50647330284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48954582214355</t>
   </si>
   <si>
     <t xml:space="preserve">3.55471539497375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59618759155273</t>
+    <t xml:space="preserve">3.59618735313416</t>
   </si>
   <si>
     <t xml:space="preserve">3.58433842658997</t>
@@ -4637,22 +4637,22 @@
     <t xml:space="preserve">3.63173413276672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68674778938293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370186805725</t>
+    <t xml:space="preserve">3.68674802780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7256805896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241313934326</t>
+    <t xml:space="preserve">3.85178828239441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241337776184</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
@@ -4661,19 +4661,19 @@
     <t xml:space="preserve">3.97366452217102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06422472000122</t>
+    <t xml:space="preserve">4.06422519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.01259660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98466682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03037023544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04052686691284</t>
+    <t xml:space="preserve">3.9846670627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03037071228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04052639007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.04899024963379</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645109176636</t>
+    <t xml:space="preserve">4.04645156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391193389893</t>
+    <t xml:space="preserve">4.04391241073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
@@ -4703,64 +4703,64 @@
     <t xml:space="preserve">4.08623027801514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09977149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0083646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98635959625244</t>
+    <t xml:space="preserve">4.14209032058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09977197647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05322170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00836515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98635983467102</t>
   </si>
   <si>
     <t xml:space="preserve">4.02359962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01344347000122</t>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01344299316406</t>
   </si>
   <si>
     <t xml:space="preserve">3.96774005889893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00667238235474</t>
+    <t xml:space="preserve">4.00667285919189</t>
   </si>
   <si>
     <t xml:space="preserve">3.955890417099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84586405754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78831124305725</t>
+    <t xml:space="preserve">3.84586381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78831100463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.86702275276184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88818168640137</t>
+    <t xml:space="preserve">3.88818144798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.96096873283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94150233268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93219232559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579892158508</t>
+    <t xml:space="preserve">3.9415020942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93219256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272592544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579963684082</t>
   </si>
   <si>
     <t xml:space="preserve">3.91865086555481</t>
@@ -4769,25 +4769,25 @@
     <t xml:space="preserve">3.8577127456665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89325952529907</t>
+    <t xml:space="preserve">3.89325976371765</t>
   </si>
   <si>
     <t xml:space="preserve">3.96435451507568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03544855117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97958874702454</t>
+    <t xml:space="preserve">4.03544902801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97958898544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01682901382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99482321739197</t>
+    <t xml:space="preserve">4.0168285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99482297897339</t>
   </si>
   <si>
     <t xml:space="preserve">3.98974537849426</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">3.9973623752594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02529239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04306554794312</t>
+    <t xml:space="preserve">4.02529191970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04306602478027</t>
   </si>
   <si>
     <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05660820007324</t>
+    <t xml:space="preserve">4.05660772323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.08792304992676</t>
@@ -4814,28 +4814,28 @@
     <t xml:space="preserve">4.12685537338257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10992860794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638643264771</t>
+    <t xml:space="preserve">4.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19117879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13362598419189</t>
+    <t xml:space="preserve">4.1911792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13362646102905</t>
   </si>
   <si>
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732431411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14462947845459</t>
+    <t xml:space="preserve">4.15732479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
     <t xml:space="preserve">4.18271541595459</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">4.20556735992432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22926568984985</t>
+    <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233797073364</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">4.17679071426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16155576705933</t>
+    <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863964080811</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">4.17932987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23349666595459</t>
+    <t xml:space="preserve">4.23349714279175</t>
   </si>
   <si>
     <t xml:space="preserve">4.24026823043823</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">4.27073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29612827301025</t>
+    <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
     <t xml:space="preserve">4.33506059646606</t>
@@ -4889,46 +4889,46 @@
     <t xml:space="preserve">4.29443454742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28427886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04560470581055</t>
+    <t xml:space="preserve">4.28427839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
     <t xml:space="preserve">4.09215497970581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85094213485718</t>
+    <t xml:space="preserve">3.8509418964386</t>
   </si>
   <si>
     <t xml:space="preserve">3.87802529335022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75784254074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8526349067688</t>
+    <t xml:space="preserve">3.75784206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85263466835022</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94658088684082</t>
+    <t xml:space="preserve">3.94658064842224</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92965364456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93811678886414</t>
+    <t xml:space="preserve">3.92965340614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93811702728271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05491495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06676340103149</t>
+    <t xml:space="preserve">4.06676387786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4943,7 +4943,7 @@
     <t xml:space="preserve">4.29274225234985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32321119308472</t>
+    <t xml:space="preserve">4.32321071624756</t>
   </si>
   <si>
     <t xml:space="preserve">4.3553729057312</t>
@@ -4952,10 +4952,10 @@
     <t xml:space="preserve">4.30289888381958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25888824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30459117889404</t>
+    <t xml:space="preserve">4.25888776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3045916557312</t>
   </si>
   <si>
     <t xml:space="preserve">4.28258562088013</t>
@@ -4964,19 +4964,19 @@
     <t xml:space="preserve">4.33336782455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31305456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23857545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32828903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37907123565674</t>
+    <t xml:space="preserve">4.31305503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32828950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938402175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37907075881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.34013795852661</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531141281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072353363037</t>
+    <t xml:space="preserve">4.33531188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3398699760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072305679321</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266326904297</t>
+    <t xml:space="preserve">4.36266374588013</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369129180908</t>
+    <t xml:space="preserve">4.40369176864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081052780151</t>
+    <t xml:space="preserve">4.35081100463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292520523071</t>
+    <t xml:space="preserve">4.48757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292568206787</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924903869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574781417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492357254028</t>
+    <t xml:space="preserve">4.43924951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492404937744</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5769214630127</t>
+    <t xml:space="preserve">4.57692193984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5915093421936</t>
+    <t xml:space="preserve">4.59150981903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891983032227</t>
+    <t xml:space="preserve">4.63891935348511</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130556106567</t>
+    <t xml:space="preserve">4.52130603790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5159,7 +5159,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786249160767</t>
+    <t xml:space="preserve">4.58786296844482</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5171,22 +5171,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732950210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897798538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197505950928</t>
+    <t xml:space="preserve">4.73191690444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644710540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197553634644</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6553316116333</t>
+    <t xml:space="preserve">4.56780481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65533113479614</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074373245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792064666748</t>
+    <t xml:space="preserve">4.68268394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792112350464</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68450689315796</t>
+    <t xml:space="preserve">4.6845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009395599365</t>
+    <t xml:space="preserve">4.73009347915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174291610718</t>
+    <t xml:space="preserve">4.67174243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7063889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6370964050293</t>
+    <t xml:space="preserve">4.70638847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63709688186646</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080188751221</t>
+    <t xml:space="preserve">4.66080141067505</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903614044189</t>
+    <t xml:space="preserve">4.67903661727905</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8887357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403158187866</t>
+    <t xml:space="preserve">4.87050104141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88873624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497308731079</t>
+    <t xml:space="preserve">4.85956048965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491445541382</t>
+    <t xml:space="preserve">4.82491397857666</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756212234497</t>
+    <t xml:space="preserve">4.79756259918213</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5348,13 +5348,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932786941528</t>
+    <t xml:space="preserve">4.77932739257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815422058105</t>
+    <t xml:space="preserve">4.6881537437439</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714496612549</t>
+    <t xml:space="preserve">4.96714544296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602994918823</t>
+    <t xml:space="preserve">4.89602947235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079229354858</t>
+    <t xml:space="preserve">4.97079277038574</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5423,7 +5423,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2333722114563</t>
+    <t xml:space="preserve">5.23337268829346</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5432,13 +5432,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2607250213623</t>
+    <t xml:space="preserve">5.26072454452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078317642212</t>
+    <t xml:space="preserve">5.28078269958496</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5450,10 +5450,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709890365601</t>
+    <t xml:space="preserve">6.38216161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709842681885</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8562650680542</t>
+    <t xml:space="preserve">6.85626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5489,13 +5489,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655679702759</t>
+    <t xml:space="preserve">6.95655632019043</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632322311401</t>
+    <t xml:space="preserve">6.87632369995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8690299987793</t>
+    <t xml:space="preserve">6.86902952194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5525,13 +5525,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625642776489</t>
+    <t xml:space="preserve">7.16625595092773</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213426589966</t>
+    <t xml:space="preserve">7.31213474273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566480636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537307739258</t>
+    <t xml:space="preserve">7.21184253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537355422974</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5558,10 +5558,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242551803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5127158164978</t>
+    <t xml:space="preserve">7.41242504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5570,19 +5570,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57653856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682933807373</t>
+    <t xml:space="preserve">7.63124227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580131530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.726975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682886123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67227029800415</t>
+    <t xml:space="preserve">7.67226982116699</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22387218475342</t>
+    <t xml:space="preserve">8.2238712310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -6555,6 +6555,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.8099994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0550003051758</t>
   </si>
 </sst>
 </file>
@@ -71555,7 +71558,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494444444</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>960517</v>
@@ -71576,6 +71579,32 @@
         <v>2180</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6501273148</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1173106</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>19.0900001525879</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>18.5200004577637</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>19.0550003051758</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2181</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="2182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="2183">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528841972351</t>
+    <t xml:space="preserve">2.44528818130493</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50193166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40895104408264</t>
+    <t xml:space="preserve">2.50193190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40895128250122</t>
   </si>
   <si>
     <t xml:space="preserve">2.35658240318298</t>
@@ -56,205 +56,205 @@
     <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29780149459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37261390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3779571056366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33413887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23474550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15458989143372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11183953285217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9964154958725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588387489319</t>
+    <t xml:space="preserve">2.29780173301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37261343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795686721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33413863182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2347457408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15458965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11183977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99641561508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588363647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.07977771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0348904132843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03168392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02954626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90343475341797</t>
+    <t xml:space="preserve">2.03489065170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03168416023254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343463420868</t>
   </si>
   <si>
     <t xml:space="preserve">2.00924015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93549692630768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84037864208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953544139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701677799225</t>
+    <t xml:space="preserve">1.93549704551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84037888050079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74953556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701653957367</t>
   </si>
   <si>
     <t xml:space="preserve">1.67792952060699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349882602692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151142597198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6886168718338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823016166687</t>
+    <t xml:space="preserve">1.59349870681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151154518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55823004245758</t>
   </si>
   <si>
     <t xml:space="preserve">1.60632348060608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72922956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899823188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312317371368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7335045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6939605474472</t>
+    <t xml:space="preserve">1.72922933101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67899811267853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350417613983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69396030902863</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419176578522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70571684837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296720504761</t>
+    <t xml:space="preserve">1.70571672916412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296744346619</t>
   </si>
   <si>
     <t xml:space="preserve">1.71533572673798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82541644573212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82327878475189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88099122047424</t>
+    <t xml:space="preserve">1.82541620731354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8232786655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88099098205566</t>
   </si>
   <si>
     <t xml:space="preserve">1.89381587505341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8948849439621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86602854728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404138565063</t>
+    <t xml:space="preserve">1.89488482475281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8660284280777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404150485992</t>
   </si>
   <si>
     <t xml:space="preserve">1.76556646823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82648527622223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79976642131805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92053461074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229103088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221518516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435344219208</t>
+    <t xml:space="preserve">1.82648468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79976630210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.920534491539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442845344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93229067325592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221566200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435296535492</t>
   </si>
   <si>
     <t xml:space="preserve">1.97183430194855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95580339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95259702205658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92374098300934</t>
+    <t xml:space="preserve">1.95580315589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95259690284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92374086380005</t>
   </si>
   <si>
     <t xml:space="preserve">1.87564718723297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88312816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91198480129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90022838115692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89167857170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579756736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81793487071991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190360546112</t>
+    <t xml:space="preserve">1.88312840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91198492050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90022826194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89167833328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579744815826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8019038438797</t>
   </si>
   <si>
     <t xml:space="preserve">1.87992238998413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90129721164703</t>
+    <t xml:space="preserve">1.90129733085632</t>
   </si>
   <si>
     <t xml:space="preserve">1.84465360641479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92587828636169</t>
+    <t xml:space="preserve">1.92587840557098</t>
   </si>
   <si>
     <t xml:space="preserve">1.92801570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91519093513489</t>
+    <t xml:space="preserve">1.91519105434418</t>
   </si>
   <si>
     <t xml:space="preserve">2.0177903175354</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">2.07015895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02634024620056</t>
+    <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
     <t xml:space="preserve">2.0551962852478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05092144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99855327606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214029312134</t>
+    <t xml:space="preserve">2.05092167854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855291843414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214041233063</t>
   </si>
   <si>
     <t xml:space="preserve">1.95045948028564</t>
@@ -293,19 +293,19 @@
     <t xml:space="preserve">1.93977189064026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84999763965607</t>
+    <t xml:space="preserve">1.84999740123749</t>
   </si>
   <si>
     <t xml:space="preserve">1.87457847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79121649265289</t>
+    <t xml:space="preserve">1.79121661186218</t>
   </si>
   <si>
     <t xml:space="preserve">1.73884797096252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388565540314</t>
+    <t xml:space="preserve">1.72388589382172</t>
   </si>
   <si>
     <t xml:space="preserve">1.69502937793732</t>
@@ -317,55 +317,55 @@
     <t xml:space="preserve">1.70785450935364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76235246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700954914093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87773144245148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8754688501358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279757022858</t>
+    <t xml:space="preserve">1.76235270500183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87773132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87546920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279697418213</t>
   </si>
   <si>
     <t xml:space="preserve">1.90601050853729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88451850414276</t>
+    <t xml:space="preserve">1.88451814651489</t>
   </si>
   <si>
     <t xml:space="preserve">1.80081212520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80986189842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81438601016998</t>
+    <t xml:space="preserve">1.80986154079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81438589096069</t>
   </si>
   <si>
     <t xml:space="preserve">1.80646824836731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75104129314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6311377286911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54290688037872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46711921691895</t>
+    <t xml:space="preserve">1.75104081630707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63113796710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54290699958801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46711909770966</t>
   </si>
   <si>
     <t xml:space="preserve">1.47390604019165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42526590824127</t>
+    <t xml:space="preserve">1.42526602745056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51689016819</t>
@@ -374,79 +374,79 @@
     <t xml:space="preserve">1.61190795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60059642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57684183120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69900739192963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38341307640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2420175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2725590467453</t>
+    <t xml:space="preserve">1.6005961894989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57684195041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69900751113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38341271877289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24201738834381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27255892753601</t>
   </si>
   <si>
     <t xml:space="preserve">1.213738322258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19111502170563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23636150360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1854590177536</t>
+    <t xml:space="preserve">1.19111514091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23636186122894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18545937538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021277427673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09949088096619</t>
+    <t xml:space="preserve">1.0994907617569</t>
   </si>
   <si>
     <t xml:space="preserve">1.09722852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2374929189682</t>
+    <t xml:space="preserve">1.23749279975891</t>
   </si>
   <si>
     <t xml:space="preserve">1.28726422786713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36870789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33477294445038</t>
+    <t xml:space="preserve">1.36870777606964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
     <t xml:space="preserve">1.39359319210052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38454401493073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3698388338089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.398118019104</t>
+    <t xml:space="preserve">1.38454389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4003803730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983895301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39811789989471</t>
   </si>
   <si>
     <t xml:space="preserve">1.37888813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37097012996674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37775731086731</t>
+    <t xml:space="preserve">1.37097024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37775707244873</t>
   </si>
   <si>
     <t xml:space="preserve">1.42979085445404</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">1.40264272689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38567531108856</t>
+    <t xml:space="preserve">1.38567507266998</t>
   </si>
   <si>
     <t xml:space="preserve">1.26011598110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29631328582764</t>
+    <t xml:space="preserve">1.29631316661835</t>
   </si>
   <si>
     <t xml:space="preserve">1.32232999801636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37549459934235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43657743930817</t>
+    <t xml:space="preserve">1.37549471855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43657767772675</t>
   </si>
   <si>
     <t xml:space="preserve">1.45354497432709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44788908958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47051239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45015132427216</t>
+    <t xml:space="preserve">1.44788932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47051227092743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45015156269073</t>
   </si>
   <si>
     <t xml:space="preserve">1.41961002349854</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">1.38001954555511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39698672294617</t>
+    <t xml:space="preserve">1.39698696136475</t>
   </si>
   <si>
     <t xml:space="preserve">1.33137941360474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33251070976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38228154182434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36757659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816647529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3540027141571</t>
+    <t xml:space="preserve">1.3325103521347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38228189945221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3675764799118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816659450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35400283336639</t>
   </si>
   <si>
     <t xml:space="preserve">1.3279857635498</t>
@@ -518,28 +518,28 @@
     <t xml:space="preserve">1.41056084632874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40377390384674</t>
+    <t xml:space="preserve">1.40377366542816</t>
   </si>
   <si>
     <t xml:space="preserve">1.42413485050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43883979320526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45920073986053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47729933261871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48747980594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48974215984344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019978046417</t>
+    <t xml:space="preserve">1.43883991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45920085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47729957103729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48748004436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48974239826202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39019989967346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40716743469238</t>
@@ -548,37 +548,37 @@
     <t xml:space="preserve">1.36078953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41282296180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513377189636</t>
+    <t xml:space="preserve">1.41282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513389110565</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947800636292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34269094467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536282062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821469306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780552864075</t>
+    <t xml:space="preserve">1.34269106388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821457386017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780540943146</t>
   </si>
   <si>
     <t xml:space="preserve">1.28613293170929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28500163555145</t>
+    <t xml:space="preserve">1.28500187397003</t>
   </si>
   <si>
     <t xml:space="preserve">1.27934598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35174024105072</t>
+    <t xml:space="preserve">1.35174036026001</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
@@ -587,43 +587,43 @@
     <t xml:space="preserve">1.37210130691528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39472460746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4162163734436</t>
+    <t xml:space="preserve">1.39472448825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41621673107147</t>
   </si>
   <si>
     <t xml:space="preserve">1.44110238552094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49313580989838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52480828762054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53159534931183</t>
+    <t xml:space="preserve">1.4931355714798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52480840682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53159523010254</t>
   </si>
   <si>
     <t xml:space="preserve">1.51575911045074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54856264591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56553041934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61077690124512</t>
+    <t xml:space="preserve">1.54856288433075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56553018093109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61077678203583</t>
   </si>
   <si>
     <t xml:space="preserve">1.63453125953674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59833383560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571053504944</t>
+    <t xml:space="preserve">1.59833371639252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571065425873</t>
   </si>
   <si>
     <t xml:space="preserve">1.57118618488312</t>
@@ -638,79 +638,79 @@
     <t xml:space="preserve">1.4750372171402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65715456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69335186481476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167891025543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63905584812164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172736644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57457935810089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661302089691</t>
+    <t xml:space="preserve">1.65715444087982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69335162639618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167914867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63905572891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172760486603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57457947731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62661325931549</t>
   </si>
   <si>
     <t xml:space="preserve">1.58476006984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56100535392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064476490021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512101650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64923632144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6662038564682</t>
+    <t xml:space="preserve">1.56100559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064440727234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512089729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64923620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66620373725891</t>
   </si>
   <si>
     <t xml:space="preserve">1.62435078620911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72049963474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284602642059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022248744965</t>
+    <t xml:space="preserve">1.72049939632416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741895198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8528459072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492754936218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022272586823</t>
   </si>
   <si>
     <t xml:space="preserve">1.86302614212036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85623919963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91053521633148</t>
+    <t xml:space="preserve">1.85623943805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91053509712219</t>
   </si>
   <si>
     <t xml:space="preserve">1.89922344684601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91166651248932</t>
+    <t xml:space="preserve">1.91166639328003</t>
   </si>
   <si>
     <t xml:space="preserve">1.92637133598328</t>
@@ -719,94 +719,94 @@
     <t xml:space="preserve">1.94560110569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446957111359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89696109294891</t>
+    <t xml:space="preserve">1.94446969032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89696097373962</t>
   </si>
   <si>
     <t xml:space="preserve">1.93655180931091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98066735267639</t>
+    <t xml:space="preserve">1.98066711425781</t>
   </si>
   <si>
     <t xml:space="preserve">2.01347088813782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00781512260437</t>
+    <t xml:space="preserve">2.00781488418579</t>
   </si>
   <si>
     <t xml:space="preserve">2.01573300361633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01912689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96483111381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99876582622528</t>
+    <t xml:space="preserve">2.01912641525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9648312330246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99876570701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.0202579498291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727394104004</t>
+    <t xml:space="preserve">1.97727382183075</t>
   </si>
   <si>
     <t xml:space="preserve">2.01007747650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97161793708801</t>
+    <t xml:space="preserve">1.97161781787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.9478634595871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97953605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02252054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99084770679474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0824716091156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08699655532837</t>
+    <t xml:space="preserve">1.97953593730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02252006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99084782600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08699607849121</t>
   </si>
   <si>
     <t xml:space="preserve">2.05079913139343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05193042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542075157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202710151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9670934677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894618034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940368175507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8913049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320637702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8799934387207</t>
+    <t xml:space="preserve">2.05193066596985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542051315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202722072601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96709322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894594192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940392017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89130532741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87320673465729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999331951141</t>
   </si>
   <si>
     <t xml:space="preserve">1.85510802268982</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">1.99424135684967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00215935707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0032901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478265762329</t>
+    <t xml:space="preserve">2.00215911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00329041481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478241920471</t>
   </si>
   <si>
     <t xml:space="preserve">2.01799559593201</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">2.00442147254944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95465075969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0293071269989</t>
+    <t xml:space="preserve">1.95465052127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02930736541748</t>
   </si>
   <si>
     <t xml:space="preserve">2.02817606925964</t>
@@ -851,67 +851,67 @@
     <t xml:space="preserve">2.13224315643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432503700256</t>
+    <t xml:space="preserve">2.12432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.12093138694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15939092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373516082764</t>
+    <t xml:space="preserve">2.1593906879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373539924622</t>
   </si>
   <si>
     <t xml:space="preserve">2.14016127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10848879814148</t>
+    <t xml:space="preserve">2.1084885597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14921069145203</t>
+    <t xml:space="preserve">2.14921045303345</t>
   </si>
   <si>
     <t xml:space="preserve">2.19332575798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1786208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23291659355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558835029602</t>
+    <t xml:space="preserve">2.17862105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23291635513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558811187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.20803117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20576906204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18314528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16617822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20350670814514</t>
+    <t xml:space="preserve">2.20576882362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18314552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16617798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20350623130798</t>
   </si>
   <si>
     <t xml:space="preserve">2.19219470024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15826010704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20011305809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17522740364075</t>
+    <t xml:space="preserve">2.15825986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20011281967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17522764205933</t>
   </si>
   <si>
     <t xml:space="preserve">2.17748975753784</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">2.09378361701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07907867431641</t>
+    <t xml:space="preserve">2.07907819747925</t>
   </si>
   <si>
     <t xml:space="preserve">2.08812761306763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11188197135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10961961746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.222736120224</t>
+    <t xml:space="preserve">2.11188220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10961985588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22273635864258</t>
   </si>
   <si>
     <t xml:space="preserve">2.26232695579529</t>
@@ -947,34 +947,34 @@
     <t xml:space="preserve">2.26006460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2578022480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31436038017273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33132791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34716439247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40032863616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41164016723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43878817558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44557547569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127993583679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32567191123962</t>
+    <t xml:space="preserve">2.25780248641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31436061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33132815361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34716415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40032887458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41164064407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43878841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127945899963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">2.38675475120544</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">2.36300039291382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33585238456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25893306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24988412857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27137613296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33769369125366</t>
+    <t xml:space="preserve">2.33585262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25893330574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24988436698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27137589454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33769392967224</t>
   </si>
   <si>
     <t xml:space="preserve">2.30216670036316</t>
@@ -1022,28 +1022,28 @@
     <t xml:space="preserve">2.21097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18137383460999</t>
+    <t xml:space="preserve">2.18137359619141</t>
   </si>
   <si>
     <t xml:space="preserve">2.1458466053009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13637232780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10913491249084</t>
+    <t xml:space="preserve">2.13637280464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10913515090942</t>
   </si>
   <si>
     <t xml:space="preserve">2.14110946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14229369163513</t>
+    <t xml:space="preserve">2.14229393005371</t>
   </si>
   <si>
     <t xml:space="preserve">2.16361021995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.186110496521</t>
+    <t xml:space="preserve">2.18611097335815</t>
   </si>
   <si>
     <t xml:space="preserve">2.13874101638794</t>
@@ -1052,49 +1052,49 @@
     <t xml:space="preserve">2.119793176651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14939951896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13755702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16597890853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15532040596008</t>
+    <t xml:space="preserve">2.1493992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13755679130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16597867012024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1553201675415</t>
   </si>
   <si>
     <t xml:space="preserve">2.20032167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1837420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23821759223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27374458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453744888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3838791847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34835171699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36848402023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37322115898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36966872215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37203669548035</t>
+    <t xml:space="preserve">2.18374252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2382173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27374482154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453768730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38387942314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34835195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36848425865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37322092056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36966800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3720371723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.38032650947571</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">2.38861608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34361529350281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30927228927612</t>
+    <t xml:space="preserve">2.34361505508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30927205085754</t>
   </si>
   <si>
     <t xml:space="preserve">2.28913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2938768863678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058834075928</t>
+    <t xml:space="preserve">2.29387712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33058857917786</t>
   </si>
   <si>
     <t xml:space="preserve">2.34953618049622</t>
@@ -1124,55 +1124,55 @@
     <t xml:space="preserve">2.36019444465637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31637740135193</t>
+    <t xml:space="preserve">2.31637716293335</t>
   </si>
   <si>
     <t xml:space="preserve">2.34479904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31756138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34006214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40401101112366</t>
+    <t xml:space="preserve">2.31756186485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34006237983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40401124954224</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099326133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37914204597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3554573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045651435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25953412055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27966618537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25598096847534</t>
+    <t xml:space="preserve">2.37914228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35545754432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045603752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25953388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27966594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25598120689392</t>
   </si>
   <si>
     <t xml:space="preserve">2.23111200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22163844108582</t>
+    <t xml:space="preserve">2.22163796424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.19676923751831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847918510437</t>
+    <t xml:space="preserve">2.19321608543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847942352295</t>
   </si>
   <si>
     <t xml:space="preserve">2.18492650985718</t>
@@ -1181,34 +1181,34 @@
     <t xml:space="preserve">2.13163566589355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16005778312683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058350563049</t>
+    <t xml:space="preserve">2.16005730628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058398246765</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13045167922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12097764015198</t>
+    <t xml:space="preserve">2.13045144081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1209774017334</t>
   </si>
   <si>
     <t xml:space="preserve">2.11031913757324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08426594734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22400641441345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24295425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29624533653259</t>
+    <t xml:space="preserve">2.0842661857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22400689125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24295449256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29624557495117</t>
   </si>
   <si>
     <t xml:space="preserve">2.28795552253723</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">2.25834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24413895606995</t>
+    <t xml:space="preserve">2.24413871765137</t>
   </si>
   <si>
     <t xml:space="preserve">2.22755908966064</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">2.24769139289856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2926926612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32111430168152</t>
+    <t xml:space="preserve">2.29269242286682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3211145401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.25716519355774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3045346736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29742932319641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25124406814575</t>
+    <t xml:space="preserve">2.30453515052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29742956161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25124430656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.3187460899353</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">2.26663947105408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28321886062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32703542709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34598350524902</t>
+    <t xml:space="preserve">2.28321862220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32703566551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34598326683044</t>
   </si>
   <si>
     <t xml:space="preserve">2.30571937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27729749679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203209877014</t>
+    <t xml:space="preserve">2.27729773521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742726325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203186035156</t>
   </si>
   <si>
     <t xml:space="preserve">2.1482150554657</t>
@@ -1298,43 +1298,43 @@
     <t xml:space="preserve">2.23348045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23584914207458</t>
+    <t xml:space="preserve">2.23584890365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.28084993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26900792121887</t>
+    <t xml:space="preserve">2.26900768280029</t>
   </si>
   <si>
     <t xml:space="preserve">2.27256059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24177026748657</t>
+    <t xml:space="preserve">2.24177002906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27019214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26308679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677129745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032373428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3009819984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3317723274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3282196521759</t>
+    <t xml:space="preserve">2.27019190788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26308608055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677153587341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032397270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30098247528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33177256584167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.31519317626953</t>
@@ -1343,49 +1343,49 @@
     <t xml:space="preserve">2.39098477363586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41585373878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41940641403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43717002868652</t>
+    <t xml:space="preserve">2.41585397720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41940665245056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4371702671051</t>
   </si>
   <si>
     <t xml:space="preserve">2.48098707199097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53309345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56743693351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54612064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56151556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57572674751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56862092018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57691073417664</t>
+    <t xml:space="preserve">2.53309369087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56743669509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54612040519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56151580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57572650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56862115859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57691121101379</t>
   </si>
   <si>
     <t xml:space="preserve">2.56980538368225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56625270843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63967561721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6574387550354</t>
+    <t xml:space="preserve">2.56625247001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63967537879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65743899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.66691303253174</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.62960934638977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58105564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57158184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56921339035034</t>
+    <t xml:space="preserve">2.58105540275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57158160209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56921291351318</t>
   </si>
   <si>
     <t xml:space="preserve">2.48039507865906</t>
@@ -1412,31 +1412,31 @@
     <t xml:space="preserve">2.53013300895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45611810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217082023621</t>
+    <t xml:space="preserve">2.45611786842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217129707336</t>
   </si>
   <si>
     <t xml:space="preserve">2.44605183601379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4069721698761</t>
+    <t xml:space="preserve">2.40697193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236733436584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47092127799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45552587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723606109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46559190750122</t>
+    <t xml:space="preserve">2.4709210395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45552563667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723582267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4655921459198</t>
   </si>
   <si>
     <t xml:space="preserve">2.473881483078</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">2.40934014320374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43480157852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3264434337616</t>
+    <t xml:space="preserve">2.43480181694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40756416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32644319534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.33473324775696</t>
@@ -1463,31 +1463,31 @@
     <t xml:space="preserve">2.35190463066101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39631390571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37440514564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35782623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42591977119446</t>
+    <t xml:space="preserve">2.39631366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37440538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35782599449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
     <t xml:space="preserve">2.36611580848694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38624811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39986658096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32881212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35249710083008</t>
+    <t xml:space="preserve">2.3862476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39986634254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32881188392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3524968624115</t>
   </si>
   <si>
     <t xml:space="preserve">2.34302282333374</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39809012413025</t>
+    <t xml:space="preserve">2.39808988571167</t>
   </si>
   <si>
     <t xml:space="preserve">2.38565540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41230082511902</t>
+    <t xml:space="preserve">2.41230130195618</t>
   </si>
   <si>
     <t xml:space="preserve">2.41822218894958</t>
@@ -1514,40 +1514,40 @@
     <t xml:space="preserve">2.45078897476196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51769828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51355361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54315972328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54079151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54375171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756852149963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61066174507141</t>
+    <t xml:space="preserve">2.51769852638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51355409622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54079127311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54375219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61066150665283</t>
   </si>
   <si>
     <t xml:space="preserve">2.58223962783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59408187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61480617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63493824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65803170204163</t>
+    <t xml:space="preserve">2.59408235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61480641365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63493847846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65803122520447</t>
   </si>
   <si>
     <t xml:space="preserve">2.64204406738281</t>
@@ -1556,25 +1556,25 @@
     <t xml:space="preserve">2.67165017127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67520260810852</t>
+    <t xml:space="preserve">2.6752028465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.58638477325439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60177969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55855488777161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59349036216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59526634216309</t>
+    <t xml:space="preserve">2.60177946090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55855512619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57039713859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59349012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59526658058167</t>
   </si>
   <si>
     <t xml:space="preserve">2.51059293746948</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">2.48621010780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4354841709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888333320618</t>
+    <t xml:space="preserve">2.43548393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
     <t xml:space="preserve">2.387850522995</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">2.3773341178894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25917887687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176114082336</t>
+    <t xml:space="preserve">2.25917863845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176090240479</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361132621765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33464980125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577899932861</t>
+    <t xml:space="preserve">2.33464956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577923774719</t>
   </si>
   <si>
     <t xml:space="preserve">2.23752737045288</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">2.23567152023315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16020035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24989938735962</t>
+    <t xml:space="preserve">2.16020059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2498996257782</t>
   </si>
   <si>
     <t xml:space="preserve">2.2319598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23938298225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20041036605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20968961715698</t>
+    <t xml:space="preserve">2.23938274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371361732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20041012763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20968985557556</t>
   </si>
   <si>
     <t xml:space="preserve">2.22329926490784</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">2.20721530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15525150299072</t>
+    <t xml:space="preserve">2.1552517414093</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298720359802</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">2.05379891395569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02843570709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04699420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04946875572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0921528339386</t>
+    <t xml:space="preserve">2.02843594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04699444770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04946851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09215307235718</t>
   </si>
   <si>
     <t xml:space="preserve">2.11689758300781</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">2.10143232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14102339744568</t>
+    <t xml:space="preserve">2.14102363586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813473701477</t>
@@ -1697,25 +1697,25 @@
     <t xml:space="preserve">2.08906006813049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06864547729492</t>
+    <t xml:space="preserve">2.0686457157135</t>
   </si>
   <si>
     <t xml:space="preserve">2.09091591835022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10638093948364</t>
+    <t xml:space="preserve">2.10638117790222</t>
   </si>
   <si>
     <t xml:space="preserve">2.12679505348206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14349818229675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13793063163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12122774124146</t>
+    <t xml:space="preserve">2.14349794387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13793015480042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12122750282288</t>
   </si>
   <si>
     <t xml:space="preserve">2.09957647323608</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473533630371</t>
+    <t xml:space="preserve">2.14473485946655</t>
   </si>
   <si>
     <t xml:space="preserve">2.18061470985413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16514945030212</t>
+    <t xml:space="preserve">2.16514992713928</t>
   </si>
   <si>
     <t xml:space="preserve">2.20102906227112</t>
@@ -1739,46 +1739,46 @@
     <t xml:space="preserve">2.09029722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11999034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07730603218079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07235717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11937212944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20474052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28392291069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23319721221924</t>
+    <t xml:space="preserve">2.12432074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699963569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07730627059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0723569393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11937189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20474076271057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28392338752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23319697380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.19174981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24309492111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26289081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25299286842346</t>
+    <t xml:space="preserve">2.24309468269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26289033889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25299263000488</t>
   </si>
   <si>
     <t xml:space="preserve">2.26969528198242</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">2.27711844444275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25608563423157</t>
+    <t xml:space="preserve">2.25608587265015</t>
   </si>
   <si>
     <t xml:space="preserve">2.24185752868652</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">2.19917321205139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22206211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27526259422302</t>
+    <t xml:space="preserve">2.2220618724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27526307106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.32846331596375</t>
@@ -1808,34 +1808,34 @@
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3142352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991047859192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33712434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33836126327515</t>
+    <t xml:space="preserve">2.31423544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36991095542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33712410926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33836150169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.3340311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3600127696991</t>
+    <t xml:space="preserve">2.36001300811768</t>
   </si>
   <si>
     <t xml:space="preserve">2.40146017074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41630697250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41445088386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42063760757446</t>
+    <t xml:space="preserve">2.41630673408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41445112228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4206371307373</t>
   </si>
   <si>
     <t xml:space="preserve">2.45589804649353</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">2.44352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47012639045715</t>
+    <t xml:space="preserve">2.47012615203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.48682856559753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50600600242615</t>
+    <t xml:space="preserve">2.50600624084473</t>
   </si>
   <si>
     <t xml:space="preserve">2.37300372123718</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">2.36496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27093243598938</t>
+    <t xml:space="preserve">2.2709321975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.28083038330078</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">2.1985547542572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20907115936279</t>
+    <t xml:space="preserve">2.20907092094421</t>
   </si>
   <si>
     <t xml:space="preserve">2.18308925628662</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">2.17504739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19979166984558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16824269294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648865699768</t>
+    <t xml:space="preserve">2.19979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16824245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15648889541626</t>
   </si>
   <si>
     <t xml:space="preserve">2.09772062301636</t>
@@ -1904,19 +1904,19 @@
     <t xml:space="preserve">2.13978624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12184643745422</t>
+    <t xml:space="preserve">2.1218466758728</t>
   </si>
   <si>
     <t xml:space="preserve">2.19669890403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380976676941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21525692939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24247646331787</t>
+    <t xml:space="preserve">2.17381024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21525716781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.24433183670044</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">2.2474250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25979733467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33217549324036</t>
+    <t xml:space="preserve">2.2597975730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33217525482178</t>
   </si>
   <si>
     <t xml:space="preserve">2.34949636459351</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">2.26598358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26227164268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28825354576111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22701096534729</t>
+    <t xml:space="preserve">2.26227211952209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28825330734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22701072692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.2041220664978</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">2.15834498405457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13731145858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443388938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2263925075531</t>
+    <t xml:space="preserve">2.13731169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23443412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22639226913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949069976807</t>
@@ -1967,34 +1967,34 @@
     <t xml:space="preserve">2.24680662155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23381567001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15277719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16947984695435</t>
+    <t xml:space="preserve">2.23381543159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15277695655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
     <t xml:space="preserve">2.15401458740234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1855640411377</t>
+    <t xml:space="preserve">2.18556356430054</t>
   </si>
   <si>
     <t xml:space="preserve">2.21278262138367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504173278809</t>
+    <t xml:space="preserve">2.19607996940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504197120667</t>
   </si>
   <si>
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17628407478333</t>
+    <t xml:space="preserve">2.1762843132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.14040470123291</t>
@@ -2009,52 +2009,52 @@
     <t xml:space="preserve">2.31794691085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35073375701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38846921920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41012072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43053483963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32227754592896</t>
+    <t xml:space="preserve">2.35073351860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846898078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41012048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43053460121155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32227730751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41259503364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43424654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44971179962158</t>
+    <t xml:space="preserve">2.41259527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.434246301651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.449711561203</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342350006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54930853843689</t>
+    <t xml:space="preserve">2.54930877685547</t>
   </si>
   <si>
     <t xml:space="preserve">2.5511646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53260564804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47321915626526</t>
+    <t xml:space="preserve">2.53260636329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">2.47136330604553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50043845176697</t>
+    <t xml:space="preserve">2.50043821334839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5152850151062</t>
@@ -2063,46 +2063,46 @@
     <t xml:space="preserve">2.52394580841064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46208429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32908201217651</t>
+    <t xml:space="preserve">2.4620840549469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32908225059509</t>
   </si>
   <si>
     <t xml:space="preserve">2.36124992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42620468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4410514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609672546387</t>
+    <t xml:space="preserve">2.42620444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44105124473572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609696388245</t>
   </si>
   <si>
     <t xml:space="preserve">2.45713520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45094895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47507476806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46579599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47569394111633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49054026603699</t>
+    <t xml:space="preserve">2.45094919204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47507500648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46579623222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47569346427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49054074287415</t>
   </si>
   <si>
     <t xml:space="preserve">2.48187971115112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47878670692444</t>
+    <t xml:space="preserve">2.47878694534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.49548935890198</t>
@@ -2111,49 +2111,49 @@
     <t xml:space="preserve">2.50662422180176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5288941860199</t>
+    <t xml:space="preserve">2.52889466285706</t>
   </si>
   <si>
     <t xml:space="preserve">2.53446221351624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50786161422729</t>
+    <t xml:space="preserve">2.50786137580872</t>
   </si>
   <si>
     <t xml:space="preserve">2.55302047729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58147668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64952421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68292951583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69901347160339</t>
+    <t xml:space="preserve">2.56601119041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58147644996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64952397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68292927742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69901323318481</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220900535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68231105804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66870141029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179465293884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69282746315002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71014833450317</t>
+    <t xml:space="preserve">2.68231081962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66870164871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179417610168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69282722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71014857292175</t>
   </si>
   <si>
     <t xml:space="preserve">2.74664688110352</t>
@@ -2165,28 +2165,28 @@
     <t xml:space="preserve">2.72994422912598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83696460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8344898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86109042167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85057377815247</t>
+    <t xml:space="preserve">2.83696413040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83448958396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86109018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85057353973389</t>
   </si>
   <si>
     <t xml:space="preserve">2.79799151420593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75716328620911</t>
+    <t xml:space="preserve">2.75716280937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.76025629043579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78500056266785</t>
+    <t xml:space="preserve">2.78500032424927</t>
   </si>
   <si>
     <t xml:space="preserve">2.78994989395142</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">2.82088041305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83943867683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8388204574585</t>
+    <t xml:space="preserve">2.83943891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83882069587708</t>
   </si>
   <si>
     <t xml:space="preserve">2.79737305641174</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">2.81160116195679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78685665130615</t>
+    <t xml:space="preserve">2.78685712814331</t>
   </si>
   <si>
     <t xml:space="preserve">2.79922890663147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80603337287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81778717041016</t>
+    <t xml:space="preserve">2.80603361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81778740882874</t>
   </si>
   <si>
     <t xml:space="preserve">2.79551720619202</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">2.74417185783386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65694785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59137463569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6909716129303</t>
+    <t xml:space="preserve">2.65694761276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014314651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59137487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69097137451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.66560816764832</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">2.73056244850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79984736442566</t>
+    <t xml:space="preserve">2.79984784126282</t>
   </si>
   <si>
     <t xml:space="preserve">2.76334929466248</t>
@@ -2252,37 +2252,37 @@
     <t xml:space="preserve">2.75045776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75625896453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79106664657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68084168434143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79235529899597</t>
+    <t xml:space="preserve">2.75625872612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79106640815735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68084192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">2.72596311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68148636817932</t>
+    <t xml:space="preserve">2.68148612976074</t>
   </si>
   <si>
     <t xml:space="preserve">2.6286301612854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65892601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66279363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63443112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68664312362671</t>
+    <t xml:space="preserve">2.65892577171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66279339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6344313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68664336204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.66666126251221</t>
@@ -2294,49 +2294,49 @@
     <t xml:space="preserve">2.66472721099854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68857717514038</t>
+    <t xml:space="preserve">2.6885769367218</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943781375885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.689866065979</t>
+    <t xml:space="preserve">2.68986630439758</t>
   </si>
   <si>
     <t xml:space="preserve">2.72016167640686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69695687294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65248012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953513145447</t>
+    <t xml:space="preserve">2.69695663452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65247964859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953489303589</t>
   </si>
   <si>
     <t xml:space="preserve">2.7530357837677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73563194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73176407814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76205992698669</t>
+    <t xml:space="preserve">2.73563170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73176431655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76206016540527</t>
   </si>
   <si>
     <t xml:space="preserve">2.75883722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79428958892822</t>
+    <t xml:space="preserve">2.79428935050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.76077079772949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79944610595703</t>
+    <t xml:space="preserve">2.79944634437561</t>
   </si>
   <si>
     <t xml:space="preserve">2.82007312774658</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">2.91160440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90773701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89162230491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89484548568726</t>
+    <t xml:space="preserve">2.90773725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89162254333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89484524726868</t>
   </si>
   <si>
     <t xml:space="preserve">2.95414733886719</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">2.98702144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96897292137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735214233398</t>
+    <t xml:space="preserve">2.96897315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735261917114</t>
   </si>
   <si>
     <t xml:space="preserve">2.91805028915405</t>
@@ -2384,28 +2384,28 @@
     <t xml:space="preserve">3.04181146621704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02118396759033</t>
+    <t xml:space="preserve">3.02118420600891</t>
   </si>
   <si>
     <t xml:space="preserve">3.03665447235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03923296928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04825758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155141830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98895478248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90902614593506</t>
+    <t xml:space="preserve">3.03923273086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04825687408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829243659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98895525932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90902590751648</t>
   </si>
   <si>
     <t xml:space="preserve">2.86003756523132</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">2.84263348579407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78655457496643</t>
+    <t xml:space="preserve">2.78655433654785</t>
   </si>
   <si>
     <t xml:space="preserve">2.7659273147583</t>
@@ -2426,28 +2426,28 @@
     <t xml:space="preserve">2.73434281349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78010845184326</t>
+    <t xml:space="preserve">2.78010869026184</t>
   </si>
   <si>
     <t xml:space="preserve">2.84843492507935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87421846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95608115196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9477014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91869449615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91676139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94705677032471</t>
+    <t xml:space="preserve">2.87421798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9560809135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94770169258118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91869497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91676115989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94705700874329</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031527519226</t>
@@ -2465,22 +2465,22 @@
     <t xml:space="preserve">2.94383382797241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97606372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95479202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95801496505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98959970474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05921506881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11013746261597</t>
+    <t xml:space="preserve">2.97606348991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95479226112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95801520347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98959946632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05921530723572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11013793945312</t>
   </si>
   <si>
     <t xml:space="preserve">3.10884833335876</t>
@@ -2492,79 +2492,79 @@
     <t xml:space="preserve">3.11464977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10240268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09853458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06372737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10175800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12431859970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14945721626282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13592100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661890983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05663704872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698588371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08757710456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12560796737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19071102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15396976470947</t>
+    <t xml:space="preserve">3.10240244865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09853553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06372690200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10175776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12431883811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1494574546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13592123985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661843299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05663728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696822166443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0875768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12560820579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19071125984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15397000312805</t>
   </si>
   <si>
     <t xml:space="preserve">3.15010213851929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17781925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20553660392761</t>
+    <t xml:space="preserve">3.17781901359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20553684234619</t>
   </si>
   <si>
     <t xml:space="preserve">3.22680807113647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22165131568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21262717247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23325371742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001311302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21391654014587</t>
+    <t xml:space="preserve">3.22165155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21262693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23325419425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21391630172729</t>
   </si>
   <si>
     <t xml:space="preserve">3.23969984054565</t>
@@ -2573,49 +2573,49 @@
     <t xml:space="preserve">3.26548314094543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2474353313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229599952698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388026237488</t>
+    <t xml:space="preserve">3.24743461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2222957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388097763062</t>
   </si>
   <si>
     <t xml:space="preserve">3.28739976882935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31447243690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185813903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39955735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116046905518</t>
+    <t xml:space="preserve">3.31447196006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3995578289032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41115999221802</t>
   </si>
   <si>
     <t xml:space="preserve">3.43307638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4910888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.438232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4537034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311170578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600347518921</t>
+    <t xml:space="preserve">3.49108934402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304105758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823289871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45370244979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311194419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600323677063</t>
   </si>
   <si>
     <t xml:space="preserve">3.41631698608398</t>
@@ -2627,37 +2627,37 @@
     <t xml:space="preserve">3.41373872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44596862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920851707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3454122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38924407958984</t>
+    <t xml:space="preserve">3.44596815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987086296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34541249275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994222640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38924479484558</t>
   </si>
   <si>
     <t xml:space="preserve">3.38795518875122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34799027442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29126715660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2719292640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32865309715271</t>
+    <t xml:space="preserve">3.3479905128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29126691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192950248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32865285873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.36861753463745</t>
@@ -2669,52 +2669,52 @@
     <t xml:space="preserve">3.43694376945496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4240517616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42147374153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47819781303406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45499205589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37635254859924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35572552680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22938704490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30544757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33252048492432</t>
+    <t xml:space="preserve">3.42405152320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45499229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3763530254364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35572576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22938656806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30544805526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3325207233429</t>
   </si>
   <si>
     <t xml:space="preserve">3.31576108932495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23841094970703</t>
+    <t xml:space="preserve">3.23841071128845</t>
   </si>
   <si>
     <t xml:space="preserve">3.1475236415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1849102973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006609916687</t>
+    <t xml:space="preserve">3.18490958213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006657600403</t>
   </si>
   <si>
     <t xml:space="preserve">3.16815090179443</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">3.13205361366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09982442855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12238454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04890179634094</t>
+    <t xml:space="preserve">3.09982466697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12238478660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04890203475952</t>
   </si>
   <si>
     <t xml:space="preserve">3.11593890190125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14623475074768</t>
+    <t xml:space="preserve">3.1462345123291</t>
   </si>
   <si>
     <t xml:space="preserve">3.02182912826538</t>
@@ -2747,58 +2747,58 @@
     <t xml:space="preserve">2.96703910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00958180427551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04310035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09466767311096</t>
+    <t xml:space="preserve">3.00958228111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04310059547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09466743469238</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848159790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18297648429871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40084671974182</t>
+    <t xml:space="preserve">3.15848207473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18297624588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4008469581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.44854617118835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47561931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39440059661865</t>
+    <t xml:space="preserve">3.54394555091858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47561955451965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39440107345581</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459654808044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1423671245575</t>
+    <t xml:space="preserve">3.14236688613892</t>
   </si>
   <si>
     <t xml:space="preserve">3.01409411430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88582110404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272227287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610512733459</t>
+    <t xml:space="preserve">2.8858208656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7427225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017981529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610536575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.51969480514526</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">2.24896812438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15937042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17741847038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646670818329</t>
+    <t xml:space="preserve">2.15936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17741870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646718502045</t>
   </si>
   <si>
     <t xml:space="preserve">1.88993239402771</t>
@@ -2822,88 +2822,88 @@
     <t xml:space="preserve">1.7661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68817627429962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500655651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91313755512238</t>
+    <t xml:space="preserve">1.6881765127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62500643730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91313767433167</t>
   </si>
   <si>
     <t xml:space="preserve">1.77261734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83965492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93827593326569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94149947166443</t>
+    <t xml:space="preserve">1.83965444564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93827641010284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94149935245514</t>
   </si>
   <si>
     <t xml:space="preserve">2.04141044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90669143199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923436641693</t>
+    <t xml:space="preserve">1.90669167041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923412799835</t>
   </si>
   <si>
     <t xml:space="preserve">2.02013921737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05236840248108</t>
+    <t xml:space="preserve">2.05236864089966</t>
   </si>
   <si>
     <t xml:space="preserve">1.98662066459656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11295986175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12327289581299</t>
+    <t xml:space="preserve">2.11295962333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12327337265015</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912755966187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04850125312805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09104371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278848171234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92087244987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93892109394073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9028240442276</t>
+    <t xml:space="preserve">2.04850101470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0910439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278836250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92087256908417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93892085552216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90282440185547</t>
   </si>
   <si>
     <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89766728878021</t>
+    <t xml:space="preserve">1.8976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379990100861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99693369865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06010365486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05623579025269</t>
+    <t xml:space="preserve">1.99693417549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06010341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05623602867126</t>
   </si>
   <si>
     <t xml:space="preserve">2.0265851020813</t>
@@ -2912,28 +2912,28 @@
     <t xml:space="preserve">2.02529573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04463338851929</t>
+    <t xml:space="preserve">2.04463315010071</t>
   </si>
   <si>
     <t xml:space="preserve">2.04721188545227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752515792847</t>
+    <t xml:space="preserve">2.05752491950989</t>
   </si>
   <si>
     <t xml:space="preserve">2.01627159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01756072044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790967464447</t>
+    <t xml:space="preserve">2.0175609588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790991306305</t>
   </si>
   <si>
     <t xml:space="preserve">1.97243964672089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32651400566101</t>
+    <t xml:space="preserve">2.32651424407959</t>
   </si>
   <si>
     <t xml:space="preserve">2.22702956199646</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17018151283264</t>
+    <t xml:space="preserve">2.17018127441406</t>
   </si>
   <si>
     <t xml:space="preserve">2.21992373466492</t>
@@ -2954,37 +2954,37 @@
     <t xml:space="preserve">2.27535080909729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26540207862854</t>
+    <t xml:space="preserve">2.26540231704712</t>
   </si>
   <si>
     <t xml:space="preserve">2.31372332572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24266266822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25687503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39046835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52406167984009</t>
+    <t xml:space="preserve">2.24266290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25687527656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39046859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46863484382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.63633704185486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61644005775452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48995280265808</t>
+    <t xml:space="preserve">2.6164402961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56669783592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48995304107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.37909889221191</t>
@@ -2996,40 +2996,40 @@
     <t xml:space="preserve">2.38762593269348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005581855774</t>
+    <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
     <t xml:space="preserve">2.44873785972595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47574067115784</t>
+    <t xml:space="preserve">2.47574090957642</t>
   </si>
   <si>
     <t xml:space="preserve">2.451580286026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44021081924438</t>
+    <t xml:space="preserve">2.44021058082581</t>
   </si>
   <si>
     <t xml:space="preserve">2.40325951576233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41889262199402</t>
+    <t xml:space="preserve">2.41889238357544</t>
   </si>
   <si>
     <t xml:space="preserve">2.42457723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48284649848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46010756492615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43310499191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53258872032166</t>
+    <t xml:space="preserve">2.48284673690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46010732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43310475349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53258895874023</t>
   </si>
   <si>
     <t xml:space="preserve">2.53116798400879</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">2.55817055702209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57238268852234</t>
+    <t xml:space="preserve">2.57238245010376</t>
   </si>
   <si>
     <t xml:space="preserve">2.58091020584106</t>
@@ -3047,16 +3047,16 @@
     <t xml:space="preserve">2.51127099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53685259819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5652768611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60933399200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64202189445496</t>
+    <t xml:space="preserve">2.53685283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56527662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60933423042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64202213287354</t>
   </si>
   <si>
     <t xml:space="preserve">2.63207340240479</t>
@@ -3071,64 +3071,64 @@
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76424551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64770698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61501908302307</t>
+    <t xml:space="preserve">2.7642457485199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64770674705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61501932144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.60649180412292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4572651386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54680109024048</t>
+    <t xml:space="preserve">2.45726490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5468008518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186713218689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66049742698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68465828895569</t>
+    <t xml:space="preserve">2.66049718856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68465805053711</t>
   </si>
   <si>
     <t xml:space="preserve">2.7528760433197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89073276519775</t>
+    <t xml:space="preserve">2.89073300361633</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768406867981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89641809463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92199945449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86373019218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83388471603394</t>
+    <t xml:space="preserve">2.89641785621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92199969291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86372995376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83388447761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.88931179046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8495180606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84099078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91773581504822</t>
+    <t xml:space="preserve">2.84951782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9177360534668</t>
   </si>
   <si>
     <t xml:space="preserve">2.93479061126709</t>
@@ -3137,28 +3137,28 @@
     <t xml:space="preserve">2.95895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94616007804871</t>
+    <t xml:space="preserve">2.94615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">2.94900250434875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87083625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88789033889771</t>
+    <t xml:space="preserve">2.87083601951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88789057731628</t>
   </si>
   <si>
     <t xml:space="preserve">2.85378122329712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81256628036499</t>
+    <t xml:space="preserve">2.81256675720215</t>
   </si>
   <si>
     <t xml:space="preserve">2.78556370735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90068101882935</t>
+    <t xml:space="preserve">2.90068125724792</t>
   </si>
   <si>
     <t xml:space="preserve">2.87794208526611</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">2.94189620018005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95184469223022</t>
+    <t xml:space="preserve">2.95184445381165</t>
   </si>
   <si>
     <t xml:space="preserve">2.9575297832489</t>
@@ -3176,25 +3176,25 @@
     <t xml:space="preserve">2.93621158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91489362716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85662412643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70313382148743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74861216545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69602799415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70455503463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765523910522</t>
+    <t xml:space="preserve">2.91489386558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85662388801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70313358306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74861240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69602751731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70455479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6576554775238</t>
   </si>
   <si>
     <t xml:space="preserve">2.72729420661926</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">2.68039441108704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62354612350464</t>
+    <t xml:space="preserve">2.62354636192322</t>
   </si>
   <si>
     <t xml:space="preserve">2.63065218925476</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">2.61359786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56243419647217</t>
+    <t xml:space="preserve">2.56243395805359</t>
   </si>
   <si>
     <t xml:space="preserve">2.45868611335754</t>
@@ -3236,16 +3236,16 @@
     <t xml:space="preserve">2.48853182792664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4970588684082</t>
+    <t xml:space="preserve">2.49705910682678</t>
   </si>
   <si>
     <t xml:space="preserve">2.52690410614014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48568892478943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42742013931274</t>
+    <t xml:space="preserve">2.48568916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42741990089417</t>
   </si>
   <si>
     <t xml:space="preserve">2.39899563789368</t>
@@ -3254,19 +3254,19 @@
     <t xml:space="preserve">2.37199282646179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25403261184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23129296302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276592254639</t>
+    <t xml:space="preserve">2.25403237342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23129320144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276616096497</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37057137489319</t>
+    <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
     <t xml:space="preserve">2.39473176002502</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">2.52264046669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52832531929016</t>
+    <t xml:space="preserve">2.52832555770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.55532836914062</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">2.71450328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76850914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7400848865509</t>
+    <t xml:space="preserve">2.76850938796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74008512496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.84383296966553</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">2.90920853614807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81967258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80972409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78840589523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78130006790161</t>
+    <t xml:space="preserve">2.81967282295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8097243309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78840613365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78130030632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.78272128105164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77561497688293</t>
+    <t xml:space="preserve">2.77561521530151</t>
   </si>
   <si>
     <t xml:space="preserve">2.70597624778748</t>
@@ -3335,22 +3335,22 @@
     <t xml:space="preserve">2.7130823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75998187065125</t>
+    <t xml:space="preserve">2.75998210906982</t>
   </si>
   <si>
     <t xml:space="preserve">2.79835438728333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72871541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75429677963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75571823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79267001152039</t>
+    <t xml:space="preserve">2.72871565818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75429725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75571846961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79266977310181</t>
   </si>
   <si>
     <t xml:space="preserve">2.77419400215149</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">2.75713968276978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83246350288391</t>
+    <t xml:space="preserve">2.83246374130249</t>
   </si>
   <si>
     <t xml:space="preserve">2.8608877658844</t>
@@ -3380,22 +3380,22 @@
     <t xml:space="preserve">2.88362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84241199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76993036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74719095230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79551219940186</t>
+    <t xml:space="preserve">2.8424117565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76993060112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7471911907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79551243782043</t>
   </si>
   <si>
     <t xml:space="preserve">2.67897343635559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68181586265564</t>
+    <t xml:space="preserve">2.68181562423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74576997756958</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">2.57522535324097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64486455917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546045303345</t>
+    <t xml:space="preserve">2.644864320755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546069145203</t>
   </si>
   <si>
     <t xml:space="preserve">2.86657238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758129119873</t>
+    <t xml:space="preserve">2.94758081436157</t>
   </si>
   <si>
     <t xml:space="preserve">3.13233804702759</t>
@@ -3425,37 +3425,37 @@
     <t xml:space="preserve">3.10533475875854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18350148200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14939284324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13944435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15791988372803</t>
+    <t xml:space="preserve">3.18350172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14939260482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13944411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15791964530945</t>
   </si>
   <si>
     <t xml:space="preserve">3.12665343284607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.039959192276</t>
+    <t xml:space="preserve">3.03995966911316</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01153540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03427457809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08259582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13375926017761</t>
+    <t xml:space="preserve">3.01153516769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03427481651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08259558677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13375902175903</t>
   </si>
   <si>
     <t xml:space="preserve">3.11812591552734</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">3.05843496322632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19344997406006</t>
+    <t xml:space="preserve">3.19345021247864</t>
   </si>
   <si>
     <t xml:space="preserve">3.16928935050964</t>
@@ -3476,31 +3476,31 @@
     <t xml:space="preserve">3.2517192363739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1479709148407</t>
+    <t xml:space="preserve">3.14797067642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.30004024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28867030143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3014612197876</t>
+    <t xml:space="preserve">3.28867053985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435563087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30146145820618</t>
   </si>
   <si>
     <t xml:space="preserve">3.32562184333801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30572533607483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110042572021</t>
+    <t xml:space="preserve">3.30572509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3526246547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110066413879</t>
   </si>
   <si>
     <t xml:space="preserve">3.41942119598389</t>
@@ -3509,19 +3509,19 @@
     <t xml:space="preserve">3.36967968940735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26450967788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27587938308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3085675239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947294235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37962794303894</t>
+    <t xml:space="preserve">3.26450991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27587962150574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856776237488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947270393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37962770462036</t>
   </si>
   <si>
     <t xml:space="preserve">3.38247036933899</t>
@@ -3530,31 +3530,31 @@
     <t xml:space="preserve">3.40378785133362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42013239860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32846403121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29790830612183</t>
+    <t xml:space="preserve">3.42013216018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32846450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29790878295898</t>
   </si>
   <si>
     <t xml:space="preserve">3.33272814750671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35902070999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3668372631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34978246688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42723822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500350952148</t>
+    <t xml:space="preserve">3.35902047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36683678627014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34978270530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42723798751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500303268433</t>
   </si>
   <si>
     <t xml:space="preserve">3.32206892967224</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">3.28014349937439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2971978187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31567335128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33201694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430388450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31780552864075</t>
+    <t xml:space="preserve">3.29719758033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.315673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33201718330383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430364608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31780576705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.28440690040588</t>
@@ -3584,10 +3584,10 @@
     <t xml:space="preserve">3.23679661750793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31211996078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27232646942139</t>
+    <t xml:space="preserve">3.31212019920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232670783997</t>
   </si>
   <si>
     <t xml:space="preserve">3.31283140182495</t>
@@ -3599,19 +3599,19 @@
     <t xml:space="preserve">3.48550772666931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47555899620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49545645713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48124432563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57575392723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143925666809</t>
+    <t xml:space="preserve">3.47555875778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49545621871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48124408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143949508667</t>
   </si>
   <si>
     <t xml:space="preserve">3.53027558326721</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">3.49829816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52459073066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61421155929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52383756637573</t>
+    <t xml:space="preserve">3.52459120750427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61421203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52383780479431</t>
   </si>
   <si>
     <t xml:space="preserve">3.38902974128723</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">3.43120431900024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41614151000977</t>
+    <t xml:space="preserve">3.41614174842834</t>
   </si>
   <si>
     <t xml:space="preserve">3.44927906990051</t>
@@ -3650,16 +3650,16 @@
     <t xml:space="preserve">3.47488474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831632614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.488440990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46132922172546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45078492164612</t>
+    <t xml:space="preserve">3.45831608772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844075202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46132898330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45078468322754</t>
   </si>
   <si>
     <t xml:space="preserve">3.44626665115356</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752341270447</t>
+    <t xml:space="preserve">3.38752365112305</t>
   </si>
   <si>
     <t xml:space="preserve">3.36041116714478</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">3.3250150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24744319915771</t>
+    <t xml:space="preserve">3.24744343757629</t>
   </si>
   <si>
     <t xml:space="preserve">3.27229619026184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23765301704407</t>
+    <t xml:space="preserve">3.23765277862549</t>
   </si>
   <si>
     <t xml:space="preserve">3.21129393577576</t>
@@ -3695,16 +3695,16 @@
     <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21430611610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24970293045044</t>
+    <t xml:space="preserve">3.21430635452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24970269203186</t>
   </si>
   <si>
     <t xml:space="preserve">3.39279556274414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35062074661255</t>
+    <t xml:space="preserve">3.35062050819397</t>
   </si>
   <si>
     <t xml:space="preserve">3.37697982788086</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2948899269104</t>
+    <t xml:space="preserve">3.29489016532898</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731853485107</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">3.30468058586121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31673049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329916000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32953333854675</t>
+    <t xml:space="preserve">3.316730260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329939842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32953357696533</t>
   </si>
   <si>
     <t xml:space="preserve">3.29112410545349</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">3.28208661079407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14878535270691</t>
+    <t xml:space="preserve">3.14878511428833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19999718666077</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">3.33028650283813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33480525016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38601684570312</t>
+    <t xml:space="preserve">3.33480501174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3860170841217</t>
   </si>
   <si>
     <t xml:space="preserve">3.37321424484253</t>
@@ -3764,19 +3764,19 @@
     <t xml:space="preserve">3.4071044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38149833679199</t>
+    <t xml:space="preserve">3.38149857521057</t>
   </si>
   <si>
     <t xml:space="preserve">3.42141366004944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37170815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36643552780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3920419216156</t>
+    <t xml:space="preserve">3.37170791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36643576622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39204216003418</t>
   </si>
   <si>
     <t xml:space="preserve">3.48994755744934</t>
@@ -3791,58 +3791,58 @@
     <t xml:space="preserve">3.6164710521698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65337371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981795310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6307806968689</t>
+    <t xml:space="preserve">3.65337347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63981771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63078045845032</t>
   </si>
   <si>
     <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72040152549744</t>
+    <t xml:space="preserve">3.72040176391602</t>
   </si>
   <si>
     <t xml:space="preserve">3.6752142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66542387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75052618980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77462601661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77311944961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79872632026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77613210678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78215718269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.767094373703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78667569160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73696994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77763843536377</t>
+    <t xml:space="preserve">3.66542410850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75052642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7746262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77311968803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79872608184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77613186836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7821569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76709461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78667593002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7369704246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77763867378235</t>
   </si>
   <si>
     <t xml:space="preserve">3.71663570404053</t>
@@ -3857,49 +3857,49 @@
     <t xml:space="preserve">3.63755798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68726420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66994214057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638613700867</t>
+    <t xml:space="preserve">3.68726396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6699423789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638637542725</t>
   </si>
   <si>
     <t xml:space="preserve">3.72567343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67144846916199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258104324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132380485535</t>
+    <t xml:space="preserve">3.67144870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258080482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64132404327393</t>
   </si>
   <si>
     <t xml:space="preserve">3.75429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80926918983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450135231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625677108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84541940689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83939433097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90717458724976</t>
+    <t xml:space="preserve">3.75203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80926942825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450182914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80625629425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84541916847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83939409255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90717506408691</t>
   </si>
   <si>
     <t xml:space="preserve">3.88006234169006</t>
@@ -3908,22 +3908,22 @@
     <t xml:space="preserve">3.9538676738739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97947382926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95989274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483017921448</t>
+    <t xml:space="preserve">3.97947359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483089447021</t>
   </si>
   <si>
     <t xml:space="preserve">3.89060616493225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92976784706116</t>
+    <t xml:space="preserve">3.88307499885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92976856231689</t>
   </si>
   <si>
     <t xml:space="preserve">3.95682621002197</t>
@@ -6558,6 +6558,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.4850006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3549995422363</t>
   </si>
 </sst>
 </file>
@@ -71610,7 +71613,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6520023148</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>1573143</v>
@@ -71631,6 +71634,32 @@
         <v>2181</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6521990741</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>1312424</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>18.5499992370605</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>18.1100006103516</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>18.4799995422363</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>18.3549995422363</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="2183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="2184">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528818130493</t>
+    <t xml:space="preserve">2.44528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -47,217 +47,217 @@
     <t xml:space="preserve">2.50193190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40895128250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35658240318298</t>
+    <t xml:space="preserve">2.40895080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35658264160156</t>
   </si>
   <si>
     <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29780173301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37261343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795686721802</t>
+    <t xml:space="preserve">2.29780149459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37261366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795734405518</t>
   </si>
   <si>
     <t xml:space="preserve">2.33413863182068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2347457408905</t>
+    <t xml:space="preserve">2.23474550247192</t>
   </si>
   <si>
     <t xml:space="preserve">2.15458965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11183977127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99641561508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588363647461</t>
+    <t xml:space="preserve">2.11184000968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99641585350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588387489319</t>
   </si>
   <si>
     <t xml:space="preserve">2.07977771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03489065170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03168416023254</t>
+    <t xml:space="preserve">2.03489017486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03168392181396</t>
   </si>
   <si>
     <t xml:space="preserve">2.0295467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90343463420868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00924015045166</t>
+    <t xml:space="preserve">1.90343451499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00924038887024</t>
   </si>
   <si>
     <t xml:space="preserve">1.93549704551697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84037888050079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701653957367</t>
+    <t xml:space="preserve">1.84037852287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74953496456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">1.67792952060699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349870681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151154518127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861675262451</t>
+    <t xml:space="preserve">1.59349882602692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151142597198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861699104309</t>
   </si>
   <si>
     <t xml:space="preserve">1.55823004245758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60632348060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72922933101654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899811267853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312281608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350417613983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69396030902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419176578522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70571672916412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296744346619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533572673798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82541620731354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8232786655426</t>
+    <t xml:space="preserve">1.60632336139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72922921180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67899835109711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7431229352951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69396066665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419164657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70571684837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7153354883194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82541608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82327902317047</t>
   </si>
   <si>
     <t xml:space="preserve">1.88099098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89381587505341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488482475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8660284280777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404150485992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556646823883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82648468017578</t>
+    <t xml:space="preserve">1.89381575584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488470554352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86602830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404138565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556634902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82648491859436</t>
   </si>
   <si>
     <t xml:space="preserve">1.79976630210876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.920534491539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442845344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229067325592</t>
+    <t xml:space="preserve">1.92053461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442785739899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93229079246521</t>
   </si>
   <si>
     <t xml:space="preserve">1.96221566200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96435296535492</t>
+    <t xml:space="preserve">1.96435308456421</t>
   </si>
   <si>
     <t xml:space="preserve">1.97183430194855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95580315589905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95259690284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92374086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87564718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88312840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91198492050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90022826194763</t>
+    <t xml:space="preserve">1.95580303668976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95259714126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92374074459076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87564742565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8831285238266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.911985039711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90022838115692</t>
   </si>
   <si>
     <t xml:space="preserve">1.89167833328247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579744815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8019038438797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129733085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92587840557098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92801570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91519105434418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0177903175354</t>
+    <t xml:space="preserve">1.81579756736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81793510913849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80190360546112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992250919342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129721164703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465324878693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92801582813263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91519093513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01779079437256</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626511573792</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0551962852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05092167854309</t>
+    <t xml:space="preserve">2.05519652366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05092144012451</t>
   </si>
   <si>
     <t xml:space="preserve">1.99855291843414</t>
@@ -287,76 +287,76 @@
     <t xml:space="preserve">1.99214041233063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95045948028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93977189064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84999740123749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79121661186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73884797096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388589382172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502937793732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678579807281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70785450935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235270500183</t>
+    <t xml:space="preserve">1.95045936107635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93977200984955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8499972820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457859516144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7912163734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73884809017181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6950296163559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678567886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70785462856293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235246658325</t>
   </si>
   <si>
     <t xml:space="preserve">1.83700942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87773132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87546920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279697418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90601050853729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451814651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081212520599</t>
+    <t xml:space="preserve">1.87773144245148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8754688501358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279745101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90601027011871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451838493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081224441528</t>
   </si>
   <si>
     <t xml:space="preserve">1.80986154079437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81438589096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80646824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75104081630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63113796710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54290699958801</t>
+    <t xml:space="preserve">1.81438612937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80646812915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75104069709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63113784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54290688037872</t>
   </si>
   <si>
     <t xml:space="preserve">1.46711909770966</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">1.42526602745056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51689016819</t>
+    <t xml:space="preserve">1.51689004898071</t>
   </si>
   <si>
     <t xml:space="preserve">1.61190795898438</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">1.6005961894989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57684195041656</t>
+    <t xml:space="preserve">1.57684206962585</t>
   </si>
   <si>
     <t xml:space="preserve">1.69900751113892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38341271877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24201738834381</t>
+    <t xml:space="preserve">1.38341283798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
     <t xml:space="preserve">1.27255892753601</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">1.19111514091492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23636186122894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18545937538147</t>
+    <t xml:space="preserve">1.23636174201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18545925617218</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021277427673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0994907617569</t>
+    <t xml:space="preserve">1.09949100017548</t>
   </si>
   <si>
     <t xml:space="preserve">1.09722852706909</t>
@@ -416,67 +416,67 @@
     <t xml:space="preserve">1.23749279975891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28726422786713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36870777606964</t>
+    <t xml:space="preserve">1.28726398944855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36870765686035</t>
   </si>
   <si>
     <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39359319210052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38454389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4003803730011</t>
+    <t xml:space="preserve">1.39359354972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38454401493073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40038049221039</t>
   </si>
   <si>
     <t xml:space="preserve">1.36983895301819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39811789989471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37888813018799</t>
+    <t xml:space="preserve">1.398118019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37888824939728</t>
   </si>
   <si>
     <t xml:space="preserve">1.37097024917603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37775707244873</t>
+    <t xml:space="preserve">1.37775719165802</t>
   </si>
   <si>
     <t xml:space="preserve">1.42979085445404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40264272689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38567507266998</t>
+    <t xml:space="preserve">1.40264248847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38567519187927</t>
   </si>
   <si>
     <t xml:space="preserve">1.26011598110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29631316661835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32232999801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37549471855164</t>
+    <t xml:space="preserve">1.29631340503693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32233023643494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37549459934235</t>
   </si>
   <si>
     <t xml:space="preserve">1.43657767772675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45354497432709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44788932800293</t>
+    <t xml:space="preserve">1.4535448551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44788920879364</t>
   </si>
   <si>
     <t xml:space="preserve">1.47051227092743</t>
@@ -485,49 +485,49 @@
     <t xml:space="preserve">1.45015156269073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41961002349854</t>
+    <t xml:space="preserve">1.41961014270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.38001954555511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39698696136475</t>
+    <t xml:space="preserve">1.39698684215546</t>
   </si>
   <si>
     <t xml:space="preserve">1.33137941360474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3325103521347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38228189945221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3675764799118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816659450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35400283336639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3279857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41056084632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40377366542816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42413485050201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43883991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45920085906982</t>
+    <t xml:space="preserve">1.33251059055328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38228166103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36757659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816647529602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3540027141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32798600196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41056072711945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40377378463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42413473129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43883979320526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45920073986053</t>
   </si>
   <si>
     <t xml:space="preserve">1.47729957103729</t>
@@ -536,67 +536,67 @@
     <t xml:space="preserve">1.48748004436493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48974239826202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019989967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40716743469238</t>
+    <t xml:space="preserve">1.48974227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39019978046417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40716707706451</t>
   </si>
   <si>
     <t xml:space="preserve">1.36078953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513389110565</t>
+    <t xml:space="preserve">1.41282331943512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513377189636</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947800636292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34269106388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821457386017</t>
+    <t xml:space="preserve">1.34269118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536258220673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821481227875</t>
   </si>
   <si>
     <t xml:space="preserve">1.31780540943146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28613293170929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28500187397003</t>
+    <t xml:space="preserve">1.2861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28500175476074</t>
   </si>
   <si>
     <t xml:space="preserve">1.27934598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35174036026001</t>
+    <t xml:space="preserve">1.35174024105072</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37210130691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39472448825836</t>
+    <t xml:space="preserve">1.37210118770599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39472460746765</t>
   </si>
   <si>
     <t xml:space="preserve">1.41621673107147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44110238552094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4931355714798</t>
+    <t xml:space="preserve">1.44110250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49313580989838</t>
   </si>
   <si>
     <t xml:space="preserve">1.52480840682983</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">1.53159523010254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51575911045074</t>
+    <t xml:space="preserve">1.51575922966003</t>
   </si>
   <si>
     <t xml:space="preserve">1.54856288433075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56553018093109</t>
+    <t xml:space="preserve">1.56553030014038</t>
   </si>
   <si>
     <t xml:space="preserve">1.61077678203583</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">1.63453125953674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59833371639252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571065425873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118618488312</t>
+    <t xml:space="preserve">1.59833407402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118606567383</t>
   </si>
   <si>
     <t xml:space="preserve">1.50444734096527</t>
@@ -650,70 +650,70 @@
     <t xml:space="preserve">1.66167914867401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905572891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172760486603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57457947731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661325931549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58476006984711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56100559234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064440727234</t>
+    <t xml:space="preserve">1.63905584812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172736644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5745792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62661290168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5847601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5610054731369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064476490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.60512089729309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64923620223999</t>
+    <t xml:space="preserve">1.64923632144928</t>
   </si>
   <si>
     <t xml:space="preserve">1.66620373725891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62435078620911</t>
+    <t xml:space="preserve">1.6243509054184</t>
   </si>
   <si>
     <t xml:space="preserve">1.72049939632416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79741895198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8528459072113</t>
+    <t xml:space="preserve">1.79741859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284554958344</t>
   </si>
   <si>
     <t xml:space="preserve">1.84492754936218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83022272586823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86302614212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623943805695</t>
+    <t xml:space="preserve">1.83022248744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86302638053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623908042908</t>
   </si>
   <si>
     <t xml:space="preserve">1.91053509712219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922344684601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91166639328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92637133598328</t>
+    <t xml:space="preserve">1.89922368526459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91166615486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92637157440186</t>
   </si>
   <si>
     <t xml:space="preserve">1.94560110569</t>
@@ -725,43 +725,43 @@
     <t xml:space="preserve">1.89696097373962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655180931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98066711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01347088813782</t>
+    <t xml:space="preserve">1.93655204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066747188568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0134711265564</t>
   </si>
   <si>
     <t xml:space="preserve">2.00781488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01573300361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01912641525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9648312330246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99876570701599</t>
+    <t xml:space="preserve">2.01573324203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01912665367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96483087539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99876594543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.0202579498291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727382183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007747650146</t>
+    <t xml:space="preserve">1.97727406024933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007771492004</t>
   </si>
   <si>
     <t xml:space="preserve">1.97161781787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9478634595871</t>
+    <t xml:space="preserve">1.94786322116852</t>
   </si>
   <si>
     <t xml:space="preserve">1.97953593730927</t>
@@ -770,76 +770,76 @@
     <t xml:space="preserve">2.02252006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08247184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08699607849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193066596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202722072601</t>
+    <t xml:space="preserve">1.99084758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247208595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08699655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05079936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542075157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202698230743</t>
   </si>
   <si>
     <t xml:space="preserve">1.96709322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894594192505</t>
+    <t xml:space="preserve">2.00894618034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.90940392017365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89130532741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320673465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999331951141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510802268982</t>
+    <t xml:space="preserve">1.89130556583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.873206615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999379634857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510790348053</t>
   </si>
   <si>
     <t xml:space="preserve">1.96596217155457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03609442710876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424135684967</t>
+    <t xml:space="preserve">2.03609418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424088001251</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329041481018</t>
+    <t xml:space="preserve">2.00329065322876</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478241920471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01799559593201</t>
+    <t xml:space="preserve">2.01799583435059</t>
   </si>
   <si>
     <t xml:space="preserve">2.00442147254944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95465052127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02930736541748</t>
+    <t xml:space="preserve">1.9546502828598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0293071269989</t>
   </si>
   <si>
     <t xml:space="preserve">2.02817606925964</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">2.09265232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13224315643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432527542114</t>
+    <t xml:space="preserve">2.13224339485168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12432479858398</t>
   </si>
   <si>
     <t xml:space="preserve">2.12093138694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1593906879425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373539924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016127586365</t>
+    <t xml:space="preserve">2.15939140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016103744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.1084885597229</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14921045303345</t>
+    <t xml:space="preserve">2.14921069145203</t>
   </si>
   <si>
     <t xml:space="preserve">2.19332575798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17862105369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23291635513306</t>
+    <t xml:space="preserve">2.17862057685852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23291707038879</t>
   </si>
   <si>
     <t xml:space="preserve">2.19558811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20803117752075</t>
+    <t xml:space="preserve">2.20803141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.20576882362366</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">2.16617798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20350623130798</t>
+    <t xml:space="preserve">2.2035059928894</t>
   </si>
   <si>
     <t xml:space="preserve">2.19219470024109</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">2.15825986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20011281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17522764205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17748975753784</t>
+    <t xml:space="preserve">2.20011305809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17522740364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17748951911926</t>
   </si>
   <si>
     <t xml:space="preserve">2.15599751472473</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">2.14129209518433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09378361701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07907819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08812761306763</t>
+    <t xml:space="preserve">2.09378337860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07907843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08812785148621</t>
   </si>
   <si>
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10961985588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22273635864258</t>
+    <t xml:space="preserve">2.10961961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22273659706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.26232695579529</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">2.25780248641968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31436061859131</t>
+    <t xml:space="preserve">2.31436038017273</t>
   </si>
   <si>
     <t xml:space="preserve">2.33132815361023</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">2.40032887458801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41164064407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43878841400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127945899963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3256721496582</t>
+    <t xml:space="preserve">2.41164040565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43878793716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44557499885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127993583679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32567191123962</t>
   </si>
   <si>
     <t xml:space="preserve">2.38675475120544</t>
@@ -989,40 +989,40 @@
     <t xml:space="preserve">2.25893330574036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24988436698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27137589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33769392967224</t>
+    <t xml:space="preserve">2.24988412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27137613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33769369125366</t>
   </si>
   <si>
     <t xml:space="preserve">2.30216670036316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36137866973877</t>
+    <t xml:space="preserve">2.36137890815735</t>
   </si>
   <si>
     <t xml:space="preserve">2.35072040557861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30808782577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453261375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926951408386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558477401733</t>
+    <t xml:space="preserve">2.30808758735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453237533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926975250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558429718018</t>
   </si>
   <si>
     <t xml:space="preserve">2.21097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18137359619141</t>
+    <t xml:space="preserve">2.18137383460999</t>
   </si>
   <si>
     <t xml:space="preserve">2.1458466053009</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">2.14110946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14229393005371</t>
+    <t xml:space="preserve">2.14229369163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.16361021995544</t>
@@ -1046,37 +1046,37 @@
     <t xml:space="preserve">2.18611097335815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13874101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.119793176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1493992805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13755679130554</t>
+    <t xml:space="preserve">2.13874125480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11979293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14939951896667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13755702972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1553201675415</t>
+    <t xml:space="preserve">2.15532064437866</t>
   </si>
   <si>
     <t xml:space="preserve">2.20032167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18374252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27374482154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453768730164</t>
+    <t xml:space="preserve">2.18374228477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821759223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27374458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453744888306</t>
   </si>
   <si>
     <t xml:space="preserve">2.38387942314148</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">2.36848425865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37322092056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36966800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3720371723175</t>
+    <t xml:space="preserve">2.37322115898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36966824531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37203693389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.38032650947571</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.38861608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34361505508423</t>
+    <t xml:space="preserve">2.34361481666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.30927205085754</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.28913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29387712478638</t>
+    <t xml:space="preserve">2.2938768863678</t>
   </si>
   <si>
     <t xml:space="preserve">2.33058857917786</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.36019444465637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31637716293335</t>
+    <t xml:space="preserve">2.31637740135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.34479904174805</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.31756186485291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34006237983704</t>
+    <t xml:space="preserve">2.34006214141846</t>
   </si>
   <si>
     <t xml:space="preserve">2.40401124954224</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">2.4099326133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37914228439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35545754432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045603752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25953388214111</t>
+    <t xml:space="preserve">2.37914252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3554573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25953412055969</t>
   </si>
   <si>
     <t xml:space="preserve">2.27966594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25598120689392</t>
+    <t xml:space="preserve">2.25598096847534</t>
   </si>
   <si>
     <t xml:space="preserve">2.23111200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22163796424866</t>
+    <t xml:space="preserve">2.22163820266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.19676923751831</t>
@@ -1172,28 +1172,28 @@
     <t xml:space="preserve">2.19321608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18847942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18492650985718</t>
+    <t xml:space="preserve">2.18847918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18492674827576</t>
   </si>
   <si>
     <t xml:space="preserve">2.13163566589355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16005730628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058398246765</t>
+    <t xml:space="preserve">2.16005754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058350563049</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13045144081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1209774017334</t>
+    <t xml:space="preserve">2.13045167922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12097764015198</t>
   </si>
   <si>
     <t xml:space="preserve">2.11031913757324</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">2.0842661857605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22400689125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24295449256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29624557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28795552253723</t>
+    <t xml:space="preserve">2.22400665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24295425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29624509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28795576095581</t>
   </si>
   <si>
     <t xml:space="preserve">2.25005984306335</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">2.23703336715698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24769139289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29269242286682</t>
+    <t xml:space="preserve">2.24769115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2926926612854</t>
   </si>
   <si>
     <t xml:space="preserve">2.3211145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25716519355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30453515052795</t>
+    <t xml:space="preserve">2.25716543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30453491210938</t>
   </si>
   <si>
     <t xml:space="preserve">2.29742956161499</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">2.25124430656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3187460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27848172187805</t>
+    <t xml:space="preserve">2.31874561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27848196029663</t>
   </si>
   <si>
     <t xml:space="preserve">2.26663947105408</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">2.32703566551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34598326683044</t>
+    <t xml:space="preserve">2.34598350524902</t>
   </si>
   <si>
     <t xml:space="preserve">2.30571937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27729773521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742726325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1482150554657</t>
+    <t xml:space="preserve">2.27729725837708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203162193298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14821481704712</t>
   </si>
   <si>
     <t xml:space="preserve">2.19795322418213</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">2.19913744926453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23348045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23584890365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28084993362427</t>
+    <t xml:space="preserve">2.23348069190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23584914207458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28085017204285</t>
   </si>
   <si>
     <t xml:space="preserve">2.26900768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27256059646606</t>
+    <t xml:space="preserve">2.27256083488464</t>
   </si>
   <si>
     <t xml:space="preserve">2.24177002906799</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">2.25361251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27019190788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26308608055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677153587341</t>
+    <t xml:space="preserve">2.27019214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26308655738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677129745483</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032397270203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30098247528076</t>
+    <t xml:space="preserve">2.30098223686218</t>
   </si>
   <si>
     <t xml:space="preserve">2.33177256584167</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31519317626953</t>
+    <t xml:space="preserve">2.31519341468811</t>
   </si>
   <si>
     <t xml:space="preserve">2.39098477363586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41585397720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41940665245056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4371702671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48098707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53309369087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56743669509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54612040519714</t>
+    <t xml:space="preserve">2.41585373878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41940641403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43717002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48098731040955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53309345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5674364566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54612016677856</t>
   </si>
   <si>
     <t xml:space="preserve">2.56151580810547</t>
@@ -1376,70 +1376,70 @@
     <t xml:space="preserve">2.57691121101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56980538368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56625247001648</t>
+    <t xml:space="preserve">2.56980514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56625270843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.63967537879944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65743899345398</t>
+    <t xml:space="preserve">2.65743923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.66691303253174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63671469688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62960934638977</t>
+    <t xml:space="preserve">2.63671493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62960958480835</t>
   </si>
   <si>
     <t xml:space="preserve">2.58105540275574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57158160209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56921291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48039507865906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53013300895691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45611786842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217129707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44605183601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40697193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236733436584</t>
+    <t xml:space="preserve">2.57158184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56921315193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48039484024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53013277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45611810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217153549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44605207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40697169303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236709594727</t>
   </si>
   <si>
     <t xml:space="preserve">2.4709210395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45552563667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723582267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4655921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.473881483078</t>
+    <t xml:space="preserve">2.45552587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723606109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46559190750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47388172149658</t>
   </si>
   <si>
     <t xml:space="preserve">2.41881465911865</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">2.43480181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40756416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32644319534302</t>
+    <t xml:space="preserve">2.40756392478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32644367218018</t>
   </si>
   <si>
     <t xml:space="preserve">2.33473324775696</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">2.39631366729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37440538406372</t>
+    <t xml:space="preserve">2.3744056224823</t>
   </si>
   <si>
     <t xml:space="preserve">2.35782599449158</t>
@@ -1475,64 +1475,64 @@
     <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611580848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3862476348877</t>
+    <t xml:space="preserve">2.36611557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38624811172485</t>
   </si>
   <si>
     <t xml:space="preserve">2.39986634254456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32881188392639</t>
+    <t xml:space="preserve">2.32881212234497</t>
   </si>
   <si>
     <t xml:space="preserve">2.3524968624115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499737739563</t>
+    <t xml:space="preserve">2.34302258491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499761581421</t>
   </si>
   <si>
     <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39808988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38565540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41230130195618</t>
+    <t xml:space="preserve">2.39809012413025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38565564155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4123010635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.41822218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45078897476196</t>
+    <t xml:space="preserve">2.45078873634338</t>
   </si>
   <si>
     <t xml:space="preserve">2.51769852638245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51355409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54315948486328</t>
+    <t xml:space="preserve">2.51355361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315972328186</t>
   </si>
   <si>
     <t xml:space="preserve">2.54079127311707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54375219345093</t>
+    <t xml:space="preserve">2.54375171661377</t>
   </si>
   <si>
     <t xml:space="preserve">2.58756875991821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61066150665283</t>
+    <t xml:space="preserve">2.61066174507141</t>
   </si>
   <si>
     <t xml:space="preserve">2.58223962783813</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">2.59408235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61480641365051</t>
+    <t xml:space="preserve">2.61480617523193</t>
   </si>
   <si>
     <t xml:space="preserve">2.63493847846985</t>
@@ -1553,43 +1553,43 @@
     <t xml:space="preserve">2.64204406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67165017127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6752028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58638477325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60177946090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55855512619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57039713859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59526658058167</t>
+    <t xml:space="preserve">2.67165040969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67520308494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58638453483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60178017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55855488777161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57039761543274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5934898853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
     <t xml:space="preserve">2.51059293746948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54967331886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48868465423584</t>
+    <t xml:space="preserve">2.54967308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48868441581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.49672627449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48621010780334</t>
+    <t xml:space="preserve">2.48621034622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548393249512</t>
@@ -1598,100 +1598,100 @@
     <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.387850522995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3773341178894</t>
+    <t xml:space="preserve">2.38785076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37733387947083</t>
   </si>
   <si>
     <t xml:space="preserve">2.25917863845825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31176090240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361132621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33464956283569</t>
+    <t xml:space="preserve">2.31176066398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33464980125427</t>
   </si>
   <si>
     <t xml:space="preserve">2.28577923774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23752737045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22577357292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23567152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020059585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2498996257782</t>
+    <t xml:space="preserve">2.23752760887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22577381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23567128181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020083427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24989938735962</t>
   </si>
   <si>
     <t xml:space="preserve">2.2319598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23938274383545</t>
+    <t xml:space="preserve">2.23938298225403</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371361732483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20041012763977</t>
+    <t xml:space="preserve">2.20041036605835</t>
   </si>
   <si>
     <t xml:space="preserve">2.20968985557556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22329926490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20721530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1552517414093</t>
+    <t xml:space="preserve">2.22329902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20721507072449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15525126457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298720359802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05812883377075</t>
+    <t xml:space="preserve">2.05812907218933</t>
   </si>
   <si>
     <t xml:space="preserve">2.05874800682068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05379891395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02843594551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04699444770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04946851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09215307235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10143232345581</t>
+    <t xml:space="preserve">2.05379867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02843546867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04699420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04946875572205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09215259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11689710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
     <t xml:space="preserve">2.14102363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11813473701477</t>
+    <t xml:space="preserve">2.11813497543335</t>
   </si>
   <si>
     <t xml:space="preserve">2.08906006813049</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">2.12679505348206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14349794387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13793015480042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12122750282288</t>
+    <t xml:space="preserve">2.14349770545959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13793039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12122774124146</t>
   </si>
   <si>
     <t xml:space="preserve">2.09957647323608</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473485946655</t>
+    <t xml:space="preserve">2.14473533630371</t>
   </si>
   <si>
     <t xml:space="preserve">2.18061470985413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16514992713928</t>
+    <t xml:space="preserve">2.1651496887207</t>
   </si>
   <si>
     <t xml:space="preserve">2.20102906227112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09029722213745</t>
+    <t xml:space="preserve">2.09029674530029</t>
   </si>
   <si>
     <t xml:space="preserve">2.12432074546814</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">2.10699963569641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13916754722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11999082565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07730627059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0723569393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11937189102173</t>
+    <t xml:space="preserve">2.13916778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1199905872345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07730603218079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07235717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11937212944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.20474076271057</t>
@@ -1766,52 +1766,52 @@
     <t xml:space="preserve">2.28392338752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23319697380066</t>
+    <t xml:space="preserve">2.23319721221924</t>
   </si>
   <si>
     <t xml:space="preserve">2.19174981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24309468269348</t>
+    <t xml:space="preserve">2.24309492111206</t>
   </si>
   <si>
     <t xml:space="preserve">2.26289033889771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25299263000488</t>
+    <t xml:space="preserve">2.2529923915863</t>
   </si>
   <si>
     <t xml:space="preserve">2.26969528198242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27711844444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25608587265015</t>
+    <t xml:space="preserve">2.27711868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25608563423157</t>
   </si>
   <si>
     <t xml:space="preserve">2.24185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19917321205139</t>
+    <t xml:space="preserve">2.19917345046997</t>
   </si>
   <si>
     <t xml:space="preserve">2.2220618724823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27526307106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32846331596375</t>
+    <t xml:space="preserve">2.2752628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32846355438232</t>
   </si>
   <si>
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31423544883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991095542908</t>
+    <t xml:space="preserve">2.31423568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3699107170105</t>
   </si>
   <si>
     <t xml:space="preserve">2.33712410926819</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">2.3340311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36001300811768</t>
+    <t xml:space="preserve">2.3600127696991</t>
   </si>
   <si>
     <t xml:space="preserve">2.40146017074585</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">2.4206371307373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45589804649353</t>
+    <t xml:space="preserve">2.45589780807495</t>
   </si>
   <si>
     <t xml:space="preserve">2.44352579116821</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">2.47012615203857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48682856559753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50600624084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37300372123718</t>
+    <t xml:space="preserve">2.48682880401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50600600242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3730034828186</t>
   </si>
   <si>
     <t xml:space="preserve">2.367436170578</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">2.30743050575256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37795257568359</t>
+    <t xml:space="preserve">2.37795281410217</t>
   </si>
   <si>
     <t xml:space="preserve">2.36496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2709321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28083038330078</t>
+    <t xml:space="preserve">2.27093243598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808301448822</t>
   </si>
   <si>
     <t xml:space="preserve">2.19793581962585</t>
@@ -1880,31 +1880,31 @@
     <t xml:space="preserve">2.1985547542572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20907092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18308925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17504739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19979190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16824245452881</t>
+    <t xml:space="preserve">2.20907115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1830894947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17504715919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19979166984558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16824269294739</t>
   </si>
   <si>
     <t xml:space="preserve">2.15648889541626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09772062301636</t>
+    <t xml:space="preserve">2.0977201461792</t>
   </si>
   <si>
     <t xml:space="preserve">2.13978624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1218466758728</t>
+    <t xml:space="preserve">2.12184643745422</t>
   </si>
   <si>
     <t xml:space="preserve">2.19669890403748</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">2.24433183670044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2474250793457</t>
+    <t xml:space="preserve">2.24742484092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.2597975730896</t>
@@ -1931,55 +1931,55 @@
     <t xml:space="preserve">2.33217525482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34949636459351</t>
+    <t xml:space="preserve">2.34949660301208</t>
   </si>
   <si>
     <t xml:space="preserve">2.26598358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26227211952209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28825330734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22701072692871</t>
+    <t xml:space="preserve">2.26227188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28825354576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22701048851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.2041220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15834498405457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13731169700623</t>
+    <t xml:space="preserve">2.15834474563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1373119354248</t>
   </si>
   <si>
     <t xml:space="preserve">2.23443412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22639226913452</t>
+    <t xml:space="preserve">2.22639203071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24680662155151</t>
+    <t xml:space="preserve">2.24680638313293</t>
   </si>
   <si>
     <t xml:space="preserve">2.23381543159485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15277695655823</t>
+    <t xml:space="preserve">2.15277719497681</t>
   </si>
   <si>
     <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15401458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18556356430054</t>
+    <t xml:space="preserve">2.15401434898376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18556380271912</t>
   </si>
   <si>
     <t xml:space="preserve">2.21278262138367</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1762843132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14040470123291</t>
+    <t xml:space="preserve">2.17628407478333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14040493965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.27959299087524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3241331577301</t>
+    <t xml:space="preserve">2.32413339614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.31794691085815</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">2.38846898078918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41012048721313</t>
+    <t xml:space="preserve">2.41012024879456</t>
   </si>
   <si>
     <t xml:space="preserve">2.43053460121155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32227730751038</t>
+    <t xml:space="preserve">2.32227754592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
@@ -2030,37 +2030,37 @@
     <t xml:space="preserve">2.41259527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.434246301651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.449711561203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5511646270752</t>
+    <t xml:space="preserve">2.43424654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44971203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342373847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930853843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55116486549377</t>
   </si>
   <si>
     <t xml:space="preserve">2.53260636329651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47321891784668</t>
+    <t xml:space="preserve">2.47321915626526</t>
   </si>
   <si>
     <t xml:space="preserve">2.47136330604553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50043821334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5152850151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52394580841064</t>
+    <t xml:space="preserve">2.50043845176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51528477668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52394556999207</t>
   </si>
   <si>
     <t xml:space="preserve">2.4620840549469</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">2.32908225059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36124992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42620444297791</t>
+    <t xml:space="preserve">2.36125016212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42620468139648</t>
   </si>
   <si>
     <t xml:space="preserve">2.44105124473572</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">2.45713520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45094919204712</t>
+    <t xml:space="preserve">2.45094895362854</t>
   </si>
   <si>
     <t xml:space="preserve">2.47507500648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46579623222351</t>
+    <t xml:space="preserve">2.46579575538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569346427917</t>
@@ -2099,43 +2099,43 @@
     <t xml:space="preserve">2.49054074287415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48187971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47878694534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49548935890198</t>
+    <t xml:space="preserve">2.48188018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47878670692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49548959732056</t>
   </si>
   <si>
     <t xml:space="preserve">2.50662422180176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52889466285706</t>
+    <t xml:space="preserve">2.5288941860199</t>
   </si>
   <si>
     <t xml:space="preserve">2.53446221351624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50786137580872</t>
+    <t xml:space="preserve">2.50786161422729</t>
   </si>
   <si>
     <t xml:space="preserve">2.55302047729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601119041443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58147644996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64952397346497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68292927742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69901323318481</t>
+    <t xml:space="preserve">2.56601095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58147668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64952421188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68292951583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69901299476624</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220900535583</t>
@@ -2153,94 +2153,94 @@
     <t xml:space="preserve">2.69282722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71014857292175</t>
+    <t xml:space="preserve">2.71014809608459</t>
   </si>
   <si>
     <t xml:space="preserve">2.74664688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396775245667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83696413040161</t>
+    <t xml:space="preserve">2.76396751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7299439907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83696436882019</t>
   </si>
   <si>
     <t xml:space="preserve">2.83448958396912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86109018325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85057353973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79799151420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716280937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76025629043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78500032424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78994989395142</t>
+    <t xml:space="preserve">2.86109042167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85057377815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79799175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716328620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76025605201721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78500080108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78994965553284</t>
   </si>
   <si>
     <t xml:space="preserve">2.82088041305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83943891525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83882069587708</t>
+    <t xml:space="preserve">2.83943915367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83882021903992</t>
   </si>
   <si>
     <t xml:space="preserve">2.79737305641174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81160116195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78685712814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922890663147</t>
+    <t xml:space="preserve">2.81160140037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78685688972473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922866821289</t>
   </si>
   <si>
     <t xml:space="preserve">2.80603361129761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81778740882874</t>
+    <t xml:space="preserve">2.81778717041016</t>
   </si>
   <si>
     <t xml:space="preserve">2.79551720619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74417185783386</t>
+    <t xml:space="preserve">2.74417209625244</t>
   </si>
   <si>
     <t xml:space="preserve">2.65694761276245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65014314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59137487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69097137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66560816764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73056244850159</t>
+    <t xml:space="preserve">2.65014266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59137439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69097113609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66560864448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73056292533875</t>
   </si>
   <si>
     <t xml:space="preserve">2.79984784126282</t>
@@ -2255,25 +2255,25 @@
     <t xml:space="preserve">2.75625872612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79106640815735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68084192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79235601425171</t>
+    <t xml:space="preserve">2.79106664657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68084168434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79235553741455</t>
   </si>
   <si>
     <t xml:space="preserve">2.72596311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68148612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6286301612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65892577171326</t>
+    <t xml:space="preserve">2.68148636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62863039970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65892624855042</t>
   </si>
   <si>
     <t xml:space="preserve">2.66279339790344</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">2.66666126251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65183544158936</t>
+    <t xml:space="preserve">2.65183520317078</t>
   </si>
   <si>
     <t xml:space="preserve">2.66472721099854</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">2.6943781375885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68986630439758</t>
+    <t xml:space="preserve">2.689866065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72016167640686</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">2.69695663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65247964859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953489303589</t>
+    <t xml:space="preserve">2.65247988700867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953513145447</t>
   </si>
   <si>
     <t xml:space="preserve">2.7530357837677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73563170433044</t>
+    <t xml:space="preserve">2.73563194274902</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176431655884</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">2.76206016540527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75883722305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79428935050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76077079772949</t>
+    <t xml:space="preserve">2.75883746147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79428958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76077055931091</t>
   </si>
   <si>
     <t xml:space="preserve">2.79944634437561</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">2.86197137832642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91160440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90773725509644</t>
+    <t xml:space="preserve">2.91160464286804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90773701667786</t>
   </si>
   <si>
     <t xml:space="preserve">2.89162254333496</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">2.97477388381958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96832823753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97541880607605</t>
+    <t xml:space="preserve">2.96832847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97541904449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.98702144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96897315979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735261917114</t>
+    <t xml:space="preserve">2.96897268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735238075256</t>
   </si>
   <si>
     <t xml:space="preserve">2.91805028915405</t>
@@ -2390,16 +2390,16 @@
     <t xml:space="preserve">3.03665447235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03923273086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04825687408447</t>
+    <t xml:space="preserve">3.03923296928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04825735092163</t>
   </si>
   <si>
     <t xml:space="preserve">3.00829243659973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97155094146729</t>
+    <t xml:space="preserve">2.97155141830444</t>
   </si>
   <si>
     <t xml:space="preserve">2.98895525932312</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">2.90902590751648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86003756523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84263348579407</t>
+    <t xml:space="preserve">2.86003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84263324737549</t>
   </si>
   <si>
     <t xml:space="preserve">2.78655433654785</t>
@@ -2420,34 +2420,34 @@
     <t xml:space="preserve">2.7659273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83812141418457</t>
+    <t xml:space="preserve">2.83812117576599</t>
   </si>
   <si>
     <t xml:space="preserve">2.73434281349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78010869026184</t>
+    <t xml:space="preserve">2.78010892868042</t>
   </si>
   <si>
     <t xml:space="preserve">2.84843492507935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87421798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9560809135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94770169258118</t>
+    <t xml:space="preserve">2.87421870231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95608115196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9477014541626</t>
   </si>
   <si>
     <t xml:space="preserve">2.91869497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91676115989685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94705700874329</t>
+    <t xml:space="preserve">2.91676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94705677032471</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031527519226</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">2.96510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94576787948608</t>
+    <t xml:space="preserve">2.94576740264893</t>
   </si>
   <si>
     <t xml:space="preserve">2.94125556945801</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">2.97606348991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95479226112366</t>
+    <t xml:space="preserve">2.95479202270508</t>
   </si>
   <si>
     <t xml:space="preserve">2.95801520347595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98959946632385</t>
+    <t xml:space="preserve">2.98959970474243</t>
   </si>
   <si>
     <t xml:space="preserve">3.05921530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11013793945312</t>
+    <t xml:space="preserve">3.11013770103455</t>
   </si>
   <si>
     <t xml:space="preserve">3.10884833335876</t>
@@ -2492,58 +2492,58 @@
     <t xml:space="preserve">3.11464977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10240244865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09853553771973</t>
+    <t xml:space="preserve">3.10240268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09853529930115</t>
   </si>
   <si>
     <t xml:space="preserve">3.06372690200806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10175776481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12431883811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1494574546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13592123985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661843299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05663728713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698612213135</t>
+    <t xml:space="preserve">3.10175824165344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12431836128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14945769309998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13592147827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05663681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698588371277</t>
   </si>
   <si>
     <t xml:space="preserve">3.07275176048279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04696822166443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0875768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12560820579529</t>
+    <t xml:space="preserve">3.04696846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08757710456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12560796737671</t>
   </si>
   <si>
     <t xml:space="preserve">3.19071125984192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15397000312805</t>
+    <t xml:space="preserve">3.15396976470947</t>
   </si>
   <si>
     <t xml:space="preserve">3.15010213851929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17781901359558</t>
+    <t xml:space="preserve">3.17781925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.20553684234619</t>
@@ -2552,73 +2552,73 @@
     <t xml:space="preserve">3.22680807113647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22165155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21262693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23325419425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001287460327</t>
+    <t xml:space="preserve">3.22165131568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21262764930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23325395584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">3.21391630172729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23969984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26548314094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24743461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2222957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388097763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739976882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447196006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3995578289032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41115999221802</t>
+    <t xml:space="preserve">3.23970007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26548337936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24743485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22229623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388073921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447219848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185790061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39955806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4111602306366</t>
   </si>
   <si>
     <t xml:space="preserve">3.43307638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49108934402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304105758667</t>
+    <t xml:space="preserve">3.49108910560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304034233093</t>
   </si>
   <si>
     <t xml:space="preserve">3.43823289871216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45370244979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41631698608398</t>
+    <t xml:space="preserve">3.45370316505432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600347518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41631770133972</t>
   </si>
   <si>
     <t xml:space="preserve">3.41502785682678</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">3.41373872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44596815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987086296082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920875549316</t>
+    <t xml:space="preserve">3.44596791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987133979797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920899391174</t>
   </si>
   <si>
     <t xml:space="preserve">3.34541249275208</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">3.32994222640991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38924479484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38795518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3479905128479</t>
+    <t xml:space="preserve">3.389244556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38795447349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34799027442932</t>
   </si>
   <si>
     <t xml:space="preserve">3.29126691818237</t>
@@ -2657,76 +2657,76 @@
     <t xml:space="preserve">3.27192950248718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32865285873413</t>
+    <t xml:space="preserve">3.32865309715271</t>
   </si>
   <si>
     <t xml:space="preserve">3.36861753463745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43049788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43694376945496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42405152320862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42147350311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47819757461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45499229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3763530254364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513454437256</t>
+    <t xml:space="preserve">3.43049812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43694353103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4240517616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42147397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4781973361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4549925327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37635278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513430595398</t>
   </si>
   <si>
     <t xml:space="preserve">3.35572576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26032662391663</t>
+    <t xml:space="preserve">3.26032638549805</t>
   </si>
   <si>
     <t xml:space="preserve">3.22938656806946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30544805526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3325207233429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576108932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841071128845</t>
+    <t xml:space="preserve">3.30544757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33252096176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576132774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841118812561</t>
   </si>
   <si>
     <t xml:space="preserve">3.1475236415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18490958213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006657600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815090179443</t>
+    <t xml:space="preserve">3.18491005897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815066337585</t>
   </si>
   <si>
     <t xml:space="preserve">3.17395162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13205361366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09982466697693</t>
+    <t xml:space="preserve">3.1320538520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09982419013977</t>
   </si>
   <si>
     <t xml:space="preserve">3.12238478660583</t>
@@ -2738,37 +2738,37 @@
     <t xml:space="preserve">3.11593890190125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1462345123291</t>
+    <t xml:space="preserve">3.14623475074768</t>
   </si>
   <si>
     <t xml:space="preserve">3.02182912826538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96703910827637</t>
+    <t xml:space="preserve">2.96703886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.00958228111267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04310059547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09466743469238</t>
+    <t xml:space="preserve">3.04310035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09466767311096</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848207473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18297624588013</t>
+    <t xml:space="preserve">3.15848183631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18297600746155</t>
   </si>
   <si>
     <t xml:space="preserve">3.4008469581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854617118835</t>
+    <t xml:space="preserve">3.44854640960693</t>
   </si>
   <si>
     <t xml:space="preserve">3.54394555091858</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">3.17459654808044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14236688613892</t>
+    <t xml:space="preserve">3.1423671245575</t>
   </si>
   <si>
     <t xml:space="preserve">3.01409411430359</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">2.7427225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70017981529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610536575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51969480514526</t>
+    <t xml:space="preserve">2.70017957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610512733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51969504356384</t>
   </si>
   <si>
     <t xml:space="preserve">2.24896812438965</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">2.15936994552612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17741870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646718502045</t>
+    <t xml:space="preserve">2.17741847038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646682739258</t>
   </si>
   <si>
     <t xml:space="preserve">1.88993239402771</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">1.7661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6881765127182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500643730164</t>
+    <t xml:space="preserve">1.68817639350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62500667572021</t>
   </si>
   <si>
     <t xml:space="preserve">1.91313767433167</t>
@@ -2834,19 +2834,19 @@
     <t xml:space="preserve">1.77261734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83965444564819</t>
+    <t xml:space="preserve">1.83965468406677</t>
   </si>
   <si>
     <t xml:space="preserve">1.93827641010284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94149935245514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04141044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90669167041779</t>
+    <t xml:space="preserve">1.94149911403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04141068458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90669143199921</t>
   </si>
   <si>
     <t xml:space="preserve">1.94923412799835</t>
@@ -2855,28 +2855,28 @@
     <t xml:space="preserve">2.02013921737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05236864089966</t>
+    <t xml:space="preserve">2.05236840248108</t>
   </si>
   <si>
     <t xml:space="preserve">1.98662066459656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11295962333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12327337265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912755966187</t>
+    <t xml:space="preserve">2.11296010017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12327313423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912779808044</t>
   </si>
   <si>
     <t xml:space="preserve">2.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0910439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278836250305</t>
+    <t xml:space="preserve">2.09104371070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278883934021</t>
   </si>
   <si>
     <t xml:space="preserve">1.92087256908417</t>
@@ -2885,22 +2885,22 @@
     <t xml:space="preserve">1.93892085552216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90282440185547</t>
+    <t xml:space="preserve">1.90282416343689</t>
   </si>
   <si>
     <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8976674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89379990100861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693417549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06010341644287</t>
+    <t xml:space="preserve">1.89766764640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89379966259003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06010365486145</t>
   </si>
   <si>
     <t xml:space="preserve">2.05623602867126</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">2.0265851020813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02529573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04463315010071</t>
+    <t xml:space="preserve">2.0252959728241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04463338851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.04721188545227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752491950989</t>
+    <t xml:space="preserve">2.05752539634705</t>
   </si>
   <si>
     <t xml:space="preserve">2.01627159118652</t>
@@ -2927,22 +2927,22 @@
     <t xml:space="preserve">2.0175609588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98790991306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97243964672089</t>
+    <t xml:space="preserve">1.98790967464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97243988513947</t>
   </si>
   <si>
     <t xml:space="preserve">2.32651424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22702956199646</t>
+    <t xml:space="preserve">2.22702980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17018127441406</t>
+    <t xml:space="preserve">2.17018151283264</t>
   </si>
   <si>
     <t xml:space="preserve">2.21992373466492</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">2.28387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27535080909729</t>
+    <t xml:space="preserve">2.27535057067871</t>
   </si>
   <si>
     <t xml:space="preserve">2.26540231704712</t>
@@ -2975,22 +2975,22 @@
     <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63633704185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6164402961731</t>
+    <t xml:space="preserve">2.63633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61644005775452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56669783592224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48995304107666</t>
+    <t xml:space="preserve">2.48995280265808</t>
   </si>
   <si>
     <t xml:space="preserve">2.37909889221191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38336253166199</t>
+    <t xml:space="preserve">2.38336229324341</t>
   </si>
   <si>
     <t xml:space="preserve">2.38762593269348</t>
@@ -2999,10 +2999,10 @@
     <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44873785972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47574090957642</t>
+    <t xml:space="preserve">2.44873809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47574067115784</t>
   </si>
   <si>
     <t xml:space="preserve">2.451580286026</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">2.44021058082581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40325951576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41889238357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42457723617554</t>
+    <t xml:space="preserve">2.40325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41889262199402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42457747459412</t>
   </si>
   <si>
     <t xml:space="preserve">2.48284673690796</t>
@@ -3032,67 +3032,67 @@
     <t xml:space="preserve">2.53258895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53116798400879</t>
+    <t xml:space="preserve">2.53116774559021</t>
   </si>
   <si>
     <t xml:space="preserve">2.55817055702209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57238245010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58091020584106</t>
+    <t xml:space="preserve">2.57238292694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58090996742249</t>
   </si>
   <si>
     <t xml:space="preserve">2.51127099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53685283660889</t>
+    <t xml:space="preserve">2.53685235977173</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527662277222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60933423042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64202213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63207340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65481305122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67755198478699</t>
+    <t xml:space="preserve">2.60933375358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64202189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63207316398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65481281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67755222320557</t>
   </si>
   <si>
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642457485199</t>
+    <t xml:space="preserve">2.76424598693848</t>
   </si>
   <si>
     <t xml:space="preserve">2.64770674705505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61501932144165</t>
+    <t xml:space="preserve">2.61501884460449</t>
   </si>
   <si>
     <t xml:space="preserve">2.60649180412292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5468008518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66049718856812</t>
+    <t xml:space="preserve">2.4572651386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54680109024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66049766540527</t>
   </si>
   <si>
     <t xml:space="preserve">2.68465805053711</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">2.7528760433197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89073300361633</t>
+    <t xml:space="preserve">2.89073276519775</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768406867981</t>
@@ -3110,79 +3110,79 @@
     <t xml:space="preserve">2.89641785621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92199969291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86372995376587</t>
+    <t xml:space="preserve">2.92199945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86373043060303</t>
   </si>
   <si>
     <t xml:space="preserve">2.83388447761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88931179046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84951782226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84099054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9177360534668</t>
+    <t xml:space="preserve">2.88931155204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8495180606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099078178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91773581504822</t>
   </si>
   <si>
     <t xml:space="preserve">2.93479061126709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95895099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94615983963013</t>
+    <t xml:space="preserve">2.95895075798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94616007804871</t>
   </si>
   <si>
     <t xml:space="preserve">2.94900250434875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87083601951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88789057731628</t>
+    <t xml:space="preserve">2.87083625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88789081573486</t>
   </si>
   <si>
     <t xml:space="preserve">2.85378122329712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81256675720215</t>
+    <t xml:space="preserve">2.81256651878357</t>
   </si>
   <si>
     <t xml:space="preserve">2.78556370735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90068125724792</t>
+    <t xml:space="preserve">2.90068101882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.87794208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94189620018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95184445381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9575297832489</t>
+    <t xml:space="preserve">2.94189643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95184469223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95753002166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.93621158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91489386558533</t>
+    <t xml:space="preserve">2.91489338874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.85662388801575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70313358306885</t>
+    <t xml:space="preserve">2.70313382148743</t>
   </si>
   <si>
     <t xml:space="preserve">2.74861240386963</t>
@@ -3194,19 +3194,19 @@
     <t xml:space="preserve">2.70455479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6576554775238</t>
+    <t xml:space="preserve">2.65765523910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.72729420661926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66902494430542</t>
+    <t xml:space="preserve">2.66902470588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.6505491733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64912796020508</t>
+    <t xml:space="preserve">2.6491277217865</t>
   </si>
   <si>
     <t xml:space="preserve">2.610755443573</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">2.68039441108704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62354636192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63065218925476</t>
+    <t xml:space="preserve">2.62354612350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63065242767334</t>
   </si>
   <si>
     <t xml:space="preserve">2.61359786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56243395805359</t>
+    <t xml:space="preserve">2.56243419647217</t>
   </si>
   <si>
     <t xml:space="preserve">2.45868611335754</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">2.5027437210083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48853182792664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49705910682678</t>
+    <t xml:space="preserve">2.48853206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.52690410614014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48568916320801</t>
+    <t xml:space="preserve">2.48568940162659</t>
   </si>
   <si>
     <t xml:space="preserve">2.42741990089417</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">2.39899563789368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37199282646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25403237342834</t>
+    <t xml:space="preserve">2.37199258804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2540328502655</t>
   </si>
   <si>
     <t xml:space="preserve">2.23129320144653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276616096497</t>
+    <t xml:space="preserve">2.22276639938354</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
@@ -3269,22 +3269,22 @@
     <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39473176002502</t>
+    <t xml:space="preserve">2.3947319984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.56385564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52264046669006</t>
+    <t xml:space="preserve">2.52264070510864</t>
   </si>
   <si>
     <t xml:space="preserve">2.52832555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71450328826904</t>
+    <t xml:space="preserve">2.55532813072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71450352668762</t>
   </si>
   <si>
     <t xml:space="preserve">2.76850938796997</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">2.74008512496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84383296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83672714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97174167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93052697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920853614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81967282295227</t>
+    <t xml:space="preserve">2.84383320808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83672690391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97174191474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81967258453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.8097243309021</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">2.78840613365173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78130030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78272128105164</t>
+    <t xml:space="preserve">2.78130006790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78272080421448</t>
   </si>
   <si>
     <t xml:space="preserve">2.77561521530151</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">2.70597624778748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7073974609375</t>
+    <t xml:space="preserve">2.70739722251892</t>
   </si>
   <si>
     <t xml:space="preserve">2.7130823135376</t>
@@ -3338,10 +3338,10 @@
     <t xml:space="preserve">2.75998210906982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835438728333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72871565818787</t>
+    <t xml:space="preserve">2.7983546257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72871518135071</t>
   </si>
   <si>
     <t xml:space="preserve">2.75429725646973</t>
@@ -3353,19 +3353,19 @@
     <t xml:space="preserve">2.79266977310181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77419400215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77845764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75713968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83246374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8608877658844</t>
+    <t xml:space="preserve">2.77419424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77845788002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75713992118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83246350288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86088752746582</t>
   </si>
   <si>
     <t xml:space="preserve">2.85946655273438</t>
@@ -3380,52 +3380,52 @@
     <t xml:space="preserve">2.88362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8424117565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76993060112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7471911907196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79551243782043</t>
+    <t xml:space="preserve">2.84241199493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76993036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74719095230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79551219940186</t>
   </si>
   <si>
     <t xml:space="preserve">2.67897343635559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68181562423706</t>
+    <t xml:space="preserve">2.68181586265564</t>
   </si>
   <si>
     <t xml:space="preserve">2.74576997756958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64344334602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57522535324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.644864320755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546069145203</t>
+    <t xml:space="preserve">2.64344310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57522559165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64486384391785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546045303345</t>
   </si>
   <si>
     <t xml:space="preserve">2.86657238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758081436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13233804702759</t>
+    <t xml:space="preserve">2.94758105278015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13233780860901</t>
   </si>
   <si>
     <t xml:space="preserve">3.10533475875854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18350172042847</t>
+    <t xml:space="preserve">3.18350124359131</t>
   </si>
   <si>
     <t xml:space="preserve">3.14939260482788</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">3.13944411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15791964530945</t>
+    <t xml:space="preserve">3.15791988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.12665343284607</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">3.03995966911316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742652893066</t>
+    <t xml:space="preserve">2.97742676734924</t>
   </si>
   <si>
     <t xml:space="preserve">3.01153516769409</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">3.13375902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11812591552734</t>
+    <t xml:space="preserve">3.11812615394592</t>
   </si>
   <si>
     <t xml:space="preserve">3.05843496322632</t>
@@ -3467,67 +3467,67 @@
     <t xml:space="preserve">3.19345021247864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16928935050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21192526817322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2517192363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14797067642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30004024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28867053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435563087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30146145820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32562184333801</t>
+    <t xml:space="preserve">3.16928911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21192598342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25171971321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14797115325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30004048347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28867077827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30146169662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32562160491943</t>
   </si>
   <si>
     <t xml:space="preserve">3.30572509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3526246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41942119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36967968940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26450991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27587962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30856776237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947270393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37962770462036</t>
+    <t xml:space="preserve">3.35262441635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110018730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41942143440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36967921257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27587985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856800079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947294235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37962794303894</t>
   </si>
   <si>
     <t xml:space="preserve">3.38247036933899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40378785133362</t>
+    <t xml:space="preserve">3.4037880897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.42013216018677</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">3.32846450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29790878295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272814750671</t>
+    <t xml:space="preserve">3.29790854454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272790908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35902047157288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36683678627014</t>
+    <t xml:space="preserve">3.3668372631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.34978270530701</t>
@@ -3554,34 +3554,34 @@
     <t xml:space="preserve">3.42723798751831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44500303268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32206892967224</t>
+    <t xml:space="preserve">3.44500327110291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">3.28014349937439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29719758033752</t>
+    <t xml:space="preserve">3.29719805717468</t>
   </si>
   <si>
     <t xml:space="preserve">3.315673828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33201718330383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430364608765</t>
+    <t xml:space="preserve">3.33201742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3043041229248</t>
   </si>
   <si>
     <t xml:space="preserve">3.31780576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28440690040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23679661750793</t>
+    <t xml:space="preserve">3.28440713882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23679637908936</t>
   </si>
   <si>
     <t xml:space="preserve">3.31212019920349</t>
@@ -3590,16 +3590,16 @@
     <t xml:space="preserve">3.27232670783997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31283140182495</t>
+    <t xml:space="preserve">3.31283116340637</t>
   </si>
   <si>
     <t xml:space="preserve">3.42226386070251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48550772666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47555875778198</t>
+    <t xml:space="preserve">3.48550796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47555923461914</t>
   </si>
   <si>
     <t xml:space="preserve">3.49545621871948</t>
@@ -3608,37 +3608,37 @@
     <t xml:space="preserve">3.48124408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57575416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143949508667</t>
+    <t xml:space="preserve">3.57575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143925666809</t>
   </si>
   <si>
     <t xml:space="preserve">3.53027558326721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49829816818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52459120750427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61421203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52383780479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38902974128723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43120431900024</t>
+    <t xml:space="preserve">3.49829840660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52459073066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61421179771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52383756637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38902950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43120455741882</t>
   </si>
   <si>
     <t xml:space="preserve">3.41614174842834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44927906990051</t>
+    <t xml:space="preserve">3.44927883148193</t>
   </si>
   <si>
     <t xml:space="preserve">3.48919415473938</t>
@@ -3650,49 +3650,49 @@
     <t xml:space="preserve">3.47488474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831608772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844075202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46132898330688</t>
+    <t xml:space="preserve">3.45831680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844122886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46132922172546</t>
   </si>
   <si>
     <t xml:space="preserve">3.45078468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44626665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44099473953247</t>
+    <t xml:space="preserve">3.44626712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44099426269531</t>
   </si>
   <si>
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752365112305</t>
+    <t xml:space="preserve">3.38752317428589</t>
   </si>
   <si>
     <t xml:space="preserve">3.36041116714478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3250150680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24744343757629</t>
+    <t xml:space="preserve">3.32501459121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24744319915771</t>
   </si>
   <si>
     <t xml:space="preserve">3.27229619026184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23765277862549</t>
+    <t xml:space="preserve">3.23765254020691</t>
   </si>
   <si>
     <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28359341621399</t>
+    <t xml:space="preserve">3.28359317779541</t>
   </si>
   <si>
     <t xml:space="preserve">3.21430635452271</t>
@@ -3701,34 +3701,34 @@
     <t xml:space="preserve">3.24970269203186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39279556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062050819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37697982788086</t>
+    <t xml:space="preserve">3.39279532432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37697958946228</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29489016532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21731853485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30468058586121</t>
+    <t xml:space="preserve">3.2948899269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21731877326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30468082427979</t>
   </si>
   <si>
     <t xml:space="preserve">3.316730260849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33329939842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32953357696533</t>
+    <t xml:space="preserve">3.33329892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32953333854675</t>
   </si>
   <si>
     <t xml:space="preserve">3.29112410545349</t>
@@ -3740,52 +3740,52 @@
     <t xml:space="preserve">3.14878511428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19999718666077</t>
+    <t xml:space="preserve">3.19999694824219</t>
   </si>
   <si>
     <t xml:space="preserve">3.32802724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33028650283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33480501174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3860170841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37321424484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42216730117798</t>
+    <t xml:space="preserve">3.33028626441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33480525016785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37321400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4221670627594</t>
   </si>
   <si>
     <t xml:space="preserve">3.4071044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38149857521057</t>
+    <t xml:space="preserve">3.38149809837341</t>
   </si>
   <si>
     <t xml:space="preserve">3.42141366004944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37170791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36643576622009</t>
+    <t xml:space="preserve">3.37170815467834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36643600463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.39204216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48994755744934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61797738075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60592746734619</t>
+    <t xml:space="preserve">3.48994731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61797761917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60592794418335</t>
   </si>
   <si>
     <t xml:space="preserve">3.6164710521698</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">3.65337347984314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63981771469116</t>
+    <t xml:space="preserve">3.63981819152832</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078045845032</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72040176391602</t>
+    <t xml:space="preserve">3.72040152549744</t>
   </si>
   <si>
     <t xml:space="preserve">3.6752142906189</t>
@@ -3812,61 +3812,61 @@
     <t xml:space="preserve">3.66542410850525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75052642822266</t>
+    <t xml:space="preserve">3.7505259513855</t>
   </si>
   <si>
     <t xml:space="preserve">3.77010703086853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7746262550354</t>
+    <t xml:space="preserve">3.77462601661682</t>
   </si>
   <si>
     <t xml:space="preserve">3.77311968803406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79872608184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77613186836243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7821569442749</t>
+    <t xml:space="preserve">3.79872584342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77613210678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78215670585632</t>
   </si>
   <si>
     <t xml:space="preserve">3.76709461212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78667593002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7369704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77763867378235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71663570404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71588253974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533895492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63755798339844</t>
+    <t xml:space="preserve">3.78667569160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73697018623352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77763819694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71663618087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71588277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533919334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6375584602356</t>
   </si>
   <si>
     <t xml:space="preserve">3.68726396560669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6699423789978</t>
+    <t xml:space="preserve">3.66994261741638</t>
   </si>
   <si>
     <t xml:space="preserve">3.65638637542725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72567343711853</t>
+    <t xml:space="preserve">3.72567319869995</t>
   </si>
   <si>
     <t xml:space="preserve">3.67144870758057</t>
@@ -3875,58 +3875,58 @@
     <t xml:space="preserve">3.58258080482483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64132404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80926942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450182914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625629425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84541916847229</t>
+    <t xml:space="preserve">3.64132380485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429177284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80926966667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450135231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80625653266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84541869163513</t>
   </si>
   <si>
     <t xml:space="preserve">3.83939409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717506408691</t>
+    <t xml:space="preserve">3.90717458724976</t>
   </si>
   <si>
     <t xml:space="preserve">3.88006234169006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9538676738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97947359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95989322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483089447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89060616493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88307499885559</t>
+    <t xml:space="preserve">3.95386791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97947382926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9598925113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483065605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89060544967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88307476043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.92976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95682621002197</t>
+    <t xml:space="preserve">3.95682597160339</t>
   </si>
   <si>
     <t xml:space="preserve">3.99502515792847</t>
@@ -3938,25 +3938,25 @@
     <t xml:space="preserve">3.96239686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95125532150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99025058746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97910904884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98388409614563</t>
+    <t xml:space="preserve">3.95125555992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99025011062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97910928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98388361930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.95523381233215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00457525253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98070025444031</t>
+    <t xml:space="preserve">4.00457572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98070049285889</t>
   </si>
   <si>
     <t xml:space="preserve">4.0189003944397</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">3.9735381603241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98706698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807195663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340135574341</t>
+    <t xml:space="preserve">3.98706746101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807171821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340111732483</t>
   </si>
   <si>
     <t xml:space="preserve">3.98229241371155</t>
@@ -3980,25 +3980,25 @@
     <t xml:space="preserve">4.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98865914344788</t>
+    <t xml:space="preserve">3.98865866661072</t>
   </si>
   <si>
     <t xml:space="preserve">3.93454313278198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97274231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90907645225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89952731132507</t>
+    <t xml:space="preserve">3.97274279594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90907692909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89952707290649</t>
   </si>
   <si>
     <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66078042984009</t>
+    <t xml:space="preserve">3.66078019142151</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590093612671</t>
@@ -4007,25 +4007,25 @@
     <t xml:space="preserve">3.66316771507263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73638343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72524237632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70057129859924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76821684837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779810905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77219462394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76264595985413</t>
+    <t xml:space="preserve">3.73638367652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72524189949036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70057153701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76821637153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7721951007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76264572143555</t>
   </si>
   <si>
     <t xml:space="preserve">3.74752497673035</t>
@@ -4034,22 +4034,22 @@
     <t xml:space="preserve">3.72922086715698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73081302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77856183052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74513721466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64565920829773</t>
+    <t xml:space="preserve">3.73081254959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77856230735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74513745307922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64565968513489</t>
   </si>
   <si>
     <t xml:space="preserve">3.74832081794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75150394439697</t>
+    <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
     <t xml:space="preserve">3.77697062492371</t>
@@ -4058,52 +4058,52 @@
     <t xml:space="preserve">3.83267760276794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80641555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80323171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85177731513977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85973596572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93613481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86212348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87008142471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146445274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97115063667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9639880657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95443844795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99980020523071</t>
+    <t xml:space="preserve">3.80641627311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80323219299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85177755355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85973572731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93613505363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86212301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87008118629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146421432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97115111351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96398854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95443820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980044364929</t>
   </si>
   <si>
     <t xml:space="preserve">3.91942238807678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76344132423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402851104736</t>
+    <t xml:space="preserve">3.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402827262878</t>
   </si>
   <si>
     <t xml:space="preserve">3.90748524665833</t>
@@ -4112,43 +4112,43 @@
     <t xml:space="preserve">3.95603036880493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90430188179016</t>
+    <t xml:space="preserve">3.90430164337158</t>
   </si>
   <si>
     <t xml:space="preserve">3.94409275054932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00775814056396</t>
+    <t xml:space="preserve">4.00775861740112</t>
   </si>
   <si>
     <t xml:space="preserve">3.96796774864197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8557562828064</t>
+    <t xml:space="preserve">3.85575652122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.82710719108582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03004121780396</t>
+    <t xml:space="preserve">4.03004169464111</t>
   </si>
   <si>
     <t xml:space="preserve">4.01253318786621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99820899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91623902320862</t>
+    <t xml:space="preserve">4.00935029983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99820876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91623950004578</t>
   </si>
   <si>
     <t xml:space="preserve">3.85814428329468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78094887733459</t>
+    <t xml:space="preserve">3.78094935417175</t>
   </si>
   <si>
     <t xml:space="preserve">3.55414009094238</t>
@@ -4157,19 +4157,19 @@
     <t xml:space="preserve">3.69261336326599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60746049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42760491371155</t>
+    <t xml:space="preserve">3.60746026039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42760443687439</t>
   </si>
   <si>
     <t xml:space="preserve">3.40293407440186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34483909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06948471069336</t>
+    <t xml:space="preserve">3.34483933448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06948494911194</t>
   </si>
   <si>
     <t xml:space="preserve">2.94374465942383</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">3.14429187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28913164138794</t>
+    <t xml:space="preserve">3.28913140296936</t>
   </si>
   <si>
     <t xml:space="preserve">3.39338421821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51912403106689</t>
+    <t xml:space="preserve">3.51912379264832</t>
   </si>
   <si>
     <t xml:space="preserve">3.56846499443054</t>
@@ -4196,31 +4196,31 @@
     <t xml:space="preserve">3.69022583961487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68385934829712</t>
+    <t xml:space="preserve">3.6838595867157</t>
   </si>
   <si>
     <t xml:space="preserve">3.70852947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74036192893982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90111804008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90668940544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92021870613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97194647789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319270133972</t>
+    <t xml:space="preserve">3.7403621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354577064514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90111875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90668916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92021822929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97194671630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319246292114</t>
   </si>
   <si>
     <t xml:space="preserve">3.93693065643311</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">4.03481674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06346654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02845001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11758232116699</t>
+    <t xml:space="preserve">4.06346607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02844953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11758184432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.09848213195801</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">4.1334981918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16055631637573</t>
+    <t xml:space="preserve">4.16055679321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.16214799880981</t>
@@ -4256,22 +4256,22 @@
     <t xml:space="preserve">4.20193958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21467208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19716453552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1541895866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599016189575</t>
+    <t xml:space="preserve">4.21467161178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599063873291</t>
   </si>
   <si>
     <t xml:space="preserve">4.13668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14623165130615</t>
+    <t xml:space="preserve">4.14623212814331</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">4.0650577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1637396812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26719617843628</t>
+    <t xml:space="preserve">4.16373920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26719665527344</t>
   </si>
   <si>
     <t xml:space="preserve">4.28470420837402</t>
@@ -4301,46 +4301,46 @@
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9050977230072</t>
+    <t xml:space="preserve">3.90509748458862</t>
   </si>
   <si>
     <t xml:space="preserve">4.00298404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00139188766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12431621551514</t>
+    <t xml:space="preserve">4.00139236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12431716918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28597116470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2504243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21487712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14547538757324</t>
+    <t xml:space="preserve">4.23011112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24703931808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28597164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25042390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21487665176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14547491073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.14124393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19202518463135</t>
+    <t xml:space="preserve">4.09723329544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19202566146851</t>
   </si>
   <si>
     <t xml:space="preserve">4.20810651779175</t>
@@ -4349,13 +4349,13 @@
     <t xml:space="preserve">4.11754560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10738945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77053785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383142471313</t>
+    <t xml:space="preserve">4.10738897323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77053737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383166313171</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4364,55 +4364,55 @@
     <t xml:space="preserve">3.82301211357117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69944334030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71213912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7730770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122784614563</t>
+    <t xml:space="preserve">3.69944310188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71213865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77307677268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122760772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6588180065155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80100655555725</t>
+    <t xml:space="preserve">3.65881776809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80100703239441</t>
   </si>
   <si>
     <t xml:space="preserve">3.70198249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71044564247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66982078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68082332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69690442085266</t>
+    <t xml:space="preserve">3.71467757225037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71044588088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66982054710388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68082308769226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69690418243408</t>
   </si>
   <si>
     <t xml:space="preserve">3.47177243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4912383556366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60634350776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62919545173645</t>
+    <t xml:space="preserve">3.49123883247375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6063437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62919569015503</t>
   </si>
   <si>
     <t xml:space="preserve">3.53355693817139</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">3.51324391365051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48700642585754</t>
+    <t xml:space="preserve">3.48700666427612</t>
   </si>
   <si>
     <t xml:space="preserve">3.33381533622742</t>
@@ -4442,34 +4442,34 @@
     <t xml:space="preserve">3.26356744766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25764298439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29657530784607</t>
+    <t xml:space="preserve">3.25764274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29657554626465</t>
   </si>
   <si>
     <t xml:space="preserve">3.24325489997864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28134107589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005282402039</t>
+    <t xml:space="preserve">3.2813413143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005258560181</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415495872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860817909241</t>
+    <t xml:space="preserve">3.46415519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860770225525</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56741118431091</t>
+    <t xml:space="preserve">3.56741142272949</t>
   </si>
   <si>
     <t xml:space="preserve">3.64358329772949</t>
@@ -4478,19 +4478,19 @@
     <t xml:space="preserve">3.66135716438293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64273691177368</t>
+    <t xml:space="preserve">3.64273715019226</t>
   </si>
   <si>
     <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70790696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74176144599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73922252655029</t>
+    <t xml:space="preserve">3.70790672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74176120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73922228813171</t>
   </si>
   <si>
     <t xml:space="preserve">3.67659139633179</t>
@@ -4499,22 +4499,22 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55979347229004</t>
+    <t xml:space="preserve">3.5597939491272</t>
   </si>
   <si>
     <t xml:space="preserve">3.46838688850403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54625201225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50224137306213</t>
+    <t xml:space="preserve">3.54625225067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50224113464355</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50816559791565</t>
+    <t xml:space="preserve">3.50816583633423</t>
   </si>
   <si>
     <t xml:space="preserve">3.54117393493652</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885559082031</t>
+    <t xml:space="preserve">3.49885582923889</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4541,19 +4541,19 @@
     <t xml:space="preserve">3.70282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67913103103638</t>
+    <t xml:space="preserve">3.6791307926178</t>
   </si>
   <si>
     <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69351863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706057548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70029020309448</t>
+    <t xml:space="preserve">3.69351887702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706081390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7002899646759</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010625839233</t>
+    <t xml:space="preserve">3.58010649681091</t>
   </si>
   <si>
     <t xml:space="preserve">3.47515749931335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4404571056366</t>
+    <t xml:space="preserve">3.44045686721802</t>
   </si>
   <si>
     <t xml:space="preserve">3.38459730148315</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">3.34735727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38036513328552</t>
+    <t xml:space="preserve">3.3803653717041</t>
   </si>
   <si>
     <t xml:space="preserve">3.40829515457153</t>
@@ -4589,19 +4589,19 @@
     <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38205790519714</t>
+    <t xml:space="preserve">3.38205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3676700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37613368034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31519556045532</t>
+    <t xml:space="preserve">3.36766982078552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37613344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3151957988739</t>
   </si>
   <si>
     <t xml:space="preserve">3.42014408111572</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">3.4531524181366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50647306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48954606056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471563339233</t>
+    <t xml:space="preserve">3.50647330284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48954582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471539497375</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">3.58433842658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6317343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674778938293</t>
+    <t xml:space="preserve">3.63173413276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.72568035125732</t>
@@ -4646,28 +4646,28 @@
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241313934326</t>
+    <t xml:space="preserve">3.85178828239441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241337776184</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366428375244</t>
+    <t xml:space="preserve">3.97366452217102</t>
   </si>
   <si>
     <t xml:space="preserve">4.06422472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01259708404541</t>
+    <t xml:space="preserve">4.01259660720825</t>
   </si>
   <si>
     <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03037023544312</t>
+    <t xml:space="preserve">4.03037071228027</t>
   </si>
   <si>
     <t xml:space="preserve">4.04052686691284</t>
@@ -4685,31 +4685,31 @@
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645156860352</t>
+    <t xml:space="preserve">4.04645109176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391193389893</t>
+    <t xml:space="preserve">4.04391241073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08623027801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14208984375</t>
+    <t xml:space="preserve">4.08623075485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14209032058716</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05322217941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00836515426636</t>
+    <t xml:space="preserve">4.05322170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0083646774292</t>
   </si>
   <si>
     <t xml:space="preserve">3.98635983467102</t>
@@ -4718,13 +4718,13 @@
     <t xml:space="preserve">4.02359962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01344347000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96774005889893</t>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01344299316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96773958206177</t>
   </si>
   <si>
     <t xml:space="preserve">4.00667238235474</t>
@@ -4733,49 +4733,49 @@
     <t xml:space="preserve">3.95589065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84586429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78831100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86702275276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88818144798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96096873283386</t>
+    <t xml:space="preserve">3.84586381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78831076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86702251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88818192481995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9609682559967</t>
   </si>
   <si>
     <t xml:space="preserve">3.94150257110596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93219232559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272664070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579892158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85771298408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89326000213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96435403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03544807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97958922386169</t>
+    <t xml:space="preserve">3.93219256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579916000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8577127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89325976371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96435451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03544855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97958898544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">4.01682901382446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99482321739197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99736213684082</t>
+    <t xml:space="preserve">3.99482297897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974537849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9973623752594</t>
   </si>
   <si>
     <t xml:space="preserve">4.02529239654541</t>
@@ -4799,22 +4799,22 @@
     <t xml:space="preserve">4.04306602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04475784301758</t>
+    <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
     <t xml:space="preserve">4.05660820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0879225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638643264771</t>
+    <t xml:space="preserve">4.08792304992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10992860794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
@@ -4823,19 +4823,19 @@
     <t xml:space="preserve">4.19117879867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13362598419189</t>
+    <t xml:space="preserve">4.13362646102905</t>
   </si>
   <si>
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732431411743</t>
+    <t xml:space="preserve">4.15732479095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18271493911743</t>
+    <t xml:space="preserve">4.18271541595459</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2123384475708</t>
+    <t xml:space="preserve">4.21233797073364</t>
   </si>
   <si>
     <t xml:space="preserve">4.17679071426392</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18864011764526</t>
+    <t xml:space="preserve">4.18863964080811</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
@@ -4868,10 +4868,10 @@
     <t xml:space="preserve">4.17933034896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23349666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24026775360107</t>
+    <t xml:space="preserve">4.23349714279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24026823043823</t>
   </si>
   <si>
     <t xml:space="preserve">4.27073669433594</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33506011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29443454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28427886962891</t>
+    <t xml:space="preserve">4.33506059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29443502426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28427839279175</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
@@ -4895,22 +4895,22 @@
     <t xml:space="preserve">4.09215450286865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85094213485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802505493164</t>
+    <t xml:space="preserve">3.8509418964386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87802481651306</t>
   </si>
   <si>
     <t xml:space="preserve">3.75784230232239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8526349067688</t>
+    <t xml:space="preserve">3.85263466835022</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9465811252594</t>
+    <t xml:space="preserve">3.94658064842224</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
@@ -4919,13 +4919,13 @@
     <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93811678886414</t>
+    <t xml:space="preserve">3.93811702728271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05491495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06676387786865</t>
+    <t xml:space="preserve">4.06676340103149</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766393661499</t>
+    <t xml:space="preserve">4.28766441345215</t>
   </si>
   <si>
     <t xml:space="preserve">4.29274272918701</t>
@@ -4958,37 +4958,37 @@
     <t xml:space="preserve">4.28258562088013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33336782455444</t>
+    <t xml:space="preserve">4.33336734771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.31305503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23857498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32828903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37907123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34013843536377</t>
+    <t xml:space="preserve">4.23857545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32828950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938402175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37907075881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34013795852661</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183168411255</t>
+    <t xml:space="preserve">4.34183120727539</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36722183227539</t>
+    <t xml:space="preserve">4.36722135543823</t>
   </si>
   <si>
     <t xml:space="preserve">4.37269258499146</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531141281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072353363037</t>
+    <t xml:space="preserve">4.33531188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3398699760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072305679321</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266326904297</t>
+    <t xml:space="preserve">4.36266374588013</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369129180908</t>
+    <t xml:space="preserve">4.40369176864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081052780151</t>
+    <t xml:space="preserve">4.35081100463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5084,10 +5084,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292520523071</t>
+    <t xml:space="preserve">4.48757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292568206787</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924903869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574781417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492357254028</t>
+    <t xml:space="preserve">4.43924951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492404937744</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5769214630127</t>
+    <t xml:space="preserve">4.57692193984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5915093421936</t>
+    <t xml:space="preserve">4.59150981903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5132,7 +5132,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891983032227</t>
+    <t xml:space="preserve">4.63891935348511</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130556106567</t>
+    <t xml:space="preserve">4.52130603790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786249160767</t>
+    <t xml:space="preserve">4.58786296844482</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5168,22 +5168,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732950210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897798538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197505950928</t>
+    <t xml:space="preserve">4.73191690444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644710540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197553634644</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5192,10 +5192,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6553316116333</t>
+    <t xml:space="preserve">4.56780481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65533113479614</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5204,13 +5204,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074373245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792064666748</t>
+    <t xml:space="preserve">4.68268394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792112350464</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68450689315796</t>
+    <t xml:space="preserve">4.6845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5228,7 +5228,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009395599365</t>
+    <t xml:space="preserve">4.73009347915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174291610718</t>
+    <t xml:space="preserve">4.67174243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5273,16 +5273,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7063889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6370964050293</t>
+    <t xml:space="preserve">4.70638847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63709688186646</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080188751221</t>
+    <t xml:space="preserve">4.66080141067505</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903614044189</t>
+    <t xml:space="preserve">4.67903661727905</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8887357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403158187866</t>
+    <t xml:space="preserve">4.87050104141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88873624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5318,10 +5318,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497308731079</t>
+    <t xml:space="preserve">4.85956048965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5330,13 +5330,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491445541382</t>
+    <t xml:space="preserve">4.82491397857666</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756212234497</t>
+    <t xml:space="preserve">4.79756259918213</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5345,13 +5345,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932786941528</t>
+    <t xml:space="preserve">4.77932739257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815422058105</t>
+    <t xml:space="preserve">4.6881537437439</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5369,13 +5369,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714496612549</t>
+    <t xml:space="preserve">4.96714544296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602994918823</t>
+    <t xml:space="preserve">4.89602947235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079229354858</t>
+    <t xml:space="preserve">4.97079277038574</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2333722114563</t>
+    <t xml:space="preserve">5.23337268829346</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5429,13 +5429,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2607250213623</t>
+    <t xml:space="preserve">5.26072454452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078317642212</t>
+    <t xml:space="preserve">5.28078269958496</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5447,10 +5447,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709890365601</t>
+    <t xml:space="preserve">6.38216161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709842681885</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8562650680542</t>
+    <t xml:space="preserve">6.85626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5486,13 +5486,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655679702759</t>
+    <t xml:space="preserve">6.95655632019043</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632322311401</t>
+    <t xml:space="preserve">6.87632369995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5501,7 +5501,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8690299987793</t>
+    <t xml:space="preserve">6.86902952194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5522,13 +5522,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625642776489</t>
+    <t xml:space="preserve">7.16625595092773</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213426589966</t>
+    <t xml:space="preserve">7.31213474273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5537,13 +5537,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566480636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537307739258</t>
+    <t xml:space="preserve">7.21184253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537355422974</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5555,10 +5555,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242551803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5127158164978</t>
+    <t xml:space="preserve">7.41242504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5567,19 +5567,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57653856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682933807373</t>
+    <t xml:space="preserve">7.63124227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580131530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.726975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682886123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5588,7 +5588,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67227029800415</t>
+    <t xml:space="preserve">7.67226982116699</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5612,7 +5612,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22387218475342</t>
+    <t xml:space="preserve">8.2238712310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -6561,6 +6561,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.3549995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1049995422363</t>
   </si>
 </sst>
 </file>
@@ -71639,7 +71642,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6521990741</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>1312424</v>
@@ -71660,6 +71663,32 @@
         <v>2182</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6500925926</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>2299178</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>18.1949996948242</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>17.7549991607666</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>18.1299991607666</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>18.1049995422363</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>2183</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="2184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="2185">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">UNI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50193190574646</t>
+    <t xml:space="preserve">2.50193166732788</t>
   </si>
   <si>
     <t xml:space="preserve">2.40895080566406</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29780149459839</t>
+    <t xml:space="preserve">2.29780173301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.37261366844177</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.37795734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33413863182068</t>
+    <t xml:space="preserve">2.33413887023926</t>
   </si>
   <si>
     <t xml:space="preserve">2.23474550247192</t>
@@ -74,25 +74,25 @@
     <t xml:space="preserve">2.15458965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11184000968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99641585350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588387489319</t>
+    <t xml:space="preserve">2.11183977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964154958725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588363647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.07977771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03489017486572</t>
+    <t xml:space="preserve">2.0348904132843</t>
   </si>
   <si>
     <t xml:space="preserve">2.03168392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0295467376709</t>
+    <t xml:space="preserve">2.02954697608948</t>
   </si>
   <si>
     <t xml:space="preserve">1.90343451499939</t>
@@ -101,46 +101,46 @@
     <t xml:space="preserve">2.00924038887024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93549704551697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84037852287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953496456146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701665878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792952060699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349882602692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151142597198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861699104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823004245758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60632336139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72922921180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899835109711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7431229352951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350429534912</t>
+    <t xml:space="preserve">1.93549692630768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84037899971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74953532218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701653957367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792963981628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349846839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151154518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55822992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60632359981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72922933101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67899799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312329292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350417613983</t>
   </si>
   <si>
     <t xml:space="preserve">1.69396066665649</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">1.74419164657593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70571684837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7153354883194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82541608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82327902317047</t>
+    <t xml:space="preserve">1.70571672916412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296696662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71533560752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82541632652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82327878475189</t>
   </si>
   <si>
     <t xml:space="preserve">1.88099098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89381575584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488470554352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86602830886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404138565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556634902954</t>
+    <t xml:space="preserve">1.89381587505341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488446712494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86602854728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404126644135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556646823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.82648491859436</t>
@@ -188,91 +188,91 @@
     <t xml:space="preserve">1.79976630210876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053461074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442785739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229079246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221566200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435308456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183430194855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95580303668976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95259714126587</t>
+    <t xml:space="preserve">1.92053472995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442809581757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93229067325592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221590042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435332298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183406352997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95580315589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95259666442871</t>
   </si>
   <si>
     <t xml:space="preserve">1.92374074459076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87564742565155</t>
+    <t xml:space="preserve">1.87564706802368</t>
   </si>
   <si>
     <t xml:space="preserve">1.8831285238266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.911985039711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90022838115692</t>
+    <t xml:space="preserve">1.91198456287384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90022826194763</t>
   </si>
   <si>
     <t xml:space="preserve">1.89167833328247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579756736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81793510913849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190360546112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992250919342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129721164703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465324878693</t>
+    <t xml:space="preserve">1.81579732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80190396308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129780769348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465348720551</t>
   </si>
   <si>
     <t xml:space="preserve">1.92587852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92801582813263</t>
+    <t xml:space="preserve">1.92801594734192</t>
   </si>
   <si>
     <t xml:space="preserve">1.91519093513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01779079437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05626511573792</t>
+    <t xml:space="preserve">2.0177903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05626535415649</t>
   </si>
   <si>
     <t xml:space="preserve">2.07443380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0616090297699</t>
+    <t xml:space="preserve">2.06160926818848</t>
   </si>
   <si>
     <t xml:space="preserve">2.07015895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02634048461914</t>
+    <t xml:space="preserve">2.02634024620056</t>
   </si>
   <si>
     <t xml:space="preserve">2.05519652366638</t>
@@ -284,49 +284,49 @@
     <t xml:space="preserve">1.99855291843414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99214041233063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95045936107635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93977200984955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8499972820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457859516144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7912163734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73884809017181</t>
+    <t xml:space="preserve">1.99214065074921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9504599571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93977212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84999716281891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121613502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73884797096252</t>
   </si>
   <si>
     <t xml:space="preserve">1.72388553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6950296163559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678567886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70785462856293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87773144245148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8754688501358</t>
+    <t xml:space="preserve">1.69502937793732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678579807281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70785415172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235234737396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700931072235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87773156166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87546908855438</t>
   </si>
   <si>
     <t xml:space="preserve">1.91279745101929</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">1.90601027011871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88451838493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80986154079437</t>
+    <t xml:space="preserve">1.88451826572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081212520599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80986166000366</t>
   </si>
   <si>
     <t xml:space="preserve">1.81438612937927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80646812915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75104069709778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63113784790039</t>
+    <t xml:space="preserve">1.80646824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75104093551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63113796710968</t>
   </si>
   <si>
     <t xml:space="preserve">1.54290688037872</t>
@@ -374,25 +374,25 @@
     <t xml:space="preserve">1.61190795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6005961894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57684206962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69900751113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38341283798218</t>
+    <t xml:space="preserve">1.60059607028961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57684171199799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69900763034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38341307640076</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27255892753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213738322258</t>
+    <t xml:space="preserve">1.27255880832672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21373844146729</t>
   </si>
   <si>
     <t xml:space="preserve">1.19111514091492</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">1.23636174201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18545925617218</t>
+    <t xml:space="preserve">1.18545937538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021277427673</t>
@@ -410,94 +410,94 @@
     <t xml:space="preserve">1.09949100017548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722852706909</t>
+    <t xml:space="preserve">1.09722864627838</t>
   </si>
   <si>
     <t xml:space="preserve">1.23749279975891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28726398944855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36870765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33477282524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39359354972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38454401493073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038049221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36983895301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.398118019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37888824939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37097024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37775719165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42979085445404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40264248847961</t>
+    <t xml:space="preserve">1.28726422786713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36870789527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33477294445038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39359331130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3845442533493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40038025379181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983907222748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39811813831329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37888836860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37097012996674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37775707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42979061603546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40264272689819</t>
   </si>
   <si>
     <t xml:space="preserve">1.38567519187927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26011598110199</t>
+    <t xml:space="preserve">1.26011610031128</t>
   </si>
   <si>
     <t xml:space="preserve">1.29631340503693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32233023643494</t>
+    <t xml:space="preserve">1.32233011722565</t>
   </si>
   <si>
     <t xml:space="preserve">1.37549459934235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43657767772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4535448551178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44788920879364</t>
+    <t xml:space="preserve">1.43657755851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45354509353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44788932800293</t>
   </si>
   <si>
     <t xml:space="preserve">1.47051227092743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45015156269073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41961014270782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38001954555511</t>
+    <t xml:space="preserve">1.45015168190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41961026191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3800196647644</t>
   </si>
   <si>
     <t xml:space="preserve">1.39698684215546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33137941360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33251059055328</t>
+    <t xml:space="preserve">1.33137953281403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33251047134399</t>
   </si>
   <si>
     <t xml:space="preserve">1.38228166103363</t>
@@ -506,79 +506,79 @@
     <t xml:space="preserve">1.36757659912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33816647529602</t>
+    <t xml:space="preserve">1.33816623687744</t>
   </si>
   <si>
     <t xml:space="preserve">1.3540027141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32798600196838</t>
+    <t xml:space="preserve">1.32798588275909</t>
   </si>
   <si>
     <t xml:space="preserve">1.41056072711945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40377378463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42413473129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43883979320526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45920073986053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47729957103729</t>
+    <t xml:space="preserve">1.40377390384674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42413485050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43883991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45920097827911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.477299451828</t>
   </si>
   <si>
     <t xml:space="preserve">1.48748004436493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48974227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019978046417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40716707706451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36078953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282331943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513377189636</t>
+    <t xml:space="preserve">1.48974239826202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39020001888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4071671962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36078941822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513365268707</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947800636292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34269118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536258220673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821481227875</t>
+    <t xml:space="preserve">1.34269106388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536282062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821457386017</t>
   </si>
   <si>
     <t xml:space="preserve">1.31780540943146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2861328125</t>
+    <t xml:space="preserve">1.28613269329071</t>
   </si>
   <si>
     <t xml:space="preserve">1.28500175476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27934598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35174024105072</t>
+    <t xml:space="preserve">1.27934587001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35174036026001</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
@@ -587,49 +587,49 @@
     <t xml:space="preserve">1.37210118770599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39472460746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41621673107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44110250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49313580989838</t>
+    <t xml:space="preserve">1.39472448825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41621649265289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44110202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4931355714798</t>
   </si>
   <si>
     <t xml:space="preserve">1.52480840682983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53159523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51575922966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54856288433075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56553030014038</t>
+    <t xml:space="preserve">1.53159511089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51575911045074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54856276512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56553018093109</t>
   </si>
   <si>
     <t xml:space="preserve">1.61077678203583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63453125953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59833407402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571077346802</t>
+    <t xml:space="preserve">1.63453137874603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5983339548111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571089267731</t>
   </si>
   <si>
     <t xml:space="preserve">1.57118606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50444734096527</t>
+    <t xml:space="preserve">1.50444746017456</t>
   </si>
   <si>
     <t xml:space="preserve">1.51802134513855</t>
@@ -644,106 +644,106 @@
     <t xml:space="preserve">1.69335162639618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66733479499817</t>
+    <t xml:space="preserve">1.66733503341675</t>
   </si>
   <si>
     <t xml:space="preserve">1.66167914867401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905584812164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172736644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5745792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5847601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5610054731369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064476490021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512089729309</t>
+    <t xml:space="preserve">1.63905620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172760486603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57457983493805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6266131401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58476006984711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100535392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064452648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512101650238</t>
   </si>
   <si>
     <t xml:space="preserve">1.64923632144928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66620373725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6243509054184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049939632416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284554958344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492754936218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022248744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86302638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623908042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91053509712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89922368526459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91166615486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92637157440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94560110569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446969032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89696097373962</t>
+    <t xml:space="preserve">1.6662038564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62435066699982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284578800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022224903107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86302626132965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91053485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8992235660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91166639328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92637145519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94560098648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94447016716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89696109294891</t>
   </si>
   <si>
     <t xml:space="preserve">1.93655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98066747188568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0134711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781488418579</t>
+    <t xml:space="preserve">1.98066699504852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01347088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781512260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.01573324203491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01912665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96483087539673</t>
+    <t xml:space="preserve">2.01912689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96483111381531</t>
   </si>
   <si>
     <t xml:space="preserve">1.99876594543457</t>
@@ -752,64 +752,64 @@
     <t xml:space="preserve">2.0202579498291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727406024933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007771492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97161781787872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94786322116852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953593730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02252006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99084758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08247208595276</t>
+    <t xml:space="preserve">1.97727370262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007747650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9716180562973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94786357879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953581809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0225203037262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99084746837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247184753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.08699655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05079936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193042755127</t>
+    <t xml:space="preserve">2.05079960823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193066596985</t>
   </si>
   <si>
     <t xml:space="preserve">1.93542075157166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93202698230743</t>
+    <t xml:space="preserve">1.93202710151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.96709322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894618034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940392017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89130556583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.873206615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999379634857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510790348053</t>
+    <t xml:space="preserve">2.00894641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940403938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89130520820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87320697307587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8799934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510802268982</t>
   </si>
   <si>
     <t xml:space="preserve">1.96596217155457</t>
@@ -818,28 +818,28 @@
     <t xml:space="preserve">2.03609418869019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99424088001251</t>
+    <t xml:space="preserve">1.99424111843109</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329065322876</t>
+    <t xml:space="preserve">2.00329041481018</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478241920471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01799583435059</t>
+    <t xml:space="preserve">2.01799559593201</t>
   </si>
   <si>
     <t xml:space="preserve">2.00442147254944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9546502828598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0293071269989</t>
+    <t xml:space="preserve">1.95465040206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02930760383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.02817606925964</t>
@@ -851,46 +851,46 @@
     <t xml:space="preserve">2.13224339485168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432479858398</t>
+    <t xml:space="preserve">2.12432503700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.12093138694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15939140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1084885597229</t>
+    <t xml:space="preserve">2.15939092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373539924622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10848879814148</t>
   </si>
   <si>
     <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14921069145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19332575798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17862057685852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23291707038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558811187744</t>
+    <t xml:space="preserve">2.14921045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1933262348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1786208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23291683197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558835029602</t>
   </si>
   <si>
     <t xml:space="preserve">2.20803141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20576882362366</t>
+    <t xml:space="preserve">2.20576906204224</t>
   </si>
   <si>
     <t xml:space="preserve">2.18314552307129</t>
@@ -899,46 +899,46 @@
     <t xml:space="preserve">2.16617798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2035059928894</t>
+    <t xml:space="preserve">2.20350623130798</t>
   </si>
   <si>
     <t xml:space="preserve">2.19219470024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20011305809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17522740364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17748951911926</t>
+    <t xml:space="preserve">2.15825963020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20011329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17522716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17748975753784</t>
   </si>
   <si>
     <t xml:space="preserve">2.15599751472473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14129209518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09378337860107</t>
+    <t xml:space="preserve">2.14129257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09378361701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.07907843589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08812785148621</t>
+    <t xml:space="preserve">2.08812761306763</t>
   </si>
   <si>
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10961961746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22273659706116</t>
+    <t xml:space="preserve">2.10961985588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22273635864258</t>
   </si>
   <si>
     <t xml:space="preserve">2.26232695579529</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">2.26006460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25780248641968</t>
+    <t xml:space="preserve">2.2578022480011</t>
   </si>
   <si>
     <t xml:space="preserve">2.31436038017273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33132815361023</t>
+    <t xml:space="preserve">2.33132791519165</t>
   </si>
   <si>
     <t xml:space="preserve">2.34716415405273</t>
@@ -965,70 +965,70 @@
     <t xml:space="preserve">2.41164040565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43878793716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44557499885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127993583679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32567191123962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38675475120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36300039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33585262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25893330574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24988412857056</t>
+    <t xml:space="preserve">2.43878841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127945899963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3256721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38675451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3630006313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33585238456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25893354415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24988389015198</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137613296509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30216670036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36137890815735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35072040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30808758735657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453237533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926975250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558429718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18137383460999</t>
+    <t xml:space="preserve">2.33769392967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30216646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36137866973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35072064399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30808806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453261375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926951408386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2109797000885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18137407302856</t>
   </si>
   <si>
     <t xml:space="preserve">2.1458466053009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13637280464172</t>
+    <t xml:space="preserve">2.13637256622314</t>
   </si>
   <si>
     <t xml:space="preserve">2.10913515090942</t>
@@ -1037,31 +1037,31 @@
     <t xml:space="preserve">2.14110946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14229369163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16361021995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18611097335815</t>
+    <t xml:space="preserve">2.14229393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16361045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.186110496521</t>
   </si>
   <si>
     <t xml:space="preserve">2.13874125480652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11979293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14939951896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13755702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16597867012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15532064437866</t>
+    <t xml:space="preserve">2.119793176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1493992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13755679130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16597890853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15532040596008</t>
   </si>
   <si>
     <t xml:space="preserve">2.20032167434692</t>
@@ -1070,40 +1070,40 @@
     <t xml:space="preserve">2.18374228477478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23821759223938</t>
+    <t xml:space="preserve">2.2382173538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.27374458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39453744888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38387942314148</t>
+    <t xml:space="preserve">2.39453768730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3838791847229</t>
   </si>
   <si>
     <t xml:space="preserve">2.34835195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36848425865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37322115898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36966824531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37203693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38032650947571</t>
+    <t xml:space="preserve">2.36848402023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37322092056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36966848373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37203669548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38032674789429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38861608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34361481666565</t>
+    <t xml:space="preserve">2.34361505508423</t>
   </si>
   <si>
     <t xml:space="preserve">2.30927205085754</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">2.28913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2938768863678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058857917786</t>
+    <t xml:space="preserve">2.29387640953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33058834075928</t>
   </si>
   <si>
     <t xml:space="preserve">2.34953618049622</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">2.31637740135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34479904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31756186485291</t>
+    <t xml:space="preserve">2.34479928016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31756162643433</t>
   </si>
   <si>
     <t xml:space="preserve">2.34006214141846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40401124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4099326133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37914252281189</t>
+    <t xml:space="preserve">2.40401148796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40993285179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37914228439331</t>
   </si>
   <si>
     <t xml:space="preserve">2.3554573059082</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">2.31045627593994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25953412055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27966594696045</t>
+    <t xml:space="preserve">2.25953388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27966618537903</t>
   </si>
   <si>
     <t xml:space="preserve">2.25598096847534</t>
@@ -1166,61 +1166,61 @@
     <t xml:space="preserve">2.22163820266724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19676923751831</t>
+    <t xml:space="preserve">2.19676899909973</t>
   </si>
   <si>
     <t xml:space="preserve">2.19321608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18847918510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18492674827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163566589355</t>
+    <t xml:space="preserve">2.18847942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18492650985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163542747498</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15058350563049</t>
+    <t xml:space="preserve">2.15058374404907</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13045167922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12097764015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11031913757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0842661857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22400665283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24295425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29624509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28795576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25005984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25834941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24413871765137</t>
+    <t xml:space="preserve">2.13045144081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1209774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11031937599182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08426570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22400641441345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24295449256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29624557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28795552253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25005960464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25834965705872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24413895606995</t>
   </si>
   <si>
     <t xml:space="preserve">2.22755908966064</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.23703336715698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24769115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2926926612854</t>
+    <t xml:space="preserve">2.24769139289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29269242286682</t>
   </si>
   <si>
     <t xml:space="preserve">2.3211145401001</t>
@@ -1244,34 +1244,34 @@
     <t xml:space="preserve">2.25716543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30453491210938</t>
+    <t xml:space="preserve">2.3045346736908</t>
   </si>
   <si>
     <t xml:space="preserve">2.29742956161499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124430656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31874561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27848196029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26663947105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28321862220764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32703566551208</t>
+    <t xml:space="preserve">2.25124382972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31874585151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27848172187805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2666392326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28321886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32703590393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.34598350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30571937561035</t>
+    <t xml:space="preserve">2.30571913719177</t>
   </si>
   <si>
     <t xml:space="preserve">2.27729725837708</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">2.20742702484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19203162193298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14821481704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19795322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20979571342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19913744926453</t>
+    <t xml:space="preserve">2.19203209877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14821529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19795298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2097954750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19913721084595</t>
   </si>
   <si>
     <t xml:space="preserve">2.23348069190979</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">2.23584914207458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28085017204285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26900768280029</t>
+    <t xml:space="preserve">2.28084993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26900792121887</t>
   </si>
   <si>
     <t xml:space="preserve">2.27256083488464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24177002906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27019214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26308655738831</t>
+    <t xml:space="preserve">2.24177026748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361275672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27019190788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26308631896973</t>
   </si>
   <si>
     <t xml:space="preserve">2.28677129745483</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">2.30098223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33177256584167</t>
+    <t xml:space="preserve">2.33177280426025</t>
   </si>
   <si>
     <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31519341468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39098477363586</t>
+    <t xml:space="preserve">2.31519317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39098525047302</t>
   </si>
   <si>
     <t xml:space="preserve">2.41585373878479</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">2.41940641403198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43717002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48098731040955</t>
+    <t xml:space="preserve">2.4371702671051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48098707199097</t>
   </si>
   <si>
     <t xml:space="preserve">2.53309345245361</t>
@@ -1361,46 +1361,46 @@
     <t xml:space="preserve">2.5674364566803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54612016677856</t>
+    <t xml:space="preserve">2.54612064361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.56151580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57572650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56862115859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57691121101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56980514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56625270843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63967537879944</t>
+    <t xml:space="preserve">2.57572627067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56862092018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57691097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56980538368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56625294685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63967561721802</t>
   </si>
   <si>
     <t xml:space="preserve">2.65743923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66691303253174</t>
+    <t xml:space="preserve">2.66691327095032</t>
   </si>
   <si>
     <t xml:space="preserve">2.63671493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62960958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58105540275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57158184051514</t>
+    <t xml:space="preserve">2.62960934638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58105564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57158160209656</t>
   </si>
   <si>
     <t xml:space="preserve">2.56921315193176</t>
@@ -1409,79 +1409,79 @@
     <t xml:space="preserve">2.48039484024048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53013277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45611810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217153549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44605207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40697169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4709210395813</t>
+    <t xml:space="preserve">2.53013300895691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45611786842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44605183601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40697193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236733436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47092080116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.45552587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44723606109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46559190750122</t>
+    <t xml:space="preserve">2.44723629951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46559166908264</t>
   </si>
   <si>
     <t xml:space="preserve">2.47388172149658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41881465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40934014320374</t>
+    <t xml:space="preserve">2.41881442070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40934038162231</t>
   </si>
   <si>
     <t xml:space="preserve">2.43480181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40756392478943</t>
+    <t xml:space="preserve">2.40756368637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.32644367218018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33473324775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35190463066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39631366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3744056224823</t>
+    <t xml:space="preserve">2.33473300933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35190486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39631390571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37440538406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.35782599449158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42592000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36611557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38624811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39986634254456</t>
+    <t xml:space="preserve">2.42591977119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36611580848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38624787330627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39986658096313</t>
   </si>
   <si>
     <t xml:space="preserve">2.32881212234497</t>
@@ -1490,61 +1490,61 @@
     <t xml:space="preserve">2.3524968624115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302258491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499761581421</t>
+    <t xml:space="preserve">2.34302282333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499785423279</t>
   </si>
   <si>
     <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39809012413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38565564155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4123010635376</t>
+    <t xml:space="preserve">2.39809060096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38565587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41230082511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.41822218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45078873634338</t>
+    <t xml:space="preserve">2.45078897476196</t>
   </si>
   <si>
     <t xml:space="preserve">2.51769852638245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51355361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54315972328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54079127311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54375171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756875991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61066174507141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58223962783813</t>
+    <t xml:space="preserve">2.51355338096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54079151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54375195503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756899833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61066126823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58224010467529</t>
   </si>
   <si>
     <t xml:space="preserve">2.59408235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61480617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63493847846985</t>
+    <t xml:space="preserve">2.61480641365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63493824005127</t>
   </si>
   <si>
     <t xml:space="preserve">2.65803122520447</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">2.67165040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67520308494568</t>
+    <t xml:space="preserve">2.6752028465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.58638453483582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60178017616272</t>
+    <t xml:space="preserve">2.60177993774414</t>
   </si>
   <si>
     <t xml:space="preserve">2.55855488777161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57039761543274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5934898853302</t>
+    <t xml:space="preserve">2.57039713859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59349012374878</t>
   </si>
   <si>
     <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51059293746948</t>
+    <t xml:space="preserve">2.51059317588806</t>
   </si>
   <si>
     <t xml:space="preserve">2.54967308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48868441581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49672627449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48621034622192</t>
+    <t xml:space="preserve">2.48868465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49672651290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48621010780334</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548393249512</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38785076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37733387947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25917863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176066398621</t>
+    <t xml:space="preserve">2.387850522995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773341178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25917840003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176114082336</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361108779907</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">2.28577923774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23752760887146</t>
+    <t xml:space="preserve">2.23752737045288</t>
   </si>
   <si>
     <t xml:space="preserve">2.22577381134033</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">2.16020083427429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24989938735962</t>
+    <t xml:space="preserve">2.24989986419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.2319598197937</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">2.23938298225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24371361732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20041036605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20968985557556</t>
+    <t xml:space="preserve">2.24371337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20041012763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2096893787384</t>
   </si>
   <si>
     <t xml:space="preserve">2.22329902648926</t>
@@ -1655,40 +1655,40 @@
     <t xml:space="preserve">2.20721507072449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15525126457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19298720359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05812907218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05874800682068</t>
+    <t xml:space="preserve">2.15525150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19298696517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05812931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0587477684021</t>
   </si>
   <si>
     <t xml:space="preserve">2.05379867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02843546867371</t>
+    <t xml:space="preserve">2.02843570709229</t>
   </si>
   <si>
     <t xml:space="preserve">2.04699420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04946875572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09215259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11689710617065</t>
+    <t xml:space="preserve">2.04946851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0921528339386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11689758300781</t>
   </si>
   <si>
     <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14102363586426</t>
+    <t xml:space="preserve">2.14102339744568</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813497543335</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">2.0686457157135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09091591835022</t>
+    <t xml:space="preserve">2.09091567993164</t>
   </si>
   <si>
     <t xml:space="preserve">2.10638117790222</t>
@@ -1712,31 +1712,31 @@
     <t xml:space="preserve">2.14349770545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13793039321899</t>
+    <t xml:space="preserve">2.13793015480042</t>
   </si>
   <si>
     <t xml:space="preserve">2.12122774124146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09957647323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11380457878113</t>
+    <t xml:space="preserve">2.0995762348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11380434036255</t>
   </si>
   <si>
     <t xml:space="preserve">2.14473533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18061470985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1651496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20102906227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09029674530029</t>
+    <t xml:space="preserve">2.18061494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16514945030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2010293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09029698371887</t>
   </si>
   <si>
     <t xml:space="preserve">2.12432074546814</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">2.10699963569641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13916778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1199905872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07730603218079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07235717773438</t>
+    <t xml:space="preserve">2.13916754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07730627059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0723569393158</t>
   </si>
   <si>
     <t xml:space="preserve">2.11937212944031</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">2.20474076271057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28392338752747</t>
+    <t xml:space="preserve">2.28392314910889</t>
   </si>
   <si>
     <t xml:space="preserve">2.23319721221924</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">2.24309492111206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26289033889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2529923915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26969528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711868286133</t>
+    <t xml:space="preserve">2.26289081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25299263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26969504356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711844444275</t>
   </si>
   <si>
     <t xml:space="preserve">2.25608563423157</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">2.24185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19917345046997</t>
+    <t xml:space="preserve">2.19917321205139</t>
   </si>
   <si>
     <t xml:space="preserve">2.2220618724823</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31423568725586</t>
+    <t xml:space="preserve">2.31423544883728</t>
   </si>
   <si>
     <t xml:space="preserve">2.3699107170105</t>
@@ -1817,67 +1817,67 @@
     <t xml:space="preserve">2.33712410926819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33836150169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3340311050415</t>
+    <t xml:space="preserve">2.33836126327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33403134346008</t>
   </si>
   <si>
     <t xml:space="preserve">2.3600127696991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40146017074585</t>
+    <t xml:space="preserve">2.40145993232727</t>
   </si>
   <si>
     <t xml:space="preserve">2.41630673408508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41445112228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4206371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45589780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44352579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47012615203857</t>
+    <t xml:space="preserve">2.41445088386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42063736915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45589828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44352602958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47012591362</t>
   </si>
   <si>
     <t xml:space="preserve">2.48682880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50600600242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3730034828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.367436170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30743050575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795281410217</t>
+    <t xml:space="preserve">2.50600576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37300372123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36743593215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30743026733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795257568359</t>
   </si>
   <si>
     <t xml:space="preserve">2.36496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27093243598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2808301448822</t>
+    <t xml:space="preserve">2.2709321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28083038330078</t>
   </si>
   <si>
     <t xml:space="preserve">2.19793581962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1985547542572</t>
+    <t xml:space="preserve">2.19855451583862</t>
   </si>
   <si>
     <t xml:space="preserve">2.20907115936279</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">2.16824269294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15648889541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0977201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13978624343872</t>
+    <t xml:space="preserve">2.15648865699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09772062301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13978600502014</t>
   </si>
   <si>
     <t xml:space="preserve">2.12184643745422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19669890403748</t>
+    <t xml:space="preserve">2.19669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.17381024360657</t>
@@ -1916,40 +1916,40 @@
     <t xml:space="preserve">2.21525716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24247598648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24433183670044</t>
+    <t xml:space="preserve">2.24247646331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24433207511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.24742484092712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2597975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33217525482178</t>
+    <t xml:space="preserve">2.25979709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3321750164032</t>
   </si>
   <si>
     <t xml:space="preserve">2.34949660301208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26598358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26227188110352</t>
+    <t xml:space="preserve">2.26598381996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26227164268494</t>
   </si>
   <si>
     <t xml:space="preserve">2.28825354576111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22701048851013</t>
+    <t xml:space="preserve">2.22701072692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.2041220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15834474563599</t>
+    <t xml:space="preserve">2.15834498405457</t>
   </si>
   <si>
     <t xml:space="preserve">2.1373119354248</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">2.23443412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22639203071594</t>
+    <t xml:space="preserve">2.2263925075531</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24680638313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23381543159485</t>
+    <t xml:space="preserve">2.24680662155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23381567001343</t>
   </si>
   <si>
     <t xml:space="preserve">2.15277719497681</t>
@@ -1982,46 +1982,46 @@
     <t xml:space="preserve">2.18556380271912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21278262138367</t>
+    <t xml:space="preserve">2.21278285980225</t>
   </si>
   <si>
     <t xml:space="preserve">2.19607996940613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504197120667</t>
+    <t xml:space="preserve">2.11504149436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17628407478333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14040493965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27959299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32413339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31794691085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35073351860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38846898078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41012024879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43053460121155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32227754592896</t>
+    <t xml:space="preserve">2.17628455162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14040470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27959322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3241331577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31794714927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35073375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41012048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43053507804871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32227778434753</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.41259527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43424654006958</t>
+    <t xml:space="preserve">2.43424677848816</t>
   </si>
   <si>
     <t xml:space="preserve">2.44971203804016</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.45342373847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54930853843689</t>
+    <t xml:space="preserve">2.54930877685547</t>
   </si>
   <si>
     <t xml:space="preserve">2.55116486549377</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">2.47321915626526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136330604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50043845176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51528477668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52394556999207</t>
+    <t xml:space="preserve">2.47136354446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50043797492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5152850151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52394533157349</t>
   </si>
   <si>
     <t xml:space="preserve">2.4620840549469</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">2.32908225059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36125016212463</t>
+    <t xml:space="preserve">2.36124992370605</t>
   </si>
   <si>
     <t xml:space="preserve">2.42620468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44105124473572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609696388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45713520050049</t>
+    <t xml:space="preserve">2.4410514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45713543891907</t>
   </si>
   <si>
     <t xml:space="preserve">2.45094895362854</t>
@@ -2090,22 +2090,22 @@
     <t xml:space="preserve">2.47507500648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46579575538635</t>
+    <t xml:space="preserve">2.46579599380493</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569346427917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49054074287415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48188018798828</t>
+    <t xml:space="preserve">2.49054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4818799495697</t>
   </si>
   <si>
     <t xml:space="preserve">2.47878670692444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49548959732056</t>
+    <t xml:space="preserve">2.49548935890198</t>
   </si>
   <si>
     <t xml:space="preserve">2.50662422180176</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">2.53446221351624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50786161422729</t>
+    <t xml:space="preserve">2.50786137580872</t>
   </si>
   <si>
     <t xml:space="preserve">2.55302047729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58147668838501</t>
+    <t xml:space="preserve">2.56601119041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58147644996643</t>
   </si>
   <si>
     <t xml:space="preserve">2.64952421188354</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">2.68292951583862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69901299476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220900535583</t>
+    <t xml:space="preserve">2.69901323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.68231081962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66870164871216</t>
+    <t xml:space="preserve">2.668701171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179417610168</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">2.69282722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71014809608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74664688110352</t>
+    <t xml:space="preserve">2.71014833450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74664664268494</t>
   </si>
   <si>
     <t xml:space="preserve">2.76396751403809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7299439907074</t>
+    <t xml:space="preserve">2.72994422912598</t>
   </si>
   <si>
     <t xml:space="preserve">2.83696436882019</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">2.83448958396912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86109042167664</t>
+    <t xml:space="preserve">2.86109018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.85057377815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79799175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716328620911</t>
+    <t xml:space="preserve">2.79799151420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716280937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.76025605201721</t>
@@ -2189,34 +2189,34 @@
     <t xml:space="preserve">2.78500080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78994965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83943915367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83882021903992</t>
+    <t xml:space="preserve">2.78994989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82088017463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83943867683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83882069587708</t>
   </si>
   <si>
     <t xml:space="preserve">2.79737305641174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81160140037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78685688972473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922866821289</t>
+    <t xml:space="preserve">2.81160116195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78685665130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922890663147</t>
   </si>
   <si>
     <t xml:space="preserve">2.80603361129761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81778717041016</t>
+    <t xml:space="preserve">2.81778693199158</t>
   </si>
   <si>
     <t xml:space="preserve">2.79551720619202</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">2.65694761276245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65014266967773</t>
+    <t xml:space="preserve">2.65014290809631</t>
   </si>
   <si>
     <t xml:space="preserve">2.59137439727783</t>
@@ -2237,28 +2237,28 @@
     <t xml:space="preserve">2.69097113609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66560864448547</t>
+    <t xml:space="preserve">2.66560816764832</t>
   </si>
   <si>
     <t xml:space="preserve">2.73056292533875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79984784126282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76334929466248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75045776367188</t>
+    <t xml:space="preserve">2.79984760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76334953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7504575252533</t>
   </si>
   <si>
     <t xml:space="preserve">2.75625872612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79106664657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68084168434143</t>
+    <t xml:space="preserve">2.79106688499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68084192276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.79235553741455</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">2.62863039970398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65892624855042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66279339790344</t>
+    <t xml:space="preserve">2.65892577171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66279363632202</t>
   </si>
   <si>
     <t xml:space="preserve">2.6344313621521</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">2.66666126251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65183520317078</t>
+    <t xml:space="preserve">2.65183544158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.66472721099854</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">2.6885769367218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6943781375885</t>
+    <t xml:space="preserve">2.69437861442566</t>
   </si>
   <si>
     <t xml:space="preserve">2.689866065979</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">2.72016167640686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69695663452148</t>
+    <t xml:space="preserve">2.69695687294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.65247988700867</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">2.69953513145447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7530357837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73563194274902</t>
+    <t xml:space="preserve">2.75303554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7356321811676</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176431655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76206016540527</t>
+    <t xml:space="preserve">2.76205992698669</t>
   </si>
   <si>
     <t xml:space="preserve">2.75883746147156</t>
@@ -2336,10 +2336,10 @@
     <t xml:space="preserve">2.76077055931091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79944634437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82007312774658</t>
+    <t xml:space="preserve">2.79944610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82007336616516</t>
   </si>
   <si>
     <t xml:space="preserve">2.86197137832642</t>
@@ -2348,31 +2348,31 @@
     <t xml:space="preserve">2.91160464286804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90773701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89162254333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89484524726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97477388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96832847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97541904449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98702144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96897268295288</t>
+    <t xml:space="preserve">2.90773677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89162230491638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8948450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414757728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97477412223816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96832823753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97541880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98702096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96897292137146</t>
   </si>
   <si>
     <t xml:space="preserve">2.97735238075256</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">2.91805028915405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04181146621704</t>
+    <t xml:space="preserve">3.04181098937988</t>
   </si>
   <si>
     <t xml:space="preserve">3.02118420600891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03665447235107</t>
+    <t xml:space="preserve">3.03665471076965</t>
   </si>
   <si>
     <t xml:space="preserve">3.03923296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04825735092163</t>
+    <t xml:space="preserve">3.04825711250305</t>
   </si>
   <si>
     <t xml:space="preserve">3.00829243659973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97155141830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98895525932312</t>
+    <t xml:space="preserve">2.97155117988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98895502090454</t>
   </si>
   <si>
     <t xml:space="preserve">2.90902590751648</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">2.86003732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84263324737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78655433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7659273147583</t>
+    <t xml:space="preserve">2.84263396263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78655409812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76592755317688</t>
   </si>
   <si>
     <t xml:space="preserve">2.83812117576599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73434281349182</t>
+    <t xml:space="preserve">2.7343430519104</t>
   </si>
   <si>
     <t xml:space="preserve">2.78010892868042</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">2.84843492507935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87421870231628</t>
+    <t xml:space="preserve">2.87421846389771</t>
   </si>
   <si>
     <t xml:space="preserve">2.95608115196228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9477014541626</t>
+    <t xml:space="preserve">2.94770121574402</t>
   </si>
   <si>
     <t xml:space="preserve">2.91869497299194</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">2.91676139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94705677032471</t>
+    <t xml:space="preserve">2.94705700874329</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031527519226</t>
@@ -2456,241 +2456,241 @@
     <t xml:space="preserve">2.96510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94576740264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94125556945801</t>
+    <t xml:space="preserve">2.94576811790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94125580787659</t>
   </si>
   <si>
     <t xml:space="preserve">2.94383382797241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97606348991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95479202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95801520347595</t>
+    <t xml:space="preserve">2.97606301307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9547917842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95801496505737</t>
   </si>
   <si>
     <t xml:space="preserve">2.98959970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05921530723572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11013770103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10884833335876</t>
+    <t xml:space="preserve">3.0592155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11013722419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10884857177734</t>
   </si>
   <si>
     <t xml:space="preserve">3.080486536026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11464977264404</t>
+    <t xml:space="preserve">3.11464929580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.10240268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09853529930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06372690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10175824165344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12431836128235</t>
+    <t xml:space="preserve">3.09853506088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06372714042664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10175776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12431859970093</t>
   </si>
   <si>
     <t xml:space="preserve">3.14945769309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592147827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661867141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05663681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698588371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275176048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696846008301</t>
+    <t xml:space="preserve">3.13592100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661890983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05663704872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696798324585</t>
   </si>
   <si>
     <t xml:space="preserve">3.08757710456848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12560796737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19071125984192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15396976470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15010213851929</t>
+    <t xml:space="preserve">3.12560772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19071102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15396952629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15010237693787</t>
   </si>
   <si>
     <t xml:space="preserve">3.17781925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20553684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22680807113647</t>
+    <t xml:space="preserve">3.20553660392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22680830955505</t>
   </si>
   <si>
     <t xml:space="preserve">3.22165131568909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21262764930725</t>
+    <t xml:space="preserve">3.21262717247009</t>
   </si>
   <si>
     <t xml:space="preserve">3.23325395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25001335144043</t>
+    <t xml:space="preserve">3.25001311302185</t>
   </si>
   <si>
     <t xml:space="preserve">3.21391630172729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23970007896423</t>
+    <t xml:space="preserve">3.23970031738281</t>
   </si>
   <si>
     <t xml:space="preserve">3.26548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24743485450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229623794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388073921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447219848633</t>
+    <t xml:space="preserve">3.24743461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2222957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388050079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739881515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447267532349</t>
   </si>
   <si>
     <t xml:space="preserve">3.35185790061951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39955806732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4111602306366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43307638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49108910560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304034233093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43823289871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45370316505432</t>
+    <t xml:space="preserve">3.39955854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41115951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43307685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4910888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823313713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45370292663574</t>
   </si>
   <si>
     <t xml:space="preserve">3.39311146736145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40600347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41631770133972</t>
+    <t xml:space="preserve">3.40600323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41631722450256</t>
   </si>
   <si>
     <t xml:space="preserve">3.41502785682678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41373872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44596791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987133979797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920899391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34541249275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.389244556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38795447349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34799027442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29126691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192950248718</t>
+    <t xml:space="preserve">3.413738489151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44596838951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920923233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3454122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994246482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38924431800842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38795518875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34799075126648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29126739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2719292640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.32865309715271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36861753463745</t>
+    <t xml:space="preserve">3.36861729621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.43049812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43694353103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4240517616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4781973361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4549925327301</t>
+    <t xml:space="preserve">3.43694376945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42405200004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45499229431152</t>
   </si>
   <si>
     <t xml:space="preserve">3.37635278701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29513430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032638549805</t>
+    <t xml:space="preserve">3.2951340675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35572552680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032686233521</t>
   </si>
   <si>
     <t xml:space="preserve">3.22938656806946</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">3.30544757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33252096176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576132774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841118812561</t>
+    <t xml:space="preserve">3.33252048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576085090637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841071128845</t>
   </si>
   <si>
     <t xml:space="preserve">3.1475236415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18491005897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006681442261</t>
+    <t xml:space="preserve">3.18490958213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006609916687</t>
   </si>
   <si>
     <t xml:space="preserve">3.16815066337585</t>
@@ -2723,10 +2723,10 @@
     <t xml:space="preserve">3.17395162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1320538520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09982419013977</t>
+    <t xml:space="preserve">3.13205361366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09982395172119</t>
   </si>
   <si>
     <t xml:space="preserve">3.12238478660583</t>
@@ -2735,25 +2735,25 @@
     <t xml:space="preserve">3.04890203475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11593890190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14623475074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02182912826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96703886985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00958228111267</t>
+    <t xml:space="preserve">3.11593914031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14623427391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0218288898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96703910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00958132743835</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09466767311096</t>
+    <t xml:space="preserve">3.09466743469238</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
@@ -2762,28 +2762,28 @@
     <t xml:space="preserve">3.15848183631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18297600746155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4008469581604</t>
+    <t xml:space="preserve">3.18297648429871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40084648132324</t>
   </si>
   <si>
     <t xml:space="preserve">3.44854640960693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54394555091858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47561955451965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39440107345581</t>
+    <t xml:space="preserve">3.5439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47561931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39440083503723</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459654808044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1423671245575</t>
+    <t xml:space="preserve">3.14236736297607</t>
   </si>
   <si>
     <t xml:space="preserve">3.01409411430359</t>
@@ -2792,31 +2792,31 @@
     <t xml:space="preserve">2.8858208656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7427225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610512733459</t>
+    <t xml:space="preserve">2.74272274971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017981529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610536575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.51969504356384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24896812438965</t>
+    <t xml:space="preserve">2.24896788597107</t>
   </si>
   <si>
     <t xml:space="preserve">2.15936994552612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17741847038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88993239402771</t>
+    <t xml:space="preserve">2.17741870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646730422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88993215560913</t>
   </si>
   <si>
     <t xml:space="preserve">1.7661714553833</t>
@@ -2825,43 +2825,43 @@
     <t xml:space="preserve">1.68817639350891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62500667572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91313767433167</t>
+    <t xml:space="preserve">1.62500655651093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91313743591309</t>
   </si>
   <si>
     <t xml:space="preserve">1.77261734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83965468406677</t>
+    <t xml:space="preserve">1.83965444564819</t>
   </si>
   <si>
     <t xml:space="preserve">1.93827641010284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94149911403656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04141068458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90669143199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923412799835</t>
+    <t xml:space="preserve">1.94149947166443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04141044616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9066915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923436641693</t>
   </si>
   <si>
     <t xml:space="preserve">2.02013921737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05236840248108</t>
+    <t xml:space="preserve">2.05236864089966</t>
   </si>
   <si>
     <t xml:space="preserve">1.98662066459656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11296010017395</t>
+    <t xml:space="preserve">2.11295986175537</t>
   </si>
   <si>
     <t xml:space="preserve">2.12327313423157</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">2.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09104371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278883934021</t>
+    <t xml:space="preserve">2.0910439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278848171234</t>
   </si>
   <si>
     <t xml:space="preserve">1.92087256908417</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">1.93892085552216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90282416343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8306303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89766764640808</t>
+    <t xml:space="preserve">1.90282392501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83063018321991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89766728878021</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379966259003</t>
@@ -2909,37 +2909,37 @@
     <t xml:space="preserve">2.0265851020813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0252959728241</t>
+    <t xml:space="preserve">2.02529621124268</t>
   </si>
   <si>
     <t xml:space="preserve">2.04463338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04721188545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05752539634705</t>
+    <t xml:space="preserve">2.04721212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05752491950989</t>
   </si>
   <si>
     <t xml:space="preserve">2.01627159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0175609588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790967464447</t>
+    <t xml:space="preserve">2.01756072044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790979385376</t>
   </si>
   <si>
     <t xml:space="preserve">1.97243988513947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32651424407959</t>
+    <t xml:space="preserve">2.32651400566101</t>
   </si>
   <si>
     <t xml:space="preserve">2.22702980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21850252151489</t>
+    <t xml:space="preserve">2.21850228309631</t>
   </si>
   <si>
     <t xml:space="preserve">2.17018151283264</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">2.21992373466492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28387808799744</t>
+    <t xml:space="preserve">2.28387784957886</t>
   </si>
   <si>
     <t xml:space="preserve">2.27535057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26540231704712</t>
+    <t xml:space="preserve">2.26540207862854</t>
   </si>
   <si>
     <t xml:space="preserve">2.31372332572937</t>
@@ -2966,31 +2966,31 @@
     <t xml:space="preserve">2.25687527656555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46863484382629</t>
+    <t xml:space="preserve">2.39046835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46863508224487</t>
   </si>
   <si>
     <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61644005775452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56669783592224</t>
+    <t xml:space="preserve">2.63633704185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6164402961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5666983127594</t>
   </si>
   <si>
     <t xml:space="preserve">2.48995280265808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37909889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38336229324341</t>
+    <t xml:space="preserve">2.37909865379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38336253166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.38762593269348</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44873809814453</t>
+    <t xml:space="preserve">2.44873785972595</t>
   </si>
   <si>
     <t xml:space="preserve">2.47574067115784</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">2.53258895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53116774559021</t>
+    <t xml:space="preserve">2.53116798400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.55817055702209</t>
@@ -3041,37 +3041,37 @@
     <t xml:space="preserve">2.57238292694092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58090996742249</t>
+    <t xml:space="preserve">2.58091020584106</t>
   </si>
   <si>
     <t xml:space="preserve">2.51127099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53685235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56527662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60933375358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64202189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63207316398621</t>
+    <t xml:space="preserve">2.53685259819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5652768611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60933423042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64202213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63207364082336</t>
   </si>
   <si>
     <t xml:space="preserve">2.65481281280518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67755222320557</t>
+    <t xml:space="preserve">2.67755198478699</t>
   </si>
   <si>
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76424598693848</t>
+    <t xml:space="preserve">2.7642457485199</t>
   </si>
   <si>
     <t xml:space="preserve">2.64770674705505</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">2.61501884460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60649180412292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4572651386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54680109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186737060547</t>
+    <t xml:space="preserve">2.60649156570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54680132865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186713218689</t>
   </si>
   <si>
     <t xml:space="preserve">2.66049766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68465805053711</t>
+    <t xml:space="preserve">2.68465828895569</t>
   </si>
   <si>
     <t xml:space="preserve">2.7528760433197</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">2.92768406867981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89641785621643</t>
+    <t xml:space="preserve">2.89641809463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.92199945449829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86373043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83388447761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88931155204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8495180606842</t>
+    <t xml:space="preserve">2.86373019218445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83388471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88931179046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84951829910278</t>
   </si>
   <si>
     <t xml:space="preserve">2.84099078178406</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">2.95895075798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94616007804871</t>
+    <t xml:space="preserve">2.94615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">2.94900250434875</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">2.88789081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85378122329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81256651878357</t>
+    <t xml:space="preserve">2.85378170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81256675720215</t>
   </si>
   <si>
     <t xml:space="preserve">2.78556370735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90068101882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87794208526611</t>
+    <t xml:space="preserve">2.9006814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87794232368469</t>
   </si>
   <si>
     <t xml:space="preserve">2.94189643859863</t>
@@ -3170,34 +3170,34 @@
     <t xml:space="preserve">2.95184469223022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95753002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93621158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91489338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85662388801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70313382148743</t>
+    <t xml:space="preserve">2.9575297832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93621134757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91489362716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85662436485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70313358306885</t>
   </si>
   <si>
     <t xml:space="preserve">2.74861240386963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69602751731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70455479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72729420661926</t>
+    <t xml:space="preserve">2.6960277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70455503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6576554775238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72729444503784</t>
   </si>
   <si>
     <t xml:space="preserve">2.66902470588684</t>
@@ -3212,28 +3212,28 @@
     <t xml:space="preserve">2.610755443573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68039441108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62354612350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63065242767334</t>
+    <t xml:space="preserve">2.68039464950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62354636192322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63065218925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.61359786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56243419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45868611335754</t>
+    <t xml:space="preserve">2.56243443489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4586865901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.5027437210083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48853206634521</t>
+    <t xml:space="preserve">2.48853158950806</t>
   </si>
   <si>
     <t xml:space="preserve">2.4970588684082</t>
@@ -3242,25 +3242,25 @@
     <t xml:space="preserve">2.52690410614014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48568940162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42741990089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39899563789368</t>
+    <t xml:space="preserve">2.48568916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42741966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39899587631226</t>
   </si>
   <si>
     <t xml:space="preserve">2.37199258804321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2540328502655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23129320144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276639938354</t>
+    <t xml:space="preserve">2.25403261184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23129343986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276616096497</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">2.52264070510864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52832555770874</t>
+    <t xml:space="preserve">2.52832579612732</t>
   </si>
   <si>
     <t xml:space="preserve">2.55532813072205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71450352668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76850938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74008512496948</t>
+    <t xml:space="preserve">2.71450328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76850914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74008536338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.84383320808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83672690391541</t>
+    <t xml:space="preserve">2.83672714233398</t>
   </si>
   <si>
     <t xml:space="preserve">2.97174191474915</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">2.93052673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90920829772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81967258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8097243309021</t>
+    <t xml:space="preserve">2.90920853614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81967282295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80972409248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.78840613365173</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">2.78130006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78272080421448</t>
+    <t xml:space="preserve">2.78272104263306</t>
   </si>
   <si>
     <t xml:space="preserve">2.77561521530151</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">2.70597624778748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70739722251892</t>
+    <t xml:space="preserve">2.7073974609375</t>
   </si>
   <si>
     <t xml:space="preserve">2.7130823135376</t>
@@ -3350,22 +3350,22 @@
     <t xml:space="preserve">2.75571846961975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79266977310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77419424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77845788002014</t>
+    <t xml:space="preserve">2.79267001152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77419400215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77845764160156</t>
   </si>
   <si>
     <t xml:space="preserve">2.75713992118835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83246350288391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86088752746582</t>
+    <t xml:space="preserve">2.83246326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8608877658844</t>
   </si>
   <si>
     <t xml:space="preserve">2.85946655273438</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">2.91347217559814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88646936416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88362693786621</t>
+    <t xml:space="preserve">2.88646912574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88362717628479</t>
   </si>
   <si>
     <t xml:space="preserve">2.84241199493408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76993036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74719095230103</t>
+    <t xml:space="preserve">2.76993060112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7471911907196</t>
   </si>
   <si>
     <t xml:space="preserve">2.79551219940186</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">2.67897343635559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68181586265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74576997756958</t>
+    <t xml:space="preserve">2.68181562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74577021598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.64344310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57522559165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64486384391785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546045303345</t>
+    <t xml:space="preserve">2.57522511482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.644864320755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546069145203</t>
   </si>
   <si>
     <t xml:space="preserve">2.86657238006592</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">2.94758105278015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13233780860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10533475875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18350124359131</t>
+    <t xml:space="preserve">3.13233804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1053352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18350148200989</t>
   </si>
   <si>
     <t xml:space="preserve">3.14939260482788</t>
@@ -3434,70 +3434,70 @@
     <t xml:space="preserve">3.13944411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15791988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12665343284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03995966911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742676734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01153516769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03427481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08259558677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13375902175903</t>
+    <t xml:space="preserve">3.15791964530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12665319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01153540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03427457809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08259582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13375949859619</t>
   </si>
   <si>
     <t xml:space="preserve">3.11812615394592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05843496322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19345021247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16928911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21192598342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25171971321106</t>
+    <t xml:space="preserve">3.0584352016449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19344997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16928935050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2119255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25171947479248</t>
   </si>
   <si>
     <t xml:space="preserve">3.14797115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30004048347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28867077827454</t>
+    <t xml:space="preserve">3.30004024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28867053985596</t>
   </si>
   <si>
     <t xml:space="preserve">3.29435539245605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30146169662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32562160491943</t>
+    <t xml:space="preserve">3.30146145820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32562184333801</t>
   </si>
   <si>
     <t xml:space="preserve">3.30572509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35262441635132</t>
+    <t xml:space="preserve">3.3526246547699</t>
   </si>
   <si>
     <t xml:space="preserve">3.37110018730164</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">3.41942143440247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36967921257019</t>
+    <t xml:space="preserve">3.36967968940735</t>
   </si>
   <si>
     <t xml:space="preserve">3.26451015472412</t>
@@ -3515,73 +3515,73 @@
     <t xml:space="preserve">3.27587985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30856800079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947294235229</t>
+    <t xml:space="preserve">3.30856728553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947318077087</t>
   </si>
   <si>
     <t xml:space="preserve">3.37962794303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38247036933899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4037880897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42013216018677</t>
+    <t xml:space="preserve">3.38247060775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40378832817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42013239860535</t>
   </si>
   <si>
     <t xml:space="preserve">3.32846450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29790854454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272790908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35902047157288</t>
+    <t xml:space="preserve">3.29790830612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272814750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3590202331543</t>
   </si>
   <si>
     <t xml:space="preserve">3.3668372631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34978270530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42723798751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500327110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32206916809082</t>
+    <t xml:space="preserve">3.34978246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42723822593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32206892967224</t>
   </si>
   <si>
     <t xml:space="preserve">3.28014349937439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29719805717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.315673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33201742172241</t>
+    <t xml:space="preserve">3.2971978187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31567335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33201766014099</t>
   </si>
   <si>
     <t xml:space="preserve">3.3043041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31780576705933</t>
+    <t xml:space="preserve">3.31780481338501</t>
   </si>
   <si>
     <t xml:space="preserve">3.28440713882446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23679637908936</t>
+    <t xml:space="preserve">3.2367959022522</t>
   </si>
   <si>
     <t xml:space="preserve">3.31212019920349</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">3.42226386070251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48550796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47555923461914</t>
+    <t xml:space="preserve">3.48550772666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47555899620056</t>
   </si>
   <si>
     <t xml:space="preserve">3.49545621871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48124408721924</t>
+    <t xml:space="preserve">3.48124432563782</t>
   </si>
   <si>
     <t xml:space="preserve">3.57575440406799</t>
@@ -3635,43 +3635,43 @@
     <t xml:space="preserve">3.43120455741882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41614174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44927883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48919415473938</t>
+    <t xml:space="preserve">3.41614198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44927906990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48919463157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.46584796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47488474845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45831680297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844122886658</t>
+    <t xml:space="preserve">3.47488498687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45831656455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844146728516</t>
   </si>
   <si>
     <t xml:space="preserve">3.46132922172546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45078468322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44626712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44099426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41764831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38752317428589</t>
+    <t xml:space="preserve">3.4507851600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44626688957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44099473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41764807701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38752341270447</t>
   </si>
   <si>
     <t xml:space="preserve">3.36041116714478</t>
@@ -3680,100 +3680,100 @@
     <t xml:space="preserve">3.32501459121704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24744319915771</t>
+    <t xml:space="preserve">3.24744367599487</t>
   </si>
   <si>
     <t xml:space="preserve">3.27229619026184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23765254020691</t>
+    <t xml:space="preserve">3.23765301704407</t>
   </si>
   <si>
     <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28359317779541</t>
+    <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
     <t xml:space="preserve">3.21430635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24970269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279532432556</t>
+    <t xml:space="preserve">3.24970293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279556274414</t>
   </si>
   <si>
     <t xml:space="preserve">3.35062074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37697958946228</t>
+    <t xml:space="preserve">3.37698006629944</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2948899269104</t>
+    <t xml:space="preserve">3.29489016532898</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731877326965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30468082427979</t>
+    <t xml:space="preserve">3.30468058586121</t>
   </si>
   <si>
     <t xml:space="preserve">3.316730260849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33329892158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32953333854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29112410545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28208661079407</t>
+    <t xml:space="preserve">3.33329916000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32953357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29112458229065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28208684921265</t>
   </si>
   <si>
     <t xml:space="preserve">3.14878511428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19999694824219</t>
+    <t xml:space="preserve">3.19999718666077</t>
   </si>
   <si>
     <t xml:space="preserve">3.32802724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33028626441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33480525016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38601684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37321400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4221670627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4071044921875</t>
+    <t xml:space="preserve">3.33028650283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33480501174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3860170841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37321424484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42216730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40710473060608</t>
   </si>
   <si>
     <t xml:space="preserve">3.38149809837341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42141366004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37170815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36643600463867</t>
+    <t xml:space="preserve">3.4214141368866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37170791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36643624305725</t>
   </si>
   <si>
     <t xml:space="preserve">3.39204216003418</t>
@@ -3785,193 +3785,193 @@
     <t xml:space="preserve">3.61797761917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60592794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6164710521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65337347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078045845032</t>
+    <t xml:space="preserve">3.60592746734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65337419509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63981795310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307806968689</t>
   </si>
   <si>
     <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72040152549744</t>
+    <t xml:space="preserve">3.72040176391602</t>
   </si>
   <si>
     <t xml:space="preserve">3.6752142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66542410850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7505259513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77462601661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77311968803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79872584342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77613210678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78215670585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76709461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78667569160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73697018623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77763819694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71663618087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71588277816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533919334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6375584602356</t>
+    <t xml:space="preserve">3.66542387008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75052642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77462577819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77311992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79872560501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77613258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7821569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76709508895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78667593002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73696994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77763843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71663570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71588230133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533895492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63755822181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.68726396560669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994261741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638637542725</t>
+    <t xml:space="preserve">3.6699423789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638661384583</t>
   </si>
   <si>
     <t xml:space="preserve">3.72567319869995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67144870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258080482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132380485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429177284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80926966667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450135231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625653266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84541869163513</t>
+    <t xml:space="preserve">3.67144918441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64132404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75203227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80926942825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450063705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8062572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84541893005371</t>
   </si>
   <si>
     <t xml:space="preserve">3.83939409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717458724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006234169006</t>
+    <t xml:space="preserve">3.90717506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006210327148</t>
   </si>
   <si>
     <t xml:space="preserve">3.95386791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97947382926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9598925113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483065605164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89060544967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95682597160339</t>
+    <t xml:space="preserve">3.97947359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483041763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89060592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88307523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92976808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95682573318481</t>
   </si>
   <si>
     <t xml:space="preserve">3.99502515792847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01571655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96239686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95125555992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99025011062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97910928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98388361930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95523381233215</t>
+    <t xml:space="preserve">4.01571702957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96239709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95125532150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99025058746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9791088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98388409614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95523428916931</t>
   </si>
   <si>
     <t xml:space="preserve">4.00457572937012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98070049285889</t>
+    <t xml:space="preserve">3.98070096969604</t>
   </si>
   <si>
     <t xml:space="preserve">4.0189003944397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9735381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98706746101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807171821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340111732483</t>
+    <t xml:space="preserve">3.97353863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807195663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340159416199</t>
   </si>
   <si>
     <t xml:space="preserve">3.98229241371155</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">4.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98865866661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93454313278198</t>
+    <t xml:space="preserve">3.98865842819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9345428943634</t>
   </si>
   <si>
     <t xml:space="preserve">3.97274279594421</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">3.66078019142151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590093612671</t>
+    <t xml:space="preserve">3.67590069770813</t>
   </si>
   <si>
     <t xml:space="preserve">3.66316771507263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73638367652893</t>
+    <t xml:space="preserve">3.73638343811035</t>
   </si>
   <si>
     <t xml:space="preserve">3.72524189949036</t>
@@ -4016,49 +4016,49 @@
     <t xml:space="preserve">3.70057153701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76821637153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779834747314</t>
+    <t xml:space="preserve">3.76821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779858589172</t>
   </si>
   <si>
     <t xml:space="preserve">3.7721951007843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76264572143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74752497673035</t>
+    <t xml:space="preserve">3.76264548301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74752521514893</t>
   </si>
   <si>
     <t xml:space="preserve">3.72922086715698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73081254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77856230735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74513745307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64565968513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74832081794739</t>
+    <t xml:space="preserve">3.73081278800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77856206893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74513721466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64565992355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74832057952881</t>
   </si>
   <si>
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77697062492371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83267760276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641627311707</t>
+    <t xml:space="preserve">3.77697038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641508102417</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
@@ -4070,58 +4070,58 @@
     <t xml:space="preserve">3.85973572731018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93613505363464</t>
+    <t xml:space="preserve">3.93613457679749</t>
   </si>
   <si>
     <t xml:space="preserve">3.86212301254272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87008118629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554738998413</t>
+    <t xml:space="preserve">3.87008142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554762840271</t>
   </si>
   <si>
     <t xml:space="preserve">3.91146421432495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97115111351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96398854255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95443820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99980044364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91942238807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76344156265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402827262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90748524665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90430164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94409275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00775861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96796774864197</t>
+    <t xml:space="preserve">3.97115063667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9639880657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95443844795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91942262649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76344132423401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90748476982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603060722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90430188179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9440929889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96796751022339</t>
   </si>
   <si>
     <t xml:space="preserve">3.85575652122498</t>
@@ -4133,19 +4133,19 @@
     <t xml:space="preserve">4.03004169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01253318786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00935029983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99820876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91623950004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85814428329468</t>
+    <t xml:space="preserve">4.01253366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00934982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91623902320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85814452171326</t>
   </si>
   <si>
     <t xml:space="preserve">3.78094935417175</t>
@@ -4154,22 +4154,22 @@
     <t xml:space="preserve">3.55414009094238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69261336326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60746026039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42760443687439</t>
+    <t xml:space="preserve">3.69261312484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60746002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42760467529297</t>
   </si>
   <si>
     <t xml:space="preserve">3.40293407440186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34483933448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06948494911194</t>
+    <t xml:space="preserve">3.34483909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06948471069336</t>
   </si>
   <si>
     <t xml:space="preserve">2.94374465942383</t>
@@ -4184,10 +4184,10 @@
     <t xml:space="preserve">3.39338421821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51912379264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56846499443054</t>
+    <t xml:space="preserve">3.51912403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5684654712677</t>
   </si>
   <si>
     <t xml:space="preserve">3.73797512054443</t>
@@ -4196,46 +4196,46 @@
     <t xml:space="preserve">3.69022583961487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6838595867157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70852947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354577064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90111875534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90668916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92021822929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97194671630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693065643311</t>
+    <t xml:space="preserve">3.68385934829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70852971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74036240577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354529380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90111827850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90668892860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9202184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97194695472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319270133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693041801453</t>
   </si>
   <si>
     <t xml:space="preserve">4.03481674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06346607208252</t>
+    <t xml:space="preserve">4.06346654891968</t>
   </si>
   <si>
     <t xml:space="preserve">4.02844953536987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11758184432983</t>
+    <t xml:space="preserve">4.11758136749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.09848213195801</t>
@@ -4244,40 +4244,40 @@
     <t xml:space="preserve">4.12235689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1334981918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16055679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16214799880981</t>
+    <t xml:space="preserve">4.13349866867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16055631637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16214847564697</t>
   </si>
   <si>
     <t xml:space="preserve">4.20193958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21467161178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1971640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599063873291</t>
+    <t xml:space="preserve">4.21467256546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19716453552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1541895866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599016189575</t>
   </si>
   <si>
     <t xml:space="preserve">4.13668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14623212814331</t>
+    <t xml:space="preserve">4.14623165130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1939811706543</t>
+    <t xml:space="preserve">4.19398069381714</t>
   </si>
   <si>
     <t xml:space="preserve">4.17488098144531</t>
@@ -4286,76 +4286,76 @@
     <t xml:space="preserve">4.12554025650024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0650577545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16373920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26719665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28470420837402</t>
+    <t xml:space="preserve">4.06505727767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1637396812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26719617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28470468521118</t>
   </si>
   <si>
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90509748458862</t>
+    <t xml:space="preserve">3.9050977230072</t>
   </si>
   <si>
     <t xml:space="preserve">4.00298404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00139236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12431716918945</t>
+    <t xml:space="preserve">4.00139188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12431621551514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24703931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28597164154053</t>
+    <t xml:space="preserve">4.23011159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24703884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28597116470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.25042390823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21487665176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14547491073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14124393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09723329544067</t>
+    <t xml:space="preserve">4.21487712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14547538757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14124345779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09723281860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.19202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20810651779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11754560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10738897323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77053737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383166313171</t>
+    <t xml:space="preserve">4.20810604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11754512786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10738945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77053785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383142471313</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4364,49 +4364,49 @@
     <t xml:space="preserve">3.82301211357117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69944310188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71213865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77307677268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122760772705</t>
+    <t xml:space="preserve">3.69944334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71213912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7730770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122736930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65881776809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80100703239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70198249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71467757225037</t>
+    <t xml:space="preserve">3.65881824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80100655555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70198225975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71467781066895</t>
   </si>
   <si>
     <t xml:space="preserve">3.71044588088989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66982054710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68082308769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69690418243408</t>
+    <t xml:space="preserve">3.66982078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68082332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69690442085266</t>
   </si>
   <si>
     <t xml:space="preserve">3.47177243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49123883247375</t>
+    <t xml:space="preserve">3.49123859405518</t>
   </si>
   <si>
     <t xml:space="preserve">3.6063437461853</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">3.62919569015503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53355693817139</t>
+    <t xml:space="preserve">3.53355669975281</t>
   </si>
   <si>
     <t xml:space="preserve">3.51324391365051</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">3.48700666427612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33381533622742</t>
+    <t xml:space="preserve">3.33381509780884</t>
   </si>
   <si>
     <t xml:space="preserve">3.38290429115295</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">3.40406322479248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44892024993896</t>
+    <t xml:space="preserve">3.44892048835754</t>
   </si>
   <si>
     <t xml:space="preserve">3.38713598251343</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">3.26356744766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25764274597168</t>
+    <t xml:space="preserve">3.25764298439026</t>
   </si>
   <si>
     <t xml:space="preserve">3.29657554626465</t>
@@ -4451,28 +4451,28 @@
     <t xml:space="preserve">3.24325489997864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2813413143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005258560181</t>
+    <t xml:space="preserve">3.28134107589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005282402039</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860770225525</t>
+    <t xml:space="preserve">3.46415495872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860794067383</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56741142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64358329772949</t>
+    <t xml:space="preserve">3.56741118431091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64358353614807</t>
   </si>
   <si>
     <t xml:space="preserve">3.66135716438293</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70790672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74176120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73922228813171</t>
+    <t xml:space="preserve">3.70790696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74176144599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73922252655029</t>
   </si>
   <si>
     <t xml:space="preserve">3.67659139633179</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5597939491272</t>
+    <t xml:space="preserve">3.55979371070862</t>
   </si>
   <si>
     <t xml:space="preserve">3.46838688850403</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">3.54625225067139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50224113464355</t>
+    <t xml:space="preserve">3.50224137306213</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709839820862</t>
+    <t xml:space="preserve">3.54709815979004</t>
   </si>
   <si>
     <t xml:space="preserve">3.6190390586853</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885582923889</t>
+    <t xml:space="preserve">3.49885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282888412476</t>
+    <t xml:space="preserve">3.70282864570618</t>
   </si>
   <si>
     <t xml:space="preserve">3.6791307926178</t>
@@ -4547,13 +4547,13 @@
     <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69351887702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7002899646759</t>
+    <t xml:space="preserve">3.69351863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706057548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70029020309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010649681091</t>
+    <t xml:space="preserve">3.58010625839233</t>
   </si>
   <si>
     <t xml:space="preserve">3.47515749931335</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">3.38459730148315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34735727310181</t>
+    <t xml:space="preserve">3.34735703468323</t>
   </si>
   <si>
     <t xml:space="preserve">3.3803653717041</t>
@@ -4589,19 +4589,19 @@
     <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38205814361572</t>
+    <t xml:space="preserve">3.38205790519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36766982078552</t>
+    <t xml:space="preserve">3.3676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">3.37613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3151957988739</t>
+    <t xml:space="preserve">3.31519556045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.42014408111572</t>
@@ -4613,16 +4613,16 @@
     <t xml:space="preserve">3.43114686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4531524181366</t>
+    <t xml:space="preserve">3.45315217971802</t>
   </si>
   <si>
     <t xml:space="preserve">3.50647330284119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48954582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471539497375</t>
+    <t xml:space="preserve">3.48954606056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471563339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4637,28 +4637,28 @@
     <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370210647583</t>
+    <t xml:space="preserve">3.7256805896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178828239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241337776184</t>
+    <t xml:space="preserve">3.85178852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241361618042</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366452217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06422472000122</t>
+    <t xml:space="preserve">3.97366428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06422519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.01259660720825</t>
@@ -4667,40 +4667,40 @@
     <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03037071228027</t>
+    <t xml:space="preserve">4.03037023544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.04052686691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04899024963379</t>
+    <t xml:space="preserve">4.04899072647095</t>
   </si>
   <si>
     <t xml:space="preserve">4.06845664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05576133728027</t>
+    <t xml:space="preserve">4.05576086044312</t>
   </si>
   <si>
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645109176636</t>
+    <t xml:space="preserve">4.04645156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391241073608</t>
+    <t xml:space="preserve">4.04391193389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08623075485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14209032058716</t>
+    <t xml:space="preserve">4.08623027801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14208984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
@@ -4709,64 +4709,64 @@
     <t xml:space="preserve">4.05322170257568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0083646774292</t>
+    <t xml:space="preserve">4.00836515426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.98635983467102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02359962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
+    <t xml:space="preserve">4.02360010147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990129470825</t>
   </si>
   <si>
     <t xml:space="preserve">4.01344299316406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96773958206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00667238235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95589065551758</t>
+    <t xml:space="preserve">3.96774005889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00667285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.955890417099</t>
   </si>
   <si>
     <t xml:space="preserve">3.84586381912231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86702251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88818192481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9609682559967</t>
+    <t xml:space="preserve">3.78831100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86702275276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88818144798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96096873283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.94150257110596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93219256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579916000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89325976371765</t>
+    <t xml:space="preserve">3.93219232559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272616386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579939842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865110397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85771298408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89326000213623</t>
   </si>
   <si>
     <t xml:space="preserve">3.96435451507568</t>
@@ -4775,22 +4775,22 @@
     <t xml:space="preserve">4.03544855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97958898544312</t>
+    <t xml:space="preserve">3.97958922386169</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01682901382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99482297897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974537849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9973623752594</t>
+    <t xml:space="preserve">4.0168285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99482321739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.02529239654541</t>
@@ -4802,25 +4802,25 @@
     <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05660820007324</t>
+    <t xml:space="preserve">4.05660772323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.08792304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12685585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10992860794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638690948486</t>
+    <t xml:space="preserve">4.12685537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638643264771</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19117879867554</t>
+    <t xml:space="preserve">4.1911792755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.13362646102905</t>
@@ -4829,13 +4829,13 @@
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732479095459</t>
+    <t xml:space="preserve">4.15732431411743</t>
   </si>
   <si>
     <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18271541595459</t>
+    <t xml:space="preserve">4.18271493911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4850,22 +4850,22 @@
     <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21233797073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17679071426392</t>
+    <t xml:space="preserve">4.2123384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17679119110107</t>
   </si>
   <si>
     <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863964080811</t>
+    <t xml:space="preserve">4.18864011764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17933034896851</t>
+    <t xml:space="preserve">4.17932987213135</t>
   </si>
   <si>
     <t xml:space="preserve">4.23349714279175</t>
@@ -4880,31 +4880,31 @@
     <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33506059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29443502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28427839279175</t>
+    <t xml:space="preserve">4.33506011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29443454742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28427886962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09215450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8509418964386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784230232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85263466835022</t>
+    <t xml:space="preserve">4.09215497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85094213485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8780255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8526349067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
@@ -4919,13 +4919,13 @@
     <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93811702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05491495132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06676340103149</t>
+    <t xml:space="preserve">3.93811726570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0549144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06676435470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4934,10 +4934,10 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29274272918701</t>
+    <t xml:space="preserve">4.28766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29274225234985</t>
   </si>
   <si>
     <t xml:space="preserve">4.32321119308472</t>
@@ -4949,46 +4949,46 @@
     <t xml:space="preserve">4.30289888381958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25888776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30459117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28258562088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33336734771729</t>
+    <t xml:space="preserve">4.25888824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3045916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28258609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33336782455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.31305503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23857545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32828950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938402175903</t>
+    <t xml:space="preserve">4.23857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32828903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938354492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.37907075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34013795852661</t>
+    <t xml:space="preserve">4.34013843536377</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183120727539</t>
+    <t xml:space="preserve">4.34183168411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36722135543823</t>
+    <t xml:space="preserve">4.36722183227539</t>
   </si>
   <si>
     <t xml:space="preserve">4.37269258499146</t>
@@ -6564,6 +6564,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.1049995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2749996185303</t>
   </si>
 </sst>
 </file>
@@ -71668,7 +71671,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6500925926</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>2299178</v>
@@ -71689,6 +71692,32 @@
         <v>2183</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6496412037</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>1262061</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>18.4099998474121</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>18.1650009155273</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>18.2150001525879</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>18.2749996185303</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2184</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="2187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="2188">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528889656067</t>
+    <t xml:space="preserve">2.44528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">2.40895080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35658240318298</t>
+    <t xml:space="preserve">2.35658264160156</t>
   </si>
   <si>
     <t xml:space="preserve">2.31490111351013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29780149459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37261390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3779571056366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33413887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2347457408905</t>
+    <t xml:space="preserve">2.29780173301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37261343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3341383934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23474597930908</t>
   </si>
   <si>
     <t xml:space="preserve">2.15458965301514</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">2.11183977127075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9964154958725</t>
+    <t xml:space="preserve">1.99641561508179</t>
   </si>
   <si>
     <t xml:space="preserve">2.06588363647461</t>
@@ -86,46 +86,46 @@
     <t xml:space="preserve">2.07977771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0348904132843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03168416023254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90343487262726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00923991203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93549704551697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8403787612915</t>
+    <t xml:space="preserve">2.03489065170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03168439865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02954649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343463420868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00924062728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93549680709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84037864208221</t>
   </si>
   <si>
     <t xml:space="preserve">1.74953532218933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75701665878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792963981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349870681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151118755341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6886168718338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.558229804039</t>
+    <t xml:space="preserve">1.75701653957367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792952060699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349882602692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151166439056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861711025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55823004245758</t>
   </si>
   <si>
     <t xml:space="preserve">1.60632359981537</t>
@@ -137,79 +137,79 @@
     <t xml:space="preserve">1.67899823188782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7431229352951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350441455841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69396042823792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419164657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7057169675827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296696662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533572673798</t>
+    <t xml:space="preserve">1.74312281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350417613983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69396090507507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419176578522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70571672916412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296708583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7153354883194</t>
   </si>
   <si>
     <t xml:space="preserve">1.82541620731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82327854633331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88099098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8938159942627</t>
+    <t xml:space="preserve">1.8232786655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88099122047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381563663483</t>
   </si>
   <si>
     <t xml:space="preserve">1.89488458633423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86602854728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404162406921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7655668258667</t>
+    <t xml:space="preserve">1.86602866649628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404126644135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556646823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.82648491859436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92053461074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442809581757</t>
+    <t xml:space="preserve">1.79976630210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.920534491539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442821502686</t>
   </si>
   <si>
     <t xml:space="preserve">1.93229067325592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221554279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435344219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183406352997</t>
+    <t xml:space="preserve">1.96221566200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435296535492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183430194855</t>
   </si>
   <si>
     <t xml:space="preserve">1.95580339431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95259714126587</t>
+    <t xml:space="preserve">1.95259690284729</t>
   </si>
   <si>
     <t xml:space="preserve">1.92374062538147</t>
@@ -218,55 +218,55 @@
     <t xml:space="preserve">1.87564718723297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88312828540802</t>
+    <t xml:space="preserve">1.88312840461731</t>
   </si>
   <si>
     <t xml:space="preserve">1.91198444366455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90022850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89167833328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579756736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81793510913849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8019038438797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992250919342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9012975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465336799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92587852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92801594734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9151908159256</t>
+    <t xml:space="preserve">1.90022826194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89167845249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579744815826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80190420150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992215156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129685401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587840557098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92801570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91519129276276</t>
   </si>
   <si>
     <t xml:space="preserve">2.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626487731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07443356513977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0616090297699</t>
+    <t xml:space="preserve">2.05626535415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07443380355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06160879135132</t>
   </si>
   <si>
     <t xml:space="preserve">2.07015895843506</t>
@@ -275,106 +275,106 @@
     <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05519652366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05092167854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9985533952713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214053153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95045971870422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93977224826813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8499972820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457823753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79121649265289</t>
+    <t xml:space="preserve">2.0551962852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05092144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855291843414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214029312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95045924186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93977189064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84999704360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121661186218</t>
   </si>
   <si>
     <t xml:space="preserve">1.73884785175323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388565540314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502949714661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678579807281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70785439014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235258579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700931072235</t>
+    <t xml:space="preserve">1.72388541698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69502937793732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678532123566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70785462856293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235270500183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700954914093</t>
   </si>
   <si>
     <t xml:space="preserve">1.87773132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87546908855438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279757022858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.906010389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451850414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80986166000366</t>
+    <t xml:space="preserve">1.87546920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279721260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90601003170013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451814651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081248283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80986154079437</t>
   </si>
   <si>
     <t xml:space="preserve">1.81438612937927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80646824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75104093551636</t>
+    <t xml:space="preserve">1.80646777153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75104081630707</t>
   </si>
   <si>
     <t xml:space="preserve">1.6311377286911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54290699958801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46711933612823</t>
+    <t xml:space="preserve">1.54290688037872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46711909770966</t>
   </si>
   <si>
     <t xml:space="preserve">1.47390592098236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42526590824127</t>
+    <t xml:space="preserve">1.42526602745056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51688992977142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6119077205658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60059642791748</t>
+    <t xml:space="preserve">1.61190783977509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6005961894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.57684195041656</t>
@@ -383,16 +383,16 @@
     <t xml:space="preserve">1.69900751113892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38341295719147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24201774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27255880832672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21373844146729</t>
+    <t xml:space="preserve">1.38341283798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2420175075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27255868911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.213738322258</t>
   </si>
   <si>
     <t xml:space="preserve">1.19111514091492</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">1.18545925617218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14021265506744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09949064254761</t>
+    <t xml:space="preserve">1.14021277427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09949088096619</t>
   </si>
   <si>
     <t xml:space="preserve">1.09722852706909</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">1.23749268054962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28726387023926</t>
+    <t xml:space="preserve">1.28726410865784</t>
   </si>
   <si>
     <t xml:space="preserve">1.36870777606964</t>
@@ -425,46 +425,46 @@
     <t xml:space="preserve">1.33477294445038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39359319210052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38454389572144</t>
+    <t xml:space="preserve">1.3935934305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38454401493073</t>
   </si>
   <si>
     <t xml:space="preserve">1.4003803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36983907222748</t>
+    <t xml:space="preserve">1.36983895301819</t>
   </si>
   <si>
     <t xml:space="preserve">1.398118019104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3788880109787</t>
+    <t xml:space="preserve">1.37888824939728</t>
   </si>
   <si>
     <t xml:space="preserve">1.37097012996674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37775719165802</t>
+    <t xml:space="preserve">1.37775731086731</t>
   </si>
   <si>
     <t xml:space="preserve">1.42979073524475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4026426076889</t>
+    <t xml:space="preserve">1.40264248847961</t>
   </si>
   <si>
     <t xml:space="preserve">1.38567531108856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26011610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29631328582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32233011722565</t>
+    <t xml:space="preserve">1.2601158618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29631340503693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32233023643494</t>
   </si>
   <si>
     <t xml:space="preserve">1.37549471855164</t>
@@ -473,37 +473,37 @@
     <t xml:space="preserve">1.43657767772675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45354473590851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44788932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4705126285553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45015132427216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41961014270782</t>
+    <t xml:space="preserve">1.4535448551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44788944721222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47051239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45015156269073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41961002349854</t>
   </si>
   <si>
     <t xml:space="preserve">1.38001942634583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39698696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33137953281403</t>
+    <t xml:space="preserve">1.39698708057404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33137941360474</t>
   </si>
   <si>
     <t xml:space="preserve">1.33251059055328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38228189945221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36757671833038</t>
+    <t xml:space="preserve">1.38228178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36757659912109</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816635608673</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">1.3279857635498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41056084632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40377402305603</t>
+    <t xml:space="preserve">1.41056072711945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40377378463745</t>
   </si>
   <si>
     <t xml:space="preserve">1.42413485050201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43884003162384</t>
+    <t xml:space="preserve">1.43883991241455</t>
   </si>
   <si>
     <t xml:space="preserve">1.45920085906982</t>
@@ -533,43 +533,43 @@
     <t xml:space="preserve">1.477299451828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48748004436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48974239826202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019978046417</t>
+    <t xml:space="preserve">1.48747992515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48974215984344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39020001888275</t>
   </si>
   <si>
     <t xml:space="preserve">1.40716731548309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3607896566391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282296180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513365268707</t>
+    <t xml:space="preserve">1.36078953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513377189636</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947800636292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34269082546234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821469306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780540943146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28613293170929</t>
+    <t xml:space="preserve">1.34269106388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536258220673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821457386017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28613269329071</t>
   </si>
   <si>
     <t xml:space="preserve">1.28500175476074</t>
@@ -578,244 +578,244 @@
     <t xml:space="preserve">1.27934598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35174036026001</t>
+    <t xml:space="preserve">1.35174024105072</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37210142612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39472448825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41621649265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44110214710236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49313580989838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52480816841125</t>
+    <t xml:space="preserve">1.37210130691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39472472667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41621673107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44110226631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49313592910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52480852603912</t>
   </si>
   <si>
     <t xml:space="preserve">1.53159534931183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51575911045074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54856252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56553018093109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61077654361725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63453137874603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59833407402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571065425873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50444746017456</t>
+    <t xml:space="preserve">1.51575887203217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54856264591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5655300617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61077678203583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63453114032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5983339548111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571041584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118594646454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50444734096527</t>
   </si>
   <si>
     <t xml:space="preserve">1.51802134513855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4750372171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6571546792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69335186481476</t>
+    <t xml:space="preserve">1.47503709793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65715444087982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69335162639618</t>
   </si>
   <si>
     <t xml:space="preserve">1.66733491420746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66167914867401</t>
+    <t xml:space="preserve">1.6616792678833</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905608654022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172736644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57457971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661325931549</t>
+    <t xml:space="preserve">1.60172748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57457947731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6266131401062</t>
   </si>
   <si>
     <t xml:space="preserve">1.58476006984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5610054731369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064476490021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6492360830307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66620397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62435054779053</t>
+    <t xml:space="preserve">1.56100559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064452648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512089729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64923632144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66620373725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6243509054184</t>
   </si>
   <si>
     <t xml:space="preserve">1.72049963474274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79741883277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284578800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492766857147</t>
+    <t xml:space="preserve">1.79741847515106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284566879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492754936218</t>
   </si>
   <si>
     <t xml:space="preserve">1.83022248744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86302614212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623919963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91053521633148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89922332763672</t>
+    <t xml:space="preserve">1.86302638053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91053485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89922320842743</t>
   </si>
   <si>
     <t xml:space="preserve">1.91166615486145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92637145519257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94560134410858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94447016716003</t>
+    <t xml:space="preserve">1.92637133598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94560110569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446992874146</t>
   </si>
   <si>
     <t xml:space="preserve">1.8969612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655204772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98066735267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0134711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781512260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01573324203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01912689208984</t>
+    <t xml:space="preserve">1.93655180931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066687583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01347088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01573300361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01912665367126</t>
   </si>
   <si>
     <t xml:space="preserve">1.96483087539673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99876582622528</t>
+    <t xml:space="preserve">1.99876546859741</t>
   </si>
   <si>
     <t xml:space="preserve">2.0202579498291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727394104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007771492004</t>
+    <t xml:space="preserve">1.97727358341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007723808289</t>
   </si>
   <si>
     <t xml:space="preserve">1.97161781787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94786357879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953617572784</t>
+    <t xml:space="preserve">1.9478634595871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953593730927</t>
   </si>
   <si>
     <t xml:space="preserve">2.0225203037262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99084770679474</t>
+    <t xml:space="preserve">1.99084782600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.08247208595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08699655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05079960823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542051315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96709311008453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940415859222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89130544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320673465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8799934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510766506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596229076385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03609395027161</t>
+    <t xml:space="preserve">2.08699631690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193018913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542075157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202722072601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96709322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894594192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940380096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89130556583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87320685386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999379634857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510814189911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96596240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03609418869019</t>
   </si>
   <si>
     <t xml:space="preserve">1.99424111843109</t>
@@ -824,25 +824,25 @@
     <t xml:space="preserve">2.00215935707092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0032901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01799535751343</t>
+    <t xml:space="preserve">2.00329065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478241920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01799559593201</t>
   </si>
   <si>
     <t xml:space="preserve">2.00442147254944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9546502828598</t>
+    <t xml:space="preserve">1.95465052127838</t>
   </si>
   <si>
     <t xml:space="preserve">2.02930736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02817630767822</t>
+    <t xml:space="preserve">2.02817606925964</t>
   </si>
   <si>
     <t xml:space="preserve">2.09265232086182</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">2.13224315643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432479858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12093138694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15939140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016151428223</t>
+    <t xml:space="preserve">2.12432503700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12093162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15939116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373563766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016103744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.1084885597229</t>
@@ -872,55 +872,55 @@
     <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14921069145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19332599639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17862105369568</t>
+    <t xml:space="preserve">2.14921045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19332575798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17862129211426</t>
   </si>
   <si>
     <t xml:space="preserve">2.23291683197021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19558835029602</t>
+    <t xml:space="preserve">2.19558811187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.20803117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20576858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18314528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16617822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20350646972656</t>
+    <t xml:space="preserve">2.20576882362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18314552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16617798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20350623130798</t>
   </si>
   <si>
     <t xml:space="preserve">2.19219446182251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15825963020325</t>
+    <t xml:space="preserve">2.15825986862183</t>
   </si>
   <si>
     <t xml:space="preserve">2.20011305809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17522716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17748951911926</t>
+    <t xml:space="preserve">2.17522740364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17748975753784</t>
   </si>
   <si>
     <t xml:space="preserve">2.15599751472473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14129257202148</t>
+    <t xml:space="preserve">2.14129233360291</t>
   </si>
   <si>
     <t xml:space="preserve">2.09378337860107</t>
@@ -929,55 +929,55 @@
     <t xml:space="preserve">2.07907843589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08812737464905</t>
+    <t xml:space="preserve">2.08812785148621</t>
   </si>
   <si>
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10961961746216</t>
+    <t xml:space="preserve">2.10961985588074</t>
   </si>
   <si>
     <t xml:space="preserve">2.22273635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26232671737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26006484031677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2578022480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31436061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33132791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34716439247131</t>
+    <t xml:space="preserve">2.26232695579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26006460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25780248641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31436038017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33132839202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34716415405273</t>
   </si>
   <si>
     <t xml:space="preserve">2.40032887458801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41164064407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43878817558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127993583679</t>
+    <t xml:space="preserve">2.41164040565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43878793716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44557499885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127969741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.32567191123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38675475120544</t>
+    <t xml:space="preserve">2.38675498962402</t>
   </si>
   <si>
     <t xml:space="preserve">2.3630006313324</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">2.33585262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25893330574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24988412857056</t>
+    <t xml:space="preserve">2.25893354415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24988436698914</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137589454651</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">2.33769392967224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.302166223526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36137843132019</t>
+    <t xml:space="preserve">2.30216646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36137866973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.35072040557861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30808806419373</t>
+    <t xml:space="preserve">2.30808782577515</t>
   </si>
   <si>
     <t xml:space="preserve">2.21453261375427</t>
@@ -1019,40 +1019,40 @@
     <t xml:space="preserve">2.19558477401733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18137383460999</t>
+    <t xml:space="preserve">2.21098017692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18137359619141</t>
   </si>
   <si>
     <t xml:space="preserve">2.1458466053009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13637256622314</t>
+    <t xml:space="preserve">2.13637280464172</t>
   </si>
   <si>
     <t xml:space="preserve">2.10913515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110970497131</t>
+    <t xml:space="preserve">2.14110946655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.14229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16360998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18611121177673</t>
+    <t xml:space="preserve">2.16361021995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18611097335815</t>
   </si>
   <si>
     <t xml:space="preserve">2.13874101638794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.119793176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14939951896667</t>
+    <t xml:space="preserve">2.11979293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14939904212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.13755679130554</t>
@@ -1061,34 +1061,34 @@
     <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15532088279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2003219127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374228477478</t>
+    <t xml:space="preserve">2.15532040596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20032167434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1837420463562</t>
   </si>
   <si>
     <t xml:space="preserve">2.2382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27374458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453744888306</t>
+    <t xml:space="preserve">2.27374482154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453768730164</t>
   </si>
   <si>
     <t xml:space="preserve">2.3838791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3483521938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36848449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37322092056274</t>
+    <t xml:space="preserve">2.34835195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36848425865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37322115898132</t>
   </si>
   <si>
     <t xml:space="preserve">2.36966824531555</t>
@@ -1100,40 +1100,40 @@
     <t xml:space="preserve">2.38032650947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38861608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34361505508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30927228927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28913974761963</t>
+    <t xml:space="preserve">2.38861632347107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34361481666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30927205085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28913950920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.29387712478638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33058834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34953594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36019420623779</t>
+    <t xml:space="preserve">2.33058857917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34953618049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36019444465637</t>
   </si>
   <si>
     <t xml:space="preserve">2.31637740135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34479904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31756186485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34006214141846</t>
+    <t xml:space="preserve">2.34479928016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31756162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34006237983704</t>
   </si>
   <si>
     <t xml:space="preserve">2.40401124954224</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">2.4099326133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37914228439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35545778274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045603752136</t>
+    <t xml:space="preserve">2.37914252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3554573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045627593994</t>
   </si>
   <si>
     <t xml:space="preserve">2.25953388214111</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">2.27966594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25598120689392</t>
+    <t xml:space="preserve">2.25598096847534</t>
   </si>
   <si>
     <t xml:space="preserve">2.23111200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22163796424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19676876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19321632385254</t>
+    <t xml:space="preserve">2.22163820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19676899909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19321608543396</t>
   </si>
   <si>
     <t xml:space="preserve">2.18847942352295</t>
@@ -1178,40 +1178,40 @@
     <t xml:space="preserve">2.18492650985718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13163566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058350563049</t>
+    <t xml:space="preserve">2.13163542747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005730628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058326721191</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834688186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13045144081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12097764015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11031937599182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08426594734192</t>
+    <t xml:space="preserve">2.13045167922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1209774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11031913757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842661857605</t>
   </si>
   <si>
     <t xml:space="preserve">2.22400665283203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24295473098755</t>
+    <t xml:space="preserve">2.24295449256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.29624533653259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28795576095581</t>
+    <t xml:space="preserve">2.28795552253723</t>
   </si>
   <si>
     <t xml:space="preserve">2.25005984306335</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">2.25834965705872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24413871765137</t>
+    <t xml:space="preserve">2.24413847923279</t>
   </si>
   <si>
     <t xml:space="preserve">2.22755932807922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22637486457825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2370331287384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24769139289856</t>
+    <t xml:space="preserve">2.22637510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23703336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24769115447998</t>
   </si>
   <si>
     <t xml:space="preserve">2.2926926612854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32111406326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25716543197632</t>
+    <t xml:space="preserve">2.3211145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2571656703949</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137613296509</t>
@@ -1250,61 +1250,61 @@
     <t xml:space="preserve">2.30453515052795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29742980003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25124406814575</t>
+    <t xml:space="preserve">2.29742956161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25124454498291</t>
   </si>
   <si>
     <t xml:space="preserve">2.31874585151672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27848172187805</t>
+    <t xml:space="preserve">2.27848196029663</t>
   </si>
   <si>
     <t xml:space="preserve">2.26663947105408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28321886062622</t>
+    <t xml:space="preserve">2.28321862220764</t>
   </si>
   <si>
     <t xml:space="preserve">2.32703590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34598326683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30571889877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27729725837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14821529388428</t>
+    <t xml:space="preserve">2.34598350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30571937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27729749679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742726325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203209877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1482150554657</t>
   </si>
   <si>
     <t xml:space="preserve">2.19795322418213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979571342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19913744926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23348045349121</t>
+    <t xml:space="preserve">2.20979595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19913768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23348069190979</t>
   </si>
   <si>
     <t xml:space="preserve">2.23584890365601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28084993362427</t>
+    <t xml:space="preserve">2.28085017204285</t>
   </si>
   <si>
     <t xml:space="preserve">2.26900792121887</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">2.27256059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24177026748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361275672913</t>
+    <t xml:space="preserve">2.24177002906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361251831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.27019190788269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26308679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677153587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032397270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30098247528076</t>
+    <t xml:space="preserve">2.26308655738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30098223686218</t>
   </si>
   <si>
     <t xml:space="preserve">2.33177280426025</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31519317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41585397720337</t>
+    <t xml:space="preserve">2.31519293785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39098477363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41585373878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.41940641403198</t>
@@ -1355,49 +1355,49 @@
     <t xml:space="preserve">2.4371702671051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48098707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53309369087219</t>
+    <t xml:space="preserve">2.48098731040955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53309345245361</t>
   </si>
   <si>
     <t xml:space="preserve">2.5674364566803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54612064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56151604652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57572650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56862115859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57691049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56980490684509</t>
+    <t xml:space="preserve">2.54612040519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56151556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57572627067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56862092018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57691073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56980538368225</t>
   </si>
   <si>
     <t xml:space="preserve">2.56625247001648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6396758556366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65743899345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66691303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63671493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62960934638977</t>
+    <t xml:space="preserve">2.63967561721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65743923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66691327095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63671517372131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62960958480835</t>
   </si>
   <si>
     <t xml:space="preserve">2.58105564117432</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">2.56921315193176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48039531707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53013277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45611810684204</t>
+    <t xml:space="preserve">2.48039484024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53013300895691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45611786842346</t>
   </si>
   <si>
     <t xml:space="preserve">2.48217129707336</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.44605207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40697193145752</t>
+    <t xml:space="preserve">2.4069721698761</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236733436584</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">2.4709210395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45552587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723629951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46559190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.473881483078</t>
+    <t xml:space="preserve">2.45552563667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723582267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4655921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47388172149658</t>
   </si>
   <si>
     <t xml:space="preserve">2.41881442070007</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">2.43480157852173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40756416320801</t>
+    <t xml:space="preserve">2.40756392478943</t>
   </si>
   <si>
     <t xml:space="preserve">2.3264434337616</t>
@@ -1463,76 +1463,76 @@
     <t xml:space="preserve">2.33473324775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35190486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39631390571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37440514564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35782623291016</t>
+    <t xml:space="preserve">2.35190463066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39631366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3744056224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35782599449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611533164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3862476348877</t>
+    <t xml:space="preserve">2.36611580848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38624787330627</t>
   </si>
   <si>
     <t xml:space="preserve">2.39986634254456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32881212234497</t>
+    <t xml:space="preserve">2.32881188392639</t>
   </si>
   <si>
     <t xml:space="preserve">2.3524968624115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302306175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36374735832214</t>
+    <t xml:space="preserve">2.34302282333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499737739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
     <t xml:space="preserve">2.39809012413025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38565540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41230082511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41822218894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45078897476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51769876480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51355338096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54316020011902</t>
+    <t xml:space="preserve">2.38565564155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41230130195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41822242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45078873634338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51769852638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51355361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315972328186</t>
   </si>
   <si>
     <t xml:space="preserve">2.54079151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54375195503235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756899833679</t>
+    <t xml:space="preserve">2.54375171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756875991821</t>
   </si>
   <si>
     <t xml:space="preserve">2.61066150665283</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">2.59408235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61480617523193</t>
+    <t xml:space="preserve">2.61480665206909</t>
   </si>
   <si>
     <t xml:space="preserve">2.63493847846985</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">2.64204382896423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67164993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67520308494568</t>
+    <t xml:space="preserve">2.67165017127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6752028465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.58638453483582</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.60177969932556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55855488777161</t>
+    <t xml:space="preserve">2.55855512619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.57039737701416</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">2.59349012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59526658058167</t>
+    <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
     <t xml:space="preserve">2.51059317588806</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">2.48868465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49672651290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48620986938477</t>
+    <t xml:space="preserve">2.49672627449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48621010780334</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4088830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.387850522995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37733387947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25917887687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176114082336</t>
+    <t xml:space="preserve">2.40888333320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38785076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773341178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25917863845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176090240479</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361108779907</t>
@@ -1619,25 +1619,25 @@
     <t xml:space="preserve">2.33464980125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28577899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23752760887146</t>
+    <t xml:space="preserve">2.28577923774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2375271320343</t>
   </si>
   <si>
     <t xml:space="preserve">2.22577357292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23567152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24989986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23195958137512</t>
+    <t xml:space="preserve">2.23567128181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24989938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319598197937</t>
   </si>
   <si>
     <t xml:space="preserve">2.23938274383545</t>
@@ -1646,46 +1646,46 @@
     <t xml:space="preserve">2.24371361732483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20041036605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20968961715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22329950332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20721483230591</t>
+    <t xml:space="preserve">2.20041012763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20968985557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22329902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20721530914307</t>
   </si>
   <si>
     <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19298720359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05812931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0587477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02843594551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04699397087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04946875572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09215307235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11689782142639</t>
+    <t xml:space="preserve">2.19298696517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05812907218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05874800682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379891395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02843570709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04699444770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04946851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0921528339386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11689734458923</t>
   </si>
   <si>
     <t xml:space="preserve">2.10143208503723</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">2.09091591835022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10638117790222</t>
+    <t xml:space="preserve">2.10638093948364</t>
   </si>
   <si>
     <t xml:space="preserve">2.12679529190063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14349794387817</t>
+    <t xml:space="preserve">2.14349770545959</t>
   </si>
   <si>
     <t xml:space="preserve">2.13793039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12122774124146</t>
+    <t xml:space="preserve">2.12122750282288</t>
   </si>
   <si>
     <t xml:space="preserve">2.09957647323608</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18061494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1651496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2010293006897</t>
+    <t xml:space="preserve">2.14473485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18061470985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16514945030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20102882385254</t>
   </si>
   <si>
     <t xml:space="preserve">2.09029698371887</t>
@@ -1748,40 +1748,40 @@
     <t xml:space="preserve">2.10699963569641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13916754722595</t>
+    <t xml:space="preserve">2.13916778564453</t>
   </si>
   <si>
     <t xml:space="preserve">2.1199905872345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07730650901794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07235717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11937212944031</t>
+    <t xml:space="preserve">2.07730627059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0723569393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11937189102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.20474076271057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28392362594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23319697380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19175004959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24309492111206</t>
+    <t xml:space="preserve">2.28392338752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23319721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19174981117249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">2.26289033889771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2529923915863</t>
+    <t xml:space="preserve">2.25299263000488</t>
   </si>
   <si>
     <t xml:space="preserve">2.26969504356384</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">2.27711844444275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25608587265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24185752868652</t>
+    <t xml:space="preserve">2.25608563423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24185729026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.19917321205139</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3142352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3699107170105</t>
+    <t xml:space="preserve">2.31423544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36991095542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.33712410926819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33836126327515</t>
+    <t xml:space="preserve">2.33836150169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.33403086662292</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">2.3600127696991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40145993232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4163064956665</t>
+    <t xml:space="preserve">2.40146017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41630673408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.41445112228394</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">2.44352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47012615203857</t>
+    <t xml:space="preserve">2.47012591362</t>
   </si>
   <si>
     <t xml:space="preserve">2.48682880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50600600242615</t>
+    <t xml:space="preserve">2.50600576400757</t>
   </si>
   <si>
     <t xml:space="preserve">2.37300372123718</t>
@@ -1865,22 +1865,22 @@
     <t xml:space="preserve">2.30743074417114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37795281410217</t>
+    <t xml:space="preserve">2.37795305252075</t>
   </si>
   <si>
     <t xml:space="preserve">2.36496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27093243598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2808301448822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19793605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1985547542572</t>
+    <t xml:space="preserve">2.2709321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28083038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19793581962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19855451583862</t>
   </si>
   <si>
     <t xml:space="preserve">2.20907115936279</t>
@@ -1889,19 +1889,19 @@
     <t xml:space="preserve">2.18308925628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17504739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.199791431427</t>
+    <t xml:space="preserve">2.17504715919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19979166984558</t>
   </si>
   <si>
     <t xml:space="preserve">2.16824269294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15648865699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09772062301636</t>
+    <t xml:space="preserve">2.15648889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09772038459778</t>
   </si>
   <si>
     <t xml:space="preserve">2.13978624343872</t>
@@ -1913,34 +1913,34 @@
     <t xml:space="preserve">2.19669890403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17381024360657</t>
+    <t xml:space="preserve">2.17380976676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.21525716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24247622489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2443323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24742531776428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25979733467102</t>
+    <t xml:space="preserve">2.24247598648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24433159828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24742484092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2597975730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.33217549324036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34949660301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26598358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26227188110352</t>
+    <t xml:space="preserve">2.34949636459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26598334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26227164268494</t>
   </si>
   <si>
     <t xml:space="preserve">2.28825330734253</t>
@@ -1949,40 +1949,40 @@
     <t xml:space="preserve">2.22701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20412230491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15834450721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1373119354248</t>
+    <t xml:space="preserve">2.2041220664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15834474563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13731169700623</t>
   </si>
   <si>
     <t xml:space="preserve">2.23443412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22639203071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28949069976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24680638313293</t>
+    <t xml:space="preserve">2.22639226913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28949093818665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24680614471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.23381543159485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15277719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16947984695435</t>
+    <t xml:space="preserve">2.15277695655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
     <t xml:space="preserve">2.15401434898376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18556356430054</t>
+    <t xml:space="preserve">2.18556380271912</t>
   </si>
   <si>
     <t xml:space="preserve">2.21278238296509</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">2.19607996940613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504149436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13607478141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17628455162048</t>
+    <t xml:space="preserve">2.11504197120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13607454299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1762843132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.14040493965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27959299087524</t>
+    <t xml:space="preserve">2.27959322929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.32413339614868</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">2.35073351860046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38846898078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41012072563171</t>
+    <t xml:space="preserve">2.38846921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41012024879456</t>
   </si>
   <si>
     <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32227730751038</t>
+    <t xml:space="preserve">2.32227754592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">2.41259527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43424677848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44971179962158</t>
+    <t xml:space="preserve">2.43424654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44971203804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342373847961</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">2.47321915626526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136354446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50043797492981</t>
+    <t xml:space="preserve">2.47136330604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50043821334839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5152850151062</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">2.4620840549469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32908248901367</t>
+    <t xml:space="preserve">2.32908225059509</t>
   </si>
   <si>
     <t xml:space="preserve">2.36125016212463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42620444297791</t>
+    <t xml:space="preserve">2.42620468139648</t>
   </si>
   <si>
     <t xml:space="preserve">2.4410514831543</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">2.37609696388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45713543891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45094895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47507500648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46579575538635</t>
+    <t xml:space="preserve">2.45713520050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45094919204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47507524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46579599380493</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49054050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48188018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47878670692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49548935890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50662446022034</t>
+    <t xml:space="preserve">2.49054074287415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48187971115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47878694534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49548959732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50662422180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.52889442443848</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">2.53446221351624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50786161422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55302047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601142883301</t>
+    <t xml:space="preserve">2.50786137580872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55302023887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601119041443</t>
   </si>
   <si>
     <t xml:space="preserve">2.58147668838501</t>
@@ -2141,40 +2141,40 @@
     <t xml:space="preserve">2.69901299476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69220852851868</t>
+    <t xml:space="preserve">2.69220900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.68231058120728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66870141029358</t>
+    <t xml:space="preserve">2.66870164871216</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179417610168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69282722473145</t>
+    <t xml:space="preserve">2.69282698631287</t>
   </si>
   <si>
     <t xml:space="preserve">2.71014857292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74664688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76396799087524</t>
+    <t xml:space="preserve">2.74664640426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76396775245667</t>
   </si>
   <si>
     <t xml:space="preserve">2.72994422912598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83696413040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8344898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86109042167664</t>
+    <t xml:space="preserve">2.83696436882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83449006080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86109066009521</t>
   </si>
   <si>
     <t xml:space="preserve">2.85057377815247</t>
@@ -2186,40 +2186,40 @@
     <t xml:space="preserve">2.75716304779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76025605201721</t>
+    <t xml:space="preserve">2.76025629043579</t>
   </si>
   <si>
     <t xml:space="preserve">2.78500080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78995037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82088017463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83943867683411</t>
+    <t xml:space="preserve">2.78994989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.820880651474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83943915367126</t>
   </si>
   <si>
     <t xml:space="preserve">2.83882069587708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79737281799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81160140037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78685665130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80603337287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81778693199158</t>
+    <t xml:space="preserve">2.79737305641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81160116195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78685712814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80603361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81778740882874</t>
   </si>
   <si>
     <t xml:space="preserve">2.79551720619202</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">2.74417233467102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65694808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59137487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6909716129303</t>
+    <t xml:space="preserve">2.65694785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59137439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69097137451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.66560840606689</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">2.73056292533875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79984736442566</t>
+    <t xml:space="preserve">2.79984760284424</t>
   </si>
   <si>
     <t xml:space="preserve">2.76334953308105</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">2.79106640815735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68084216117859</t>
+    <t xml:space="preserve">2.68084192276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.79235577583313</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">2.72596335411072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6814866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62862992286682</t>
+    <t xml:space="preserve">2.68148636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6286301612854</t>
   </si>
   <si>
     <t xml:space="preserve">2.65892577171326</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">2.66279339790344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63443160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68664312362671</t>
+    <t xml:space="preserve">2.6344313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68664336204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.66666126251221</t>
@@ -2294,61 +2294,61 @@
     <t xml:space="preserve">2.65183520317078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472721099854</t>
+    <t xml:space="preserve">2.66472697257996</t>
   </si>
   <si>
     <t xml:space="preserve">2.6885769367218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6943781375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68986630439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72016167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69695687294006</t>
+    <t xml:space="preserve">2.69437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72016143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69695663452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.65247988700867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69953489303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75303554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73563194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73176407814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76205992698669</t>
+    <t xml:space="preserve">2.69953513145447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7530357837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73563170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73176431655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76206016540527</t>
   </si>
   <si>
     <t xml:space="preserve">2.75883722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79428958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76077079772949</t>
+    <t xml:space="preserve">2.79428935050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76077103614807</t>
   </si>
   <si>
     <t xml:space="preserve">2.79944610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82007336616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86197137832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91160464286804</t>
+    <t xml:space="preserve">2.820072889328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86197113990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91160440444946</t>
   </si>
   <si>
     <t xml:space="preserve">2.90773701667786</t>
@@ -2357,28 +2357,28 @@
     <t xml:space="preserve">2.8916220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89484524726868</t>
+    <t xml:space="preserve">2.89484548568726</t>
   </si>
   <si>
     <t xml:space="preserve">2.95414757728577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97477412223816</t>
+    <t xml:space="preserve">2.97477436065674</t>
   </si>
   <si>
     <t xml:space="preserve">2.96832823753357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97541904449463</t>
+    <t xml:space="preserve">2.97541880607605</t>
   </si>
   <si>
     <t xml:space="preserve">2.98702096939087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96897268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735261917114</t>
+    <t xml:space="preserve">2.9689724445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735238075256</t>
   </si>
   <si>
     <t xml:space="preserve">2.91805028915405</t>
@@ -2387,34 +2387,34 @@
     <t xml:space="preserve">3.04181122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02118396759033</t>
+    <t xml:space="preserve">3.02118420600891</t>
   </si>
   <si>
     <t xml:space="preserve">3.03665447235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03923320770264</t>
+    <t xml:space="preserve">3.03923296928406</t>
   </si>
   <si>
     <t xml:space="preserve">3.04825735092163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00829243659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155141830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9889554977417</t>
+    <t xml:space="preserve">3.00829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155117988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98895525932312</t>
   </si>
   <si>
     <t xml:space="preserve">2.90902614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86003732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84263348579407</t>
+    <t xml:space="preserve">2.86003756523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84263372421265</t>
   </si>
   <si>
     <t xml:space="preserve">2.78655433654785</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">2.76592755317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83812117576599</t>
+    <t xml:space="preserve">2.83812141418457</t>
   </si>
   <si>
     <t xml:space="preserve">2.73434281349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78010869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84843492507935</t>
+    <t xml:space="preserve">2.78010892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84843468666077</t>
   </si>
   <si>
     <t xml:space="preserve">2.87421846389771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95608067512512</t>
+    <t xml:space="preserve">2.9560809135437</t>
   </si>
   <si>
     <t xml:space="preserve">2.9477014541626</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">2.91869497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91676139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94705724716187</t>
+    <t xml:space="preserve">2.91676115989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94705677032471</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031503677368</t>
@@ -2459,25 +2459,25 @@
     <t xml:space="preserve">2.96510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94576740264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94125580787659</t>
+    <t xml:space="preserve">2.94576787948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94125556945801</t>
   </si>
   <si>
     <t xml:space="preserve">2.94383382797241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97606325149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95479226112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95801496505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98959994316101</t>
+    <t xml:space="preserve">2.97606372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95479202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95801472663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98959970474243</t>
   </si>
   <si>
     <t xml:space="preserve">3.05921530723572</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">3.11013746261597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10884833335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08048629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11464929580688</t>
+    <t xml:space="preserve">3.10884857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.080486536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11464977264404</t>
   </si>
   <si>
     <t xml:space="preserve">3.10240268707275</t>
@@ -2507,34 +2507,34 @@
     <t xml:space="preserve">3.10175800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12431836128235</t>
+    <t xml:space="preserve">3.12431883811951</t>
   </si>
   <si>
     <t xml:space="preserve">3.14945769309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592076301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05663704872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698588371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275128364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696822166443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08757758140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12560749053955</t>
+    <t xml:space="preserve">3.13592123985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661843299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05663681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08757710456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12560820579529</t>
   </si>
   <si>
     <t xml:space="preserve">3.19071102142334</t>
@@ -2543,28 +2543,28 @@
     <t xml:space="preserve">3.15396952629089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15010237693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17781949043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20553660392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22680807113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22165155410767</t>
+    <t xml:space="preserve">3.15010190010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17781901359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20553684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22680854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22165131568909</t>
   </si>
   <si>
     <t xml:space="preserve">3.21262741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23325395584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001311302185</t>
+    <t xml:space="preserve">3.23325371742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001358985901</t>
   </si>
   <si>
     <t xml:space="preserve">3.21391630172729</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">3.26548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24743437767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229599952698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739905357361</t>
+    <t xml:space="preserve">3.24743509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2222957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388097763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739976882935</t>
   </si>
   <si>
     <t xml:space="preserve">3.31447243690491</t>
@@ -2594,124 +2594,124 @@
     <t xml:space="preserve">3.35185790061951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39955830574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41115999221802</t>
+    <t xml:space="preserve">3.39955806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4111602306366</t>
   </si>
   <si>
     <t xml:space="preserve">3.43307638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49108934402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43823313713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45370292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600299835205</t>
+    <t xml:space="preserve">3.49108958244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823289871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45370316505432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">3.41631722450256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41502785682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41373944282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44596791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920851707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3454122543335</t>
+    <t xml:space="preserve">3.41502737998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.413738489151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44596767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987133979797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920827865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34541249275208</t>
   </si>
   <si>
     <t xml:space="preserve">3.32994198799133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38924431800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38795518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3479905128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29126715660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192950248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32865333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36861729621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43049812316895</t>
+    <t xml:space="preserve">3.389244556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38795495033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34799027442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29126667976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2719292640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32865309715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43049788475037</t>
   </si>
   <si>
     <t xml:space="preserve">3.43694376945496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42405223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4781973361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45499229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22938656806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3054473400116</t>
+    <t xml:space="preserve">3.42405152320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47819805145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4549925327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37635278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35572528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22938680648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30544781684875</t>
   </si>
   <si>
     <t xml:space="preserve">3.3325207233429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31576132774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841142654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1475236415863</t>
+    <t xml:space="preserve">3.31576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14752340316772</t>
   </si>
   <si>
     <t xml:space="preserve">3.18490982055664</t>
@@ -2720,43 +2720,43 @@
     <t xml:space="preserve">3.19006657600403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16815066337585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1739513874054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205361366272</t>
+    <t xml:space="preserve">3.16815042495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17395186424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1320538520813</t>
   </si>
   <si>
     <t xml:space="preserve">3.09982442855835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12238502502441</t>
+    <t xml:space="preserve">3.12238454818726</t>
   </si>
   <si>
     <t xml:space="preserve">3.04890179634094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11593914031982</t>
+    <t xml:space="preserve">3.11593890190125</t>
   </si>
   <si>
     <t xml:space="preserve">3.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0218288898468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96703863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00958180427551</t>
+    <t xml:space="preserve">3.02182912826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96703934669495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00958204269409</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310059547424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0946671962738</t>
+    <t xml:space="preserve">3.09466743469238</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">3.15848183631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18297624588013</t>
+    <t xml:space="preserve">3.18297600746155</t>
   </si>
   <si>
     <t xml:space="preserve">3.40084719657898</t>
@@ -2780,79 +2780,79 @@
     <t xml:space="preserve">3.47561955451965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39440059661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17459654808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1423671245575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01409387588501</t>
+    <t xml:space="preserve">3.39440083503723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17459630966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14236688613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01409411430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.8858208656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272274971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017981529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610560417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51969504356384</t>
+    <t xml:space="preserve">2.7427225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610512733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51969480514526</t>
   </si>
   <si>
     <t xml:space="preserve">2.24896812438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1593701839447</t>
+    <t xml:space="preserve">2.15936994552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.17741870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646730422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88993239402771</t>
+    <t xml:space="preserve">1.79646694660187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88993263244629</t>
   </si>
   <si>
     <t xml:space="preserve">1.7661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68817615509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500655651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91313791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77261734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83965456485748</t>
+    <t xml:space="preserve">1.68817639350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6250067949295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91313743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77261757850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83965444564819</t>
   </si>
   <si>
     <t xml:space="preserve">1.93827664852142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94149947166443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04141044616699</t>
+    <t xml:space="preserve">1.94149959087372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04141068458557</t>
   </si>
   <si>
     <t xml:space="preserve">1.90669167041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923424720764</t>
+    <t xml:space="preserve">1.94923412799835</t>
   </si>
   <si>
     <t xml:space="preserve">2.02013921737671</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">2.05236840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98662030696869</t>
+    <t xml:space="preserve">1.98662042617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.11295986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12327289581299</t>
+    <t xml:space="preserve">2.12327313423157</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912779808044</t>
@@ -2879,28 +2879,28 @@
     <t xml:space="preserve">2.0910439491272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94278848171234</t>
+    <t xml:space="preserve">1.94278836250305</t>
   </si>
   <si>
     <t xml:space="preserve">1.92087244987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93892109394073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9028240442276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83063018321991</t>
+    <t xml:space="preserve">1.93892085552216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90282416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">1.8976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89379966259003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693381786346</t>
+    <t xml:space="preserve">1.89379990100861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693393707275</t>
   </si>
   <si>
     <t xml:space="preserve">2.06010365486145</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">2.05623602867126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0265851020813</t>
+    <t xml:space="preserve">2.02658486366272</t>
   </si>
   <si>
     <t xml:space="preserve">2.02529573440552</t>
@@ -2924,40 +2924,40 @@
     <t xml:space="preserve">2.05752515792847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0162718296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01756072044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98791003227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9724395275116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32651424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22702980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21850228309631</t>
+    <t xml:space="preserve">2.01627159118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0175609588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790967464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97243964672089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32651400566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22702956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
     <t xml:space="preserve">2.17018151283264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2199239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387784957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27535080909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26540231704712</t>
+    <t xml:space="preserve">2.21992373466492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387808799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27535057067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2654025554657</t>
   </si>
   <si>
     <t xml:space="preserve">2.31372356414795</t>
@@ -2966,25 +2966,25 @@
     <t xml:space="preserve">2.24266290664673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25687503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52406167984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63633704185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6164402961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56669807434082</t>
+    <t xml:space="preserve">2.25687527656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39046883583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46863484382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52406191825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61644005775452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56669783592224</t>
   </si>
   <si>
     <t xml:space="preserve">2.48995280265808</t>
@@ -3005,19 +3005,19 @@
     <t xml:space="preserve">2.44873809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47574067115784</t>
+    <t xml:space="preserve">2.47574090957642</t>
   </si>
   <si>
     <t xml:space="preserve">2.451580286026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44021058082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40325951576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41889262199402</t>
+    <t xml:space="preserve">2.44021034240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40325903892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4188928604126</t>
   </si>
   <si>
     <t xml:space="preserve">2.42457723617554</t>
@@ -3032,64 +3032,64 @@
     <t xml:space="preserve">2.43310475349426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53258895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53116822242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55817031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57238268852234</t>
+    <t xml:space="preserve">2.53258872032166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53116774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55817055702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57238292694092</t>
   </si>
   <si>
     <t xml:space="preserve">2.58090996742249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51127076148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53685259819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56527662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60933423042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64202213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63207364082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65481281280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67755198478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65907669067383</t>
+    <t xml:space="preserve">2.51127099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53685235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5652768611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60933375358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64202189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63207340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65481305122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67755222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
     <t xml:space="preserve">2.76424551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64770674705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61501932144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60649156570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54680132865906</t>
+    <t xml:space="preserve">2.64770698547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61501884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6064920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4572651386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54680109024048</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186713218689</t>
@@ -3107,40 +3107,40 @@
     <t xml:space="preserve">2.89073276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92768430709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89641809463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92199945449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86372995376587</t>
+    <t xml:space="preserve">2.92768406867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89641785621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92199921607971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86373019218445</t>
   </si>
   <si>
     <t xml:space="preserve">2.83388447761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88931179046631</t>
+    <t xml:space="preserve">2.88931155204773</t>
   </si>
   <si>
     <t xml:space="preserve">2.8495180606842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84099078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91773581504822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93479061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95895051956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94615960121155</t>
+    <t xml:space="preserve">2.84099054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9177360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93479037284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95895099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">2.94900250434875</t>
@@ -3152,16 +3152,16 @@
     <t xml:space="preserve">2.88789081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85378170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81256675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78556346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90068125724792</t>
+    <t xml:space="preserve">2.85378122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81256651878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78556394577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90068101882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.87794208526611</t>
@@ -3170,52 +3170,52 @@
     <t xml:space="preserve">2.94189643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95184445381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95753002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93621110916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91489338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85662412643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70313358306885</t>
+    <t xml:space="preserve">2.95184469223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9575297832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93621158599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91489386558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85662388801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70313382148743</t>
   </si>
   <si>
     <t xml:space="preserve">2.74861240386963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69602751731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70455503463745</t>
+    <t xml:space="preserve">2.6960277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70455479621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.65765523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72729468345642</t>
+    <t xml:space="preserve">2.72729420661926</t>
   </si>
   <si>
     <t xml:space="preserve">2.66902470588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6505491733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6491277217865</t>
+    <t xml:space="preserve">2.65054893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64912819862366</t>
   </si>
   <si>
     <t xml:space="preserve">2.610755443573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68039441108704</t>
+    <t xml:space="preserve">2.68039417266846</t>
   </si>
   <si>
     <t xml:space="preserve">2.62354612350464</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">2.61359786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56243443489075</t>
+    <t xml:space="preserve">2.56243419647217</t>
   </si>
   <si>
     <t xml:space="preserve">2.45868635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50274395942688</t>
+    <t xml:space="preserve">2.5027437210083</t>
   </si>
   <si>
     <t xml:space="preserve">2.48853158950806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49705862998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52690386772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48568892478943</t>
+    <t xml:space="preserve">2.4970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52690410614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48568916320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.42741966247559</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">2.39899563789368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37199258804321</t>
+    <t xml:space="preserve">2.37199282646179</t>
   </si>
   <si>
     <t xml:space="preserve">2.25403261184692</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">2.23129320144653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276639938354</t>
+    <t xml:space="preserve">2.22276616096497</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39473176002502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56385564804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52264046669006</t>
+    <t xml:space="preserve">2.39473223686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56385588645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52264070510864</t>
   </si>
   <si>
     <t xml:space="preserve">2.52832555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55532813072205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7145037651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76850938796997</t>
+    <t xml:space="preserve">2.55532836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71450328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76850914955139</t>
   </si>
   <si>
     <t xml:space="preserve">2.74008512496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84383320808411</t>
+    <t xml:space="preserve">2.84383296966553</t>
   </si>
   <si>
     <t xml:space="preserve">2.83672714233398</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">2.97174191474915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93052649497986</t>
+    <t xml:space="preserve">2.93052697181702</t>
   </si>
   <si>
     <t xml:space="preserve">2.90920853614807</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">2.70597624778748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7073974609375</t>
+    <t xml:space="preserve">2.70739722251892</t>
   </si>
   <si>
     <t xml:space="preserve">2.7130823135376</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">2.75998210906982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7983546257019</t>
+    <t xml:space="preserve">2.79835438728333</t>
   </si>
   <si>
     <t xml:space="preserve">2.72871541976929</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">2.75429701805115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75571870803833</t>
+    <t xml:space="preserve">2.75571823120117</t>
   </si>
   <si>
     <t xml:space="preserve">2.79266977310181</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">2.77419424057007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77845764160156</t>
+    <t xml:space="preserve">2.77845788002014</t>
   </si>
   <si>
     <t xml:space="preserve">2.75713968276978</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">2.85946655273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91347193717957</t>
+    <t xml:space="preserve">2.91347217559814</t>
   </si>
   <si>
     <t xml:space="preserve">2.88646912574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88362717628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84241199493408</t>
+    <t xml:space="preserve">2.88362693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8424117565155</t>
   </si>
   <si>
     <t xml:space="preserve">2.76993036270142</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">2.79551196098328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67897319793701</t>
+    <t xml:space="preserve">2.67897343635559</t>
   </si>
   <si>
     <t xml:space="preserve">2.68181562423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74577021598816</t>
+    <t xml:space="preserve">2.745769739151</t>
   </si>
   <si>
     <t xml:space="preserve">2.64344334602356</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">2.57522535324097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.644864320755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546069145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86657238006592</t>
+    <t xml:space="preserve">2.64486408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8665726184845</t>
   </si>
   <si>
     <t xml:space="preserve">2.94758105278015</t>
@@ -3425,37 +3425,37 @@
     <t xml:space="preserve">3.13233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1053352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18350172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14939260482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13944435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15791940689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12665343284607</t>
+    <t xml:space="preserve">3.10533452033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18350124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1493923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13944411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15791964530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12665319442749</t>
   </si>
   <si>
     <t xml:space="preserve">3.03995966911316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742629051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01153540611267</t>
+    <t xml:space="preserve">2.97742652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01153516769409</t>
   </si>
   <si>
     <t xml:space="preserve">3.03427457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08259582519531</t>
+    <t xml:space="preserve">3.08259558677673</t>
   </si>
   <si>
     <t xml:space="preserve">3.13375926017761</t>
@@ -3464,31 +3464,31 @@
     <t xml:space="preserve">3.11812591552734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0584352016449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19344997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16928935050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2119255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25171947479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479709148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30004024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28867077827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435586929321</t>
+    <t xml:space="preserve">3.05843496322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19344973564148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16928911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21192526817322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2517192363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14797067642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30004048347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28867053985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435539245605</t>
   </si>
   <si>
     <t xml:space="preserve">3.30146145820618</t>
@@ -3500,55 +3500,55 @@
     <t xml:space="preserve">3.30572509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3526246547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110042572021</t>
+    <t xml:space="preserve">3.35262489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110066413879</t>
   </si>
   <si>
     <t xml:space="preserve">3.41942143440247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36967968940735</t>
+    <t xml:space="preserve">3.36967921257019</t>
   </si>
   <si>
     <t xml:space="preserve">3.26450991630554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2758800983429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3085675239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947294235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37962770462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38247060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40378880500793</t>
+    <t xml:space="preserve">3.27587985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856776237488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947318077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37962794303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38247036933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40378856658936</t>
   </si>
   <si>
     <t xml:space="preserve">3.42013239860535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32846426963806</t>
+    <t xml:space="preserve">3.32846450805664</t>
   </si>
   <si>
     <t xml:space="preserve">3.29790830612183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33272814750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35902047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36683678627014</t>
+    <t xml:space="preserve">3.33272790908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35902070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36683702468872</t>
   </si>
   <si>
     <t xml:space="preserve">3.34978270530701</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">3.44500327110291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32206869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28014373779297</t>
+    <t xml:space="preserve">3.3220694065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28014349937439</t>
   </si>
   <si>
     <t xml:space="preserve">3.29719758033752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31567311286926</t>
+    <t xml:space="preserve">3.31567358970642</t>
   </si>
   <si>
     <t xml:space="preserve">3.33201742172241</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">3.3043041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31780529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28440690040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23679637908936</t>
+    <t xml:space="preserve">3.31780552864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28440713882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23679661750793</t>
   </si>
   <si>
     <t xml:space="preserve">3.31212019920349</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">3.27232670783997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31283140182495</t>
+    <t xml:space="preserve">3.31283116340637</t>
   </si>
   <si>
     <t xml:space="preserve">3.42226386070251</t>
@@ -3611,25 +3611,25 @@
     <t xml:space="preserve">3.48124432563782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57575440406799</t>
+    <t xml:space="preserve">3.57575464248657</t>
   </si>
   <si>
     <t xml:space="preserve">3.58143925666809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53027534484863</t>
+    <t xml:space="preserve">3.53027558326721</t>
   </si>
   <si>
     <t xml:space="preserve">3.49829840660095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52459073066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61421179771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52383780479431</t>
+    <t xml:space="preserve">3.52459049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61421132087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52383732795715</t>
   </si>
   <si>
     <t xml:space="preserve">3.38902974128723</t>
@@ -3641,31 +3641,31 @@
     <t xml:space="preserve">3.41614198684692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44927930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48919439315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4658477306366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47488498687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45831680297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844122886658</t>
+    <t xml:space="preserve">3.44927883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48919415473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46584796905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47488474845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45831656455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844146728516</t>
   </si>
   <si>
     <t xml:space="preserve">3.46132922172546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4507851600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44626688957214</t>
+    <t xml:space="preserve">3.45078492164612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44626665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.44099450111389</t>
@@ -3683,31 +3683,31 @@
     <t xml:space="preserve">3.32501459121704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24744343757629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27229619026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23765301704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21129393577576</t>
+    <t xml:space="preserve">3.24744296073914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27229642868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23765254020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21129369735718</t>
   </si>
   <si>
     <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21430635452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24970293045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279532432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062074661255</t>
+    <t xml:space="preserve">3.21430659294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24970269203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279508590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062050819397</t>
   </si>
   <si>
     <t xml:space="preserve">3.37698006629944</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29489016532898</t>
+    <t xml:space="preserve">3.2948899269104</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731877326965</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">3.30468058586121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.316730260849</t>
+    <t xml:space="preserve">3.31673002243042</t>
   </si>
   <si>
     <t xml:space="preserve">3.33329916000366</t>
@@ -3734,19 +3734,19 @@
     <t xml:space="preserve">3.32953333854675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112458229065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28208661079407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14878511428833</t>
+    <t xml:space="preserve">3.29112386703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28208684921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14878535270691</t>
   </si>
   <si>
     <t xml:space="preserve">3.19999694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32802724838257</t>
+    <t xml:space="preserve">3.32802700996399</t>
   </si>
   <si>
     <t xml:space="preserve">3.33028650283813</t>
@@ -3755,22 +3755,22 @@
     <t xml:space="preserve">3.33480501174927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3860170841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37321448326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4221670627594</t>
+    <t xml:space="preserve">3.38601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37321424484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42216682434082</t>
   </si>
   <si>
     <t xml:space="preserve">3.40710473060608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38149833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42141389846802</t>
+    <t xml:space="preserve">3.38149809837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42141366004944</t>
   </si>
   <si>
     <t xml:space="preserve">3.37170791625977</t>
@@ -3791,46 +3791,46 @@
     <t xml:space="preserve">3.60592770576477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61647081375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65337419509888</t>
+    <t xml:space="preserve">3.61647152900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6533739566803</t>
   </si>
   <si>
     <t xml:space="preserve">3.63981795310974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6307806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63831162452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72040176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6752142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66542387008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75052690505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77462577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77311992645264</t>
+    <t xml:space="preserve">3.63078045845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6383113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72040128707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67521452903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66542339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75052618980408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010750770569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7746262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77312016487122</t>
   </si>
   <si>
     <t xml:space="preserve">3.79872560501099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77613210678101</t>
+    <t xml:space="preserve">3.77613234519958</t>
   </si>
   <si>
     <t xml:space="preserve">3.7821569442749</t>
@@ -3839,28 +3839,28 @@
     <t xml:space="preserve">3.76709461212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78667593002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7369704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77763843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71663618087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71588277816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533895492554</t>
+    <t xml:space="preserve">3.78667569160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73696994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77763819694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71663570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71588253974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533919334412</t>
   </si>
   <si>
     <t xml:space="preserve">3.6375584602356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68726420402527</t>
+    <t xml:space="preserve">3.68726444244385</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994261741638</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">3.72567319869995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67144894599915</t>
+    <t xml:space="preserve">3.67144870758057</t>
   </si>
   <si>
     <t xml:space="preserve">3.58258080482483</t>
@@ -3881,55 +3881,55 @@
     <t xml:space="preserve">3.6413242816925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75429153442383</t>
+    <t xml:space="preserve">3.75429224967957</t>
   </si>
   <si>
     <t xml:space="preserve">3.75203227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80926990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450063705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625677108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84541940689087</t>
+    <t xml:space="preserve">3.80926918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7445011138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80625653266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84541869163513</t>
   </si>
   <si>
     <t xml:space="preserve">3.83939409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006258010864</t>
+    <t xml:space="preserve">3.90717458724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006281852722</t>
   </si>
   <si>
     <t xml:space="preserve">3.95386791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97947359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95989322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483041763306</t>
+    <t xml:space="preserve">3.97947430610657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989298820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483065605164</t>
   </si>
   <si>
     <t xml:space="preserve">3.89060592651367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88307476043701</t>
+    <t xml:space="preserve">3.88307523727417</t>
   </si>
   <si>
     <t xml:space="preserve">3.92976808547974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95682573318481</t>
+    <t xml:space="preserve">3.95682597160339</t>
   </si>
   <si>
     <t xml:space="preserve">3.99502515792847</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">4.01571702957153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96239709854126</t>
+    <t xml:space="preserve">3.96239686012268</t>
   </si>
   <si>
     <t xml:space="preserve">3.95125532150269</t>
@@ -3959,40 +3959,40 @@
     <t xml:space="preserve">4.00457572937012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98070049285889</t>
+    <t xml:space="preserve">3.98070096969604</t>
   </si>
   <si>
     <t xml:space="preserve">4.0189003944397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97353863716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98706769943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340159416199</t>
+    <t xml:space="preserve">3.97353839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98706746101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9480721950531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340111732483</t>
   </si>
   <si>
     <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04277515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9345428943634</t>
+    <t xml:space="preserve">4.04277467727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98865914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93454313278198</t>
   </si>
   <si>
     <t xml:space="preserve">3.97274279594421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90907669067383</t>
+    <t xml:space="preserve">3.90907645225525</t>
   </si>
   <si>
     <t xml:space="preserve">3.89952707290649</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66078019142151</t>
+    <t xml:space="preserve">3.66078042984009</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590093612671</t>
@@ -4013,16 +4013,16 @@
     <t xml:space="preserve">3.73638391494751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72524237632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70057129859924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76821613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779858589172</t>
+    <t xml:space="preserve">3.72524213790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7005717754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76821637153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8477988243103</t>
   </si>
   <si>
     <t xml:space="preserve">3.7721951007843</t>
@@ -4034,13 +4034,13 @@
     <t xml:space="preserve">3.74752473831177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72922086715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73081278800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77856183052063</t>
+    <t xml:space="preserve">3.72922110557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73081254959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77856206893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.74513721466064</t>
@@ -4049,22 +4049,22 @@
     <t xml:space="preserve">3.64565992355347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74832105636597</t>
+    <t xml:space="preserve">3.74832081794739</t>
   </si>
   <si>
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77697038650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80323219299316</t>
+    <t xml:space="preserve">3.77696990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8326780796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641579627991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80323171615601</t>
   </si>
   <si>
     <t xml:space="preserve">3.85177755355835</t>
@@ -4076,88 +4076,88 @@
     <t xml:space="preserve">3.93613457679749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86212348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87008142471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146421432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97115063667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96398854255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95443844795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99980068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91942262649536</t>
+    <t xml:space="preserve">3.86212301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87008118629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97115015983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9639880657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95443868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980044364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91942238807678</t>
   </si>
   <si>
     <t xml:space="preserve">3.76344132423401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80402851104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90748476982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603060722351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90430188179016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94409251213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00775814056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96796751022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85575652122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82710742950439</t>
+    <t xml:space="preserve">3.80402827262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90748524665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603036880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90430164337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94409275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00775861740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96796774864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85575604438782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82710719108582</t>
   </si>
   <si>
     <t xml:space="preserve">4.03004121780396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01253366470337</t>
+    <t xml:space="preserve">4.01253318786621</t>
   </si>
   <si>
     <t xml:space="preserve">4.00934982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99820947647095</t>
+    <t xml:space="preserve">3.99820923805237</t>
   </si>
   <si>
     <t xml:space="preserve">3.91623902320862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8581440448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78094935417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55414032936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69261288642883</t>
+    <t xml:space="preserve">3.85814428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78094911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55414056777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69261312484741</t>
   </si>
   <si>
     <t xml:space="preserve">3.60746002197266</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">3.34483909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06948471069336</t>
+    <t xml:space="preserve">3.06948494911194</t>
   </si>
   <si>
     <t xml:space="preserve">2.94374465942383</t>
@@ -4199,40 +4199,40 @@
     <t xml:space="preserve">3.69022607803345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68385934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70852971076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74036240577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354529380798</t>
+    <t xml:space="preserve">3.6838595867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70852994918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7403621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354553222656</t>
   </si>
   <si>
     <t xml:space="preserve">3.90111827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668892860413</t>
+    <t xml:space="preserve">3.90668964385986</t>
   </si>
   <si>
     <t xml:space="preserve">3.9202184677124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97194647789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693041801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03481674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06346654891968</t>
+    <t xml:space="preserve">3.97194671630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319246292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693017959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03481721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06346607208252</t>
   </si>
   <si>
     <t xml:space="preserve">4.02845001220703</t>
@@ -4256,94 +4256,94 @@
     <t xml:space="preserve">4.16214847564697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20193910598755</t>
+    <t xml:space="preserve">4.20193958282471</t>
   </si>
   <si>
     <t xml:space="preserve">4.21467256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716501235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1541895866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599016189575</t>
+    <t xml:space="preserve">4.1971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599063873291</t>
   </si>
   <si>
     <t xml:space="preserve">4.13668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14623117446899</t>
+    <t xml:space="preserve">4.14623165130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17488098144531</t>
+    <t xml:space="preserve">4.19398069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17488145828247</t>
   </si>
   <si>
     <t xml:space="preserve">4.12554025650024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06505727767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1637396812439</t>
+    <t xml:space="preserve">4.0650577545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16373920440674</t>
   </si>
   <si>
     <t xml:space="preserve">4.26719617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28470468521118</t>
+    <t xml:space="preserve">4.28470420837402</t>
   </si>
   <si>
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9050977230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00298404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00139188766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12431621551514</t>
+    <t xml:space="preserve">3.90509748458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00298357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00139236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12431716918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28597116470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2504243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21487712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14547538757324</t>
+    <t xml:space="preserve">4.23011112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24703931808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28597164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25042390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21487665176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14547491073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.14124393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19202518463135</t>
+    <t xml:space="preserve">4.09723329544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19202566146851</t>
   </si>
   <si>
     <t xml:space="preserve">4.20810651779175</t>
@@ -4352,13 +4352,13 @@
     <t xml:space="preserve">4.11754560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10738945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77053785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383142471313</t>
+    <t xml:space="preserve">4.10738897323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77053737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383166313171</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4367,55 +4367,55 @@
     <t xml:space="preserve">3.82301211357117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69944334030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71213912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7730770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122784614563</t>
+    <t xml:space="preserve">3.69944310188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71213865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77307677268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122760772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6588180065155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80100655555725</t>
+    <t xml:space="preserve">3.65881776809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80100703239441</t>
   </si>
   <si>
     <t xml:space="preserve">3.70198249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71044564247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66982078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68082332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69690442085266</t>
+    <t xml:space="preserve">3.71467757225037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71044588088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66982054710388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68082308769226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69690418243408</t>
   </si>
   <si>
     <t xml:space="preserve">3.47177243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4912383556366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60634350776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62919545173645</t>
+    <t xml:space="preserve">3.49123883247375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6063437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62919569015503</t>
   </si>
   <si>
     <t xml:space="preserve">3.53355693817139</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">3.51324391365051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48700642585754</t>
+    <t xml:space="preserve">3.48700666427612</t>
   </si>
   <si>
     <t xml:space="preserve">3.33381533622742</t>
@@ -4445,34 +4445,34 @@
     <t xml:space="preserve">3.26356744766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25764298439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29657530784607</t>
+    <t xml:space="preserve">3.25764274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29657554626465</t>
   </si>
   <si>
     <t xml:space="preserve">3.24325489997864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28134107589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005282402039</t>
+    <t xml:space="preserve">3.2813413143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005258560181</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415495872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860817909241</t>
+    <t xml:space="preserve">3.46415519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860770225525</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56741118431091</t>
+    <t xml:space="preserve">3.56741142272949</t>
   </si>
   <si>
     <t xml:space="preserve">3.64358329772949</t>
@@ -4481,19 +4481,19 @@
     <t xml:space="preserve">3.66135716438293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64273691177368</t>
+    <t xml:space="preserve">3.64273715019226</t>
   </si>
   <si>
     <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70790696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74176144599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73922252655029</t>
+    <t xml:space="preserve">3.70790672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74176120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73922228813171</t>
   </si>
   <si>
     <t xml:space="preserve">3.67659139633179</t>
@@ -4502,22 +4502,22 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55979347229004</t>
+    <t xml:space="preserve">3.5597939491272</t>
   </si>
   <si>
     <t xml:space="preserve">3.46838688850403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54625201225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50224137306213</t>
+    <t xml:space="preserve">3.54625225067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50224113464355</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50816559791565</t>
+    <t xml:space="preserve">3.50816583633423</t>
   </si>
   <si>
     <t xml:space="preserve">3.54117393493652</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885559082031</t>
+    <t xml:space="preserve">3.49885582923889</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4544,19 +4544,19 @@
     <t xml:space="preserve">3.70282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67913103103638</t>
+    <t xml:space="preserve">3.6791307926178</t>
   </si>
   <si>
     <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69351863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706057548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70029020309448</t>
+    <t xml:space="preserve">3.69351887702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706081390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7002899646759</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010625839233</t>
+    <t xml:space="preserve">3.58010649681091</t>
   </si>
   <si>
     <t xml:space="preserve">3.47515749931335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4404571056366</t>
+    <t xml:space="preserve">3.44045686721802</t>
   </si>
   <si>
     <t xml:space="preserve">3.38459730148315</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">3.34735727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38036513328552</t>
+    <t xml:space="preserve">3.3803653717041</t>
   </si>
   <si>
     <t xml:space="preserve">3.40829515457153</t>
@@ -4592,19 +4592,19 @@
     <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38205790519714</t>
+    <t xml:space="preserve">3.38205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3676700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37613368034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31519556045532</t>
+    <t xml:space="preserve">3.36766982078552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37613344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3151957988739</t>
   </si>
   <si>
     <t xml:space="preserve">3.42014408111572</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">3.4531524181366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50647306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48954606056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471563339233</t>
+    <t xml:space="preserve">3.50647330284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48954582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471539497375</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">3.58433842658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6317343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674778938293</t>
+    <t xml:space="preserve">3.63173413276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.72568035125732</t>
@@ -4649,28 +4649,28 @@
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241313934326</t>
+    <t xml:space="preserve">3.85178828239441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241337776184</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366428375244</t>
+    <t xml:space="preserve">3.97366452217102</t>
   </si>
   <si>
     <t xml:space="preserve">4.06422472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01259708404541</t>
+    <t xml:space="preserve">4.01259660720825</t>
   </si>
   <si>
     <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03037023544312</t>
+    <t xml:space="preserve">4.03037071228027</t>
   </si>
   <si>
     <t xml:space="preserve">4.04052686691284</t>
@@ -4688,31 +4688,31 @@
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645156860352</t>
+    <t xml:space="preserve">4.04645109176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391193389893</t>
+    <t xml:space="preserve">4.04391241073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08623027801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14208984375</t>
+    <t xml:space="preserve">4.08623075485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14209032058716</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05322217941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00836515426636</t>
+    <t xml:space="preserve">4.05322170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0083646774292</t>
   </si>
   <si>
     <t xml:space="preserve">3.98635983467102</t>
@@ -4721,13 +4721,13 @@
     <t xml:space="preserve">4.02359962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01344347000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96774005889893</t>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01344299316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96773958206177</t>
   </si>
   <si>
     <t xml:space="preserve">4.00667238235474</t>
@@ -4736,49 +4736,49 @@
     <t xml:space="preserve">3.95589065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84586429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78831100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86702275276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88818144798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96096873283386</t>
+    <t xml:space="preserve">3.84586381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78831076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86702251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88818192481995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9609682559967</t>
   </si>
   <si>
     <t xml:space="preserve">3.94150257110596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93219232559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272664070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579892158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85771298408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89326000213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96435403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03544807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97958922386169</t>
+    <t xml:space="preserve">3.93219256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579916000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8577127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89325976371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96435451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03544855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97958898544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
@@ -4787,13 +4787,13 @@
     <t xml:space="preserve">4.01682901382446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99482321739197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99736213684082</t>
+    <t xml:space="preserve">3.99482297897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974537849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9973623752594</t>
   </si>
   <si>
     <t xml:space="preserve">4.02529239654541</t>
@@ -4802,22 +4802,22 @@
     <t xml:space="preserve">4.04306602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04475784301758</t>
+    <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
     <t xml:space="preserve">4.05660820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0879225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638643264771</t>
+    <t xml:space="preserve">4.08792304992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10992860794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
@@ -4826,19 +4826,19 @@
     <t xml:space="preserve">4.19117879867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13362598419189</t>
+    <t xml:space="preserve">4.13362646102905</t>
   </si>
   <si>
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732431411743</t>
+    <t xml:space="preserve">4.15732479095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18271493911743</t>
+    <t xml:space="preserve">4.18271541595459</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2123384475708</t>
+    <t xml:space="preserve">4.21233797073364</t>
   </si>
   <si>
     <t xml:space="preserve">4.17679071426392</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18864011764526</t>
+    <t xml:space="preserve">4.18863964080811</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
@@ -4871,10 +4871,10 @@
     <t xml:space="preserve">4.17933034896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23349666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24026775360107</t>
+    <t xml:space="preserve">4.23349714279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24026823043823</t>
   </si>
   <si>
     <t xml:space="preserve">4.27073669433594</t>
@@ -4883,13 +4883,13 @@
     <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33506011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29443454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28427886962891</t>
+    <t xml:space="preserve">4.33506059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29443502426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28427839279175</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
@@ -4898,22 +4898,22 @@
     <t xml:space="preserve">4.09215450286865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85094213485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802505493164</t>
+    <t xml:space="preserve">3.8509418964386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87802481651306</t>
   </si>
   <si>
     <t xml:space="preserve">3.75784230232239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8526349067688</t>
+    <t xml:space="preserve">3.85263466835022</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9465811252594</t>
+    <t xml:space="preserve">3.94658064842224</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
@@ -4922,13 +4922,13 @@
     <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93811678886414</t>
+    <t xml:space="preserve">3.93811702728271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05491495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06676387786865</t>
+    <t xml:space="preserve">4.06676340103149</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766393661499</t>
+    <t xml:space="preserve">4.28766441345215</t>
   </si>
   <si>
     <t xml:space="preserve">4.29274272918701</t>
@@ -4961,37 +4961,37 @@
     <t xml:space="preserve">4.28258562088013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33336782455444</t>
+    <t xml:space="preserve">4.33336734771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.31305503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23857498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32828903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37907123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34013843536377</t>
+    <t xml:space="preserve">4.23857545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32828950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938402175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37907075881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34013795852661</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183168411255</t>
+    <t xml:space="preserve">4.34183120727539</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36722183227539</t>
+    <t xml:space="preserve">4.36722135543823</t>
   </si>
   <si>
     <t xml:space="preserve">4.37269258499146</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531141281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072353363037</t>
+    <t xml:space="preserve">4.33531188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3398699760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072305679321</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266326904297</t>
+    <t xml:space="preserve">4.36266374588013</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369129180908</t>
+    <t xml:space="preserve">4.40369176864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081052780151</t>
+    <t xml:space="preserve">4.35081100463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292520523071</t>
+    <t xml:space="preserve">4.48757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292568206787</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924903869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574781417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492357254028</t>
+    <t xml:space="preserve">4.43924951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492404937744</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5769214630127</t>
+    <t xml:space="preserve">4.57692193984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5915093421936</t>
+    <t xml:space="preserve">4.59150981903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891983032227</t>
+    <t xml:space="preserve">4.63891935348511</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130556106567</t>
+    <t xml:space="preserve">4.52130603790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5159,7 +5159,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786249160767</t>
+    <t xml:space="preserve">4.58786296844482</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5171,22 +5171,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732950210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897798538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197505950928</t>
+    <t xml:space="preserve">4.73191690444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644710540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197553634644</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6553316116333</t>
+    <t xml:space="preserve">4.56780481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65533113479614</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074373245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792064666748</t>
+    <t xml:space="preserve">4.68268394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792112350464</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68450689315796</t>
+    <t xml:space="preserve">4.6845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009395599365</t>
+    <t xml:space="preserve">4.73009347915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174291610718</t>
+    <t xml:space="preserve">4.67174243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7063889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6370964050293</t>
+    <t xml:space="preserve">4.70638847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63709688186646</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080188751221</t>
+    <t xml:space="preserve">4.66080141067505</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903614044189</t>
+    <t xml:space="preserve">4.67903661727905</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8887357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403158187866</t>
+    <t xml:space="preserve">4.87050104141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88873624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497308731079</t>
+    <t xml:space="preserve">4.85956048965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491445541382</t>
+    <t xml:space="preserve">4.82491397857666</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756212234497</t>
+    <t xml:space="preserve">4.79756259918213</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5348,13 +5348,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932786941528</t>
+    <t xml:space="preserve">4.77932739257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815422058105</t>
+    <t xml:space="preserve">4.6881537437439</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714496612549</t>
+    <t xml:space="preserve">4.96714544296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602994918823</t>
+    <t xml:space="preserve">4.89602947235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079229354858</t>
+    <t xml:space="preserve">4.97079277038574</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5423,7 +5423,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2333722114563</t>
+    <t xml:space="preserve">5.23337268829346</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5432,13 +5432,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2607250213623</t>
+    <t xml:space="preserve">5.26072454452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078317642212</t>
+    <t xml:space="preserve">5.28078269958496</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5450,10 +5450,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709890365601</t>
+    <t xml:space="preserve">6.38216161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709842681885</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8562650680542</t>
+    <t xml:space="preserve">6.85626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5489,13 +5489,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655679702759</t>
+    <t xml:space="preserve">6.95655632019043</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632322311401</t>
+    <t xml:space="preserve">6.87632369995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8690299987793</t>
+    <t xml:space="preserve">6.86902952194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5525,13 +5525,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625642776489</t>
+    <t xml:space="preserve">7.16625595092773</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213426589966</t>
+    <t xml:space="preserve">7.31213474273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566480636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537307739258</t>
+    <t xml:space="preserve">7.21184253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537355422974</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5558,10 +5558,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242551803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5127158164978</t>
+    <t xml:space="preserve">7.41242504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5570,19 +5570,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57653856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682933807373</t>
+    <t xml:space="preserve">7.63124227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580131530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.726975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682886123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67227029800415</t>
+    <t xml:space="preserve">7.67226982116699</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22387218475342</t>
+    <t xml:space="preserve">8.2238712310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -6573,6 +6573,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -71729,7 +71732,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6496412037</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>2800560</v>
@@ -71750,6 +71753,32 @@
         <v>2186</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494907407</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>1371615</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>18.7250003814697</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>18.1399993896484</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>18.625</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2187</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="2189">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528865814209</t>
+    <t xml:space="preserve">2.44528841972351</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">2.50193190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40895080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35658264160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31490111351013</t>
+    <t xml:space="preserve">2.40895104408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35658240318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.29780173301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37261343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3341383934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23474597930908</t>
+    <t xml:space="preserve">2.37261366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795758247375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33413887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2347457408905</t>
   </si>
   <si>
     <t xml:space="preserve">2.15458965301514</t>
@@ -77,85 +77,85 @@
     <t xml:space="preserve">2.11183977127075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99641561508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07977771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03489065170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03168439865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02954649925232</t>
+    <t xml:space="preserve">1.99641537666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588387489319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07977747917175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0348904132843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03168392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02954626083374</t>
   </si>
   <si>
     <t xml:space="preserve">1.90343463420868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00924062728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93549680709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84037864208221</t>
+    <t xml:space="preserve">2.00924015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93549704551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84037888050079</t>
   </si>
   <si>
     <t xml:space="preserve">1.74953532218933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75701653957367</t>
+    <t xml:space="preserve">1.75701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">1.67792952060699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349882602692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151166439056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861711025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823004245758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60632359981537</t>
+    <t xml:space="preserve">1.59349858760834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151154518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861699104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55822992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60632348060608</t>
   </si>
   <si>
     <t xml:space="preserve">1.72922933101654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67899823188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312281608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350417613983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69396090507507</t>
+    <t xml:space="preserve">1.67899811267853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312305450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69396066665649</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419176578522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70571672916412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296708583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7153354883194</t>
+    <t xml:space="preserve">1.70571660995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71533572673798</t>
   </si>
   <si>
     <t xml:space="preserve">1.82541620731354</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">1.8232786655426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88099122047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381563663483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488458633423</t>
+    <t xml:space="preserve">1.88099098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381575584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488470554352</t>
   </si>
   <si>
     <t xml:space="preserve">1.86602866649628</t>
@@ -179,223 +179,223 @@
     <t xml:space="preserve">1.80404126644135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76556646823883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82648491859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79976630210876</t>
+    <t xml:space="preserve">1.76556658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82648527622223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79976642131805</t>
   </si>
   <si>
     <t xml:space="preserve">1.920534491539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93442821502686</t>
+    <t xml:space="preserve">1.93442845344543</t>
   </si>
   <si>
     <t xml:space="preserve">1.93229067325592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221566200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435296535492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183430194855</t>
+    <t xml:space="preserve">1.96221506595612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435332298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183465957642</t>
   </si>
   <si>
     <t xml:space="preserve">1.95580339431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95259690284729</t>
+    <t xml:space="preserve">1.95259702205658</t>
   </si>
   <si>
     <t xml:space="preserve">1.92374062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87564718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88312840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91198444366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90022826194763</t>
+    <t xml:space="preserve">1.87564742565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8831285238266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91198456287384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9002286195755</t>
   </si>
   <si>
     <t xml:space="preserve">1.89167845249176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579744815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190420150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992215156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129685401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92587840557098</t>
+    <t xml:space="preserve">1.81579768657684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81793510913849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8019038438797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992227077484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465324878693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587828636169</t>
   </si>
   <si>
     <t xml:space="preserve">1.92801570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91519129276276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0177903175354</t>
+    <t xml:space="preserve">1.91519069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01779055595398</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626535415649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07443380355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06160879135132</t>
+    <t xml:space="preserve">2.07443356513977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0616090297699</t>
   </si>
   <si>
     <t xml:space="preserve">2.07015895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02634048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0551962852478</t>
+    <t xml:space="preserve">2.02634072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05519604682922</t>
   </si>
   <si>
     <t xml:space="preserve">2.05092144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99855291843414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214029312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95045924186707</t>
+    <t xml:space="preserve">1.99855315685272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214041233063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95045959949493</t>
   </si>
   <si>
     <t xml:space="preserve">1.93977189064026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84999704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457847595215</t>
+    <t xml:space="preserve">1.84999752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457835674286</t>
   </si>
   <si>
     <t xml:space="preserve">1.79121661186218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73884785175323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388541698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502937793732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678532123566</t>
+    <t xml:space="preserve">1.73884773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388565540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69502949714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678567886353</t>
   </si>
   <si>
     <t xml:space="preserve">1.70785462856293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76235270500183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700954914093</t>
+    <t xml:space="preserve">1.76235258579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700931072235</t>
   </si>
   <si>
     <t xml:space="preserve">1.87773132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87546920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279721260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90601003170013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451814651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081248283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80986154079437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81438612937927</t>
+    <t xml:space="preserve">1.87546896934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279768943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.906010389328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451826572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081212520599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80986142158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81438624858856</t>
   </si>
   <si>
     <t xml:space="preserve">1.80646777153015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75104081630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6311377286911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54290688037872</t>
+    <t xml:space="preserve">1.75104069709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63113760948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54290699958801</t>
   </si>
   <si>
     <t xml:space="preserve">1.46711909770966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47390592098236</t>
+    <t xml:space="preserve">1.47390615940094</t>
   </si>
   <si>
     <t xml:space="preserve">1.42526602745056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51688992977142</t>
+    <t xml:space="preserve">1.51689028739929</t>
   </si>
   <si>
     <t xml:space="preserve">1.61190783977509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6005961894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57684195041656</t>
+    <t xml:space="preserve">1.60059642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57684183120728</t>
   </si>
   <si>
     <t xml:space="preserve">1.69900751113892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38341283798218</t>
+    <t xml:space="preserve">1.38341295719147</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27255868911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213738322258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19111514091492</t>
+    <t xml:space="preserve">1.27255892753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21373844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19111526012421</t>
   </si>
   <si>
     <t xml:space="preserve">1.23636174201965</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">1.18545925617218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14021277427673</t>
+    <t xml:space="preserve">1.14021289348602</t>
   </si>
   <si>
     <t xml:space="preserve">1.09949088096619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722852706909</t>
+    <t xml:space="preserve">1.09722864627838</t>
   </si>
   <si>
     <t xml:space="preserve">1.23749268054962</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">1.28726410865784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36870777606964</t>
+    <t xml:space="preserve">1.36870789527893</t>
   </si>
   <si>
     <t xml:space="preserve">1.33477294445038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3935934305191</t>
+    <t xml:space="preserve">1.39359319210052</t>
   </si>
   <si>
     <t xml:space="preserve">1.38454401493073</t>
@@ -443,73 +443,73 @@
     <t xml:space="preserve">1.37888824939728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37097012996674</t>
+    <t xml:space="preserve">1.37097024917603</t>
   </si>
   <si>
     <t xml:space="preserve">1.37775731086731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42979073524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40264248847961</t>
+    <t xml:space="preserve">1.42979061603546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4026426076889</t>
   </si>
   <si>
     <t xml:space="preserve">1.38567531108856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2601158618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29631340503693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32233023643494</t>
+    <t xml:space="preserve">1.26011610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29631328582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32233011722565</t>
   </si>
   <si>
     <t xml:space="preserve">1.37549471855164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43657767772675</t>
+    <t xml:space="preserve">1.43657755851746</t>
   </si>
   <si>
     <t xml:space="preserve">1.4535448551178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44788944721222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47051239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45015156269073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41961002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38001942634583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39698708057404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33137941360474</t>
+    <t xml:space="preserve">1.44788908958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47051250934601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45015144348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41961026191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38001930713654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39698684215546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33137953281403</t>
   </si>
   <si>
     <t xml:space="preserve">1.33251059055328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38228178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36757659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816635608673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3540027141571</t>
+    <t xml:space="preserve">1.38228189945221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36757671833038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35400259494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.3279857635498</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">1.41056072711945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40377378463745</t>
+    <t xml:space="preserve">1.40377390384674</t>
   </si>
   <si>
     <t xml:space="preserve">1.42413485050201</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">1.45920085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.477299451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48747992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48974215984344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39020001888275</t>
+    <t xml:space="preserve">1.47729933261871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48748016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48974227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39019978046417</t>
   </si>
   <si>
     <t xml:space="preserve">1.40716731548309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36078953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282308101654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513377189636</t>
+    <t xml:space="preserve">1.36078941822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282296180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513365268707</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947800636292</t>
@@ -563,97 +563,97 @@
     <t xml:space="preserve">1.30536258220673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27821457386017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28613269329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28500175476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27934598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35174024105072</t>
+    <t xml:space="preserve">1.27821469306946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780552864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28500187397003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27934587001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3517404794693</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37210130691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39472472667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41621673107147</t>
+    <t xml:space="preserve">1.37210142612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39472460746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41621661186218</t>
   </si>
   <si>
     <t xml:space="preserve">1.44110226631165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49313592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52480852603912</t>
+    <t xml:space="preserve">1.49313569068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52480864524841</t>
   </si>
   <si>
     <t xml:space="preserve">1.53159534931183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51575887203217</t>
+    <t xml:space="preserve">1.51575899124146</t>
   </si>
   <si>
     <t xml:space="preserve">1.54856264591217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5655300617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61077678203583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63453114032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5983339548111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571041584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118594646454</t>
+    <t xml:space="preserve">1.56553030014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61077654361725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63453102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59833383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118630409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.50444734096527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51802134513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47503709793091</t>
+    <t xml:space="preserve">1.51802122592926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47503733634949</t>
   </si>
   <si>
     <t xml:space="preserve">1.65715444087982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69335162639618</t>
+    <t xml:space="preserve">1.69335186481476</t>
   </si>
   <si>
     <t xml:space="preserve">1.66733491420746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6616792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63905608654022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172748565674</t>
+    <t xml:space="preserve">1.66167891025543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63905572891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172736644745</t>
   </si>
   <si>
     <t xml:space="preserve">1.57457947731018</t>
@@ -662,61 +662,61 @@
     <t xml:space="preserve">1.6266131401062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58476006984711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56100559234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064452648163</t>
+    <t xml:space="preserve">1.58475995063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5610054731369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064464569092</t>
   </si>
   <si>
     <t xml:space="preserve">1.60512089729309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64923632144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66620373725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6243509054184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049963474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741847515106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284566879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492754936218</t>
+    <t xml:space="preserve">1.64923620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6662038564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049987316132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741871356964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284578800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492766857147</t>
   </si>
   <si>
     <t xml:space="preserve">1.83022248744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86302638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91053485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89922320842743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91166615486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92637133598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94560110569</t>
+    <t xml:space="preserve">1.86302649974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623943805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9105349779129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89922380447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91166627407074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92637145519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94560134410858</t>
   </si>
   <si>
     <t xml:space="preserve">1.94446992874146</t>
@@ -728,73 +728,73 @@
     <t xml:space="preserve">1.93655180931091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98066687583923</t>
+    <t xml:space="preserve">1.9806672334671</t>
   </si>
   <si>
     <t xml:space="preserve">2.01347088813782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00781488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01573300361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01912665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96483087539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99876546859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0202579498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727358341217</t>
+    <t xml:space="preserve">2.00781536102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01573348045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01912689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96483111381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99876582622528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02025818824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727370262146</t>
   </si>
   <si>
     <t xml:space="preserve">2.01007723808289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97161781787872</t>
+    <t xml:space="preserve">1.97161841392517</t>
   </si>
   <si>
     <t xml:space="preserve">1.9478634595871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97953593730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0225203037262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08247208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08699631690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193018913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542075157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202722072601</t>
+    <t xml:space="preserve">1.97953629493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02252054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99084758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08699679374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05079936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542063236237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202710151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.96709322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894594192505</t>
+    <t xml:space="preserve">2.00894618034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.90940380096436</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">1.89130556583405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87320685386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999379634857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510814189911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596240997314</t>
+    <t xml:space="preserve">1.873206615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999355792999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8551082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96596205234528</t>
   </si>
   <si>
     <t xml:space="preserve">2.03609418869019</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">1.99424111843109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00215935707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00329065322876</t>
+    <t xml:space="preserve">2.00215911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0032901763916</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478241920471</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">2.01799559593201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00442147254944</t>
+    <t xml:space="preserve">2.00442123413086</t>
   </si>
   <si>
     <t xml:space="preserve">1.95465052127838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02930736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02817606925964</t>
+    <t xml:space="preserve">2.02930760383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02817630767822</t>
   </si>
   <si>
     <t xml:space="preserve">2.09265232086182</t>
@@ -851,46 +851,46 @@
     <t xml:space="preserve">2.13224315643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432503700256</t>
+    <t xml:space="preserve">2.12432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.12093162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15939116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373563766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07568502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14921045303345</t>
+    <t xml:space="preserve">2.15939092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016127586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10848879814148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0756847858429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14921069145203</t>
   </si>
   <si>
     <t xml:space="preserve">2.19332575798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17862129211426</t>
+    <t xml:space="preserve">2.1786208152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.23291683197021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19558811187744</t>
+    <t xml:space="preserve">2.1955885887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.20803117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20576882362366</t>
+    <t xml:space="preserve">2.20576858520508</t>
   </si>
   <si>
     <t xml:space="preserve">2.18314552307129</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">2.16617798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20350623130798</t>
+    <t xml:space="preserve">2.20350670814514</t>
   </si>
   <si>
     <t xml:space="preserve">2.19219446182251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20011305809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17522740364075</t>
+    <t xml:space="preserve">2.15826010704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20011258125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17522764205933</t>
   </si>
   <si>
     <t xml:space="preserve">2.17748975753784</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">2.15599751472473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14129233360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09378337860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07907843589783</t>
+    <t xml:space="preserve">2.14129257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09378361701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07907867431641</t>
   </si>
   <si>
     <t xml:space="preserve">2.08812785148621</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">2.10961985588074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22273635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26232695579529</t>
+    <t xml:space="preserve">2.222736120224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26232719421387</t>
   </si>
   <si>
     <t xml:space="preserve">2.26006460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25780248641968</t>
+    <t xml:space="preserve">2.2578022480011</t>
   </si>
   <si>
     <t xml:space="preserve">2.31436038017273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33132839202881</t>
+    <t xml:space="preserve">2.33132791519165</t>
   </si>
   <si>
     <t xml:space="preserve">2.34716415405273</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">2.41164040565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43878793716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44557499885559</t>
+    <t xml:space="preserve">2.43878817558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44557523727417</t>
   </si>
   <si>
     <t xml:space="preserve">2.39127969741821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32567191123962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38675498962402</t>
+    <t xml:space="preserve">2.32567238807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38675475120544</t>
   </si>
   <si>
     <t xml:space="preserve">2.3630006313324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33585262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25893354415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24988436698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27137589454651</t>
+    <t xml:space="preserve">2.33585238456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25893330574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24988412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27137613296509</t>
   </si>
   <si>
     <t xml:space="preserve">2.33769392967224</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">2.30216646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36137866973877</t>
+    <t xml:space="preserve">2.36137819290161</t>
   </si>
   <si>
     <t xml:space="preserve">2.35072040557861</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">2.30808782577515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21453261375427</t>
+    <t xml:space="preserve">2.21453285217285</t>
   </si>
   <si>
     <t xml:space="preserve">2.21926951408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19558477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21098017692566</t>
+    <t xml:space="preserve">2.19558429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2109797000885</t>
   </si>
   <si>
     <t xml:space="preserve">2.18137359619141</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">2.1458466053009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13637280464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10913515090942</t>
+    <t xml:space="preserve">2.13637256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.109135389328</t>
   </si>
   <si>
     <t xml:space="preserve">2.14110946655273</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">2.14229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16361021995544</t>
+    <t xml:space="preserve">2.16361045837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.18611097335815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13874101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11979293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14939904212952</t>
+    <t xml:space="preserve">2.13874125480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.119793176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1493992805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.13755679130554</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15532040596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20032167434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1837420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27374482154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453768730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3838791847229</t>
+    <t xml:space="preserve">2.1553201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2003219127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18374228477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821759223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27374458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38387894630432</t>
   </si>
   <si>
     <t xml:space="preserve">2.34835195541382</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">2.36848425865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37322115898132</t>
+    <t xml:space="preserve">2.37322092056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.36966824531555</t>
@@ -1097,25 +1097,25 @@
     <t xml:space="preserve">2.37203693389893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38032650947571</t>
+    <t xml:space="preserve">2.38032627105713</t>
   </si>
   <si>
     <t xml:space="preserve">2.38861632347107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34361481666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30927205085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28913950920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29387712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058857917786</t>
+    <t xml:space="preserve">2.34361505508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30927181243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28913998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2938768863678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33058834075928</t>
   </si>
   <si>
     <t xml:space="preserve">2.34953618049622</t>
@@ -1127,28 +1127,28 @@
     <t xml:space="preserve">2.31637740135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34479928016663</t>
+    <t xml:space="preserve">2.34479951858521</t>
   </si>
   <si>
     <t xml:space="preserve">2.31756162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34006237983704</t>
+    <t xml:space="preserve">2.34006214141846</t>
   </si>
   <si>
     <t xml:space="preserve">2.40401124954224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4099326133728</t>
+    <t xml:space="preserve">2.40993237495422</t>
   </si>
   <si>
     <t xml:space="preserve">2.37914252281189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3554573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045627593994</t>
+    <t xml:space="preserve">2.35545754432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045603752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25953388214111</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">2.25598096847534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23111200332642</t>
+    <t xml:space="preserve">2.23111248016357</t>
   </si>
   <si>
     <t xml:space="preserve">2.22163820266724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19676899909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19321608543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18492650985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163542747498</t>
+    <t xml:space="preserve">2.19676876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18492674827576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163566589355</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005730628967</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">2.15058326721191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16834688186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13045167922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11031913757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0842661857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22400665283203</t>
+    <t xml:space="preserve">2.16834712028503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13045144081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12097764015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1103196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08426594734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22400689125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.24295449256897</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">2.28795552253723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25005984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25834965705872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24413847923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22755932807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22637510299683</t>
+    <t xml:space="preserve">2.25006008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24413824081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2275595664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22637486457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.23703336715698</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">2.3211145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2571656703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27137613296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30453515052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29742956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25124454498291</t>
+    <t xml:space="preserve">2.25716519355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27137637138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3045346736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29742980003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25124406814575</t>
   </si>
   <si>
     <t xml:space="preserve">2.31874585151672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27848196029663</t>
+    <t xml:space="preserve">2.27848172187805</t>
   </si>
   <si>
     <t xml:space="preserve">2.26663947105408</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">2.28321862220764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32703590393066</t>
+    <t xml:space="preserve">2.32703566551208</t>
   </si>
   <si>
     <t xml:space="preserve">2.34598350524902</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">2.1482150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19795322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20979595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19913768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23348069190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23584890365601</t>
+    <t xml:space="preserve">2.19795298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20979571342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19913744926453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23348021507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23584914207458</t>
   </si>
   <si>
     <t xml:space="preserve">2.28085017204285</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">2.26900792121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24177002906799</t>
+    <t xml:space="preserve">2.27256035804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24177050590515</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361251831055</t>
@@ -1325,43 +1325,43 @@
     <t xml:space="preserve">2.26308655738831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28677177429199</t>
+    <t xml:space="preserve">2.28677105903625</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30098223686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33177280426025</t>
+    <t xml:space="preserve">2.30098247528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3317723274231</t>
   </si>
   <si>
     <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31519293785095</t>
+    <t xml:space="preserve">2.31519341468811</t>
   </si>
   <si>
     <t xml:space="preserve">2.39098477363586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41585373878479</t>
+    <t xml:space="preserve">2.41585350036621</t>
   </si>
   <si>
     <t xml:space="preserve">2.41940641403198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4371702671051</t>
+    <t xml:space="preserve">2.43717050552368</t>
   </si>
   <si>
     <t xml:space="preserve">2.48098731040955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53309345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5674364566803</t>
+    <t xml:space="preserve">2.53309392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56743669509888</t>
   </si>
   <si>
     <t xml:space="preserve">2.54612040519714</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">2.57691073417664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56980538368225</t>
+    <t xml:space="preserve">2.56980514526367</t>
   </si>
   <si>
     <t xml:space="preserve">2.56625247001648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63967561721802</t>
+    <t xml:space="preserve">2.63967537879944</t>
   </si>
   <si>
     <t xml:space="preserve">2.65743923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66691327095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63671517372131</t>
+    <t xml:space="preserve">2.66691303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63671469688416</t>
   </si>
   <si>
     <t xml:space="preserve">2.62960958480835</t>
@@ -1403,28 +1403,28 @@
     <t xml:space="preserve">2.58105564117432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57158160209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56921315193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48039484024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53013300895691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45611786842346</t>
+    <t xml:space="preserve">2.5715811252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56921339035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48039507865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53013324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45611810684204</t>
   </si>
   <si>
     <t xml:space="preserve">2.48217129707336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44605207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4069721698761</t>
+    <t xml:space="preserve">2.44605183601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40697193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236733436584</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">2.4709210395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45552563667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723582267761</t>
+    <t xml:space="preserve">2.45552587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723629951477</t>
   </si>
   <si>
     <t xml:space="preserve">2.4655921459198</t>
@@ -1448,25 +1448,25 @@
     <t xml:space="preserve">2.41881442070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40934014320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43480157852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756392478943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3264434337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33473324775696</t>
+    <t xml:space="preserve">2.40934038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43480181694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40756416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32644367218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33473348617554</t>
   </si>
   <si>
     <t xml:space="preserve">2.35190463066101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39631366729736</t>
+    <t xml:space="preserve">2.39631390571594</t>
   </si>
   <si>
     <t xml:space="preserve">2.3744056224823</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611580848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38624787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39986634254456</t>
+    <t xml:space="preserve">2.36611557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38624811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39986658096313</t>
   </si>
   <si>
     <t xml:space="preserve">2.32881188392639</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">2.37499737739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36374711990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39809012413025</t>
+    <t xml:space="preserve">2.36374735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39809036254883</t>
   </si>
   <si>
     <t xml:space="preserve">2.38565564155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41230130195618</t>
+    <t xml:space="preserve">2.4123010635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.41822242736816</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">2.45078873634338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51769852638245</t>
+    <t xml:space="preserve">2.51769828796387</t>
   </si>
   <si>
     <t xml:space="preserve">2.51355361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54315972328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54079151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54375171661377</t>
+    <t xml:space="preserve">2.54315948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54079127311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54375195503235</t>
   </si>
   <si>
     <t xml:space="preserve">2.58756875991821</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">2.61066150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58223962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59408235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61480665206909</t>
+    <t xml:space="preserve">2.58223986625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59408211708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61480617523193</t>
   </si>
   <si>
     <t xml:space="preserve">2.63493847846985</t>
@@ -1556,106 +1556,106 @@
     <t xml:space="preserve">2.64204382896423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67165017127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6752028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58638453483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60177969932556</t>
+    <t xml:space="preserve">2.67165040969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67520260810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58638429641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60178017616272</t>
   </si>
   <si>
     <t xml:space="preserve">2.55855512619019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59526634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51059317588806</t>
+    <t xml:space="preserve">2.57039713859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59349036216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59526610374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51059293746948</t>
   </si>
   <si>
     <t xml:space="preserve">2.54967331886292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48868465423584</t>
+    <t xml:space="preserve">2.48868489265442</t>
   </si>
   <si>
     <t xml:space="preserve">2.49672627449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48621010780334</t>
+    <t xml:space="preserve">2.48621034622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40888333320618</t>
+    <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
     <t xml:space="preserve">2.38785076141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3773341178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25917863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176090240479</t>
+    <t xml:space="preserve">2.37733435630798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25917887687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176137924194</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361108779907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33464980125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577923774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2375271320343</t>
+    <t xml:space="preserve">2.33464956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577899932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23752737045288</t>
   </si>
   <si>
     <t xml:space="preserve">2.22577357292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23567128181458</t>
+    <t xml:space="preserve">2.23567175865173</t>
   </si>
   <si>
     <t xml:space="preserve">2.16020059585571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24989938735962</t>
+    <t xml:space="preserve">2.2498996257782</t>
   </si>
   <si>
     <t xml:space="preserve">2.2319598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23938274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371361732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20041012763977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20968985557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22329902648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20721530914307</t>
+    <t xml:space="preserve">2.23938322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371314048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20041060447693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2096893787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22329926490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20721507072449</t>
   </si>
   <si>
     <t xml:space="preserve">2.15525150299072</t>
@@ -1667,31 +1667,31 @@
     <t xml:space="preserve">2.05812907218933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05874800682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379891395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02843570709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04699444770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04946851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0921528339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11689734458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10143208503723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14102339744568</t>
+    <t xml:space="preserve">2.0587477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02843546867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04699397087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04946875572205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09215307235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11689758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10143184661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14102363586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813473701477</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">2.08906006813049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0686457157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09091591835022</t>
+    <t xml:space="preserve">2.06864595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09091567993164</t>
   </si>
   <si>
     <t xml:space="preserve">2.10638093948364</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">2.12679529190063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14349770545959</t>
+    <t xml:space="preserve">2.14349794387817</t>
   </si>
   <si>
     <t xml:space="preserve">2.13793039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12122750282288</t>
+    <t xml:space="preserve">2.12122821807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.09957647323608</t>
@@ -1727,55 +1727,55 @@
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473485946655</t>
+    <t xml:space="preserve">2.14473509788513</t>
   </si>
   <si>
     <t xml:space="preserve">2.18061470985413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16514945030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20102882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09029698371887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432098388672</t>
+    <t xml:space="preserve">2.16514921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20102906227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09029722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1243212223053</t>
   </si>
   <si>
     <t xml:space="preserve">2.10699963569641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13916778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1199905872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07730627059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0723569393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11937189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20474076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28392338752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23319721221924</t>
+    <t xml:space="preserve">2.13916754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07730650901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07235717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11937212944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20474052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28392314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23319697380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.19174981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2430944442749</t>
+    <t xml:space="preserve">2.24309468269348</t>
   </si>
   <si>
     <t xml:space="preserve">2.26289033889771</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">2.25299263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26969504356384</t>
+    <t xml:space="preserve">2.26969528198242</t>
   </si>
   <si>
     <t xml:space="preserve">2.27711844444275</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">2.25608563423157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24185729026794</t>
+    <t xml:space="preserve">2.2418577671051</t>
   </si>
   <si>
     <t xml:space="preserve">2.19917321205139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2220618724823</t>
+    <t xml:space="preserve">2.22206211090088</t>
   </si>
   <si>
     <t xml:space="preserve">2.2752628326416</t>
@@ -1811,28 +1811,28 @@
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31423544883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991095542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33712410926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33836150169373</t>
+    <t xml:space="preserve">2.31423568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3699107170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33712434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33836126327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.33403086662292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3600127696991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40146017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41630673408508</t>
+    <t xml:space="preserve">2.36001300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40145969390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4163064956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.41445112228394</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">2.45589804649353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44352579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47012591362</t>
+    <t xml:space="preserve">2.44352555274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47012615203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.48682880401611</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">2.50600576400757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37300372123718</t>
+    <t xml:space="preserve">2.37300395965576</t>
   </si>
   <si>
     <t xml:space="preserve">2.367436170578</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">2.30743074417114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37795305252075</t>
+    <t xml:space="preserve">2.37795281410217</t>
   </si>
   <si>
     <t xml:space="preserve">2.36496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2709321975708</t>
+    <t xml:space="preserve">2.27093243598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.28083038330078</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">2.19855451583862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20907115936279</t>
+    <t xml:space="preserve">2.20907092094421</t>
   </si>
   <si>
     <t xml:space="preserve">2.18308925628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17504715919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19979166984558</t>
+    <t xml:space="preserve">2.17504739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19979190826416</t>
   </si>
   <si>
     <t xml:space="preserve">2.16824269294739</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">2.13978624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12184643745422</t>
+    <t xml:space="preserve">2.1218466758728</t>
   </si>
   <si>
     <t xml:space="preserve">2.19669890403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380976676941</t>
+    <t xml:space="preserve">2.17380952835083</t>
   </si>
   <si>
     <t xml:space="preserve">2.21525716781616</t>
@@ -1922,28 +1922,28 @@
     <t xml:space="preserve">2.24247598648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24433159828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24742484092712</t>
+    <t xml:space="preserve">2.24433207511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2474250793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.2597975730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33217549324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34949636459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26598334312439</t>
+    <t xml:space="preserve">2.33217525482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34949660301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26598358154297</t>
   </si>
   <si>
     <t xml:space="preserve">2.26227164268494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28825330734253</t>
+    <t xml:space="preserve">2.28825354576111</t>
   </si>
   <si>
     <t xml:space="preserve">2.22701072692871</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">2.28949093818665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24680614471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23381543159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15277695655823</t>
+    <t xml:space="preserve">2.24680638313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23381567001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15277743339539</t>
   </si>
   <si>
     <t xml:space="preserve">2.16947960853577</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">2.18556380271912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21278238296509</t>
+    <t xml:space="preserve">2.21278262138367</t>
   </si>
   <si>
     <t xml:space="preserve">2.19607996940613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504197120667</t>
+    <t xml:space="preserve">2.11504173278809</t>
   </si>
   <si>
     <t xml:space="preserve">2.13607454299927</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">2.14040493965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27959322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32413339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31794714927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35073351860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38846921920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41012024879456</t>
+    <t xml:space="preserve">2.27959275245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3241331577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31794691085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35073375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846898078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41012048721313</t>
   </si>
   <si>
     <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32227754592896</t>
+    <t xml:space="preserve">2.32227730751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">2.43424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44971203804016</t>
+    <t xml:space="preserve">2.44971179962158</t>
   </si>
   <si>
     <t xml:space="preserve">2.45342373847961</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">2.5511646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53260612487793</t>
+    <t xml:space="preserve">2.53260636329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.47321915626526</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">2.47136330604553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50043821334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5152850151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52394580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4620840549469</t>
+    <t xml:space="preserve">2.50043797492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51528525352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52394556999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46208429336548</t>
   </si>
   <si>
     <t xml:space="preserve">2.32908225059509</t>
@@ -2087,22 +2087,22 @@
     <t xml:space="preserve">2.45713520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45094919204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47507524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46579599380493</t>
+    <t xml:space="preserve">2.4509494304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47507500648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46579575538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49054074287415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48187971115112</t>
+    <t xml:space="preserve">2.49054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4818799495697</t>
   </si>
   <si>
     <t xml:space="preserve">2.47878694534302</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">2.49548959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50662422180176</t>
+    <t xml:space="preserve">2.50662446022034</t>
   </si>
   <si>
     <t xml:space="preserve">2.52889442443848</t>
@@ -2123,46 +2123,46 @@
     <t xml:space="preserve">2.50786137580872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55302023887634</t>
+    <t xml:space="preserve">2.55302047729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.56601119041443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58147668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64952421188354</t>
+    <t xml:space="preserve">2.58147644996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64952445030212</t>
   </si>
   <si>
     <t xml:space="preserve">2.68292927742004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69901299476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68231058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66870164871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179417610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69282698631287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71014857292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74664640426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76396775245667</t>
+    <t xml:space="preserve">2.69901323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68231105804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66870141029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179465293884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69282722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71014881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74664664268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76396799087524</t>
   </si>
   <si>
     <t xml:space="preserve">2.72994422912598</t>
@@ -2171,52 +2171,52 @@
     <t xml:space="preserve">2.83696436882019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83449006080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86109066009521</t>
+    <t xml:space="preserve">2.8344898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86109042167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.85057377815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79799151420593</t>
+    <t xml:space="preserve">2.79799127578735</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716304779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76025629043579</t>
+    <t xml:space="preserve">2.76025581359863</t>
   </si>
   <si>
     <t xml:space="preserve">2.78500080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78994989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.820880651474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83943915367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83882069587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79737305641174</t>
+    <t xml:space="preserve">2.78995013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82088088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83943867683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8388204574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79737281799316</t>
   </si>
   <si>
     <t xml:space="preserve">2.81160116195679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78685712814331</t>
+    <t xml:space="preserve">2.78685641288757</t>
   </si>
   <si>
     <t xml:space="preserve">2.79922890663147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80603361129761</t>
+    <t xml:space="preserve">2.80603384971619</t>
   </si>
   <si>
     <t xml:space="preserve">2.81778740882874</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">2.79551720619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74417233467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65694785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59137439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69097137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66560840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73056292533875</t>
+    <t xml:space="preserve">2.74417209625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65694737434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014290809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59137487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6909716129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66560816764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73056268692017</t>
   </si>
   <si>
     <t xml:space="preserve">2.79984760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76334953308105</t>
+    <t xml:space="preserve">2.76334929466248</t>
   </si>
   <si>
     <t xml:space="preserve">2.7504575252533</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">2.75625896453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79106640815735</t>
+    <t xml:space="preserve">2.79106664657593</t>
   </si>
   <si>
     <t xml:space="preserve">2.68084192276001</t>
@@ -2267,58 +2267,58 @@
     <t xml:space="preserve">2.79235577583313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72596335411072</t>
+    <t xml:space="preserve">2.72596311569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.68148636817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6286301612854</t>
+    <t xml:space="preserve">2.62863063812256</t>
   </si>
   <si>
     <t xml:space="preserve">2.65892577171326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66279339790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6344313621521</t>
+    <t xml:space="preserve">2.66279363632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63443160057068</t>
   </si>
   <si>
     <t xml:space="preserve">2.68664336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66666126251221</t>
+    <t xml:space="preserve">2.66666102409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.65183520317078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472697257996</t>
+    <t xml:space="preserve">2.66472721099854</t>
   </si>
   <si>
     <t xml:space="preserve">2.6885769367218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72016143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69695663452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65247988700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953513145447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7530357837677</t>
+    <t xml:space="preserve">2.6943781375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68986582756042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72016167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69695639610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65247964859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953489303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75303554534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.73563170433044</t>
@@ -2330,43 +2330,43 @@
     <t xml:space="preserve">2.76206016540527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75883722305298</t>
+    <t xml:space="preserve">2.7588369846344</t>
   </si>
   <si>
     <t xml:space="preserve">2.79428935050964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76077103614807</t>
+    <t xml:space="preserve">2.76077127456665</t>
   </si>
   <si>
     <t xml:space="preserve">2.79944610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.820072889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86197113990784</t>
+    <t xml:space="preserve">2.82007312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86197090148926</t>
   </si>
   <si>
     <t xml:space="preserve">2.91160440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90773701667786</t>
+    <t xml:space="preserve">2.90773677825928</t>
   </si>
   <si>
     <t xml:space="preserve">2.8916220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89484548568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414757728577</t>
+    <t xml:space="preserve">2.89484524726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414781570435</t>
   </si>
   <si>
     <t xml:space="preserve">2.97477436065674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96832823753357</t>
+    <t xml:space="preserve">2.96832847595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.97541880607605</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">2.98702096939087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9689724445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735238075256</t>
+    <t xml:space="preserve">2.96897268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735261917114</t>
   </si>
   <si>
     <t xml:space="preserve">2.91805028915405</t>
@@ -2387,25 +2387,25 @@
     <t xml:space="preserve">3.04181122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02118420600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03665447235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03923296928406</t>
+    <t xml:space="preserve">3.02118444442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03665471076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03923320770264</t>
   </si>
   <si>
     <t xml:space="preserve">3.04825735092163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155117988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98895525932312</t>
+    <t xml:space="preserve">3.00829243659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155141830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98895478248596</t>
   </si>
   <si>
     <t xml:space="preserve">2.90902614593506</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">2.86003756523132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84263372421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78655433654785</t>
+    <t xml:space="preserve">2.84263348579407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78655457496643</t>
   </si>
   <si>
     <t xml:space="preserve">2.76592755317688</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">2.73434281349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78010892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84843468666077</t>
+    <t xml:space="preserve">2.78010869026184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84843492507935</t>
   </si>
   <si>
     <t xml:space="preserve">2.87421846389771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9560809135437</t>
+    <t xml:space="preserve">2.95608067512512</t>
   </si>
   <si>
     <t xml:space="preserve">2.9477014541626</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.91676115989685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94705677032471</t>
+    <t xml:space="preserve">2.94705700874329</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031503677368</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">2.96510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94576787948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94125556945801</t>
+    <t xml:space="preserve">2.9457676410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94125533103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.94383382797241</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">2.95479202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801472663879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98959970474243</t>
+    <t xml:space="preserve">2.95801496505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98959946632385</t>
   </si>
   <si>
     <t xml:space="preserve">3.05921530723572</t>
@@ -2486,16 +2486,16 @@
     <t xml:space="preserve">3.11013746261597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10884857177734</t>
+    <t xml:space="preserve">3.10884881019592</t>
   </si>
   <si>
     <t xml:space="preserve">3.080486536026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10240268707275</t>
+    <t xml:space="preserve">3.11464953422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10240292549133</t>
   </si>
   <si>
     <t xml:space="preserve">3.09853529930115</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">3.14945769309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592123985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661843299866</t>
+    <t xml:space="preserve">3.13592100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661867141724</t>
   </si>
   <si>
     <t xml:space="preserve">3.05663681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02698540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275152206421</t>
+    <t xml:space="preserve">3.02698564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275128364563</t>
   </si>
   <si>
     <t xml:space="preserve">3.04696846008301</t>
@@ -2540,25 +2540,25 @@
     <t xml:space="preserve">3.19071102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15396952629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15010190010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17781901359558</t>
+    <t xml:space="preserve">3.15396976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15010166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17781925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.20553684234619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22680854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22165131568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21262741088867</t>
+    <t xml:space="preserve">3.22680830955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22165179252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21262764930725</t>
   </si>
   <si>
     <t xml:space="preserve">3.23325371742249</t>
@@ -2570,31 +2570,31 @@
     <t xml:space="preserve">3.21391630172729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23970007896423</t>
+    <t xml:space="preserve">3.23969960212708</t>
   </si>
   <si>
     <t xml:space="preserve">3.26548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24743509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2222957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388097763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739976882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447243690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185790061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39955806732178</t>
+    <t xml:space="preserve">3.2474353313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22229599952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388073921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447219848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39955830574036</t>
   </si>
   <si>
     <t xml:space="preserve">3.4111602306366</t>
@@ -2606,46 +2606,46 @@
     <t xml:space="preserve">3.49108958244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47304058074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43823289871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45370316505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311170578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41631722450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41502737998962</t>
+    <t xml:space="preserve">3.47304081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823313713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41631698608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41502785682678</t>
   </si>
   <si>
     <t xml:space="preserve">3.413738489151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44596767425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987133979797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920827865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34541249275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994198799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.389244556427</t>
+    <t xml:space="preserve">3.44596815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920851707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3454122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994222640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38924431800842</t>
   </si>
   <si>
     <t xml:space="preserve">3.38795495033264</t>
@@ -2657,79 +2657,79 @@
     <t xml:space="preserve">3.29126667976379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2719292640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32865309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36861753463745</t>
+    <t xml:space="preserve">3.27192902565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32865333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36861705780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.43049788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43694376945496</t>
+    <t xml:space="preserve">3.43694400787354</t>
   </si>
   <si>
     <t xml:space="preserve">3.42405152320862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42147350311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47819805145264</t>
+    <t xml:space="preserve">3.42147397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47819781303406</t>
   </si>
   <si>
     <t xml:space="preserve">3.4549925327301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37635278701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513454437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35572528839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22938680648804</t>
+    <t xml:space="preserve">3.37635254859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2951340675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35572600364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22938704490662</t>
   </si>
   <si>
     <t xml:space="preserve">3.30544781684875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3325207233429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841094970703</t>
+    <t xml:space="preserve">3.33252048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576132774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841071128845</t>
   </si>
   <si>
     <t xml:space="preserve">3.14752340316772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18490982055664</t>
+    <t xml:space="preserve">3.18491005897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.19006657600403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16815042495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17395186424255</t>
+    <t xml:space="preserve">3.1681501865387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17395210266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.1320538520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09982442855835</t>
+    <t xml:space="preserve">3.09982419013977</t>
   </si>
   <si>
     <t xml:space="preserve">3.12238454818726</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">3.11593890190125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1462345123291</t>
+    <t xml:space="preserve">3.14623475074768</t>
   </si>
   <si>
     <t xml:space="preserve">3.02182912826538</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">3.00958204269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04310059547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09466743469238</t>
+    <t xml:space="preserve">3.04310083389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09466767311096</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
@@ -2777,22 +2777,22 @@
     <t xml:space="preserve">3.54394555091858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47561955451965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39440083503723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17459630966187</t>
+    <t xml:space="preserve">3.47561931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39440059661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17459654808044</t>
   </si>
   <si>
     <t xml:space="preserve">3.14236688613892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01409411430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8858208656311</t>
+    <t xml:space="preserve">3.01409435272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88582110404968</t>
   </si>
   <si>
     <t xml:space="preserve">2.7427225112915</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">2.70017957687378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56610512733459</t>
+    <t xml:space="preserve">2.56610536575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.51969480514526</t>
@@ -2810,40 +2810,40 @@
     <t xml:space="preserve">2.24896812438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15936994552612</t>
+    <t xml:space="preserve">2.1593701839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.17741870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646694660187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88993263244629</t>
+    <t xml:space="preserve">1.79646706581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88993239402771</t>
   </si>
   <si>
     <t xml:space="preserve">1.7661714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68817639350891</t>
+    <t xml:space="preserve">1.68817627429962</t>
   </si>
   <si>
     <t xml:space="preserve">1.6250067949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91313743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77261757850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83965444564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93827664852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94149959087372</t>
+    <t xml:space="preserve">1.91313719749451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77261734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83965456485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93827688694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94149935245514</t>
   </si>
   <si>
     <t xml:space="preserve">2.04141068458557</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">2.05236840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98662042617798</t>
+    <t xml:space="preserve">1.98662030696869</t>
   </si>
   <si>
     <t xml:space="preserve">2.11295986175537</t>
@@ -2876,28 +2876,28 @@
     <t xml:space="preserve">2.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0910439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278836250305</t>
+    <t xml:space="preserve">2.09104371070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278848171234</t>
   </si>
   <si>
     <t xml:space="preserve">1.92087244987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93892085552216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90282416343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8306303024292</t>
+    <t xml:space="preserve">1.93892109394073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90282380580902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83062994480133</t>
   </si>
   <si>
     <t xml:space="preserve">1.8976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89379990100861</t>
+    <t xml:space="preserve">1.89379978179932</t>
   </si>
   <si>
     <t xml:space="preserve">1.99693393707275</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">2.05623602867126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02658486366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02529573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04463338851929</t>
+    <t xml:space="preserve">2.0265851020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02529549598694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04463315010071</t>
   </si>
   <si>
     <t xml:space="preserve">2.04721188545227</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">2.01627159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0175609588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790967464447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97243964672089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32651400566101</t>
+    <t xml:space="preserve">2.01756072044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9724395275116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32651424407959</t>
   </si>
   <si>
     <t xml:space="preserve">2.22702956199646</t>
@@ -2945,31 +2945,31 @@
     <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17018151283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21992373466492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387808799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27535057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2654025554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31372356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24266290664673</t>
+    <t xml:space="preserve">2.17018127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2199239730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387761116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27535033226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26540231704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31372332572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24266266822815</t>
   </si>
   <si>
     <t xml:space="preserve">2.25687527656555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39046883583069</t>
+    <t xml:space="preserve">2.39046835899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.46863484382629</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61644005775452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56669783592224</t>
+    <t xml:space="preserve">2.63633704185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6164402961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56669807434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.48995280265808</t>
@@ -2996,31 +2996,31 @@
     <t xml:space="preserve">2.38336253166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38762593269348</t>
+    <t xml:space="preserve">2.38762617111206</t>
   </si>
   <si>
     <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44873809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47574090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.451580286026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44021034240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40325903892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4188928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42457723617554</t>
+    <t xml:space="preserve">2.44873785972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47574067115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45158004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44021081924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41889262199402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42457747459412</t>
   </si>
   <si>
     <t xml:space="preserve">2.48284673690796</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">2.53116774559021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55817055702209</t>
+    <t xml:space="preserve">2.55817079544067</t>
   </si>
   <si>
     <t xml:space="preserve">2.57238292694092</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">2.58090996742249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51127099990845</t>
+    <t xml:space="preserve">2.51127076148987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53685235977173</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">2.5652768611908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60933375358582</t>
+    <t xml:space="preserve">2.60933423042297</t>
   </si>
   <si>
     <t xml:space="preserve">2.64202189445496</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">2.65481305122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67755222320557</t>
+    <t xml:space="preserve">2.67755198478699</t>
   </si>
   <si>
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76424551010132</t>
+    <t xml:space="preserve">2.7642457485199</t>
   </si>
   <si>
     <t xml:space="preserve">2.64770698547363</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">2.6064920425415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4572651386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54680109024048</t>
+    <t xml:space="preserve">2.45726490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54680132865906</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186713218689</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">2.66049766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68465828895569</t>
+    <t xml:space="preserve">2.68465805053711</t>
   </si>
   <si>
     <t xml:space="preserve">2.7528760433197</t>
@@ -3110,34 +3110,34 @@
     <t xml:space="preserve">2.92768406867981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89641785621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92199921607971</t>
+    <t xml:space="preserve">2.89641809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92199945449829</t>
   </si>
   <si>
     <t xml:space="preserve">2.86373019218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83388447761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88931155204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8495180606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84099054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9177360534668</t>
+    <t xml:space="preserve">2.83388471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88931179046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84951829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099078178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91773581504822</t>
   </si>
   <si>
     <t xml:space="preserve">2.93479037284851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95895099639893</t>
+    <t xml:space="preserve">2.95895075798035</t>
   </si>
   <si>
     <t xml:space="preserve">2.94615983963013</t>
@@ -3146,25 +3146,25 @@
     <t xml:space="preserve">2.94900250434875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87083625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88789081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85378122329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81256651878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78556394577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90068101882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87794208526611</t>
+    <t xml:space="preserve">2.87083601951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88789057731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85378170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81256675720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78556370735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90068125724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87794232368469</t>
   </si>
   <si>
     <t xml:space="preserve">2.94189643859863</t>
@@ -3173,61 +3173,61 @@
     <t xml:space="preserve">2.95184469223022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9575297832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93621158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91489386558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85662388801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70313382148743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74861240386963</t>
+    <t xml:space="preserve">2.95753002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93621134757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91489362716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85662436485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70313358306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74861216545105</t>
   </si>
   <si>
     <t xml:space="preserve">2.6960277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70455479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72729420661926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66902470588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65054893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64912819862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.610755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68039417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62354612350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63065218925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61359786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56243419647217</t>
+    <t xml:space="preserve">2.70455503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6576554775238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72729444503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66902494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6505491733551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6491277217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61075568199158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68039464950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62354636192322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63065195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61359810829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56243443489075</t>
   </si>
   <si>
     <t xml:space="preserve">2.45868635177612</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">2.48568916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42741966247559</t>
+    <t xml:space="preserve">2.42741990089417</t>
   </si>
   <si>
     <t xml:space="preserve">2.39899563789368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37199282646179</t>
+    <t xml:space="preserve">2.37199258804321</t>
   </si>
   <si>
     <t xml:space="preserve">2.25403261184692</t>
@@ -3272,19 +3272,19 @@
     <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39473223686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56385588645935</t>
+    <t xml:space="preserve">2.3947319984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56385564804077</t>
   </si>
   <si>
     <t xml:space="preserve">2.52264070510864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52832555770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55532836914062</t>
+    <t xml:space="preserve">2.52832579612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55532813072205</t>
   </si>
   <si>
     <t xml:space="preserve">2.71450328826904</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">2.76850914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74008512496948</t>
+    <t xml:space="preserve">2.74008536338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.84383296966553</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">2.97174191474915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93052697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920853614807</t>
+    <t xml:space="preserve">2.93052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920877456665</t>
   </si>
   <si>
     <t xml:space="preserve">2.81967258453369</t>
@@ -3323,19 +3323,19 @@
     <t xml:space="preserve">2.78130006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78272128105164</t>
+    <t xml:space="preserve">2.78272151947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.77561521530151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70597624778748</t>
+    <t xml:space="preserve">2.7059760093689</t>
   </si>
   <si>
     <t xml:space="preserve">2.70739722251892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7130823135376</t>
+    <t xml:space="preserve">2.71308207511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.75998210906982</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">2.72871541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75429701805115</t>
+    <t xml:space="preserve">2.75429677963257</t>
   </si>
   <si>
     <t xml:space="preserve">2.75571823120117</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">2.77845788002014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75713968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83246350288391</t>
+    <t xml:space="preserve">2.7571394443512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83246326446533</t>
   </si>
   <si>
     <t xml:space="preserve">2.86088752746582</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">2.85946655273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91347217559814</t>
+    <t xml:space="preserve">2.91347241401672</t>
   </si>
   <si>
     <t xml:space="preserve">2.88646912574768</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">2.88362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8424117565155</t>
+    <t xml:space="preserve">2.84241199493408</t>
   </si>
   <si>
     <t xml:space="preserve">2.76993036270142</t>
@@ -3404,19 +3404,19 @@
     <t xml:space="preserve">2.745769739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64344334602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57522535324097</t>
+    <t xml:space="preserve">2.64344310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57522511482239</t>
   </si>
   <si>
     <t xml:space="preserve">2.64486408233643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80546045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8665726184845</t>
+    <t xml:space="preserve">2.80546069145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86657238006592</t>
   </si>
   <si>
     <t xml:space="preserve">2.94758105278015</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">3.13233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10533452033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18350124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1493923664093</t>
+    <t xml:space="preserve">3.10533475875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18350148200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14939260482788</t>
   </si>
   <si>
     <t xml:space="preserve">3.13944411277771</t>
@@ -3443,28 +3443,28 @@
     <t xml:space="preserve">3.12665319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03995966911316</t>
+    <t xml:space="preserve">3.03995943069458</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01153516769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03427457809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08259558677673</t>
+    <t xml:space="preserve">3.01153540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03427481651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08259582519531</t>
   </si>
   <si>
     <t xml:space="preserve">3.13375926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11812591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05843496322632</t>
+    <t xml:space="preserve">3.11812615394592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0584352016449</t>
   </si>
   <si>
     <t xml:space="preserve">3.19344973564148</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">3.16928911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21192526817322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2517192363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14797067642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30004048347473</t>
+    <t xml:space="preserve">3.2119255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25171899795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1479709148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30004024505615</t>
   </si>
   <si>
     <t xml:space="preserve">3.28867053985596</t>
@@ -3494,28 +3494,28 @@
     <t xml:space="preserve">3.30146145820618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32562208175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30572509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41942143440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36967921257019</t>
+    <t xml:space="preserve">3.32562232017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30572533607483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3526246547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41942119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36967968940735</t>
   </si>
   <si>
     <t xml:space="preserve">3.26450991630554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27587985992432</t>
+    <t xml:space="preserve">3.27587962150574</t>
   </si>
   <si>
     <t xml:space="preserve">3.30856776237488</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">3.38247036933899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40378856658936</t>
+    <t xml:space="preserve">3.40378832817078</t>
   </si>
   <si>
     <t xml:space="preserve">3.42013239860535</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">3.32846450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29790830612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272790908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35902070999146</t>
+    <t xml:space="preserve">3.29790854454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272814750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35902047157288</t>
   </si>
   <si>
     <t xml:space="preserve">3.36683702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34978270530701</t>
+    <t xml:space="preserve">3.34978246688843</t>
   </si>
   <si>
     <t xml:space="preserve">3.42723822593689</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">3.44500327110291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3220694065094</t>
+    <t xml:space="preserve">3.32206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">3.28014349937439</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">3.29719758033752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31567358970642</t>
+    <t xml:space="preserve">3.31567335128784</t>
   </si>
   <si>
     <t xml:space="preserve">3.33201742172241</t>
@@ -3578,10 +3578,10 @@
     <t xml:space="preserve">3.3043041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31780552864075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28440713882446</t>
+    <t xml:space="preserve">3.31780529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28440737724304</t>
   </si>
   <si>
     <t xml:space="preserve">3.23679661750793</t>
@@ -3590,16 +3590,16 @@
     <t xml:space="preserve">3.31212019920349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27232670783997</t>
+    <t xml:space="preserve">3.27232694625854</t>
   </si>
   <si>
     <t xml:space="preserve">3.31283116340637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42226386070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48550796508789</t>
+    <t xml:space="preserve">3.42226362228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48550772666931</t>
   </si>
   <si>
     <t xml:space="preserve">3.47555875778198</t>
@@ -3608,19 +3608,19 @@
     <t xml:space="preserve">3.4954559803009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48124432563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57575464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143925666809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53027558326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49829840660095</t>
+    <t xml:space="preserve">3.48124384880066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">3.52459049224854</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">3.46584796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47488474845886</t>
+    <t xml:space="preserve">3.47488498687744</t>
   </si>
   <si>
     <t xml:space="preserve">3.45831656455994</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">3.44626665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44099450111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41764831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38752341270447</t>
+    <t xml:space="preserve">3.44099473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41764855384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38752365112305</t>
   </si>
   <si>
     <t xml:space="preserve">3.36041116714478</t>
@@ -3683,25 +3683,25 @@
     <t xml:space="preserve">3.32501459121704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24744296073914</t>
+    <t xml:space="preserve">3.24744319915771</t>
   </si>
   <si>
     <t xml:space="preserve">3.27229642868042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23765254020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21129369735718</t>
+    <t xml:space="preserve">3.23765277862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
     <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21430659294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24970269203186</t>
+    <t xml:space="preserve">3.21430635452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24970293045044</t>
   </si>
   <si>
     <t xml:space="preserve">3.39279508590698</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">3.37698006629944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29865550994873</t>
+    <t xml:space="preserve">3.29865574836731</t>
   </si>
   <si>
     <t xml:space="preserve">3.2948899269104</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">3.30468058586121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31673002243042</t>
+    <t xml:space="preserve">3.316730260849</t>
   </si>
   <si>
     <t xml:space="preserve">3.33329916000366</t>
@@ -3734,19 +3734,19 @@
     <t xml:space="preserve">3.32953333854675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112386703491</t>
+    <t xml:space="preserve">3.29112410545349</t>
   </si>
   <si>
     <t xml:space="preserve">3.28208684921265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14878535270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19999694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32802700996399</t>
+    <t xml:space="preserve">3.14878511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19999718666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32802724838257</t>
   </si>
   <si>
     <t xml:space="preserve">3.33028650283813</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">3.37321424484253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42216682434082</t>
+    <t xml:space="preserve">3.4221670627594</t>
   </si>
   <si>
     <t xml:space="preserve">3.40710473060608</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">3.38149809837341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42141366004944</t>
+    <t xml:space="preserve">3.42141389846802</t>
   </si>
   <si>
     <t xml:space="preserve">3.37170791625977</t>
@@ -3779,145 +3779,145 @@
     <t xml:space="preserve">3.36643600463867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39204216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48994708061218</t>
+    <t xml:space="preserve">3.39204239845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48994731903076</t>
   </si>
   <si>
     <t xml:space="preserve">3.61797761917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60592770576477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647152900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6533739566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981795310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078045845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6383113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72040128707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67521452903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66542339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75052618980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010750770569</t>
+    <t xml:space="preserve">3.60592794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65337419509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63981819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63831162452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72040176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6752142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66542387008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7505259513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010726928711</t>
   </si>
   <si>
     <t xml:space="preserve">3.7746262550354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77312016487122</t>
+    <t xml:space="preserve">3.77311992645264</t>
   </si>
   <si>
     <t xml:space="preserve">3.79872560501099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77613234519958</t>
+    <t xml:space="preserve">3.77613258361816</t>
   </si>
   <si>
     <t xml:space="preserve">3.7821569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76709461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78667569160461</t>
+    <t xml:space="preserve">3.76709508895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78667593002319</t>
   </si>
   <si>
     <t xml:space="preserve">3.73696994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77763819694519</t>
+    <t xml:space="preserve">3.77763843536377</t>
   </si>
   <si>
     <t xml:space="preserve">3.71663570404053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71588253974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533919334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6375584602356</t>
+    <t xml:space="preserve">3.71588230133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7053394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63755822181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.68726444244385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994261741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72567319869995</t>
+    <t xml:space="preserve">3.6699423789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638661384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72567367553711</t>
   </si>
   <si>
     <t xml:space="preserve">3.67144870758057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58258080482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6413242816925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429224967957</t>
+    <t xml:space="preserve">3.58258104324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64132404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429201126099</t>
   </si>
   <si>
     <t xml:space="preserve">3.75203227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80926918983459</t>
+    <t xml:space="preserve">3.80926895141602</t>
   </si>
   <si>
     <t xml:space="preserve">3.7445011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80625653266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84541869163513</t>
+    <t xml:space="preserve">3.80625677108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84541845321655</t>
   </si>
   <si>
     <t xml:space="preserve">3.83939409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717458724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006281852722</t>
+    <t xml:space="preserve">3.90717506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006258010864</t>
   </si>
   <si>
     <t xml:space="preserve">3.95386791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97947430610657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95989298820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483065605164</t>
+    <t xml:space="preserve">3.97947359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483041763306</t>
   </si>
   <si>
     <t xml:space="preserve">3.89060592651367</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">3.88307523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92976808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95682597160339</t>
+    <t xml:space="preserve">3.92976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95682573318481</t>
   </si>
   <si>
     <t xml:space="preserve">3.99502515792847</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">4.01571702957153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96239686012268</t>
+    <t xml:space="preserve">3.96239709854126</t>
   </si>
   <si>
     <t xml:space="preserve">3.95125532150269</t>
@@ -3965,34 +3965,34 @@
     <t xml:space="preserve">4.0189003944397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97353839874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98706746101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9480721950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340111732483</t>
+    <t xml:space="preserve">3.97353863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807195663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340159416199</t>
   </si>
   <si>
     <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04277467727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98865914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93454313278198</t>
+    <t xml:space="preserve">4.04277515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98865842819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9345428943634</t>
   </si>
   <si>
     <t xml:space="preserve">3.97274279594421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90907645225525</t>
+    <t xml:space="preserve">3.90907692909241</t>
   </si>
   <si>
     <t xml:space="preserve">3.89952707290649</t>
@@ -4001,43 +4001,43 @@
     <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66078042984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66316747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73638391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72524213790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7005717754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76821637153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8477988243103</t>
+    <t xml:space="preserve">3.66078019142151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590069770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66316771507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73638343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72524189949036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70057153701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779858589172</t>
   </si>
   <si>
     <t xml:space="preserve">3.7721951007843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76264595985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74752473831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72922110557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73081254959106</t>
+    <t xml:space="preserve">3.76264548301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74752521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72922086715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73081278800964</t>
   </si>
   <si>
     <t xml:space="preserve">3.77856206893921</t>
@@ -4049,22 +4049,22 @@
     <t xml:space="preserve">3.64565992355347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74832081794739</t>
+    <t xml:space="preserve">3.74832057952881</t>
   </si>
   <si>
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77696990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8326780796051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641579627991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80323171615601</t>
+    <t xml:space="preserve">3.77697038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641508102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80323219299316</t>
   </si>
   <si>
     <t xml:space="preserve">3.85177755355835</t>
@@ -4079,82 +4079,82 @@
     <t xml:space="preserve">3.86212301254272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87008118629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554738998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97115015983582</t>
+    <t xml:space="preserve">3.87008142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146421432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97115063667297</t>
   </si>
   <si>
     <t xml:space="preserve">3.9639880657196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95443868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99980044364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91942238807678</t>
+    <t xml:space="preserve">3.95443844795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91942262649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.76344132423401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80402827262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90748524665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90430164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94409275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00775861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96796774864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85575604438782</t>
+    <t xml:space="preserve">3.80402851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90748476982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603060722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90430188179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9440929889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96796751022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85575652122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.82710719108582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03004121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01253318786621</t>
+    <t xml:space="preserve">4.03004169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01253366470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.00934982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99820923805237</t>
+    <t xml:space="preserve">3.99820899963379</t>
   </si>
   <si>
     <t xml:space="preserve">3.91623902320862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85814428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78094911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55414056777954</t>
+    <t xml:space="preserve">3.85814452171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78094935417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55414009094238</t>
   </si>
   <si>
     <t xml:space="preserve">3.69261312484741</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">3.34483909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06948494911194</t>
+    <t xml:space="preserve">3.06948471069336</t>
   </si>
   <si>
     <t xml:space="preserve">2.94374465942383</t>
@@ -4196,61 +4196,61 @@
     <t xml:space="preserve">3.73797512054443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69022607803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6838595867157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70852994918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354553222656</t>
+    <t xml:space="preserve">3.69022583961487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68385934829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70852971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74036240577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354529380798</t>
   </si>
   <si>
     <t xml:space="preserve">3.90111827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668964385986</t>
+    <t xml:space="preserve">3.90668892860413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9202184677124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97194671630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693017959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03481721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06346607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02845001220703</t>
+    <t xml:space="preserve">3.97194695472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319270133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693041801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03481674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06346654891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02844953536987</t>
   </si>
   <si>
     <t xml:space="preserve">4.11758136749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09848260879517</t>
+    <t xml:space="preserve">4.09848213195801</t>
   </si>
   <si>
     <t xml:space="preserve">4.12235689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1334981918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16055679321289</t>
+    <t xml:space="preserve">4.13349866867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16055631637573</t>
   </si>
   <si>
     <t xml:space="preserve">4.16214847564697</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">4.21467256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1971640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599063873291</t>
+    <t xml:space="preserve">4.19716453552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1541895866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599016189575</t>
   </si>
   <si>
     <t xml:space="preserve">4.13668155670166</t>
@@ -4283,82 +4283,82 @@
     <t xml:space="preserve">4.19398069381714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17488145828247</t>
+    <t xml:space="preserve">4.17488098144531</t>
   </si>
   <si>
     <t xml:space="preserve">4.12554025650024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0650577545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16373920440674</t>
+    <t xml:space="preserve">4.06505727767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1637396812439</t>
   </si>
   <si>
     <t xml:space="preserve">4.26719617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28470420837402</t>
+    <t xml:space="preserve">4.28470468521118</t>
   </si>
   <si>
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90509748458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00298357009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00139236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12431716918945</t>
+    <t xml:space="preserve">3.9050977230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00298404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00139188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12431621551514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24703931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28597164154053</t>
+    <t xml:space="preserve">4.23011159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24703884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28597116470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.25042390823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21487665176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14547491073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14124393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09723329544067</t>
+    <t xml:space="preserve">4.21487712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14547538757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14124345779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09723281860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.19202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20810651779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11754560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10738897323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77053737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383166313171</t>
+    <t xml:space="preserve">4.20810604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11754512786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10738945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77053785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383142471313</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4367,49 +4367,49 @@
     <t xml:space="preserve">3.82301211357117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69944310188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71213865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77307677268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122760772705</t>
+    <t xml:space="preserve">3.69944334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71213912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7730770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122736930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65881776809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80100703239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70198249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71467757225037</t>
+    <t xml:space="preserve">3.65881824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80100655555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70198225975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71467781066895</t>
   </si>
   <si>
     <t xml:space="preserve">3.71044588088989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66982054710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68082308769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69690418243408</t>
+    <t xml:space="preserve">3.66982078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68082332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69690442085266</t>
   </si>
   <si>
     <t xml:space="preserve">3.47177243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49123883247375</t>
+    <t xml:space="preserve">3.49123859405518</t>
   </si>
   <si>
     <t xml:space="preserve">3.6063437461853</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">3.62919569015503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53355693817139</t>
+    <t xml:space="preserve">3.53355669975281</t>
   </si>
   <si>
     <t xml:space="preserve">3.51324391365051</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">3.48700666427612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33381533622742</t>
+    <t xml:space="preserve">3.33381509780884</t>
   </si>
   <si>
     <t xml:space="preserve">3.38290429115295</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">3.40406322479248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44892024993896</t>
+    <t xml:space="preserve">3.44892048835754</t>
   </si>
   <si>
     <t xml:space="preserve">3.38713598251343</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">3.26356744766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25764274597168</t>
+    <t xml:space="preserve">3.25764298439026</t>
   </si>
   <si>
     <t xml:space="preserve">3.29657554626465</t>
@@ -4454,28 +4454,28 @@
     <t xml:space="preserve">3.24325489997864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2813413143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005258560181</t>
+    <t xml:space="preserve">3.28134107589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005282402039</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860770225525</t>
+    <t xml:space="preserve">3.46415495872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860794067383</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56741142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64358329772949</t>
+    <t xml:space="preserve">3.56741118431091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64358353614807</t>
   </si>
   <si>
     <t xml:space="preserve">3.66135716438293</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70790672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74176120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73922228813171</t>
+    <t xml:space="preserve">3.70790696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74176144599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73922252655029</t>
   </si>
   <si>
     <t xml:space="preserve">3.67659139633179</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5597939491272</t>
+    <t xml:space="preserve">3.55979371070862</t>
   </si>
   <si>
     <t xml:space="preserve">3.46838688850403</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">3.54625225067139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50224113464355</t>
+    <t xml:space="preserve">3.50224137306213</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709839820862</t>
+    <t xml:space="preserve">3.54709815979004</t>
   </si>
   <si>
     <t xml:space="preserve">3.6190390586853</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885582923889</t>
+    <t xml:space="preserve">3.49885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282888412476</t>
+    <t xml:space="preserve">3.70282864570618</t>
   </si>
   <si>
     <t xml:space="preserve">3.6791307926178</t>
@@ -4550,13 +4550,13 @@
     <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69351887702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7002899646759</t>
+    <t xml:space="preserve">3.69351863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706057548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70029020309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010649681091</t>
+    <t xml:space="preserve">3.58010625839233</t>
   </si>
   <si>
     <t xml:space="preserve">3.47515749931335</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">3.38459730148315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34735727310181</t>
+    <t xml:space="preserve">3.34735703468323</t>
   </si>
   <si>
     <t xml:space="preserve">3.3803653717041</t>
@@ -4592,19 +4592,19 @@
     <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38205814361572</t>
+    <t xml:space="preserve">3.38205790519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36766982078552</t>
+    <t xml:space="preserve">3.3676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">3.37613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3151957988739</t>
+    <t xml:space="preserve">3.31519556045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.42014408111572</t>
@@ -4616,16 +4616,16 @@
     <t xml:space="preserve">3.43114686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4531524181366</t>
+    <t xml:space="preserve">3.45315217971802</t>
   </si>
   <si>
     <t xml:space="preserve">3.50647330284119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48954582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471539497375</t>
+    <t xml:space="preserve">3.48954606056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471563339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4640,28 +4640,28 @@
     <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370210647583</t>
+    <t xml:space="preserve">3.7256805896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178828239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241337776184</t>
+    <t xml:space="preserve">3.85178852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241361618042</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366452217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06422472000122</t>
+    <t xml:space="preserve">3.97366428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06422519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.01259660720825</t>
@@ -4670,40 +4670,40 @@
     <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03037071228027</t>
+    <t xml:space="preserve">4.03037023544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.04052686691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04899024963379</t>
+    <t xml:space="preserve">4.04899072647095</t>
   </si>
   <si>
     <t xml:space="preserve">4.06845664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05576133728027</t>
+    <t xml:space="preserve">4.05576086044312</t>
   </si>
   <si>
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645109176636</t>
+    <t xml:space="preserve">4.04645156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391241073608</t>
+    <t xml:space="preserve">4.04391193389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08623075485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14209032058716</t>
+    <t xml:space="preserve">4.08623027801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14208984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
@@ -4712,64 +4712,64 @@
     <t xml:space="preserve">4.05322170257568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0083646774292</t>
+    <t xml:space="preserve">4.00836515426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.98635983467102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02359962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
+    <t xml:space="preserve">4.02360010147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990129470825</t>
   </si>
   <si>
     <t xml:space="preserve">4.01344299316406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96773958206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00667238235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95589065551758</t>
+    <t xml:space="preserve">3.96774005889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00667285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.955890417099</t>
   </si>
   <si>
     <t xml:space="preserve">3.84586381912231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86702251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88818192481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9609682559967</t>
+    <t xml:space="preserve">3.78831100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86702275276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88818144798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96096873283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.94150257110596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93219256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579916000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89325976371765</t>
+    <t xml:space="preserve">3.93219232559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272616386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579939842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865110397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85771298408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89326000213623</t>
   </si>
   <si>
     <t xml:space="preserve">3.96435451507568</t>
@@ -4778,22 +4778,22 @@
     <t xml:space="preserve">4.03544855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97958898544312</t>
+    <t xml:space="preserve">3.97958922386169</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01682901382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99482297897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974537849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9973623752594</t>
+    <t xml:space="preserve">4.0168285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99482321739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.02529239654541</t>
@@ -4805,25 +4805,25 @@
     <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05660820007324</t>
+    <t xml:space="preserve">4.05660772323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.08792304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12685585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10992860794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638690948486</t>
+    <t xml:space="preserve">4.12685537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638643264771</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19117879867554</t>
+    <t xml:space="preserve">4.1911792755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.13362646102905</t>
@@ -4832,13 +4832,13 @@
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732479095459</t>
+    <t xml:space="preserve">4.15732431411743</t>
   </si>
   <si>
     <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18271541595459</t>
+    <t xml:space="preserve">4.18271493911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4853,22 +4853,22 @@
     <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21233797073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17679071426392</t>
+    <t xml:space="preserve">4.2123384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17679119110107</t>
   </si>
   <si>
     <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863964080811</t>
+    <t xml:space="preserve">4.18864011764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17933034896851</t>
+    <t xml:space="preserve">4.17932987213135</t>
   </si>
   <si>
     <t xml:space="preserve">4.23349714279175</t>
@@ -4883,31 +4883,31 @@
     <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33506059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29443502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28427839279175</t>
+    <t xml:space="preserve">4.33506011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29443454742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28427886962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09215450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8509418964386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784230232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85263466835022</t>
+    <t xml:space="preserve">4.09215497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85094213485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8780255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8526349067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
@@ -4922,13 +4922,13 @@
     <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93811702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05491495132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06676340103149</t>
+    <t xml:space="preserve">3.93811726570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0549144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06676435470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4937,10 +4937,10 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29274272918701</t>
+    <t xml:space="preserve">4.28766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29274225234985</t>
   </si>
   <si>
     <t xml:space="preserve">4.32321119308472</t>
@@ -4952,46 +4952,46 @@
     <t xml:space="preserve">4.30289888381958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25888776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30459117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28258562088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33336734771729</t>
+    <t xml:space="preserve">4.25888824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3045916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28258609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33336782455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.31305503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23857545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32828950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938402175903</t>
+    <t xml:space="preserve">4.23857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32828903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938354492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.37907075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34013795852661</t>
+    <t xml:space="preserve">4.34013843536377</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183120727539</t>
+    <t xml:space="preserve">4.34183168411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36722135543823</t>
+    <t xml:space="preserve">4.36722183227539</t>
   </si>
   <si>
     <t xml:space="preserve">4.37269258499146</t>
@@ -6576,6 +6576,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.2999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949996948242</t>
   </si>
 </sst>
 </file>
@@ -71758,7 +71761,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494907407</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1371615</v>
@@ -71779,6 +71782,32 @@
         <v>2187</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6494097222</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>2265897</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>18.8899993896484</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>18.3099994659424</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>18.3799991607666</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>18.6949996948242</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2188</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="2194">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,31 +44,31 @@
     <t xml:space="preserve">UNI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50193166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40895128250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35658264160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31490087509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29780149459839</t>
+    <t xml:space="preserve">2.50193190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40895080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3565821647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31490159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29780173301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.37261343002319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37795758247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33413863182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2347457408905</t>
+    <t xml:space="preserve">2.37795734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33413887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23474526405334</t>
   </si>
   <si>
     <t xml:space="preserve">2.15458989143372</t>
@@ -89,73 +89,73 @@
     <t xml:space="preserve">2.0348904132843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03168416023254</t>
+    <t xml:space="preserve">2.03168392181396</t>
   </si>
   <si>
     <t xml:space="preserve">2.02954649925232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90343487262726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00924062728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93549692630768</t>
+    <t xml:space="preserve">1.9034343957901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00924015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93549716472626</t>
   </si>
   <si>
     <t xml:space="preserve">1.8403787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74953532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701665878296</t>
+    <t xml:space="preserve">1.74953544139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701689720154</t>
   </si>
   <si>
     <t xml:space="preserve">1.67792963981628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349858760834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5315113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861699104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823016166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60632371902466</t>
+    <t xml:space="preserve">1.59349870681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151118755341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6886168718338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55822992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60632336139679</t>
   </si>
   <si>
     <t xml:space="preserve">1.72922933101654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67899811267853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312317371368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350381851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69396078586578</t>
+    <t xml:space="preserve">1.67899823188782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350441455841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69396090507507</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419152736664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7057169675827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296684741974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533560752869</t>
+    <t xml:space="preserve">1.70571684837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71533524990082</t>
   </si>
   <si>
     <t xml:space="preserve">1.82541608810425</t>
@@ -164,46 +164,46 @@
     <t xml:space="preserve">1.8232786655426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88099098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381587505341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488482475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86602866649628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404126644135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556646823883</t>
+    <t xml:space="preserve">1.88099110126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381563663483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488458633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86602830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404114723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556670665741</t>
   </si>
   <si>
     <t xml:space="preserve">1.82648503780365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79976642131805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92053484916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229115009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221518516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435332298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183430194855</t>
+    <t xml:space="preserve">1.79976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92053461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442845344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9322909116745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221554279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435356140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183454036713</t>
   </si>
   <si>
     <t xml:space="preserve">1.95580303668976</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">1.95259702205658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92374086380005</t>
+    <t xml:space="preserve">1.92374110221863</t>
   </si>
   <si>
     <t xml:space="preserve">1.87564730644226</t>
@@ -221,67 +221,67 @@
     <t xml:space="preserve">1.8831285238266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91198456287384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9002286195755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89167809486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579756736755</t>
+    <t xml:space="preserve">1.91198468208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90022838115692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89167881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579744815826</t>
   </si>
   <si>
     <t xml:space="preserve">1.81793510913849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80190372467041</t>
+    <t xml:space="preserve">1.80190420150757</t>
   </si>
   <si>
     <t xml:space="preserve">1.87992227077484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90129733085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465348720551</t>
+    <t xml:space="preserve">1.90129709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465312957764</t>
   </si>
   <si>
     <t xml:space="preserve">1.9258781671524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92801594734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91519069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01779079437256</t>
+    <t xml:space="preserve">1.92801570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91519117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0177903175354</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626511573792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07443404197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0616090297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07015895843506</t>
+    <t xml:space="preserve">2.07443380355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06160879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07015919685364</t>
   </si>
   <si>
     <t xml:space="preserve">2.02634024620056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05519652366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05092167854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99855315685272</t>
+    <t xml:space="preserve">2.05519604682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05092120170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855279922485</t>
   </si>
   <si>
     <t xml:space="preserve">1.99214053153992</t>
@@ -290,67 +290,67 @@
     <t xml:space="preserve">1.95045924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93977165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8499972820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79121625423431</t>
+    <t xml:space="preserve">1.93977200984955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84999763965607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457835674286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121649265289</t>
   </si>
   <si>
     <t xml:space="preserve">1.73884797096252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388529777527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502937793732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678544044495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70785450935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87773144245148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87546873092651</t>
+    <t xml:space="preserve">1.72388577461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69502949714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678567886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70785439014435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235282421112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700931072235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87773108482361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87546896934509</t>
   </si>
   <si>
     <t xml:space="preserve">1.91279733181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90601027011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8845180273056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081188678741</t>
+    <t xml:space="preserve">1.90601050853729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451814651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081224441528</t>
   </si>
   <si>
     <t xml:space="preserve">1.80986142158508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81438589096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80646812915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75104105472565</t>
+    <t xml:space="preserve">1.81438612937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80646824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75104129314423</t>
   </si>
   <si>
     <t xml:space="preserve">1.63113760948181</t>
@@ -359,91 +359,91 @@
     <t xml:space="preserve">1.54290699958801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46711921691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47390604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42526602745056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51689004898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190795898438</t>
+    <t xml:space="preserve">1.46711897850037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47390592098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42526590824127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51689016819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190783977509</t>
   </si>
   <si>
     <t xml:space="preserve">1.60059607028961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57684195041656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69900727272034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38341307640076</t>
+    <t xml:space="preserve">1.57684206962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69900739192963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38341295719147</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2725590467453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21373844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19111490249634</t>
+    <t xml:space="preserve">1.27255892753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21373820304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19111514091492</t>
   </si>
   <si>
     <t xml:space="preserve">1.23636174201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18545949459076</t>
+    <t xml:space="preserve">1.18545913696289</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021277427673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09949088096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722852706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2374929189682</t>
+    <t xml:space="preserve">1.0994907617569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722864627838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23749279975891</t>
   </si>
   <si>
     <t xml:space="preserve">1.28726410865784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36870777606964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33477258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3935934305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38454401493073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038061141968</t>
+    <t xml:space="preserve">1.36870789527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3347727060318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39359331130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38454413414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40038025379181</t>
   </si>
   <si>
     <t xml:space="preserve">1.36983907222748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39811778068542</t>
+    <t xml:space="preserve">1.39811789989471</t>
   </si>
   <si>
     <t xml:space="preserve">1.37888824939728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37096989154816</t>
+    <t xml:space="preserve">1.37097012996674</t>
   </si>
   <si>
     <t xml:space="preserve">1.37775719165802</t>
@@ -452,34 +452,34 @@
     <t xml:space="preserve">1.42979061603546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4026426076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38567507266998</t>
+    <t xml:space="preserve">1.40264272689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38567519187927</t>
   </si>
   <si>
     <t xml:space="preserve">1.26011610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29631340503693</t>
+    <t xml:space="preserve">1.29631328582764</t>
   </si>
   <si>
     <t xml:space="preserve">1.32233011722565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37549471855164</t>
+    <t xml:space="preserve">1.37549483776093</t>
   </si>
   <si>
     <t xml:space="preserve">1.43657767772675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45354509353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44788932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4705126285553</t>
+    <t xml:space="preserve">1.45354497432709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44788920879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47051250934601</t>
   </si>
   <si>
     <t xml:space="preserve">1.45015144348145</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">1.41961014270782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38001918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39698684215546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33137929439545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33251059055328</t>
+    <t xml:space="preserve">1.38001930713654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39698672294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33137953281403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33251047134399</t>
   </si>
   <si>
     <t xml:space="preserve">1.38228166103363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36757671833038</t>
+    <t xml:space="preserve">1.3675764799118</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816623687744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3540027141571</t>
+    <t xml:space="preserve">1.35400259494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.32798600196838</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">1.41056072711945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40377402305603</t>
+    <t xml:space="preserve">1.40377414226532</t>
   </si>
   <si>
     <t xml:space="preserve">1.42413473129272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43883979320526</t>
+    <t xml:space="preserve">1.43883967399597</t>
   </si>
   <si>
     <t xml:space="preserve">1.45920085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.477299451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48747992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48974251747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019989967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40716755390167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36078953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282296180725</t>
+    <t xml:space="preserve">1.47729933261871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48747980594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4897426366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39019978046417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40716731548309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3607896566391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282308101654</t>
   </si>
   <si>
     <t xml:space="preserve">1.35513377189636</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">1.30536270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27821469306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780540943146</t>
+    <t xml:space="preserve">1.27821493148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780529022217</t>
   </si>
   <si>
     <t xml:space="preserve">1.2861328125</t>
@@ -581,97 +581,97 @@
     <t xml:space="preserve">1.35174024105072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35852742195129</t>
+    <t xml:space="preserve">1.358527302742</t>
   </si>
   <si>
     <t xml:space="preserve">1.37210142612457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39472448825836</t>
+    <t xml:space="preserve">1.39472472667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.41621649265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44110226631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49313592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52480852603912</t>
+    <t xml:space="preserve">1.44110238552094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49313580989838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52480840682983</t>
   </si>
   <si>
     <t xml:space="preserve">1.53159534931183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51575911045074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54856264591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56553018093109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61077654361725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63453114032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59833407402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571077346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118594646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50444746017456</t>
+    <t xml:space="preserve">1.51575899124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54856276512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56553030014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61077678203583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63453102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59833371639252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571089267731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118618488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50444757938385</t>
   </si>
   <si>
     <t xml:space="preserve">1.51802146434784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4750372171402</t>
+    <t xml:space="preserve">1.47503745555878</t>
   </si>
   <si>
     <t xml:space="preserve">1.65715444087982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69335174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733539104462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167902946472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63905596733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57457935810089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6266131401062</t>
+    <t xml:space="preserve">1.69335162639618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167914867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63905572891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172736644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57457947731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62661290168762</t>
   </si>
   <si>
     <t xml:space="preserve">1.58476006984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56100571155548</t>
+    <t xml:space="preserve">1.5610054731369</t>
   </si>
   <si>
     <t xml:space="preserve">1.54064452648163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6051207780838</t>
+    <t xml:space="preserve">1.60512113571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.64923632144928</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">1.72049963474274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79741871356964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284566879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492802619934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022260665894</t>
+    <t xml:space="preserve">1.79741847515106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284578800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492754936218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022248744965</t>
   </si>
   <si>
     <t xml:space="preserve">1.86302626132965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85623919963837</t>
+    <t xml:space="preserve">1.85623908042908</t>
   </si>
   <si>
     <t xml:space="preserve">1.9105349779129</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">1.89922344684601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91166639328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92637157440186</t>
+    <t xml:space="preserve">1.91166615486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92637133598328</t>
   </si>
   <si>
     <t xml:space="preserve">1.94560122489929</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">1.94447004795074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89696145057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655169010162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98066735267639</t>
+    <t xml:space="preserve">1.8969612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365519285202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066759109497</t>
   </si>
   <si>
     <t xml:space="preserve">2.01347088813782</t>
@@ -737,28 +737,28 @@
     <t xml:space="preserve">2.00781512260437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01573348045349</t>
+    <t xml:space="preserve">2.01573324203491</t>
   </si>
   <si>
     <t xml:space="preserve">2.01912713050842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96483111381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99876570701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0202579498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727382183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007747650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97161781787872</t>
+    <t xml:space="preserve">1.96483135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99876594543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02025818824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727370262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007723808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97161817550659</t>
   </si>
   <si>
     <t xml:space="preserve">1.9478634595871</t>
@@ -776,94 +776,94 @@
     <t xml:space="preserve">2.08247184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08699679374695</t>
+    <t xml:space="preserve">2.08699655532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.05079913139343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05193066596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542087078094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96709311008453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894618034363</t>
+    <t xml:space="preserve">2.05193018913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542075157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202722072601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96709334850311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894641876221</t>
   </si>
   <si>
     <t xml:space="preserve">1.90940392017365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89130532741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320709228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999355792999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510838031769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596229076385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03609418869019</t>
+    <t xml:space="preserve">1.89130508899689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87320649623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999331951141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510790348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96596252918243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03609395027161</t>
   </si>
   <si>
     <t xml:space="preserve">1.99424123764038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00215911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00329041481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478241920471</t>
+    <t xml:space="preserve">2.00215935707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00329065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478194236755</t>
   </si>
   <si>
     <t xml:space="preserve">2.01799559593201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00442171096802</t>
+    <t xml:space="preserve">2.00442147254944</t>
   </si>
   <si>
     <t xml:space="preserve">1.95465075969696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02930784225464</t>
+    <t xml:space="preserve">2.02930736541748</t>
   </si>
   <si>
     <t xml:space="preserve">2.02817606925964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09265232086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13224339485168</t>
+    <t xml:space="preserve">2.09265184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13224315643311</t>
   </si>
   <si>
     <t xml:space="preserve">2.12432527542114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12093138694763</t>
+    <t xml:space="preserve">2.12093114852905</t>
   </si>
   <si>
     <t xml:space="preserve">2.15939092636108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15373516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016127586365</t>
+    <t xml:space="preserve">2.15373563766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016151428223</t>
   </si>
   <si>
     <t xml:space="preserve">2.1084885597229</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14921045303345</t>
+    <t xml:space="preserve">2.14921021461487</t>
   </si>
   <si>
     <t xml:space="preserve">2.19332599639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1786208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23291659355164</t>
+    <t xml:space="preserve">2.17862105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23291635513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.1955885887146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20803070068359</t>
+    <t xml:space="preserve">2.20803117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.20576882362366</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">2.19219470024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15826010704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20011305809021</t>
+    <t xml:space="preserve">2.15825963020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20011281967163</t>
   </si>
   <si>
     <t xml:space="preserve">2.17522740364075</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">2.07907843589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08812737464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11188173294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10962009429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.222736120224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26232695579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26006484031677</t>
+    <t xml:space="preserve">2.08812785148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11188220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10961961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22273635864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26232719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26006460189819</t>
   </si>
   <si>
     <t xml:space="preserve">2.2578022480011</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">2.31436038017273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33132839202881</t>
+    <t xml:space="preserve">2.33132815361023</t>
   </si>
   <si>
     <t xml:space="preserve">2.34716415405273</t>
@@ -974,85 +974,85 @@
     <t xml:space="preserve">2.39127945899963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3256721496582</t>
+    <t xml:space="preserve">2.32567238807678</t>
   </si>
   <si>
     <t xml:space="preserve">2.38675475120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36300015449524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33585238456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25893354415894</t>
+    <t xml:space="preserve">2.36300039291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33585262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25893330574036</t>
   </si>
   <si>
     <t xml:space="preserve">2.24988412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27137613296509</t>
+    <t xml:space="preserve">2.27137589454651</t>
   </si>
   <si>
     <t xml:space="preserve">2.33769369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30216646194458</t>
+    <t xml:space="preserve">2.30216670036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.36137866973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35072064399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30808758735657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453261375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926951408386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558477401733</t>
+    <t xml:space="preserve">2.35072040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30808782577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453237533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558453559875</t>
   </si>
   <si>
     <t xml:space="preserve">2.2109797000885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18137359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1458466053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13637256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.109135389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14110970497131</t>
+    <t xml:space="preserve">2.18137383460999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14584636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13637280464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10913491249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14110946655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.14229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16361021995544</t>
+    <t xml:space="preserve">2.16361045837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.18611073493958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13874101638794</t>
+    <t xml:space="preserve">2.13874077796936</t>
   </si>
   <si>
     <t xml:space="preserve">2.11979293823242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14939880371094</t>
+    <t xml:space="preserve">2.1493992805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.13755679130554</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15532040596008</t>
+    <t xml:space="preserve">2.15532064437866</t>
   </si>
   <si>
     <t xml:space="preserve">2.20032167434692</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">2.2382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27374482154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453768730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3838791847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34835171699524</t>
+    <t xml:space="preserve">2.2737443447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38387894630432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34835195541382</t>
   </si>
   <si>
     <t xml:space="preserve">2.36848402023315</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">2.37322115898132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36966848373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37203669548035</t>
+    <t xml:space="preserve">2.36966824531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37203693389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.38032650947571</t>
@@ -1106,37 +1106,37 @@
     <t xml:space="preserve">2.34361505508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30927228927612</t>
+    <t xml:space="preserve">2.30927181243896</t>
   </si>
   <si>
     <t xml:space="preserve">2.28913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2938768863678</t>
+    <t xml:space="preserve">2.29387664794922</t>
   </si>
   <si>
     <t xml:space="preserve">2.33058834075928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34953594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36019420623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31637763977051</t>
+    <t xml:space="preserve">2.34953641891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36019444465637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31637740135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.34479928016663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31756138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34006261825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40401148796082</t>
+    <t xml:space="preserve">2.31756186485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34006237983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40401124954224</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099326133728</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">2.31045651435852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25953388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27966618537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2559814453125</t>
+    <t xml:space="preserve">2.25953364372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27966570854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25598120689392</t>
   </si>
   <si>
     <t xml:space="preserve">2.23111200332642</t>
@@ -1169,40 +1169,40 @@
     <t xml:space="preserve">2.19676899909973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19321608543396</t>
+    <t xml:space="preserve">2.19321632385254</t>
   </si>
   <si>
     <t xml:space="preserve">2.18847942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18492650985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163566589355</t>
+    <t xml:space="preserve">2.18492674827576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163590431213</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15058374404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16834735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13045167922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12097787857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11031937599182</t>
+    <t xml:space="preserve">2.15058350563049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16834712028503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13045144081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12097764015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11031889915466</t>
   </si>
   <si>
     <t xml:space="preserve">2.08426570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22400689125061</t>
+    <t xml:space="preserve">2.22400665283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.24295473098755</t>
@@ -1211,49 +1211,49 @@
     <t xml:space="preserve">2.29624533653259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28795576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25006008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25834965705872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24413871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22755932807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22637510299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2370331287384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24769139289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2926926612854</t>
+    <t xml:space="preserve">2.28795528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25005960464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24413847923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2275595664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22637534141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23703336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24769163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29269242286682</t>
   </si>
   <si>
     <t xml:space="preserve">2.3211145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25716543197632</t>
+    <t xml:space="preserve">2.25716519355774</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137637138367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30453491210938</t>
+    <t xml:space="preserve">2.30453515052795</t>
   </si>
   <si>
     <t xml:space="preserve">2.29742980003357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124430656433</t>
+    <t xml:space="preserve">2.25124454498291</t>
   </si>
   <si>
     <t xml:space="preserve">2.31874585151672</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">2.27848172187805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26663947105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28321886062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32703590393066</t>
+    <t xml:space="preserve">2.2666392326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28321838378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32703566551208</t>
   </si>
   <si>
     <t xml:space="preserve">2.34598350524902</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">2.27729725837708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20742702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203186035156</t>
+    <t xml:space="preserve">2.20742726325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203209877014</t>
   </si>
   <si>
     <t xml:space="preserve">2.1482150554657</t>
@@ -1292,22 +1292,22 @@
     <t xml:space="preserve">2.19795322418213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979571342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19913792610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23348021507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23584914207458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28085017204285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26900792121887</t>
+    <t xml:space="preserve">2.2097954750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19913768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23348045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23584890365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28085041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26900744438171</t>
   </si>
   <si>
     <t xml:space="preserve">2.27256059646606</t>
@@ -1322,28 +1322,28 @@
     <t xml:space="preserve">2.27019214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26308655738831</t>
+    <t xml:space="preserve">2.26308631896973</t>
   </si>
   <si>
     <t xml:space="preserve">2.28677153587341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29032397270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3009819984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3317723274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3282196521759</t>
+    <t xml:space="preserve">2.29032421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30098223686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33177256584167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.31519317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39098453521729</t>
+    <t xml:space="preserve">2.39098477363586</t>
   </si>
   <si>
     <t xml:space="preserve">2.41585373878479</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">2.57572627067566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56862092018127</t>
+    <t xml:space="preserve">2.5686206817627</t>
   </si>
   <si>
     <t xml:space="preserve">2.57691097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56980538368225</t>
+    <t xml:space="preserve">2.56980514526367</t>
   </si>
   <si>
     <t xml:space="preserve">2.56625270843506</t>
@@ -1388,28 +1388,28 @@
     <t xml:space="preserve">2.63967561721802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6574387550354</t>
+    <t xml:space="preserve">2.65743899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.66691303253174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63671469688416</t>
+    <t xml:space="preserve">2.63671493530273</t>
   </si>
   <si>
     <t xml:space="preserve">2.62960934638977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5810558795929</t>
+    <t xml:space="preserve">2.58105564117432</t>
   </si>
   <si>
     <t xml:space="preserve">2.57158136367798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56921362876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48039531707764</t>
+    <t xml:space="preserve">2.56921339035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48039507865906</t>
   </si>
   <si>
     <t xml:space="preserve">2.53013300895691</t>
@@ -1418,40 +1418,40 @@
     <t xml:space="preserve">2.45611810684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48217153549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44605207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4069721698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236709594727</t>
+    <t xml:space="preserve">2.48217129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44605183601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40697193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236733436584</t>
   </si>
   <si>
     <t xml:space="preserve">2.4709210395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45552587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723582267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46559190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.473881483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41881442070007</t>
+    <t xml:space="preserve">2.45552611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723629951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4655921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47388172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41881418228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.40934014320374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43480157852173</t>
+    <t xml:space="preserve">2.43480134010315</t>
   </si>
   <si>
     <t xml:space="preserve">2.40756392478943</t>
@@ -1460,19 +1460,19 @@
     <t xml:space="preserve">2.3264434337616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33473300933838</t>
+    <t xml:space="preserve">2.33473324775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.35190486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39631366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37440514564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35782623291016</t>
+    <t xml:space="preserve">2.39631342887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37440538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35782599449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.42591977119446</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">2.36611557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38624787330627</t>
+    <t xml:space="preserve">2.3862476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.39986658096313</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">2.32881212234497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3524968624115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302306175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499737739563</t>
+    <t xml:space="preserve">2.35249710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302282333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499761581421</t>
   </si>
   <si>
     <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39809036254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38565587997437</t>
+    <t xml:space="preserve">2.39809012413025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38565540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.4123010635376</t>
@@ -1517,16 +1517,16 @@
     <t xml:space="preserve">2.45078921318054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51769828796387</t>
+    <t xml:space="preserve">2.51769852638245</t>
   </si>
   <si>
     <t xml:space="preserve">2.51355361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54315972328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54079103469849</t>
+    <t xml:space="preserve">2.54315996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54079127311707</t>
   </si>
   <si>
     <t xml:space="preserve">2.54375195503235</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">2.58756899833679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61066174507141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58223986625671</t>
+    <t xml:space="preserve">2.61066150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58223962783813</t>
   </si>
   <si>
     <t xml:space="preserve">2.59408211708069</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">2.65803122520447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64204430580139</t>
+    <t xml:space="preserve">2.64204406738281</t>
   </si>
   <si>
     <t xml:space="preserve">2.67165040969849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67520308494568</t>
+    <t xml:space="preserve">2.6752028465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.58638453483582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60177946090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55855488777161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57039761543274</t>
+    <t xml:space="preserve">2.60177993774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55855464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57039737701416</t>
   </si>
   <si>
     <t xml:space="preserve">2.59349012374878</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51059293746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54967308044434</t>
+    <t xml:space="preserve">2.5105926990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54967355728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.48868465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49672627449036</t>
+    <t xml:space="preserve">2.49672651290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.4862105846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43548345565796</t>
+    <t xml:space="preserve">2.43548369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.40888333320618</t>
@@ -1613,40 +1613,40 @@
     <t xml:space="preserve">2.31176090240479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25361108779907</t>
+    <t xml:space="preserve">2.25361132621765</t>
   </si>
   <si>
     <t xml:space="preserve">2.33464980125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28577947616577</t>
+    <t xml:space="preserve">2.28577923774719</t>
   </si>
   <si>
     <t xml:space="preserve">2.23752737045288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22577381134033</t>
+    <t xml:space="preserve">2.22577357292175</t>
   </si>
   <si>
     <t xml:space="preserve">2.23567175865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16020035743713</t>
+    <t xml:space="preserve">2.16020059585571</t>
   </si>
   <si>
     <t xml:space="preserve">2.24989986419678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2319598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23938298225403</t>
+    <t xml:space="preserve">2.23195934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23938322067261</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20041036605835</t>
+    <t xml:space="preserve">2.20041060447693</t>
   </si>
   <si>
     <t xml:space="preserve">2.20968961715698</t>
@@ -1664,31 +1664,31 @@
     <t xml:space="preserve">2.19298720359802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05812907218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0587477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379891395569</t>
+    <t xml:space="preserve">2.05812883377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05874800682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379867553711</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843570709229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04699420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04946875572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0921528339386</t>
+    <t xml:space="preserve">2.04699397087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04946851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09215307235718</t>
   </si>
   <si>
     <t xml:space="preserve">2.11689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10143232345581</t>
+    <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
     <t xml:space="preserve">2.14102339744568</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.12679529190063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14349770545959</t>
+    <t xml:space="preserve">2.14349794387817</t>
   </si>
   <si>
     <t xml:space="preserve">2.13793063163757</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">2.12122797966003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09957671165466</t>
+    <t xml:space="preserve">2.09957647323608</t>
   </si>
   <si>
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473509788513</t>
+    <t xml:space="preserve">2.14473533630371</t>
   </si>
   <si>
     <t xml:space="preserve">2.18061494827271</t>
@@ -1739,28 +1739,28 @@
     <t xml:space="preserve">2.20102906227112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09029746055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432074546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916754722595</t>
+    <t xml:space="preserve">2.09029722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1243212223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699963569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916730880737</t>
   </si>
   <si>
     <t xml:space="preserve">2.1199905872345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07730627059937</t>
+    <t xml:space="preserve">2.07730603218079</t>
   </si>
   <si>
     <t xml:space="preserve">2.07235741615295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11937189102173</t>
+    <t xml:space="preserve">2.11937165260315</t>
   </si>
   <si>
     <t xml:space="preserve">2.20474052429199</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">2.23319697380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19175004959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24309468269348</t>
+    <t xml:space="preserve">2.19174981117249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24309492111206</t>
   </si>
   <si>
     <t xml:space="preserve">2.26289033889771</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">2.25299263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26969504356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711868286133</t>
+    <t xml:space="preserve">2.26969528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711844444275</t>
   </si>
   <si>
     <t xml:space="preserve">2.25608563423157</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.2418577671051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19917273521423</t>
+    <t xml:space="preserve">2.19917297363281</t>
   </si>
   <si>
     <t xml:space="preserve">2.2220618724823</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">2.27526259422302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32846331596375</t>
+    <t xml:space="preserve">2.32846355438232</t>
   </si>
   <si>
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3142352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991047859192</t>
+    <t xml:space="preserve">2.31423544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3699107170105</t>
   </si>
   <si>
     <t xml:space="preserve">2.33712410926819</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">2.33836126327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33403086662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36001324653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40146040916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4163064956665</t>
+    <t xml:space="preserve">2.3340311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36001300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40145993232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41630625724792</t>
   </si>
   <si>
     <t xml:space="preserve">2.41445112228394</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">2.42063736915588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45589828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44352555274963</t>
+    <t xml:space="preserve">2.45589780807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44352579116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.47012639045715</t>
@@ -1853,22 +1853,22 @@
     <t xml:space="preserve">2.48682880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50600576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37300395965576</t>
+    <t xml:space="preserve">2.50600600242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37300372123718</t>
   </si>
   <si>
     <t xml:space="preserve">2.36743640899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30743074417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795233726501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36496162414551</t>
+    <t xml:space="preserve">2.30743050575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36496186256409</t>
   </si>
   <si>
     <t xml:space="preserve">2.2709321975708</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">2.2808301448822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19793605804443</t>
+    <t xml:space="preserve">2.19793581962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.19855451583862</t>
@@ -1895,25 +1895,25 @@
     <t xml:space="preserve">2.19979190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16824245452881</t>
+    <t xml:space="preserve">2.16824269294739</t>
   </si>
   <si>
     <t xml:space="preserve">2.15648889541626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0977201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1397864818573</t>
+    <t xml:space="preserve">2.09772038459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13978624343872</t>
   </si>
   <si>
     <t xml:space="preserve">2.12184643745422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19669914245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17381000518799</t>
+    <t xml:space="preserve">2.19669890403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380976676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.21525716781616</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">2.24433207511902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24742531776428</t>
+    <t xml:space="preserve">2.2474250793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.25979733467102</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.26598381996155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26227164268494</t>
+    <t xml:space="preserve">2.26227188110352</t>
   </si>
   <si>
     <t xml:space="preserve">2.28825354576111</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">2.22701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2041220664978</t>
+    <t xml:space="preserve">2.20412230491638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15834450721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13731169700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443388938904</t>
+    <t xml:space="preserve">2.1373119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23443412780762</t>
   </si>
   <si>
     <t xml:space="preserve">2.22639226913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28949069976807</t>
+    <t xml:space="preserve">2.28949093818665</t>
   </si>
   <si>
     <t xml:space="preserve">2.24680662155151</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15401458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18556332588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21278262138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19607996940613</t>
+    <t xml:space="preserve">2.15401434898376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18556356430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21278238296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19608020782471</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504173278809</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1762843132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14040470123291</t>
+    <t xml:space="preserve">2.17628455162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14040493965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.27959299087524</t>
@@ -2009,28 +2009,28 @@
     <t xml:space="preserve">2.3241331577301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31794691085815</t>
+    <t xml:space="preserve">2.31794714927673</t>
   </si>
   <si>
     <t xml:space="preserve">2.35073351860046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38846921920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41012048721313</t>
+    <t xml:space="preserve">2.38846898078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41012072563171</t>
   </si>
   <si>
     <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32227730751038</t>
+    <t xml:space="preserve">2.32227754592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41259527206421</t>
+    <t xml:space="preserve">2.41259503364563</t>
   </si>
   <si>
     <t xml:space="preserve">2.43424654006958</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">2.44971179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45342326164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930877685547</t>
+    <t xml:space="preserve">2.45342350006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930853843689</t>
   </si>
   <si>
     <t xml:space="preserve">2.5511646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53260636329651</t>
+    <t xml:space="preserve">2.53260612487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.47321915626526</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">2.47136306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50043821334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51528477668762</t>
+    <t xml:space="preserve">2.50043797492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5152850151062</t>
   </si>
   <si>
     <t xml:space="preserve">2.52394556999207</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">2.46208429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32908248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36125016212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42620468139648</t>
+    <t xml:space="preserve">2.32908225059509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36124992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42620491981506</t>
   </si>
   <si>
     <t xml:space="preserve">2.44105124473572</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">2.37609672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45713520050049</t>
+    <t xml:space="preserve">2.45713496208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.45094919204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47507500648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46579551696777</t>
+    <t xml:space="preserve">2.47507476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46579599380493</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49054050445557</t>
+    <t xml:space="preserve">2.49054026603699</t>
   </si>
   <si>
     <t xml:space="preserve">2.48187971115112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47878670692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49548935890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50662446022034</t>
+    <t xml:space="preserve">2.47878694534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4954891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50662422180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.5288941860199</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">2.50786185264587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5530207157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58147668838501</t>
+    <t xml:space="preserve">2.55302023887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601119041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58147644996643</t>
   </si>
   <si>
     <t xml:space="preserve">2.64952421188354</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">2.68292903900146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69901323318481</t>
+    <t xml:space="preserve">2.69901299476624</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220900535583</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">2.68231105804443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.668701171875</t>
+    <t xml:space="preserve">2.66870141029358</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179417610168</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">2.86109042167664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85057330131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79799151420593</t>
+    <t xml:space="preserve">2.85057353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79799175262451</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716280937195</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.78500080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78994989395142</t>
+    <t xml:space="preserve">2.78994965553284</t>
   </si>
   <si>
     <t xml:space="preserve">2.82088041305542</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">2.79737281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81160116195679</t>
+    <t xml:space="preserve">2.81160092353821</t>
   </si>
   <si>
     <t xml:space="preserve">2.78685665130615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79922914505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80603337287903</t>
+    <t xml:space="preserve">2.79922890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80603384971619</t>
   </si>
   <si>
     <t xml:space="preserve">2.81778717041016</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">2.74417209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65694761276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014266967773</t>
+    <t xml:space="preserve">2.65694785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014290809631</t>
   </si>
   <si>
     <t xml:space="preserve">2.59137463569641</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">2.66560816764832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73056268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79984736442566</t>
+    <t xml:space="preserve">2.73056244850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79984760284424</t>
   </si>
   <si>
     <t xml:space="preserve">2.76334953308105</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">2.66279363632202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63443112373352</t>
+    <t xml:space="preserve">2.6344313621521</t>
   </si>
   <si>
     <t xml:space="preserve">2.68664336204529</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">2.65183568000793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68857717514038</t>
+    <t xml:space="preserve">2.66472697257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6885769367218</t>
   </si>
   <si>
     <t xml:space="preserve">2.69437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68986630439758</t>
+    <t xml:space="preserve">2.689866065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72016167640686</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">2.69695663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65247988700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953489303589</t>
+    <t xml:space="preserve">2.65247964859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953513145447</t>
   </si>
   <si>
     <t xml:space="preserve">2.75303602218628</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">2.73563170433044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176455497742</t>
+    <t xml:space="preserve">2.73176431655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.76206016540527</t>
@@ -2333,40 +2333,40 @@
     <t xml:space="preserve">2.7588369846344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79428935050964</t>
+    <t xml:space="preserve">2.79428958892822</t>
   </si>
   <si>
     <t xml:space="preserve">2.76077079772949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79944610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82007312774658</t>
+    <t xml:space="preserve">2.79944586753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.820072889328</t>
   </si>
   <si>
     <t xml:space="preserve">2.86197113990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91160464286804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90773677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89162254333496</t>
+    <t xml:space="preserve">2.91160440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90773701667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89162230491638</t>
   </si>
   <si>
     <t xml:space="preserve">2.89484524726868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95414710044861</t>
+    <t xml:space="preserve">2.95414733886719</t>
   </si>
   <si>
     <t xml:space="preserve">2.97477412223816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96832847595215</t>
+    <t xml:space="preserve">2.96832823753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.97541880607605</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">2.97735238075256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91805028915405</t>
+    <t xml:space="preserve">2.91805005073547</t>
   </si>
   <si>
     <t xml:space="preserve">3.04181122779846</t>
@@ -2390,31 +2390,31 @@
     <t xml:space="preserve">3.02118420600891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03665447235107</t>
+    <t xml:space="preserve">3.0366542339325</t>
   </si>
   <si>
     <t xml:space="preserve">3.03923320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04825711250305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155165672302</t>
+    <t xml:space="preserve">3.04825735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829243659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155141830444</t>
   </si>
   <si>
     <t xml:space="preserve">2.98895502090454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90902614593506</t>
+    <t xml:space="preserve">2.90902638435364</t>
   </si>
   <si>
     <t xml:space="preserve">2.86003756523132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84263372421265</t>
+    <t xml:space="preserve">2.84263348579407</t>
   </si>
   <si>
     <t xml:space="preserve">2.78655457496643</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">2.76592755317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83812141418457</t>
+    <t xml:space="preserve">2.83812117576599</t>
   </si>
   <si>
     <t xml:space="preserve">2.7343430519104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78010892868042</t>
+    <t xml:space="preserve">2.78010869026184</t>
   </si>
   <si>
     <t xml:space="preserve">2.84843468666077</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">2.87421822547913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95608115196228</t>
+    <t xml:space="preserve">2.95608139038086</t>
   </si>
   <si>
     <t xml:space="preserve">2.94770121574402</t>
@@ -2447,16 +2447,16 @@
     <t xml:space="preserve">2.91869473457336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91676139831543</t>
+    <t xml:space="preserve">2.91676115989685</t>
   </si>
   <si>
     <t xml:space="preserve">2.94705677032471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91031503677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96510553359985</t>
+    <t xml:space="preserve">2.91031527519226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96510529518127</t>
   </si>
   <si>
     <t xml:space="preserve">2.94576787948608</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">2.9547917842865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801472663879</t>
+    <t xml:space="preserve">2.95801496505737</t>
   </si>
   <si>
     <t xml:space="preserve">2.98959970474243</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">3.05921506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11013722419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10884809494019</t>
+    <t xml:space="preserve">3.11013746261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10884833335876</t>
   </si>
   <si>
     <t xml:space="preserve">3.080486536026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11464977264404</t>
+    <t xml:space="preserve">3.11464953422546</t>
   </si>
   <si>
     <t xml:space="preserve">3.10240268707275</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">3.10175776481628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12431836128235</t>
+    <t xml:space="preserve">3.12431859970093</t>
   </si>
   <si>
     <t xml:space="preserve">3.14945769309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592100143433</t>
+    <t xml:space="preserve">3.13592076301575</t>
   </si>
   <si>
     <t xml:space="preserve">3.07661890983582</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">3.05663681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02698588371277</t>
+    <t xml:space="preserve">3.02698612213135</t>
   </si>
   <si>
     <t xml:space="preserve">3.07275152206421</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">3.08757710456848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12560796737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19071078300476</t>
+    <t xml:space="preserve">3.12560820579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19071102142334</t>
   </si>
   <si>
     <t xml:space="preserve">3.15396952629089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15010213851929</t>
+    <t xml:space="preserve">3.15010237693787</t>
   </si>
   <si>
     <t xml:space="preserve">3.17781972885132</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">3.22165179252625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21262717247009</t>
+    <t xml:space="preserve">3.21262693405151</t>
   </si>
   <si>
     <t xml:space="preserve">3.23325395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25001311302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21391677856445</t>
+    <t xml:space="preserve">3.25001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21391654014587</t>
   </si>
   <si>
     <t xml:space="preserve">3.23970007896423</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">3.25388050079346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28739953041077</t>
+    <t xml:space="preserve">3.28739929199219</t>
   </si>
   <si>
     <t xml:space="preserve">3.31447243690491</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">3.35185837745667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39955759048462</t>
+    <t xml:space="preserve">3.3995578289032</t>
   </si>
   <si>
     <t xml:space="preserve">3.4111602306366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43307638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49108934402466</t>
+    <t xml:space="preserve">3.43307662010193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49108958244324</t>
   </si>
   <si>
     <t xml:space="preserve">3.47304081916809</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">3.43823289871216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45370316505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600323677063</t>
+    <t xml:space="preserve">3.45370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311194419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600347518921</t>
   </si>
   <si>
     <t xml:space="preserve">3.41631698608398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41502785682678</t>
+    <t xml:space="preserve">3.4150276184082</t>
   </si>
   <si>
     <t xml:space="preserve">3.413738489151</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">3.44596815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40987133979797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920875549316</t>
+    <t xml:space="preserve">3.40987110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920851707458</t>
   </si>
   <si>
     <t xml:space="preserve">3.34541249275208</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">3.3879554271698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3479905128479</t>
+    <t xml:space="preserve">3.34799075126648</t>
   </si>
   <si>
     <t xml:space="preserve">3.29126691818237</t>
@@ -2660,22 +2660,22 @@
     <t xml:space="preserve">3.2719292640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32865309715271</t>
+    <t xml:space="preserve">3.32865333557129</t>
   </si>
   <si>
     <t xml:space="preserve">3.36861753463745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43049764633179</t>
+    <t xml:space="preserve">3.43049788475037</t>
   </si>
   <si>
     <t xml:space="preserve">3.43694353103638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42405200004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42147374153137</t>
+    <t xml:space="preserve">3.42405223846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42147350311279</t>
   </si>
   <si>
     <t xml:space="preserve">3.4781973361969</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">3.4549925327301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513430595398</t>
+    <t xml:space="preserve">3.37635278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513454437256</t>
   </si>
   <si>
     <t xml:space="preserve">3.35572552680969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26032662391663</t>
+    <t xml:space="preserve">3.26032638549805</t>
   </si>
   <si>
     <t xml:space="preserve">3.22938656806946</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">3.30544781684875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33252048492432</t>
+    <t xml:space="preserve">3.33252024650574</t>
   </si>
   <si>
     <t xml:space="preserve">3.31576108932495</t>
@@ -2723,46 +2723,46 @@
     <t xml:space="preserve">3.16815042495728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17395186424255</t>
+    <t xml:space="preserve">3.17395210266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205361366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09982442855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12238478660583</t>
+    <t xml:space="preserve">3.09982466697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12238454818726</t>
   </si>
   <si>
     <t xml:space="preserve">3.04890155792236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11593890190125</t>
+    <t xml:space="preserve">3.11593866348267</t>
   </si>
   <si>
     <t xml:space="preserve">3.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02182912826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96703910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00958204269409</t>
+    <t xml:space="preserve">3.02182936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96703886985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00958180427551</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310059547424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09466767311096</t>
+    <t xml:space="preserve">3.09466743469238</t>
   </si>
   <si>
     <t xml:space="preserve">3.07017350196838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848159790039</t>
+    <t xml:space="preserve">3.15848183631897</t>
   </si>
   <si>
     <t xml:space="preserve">3.18297624588013</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">3.4008469581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854640960693</t>
+    <t xml:space="preserve">3.44854664802551</t>
   </si>
   <si>
     <t xml:space="preserve">3.54394555091858</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">3.39440107345581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17459654808044</t>
+    <t xml:space="preserve">3.17459678649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.14236688613892</t>
@@ -2819,34 +2819,34 @@
     <t xml:space="preserve">1.79646682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88993215560913</t>
+    <t xml:space="preserve">1.88993239402771</t>
   </si>
   <si>
     <t xml:space="preserve">1.76617133617401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68817615509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500655651093</t>
+    <t xml:space="preserve">1.68817639350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62500667572021</t>
   </si>
   <si>
     <t xml:space="preserve">1.91313743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77261710166931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83965456485748</t>
+    <t xml:space="preserve">1.7726172208786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8396543264389</t>
   </si>
   <si>
     <t xml:space="preserve">1.93827605247498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94149935245514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04141068458557</t>
+    <t xml:space="preserve">1.94149959087372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04141044616699</t>
   </si>
   <si>
     <t xml:space="preserve">1.9066915512085</t>
@@ -2855,28 +2855,28 @@
     <t xml:space="preserve">1.94923436641693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02013921737671</t>
+    <t xml:space="preserve">2.02013897895813</t>
   </si>
   <si>
     <t xml:space="preserve">2.0523681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98662042617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11295986175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12327337265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912779808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04850101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09104347229004</t>
+    <t xml:space="preserve">1.98662066459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11296010017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12327313423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04850077629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09104371070862</t>
   </si>
   <si>
     <t xml:space="preserve">1.94278848171234</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">1.92087244987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93892085552216</t>
+    <t xml:space="preserve">1.93892109394073</t>
   </si>
   <si>
     <t xml:space="preserve">1.9028240442276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83063018321991</t>
+    <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">1.89766716957092</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">1.89379978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99693417549133</t>
+    <t xml:space="preserve">1.99693393707275</t>
   </si>
   <si>
     <t xml:space="preserve">2.06010365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05623602867126</t>
+    <t xml:space="preserve">2.05623579025269</t>
   </si>
   <si>
     <t xml:space="preserve">2.02658486366272</t>
@@ -2918,10 +2918,10 @@
     <t xml:space="preserve">2.04463338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04721188545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05752539634705</t>
+    <t xml:space="preserve">2.04721212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05752515792847</t>
   </si>
   <si>
     <t xml:space="preserve">2.01627159118652</t>
@@ -2942,10 +2942,10 @@
     <t xml:space="preserve">2.22702980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21850252151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17018127441406</t>
+    <t xml:space="preserve">2.21850275993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17018151283264</t>
   </si>
   <si>
     <t xml:space="preserve">2.21992373466492</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">2.28387784957886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27535080909729</t>
+    <t xml:space="preserve">2.27535057067871</t>
   </si>
   <si>
     <t xml:space="preserve">2.26540207862854</t>
@@ -2975,22 +2975,22 @@
     <t xml:space="preserve">2.46863460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52406167984009</t>
+    <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.63633704185486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61644005775452</t>
+    <t xml:space="preserve">2.6164402961731</t>
   </si>
   <si>
     <t xml:space="preserve">2.56669783592224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48995280265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37909865379333</t>
+    <t xml:space="preserve">2.48995304107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37909889221191</t>
   </si>
   <si>
     <t xml:space="preserve">2.38336229324341</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">2.38762617111206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4700562953949</t>
+    <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
     <t xml:space="preserve">2.44873809814453</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">2.47574067115784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.451580286026</t>
+    <t xml:space="preserve">2.45158052444458</t>
   </si>
   <si>
     <t xml:space="preserve">2.44021058082581</t>
@@ -3041,19 +3041,19 @@
     <t xml:space="preserve">2.55817055702209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57238245010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58090996742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51127099990845</t>
+    <t xml:space="preserve">2.57238268852234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58090972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51127076148987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53685259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5652768611908</t>
+    <t xml:space="preserve">2.56527662277222</t>
   </si>
   <si>
     <t xml:space="preserve">2.60933399200439</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">2.65481281280518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67755198478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65907669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76424551010132</t>
+    <t xml:space="preserve">2.67755222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65907645225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7642457485199</t>
   </si>
   <si>
     <t xml:space="preserve">2.64770674705505</t>
@@ -3083,19 +3083,19 @@
     <t xml:space="preserve">2.61501908302307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60649156570435</t>
+    <t xml:space="preserve">2.60649180412292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4572651386261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54680132865906</t>
+    <t xml:space="preserve">2.54680109024048</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186713218689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66049742698669</t>
+    <t xml:space="preserve">2.66049718856812</t>
   </si>
   <si>
     <t xml:space="preserve">2.68465805053711</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">2.7528760433197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89073276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768430709839</t>
+    <t xml:space="preserve">2.89073300361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768406867981</t>
   </si>
   <si>
     <t xml:space="preserve">2.89641785621643</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">2.86373019218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83388495445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88931202888489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84951829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84099054336548</t>
+    <t xml:space="preserve">2.83388471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88931179046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8495180606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099078178406</t>
   </si>
   <si>
     <t xml:space="preserve">2.91773581504822</t>
@@ -3140,25 +3140,25 @@
     <t xml:space="preserve">2.95895075798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94616007804871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94900274276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87083578109741</t>
+    <t xml:space="preserve">2.94615983963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94900250434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87083601951599</t>
   </si>
   <si>
     <t xml:space="preserve">2.88789081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85378170013428</t>
+    <t xml:space="preserve">2.8537814617157</t>
   </si>
   <si>
     <t xml:space="preserve">2.81256651878357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78556394577026</t>
+    <t xml:space="preserve">2.78556370735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.90068125724792</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">2.87794232368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94189643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9518449306488</t>
+    <t xml:space="preserve">2.94189620018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95184469223022</t>
   </si>
   <si>
     <t xml:space="preserve">2.9575297832489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93621158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91489362716675</t>
+    <t xml:space="preserve">2.93621134757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91489386558533</t>
   </si>
   <si>
     <t xml:space="preserve">2.85662412643433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70313382148743</t>
+    <t xml:space="preserve">2.70313358306885</t>
   </si>
   <si>
     <t xml:space="preserve">2.74861240386963</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">2.69602751731873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70455503463745</t>
+    <t xml:space="preserve">2.70455479621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.65765523910522</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">2.66902494430542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6505491733551</t>
+    <t xml:space="preserve">2.65054893493652</t>
   </si>
   <si>
     <t xml:space="preserve">2.64912796020508</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">2.68039464950562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62354636192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63065218925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61359786987305</t>
+    <t xml:space="preserve">2.62354612350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63065195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61359810829163</t>
   </si>
   <si>
     <t xml:space="preserve">2.56243443489075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45868635177612</t>
+    <t xml:space="preserve">2.4586865901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.5027437210083</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">2.42741966247559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39899563789368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199282646179</t>
+    <t xml:space="preserve">2.3989953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199306488037</t>
   </si>
   <si>
     <t xml:space="preserve">2.25403261184692</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">2.37057137489319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39473176002502</t>
+    <t xml:space="preserve">2.3947319984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.56385564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52264046669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52832555770874</t>
+    <t xml:space="preserve">2.52264070510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52832579612732</t>
   </si>
   <si>
     <t xml:space="preserve">2.55532813072205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71450328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76850938796997</t>
+    <t xml:space="preserve">2.71450304985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76850914955139</t>
   </si>
   <si>
     <t xml:space="preserve">2.74008512496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84383296966553</t>
+    <t xml:space="preserve">2.84383320808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.83672738075256</t>
@@ -3305,22 +3305,22 @@
     <t xml:space="preserve">2.97174191474915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93052697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920853614807</t>
+    <t xml:space="preserve">2.93052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920877456665</t>
   </si>
   <si>
     <t xml:space="preserve">2.81967258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8097243309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78840613365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78129982948303</t>
+    <t xml:space="preserve">2.80972409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78840589523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78130006790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.78272128105164</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">2.77561497688293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70597648620605</t>
+    <t xml:space="preserve">2.70597624778748</t>
   </si>
   <si>
     <t xml:space="preserve">2.70739722251892</t>
@@ -3347,31 +3347,31 @@
     <t xml:space="preserve">2.72871541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75429725646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75571823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79266977310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77419424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77845764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75713968276978</t>
+    <t xml:space="preserve">2.75429701805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75571846961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79266953468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77419400215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77845740318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75713992118835</t>
   </si>
   <si>
     <t xml:space="preserve">2.83246350288391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86088728904724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946679115295</t>
+    <t xml:space="preserve">2.86088752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85946655273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.91347241401672</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">2.88646912574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88362717628479</t>
+    <t xml:space="preserve">2.88362693786621</t>
   </si>
   <si>
     <t xml:space="preserve">2.8424117565155</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">2.7471911907196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79551196098328</t>
+    <t xml:space="preserve">2.79551219940186</t>
   </si>
   <si>
     <t xml:space="preserve">2.67897319793701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68181538581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.745769739151</t>
+    <t xml:space="preserve">2.68181562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74576997756958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64344310760498</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">2.57522535324097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.644864320755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546045303345</t>
+    <t xml:space="preserve">2.64486408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546069145203</t>
   </si>
   <si>
     <t xml:space="preserve">2.86657238006592</t>
@@ -3422,22 +3422,22 @@
     <t xml:space="preserve">2.94758081436157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13233780860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10533499717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18350124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1493923664093</t>
+    <t xml:space="preserve">3.13233804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10533475875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18350148200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14939260482788</t>
   </si>
   <si>
     <t xml:space="preserve">3.13944411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15791964530945</t>
+    <t xml:space="preserve">3.15791940689087</t>
   </si>
   <si>
     <t xml:space="preserve">3.12665319442749</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">3.03995943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742676734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01153540611267</t>
+    <t xml:space="preserve">2.97742652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01153516769409</t>
   </si>
   <si>
     <t xml:space="preserve">3.03427481651306</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">3.13375902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11812591552734</t>
+    <t xml:space="preserve">3.11812615394592</t>
   </si>
   <si>
     <t xml:space="preserve">3.05843544006348</t>
@@ -3470,16 +3470,16 @@
     <t xml:space="preserve">3.19344973564148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16928935050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21192526817322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25171947479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479709148407</t>
+    <t xml:space="preserve">3.16928911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2119255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2517192363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14797115325928</t>
   </si>
   <si>
     <t xml:space="preserve">3.30004048347473</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">3.28867053985596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29435515403748</t>
+    <t xml:space="preserve">3.29435539245605</t>
   </si>
   <si>
     <t xml:space="preserve">3.3014612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32562184333801</t>
+    <t xml:space="preserve">3.32562208175659</t>
   </si>
   <si>
     <t xml:space="preserve">3.30572509765625</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">3.37110066413879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41942119598389</t>
+    <t xml:space="preserve">3.41942095756531</t>
   </si>
   <si>
     <t xml:space="preserve">3.36967968940735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26451015472412</t>
+    <t xml:space="preserve">3.26450991630554</t>
   </si>
   <si>
     <t xml:space="preserve">3.27587962150574</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">3.40378832817078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42013239860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32846450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29790854454041</t>
+    <t xml:space="preserve">3.42013263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32846474647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29790878295898</t>
   </si>
   <si>
     <t xml:space="preserve">3.33272838592529</t>
@@ -3548,25 +3548,25 @@
     <t xml:space="preserve">3.35902047157288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36683678627014</t>
+    <t xml:space="preserve">3.36683702468872</t>
   </si>
   <si>
     <t xml:space="preserve">3.34978270530701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42723870277405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500303268433</t>
+    <t xml:space="preserve">3.42723846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500327110291</t>
   </si>
   <si>
     <t xml:space="preserve">3.32206916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28014326095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2971978187561</t>
+    <t xml:space="preserve">3.28014349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29719758033752</t>
   </si>
   <si>
     <t xml:space="preserve">3.31567335128784</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28440737724304</t>
+    <t xml:space="preserve">3.28440761566162</t>
   </si>
   <si>
     <t xml:space="preserve">3.23679637908936</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">3.31212043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27232670783997</t>
+    <t xml:space="preserve">3.27232694625854</t>
   </si>
   <si>
     <t xml:space="preserve">3.31283092498779</t>
@@ -3608,40 +3608,40 @@
     <t xml:space="preserve">3.49545621871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48124384880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57575368881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143925666809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53027558326721</t>
+    <t xml:space="preserve">3.48124408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57575392723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143901824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53027534484863</t>
   </si>
   <si>
     <t xml:space="preserve">3.49829864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52459096908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61421155929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52383756637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38902950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43120455741882</t>
+    <t xml:space="preserve">3.52459073066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61421132087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52383732795715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38902974128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43120431900024</t>
   </si>
   <si>
     <t xml:space="preserve">3.41614174842834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44927906990051</t>
+    <t xml:space="preserve">3.44927883148193</t>
   </si>
   <si>
     <t xml:space="preserve">3.48919415473938</t>
@@ -3653,19 +3653,19 @@
     <t xml:space="preserve">3.47488474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831632614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46132922172546</t>
+    <t xml:space="preserve">3.45831656455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844170570374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46132946014404</t>
   </si>
   <si>
     <t xml:space="preserve">3.45078492164612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44626688957214</t>
+    <t xml:space="preserve">3.44626665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.44099450111389</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">3.24744319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27229642868042</t>
+    <t xml:space="preserve">3.27229619026184</t>
   </si>
   <si>
     <t xml:space="preserve">3.23765277862549</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">3.24970316886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39279508590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062050819397</t>
+    <t xml:space="preserve">3.39279532432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062026977539</t>
   </si>
   <si>
     <t xml:space="preserve">3.37698006629944</t>
@@ -3722,19 +3722,19 @@
     <t xml:space="preserve">3.21731877326965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30468034744263</t>
+    <t xml:space="preserve">3.30468058586121</t>
   </si>
   <si>
     <t xml:space="preserve">3.31673002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33329916000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32953310012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29112434387207</t>
+    <t xml:space="preserve">3.33329939842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32953333854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29112410545349</t>
   </si>
   <si>
     <t xml:space="preserve">3.28208684921265</t>
@@ -3749,37 +3749,37 @@
     <t xml:space="preserve">3.32802700996399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33028626441956</t>
+    <t xml:space="preserve">3.33028650283813</t>
   </si>
   <si>
     <t xml:space="preserve">3.33480501174927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38601684570312</t>
+    <t xml:space="preserve">3.3860170841217</t>
   </si>
   <si>
     <t xml:space="preserve">3.37321400642395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42216658592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4071044921875</t>
+    <t xml:space="preserve">3.42216682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40710473060608</t>
   </si>
   <si>
     <t xml:space="preserve">3.38149833679199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4214141368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37170815467834</t>
+    <t xml:space="preserve">3.42141389846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37170791625977</t>
   </si>
   <si>
     <t xml:space="preserve">3.36643600463867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39204216003418</t>
+    <t xml:space="preserve">3.39204239845276</t>
   </si>
   <si>
     <t xml:space="preserve">3.48994708061218</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">3.60592770576477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61647129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65337371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981795310974</t>
+    <t xml:space="preserve">3.6164710521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6533739566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63981819152832</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078045845032</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">3.72040152549744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6752142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66542410850525</t>
+    <t xml:space="preserve">3.67521405220032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66542363166809</t>
   </si>
   <si>
     <t xml:space="preserve">3.7505259513855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77010703086853</t>
+    <t xml:space="preserve">3.77010750770569</t>
   </si>
   <si>
     <t xml:space="preserve">3.7746262550354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77311968803406</t>
+    <t xml:space="preserve">3.77312016487122</t>
   </si>
   <si>
     <t xml:space="preserve">3.79872560501099</t>
@@ -3836,16 +3836,16 @@
     <t xml:space="preserve">3.78215742111206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76709461212158</t>
+    <t xml:space="preserve">3.76709508895874</t>
   </si>
   <si>
     <t xml:space="preserve">3.78667545318604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73696970939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77763772010803</t>
+    <t xml:space="preserve">3.73696994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77763819694519</t>
   </si>
   <si>
     <t xml:space="preserve">3.71663570404053</t>
@@ -3854,40 +3854,40 @@
     <t xml:space="preserve">3.71588277816772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7053394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6375584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68726396560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699423789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638613700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72567319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67144918441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258080482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80926942825317</t>
+    <t xml:space="preserve">3.70533919334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63755893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68726420402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638661384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72567343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67144870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258104324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6413242816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429177284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80926895141602</t>
   </si>
   <si>
     <t xml:space="preserve">3.74450135231018</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">3.80625677108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84541916847229</t>
+    <t xml:space="preserve">3.84541869163513</t>
   </si>
   <si>
     <t xml:space="preserve">3.83939409255981</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">3.90717506408691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88006210327148</t>
+    <t xml:space="preserve">3.88006234169006</t>
   </si>
   <si>
     <t xml:space="preserve">3.9538676738739</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">3.95989274978638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94483089447021</t>
+    <t xml:space="preserve">3.94483041763306</t>
   </si>
   <si>
     <t xml:space="preserve">3.89060568809509</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">3.88307499885559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92976808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95682597160339</t>
+    <t xml:space="preserve">3.92976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95682621002197</t>
   </si>
   <si>
     <t xml:space="preserve">3.99502563476562</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">3.95125532150269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025058746338</t>
+    <t xml:space="preserve">3.99025011062622</t>
   </si>
   <si>
     <t xml:space="preserve">3.97910904884338</t>
@@ -3956,13 +3956,13 @@
     <t xml:space="preserve">3.95523428916931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00457572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98070025444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01889991760254</t>
+    <t xml:space="preserve">4.00457525253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98070073127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0189003944397</t>
   </si>
   <si>
     <t xml:space="preserve">3.9735381603241</t>
@@ -3977,13 +3977,13 @@
     <t xml:space="preserve">3.92340135574341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98229193687439</t>
+    <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
     <t xml:space="preserve">4.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98865914344788</t>
+    <t xml:space="preserve">3.9886589050293</t>
   </si>
   <si>
     <t xml:space="preserve">3.93454313278198</t>
@@ -4001,19 +4001,19 @@
     <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66078042984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590045928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66316771507263</t>
+    <t xml:space="preserve">3.66078019142151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590093612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66316795349121</t>
   </si>
   <si>
     <t xml:space="preserve">3.73638367652893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72524213790894</t>
+    <t xml:space="preserve">3.72524189949036</t>
   </si>
   <si>
     <t xml:space="preserve">3.70057153701782</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">3.76821637153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84779858589172</t>
+    <t xml:space="preserve">3.84779810905457</t>
   </si>
   <si>
     <t xml:space="preserve">3.7721951007843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76264548301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74752521514893</t>
+    <t xml:space="preserve">3.76264595985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74752497673035</t>
   </si>
   <si>
     <t xml:space="preserve">3.72922086715698</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">3.74513721466064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64565992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74832057952881</t>
+    <t xml:space="preserve">3.64565944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74832081794739</t>
   </si>
   <si>
     <t xml:space="preserve">3.75150418281555</t>
@@ -4058,10 +4058,10 @@
     <t xml:space="preserve">3.77697062492371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8326780796051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641555786133</t>
+    <t xml:space="preserve">3.83267760276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641603469849</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">3.93613481521606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86212348937988</t>
+    <t xml:space="preserve">3.86212301254272</t>
   </si>
   <si>
     <t xml:space="preserve">3.87008142471313</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">3.95443844795227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99980020523071</t>
+    <t xml:space="preserve">3.99980068206787</t>
   </si>
   <si>
     <t xml:space="preserve">3.91942238807678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76344132423401</t>
+    <t xml:space="preserve">3.76344180107117</t>
   </si>
   <si>
     <t xml:space="preserve">3.80402851104736</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">3.90430188179016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94409227371216</t>
+    <t xml:space="preserve">3.94409275054932</t>
   </si>
   <si>
     <t xml:space="preserve">4.00775861740112</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">3.96796774864197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8557562828064</t>
+    <t xml:space="preserve">3.85575675964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.82710766792297</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">3.69261336326599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60746002197266</t>
+    <t xml:space="preserve">3.60746026039124</t>
   </si>
   <si>
     <t xml:space="preserve">3.42760467529297</t>
@@ -4196,16 +4196,16 @@
     <t xml:space="preserve">3.73797488212585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69022607803345</t>
+    <t xml:space="preserve">3.69022583961487</t>
   </si>
   <si>
     <t xml:space="preserve">3.6838595867157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70852971076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74036240577698</t>
+    <t xml:space="preserve">3.70852947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7403621673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.74354553222656</t>
@@ -4214,10 +4214,10 @@
     <t xml:space="preserve">3.901118516922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668892860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92021870613098</t>
+    <t xml:space="preserve">3.90668940544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92021822929382</t>
   </si>
   <si>
     <t xml:space="preserve">3.97194695472717</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">4.0348162651062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06346654891968</t>
+    <t xml:space="preserve">4.06346607208252</t>
   </si>
   <si>
     <t xml:space="preserve">4.02844953536987</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">4.09848213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12235689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13349866867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16055631637573</t>
+    <t xml:space="preserve">4.12235736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1334981918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16055679321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.16214799880981</t>
@@ -4271,37 +4271,37 @@
     <t xml:space="preserve">4.11599063873291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13668155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14623212814331</t>
+    <t xml:space="preserve">4.13668203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14623165130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19398069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17488098144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12553977966309</t>
+    <t xml:space="preserve">4.1939811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17488145828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12554025650024</t>
   </si>
   <si>
     <t xml:space="preserve">4.0650577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1637396812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26719617843628</t>
+    <t xml:space="preserve">4.16373920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26719665527344</t>
   </si>
   <si>
     <t xml:space="preserve">4.28470420837402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93135929107666</t>
+    <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
     <t xml:space="preserve">3.9050977230072</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">4.00139188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12431669235229</t>
+    <t xml:space="preserve">4.12431716918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24703884124756</t>
+    <t xml:space="preserve">4.23011112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24703931808472</t>
   </si>
   <si>
     <t xml:space="preserve">4.28597164154053</t>
@@ -4334,25 +4334,25 @@
     <t xml:space="preserve">4.21487665176392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14547538757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14124345779419</t>
+    <t xml:space="preserve">4.14547491073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14124393463135</t>
   </si>
   <si>
     <t xml:space="preserve">4.09723329544067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19202518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20810604095459</t>
+    <t xml:space="preserve">4.19202566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20810651779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10738945007324</t>
+    <t xml:space="preserve">4.10738897323608</t>
   </si>
   <si>
     <t xml:space="preserve">3.77053737640381</t>
@@ -4361,10 +4361,10 @@
     <t xml:space="preserve">3.71383166313171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71975612640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82301235198975</t>
+    <t xml:space="preserve">3.71975588798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82301211357117</t>
   </si>
   <si>
     <t xml:space="preserve">3.69944310188293</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">3.65881776809692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80100679397583</t>
+    <t xml:space="preserve">3.80100703239441</t>
   </si>
   <si>
     <t xml:space="preserve">3.70198249816895</t>
@@ -4397,10 +4397,10 @@
     <t xml:space="preserve">3.71044588088989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66982078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68082332611084</t>
+    <t xml:space="preserve">3.66982054710388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68082308769226</t>
   </si>
   <si>
     <t xml:space="preserve">3.69690418243408</t>
@@ -4409,22 +4409,22 @@
     <t xml:space="preserve">3.47177243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49123859405518</t>
+    <t xml:space="preserve">3.49123883247375</t>
   </si>
   <si>
     <t xml:space="preserve">3.6063437461853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62919545173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53355669975281</t>
+    <t xml:space="preserve">3.62919569015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53355693817139</t>
   </si>
   <si>
     <t xml:space="preserve">3.51324391365051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48700642585754</t>
+    <t xml:space="preserve">3.48700666427612</t>
   </si>
   <si>
     <t xml:space="preserve">3.33381533622742</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">3.38290429115295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4040629863739</t>
+    <t xml:space="preserve">3.40406322479248</t>
   </si>
   <si>
     <t xml:space="preserve">3.44892024993896</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">3.26356744766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25764298439026</t>
+    <t xml:space="preserve">3.25764274597168</t>
   </si>
   <si>
     <t xml:space="preserve">3.29657554626465</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">3.24325489997864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28134107589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005282402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45738410949707</t>
+    <t xml:space="preserve">3.2813413143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005258560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
     <t xml:space="preserve">3.46415519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42860794067383</t>
+    <t xml:space="preserve">3.42860770225525</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">3.56741142272949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64358353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66135740280151</t>
+    <t xml:space="preserve">3.64358329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66135716438293</t>
   </si>
   <si>
     <t xml:space="preserve">3.64273715019226</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70790696144104</t>
+    <t xml:space="preserve">3.70790672302246</t>
   </si>
   <si>
     <t xml:space="preserve">3.74176120758057</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55979371070862</t>
+    <t xml:space="preserve">3.5597939491272</t>
   </si>
   <si>
     <t xml:space="preserve">3.46838688850403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54625201225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50224137306213</t>
+    <t xml:space="preserve">3.54625225067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50224113464355</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885559082031</t>
+    <t xml:space="preserve">3.49885582923889</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">3.70282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67913055419922</t>
+    <t xml:space="preserve">3.6791307926178</t>
   </si>
   <si>
     <t xml:space="preserve">3.68336272239685</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">3.70706081390381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70029020309448</t>
+    <t xml:space="preserve">3.7002899646759</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4565,31 +4565,31 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010625839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47515773773193</t>
+    <t xml:space="preserve">3.58010649681091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47515749931335</t>
   </si>
   <si>
     <t xml:space="preserve">3.44045686721802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38459706306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34735703468323</t>
+    <t xml:space="preserve">3.38459730148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34735727310181</t>
   </si>
   <si>
     <t xml:space="preserve">3.3803653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40829539299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52678537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4743115901947</t>
+    <t xml:space="preserve">3.40829515457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52678561210632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
     <t xml:space="preserve">3.38205814361572</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">3.43114686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45315217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50647306442261</t>
+    <t xml:space="preserve">3.4531524181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50647330284119</t>
   </si>
   <si>
     <t xml:space="preserve">3.48954582214355</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72568011283875</t>
+    <t xml:space="preserve">3.72568035125732</t>
   </si>
   <si>
     <t xml:space="preserve">3.81370210647583</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241361618042</t>
+    <t xml:space="preserve">3.85178828239441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241337776184</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">4.01259660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98466730117798</t>
+    <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
     <t xml:space="preserve">4.03037071228027</t>
@@ -4676,16 +4676,16 @@
     <t xml:space="preserve">4.04052686691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04898977279663</t>
+    <t xml:space="preserve">4.04899024963379</t>
   </si>
   <si>
     <t xml:space="preserve">4.06845664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05576086044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0625319480896</t>
+    <t xml:space="preserve">4.05576133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
     <t xml:space="preserve">4.04645109176636</t>
@@ -4700,31 +4700,31 @@
     <t xml:space="preserve">4.03460264205933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08623027801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14208984375</t>
+    <t xml:space="preserve">4.08623075485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14209032058716</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05322217941284</t>
+    <t xml:space="preserve">4.05322170257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.0083646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98635959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02360010147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01344347000122</t>
+    <t xml:space="preserve">3.98635983467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02359962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01344299316406</t>
   </si>
   <si>
     <t xml:space="preserve">3.96773958206177</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">4.00667238235474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.955890417099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84586405754089</t>
+    <t xml:space="preserve">3.95589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84586381912231</t>
   </si>
   <si>
     <t xml:space="preserve">3.78831076622009</t>
@@ -4745,22 +4745,22 @@
     <t xml:space="preserve">3.86702251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88818168640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96096849441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94150233268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93219232559204</t>
+    <t xml:space="preserve">3.88818192481995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9609682559967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94150257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93219256401062</t>
   </si>
   <si>
     <t xml:space="preserve">3.91272640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89579892158508</t>
+    <t xml:space="preserve">3.89579916000366</t>
   </si>
   <si>
     <t xml:space="preserve">3.91865086555481</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">3.8577127456665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89326000213623</t>
+    <t xml:space="preserve">3.89325976371765</t>
   </si>
   <si>
     <t xml:space="preserve">3.96435451507568</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">4.03544855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97958874702454</t>
+    <t xml:space="preserve">3.97958898544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">4.01682901382446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99482274055481</t>
+    <t xml:space="preserve">3.99482297897339</t>
   </si>
   <si>
     <t xml:space="preserve">3.98974537849426</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1911792755127</t>
+    <t xml:space="preserve">4.19117879867554</t>
   </si>
   <si>
     <t xml:space="preserve">4.13362646102905</t>
@@ -4835,13 +4835,13 @@
     <t xml:space="preserve">4.15732479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14462947845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18271589279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18948650360107</t>
+    <t xml:space="preserve">4.14462900161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18271541595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18948602676392</t>
   </si>
   <si>
     <t xml:space="preserve">4.19794988632202</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">4.20556688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22926568984985</t>
+    <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233797073364</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">4.17679071426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16155576705933</t>
+    <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863964080811</t>
@@ -4868,10 +4868,10 @@
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17932987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23349666595459</t>
+    <t xml:space="preserve">4.17933034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23349714279175</t>
   </si>
   <si>
     <t xml:space="preserve">4.24026823043823</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">4.27073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29612827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33506107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29443454742432</t>
+    <t xml:space="preserve">4.2961277961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33506059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29443502426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.28427839279175</t>
@@ -4895,34 +4895,34 @@
     <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09215497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85094213485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802529335022</t>
+    <t xml:space="preserve">4.09215450286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8509418964386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87802481651306</t>
   </si>
   <si>
     <t xml:space="preserve">3.75784230232239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8526349067688</t>
+    <t xml:space="preserve">3.85263466835022</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94658088684082</t>
+    <t xml:space="preserve">3.94658064842224</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92965316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93811726570129</t>
+    <t xml:space="preserve">3.92965340614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93811702728271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05491495132446</t>
@@ -4931,34 +4931,34 @@
     <t xml:space="preserve">4.06676340103149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518943786621</t>
+    <t xml:space="preserve">4.23518991470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766393661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29274225234985</t>
+    <t xml:space="preserve">4.28766441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29274272918701</t>
   </si>
   <si>
     <t xml:space="preserve">4.32321119308472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35537338256836</t>
+    <t xml:space="preserve">4.3553729057312</t>
   </si>
   <si>
     <t xml:space="preserve">4.30289888381958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25888824462891</t>
+    <t xml:space="preserve">4.25888776779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.30459117889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28258609771729</t>
+    <t xml:space="preserve">4.28258562088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.33336734771729</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">4.32828950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39938354492188</t>
+    <t xml:space="preserve">4.39938402175903</t>
   </si>
   <si>
     <t xml:space="preserve">4.37907075881958</t>
@@ -4985,7 +4985,7 @@
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183168411255</t>
+    <t xml:space="preserve">4.34183120727539</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531141281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072353363037</t>
+    <t xml:space="preserve">4.33531188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3398699760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072305679321</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266326904297</t>
+    <t xml:space="preserve">4.36266374588013</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369129180908</t>
+    <t xml:space="preserve">4.40369176864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081052780151</t>
+    <t xml:space="preserve">4.35081100463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292520523071</t>
+    <t xml:space="preserve">4.48757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292568206787</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924903869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574781417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492357254028</t>
+    <t xml:space="preserve">4.43924951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492404937744</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5769214630127</t>
+    <t xml:space="preserve">4.57692193984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5915093421936</t>
+    <t xml:space="preserve">4.59150981903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891983032227</t>
+    <t xml:space="preserve">4.63891935348511</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130556106567</t>
+    <t xml:space="preserve">4.52130603790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5159,7 +5159,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786249160767</t>
+    <t xml:space="preserve">4.58786296844482</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5171,22 +5171,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732950210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897798538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197505950928</t>
+    <t xml:space="preserve">4.73191690444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644710540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197553634644</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6553316116333</t>
+    <t xml:space="preserve">4.56780481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65533113479614</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074373245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792064666748</t>
+    <t xml:space="preserve">4.68268394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792112350464</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68450689315796</t>
+    <t xml:space="preserve">4.6845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009395599365</t>
+    <t xml:space="preserve">4.73009347915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174291610718</t>
+    <t xml:space="preserve">4.67174243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7063889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6370964050293</t>
+    <t xml:space="preserve">4.70638847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63709688186646</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080188751221</t>
+    <t xml:space="preserve">4.66080141067505</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903614044189</t>
+    <t xml:space="preserve">4.67903661727905</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8887357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403158187866</t>
+    <t xml:space="preserve">4.87050104141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88873624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497308731079</t>
+    <t xml:space="preserve">4.85956048965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491445541382</t>
+    <t xml:space="preserve">4.82491397857666</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756212234497</t>
+    <t xml:space="preserve">4.79756259918213</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5348,13 +5348,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932786941528</t>
+    <t xml:space="preserve">4.77932739257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815422058105</t>
+    <t xml:space="preserve">4.6881537437439</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714496612549</t>
+    <t xml:space="preserve">4.96714544296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602994918823</t>
+    <t xml:space="preserve">4.89602947235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079229354858</t>
+    <t xml:space="preserve">4.97079277038574</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5423,7 +5423,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2333722114563</t>
+    <t xml:space="preserve">5.23337268829346</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5432,13 +5432,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2607250213623</t>
+    <t xml:space="preserve">5.26072454452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078317642212</t>
+    <t xml:space="preserve">5.28078269958496</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5450,10 +5450,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709890365601</t>
+    <t xml:space="preserve">6.38216161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709842681885</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8562650680542</t>
+    <t xml:space="preserve">6.85626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5489,13 +5489,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655679702759</t>
+    <t xml:space="preserve">6.95655632019043</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632322311401</t>
+    <t xml:space="preserve">6.87632369995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8690299987793</t>
+    <t xml:space="preserve">6.86902952194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5525,13 +5525,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625642776489</t>
+    <t xml:space="preserve">7.16625595092773</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213426589966</t>
+    <t xml:space="preserve">7.31213474273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566480636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537307739258</t>
+    <t xml:space="preserve">7.21184253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537355422974</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5558,10 +5558,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242551803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5127158164978</t>
+    <t xml:space="preserve">7.41242504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5570,19 +5570,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57653856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682933807373</t>
+    <t xml:space="preserve">7.63124227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580131530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.726975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682886123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67227029800415</t>
+    <t xml:space="preserve">7.67226982116699</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22387218475342</t>
+    <t xml:space="preserve">8.2238712310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -6591,6 +6591,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.9599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2049999237061</t>
   </si>
 </sst>
 </file>
@@ -71903,7 +71906,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6930671296</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>1005039</v>
@@ -71924,6 +71927,32 @@
         <v>2192</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6909722222</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>1096554</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>19.2049999237061</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>18.7399997711182</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>19.0100002288818</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>19.2049999237061</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>2193</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="2194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="2195">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528865814209</t>
+    <t xml:space="preserve">2.44528889656067</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">2.50193190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40895080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3565821647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31490159034729</t>
+    <t xml:space="preserve">2.40895056724548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35658240318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.29780173301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37261343002319</t>
+    <t xml:space="preserve">2.37261390686035</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795734405518</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">2.33413887023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23474526405334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15458989143372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11184000968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99641561508179</t>
+    <t xml:space="preserve">2.2347457408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15458965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11183977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964154958725</t>
   </si>
   <si>
     <t xml:space="preserve">2.06588363647461</t>
@@ -89,46 +89,46 @@
     <t xml:space="preserve">2.0348904132843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03168392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02954649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9034343957901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00924015045166</t>
+    <t xml:space="preserve">2.03168416023254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00924038887024</t>
   </si>
   <si>
     <t xml:space="preserve">1.93549716472626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8403787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953544139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701689720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792963981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349870681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151118755341</t>
+    <t xml:space="preserve">1.84037888050079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7495356798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701653957367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792952060699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349882602692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151142597198</t>
   </si>
   <si>
     <t xml:space="preserve">1.6886168718338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60632336139679</t>
+    <t xml:space="preserve">1.55823016166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60632359981537</t>
   </si>
   <si>
     <t xml:space="preserve">1.72922933101654</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">1.67899823188782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74312281608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350441455841</t>
+    <t xml:space="preserve">1.74312317371368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350405693054</t>
   </si>
   <si>
     <t xml:space="preserve">1.69396090507507</t>
@@ -149,115 +149,115 @@
     <t xml:space="preserve">1.74419152736664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70571684837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533524990082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82541608810425</t>
+    <t xml:space="preserve">1.7057169675827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66296708583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71533560752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82541620731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.8232786655426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88099110126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381563663483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86602830886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404114723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556670665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82648503780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92053461074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442845344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9322909116745</t>
+    <t xml:space="preserve">1.88099086284637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381611347198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488470554352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86602854728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404150485992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82648479938507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79976618289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92053484916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442809581757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93229103088379</t>
   </si>
   <si>
     <t xml:space="preserve">1.96221554279327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96435356140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183454036713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95580303668976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95259702205658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92374110221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87564730644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8831285238266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91198468208313</t>
+    <t xml:space="preserve">1.96435296535492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95580315589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95259726047516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92374074459076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87564706802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88312840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91198456287384</t>
   </si>
   <si>
     <t xml:space="preserve">1.90022838115692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89167881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579744815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81793510913849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190420150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992227077484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465312957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9258781671524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92801570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91519117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0177903175354</t>
+    <t xml:space="preserve">1.89167845249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81793487071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80190372467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992215156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129721164703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465372562408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587828636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92801558971405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91519093513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01779055595398</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626511573792</t>
@@ -269,76 +269,76 @@
     <t xml:space="preserve">2.06160879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07015919685364</t>
+    <t xml:space="preserve">2.07015872001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.02634024620056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05519604682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05092120170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99855279922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214053153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95045924186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93977200984955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84999763965607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457835674286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79121649265289</t>
+    <t xml:space="preserve">2.0551962852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05092144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855256080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214041233063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95045959949493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93977177143097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84999752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121625423431</t>
   </si>
   <si>
     <t xml:space="preserve">1.73884797096252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388577461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502949714661</t>
+    <t xml:space="preserve">1.72388541698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69502925872803</t>
   </si>
   <si>
     <t xml:space="preserve">1.70678567886353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70785439014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235282421112</t>
+    <t xml:space="preserve">1.70785462856293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235258579254</t>
   </si>
   <si>
     <t xml:space="preserve">1.83700931072235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87773108482361</t>
+    <t xml:space="preserve">1.87773132324219</t>
   </si>
   <si>
     <t xml:space="preserve">1.87546896934509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91279733181</t>
+    <t xml:space="preserve">1.91279745101929</t>
   </si>
   <si>
     <t xml:space="preserve">1.90601050853729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88451814651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081224441528</t>
+    <t xml:space="preserve">1.88451838493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081236362457</t>
   </si>
   <si>
     <t xml:space="preserve">1.80986142158508</t>
@@ -347,34 +347,34 @@
     <t xml:space="preserve">1.81438612937927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80646824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75104129314423</t>
+    <t xml:space="preserve">1.80646800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75104117393494</t>
   </si>
   <si>
     <t xml:space="preserve">1.63113760948181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54290699958801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46711897850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47390592098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42526590824127</t>
+    <t xml:space="preserve">1.54290688037872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46711921691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47390604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42526578903198</t>
   </si>
   <si>
     <t xml:space="preserve">1.51689016819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61190783977509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60059607028961</t>
+    <t xml:space="preserve">1.61190807819366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60059630870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.57684206962585</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">1.38341295719147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2420175075531</t>
+    <t xml:space="preserve">1.24201762676239</t>
   </si>
   <si>
     <t xml:space="preserve">1.27255892753601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21373820304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19111514091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23636174201965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18545913696289</t>
+    <t xml:space="preserve">1.213738322258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19111502170563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23636186122894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18545937538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021277427673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0994907617569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722864627838</t>
+    <t xml:space="preserve">1.09949088096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722852706909</t>
   </si>
   <si>
     <t xml:space="preserve">1.23749279975891</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">1.28726410865784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36870789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3347727060318</t>
+    <t xml:space="preserve">1.36870765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
     <t xml:space="preserve">1.39359331130981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38454413414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038025379181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36983907222748</t>
+    <t xml:space="preserve">1.38454401493073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40038049221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983895301819</t>
   </si>
   <si>
     <t xml:space="preserve">1.39811789989471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37888824939728</t>
+    <t xml:space="preserve">1.37888836860657</t>
   </si>
   <si>
     <t xml:space="preserve">1.37097012996674</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">1.37775719165802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42979061603546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40264272689819</t>
+    <t xml:space="preserve">1.42979073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4026426076889</t>
   </si>
   <si>
     <t xml:space="preserve">1.38567519187927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26011610031128</t>
+    <t xml:space="preserve">1.26011621952057</t>
   </si>
   <si>
     <t xml:space="preserve">1.29631328582764</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">1.32233011722565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37549483776093</t>
+    <t xml:space="preserve">1.37549459934235</t>
   </si>
   <si>
     <t xml:space="preserve">1.43657767772675</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">1.44788920879364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47051250934601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45015144348145</t>
+    <t xml:space="preserve">1.47051239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45015132427216</t>
   </si>
   <si>
     <t xml:space="preserve">1.41961014270782</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">1.38001930713654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39698672294617</t>
+    <t xml:space="preserve">1.39698684215546</t>
   </si>
   <si>
     <t xml:space="preserve">1.33137953281403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33251047134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38228166103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3675764799118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35400259494781</t>
+    <t xml:space="preserve">1.33251059055328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38228154182434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36757659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816635608673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35400283336639</t>
   </si>
   <si>
     <t xml:space="preserve">1.32798600196838</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">1.41056072711945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40377414226532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42413473129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43883967399597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45920085906982</t>
+    <t xml:space="preserve">1.40377378463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42413485050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43883991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45920050144196</t>
   </si>
   <si>
     <t xml:space="preserve">1.47729933261871</t>
@@ -536,16 +536,16 @@
     <t xml:space="preserve">1.48747980594635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4897426366806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019978046417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40716731548309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3607896566391</t>
+    <t xml:space="preserve">1.48974251747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39020001888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4071671962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36078953742981</t>
   </si>
   <si>
     <t xml:space="preserve">1.41282308101654</t>
@@ -554,31 +554,31 @@
     <t xml:space="preserve">1.35513377189636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34947800636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34269106388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821493148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28500163555145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27934598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35174024105072</t>
+    <t xml:space="preserve">1.3494781255722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34269094467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536258220673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821469306946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780517101288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28613269329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28500175476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27934587001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35174036026001</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">1.37210142612457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39472472667694</t>
+    <t xml:space="preserve">1.39472460746765</t>
   </si>
   <si>
     <t xml:space="preserve">1.41621649265289</t>
@@ -599,172 +599,172 @@
     <t xml:space="preserve">1.49313580989838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52480840682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53159534931183</t>
+    <t xml:space="preserve">1.52480864524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53159558773041</t>
   </si>
   <si>
     <t xml:space="preserve">1.51575899124146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54856276512146</t>
+    <t xml:space="preserve">1.54856300354004</t>
   </si>
   <si>
     <t xml:space="preserve">1.56553030014038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61077678203583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63453102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59833371639252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571089267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118618488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50444757938385</t>
+    <t xml:space="preserve">1.61077690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63453125953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59833383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571065425873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50444722175598</t>
   </si>
   <si>
     <t xml:space="preserve">1.51802146434784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47503745555878</t>
+    <t xml:space="preserve">1.47503733634949</t>
   </si>
   <si>
     <t xml:space="preserve">1.65715444087982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69335162639618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733479499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167914867401</t>
+    <t xml:space="preserve">1.69335150718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733491420746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167891025543</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905572891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172736644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57457947731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58476006984711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5610054731369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064452648163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512113571167</t>
+    <t xml:space="preserve">1.60172772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57457959651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6266131401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58475983142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100535392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064476490021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512101650238</t>
   </si>
   <si>
     <t xml:space="preserve">1.64923632144928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66620373725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62435066699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049963474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741847515106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284578800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492754936218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022248744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86302626132965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623908042908</t>
+    <t xml:space="preserve">1.66620397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284554958344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492790699005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022260665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86302614212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623896121979</t>
   </si>
   <si>
     <t xml:space="preserve">1.9105349779129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922344684601</t>
+    <t xml:space="preserve">1.89922308921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.91166615486145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92637133598328</t>
+    <t xml:space="preserve">1.92637157440186</t>
   </si>
   <si>
     <t xml:space="preserve">1.94560122489929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94447004795074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8969612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365519285202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98066759109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01347088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781512260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01573324203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01912713050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96483135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99876594543457</t>
+    <t xml:space="preserve">1.94446992874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89696133136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655180931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066735267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01347064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01573348045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01912665367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96483099460602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99876570701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.02025818824768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727370262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007723808289</t>
+    <t xml:space="preserve">1.97727417945862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007747650146</t>
   </si>
   <si>
     <t xml:space="preserve">1.97161817550659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9478634595871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953605651855</t>
+    <t xml:space="preserve">1.94786369800568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953593730927</t>
   </si>
   <si>
     <t xml:space="preserve">2.02252054214478</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">2.08699655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193018913269</t>
+    <t xml:space="preserve">2.05079936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193066596985</t>
   </si>
   <si>
     <t xml:space="preserve">1.93542075157166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93202722072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96709334850311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940392017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89130508899689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320649623871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999331951141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510790348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596252918243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03609395027161</t>
+    <t xml:space="preserve">1.93202710151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96709299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894618034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940403938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89130544662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.873206615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8799934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8551082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96596205234528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03609418869019</t>
   </si>
   <si>
     <t xml:space="preserve">1.99424123764038</t>
@@ -827,67 +827,67 @@
     <t xml:space="preserve">2.00329065322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02478194236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01799559593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00442147254944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95465075969696</t>
+    <t xml:space="preserve">2.02478265762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01799535751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00442171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95465064048767</t>
   </si>
   <si>
     <t xml:space="preserve">2.02930736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02817606925964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09265184402466</t>
+    <t xml:space="preserve">2.02817583084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09265232086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.13224315643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12432527542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12093114852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15939092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373563766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016151428223</t>
+    <t xml:space="preserve">2.12432503700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12093138694763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15939116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016127586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.1084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07568502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14921021461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19332599639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17862105369568</t>
+    <t xml:space="preserve">2.0756847858429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14921045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1933262348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1786208152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.23291635513306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1955885887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20803117752075</t>
+    <t xml:space="preserve">2.19558811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20803141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.20576882362366</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">2.18314528465271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16617822647095</t>
+    <t xml:space="preserve">2.16617798805237</t>
   </si>
   <si>
     <t xml:space="preserve">2.20350646972656</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">2.19219470024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15825963020325</t>
+    <t xml:space="preserve">2.15825986862183</t>
   </si>
   <si>
     <t xml:space="preserve">2.20011281967163</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">2.17522740364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17748951911926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15599775314331</t>
+    <t xml:space="preserve">2.17748975753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15599751472473</t>
   </si>
   <si>
     <t xml:space="preserve">2.14129233360291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09378337860107</t>
+    <t xml:space="preserve">2.09378361701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.07907843589783</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10961961746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22273635864258</t>
+    <t xml:space="preserve">2.10961985588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.222736120224</t>
   </si>
   <si>
     <t xml:space="preserve">2.26232719421387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26006460189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2578022480011</t>
+    <t xml:space="preserve">2.26006436347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25780248641968</t>
   </si>
   <si>
     <t xml:space="preserve">2.31436038017273</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">2.33132815361023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34716415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40032839775085</t>
+    <t xml:space="preserve">2.34716439247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40032887458801</t>
   </si>
   <si>
     <t xml:space="preserve">2.41164040565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43878793716431</t>
+    <t xml:space="preserve">2.43878841400146</t>
   </si>
   <si>
     <t xml:space="preserve">2.44557523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39127945899963</t>
+    <t xml:space="preserve">2.39127969741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.32567238807678</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">2.36300039291382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33585262298584</t>
+    <t xml:space="preserve">2.33585214614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.25893330574036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24988412857056</t>
+    <t xml:space="preserve">2.2498836517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137589454651</t>
@@ -1007,37 +1007,37 @@
     <t xml:space="preserve">2.35072040557861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30808782577515</t>
+    <t xml:space="preserve">2.30808758735657</t>
   </si>
   <si>
     <t xml:space="preserve">2.21453237533569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926927566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558453559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2109797000885</t>
+    <t xml:space="preserve">2.21926951408386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21098017692566</t>
   </si>
   <si>
     <t xml:space="preserve">2.18137383460999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14584636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13637280464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10913491249084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14110946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14229393005371</t>
+    <t xml:space="preserve">2.1458466053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13637256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10913515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14110970497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14229369163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.16361045837402</t>
@@ -1046,49 +1046,49 @@
     <t xml:space="preserve">2.18611073493958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13874077796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11979293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1493992805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13755679130554</t>
+    <t xml:space="preserve">2.13874125480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.119793176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14939951896667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1375572681427</t>
   </si>
   <si>
     <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15532064437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20032167434692</t>
+    <t xml:space="preserve">2.15532040596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20032215118408</t>
   </si>
   <si>
     <t xml:space="preserve">2.18374228477478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2737443447113</t>
+    <t xml:space="preserve">2.23821759223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27374458312988</t>
   </si>
   <si>
     <t xml:space="preserve">2.39453744888306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38387894630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34835195541382</t>
+    <t xml:space="preserve">2.3838791847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3483521938324</t>
   </si>
   <si>
     <t xml:space="preserve">2.36848402023315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37322115898132</t>
+    <t xml:space="preserve">2.37322092056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.36966824531555</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">2.37203693389893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38032650947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38861608505249</t>
+    <t xml:space="preserve">2.38032674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38861632347107</t>
   </si>
   <si>
     <t xml:space="preserve">2.34361505508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30927181243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28913974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29387664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34953641891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36019444465637</t>
+    <t xml:space="preserve">2.30927228927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28913998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2938768863678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33058857917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34953618049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36019468307495</t>
   </si>
   <si>
     <t xml:space="preserve">2.31637740135193</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">2.34006237983704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40401124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4099326133728</t>
+    <t xml:space="preserve">2.40401077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40993285179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.37914228439331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3554573059082</t>
+    <t xml:space="preserve">2.35545754432678</t>
   </si>
   <si>
     <t xml:space="preserve">2.31045651435852</t>
@@ -1154,37 +1154,37 @@
     <t xml:space="preserve">2.25953364372253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27966570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25598120689392</t>
+    <t xml:space="preserve">2.27966594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25598096847534</t>
   </si>
   <si>
     <t xml:space="preserve">2.23111200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22163820266724</t>
+    <t xml:space="preserve">2.22163796424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.19676899909973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19321632385254</t>
+    <t xml:space="preserve">2.19321656227112</t>
   </si>
   <si>
     <t xml:space="preserve">2.18847942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18492674827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163590431213</t>
+    <t xml:space="preserve">2.18492650985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163542747498</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15058350563049</t>
+    <t xml:space="preserve">2.15058374404907</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
@@ -1196,37 +1196,37 @@
     <t xml:space="preserve">2.12097764015198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11031889915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08426570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22400665283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24295473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29624533653259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28795528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25005960464478</t>
+    <t xml:space="preserve">2.11031937599182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842661857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22400641441345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24295449256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29624557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28795552253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25006008148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.25834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24413847923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2275595664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22637534141541</t>
+    <t xml:space="preserve">2.24413871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22755932807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22637510299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.23703336715698</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">2.3211145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25716519355774</t>
+    <t xml:space="preserve">2.25716543197632</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137637138367</t>
@@ -1253,22 +1253,22 @@
     <t xml:space="preserve">2.29742980003357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124454498291</t>
+    <t xml:space="preserve">2.25124406814575</t>
   </si>
   <si>
     <t xml:space="preserve">2.31874585151672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27848172187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2666392326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28321838378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32703566551208</t>
+    <t xml:space="preserve">2.27848148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26663947105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28321862220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32703590393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.34598350524902</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">2.30571937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27729725837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742726325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203209877014</t>
+    <t xml:space="preserve">2.27729749679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203186035156</t>
   </si>
   <si>
     <t xml:space="preserve">2.1482150554657</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">2.19795322418213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2097954750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19913768768311</t>
+    <t xml:space="preserve">2.20979571342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19913721084595</t>
   </si>
   <si>
     <t xml:space="preserve">2.23348045349121</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">2.28085041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26900744438171</t>
+    <t xml:space="preserve">2.26900768280029</t>
   </si>
   <si>
     <t xml:space="preserve">2.27256059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24177026748657</t>
+    <t xml:space="preserve">2.24177002906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.25361251831055</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">2.27019214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26308631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677153587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032421112061</t>
+    <t xml:space="preserve">2.26308655738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032444953918</t>
   </si>
   <si>
     <t xml:space="preserve">2.30098223686218</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">2.33177256584167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32821989059448</t>
+    <t xml:space="preserve">2.3282196521759</t>
   </si>
   <si>
     <t xml:space="preserve">2.31519317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39098477363586</t>
+    <t xml:space="preserve">2.39098453521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.41585373878479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41940641403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4371702671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48098707199097</t>
+    <t xml:space="preserve">2.41940665245056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43716979026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48098683357239</t>
   </si>
   <si>
     <t xml:space="preserve">2.53309369087219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56743693351746</t>
+    <t xml:space="preserve">2.56743669509888</t>
   </si>
   <si>
     <t xml:space="preserve">2.54612040519714</t>
@@ -1373,28 +1373,28 @@
     <t xml:space="preserve">2.57572627067566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5686206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57691097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56980514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56625270843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63967561721802</t>
+    <t xml:space="preserve">2.56862115859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57691073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56980562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56625247001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63967537879944</t>
   </si>
   <si>
     <t xml:space="preserve">2.65743899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66691303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63671493530273</t>
+    <t xml:space="preserve">2.66691327095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63671517372131</t>
   </si>
   <si>
     <t xml:space="preserve">2.62960934638977</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.58105564117432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57158136367798</t>
+    <t xml:space="preserve">2.57158160209656</t>
   </si>
   <si>
     <t xml:space="preserve">2.56921339035034</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">2.48039507865906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53013300895691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45611810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217129707336</t>
+    <t xml:space="preserve">2.53013324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45611786842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217105865479</t>
   </si>
   <si>
     <t xml:space="preserve">2.44605183601379</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">2.40697193145752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42236733436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4709210395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45552611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723629951477</t>
+    <t xml:space="preserve">2.42236709594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47092127799988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45552563667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723606109619</t>
   </si>
   <si>
     <t xml:space="preserve">2.4655921459198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388172149658</t>
+    <t xml:space="preserve">2.473881483078</t>
   </si>
   <si>
     <t xml:space="preserve">2.41881418228149</t>
@@ -1451,61 +1451,61 @@
     <t xml:space="preserve">2.40934014320374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43480134010315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756392478943</t>
+    <t xml:space="preserve">2.43480181694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40756416320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.3264434337616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33473324775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35190486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39631342887878</t>
+    <t xml:space="preserve">2.33473348617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35190439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39631366729736</t>
   </si>
   <si>
     <t xml:space="preserve">2.37440538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35782599449158</t>
+    <t xml:space="preserve">2.357825756073</t>
   </si>
   <si>
     <t xml:space="preserve">2.42591977119446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611557006836</t>
+    <t xml:space="preserve">2.36611533164978</t>
   </si>
   <si>
     <t xml:space="preserve">2.3862476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39986658096313</t>
+    <t xml:space="preserve">2.39986681938171</t>
   </si>
   <si>
     <t xml:space="preserve">2.32881212234497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35249710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36374711990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39809012413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38565540313721</t>
+    <t xml:space="preserve">2.35249662399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302258491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499785423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36374735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39809036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38565564155579</t>
   </si>
   <si>
     <t xml:space="preserve">2.4123010635376</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">2.41822218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45078921318054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51769852638245</t>
+    <t xml:space="preserve">2.45078897476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51769828796387</t>
   </si>
   <si>
     <t xml:space="preserve">2.51355361938477</t>
@@ -1526,37 +1526,37 @@
     <t xml:space="preserve">2.54315996170044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54079127311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54375195503235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756899833679</t>
+    <t xml:space="preserve">2.54079103469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54375171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756875991821</t>
   </si>
   <si>
     <t xml:space="preserve">2.61066150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58223962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59408211708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61480665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63493847846985</t>
+    <t xml:space="preserve">2.58223986625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59408235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61480641365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63493824005127</t>
   </si>
   <si>
     <t xml:space="preserve">2.65803122520447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64204406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67165040969849</t>
+    <t xml:space="preserve">2.64204359054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67164969444275</t>
   </si>
   <si>
     <t xml:space="preserve">2.6752028465271</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.60177993774414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55855464935303</t>
+    <t xml:space="preserve">2.55855512619019</t>
   </si>
   <si>
     <t xml:space="preserve">2.57039737701416</t>
@@ -1577,34 +1577,34 @@
     <t xml:space="preserve">2.59349012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59526634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5105926990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54967355728149</t>
+    <t xml:space="preserve">2.59526610374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51059293746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54967331886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.48868465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49672651290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4862105846405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43548369407654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888333320618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.387850522995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37733387947083</t>
+    <t xml:space="preserve">2.49672675132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48621034622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4354841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888357162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38785028457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773341178894</t>
   </si>
   <si>
     <t xml:space="preserve">2.25917863845825</t>
@@ -1613,43 +1613,43 @@
     <t xml:space="preserve">2.31176090240479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25361132621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33464980125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577923774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23752737045288</t>
+    <t xml:space="preserve">2.25361108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33464932441711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577947616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2375271320343</t>
   </si>
   <si>
     <t xml:space="preserve">2.22577357292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23567175865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020059585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24989986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23195934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23938322067261</t>
+    <t xml:space="preserve">2.23567152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020035743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2498996257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23195958137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23938298225403</t>
   </si>
   <si>
     <t xml:space="preserve">2.24371337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20041060447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20968961715698</t>
+    <t xml:space="preserve">2.20041012763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20968985557556</t>
   </si>
   <si>
     <t xml:space="preserve">2.22329950332642</t>
@@ -1658,124 +1658,124 @@
     <t xml:space="preserve">2.20721530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15525126457214</t>
+    <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298720359802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05812883377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05874800682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379867553711</t>
+    <t xml:space="preserve">2.05812954902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0587477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379891395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843570709229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04699397087097</t>
+    <t xml:space="preserve">2.04699420928955</t>
   </si>
   <si>
     <t xml:space="preserve">2.04946851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09215307235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11689758300781</t>
+    <t xml:space="preserve">2.09215259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11689734458923</t>
   </si>
   <si>
     <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14102339744568</t>
+    <t xml:space="preserve">2.14102363586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813473701477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08905982971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0686457157135</t>
+    <t xml:space="preserve">2.08906006813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06864547729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.09091591835022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10638117790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12679529190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14349794387817</t>
+    <t xml:space="preserve">2.10638093948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12679553031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14349746704102</t>
   </si>
   <si>
     <t xml:space="preserve">2.13793063163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12122797966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09957647323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11380457878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14473533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18061494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1651496887207</t>
+    <t xml:space="preserve">2.12122750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0995762348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11380410194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14473485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18061470985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16514945030212</t>
   </si>
   <si>
     <t xml:space="preserve">2.20102906227112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09029722213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1243212223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699963569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916730880737</t>
+    <t xml:space="preserve">2.09029698371887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12432074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916754722595</t>
   </si>
   <si>
     <t xml:space="preserve">2.1199905872345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07730603218079</t>
+    <t xml:space="preserve">2.07730650901794</t>
   </si>
   <si>
     <t xml:space="preserve">2.07235741615295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11937165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20474052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28392291069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23319697380066</t>
+    <t xml:space="preserve">2.11937236785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20474076271057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28392314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23319721221924</t>
   </si>
   <si>
     <t xml:space="preserve">2.19174981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24309492111206</t>
+    <t xml:space="preserve">2.2430944442749</t>
   </si>
   <si>
     <t xml:space="preserve">2.26289033889771</t>
@@ -1787,25 +1787,25 @@
     <t xml:space="preserve">2.26969528198242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27711844444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25608563423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2418577671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19917297363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2220618724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27526259422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32846355438232</t>
+    <t xml:space="preserve">2.27711868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25608611106873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24185752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19917321205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22206211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2752628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32846331596375</t>
   </si>
   <si>
     <t xml:space="preserve">2.31485414505005</t>
@@ -1814,40 +1814,40 @@
     <t xml:space="preserve">2.31423544883728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3699107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33712410926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33836126327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3340311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36001300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40145993232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41630625724792</t>
+    <t xml:space="preserve">2.36991095542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33712434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33836150169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33403086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3600127696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40146017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4163064956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.41445112228394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42063736915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45589780807495</t>
+    <t xml:space="preserve">2.4206371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45589804649353</t>
   </si>
   <si>
     <t xml:space="preserve">2.44352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47012639045715</t>
+    <t xml:space="preserve">2.47012615203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.48682880401611</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">2.50600600242615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37300372123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36743640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30743050575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36496186256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2709321975708</t>
+    <t xml:space="preserve">2.37300395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36743593215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30743098258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795281410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36496162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27093243598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.2808301448822</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">2.20907115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18308925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17504739761353</t>
+    <t xml:space="preserve">2.1830894947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17504715919495</t>
   </si>
   <si>
     <t xml:space="preserve">2.19979190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16824269294739</t>
+    <t xml:space="preserve">2.16824245452881</t>
   </si>
   <si>
     <t xml:space="preserve">2.15648889541626</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">2.12184643745422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19669890403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380976676941</t>
+    <t xml:space="preserve">2.1966986656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17381000518799</t>
   </si>
   <si>
     <t xml:space="preserve">2.21525716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24247622489929</t>
+    <t xml:space="preserve">2.24247646331787</t>
   </si>
   <si>
     <t xml:space="preserve">2.24433207511902</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.34949636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26598381996155</t>
+    <t xml:space="preserve">2.26598334312439</t>
   </si>
   <si>
     <t xml:space="preserve">2.26227188110352</t>
@@ -1946,22 +1946,22 @@
     <t xml:space="preserve">2.28825354576111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22701072692871</t>
+    <t xml:space="preserve">2.22701048851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.20412230491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15834450721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1373119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22639226913452</t>
+    <t xml:space="preserve">2.15834474563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13731169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2344343662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2263925075531</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949093818665</t>
@@ -1979,25 +1979,25 @@
     <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15401434898376</t>
+    <t xml:space="preserve">2.15401411056519</t>
   </si>
   <si>
     <t xml:space="preserve">2.18556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21278238296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504173278809</t>
+    <t xml:space="preserve">2.21278285980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19607996940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504149436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17628455162048</t>
+    <t xml:space="preserve">2.1762843132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.14040493965149</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">2.27959299087524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3241331577301</t>
+    <t xml:space="preserve">2.32413291931152</t>
   </si>
   <si>
     <t xml:space="preserve">2.31794714927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35073351860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38846898078918</t>
+    <t xml:space="preserve">2.35073375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846921920776</t>
   </si>
   <si>
     <t xml:space="preserve">2.41012072563171</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32227754592896</t>
+    <t xml:space="preserve">2.32227730751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.37424111366272</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">2.43424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44971179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930853843689</t>
+    <t xml:space="preserve">2.44971203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342397689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930877685547</t>
   </si>
   <si>
     <t xml:space="preserve">2.5511646270752</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">2.47321915626526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136306762695</t>
+    <t xml:space="preserve">2.47136330604553</t>
   </si>
   <si>
     <t xml:space="preserve">2.50043797492981</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">2.45094919204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47507476806641</t>
+    <t xml:space="preserve">2.47507500648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46579599380493</t>
@@ -2099,28 +2099,28 @@
     <t xml:space="preserve">2.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49054026603699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48187971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47878694534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4954891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50662422180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5288941860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53446197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50786185264587</t>
+    <t xml:space="preserve">2.49054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48188018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47878670692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49548935890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50662446022034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52889442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53446221351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50786161422729</t>
   </si>
   <si>
     <t xml:space="preserve">2.55302023887634</t>
@@ -2129,43 +2129,43 @@
     <t xml:space="preserve">2.56601119041443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58147644996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64952421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68292903900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69901299476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68231105804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66870141029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179417610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69282746315002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71014833450317</t>
+    <t xml:space="preserve">2.58147692680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64952397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68292951583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69901347160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68231081962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.668701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179441452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69282722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71014857292175</t>
   </si>
   <si>
     <t xml:space="preserve">2.74664664268494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7299439907074</t>
+    <t xml:space="preserve">2.76396822929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72994422912598</t>
   </si>
   <si>
     <t xml:space="preserve">2.83696436882019</t>
@@ -2174,55 +2174,55 @@
     <t xml:space="preserve">2.8344898223877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86109042167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85057353973389</t>
+    <t xml:space="preserve">2.86109018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85057401657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75716280937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76025629043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78500080108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78994965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83943867683411</t>
+    <t xml:space="preserve">2.75716304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76025581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78500056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78994941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82088017463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83943843841553</t>
   </si>
   <si>
     <t xml:space="preserve">2.83882021903992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79737281799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81160092353821</t>
+    <t xml:space="preserve">2.79737305641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81160116195679</t>
   </si>
   <si>
     <t xml:space="preserve">2.78685665130615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79922890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80603384971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81778717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79551720619202</t>
+    <t xml:space="preserve">2.79922866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80603361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81778740882874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79551768302917</t>
   </si>
   <si>
     <t xml:space="preserve">2.74417209625244</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">2.65014290809631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59137463569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69097113609314</t>
+    <t xml:space="preserve">2.59137487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69097137451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.66560816764832</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">2.73056244850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79984760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76334953308105</t>
+    <t xml:space="preserve">2.79984736442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7633490562439</t>
   </si>
   <si>
     <t xml:space="preserve">2.7504575252533</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">2.68148636817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62863039970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65892624855042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66279363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6344313621521</t>
+    <t xml:space="preserve">2.62863063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65892601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66279339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63443160057068</t>
   </si>
   <si>
     <t xml:space="preserve">2.68664336204529</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.66666102409363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65183568000793</t>
+    <t xml:space="preserve">2.65183520317078</t>
   </si>
   <si>
     <t xml:space="preserve">2.66472697257996</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">2.6885769367218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72016167640686</t>
+    <t xml:space="preserve">2.6943781375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68986630439758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72016191482544</t>
   </si>
   <si>
     <t xml:space="preserve">2.69695663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65247964859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953513145447</t>
+    <t xml:space="preserve">2.65247988700867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953560829163</t>
   </si>
   <si>
     <t xml:space="preserve">2.75303602218628</t>
@@ -2327,19 +2327,19 @@
     <t xml:space="preserve">2.73176431655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7588369846344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79428958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76077079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79944586753845</t>
+    <t xml:space="preserve">2.76205992698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75883722305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79428935050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76077055931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79944610595703</t>
   </si>
   <si>
     <t xml:space="preserve">2.820072889328</t>
@@ -2348,25 +2348,25 @@
     <t xml:space="preserve">2.86197113990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91160440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90773701667786</t>
+    <t xml:space="preserve">2.91160488128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90773677825928</t>
   </si>
   <si>
     <t xml:space="preserve">2.89162230491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89484524726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97477412223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96832823753357</t>
+    <t xml:space="preserve">2.89484548568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414757728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97477388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96832847595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.97541880607605</t>
@@ -2378,40 +2378,40 @@
     <t xml:space="preserve">2.96897268295288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97735238075256</t>
+    <t xml:space="preserve">2.97735261917114</t>
   </si>
   <si>
     <t xml:space="preserve">2.91805005073547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04181122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02118420600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0366542339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03923320770264</t>
+    <t xml:space="preserve">3.04181146621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02118444442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03665447235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03923296928406</t>
   </si>
   <si>
     <t xml:space="preserve">3.04825735092163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00829243659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155141830444</t>
+    <t xml:space="preserve">3.00829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155117988586</t>
   </si>
   <si>
     <t xml:space="preserve">2.98895502090454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90902638435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86003756523132</t>
+    <t xml:space="preserve">2.90902614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86003708839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.84263348579407</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">2.78655457496643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76592755317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83812117576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7343430519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78010869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84843468666077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87421822547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95608139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94770121574402</t>
+    <t xml:space="preserve">2.7659273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83812141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73434281349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78010821342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84843492507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87421798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9560809135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94770097732544</t>
   </si>
   <si>
     <t xml:space="preserve">2.91869473457336</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">2.91676115989685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94705677032471</t>
+    <t xml:space="preserve">2.94705700874329</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031527519226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96510529518127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94576787948608</t>
+    <t xml:space="preserve">2.96510553359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94576811790466</t>
   </si>
   <si>
     <t xml:space="preserve">2.94125533103943</t>
@@ -2474,37 +2474,37 @@
     <t xml:space="preserve">2.9547917842865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801496505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98959970474243</t>
+    <t xml:space="preserve">2.95801472663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98959994316101</t>
   </si>
   <si>
     <t xml:space="preserve">3.05921506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11013746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10884833335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.080486536026</t>
+    <t xml:space="preserve">3.11013770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10884857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08048677444458</t>
   </si>
   <si>
     <t xml:space="preserve">3.11464953422546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10240268707275</t>
+    <t xml:space="preserve">3.10240244865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.09853482246399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06372737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10175776481628</t>
+    <t xml:space="preserve">3.06372761726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10175752639771</t>
   </si>
   <si>
     <t xml:space="preserve">3.12431859970093</t>
@@ -2513,85 +2513,85 @@
     <t xml:space="preserve">3.14945769309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592076301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07661890983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05663681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698612213135</t>
+    <t xml:space="preserve">3.13592123985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07661867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05663704872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698588371277</t>
   </si>
   <si>
     <t xml:space="preserve">3.07275152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04696822166443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08757710456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12560820579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19071102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15396952629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15010237693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17781972885132</t>
+    <t xml:space="preserve">3.04696846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08757662773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12560796737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19071125984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15396976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15010213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17781925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.20553660392761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2268078327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22165179252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21262693405151</t>
+    <t xml:space="preserve">3.22680807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22165155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21262764930725</t>
   </si>
   <si>
     <t xml:space="preserve">3.23325395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25001335144043</t>
+    <t xml:space="preserve">3.25001287460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.21391654014587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23970007896423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26548337936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2474353313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229599952698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739929199219</t>
+    <t xml:space="preserve">3.23969984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26548314094543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24743509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22229623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388097763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739953041077</t>
   </si>
   <si>
     <t xml:space="preserve">3.31447243690491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35185837745667</t>
+    <t xml:space="preserve">3.35185790061951</t>
   </si>
   <si>
     <t xml:space="preserve">3.3995578289032</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">3.43823289871216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45370292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600347518921</t>
+    <t xml:space="preserve">3.45370316505432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600371360779</t>
   </si>
   <si>
     <t xml:space="preserve">3.41631698608398</t>
@@ -2627,118 +2627,118 @@
     <t xml:space="preserve">3.4150276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.413738489151</t>
+    <t xml:space="preserve">3.41373872756958</t>
   </si>
   <si>
     <t xml:space="preserve">3.44596815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40987110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920851707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34541249275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994222640991</t>
+    <t xml:space="preserve">3.40987086296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920899391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34541273117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994198799133</t>
   </si>
   <si>
     <t xml:space="preserve">3.38924407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3879554271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34799075126648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29126691818237</t>
+    <t xml:space="preserve">3.38795495033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34799027442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29126667976379</t>
   </si>
   <si>
     <t xml:space="preserve">3.2719292640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32865333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43049788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43694353103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42405223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42147350311279</t>
+    <t xml:space="preserve">3.32865262031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43049812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4369432926178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42405200004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42147374153137</t>
   </si>
   <si>
     <t xml:space="preserve">3.4781973361969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4549925327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37635278701782</t>
+    <t xml:space="preserve">3.45499181747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37635254859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.29513454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35572552680969</t>
+    <t xml:space="preserve">3.35572528839111</t>
   </si>
   <si>
     <t xml:space="preserve">3.26032638549805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22938656806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30544781684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33252024650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576108932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841071128845</t>
+    <t xml:space="preserve">3.22938632965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30544757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3325207233429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841094970703</t>
   </si>
   <si>
     <t xml:space="preserve">3.1475236415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18491005897522</t>
+    <t xml:space="preserve">3.18490958213806</t>
   </si>
   <si>
     <t xml:space="preserve">3.19006633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16815042495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17395210266113</t>
+    <t xml:space="preserve">3.16815090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1739513874054</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205361366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09982466697693</t>
+    <t xml:space="preserve">3.09982419013977</t>
   </si>
   <si>
     <t xml:space="preserve">3.12238454818726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04890155792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11593866348267</t>
+    <t xml:space="preserve">3.04890179634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11593890190125</t>
   </si>
   <si>
     <t xml:space="preserve">3.1462345123291</t>
@@ -2747,22 +2747,22 @@
     <t xml:space="preserve">3.02182936668396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96703886985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00958180427551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04310059547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09466743469238</t>
+    <t xml:space="preserve">2.96703934669495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00958204269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04310083389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09466767311096</t>
   </si>
   <si>
     <t xml:space="preserve">3.07017350196838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848183631897</t>
+    <t xml:space="preserve">3.15848207473755</t>
   </si>
   <si>
     <t xml:space="preserve">3.18297624588013</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">3.4008469581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854664802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54394555091858</t>
+    <t xml:space="preserve">3.44854640960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54394578933716</t>
   </si>
   <si>
     <t xml:space="preserve">3.47561931610107</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">3.39440107345581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17459678649902</t>
+    <t xml:space="preserve">3.17459654808044</t>
   </si>
   <si>
     <t xml:space="preserve">3.14236688613892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01409411430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8858208656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272227287292</t>
+    <t xml:space="preserve">3.01409435272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88582134246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7427225112915</t>
   </si>
   <si>
     <t xml:space="preserve">2.70017981529236</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">2.56610512733459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51969480514526</t>
+    <t xml:space="preserve">2.51969456672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.24896788597107</t>
@@ -2813,46 +2813,46 @@
     <t xml:space="preserve">2.1593701839447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17741847038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88993239402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76617133617401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68817639350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500667572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91313743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7726172208786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8396543264389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93827605247498</t>
+    <t xml:space="preserve">2.17741870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646694660187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88993227481842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7661714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68817627429962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62500643730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91313767433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77261745929718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83965456485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93827664852142</t>
   </si>
   <si>
     <t xml:space="preserve">1.94149959087372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04141044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9066915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923436641693</t>
+    <t xml:space="preserve">2.04141068458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90669167041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923424720764</t>
   </si>
   <si>
     <t xml:space="preserve">2.02013897895813</t>
@@ -2861,28 +2861,28 @@
     <t xml:space="preserve">2.0523681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98662066459656</t>
+    <t xml:space="preserve">1.98662078380585</t>
   </si>
   <si>
     <t xml:space="preserve">2.11296010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12327313423157</t>
+    <t xml:space="preserve">2.12327289581299</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912755966187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04850077629089</t>
+    <t xml:space="preserve">2.04850101470947</t>
   </si>
   <si>
     <t xml:space="preserve">2.09104371070862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94278848171234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92087244987488</t>
+    <t xml:space="preserve">1.94278860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92087256908417</t>
   </si>
   <si>
     <t xml:space="preserve">1.93892109394073</t>
@@ -2894,37 +2894,37 @@
     <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89766716957092</t>
+    <t xml:space="preserve">1.8976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">1.89379978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99693393707275</t>
+    <t xml:space="preserve">1.99693417549133</t>
   </si>
   <si>
     <t xml:space="preserve">2.06010365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05623579025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02658486366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0252959728241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04463338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04721212387085</t>
+    <t xml:space="preserve">2.05623626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0265851020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02529573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04463362693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04721164703369</t>
   </si>
   <si>
     <t xml:space="preserve">2.05752515792847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01627159118652</t>
+    <t xml:space="preserve">2.0162718296051</t>
   </si>
   <si>
     <t xml:space="preserve">2.0175609588623</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">2.32651424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22702980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21850275993347</t>
+    <t xml:space="preserve">2.22702956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
     <t xml:space="preserve">2.17018151283264</t>
@@ -2951,22 +2951,22 @@
     <t xml:space="preserve">2.21992373466492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28387784957886</t>
+    <t xml:space="preserve">2.28387808799744</t>
   </si>
   <si>
     <t xml:space="preserve">2.27535057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26540207862854</t>
+    <t xml:space="preserve">2.2654025554657</t>
   </si>
   <si>
     <t xml:space="preserve">2.31372356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24266290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25687527656555</t>
+    <t xml:space="preserve">2.24266314506531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25687479972839</t>
   </si>
   <si>
     <t xml:space="preserve">2.39046859741211</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">2.46863460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52406191825867</t>
+    <t xml:space="preserve">2.52406167984009</t>
   </si>
   <si>
     <t xml:space="preserve">2.63633704185486</t>
@@ -2984,52 +2984,52 @@
     <t xml:space="preserve">2.6164402961731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56669783592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48995304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37909889221191</t>
+    <t xml:space="preserve">2.56669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48995280265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37909913063049</t>
   </si>
   <si>
     <t xml:space="preserve">2.38336229324341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38762617111206</t>
+    <t xml:space="preserve">2.38762593269348</t>
   </si>
   <si>
     <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44873809814453</t>
+    <t xml:space="preserve">2.44873785972595</t>
   </si>
   <si>
     <t xml:space="preserve">2.47574067115784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45158052444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44021058082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40325927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41889262199402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42457723617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48284673690796</t>
+    <t xml:space="preserve">2.451580286026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44021081924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40325903892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41889238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42457747459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48284697532654</t>
   </si>
   <si>
     <t xml:space="preserve">2.46010756492615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43310451507568</t>
+    <t xml:space="preserve">2.43310475349426</t>
   </si>
   <si>
     <t xml:space="preserve">2.53258895874023</t>
@@ -3038,34 +3038,34 @@
     <t xml:space="preserve">2.53116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55817055702209</t>
+    <t xml:space="preserve">2.55817031860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.57238268852234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58090972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51127076148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53685259819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56527662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60933399200439</t>
+    <t xml:space="preserve">2.58091020584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51127099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53685283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5652768611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60933423042297</t>
   </si>
   <si>
     <t xml:space="preserve">2.64202189445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63207340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65481281280518</t>
+    <t xml:space="preserve">2.63207364082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6548125743866</t>
   </si>
   <si>
     <t xml:space="preserve">2.67755222320557</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642457485199</t>
+    <t xml:space="preserve">2.76424551010132</t>
   </si>
   <si>
     <t xml:space="preserve">2.64770674705505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61501908302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60649180412292</t>
+    <t xml:space="preserve">2.61501932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60649156570435</t>
   </si>
   <si>
     <t xml:space="preserve">2.4572651386261</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">2.67186713218689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66049718856812</t>
+    <t xml:space="preserve">2.66049766540527</t>
   </si>
   <si>
     <t xml:space="preserve">2.68465805053711</t>
@@ -3104,19 +3104,19 @@
     <t xml:space="preserve">2.7528760433197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89073300361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768406867981</t>
+    <t xml:space="preserve">2.89073276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768454551697</t>
   </si>
   <si>
     <t xml:space="preserve">2.89641785621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92199921607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86373019218445</t>
+    <t xml:space="preserve">2.92199969291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86372995376587</t>
   </si>
   <si>
     <t xml:space="preserve">2.83388471603394</t>
@@ -3125,19 +3125,19 @@
     <t xml:space="preserve">2.88931179046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8495180606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84099078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91773581504822</t>
+    <t xml:space="preserve">2.84951829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91773557662964</t>
   </si>
   <si>
     <t xml:space="preserve">2.93479013442993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95895075798035</t>
+    <t xml:space="preserve">2.95895099639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.94615983963013</t>
@@ -3149,28 +3149,28 @@
     <t xml:space="preserve">2.87083601951599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88789081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8537814617157</t>
+    <t xml:space="preserve">2.88789057731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85378122329712</t>
   </si>
   <si>
     <t xml:space="preserve">2.81256651878357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78556370735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90068125724792</t>
+    <t xml:space="preserve">2.78556394577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90068101882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.87794232368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94189620018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95184469223022</t>
+    <t xml:space="preserve">2.94189643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95184445381165</t>
   </si>
   <si>
     <t xml:space="preserve">2.9575297832489</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">2.93621134757996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91489386558533</t>
+    <t xml:space="preserve">2.91489362716675</t>
   </si>
   <si>
     <t xml:space="preserve">2.85662412643433</t>
@@ -3188,34 +3188,34 @@
     <t xml:space="preserve">2.70313358306885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74861240386963</t>
+    <t xml:space="preserve">2.74861264228821</t>
   </si>
   <si>
     <t xml:space="preserve">2.69602751731873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70455479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765523910522</t>
+    <t xml:space="preserve">2.70455503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65765500068665</t>
   </si>
   <si>
     <t xml:space="preserve">2.72729420661926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66902494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65054893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64912796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.610755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68039464950562</t>
+    <t xml:space="preserve">2.66902470588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65054941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6491277217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61075520515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68039441108704</t>
   </si>
   <si>
     <t xml:space="preserve">2.62354612350464</t>
@@ -3224,25 +3224,25 @@
     <t xml:space="preserve">2.63065195083618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61359810829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56243443489075</t>
+    <t xml:space="preserve">2.61359786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56243419647217</t>
   </si>
   <si>
     <t xml:space="preserve">2.4586865901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5027437210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48853158950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52690410614014</t>
+    <t xml:space="preserve">2.50274395942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48853182792664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49705862998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52690434455872</t>
   </si>
   <si>
     <t xml:space="preserve">2.48568916320801</t>
@@ -3251,19 +3251,19 @@
     <t xml:space="preserve">2.42741966247559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3989953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25403261184692</t>
+    <t xml:space="preserve">2.39899563789368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199282646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2540328502655</t>
   </si>
   <si>
     <t xml:space="preserve">2.23129343986511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276616096497</t>
+    <t xml:space="preserve">2.22276639938354</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235385894775</t>
@@ -3278,16 +3278,16 @@
     <t xml:space="preserve">2.56385564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52264070510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52832579612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55532813072205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71450304985046</t>
+    <t xml:space="preserve">2.52264046669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52832531929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55532836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71450352668762</t>
   </si>
   <si>
     <t xml:space="preserve">2.76850914955139</t>
@@ -3299,25 +3299,25 @@
     <t xml:space="preserve">2.84383320808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83672738075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97174191474915</t>
+    <t xml:space="preserve">2.83672714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97174167633057</t>
   </si>
   <si>
     <t xml:space="preserve">2.93052673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90920877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81967258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80972409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78840589523315</t>
+    <t xml:space="preserve">2.90920853614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81967282295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8097243309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78840613365173</t>
   </si>
   <si>
     <t xml:space="preserve">2.78130006790161</t>
@@ -3341,52 +3341,52 @@
     <t xml:space="preserve">2.75998210906982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7983546257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72871541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75429701805115</t>
+    <t xml:space="preserve">2.79835438728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72871518135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75429725646973</t>
   </si>
   <si>
     <t xml:space="preserve">2.75571846961975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79266953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77419400215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77845740318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75713992118835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83246350288391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86088752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91347241401672</t>
+    <t xml:space="preserve">2.79266977310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77419424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77845764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75713968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83246374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8608877658844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8594663143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91347217559814</t>
   </si>
   <si>
     <t xml:space="preserve">2.88646912574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88362693786621</t>
+    <t xml:space="preserve">2.88362669944763</t>
   </si>
   <si>
     <t xml:space="preserve">2.8424117565155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76993060112</t>
+    <t xml:space="preserve">2.76993036270142</t>
   </si>
   <si>
     <t xml:space="preserve">2.7471911907196</t>
@@ -3395,49 +3395,49 @@
     <t xml:space="preserve">2.79551219940186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67897319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68181562423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74576997756958</t>
+    <t xml:space="preserve">2.67897343635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68181538581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.745769739151</t>
   </si>
   <si>
     <t xml:space="preserve">2.64344310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57522535324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64486408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546069145203</t>
+    <t xml:space="preserve">2.57522511482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.644864320755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546045303345</t>
   </si>
   <si>
     <t xml:space="preserve">2.86657238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758081436157</t>
+    <t xml:space="preserve">2.94758105278015</t>
   </si>
   <si>
     <t xml:space="preserve">3.13233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10533475875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18350148200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14939260482788</t>
+    <t xml:space="preserve">3.10533499717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18350100517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14939284324646</t>
   </si>
   <si>
     <t xml:space="preserve">3.13944411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15791940689087</t>
+    <t xml:space="preserve">3.15791916847229</t>
   </si>
   <si>
     <t xml:space="preserve">3.12665319442749</t>
@@ -3449,34 +3449,34 @@
     <t xml:space="preserve">2.97742652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01153516769409</t>
+    <t xml:space="preserve">3.01153540611267</t>
   </si>
   <si>
     <t xml:space="preserve">3.03427481651306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08259582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13375902175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11812615394592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05843544006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19344973564148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16928911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2119255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2517192363739</t>
+    <t xml:space="preserve">3.08259558677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13375926017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05843496322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19344997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16928935050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21192574501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25171947479248</t>
   </si>
   <si>
     <t xml:space="preserve">3.14797115325928</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">3.28867053985596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29435539245605</t>
+    <t xml:space="preserve">3.29435563087463</t>
   </si>
   <si>
     <t xml:space="preserve">3.3014612197876</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">3.35262489318848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37110066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41942095756531</t>
+    <t xml:space="preserve">3.37110042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41942119598389</t>
   </si>
   <si>
     <t xml:space="preserve">3.36967968940735</t>
@@ -3515,10 +3515,10 @@
     <t xml:space="preserve">3.26450991630554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27587962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30856776237488</t>
+    <t xml:space="preserve">3.27587985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3085675239563</t>
   </si>
   <si>
     <t xml:space="preserve">3.40947294235229</t>
@@ -3530,22 +3530,22 @@
     <t xml:space="preserve">3.38247036933899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40378832817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42013263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32846474647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29790878295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35902047157288</t>
+    <t xml:space="preserve">3.4037880897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42013216018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32846426963806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29790806770325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272790908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35902070999146</t>
   </si>
   <si>
     <t xml:space="preserve">3.36683702468872</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">3.34978270530701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42723846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500327110291</t>
+    <t xml:space="preserve">3.42723822593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500350952148</t>
   </si>
   <si>
     <t xml:space="preserve">3.32206916809082</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">3.29719758033752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31567335128784</t>
+    <t xml:space="preserve">3.31567358970642</t>
   </si>
   <si>
     <t xml:space="preserve">3.33201742172241</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28440761566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23679637908936</t>
+    <t xml:space="preserve">3.28440737724304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23679661750793</t>
   </si>
   <si>
     <t xml:space="preserve">3.31212043762207</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">3.27232694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31283092498779</t>
+    <t xml:space="preserve">3.31283116340637</t>
   </si>
   <si>
     <t xml:space="preserve">3.42226386070251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48550772666931</t>
+    <t xml:space="preserve">3.48550724983215</t>
   </si>
   <si>
     <t xml:space="preserve">3.47555899620056</t>
@@ -3608,34 +3608,34 @@
     <t xml:space="preserve">3.49545621871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48124408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57575392723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143901824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53027534484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49829864501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52459073066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61421132087708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52383732795715</t>
+    <t xml:space="preserve">3.4812445640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143854141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53027558326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829816818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52459096908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61421179771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52383756637573</t>
   </si>
   <si>
     <t xml:space="preserve">3.38902974128723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43120431900024</t>
+    <t xml:space="preserve">3.43120408058167</t>
   </si>
   <si>
     <t xml:space="preserve">3.41614174842834</t>
@@ -3647,40 +3647,40 @@
     <t xml:space="preserve">3.48919415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46584820747375</t>
+    <t xml:space="preserve">3.46584796905518</t>
   </si>
   <si>
     <t xml:space="preserve">3.47488474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831656455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844170570374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46132946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45078492164612</t>
+    <t xml:space="preserve">3.45831632614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844122886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46132922172546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4507851600647</t>
   </si>
   <si>
     <t xml:space="preserve">3.44626665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44099450111389</t>
+    <t xml:space="preserve">3.44099473953247</t>
   </si>
   <si>
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752365112305</t>
+    <t xml:space="preserve">3.38752317428589</t>
   </si>
   <si>
     <t xml:space="preserve">3.3604109287262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32501459121704</t>
+    <t xml:space="preserve">3.32501482963562</t>
   </si>
   <si>
     <t xml:space="preserve">3.24744319915771</t>
@@ -3695,58 +3695,58 @@
     <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28359341621399</t>
+    <t xml:space="preserve">3.28359317779541</t>
   </si>
   <si>
     <t xml:space="preserve">3.21430635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24970316886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279532432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37698006629944</t>
+    <t xml:space="preserve">3.24970269203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279556274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37697982788086</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2948899269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21731877326965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30468058586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31673002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329939842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32953333854675</t>
+    <t xml:space="preserve">3.29488968849182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21731901168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30468082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.316730260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32953357696533</t>
   </si>
   <si>
     <t xml:space="preserve">3.29112410545349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28208684921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14878535270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19999718666077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32802700996399</t>
+    <t xml:space="preserve">3.28208637237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14878511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19999694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32802724838257</t>
   </si>
   <si>
     <t xml:space="preserve">3.33028650283813</t>
@@ -3755,22 +3755,22 @@
     <t xml:space="preserve">3.33480501174927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3860170841217</t>
+    <t xml:space="preserve">3.38601684570312</t>
   </si>
   <si>
     <t xml:space="preserve">3.37321400642395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42216682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40710473060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38149833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42141389846802</t>
+    <t xml:space="preserve">3.4221670627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4071044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38149809837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42141366004944</t>
   </si>
   <si>
     <t xml:space="preserve">3.37170791625977</t>
@@ -3779,76 +3779,76 @@
     <t xml:space="preserve">3.36643600463867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39204239845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48994708061218</t>
+    <t xml:space="preserve">3.39204216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48994731903076</t>
   </si>
   <si>
     <t xml:space="preserve">3.61797761917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60592770576477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6164710521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6533739566803</t>
+    <t xml:space="preserve">3.60592794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647152900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65337347984314</t>
   </si>
   <si>
     <t xml:space="preserve">3.63981819152832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63078045845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6383113861084</t>
+    <t xml:space="preserve">3.63078093528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.72040152549744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67521405220032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66542363166809</t>
+    <t xml:space="preserve">3.6752142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66542410850525</t>
   </si>
   <si>
     <t xml:space="preserve">3.7505259513855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77010750770569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7746262550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77312016487122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79872560501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77613258361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78215742111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76709508895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78667545318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73696994781494</t>
+    <t xml:space="preserve">3.77010703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77462601661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77311968803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79872584342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77613210678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78215670585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76709461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78667569160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73697018623352</t>
   </si>
   <si>
     <t xml:space="preserve">3.77763819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71663570404053</t>
+    <t xml:space="preserve">3.71663618087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.71588277816772</t>
@@ -3857,43 +3857,43 @@
     <t xml:space="preserve">3.70533919334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68726420402527</t>
+    <t xml:space="preserve">3.6375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68726396560669</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994261741638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65638661384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72567343711853</t>
+    <t xml:space="preserve">3.65638637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72567319869995</t>
   </si>
   <si>
     <t xml:space="preserve">3.67144870758057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58258104324341</t>
+    <t xml:space="preserve">3.58258080482483</t>
   </si>
   <si>
     <t xml:space="preserve">3.6413242816925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75429177284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80926895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450135231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625677108765</t>
+    <t xml:space="preserve">3.75429224967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75203204154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80926966667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450087547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80625700950623</t>
   </si>
   <si>
     <t xml:space="preserve">3.84541869163513</t>
@@ -3902,34 +3902,34 @@
     <t xml:space="preserve">3.83939409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717506408691</t>
+    <t xml:space="preserve">3.90717458724976</t>
   </si>
   <si>
     <t xml:space="preserve">3.88006234169006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9538676738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97947359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95989274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483041763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89060568809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88307499885559</t>
+    <t xml:space="preserve">3.95386791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97947382926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989298820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483065605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89060544967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88307476043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.92976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95682621002197</t>
+    <t xml:space="preserve">3.95682549476624</t>
   </si>
   <si>
     <t xml:space="preserve">3.99502563476562</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">3.96239686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95125532150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99025011062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97910904884338</t>
+    <t xml:space="preserve">3.95125555992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99025058746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97910928726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.98388361930847</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">3.95523428916931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00457525253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98070073127747</t>
+    <t xml:space="preserve">4.00457572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98070049285889</t>
   </si>
   <si>
     <t xml:space="preserve">4.0189003944397</t>
@@ -3971,31 +3971,31 @@
     <t xml:space="preserve">3.98706746101379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94807147979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340135574341</t>
+    <t xml:space="preserve">3.9480721950531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340111732483</t>
   </si>
   <si>
     <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04277515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93454313278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97274279594421</t>
+    <t xml:space="preserve">4.04277467727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98865866661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97274231910706</t>
   </si>
   <si>
     <t xml:space="preserve">3.90907692909241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89952683448792</t>
+    <t xml:space="preserve">3.89952707290649</t>
   </si>
   <si>
     <t xml:space="preserve">3.83984017372131</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">3.67590093612671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66316795349121</t>
+    <t xml:space="preserve">3.66316819190979</t>
   </si>
   <si>
     <t xml:space="preserve">3.73638367652893</t>
@@ -4022,13 +4022,13 @@
     <t xml:space="preserve">3.76821637153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84779810905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7721951007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76264595985413</t>
+    <t xml:space="preserve">3.8477988243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77219486236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76264572143555</t>
   </si>
   <si>
     <t xml:space="preserve">3.74752497673035</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">3.72922086715698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73081254959106</t>
+    <t xml:space="preserve">3.73081302642822</t>
   </si>
   <si>
     <t xml:space="preserve">3.77856230735779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74513721466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64565944671631</t>
+    <t xml:space="preserve">3.74513697624207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64565968513489</t>
   </si>
   <si>
     <t xml:space="preserve">3.74832081794739</t>
@@ -4055,67 +4055,67 @@
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77697062492371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83267760276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641603469849</t>
+    <t xml:space="preserve">3.77697014808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8326780796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641579627991</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85177779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8597354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93613481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86212301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87008142471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146397590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97115111351013</t>
+    <t xml:space="preserve">3.85177755355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85973620414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93613505363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86212348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87008118629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146421432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97115063667297</t>
   </si>
   <si>
     <t xml:space="preserve">3.96398854255676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95443844795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99980068206787</t>
+    <t xml:space="preserve">3.95443868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980044364929</t>
   </si>
   <si>
     <t xml:space="preserve">3.91942238807678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76344180107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80402851104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90748524665833</t>
+    <t xml:space="preserve">3.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80402827262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90748476982117</t>
   </si>
   <si>
     <t xml:space="preserve">3.95603036880493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90430188179016</t>
+    <t xml:space="preserve">3.90430164337158</t>
   </si>
   <si>
     <t xml:space="preserve">3.94409275054932</t>
@@ -4124,16 +4124,16 @@
     <t xml:space="preserve">4.00775861740112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96796774864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85575675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82710766792297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03004169464111</t>
+    <t xml:space="preserve">3.96796822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85575652122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82710671424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03004121780396</t>
   </si>
   <si>
     <t xml:space="preserve">4.01253318786621</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">4.00935029983521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99820899963379</t>
+    <t xml:space="preserve">3.99820876121521</t>
   </si>
   <si>
     <t xml:space="preserve">3.91623950004578</t>
@@ -4154,25 +4154,25 @@
     <t xml:space="preserve">3.78094935417175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55414009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69261336326599</t>
+    <t xml:space="preserve">3.55414032936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69261288642883</t>
   </si>
   <si>
     <t xml:space="preserve">3.60746026039124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42760467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40293407440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34483909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06948471069336</t>
+    <t xml:space="preserve">3.42760419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40293383598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34483933448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06948494911194</t>
   </si>
   <si>
     <t xml:space="preserve">2.94374465942383</t>
@@ -4181,55 +4181,55 @@
     <t xml:space="preserve">3.14429187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28913164138794</t>
+    <t xml:space="preserve">3.28913140296936</t>
   </si>
   <si>
     <t xml:space="preserve">3.39338421821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51912379264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56846499443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73797488212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69022583961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6838595867157</t>
+    <t xml:space="preserve">3.51912403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56846523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73797512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69022607803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68385934829712</t>
   </si>
   <si>
     <t xml:space="preserve">3.70852947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.901118516922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90668940544128</t>
+    <t xml:space="preserve">3.74036264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354600906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90111875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90668869018555</t>
   </si>
   <si>
     <t xml:space="preserve">3.92021822929382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97194695472717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319222450256</t>
+    <t xml:space="preserve">3.97194671630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319246292114</t>
   </si>
   <si>
     <t xml:space="preserve">3.93693065643311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0348162651062</t>
+    <t xml:space="preserve">4.03481674194336</t>
   </si>
   <si>
     <t xml:space="preserve">4.06346607208252</t>
@@ -4241,10 +4241,10 @@
     <t xml:space="preserve">4.11758184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09848213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12235736846924</t>
+    <t xml:space="preserve">4.09848260879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12235689163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.1334981918335</t>
@@ -4265,13 +4265,13 @@
     <t xml:space="preserve">4.1971640586853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1541895866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13668203353882</t>
+    <t xml:space="preserve">4.15419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599016189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13668155670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.14623165130615</t>
@@ -4280,19 +4280,19 @@
     <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1939811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17488145828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12554025650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0650577545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16373920440674</t>
+    <t xml:space="preserve">4.19398069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17488098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1255407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06505727767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1637396812439</t>
   </si>
   <si>
     <t xml:space="preserve">4.26719665527344</t>
@@ -4304,37 +4304,37 @@
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9050977230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00298357009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00139188766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12431716918945</t>
+    <t xml:space="preserve">3.90509748458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00298404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00139236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12431669235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011112213135</t>
+    <t xml:space="preserve">4.23011159896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.24703931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28597164154053</t>
+    <t xml:space="preserve">4.28597116470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.25042390823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21487665176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14547491073608</t>
+    <t xml:space="preserve">4.21487712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14547538757324</t>
   </si>
   <si>
     <t xml:space="preserve">4.14124393463135</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">4.19202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20810651779175</t>
+    <t xml:space="preserve">4.20810604095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10738897323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77053737640381</t>
+    <t xml:space="preserve">4.10738945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77053761482239</t>
   </si>
   <si>
     <t xml:space="preserve">3.71383166313171</t>
@@ -4367,61 +4367,61 @@
     <t xml:space="preserve">3.82301211357117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69944310188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71213865280151</t>
+    <t xml:space="preserve">3.69944334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71213912963867</t>
   </si>
   <si>
     <t xml:space="preserve">3.77307677268982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76122760772705</t>
+    <t xml:space="preserve">3.76122736930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65881776809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80100703239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70198249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71467757225037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71044588088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66982054710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68082308769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69690418243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47177243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49123883247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6063437461853</t>
+    <t xml:space="preserve">3.65881824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80100655555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70198225975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71467781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71044611930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66982078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68082332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69690442085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47177267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49123859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60634350776672</t>
   </si>
   <si>
     <t xml:space="preserve">3.62919569015503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53355693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51324391365051</t>
+    <t xml:space="preserve">3.53355669975281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51324415206909</t>
   </si>
   <si>
     <t xml:space="preserve">3.48700666427612</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">3.38713598251343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26356744766235</t>
+    <t xml:space="preserve">3.26356720924377</t>
   </si>
   <si>
     <t xml:space="preserve">3.25764274597168</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">3.29657554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24325489997864</t>
+    <t xml:space="preserve">3.24325466156006</t>
   </si>
   <si>
     <t xml:space="preserve">3.2813413143158</t>
@@ -4466,34 +4466,34 @@
     <t xml:space="preserve">3.46415519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42860770225525</t>
+    <t xml:space="preserve">3.42860794067383</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56741142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66135716438293</t>
+    <t xml:space="preserve">3.56741118431091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64358353614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66135692596436</t>
   </si>
   <si>
     <t xml:space="preserve">3.64273715019226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70875334739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70790672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74176120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73922228813171</t>
+    <t xml:space="preserve">3.70875310897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70790696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74176144599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73922252655029</t>
   </si>
   <si>
     <t xml:space="preserve">3.67659139633179</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">3.5597939491272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46838688850403</t>
+    <t xml:space="preserve">3.46838665008545</t>
   </si>
   <si>
     <t xml:space="preserve">3.54625225067139</t>
@@ -4523,10 +4523,10 @@
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709839820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6190390586853</t>
+    <t xml:space="preserve">3.54709815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61903882026672</t>
   </si>
   <si>
     <t xml:space="preserve">3.50901198387146</t>
@@ -4541,19 +4541,19 @@
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282888412476</t>
+    <t xml:space="preserve">3.70282864570618</t>
   </si>
   <si>
     <t xml:space="preserve">3.6791307926178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68336272239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69351887702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706081390381</t>
+    <t xml:space="preserve">3.68336296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69351863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706057548523</t>
   </si>
   <si>
     <t xml:space="preserve">3.7002899646759</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">3.44045686721802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38459730148315</t>
+    <t xml:space="preserve">3.38459706306458</t>
   </si>
   <si>
     <t xml:space="preserve">3.34735727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3803653717041</t>
+    <t xml:space="preserve">3.38036513328552</t>
   </si>
   <si>
     <t xml:space="preserve">3.40829515457153</t>
@@ -4598,13 +4598,13 @@
     <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36766982078552</t>
+    <t xml:space="preserve">3.3676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">3.37613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3151957988739</t>
+    <t xml:space="preserve">3.31519556045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.42014408111572</t>
@@ -4613,10 +4613,10 @@
     <t xml:space="preserve">3.42437601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43114686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4531524181366</t>
+    <t xml:space="preserve">3.43114709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45315217971802</t>
   </si>
   <si>
     <t xml:space="preserve">3.50647330284119</t>
@@ -4640,10 +4640,10 @@
     <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370210647583</t>
+    <t xml:space="preserve">3.7256805896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">3.97366452217102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06422472000122</t>
+    <t xml:space="preserve">4.06422519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.01259660720825</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">4.03037071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04052686691284</t>
+    <t xml:space="preserve">4.04052639007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.04899024963379</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645109176636</t>
+    <t xml:space="preserve">4.04645156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">4.03460264205933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08623075485229</t>
+    <t xml:space="preserve">4.08623027801514</t>
   </si>
   <si>
     <t xml:space="preserve">4.14209032058716</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">4.05322170257568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0083646774292</t>
+    <t xml:space="preserve">4.00836515426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.98635983467102</t>
@@ -4727,40 +4727,40 @@
     <t xml:space="preserve">4.01344299316406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96773958206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00667238235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95589065551758</t>
+    <t xml:space="preserve">3.96774005889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00667285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.955890417099</t>
   </si>
   <si>
     <t xml:space="preserve">3.84586381912231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86702251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88818192481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9609682559967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94150257110596</t>
+    <t xml:space="preserve">3.78831100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86702275276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88818144798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96096873283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9415020942688</t>
   </si>
   <si>
     <t xml:space="preserve">3.93219256401062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91272640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579916000366</t>
+    <t xml:space="preserve">3.91272592544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579963684082</t>
   </si>
   <si>
     <t xml:space="preserve">3.91865086555481</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.96435451507568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03544855117798</t>
+    <t xml:space="preserve">4.03544902801514</t>
   </si>
   <si>
     <t xml:space="preserve">3.97958898544312</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01682901382446</t>
+    <t xml:space="preserve">4.0168285369873</t>
   </si>
   <si>
     <t xml:space="preserve">3.99482297897339</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">3.9973623752594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02529239654541</t>
+    <t xml:space="preserve">4.02529191970825</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306602478027</t>
@@ -4805,16 +4805,16 @@
     <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05660820007324</t>
+    <t xml:space="preserve">4.05660772323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.08792304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12685585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10992860794067</t>
+    <t xml:space="preserve">4.12685537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10992813110352</t>
   </si>
   <si>
     <t xml:space="preserve">4.09638690948486</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19117879867554</t>
+    <t xml:space="preserve">4.1911792755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.13362646102905</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">4.19794988632202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20556688308716</t>
+    <t xml:space="preserve">4.20556735992432</t>
   </si>
   <si>
     <t xml:space="preserve">4.2292652130127</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17933034896851</t>
+    <t xml:space="preserve">4.17932987213135</t>
   </si>
   <si>
     <t xml:space="preserve">4.23349714279175</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">4.33506059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29443502426147</t>
+    <t xml:space="preserve">4.29443454742432</t>
   </si>
   <si>
     <t xml:space="preserve">4.28427839279175</t>
@@ -4895,16 +4895,16 @@
     <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09215450286865</t>
+    <t xml:space="preserve">4.09215497970581</t>
   </si>
   <si>
     <t xml:space="preserve">3.8509418964386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87802481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784230232239</t>
+    <t xml:space="preserve">3.87802529335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784206390381</t>
   </si>
   <si>
     <t xml:space="preserve">3.85263466835022</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">4.05491495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06676340103149</t>
+    <t xml:space="preserve">4.06676387786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4940,10 +4940,10 @@
     <t xml:space="preserve">4.28766441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29274272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32321119308472</t>
+    <t xml:space="preserve">4.29274225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32321071624756</t>
   </si>
   <si>
     <t xml:space="preserve">4.3553729057312</t>
@@ -4955,19 +4955,19 @@
     <t xml:space="preserve">4.25888776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30459117889404</t>
+    <t xml:space="preserve">4.3045916557312</t>
   </si>
   <si>
     <t xml:space="preserve">4.28258562088013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33336734771729</t>
+    <t xml:space="preserve">4.33336782455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.31305503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23857545852661</t>
+    <t xml:space="preserve">4.23857498168945</t>
   </si>
   <si>
     <t xml:space="preserve">4.32828950881958</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">4.31644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36722135543823</t>
+    <t xml:space="preserve">4.36722183227539</t>
   </si>
   <si>
     <t xml:space="preserve">4.37269258499146</t>
@@ -6594,6 +6594,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.2049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9650001525879</t>
   </si>
 </sst>
 </file>
@@ -71932,7 +71935,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6909722222</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>1096554</v>
@@ -71953,6 +71956,32 @@
         <v>2193</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6912384259</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>1286742</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>19.2099990844727</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>18.8850002288818</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>19.2049999237061</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>18.9650001525879</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="2195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="2196">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,76 +44,76 @@
     <t xml:space="preserve">UNI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50193166732788</t>
+    <t xml:space="preserve">2.50193190574646</t>
   </si>
   <si>
     <t xml:space="preserve">2.40895080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3565821647644</t>
+    <t xml:space="preserve">2.35658264160156</t>
   </si>
   <si>
     <t xml:space="preserve">2.31490135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29780149459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37261390686035</t>
+    <t xml:space="preserve">2.29780173301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37261366844177</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33413910865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23474550247192</t>
+    <t xml:space="preserve">2.33413887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2347457408905</t>
   </si>
   <si>
     <t xml:space="preserve">2.15458965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11183977127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9964154958725</t>
+    <t xml:space="preserve">2.11183953285217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99641537666321</t>
   </si>
   <si>
     <t xml:space="preserve">2.06588387489319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07977795600891</t>
+    <t xml:space="preserve">2.07977747917175</t>
   </si>
   <si>
     <t xml:space="preserve">2.0348904132843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03168416023254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90343451499939</t>
+    <t xml:space="preserve">2.03168439865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02954649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343463420868</t>
   </si>
   <si>
     <t xml:space="preserve">2.00924038887024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9354966878891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84037852287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953520298004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701653957367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792952060699</t>
+    <t xml:space="preserve">1.93549704551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74953544139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701677799225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792940139771</t>
   </si>
   <si>
     <t xml:space="preserve">1.59349882602692</t>
@@ -122,97 +122,97 @@
     <t xml:space="preserve">1.53151142597198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68861711025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823028087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60632348060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72922921180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899787425995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312305450439</t>
+    <t xml:space="preserve">1.68861663341522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55823004245758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60632383823395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72922933101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6789984703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312269687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.73350417613983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69396066665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419188499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70571672916412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66296696662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533560752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82541596889496</t>
+    <t xml:space="preserve">1.69396078586578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419152736664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7057169675827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6629673242569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7153354883194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82541632652283</t>
   </si>
   <si>
     <t xml:space="preserve">1.82327890396118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88099098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381587505341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8948849439621</t>
+    <t xml:space="preserve">1.88099074363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381623268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488470554352</t>
   </si>
   <si>
     <t xml:space="preserve">1.86602854728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80404150485992</t>
+    <t xml:space="preserve">1.80404138565063</t>
   </si>
   <si>
     <t xml:space="preserve">1.76556634902954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82648503780365</t>
+    <t xml:space="preserve">1.82648515701294</t>
   </si>
   <si>
     <t xml:space="preserve">1.79976630210876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053437232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442809581757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229055404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221578121185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435308456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183418273926</t>
+    <t xml:space="preserve">1.92053472995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442785739899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9322909116745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221554279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435332298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183442115784</t>
   </si>
   <si>
     <t xml:space="preserve">1.95580315589905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95259726047516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92374050617218</t>
+    <t xml:space="preserve">1.95259702205658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92374062538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.87564718723297</t>
@@ -224,34 +224,34 @@
     <t xml:space="preserve">1.91198456287384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90022826194763</t>
+    <t xml:space="preserve">1.90022814273834</t>
   </si>
   <si>
     <t xml:space="preserve">1.89167845249176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579756736755</t>
+    <t xml:space="preserve">1.81579792499542</t>
   </si>
   <si>
     <t xml:space="preserve">1.81793487071991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8019038438797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465348720551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92587852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92801558971405</t>
+    <t xml:space="preserve">1.80190372467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992227077484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129733085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465372562408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587828636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92801570892334</t>
   </si>
   <si>
     <t xml:space="preserve">1.91519093513489</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">2.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626511573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07443404197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06160879135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07015872001648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02634024620056</t>
+    <t xml:space="preserve">2.05626559257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07443428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06160926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07015895843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
     <t xml:space="preserve">2.0551962852478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05092144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99855279922485</t>
+    <t xml:space="preserve">2.05092167854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855291843414</t>
   </si>
   <si>
     <t xml:space="preserve">1.99214041233063</t>
@@ -290,37 +290,37 @@
     <t xml:space="preserve">1.95045959949493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93977200984955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84999752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79121649265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73884785175323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388517856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502937793732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678567886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70785450935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700966835022</t>
+    <t xml:space="preserve">1.93977189064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8499972820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457859516144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121661186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73884797096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388529777527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69502913951874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678555965424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70785427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700931072235</t>
   </si>
   <si>
     <t xml:space="preserve">1.87773132324219</t>
@@ -329,52 +329,52 @@
     <t xml:space="preserve">1.87546920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91279721260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90601050853729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451838493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80986154079437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81438624858856</t>
+    <t xml:space="preserve">1.91279757022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90601015090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451826572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081248283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80986130237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81438601016998</t>
   </si>
   <si>
     <t xml:space="preserve">1.80646812915802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75104093551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63113760948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54290688037872</t>
+    <t xml:space="preserve">1.75104141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63113749027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54290676116943</t>
   </si>
   <si>
     <t xml:space="preserve">1.46711897850037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47390580177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42526578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51689028739929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190795898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60059607028961</t>
+    <t xml:space="preserve">1.47390592098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42526590824127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190783977509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60059630870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.57684195041656</t>
@@ -383,82 +383,82 @@
     <t xml:space="preserve">1.6990077495575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38341283798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24201738834381</t>
+    <t xml:space="preserve">1.38341307640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
     <t xml:space="preserve">1.27255880832672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.213738322258</t>
+    <t xml:space="preserve">1.21373844146729</t>
   </si>
   <si>
     <t xml:space="preserve">1.19111502170563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23636174201965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18545925617218</t>
+    <t xml:space="preserve">1.23636198043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18545913696289</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021289348602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09949088096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722864627838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2374929189682</t>
+    <t xml:space="preserve">1.09949100017548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722876548767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23749268054962</t>
   </si>
   <si>
     <t xml:space="preserve">1.28726398944855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36870789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33477294445038</t>
+    <t xml:space="preserve">1.36870777606964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
     <t xml:space="preserve">1.39359331130981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38454401493073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038049221039</t>
+    <t xml:space="preserve">1.38454389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40038025379181</t>
   </si>
   <si>
     <t xml:space="preserve">1.36983871459961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.398118019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37888813018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37097001075745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37775695323944</t>
+    <t xml:space="preserve">1.39811789989471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37888824939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37097024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37775707244873</t>
   </si>
   <si>
     <t xml:space="preserve">1.42979061603546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40264248847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38567519187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26011610031128</t>
+    <t xml:space="preserve">1.40264284610748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38567495346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26011598110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.29631340503693</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">1.32233011722565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37549471855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43657743930817</t>
+    <t xml:space="preserve">1.37549483776093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43657767772675</t>
   </si>
   <si>
     <t xml:space="preserve">1.45354497432709</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">1.47051239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45015156269073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41961026191711</t>
+    <t xml:space="preserve">1.45015108585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41961014270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.38001942634583</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">1.39698696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33137953281403</t>
+    <t xml:space="preserve">1.33137941360474</t>
   </si>
   <si>
     <t xml:space="preserve">1.33251047134399</t>
@@ -503,37 +503,37 @@
     <t xml:space="preserve">1.38228166103363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36757683753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33816647529602</t>
+    <t xml:space="preserve">1.36757659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33816635608673</t>
   </si>
   <si>
     <t xml:space="preserve">1.3540027141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32798588275909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41056084632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40377390384674</t>
+    <t xml:space="preserve">1.32798612117767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41056072711945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40377378463745</t>
   </si>
   <si>
     <t xml:space="preserve">1.42413473129272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43883979320526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45920062065125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47729957103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48748016357422</t>
+    <t xml:space="preserve">1.43883991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45920085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47729969024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48748004436493</t>
   </si>
   <si>
     <t xml:space="preserve">1.48974227905273</t>
@@ -542,88 +542,88 @@
     <t xml:space="preserve">1.39019989967346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40716707706451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36078953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282308101654</t>
+    <t xml:space="preserve">1.40716743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36078941822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282296180725</t>
   </si>
   <si>
     <t xml:space="preserve">1.35513377189636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34947800636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34269118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536282062531</t>
+    <t xml:space="preserve">1.3494781255722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34269106388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536246299744</t>
   </si>
   <si>
     <t xml:space="preserve">1.27821469306946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31780517101288</t>
+    <t xml:space="preserve">1.31780540943146</t>
   </si>
   <si>
     <t xml:space="preserve">1.28613293170929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28500175476074</t>
+    <t xml:space="preserve">1.28500187397003</t>
   </si>
   <si>
     <t xml:space="preserve">1.27934575080872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35174059867859</t>
+    <t xml:space="preserve">1.35174024105072</t>
   </si>
   <si>
     <t xml:space="preserve">1.358527302742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37210154533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39472448825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41621649265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44110214710236</t>
+    <t xml:space="preserve">1.37210130691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39472472667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41621673107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44110226631165</t>
   </si>
   <si>
     <t xml:space="preserve">1.49313580989838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52480852603912</t>
+    <t xml:space="preserve">1.52480840682983</t>
   </si>
   <si>
     <t xml:space="preserve">1.53159534931183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51575899124146</t>
+    <t xml:space="preserve">1.51575911045074</t>
   </si>
   <si>
     <t xml:space="preserve">1.54856276512146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56553030014038</t>
+    <t xml:space="preserve">1.56553018093109</t>
   </si>
   <si>
     <t xml:space="preserve">1.61077678203583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63453137874603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59833407402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571077346802</t>
+    <t xml:space="preserve">1.63453114032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5983339548111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571065425873</t>
   </si>
   <si>
     <t xml:space="preserve">1.57118606567383</t>
@@ -635,298 +635,298 @@
     <t xml:space="preserve">1.51802134513855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47503709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65715456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69335162639618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733479499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167914867401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63905584812164</t>
+    <t xml:space="preserve">1.47503697872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65715444087982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6933513879776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167902946472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63905596733093</t>
   </si>
   <si>
     <t xml:space="preserve">1.60172748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57457947731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58475995063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56100559234619</t>
+    <t xml:space="preserve">1.57457959651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62661337852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58476006984711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100535392761</t>
   </si>
   <si>
     <t xml:space="preserve">1.54064440727234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60512101650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64923655986786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6662038564682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62435066699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049963474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741871356964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284566879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022260665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86302638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623919963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9105349779129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89922332763672</t>
+    <t xml:space="preserve">1.60512089729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64923632144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66620373725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6243509054184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049951553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8528459072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492743015289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022248744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86302649974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91053509712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8992235660553</t>
   </si>
   <si>
     <t xml:space="preserve">1.91166627407074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92637157440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94560098648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94447016716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89696156978607</t>
+    <t xml:space="preserve">1.92637121677399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94560134410858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446992874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8969612121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.93655180931091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98066735267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0134711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781512260437</t>
+    <t xml:space="preserve">1.9806672334671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01347088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781536102295</t>
   </si>
   <si>
     <t xml:space="preserve">2.01573324203491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01912665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96483075618744</t>
+    <t xml:space="preserve">2.01912689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96483051776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.99876570701599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0202579498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727370262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007747650146</t>
+    <t xml:space="preserve">2.02025818824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007723808289</t>
   </si>
   <si>
     <t xml:space="preserve">1.97161793708801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94786322116852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953593730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02252006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99084782600403</t>
+    <t xml:space="preserve">1.94786369800568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953629493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02252054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99084758758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.08247184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08699631690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193090438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542075157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202710151672</t>
+    <t xml:space="preserve">2.08699655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05079960823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542039394379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9320273399353</t>
   </si>
   <si>
     <t xml:space="preserve">1.96709322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89130532741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87320673465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999367713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85510814189911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596205234528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03609395027161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424123764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00215935707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00329041481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478265762329</t>
+    <t xml:space="preserve">2.00894618034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940392017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89130508899689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.873206615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999391555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510790348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9659618139267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03609418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424135684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00215911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00329065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478289604187</t>
   </si>
   <si>
     <t xml:space="preserve">2.01799559593201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00442147254944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95465064048767</t>
+    <t xml:space="preserve">2.0044219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9546502828598</t>
   </si>
   <si>
     <t xml:space="preserve">2.02930736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02817583084106</t>
+    <t xml:space="preserve">2.02817606925964</t>
   </si>
   <si>
     <t xml:space="preserve">2.09265232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13224291801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432503700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12093138694763</t>
+    <t xml:space="preserve">2.13224339485168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12432527542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12093162536621</t>
   </si>
   <si>
     <t xml:space="preserve">2.15939092636108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15373492240906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016127586365</t>
+    <t xml:space="preserve">2.15373539924622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016103744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.10848879814148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07568526268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14921045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1933262348175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1786208152771</t>
+    <t xml:space="preserve">2.0756847858429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14921069145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19332599639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17862057685852</t>
   </si>
   <si>
     <t xml:space="preserve">2.23291659355164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19558835029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20803093910217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20576858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18314528465271</t>
+    <t xml:space="preserve">2.1955885887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20803117752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20576882362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18314552307129</t>
   </si>
   <si>
     <t xml:space="preserve">2.16617798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20350623130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19219470024109</t>
+    <t xml:space="preserve">2.20350646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19219446182251</t>
   </si>
   <si>
     <t xml:space="preserve">2.15825986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20011281967163</t>
+    <t xml:space="preserve">2.20011305809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.17522740364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17748951911926</t>
+    <t xml:space="preserve">2.17748975753784</t>
   </si>
   <si>
     <t xml:space="preserve">2.15599751472473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14129209518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09378361701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07907843589783</t>
+    <t xml:space="preserve">2.14129257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09378337860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07907867431641</t>
   </si>
   <si>
     <t xml:space="preserve">2.08812761306763</t>
@@ -935,58 +935,58 @@
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10961961746216</t>
+    <t xml:space="preserve">2.10961985588074</t>
   </si>
   <si>
     <t xml:space="preserve">2.222736120224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26232719421387</t>
+    <t xml:space="preserve">2.26232671737671</t>
   </si>
   <si>
     <t xml:space="preserve">2.26006436347961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25780200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31436061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33132815361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34716439247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40032863616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41164064407349</t>
+    <t xml:space="preserve">2.25780248641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31436038017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33132791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34716415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40032887458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41164040565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.43878841400146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127945899963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32567191123962</t>
+    <t xml:space="preserve">2.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127993583679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">2.38675475120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36300015449524</t>
+    <t xml:space="preserve">2.36300039291382</t>
   </si>
   <si>
     <t xml:space="preserve">2.33585262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25893330574036</t>
+    <t xml:space="preserve">2.25893306732178</t>
   </si>
   <si>
     <t xml:space="preserve">2.24988412857056</t>
@@ -998,25 +998,25 @@
     <t xml:space="preserve">2.33769369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30216670036316</t>
+    <t xml:space="preserve">2.30216646194458</t>
   </si>
   <si>
     <t xml:space="preserve">2.36137843132019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35072064399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30808758735657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453237533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2192690372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558453559875</t>
+    <t xml:space="preserve">2.35072040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30808782577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453261375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926975250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558501243591</t>
   </si>
   <si>
     <t xml:space="preserve">2.2109797000885</t>
@@ -1025,40 +1025,40 @@
     <t xml:space="preserve">2.18137383460999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14584636688232</t>
+    <t xml:space="preserve">2.14584684371948</t>
   </si>
   <si>
     <t xml:space="preserve">2.13637256622314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10913491249084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14110946655273</t>
+    <t xml:space="preserve">2.10913515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14110922813416</t>
   </si>
   <si>
     <t xml:space="preserve">2.14229416847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16361045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.186110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13874125480652</t>
+    <t xml:space="preserve">2.16361021995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18611073493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13874101638794</t>
   </si>
   <si>
     <t xml:space="preserve">2.11979341506958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1493992805481</t>
+    <t xml:space="preserve">2.14939951896667</t>
   </si>
   <si>
     <t xml:space="preserve">2.13755679130554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1659791469574</t>
+    <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
     <t xml:space="preserve">2.15532064437866</t>
@@ -1067,25 +1067,25 @@
     <t xml:space="preserve">2.20032167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18374228477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27374458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453744888306</t>
+    <t xml:space="preserve">2.18374252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821711540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2737443447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453768730164</t>
   </si>
   <si>
     <t xml:space="preserve">2.38387942314148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34835195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36848449707031</t>
+    <t xml:space="preserve">2.34835243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36848425865173</t>
   </si>
   <si>
     <t xml:space="preserve">2.37322092056274</t>
@@ -1094,22 +1094,22 @@
     <t xml:space="preserve">2.36966824531555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37203693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38032674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38861608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34361505508423</t>
+    <t xml:space="preserve">2.3720371723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38032650947571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38861632347107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34361457824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.30927205085754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28913974761963</t>
+    <t xml:space="preserve">2.28913998603821</t>
   </si>
   <si>
     <t xml:space="preserve">2.2938768863678</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">2.33058857917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34953641891479</t>
+    <t xml:space="preserve">2.34953594207764</t>
   </si>
   <si>
     <t xml:space="preserve">2.36019468307495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31637740135193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34479951858521</t>
+    <t xml:space="preserve">2.31637787818909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34479928016663</t>
   </si>
   <si>
     <t xml:space="preserve">2.31756162643433</t>
@@ -1136,55 +1136,55 @@
     <t xml:space="preserve">2.34006214141846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40401124954224</t>
+    <t xml:space="preserve">2.40401148796082</t>
   </si>
   <si>
     <t xml:space="preserve">2.40993285179138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37914204597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3554573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045651435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25953388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27966594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2559814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23111200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22163820266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19676923751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19321656227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18492674827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163542747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005730628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058350563049</t>
+    <t xml:space="preserve">2.37914228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35545754432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25953364372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27966570854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25598120689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.231112241745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22163796424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19676876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18492650985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058374404907</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">2.13045144081116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1209774017334</t>
+    <t xml:space="preserve">2.12097764015198</t>
   </si>
   <si>
     <t xml:space="preserve">2.11031913757324</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">2.28795552253723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25005960464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25834941864014</t>
+    <t xml:space="preserve">2.25005984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25834918022156</t>
   </si>
   <si>
     <t xml:space="preserve">2.24413847923279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22755908966064</t>
+    <t xml:space="preserve">2.22755932807922</t>
   </si>
   <si>
     <t xml:space="preserve">2.22637510299683</t>
@@ -1232,70 +1232,70 @@
     <t xml:space="preserve">2.23703336715698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24769163131714</t>
+    <t xml:space="preserve">2.24769139289856</t>
   </si>
   <si>
     <t xml:space="preserve">2.2926926612854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32111430168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25716543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30453491210938</t>
+    <t xml:space="preserve">2.32111406326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2571656703949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30453515052795</t>
   </si>
   <si>
     <t xml:space="preserve">2.29742980003357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124430656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31874585151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27848172187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2666392326355</t>
+    <t xml:space="preserve">2.25124406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3187460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27848196029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26663947105408</t>
   </si>
   <si>
     <t xml:space="preserve">2.28321862220764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32703566551208</t>
+    <t xml:space="preserve">2.32703590393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.34598350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30571961402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27729725837708</t>
+    <t xml:space="preserve">2.30571913719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27729773521423</t>
   </si>
   <si>
     <t xml:space="preserve">2.20742702484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19203186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14821529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19795322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20979595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19913721084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23348045349121</t>
+    <t xml:space="preserve">2.19203209877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1482150554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19795298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20979571342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19913744926453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23348069190979</t>
   </si>
   <si>
     <t xml:space="preserve">2.23584890365601</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">2.28085017204285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26900744438171</t>
+    <t xml:space="preserve">2.26900792121887</t>
   </si>
   <si>
     <t xml:space="preserve">2.27256059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24177002906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361227989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27019214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26308631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677153587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032421112061</t>
+    <t xml:space="preserve">2.24177050590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361275672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27019190788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26308655738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032373428345</t>
   </si>
   <si>
     <t xml:space="preserve">2.30098223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33177256584167</t>
+    <t xml:space="preserve">2.3317723274231</t>
   </si>
   <si>
     <t xml:space="preserve">2.32821989059448</t>
@@ -1340,43 +1340,43 @@
     <t xml:space="preserve">2.31519341468811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41585350036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41940665245056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43717050552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48098754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53309345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56743669509888</t>
+    <t xml:space="preserve">2.39098477363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41585397720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41940641403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4371702671051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48098707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53309369087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56743693351746</t>
   </si>
   <si>
     <t xml:space="preserve">2.54612040519714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56151556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57572627067566</t>
+    <t xml:space="preserve">2.56151580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57572650909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.56862092018127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57691097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56980538368225</t>
+    <t xml:space="preserve">2.57691073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56980514526367</t>
   </si>
   <si>
     <t xml:space="preserve">2.56625247001648</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.63967561721802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65743970870972</t>
+    <t xml:space="preserve">2.65743899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.66691303253174</t>
@@ -1394,37 +1394,37 @@
     <t xml:space="preserve">2.63671493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62960934638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58105564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57158160209656</t>
+    <t xml:space="preserve">2.62960910797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5810558795929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57158136367798</t>
   </si>
   <si>
     <t xml:space="preserve">2.56921339035034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48039507865906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53013324737549</t>
+    <t xml:space="preserve">2.48039531707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53013277053833</t>
   </si>
   <si>
     <t xml:space="preserve">2.45611786842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48217129707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44605207443237</t>
+    <t xml:space="preserve">2.48217105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44605183601379</t>
   </si>
   <si>
     <t xml:space="preserve">2.4069721698761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42236709594727</t>
+    <t xml:space="preserve">2.42236685752869</t>
   </si>
   <si>
     <t xml:space="preserve">2.4709210395813</t>
@@ -1436,79 +1436,79 @@
     <t xml:space="preserve">2.44723606109619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46559190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.473881483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41881442070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40934038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43480181694031</t>
+    <t xml:space="preserve">2.4655921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47388172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41881465911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40934014320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43480157852173</t>
   </si>
   <si>
     <t xml:space="preserve">2.40756416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3264434337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33473300933838</t>
+    <t xml:space="preserve">2.32644367218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33473348617554</t>
   </si>
   <si>
     <t xml:space="preserve">2.35190463066101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39631390571594</t>
+    <t xml:space="preserve">2.39631414413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.37440538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35782599449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42591977119446</t>
+    <t xml:space="preserve">2.357825756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
     <t xml:space="preserve">2.36611557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3862476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39986658096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32881212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35249662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302258491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499737739563</t>
+    <t xml:space="preserve">2.38624811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39986681938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32881188392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3524968624115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302282333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499761581421</t>
   </si>
   <si>
     <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39809012413025</t>
+    <t xml:space="preserve">2.39809036254883</t>
   </si>
   <si>
     <t xml:space="preserve">2.38565564155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41230082511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41822242736816</t>
+    <t xml:space="preserve">2.4123010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41822266578674</t>
   </si>
   <si>
     <t xml:space="preserve">2.45078897476196</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">2.54315996170044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54079127311707</t>
+    <t xml:space="preserve">2.54079151153564</t>
   </si>
   <si>
     <t xml:space="preserve">2.54375195503235</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">2.58756875991821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61066126823425</t>
+    <t xml:space="preserve">2.61066150665283</t>
   </si>
   <si>
     <t xml:space="preserve">2.58223986625671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59408235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61480641365051</t>
+    <t xml:space="preserve">2.59408211708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61480617523193</t>
   </si>
   <si>
     <t xml:space="preserve">2.63493847846985</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">2.65803146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64204359054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67164993286133</t>
+    <t xml:space="preserve">2.64204406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67165040969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.6752028465271</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">2.57039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59526658058167</t>
+    <t xml:space="preserve">2.5934898853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
     <t xml:space="preserve">2.51059293746948</t>
@@ -1592,61 +1592,61 @@
     <t xml:space="preserve">2.48621010780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43548393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888381004333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38785004615784</t>
+    <t xml:space="preserve">2.43548345565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888333320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.387850522995</t>
   </si>
   <si>
     <t xml:space="preserve">2.3773341178894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25917887687683</t>
+    <t xml:space="preserve">2.25917863845825</t>
   </si>
   <si>
     <t xml:space="preserve">2.31176114082336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25361132621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33464956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577947616577</t>
+    <t xml:space="preserve">2.25361084938049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33464980125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577923774719</t>
   </si>
   <si>
     <t xml:space="preserve">2.2375271320343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22577357292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23567152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2498996257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23195934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23938322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371337890625</t>
+    <t xml:space="preserve">2.22577381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23567175865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24989938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319598197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23938298225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371314048767</t>
   </si>
   <si>
     <t xml:space="preserve">2.20041036605835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20968985557556</t>
+    <t xml:space="preserve">2.20968961715698</t>
   </si>
   <si>
     <t xml:space="preserve">2.22329926490784</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">2.20721530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1552517414093</t>
+    <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298696517944</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">2.0587477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05379867553711</t>
+    <t xml:space="preserve">2.05379891395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843570709229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04699420928955</t>
+    <t xml:space="preserve">2.04699397087097</t>
   </si>
   <si>
     <t xml:space="preserve">2.04946851730347</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">2.11689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10143232345581</t>
+    <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
     <t xml:space="preserve">2.14102339744568</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">2.11813473701477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08905982971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0686457157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09091591835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1063814163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12679553031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14349770545959</t>
+    <t xml:space="preserve">2.08906030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06864595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09091544151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10638093948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12679529190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14349794387817</t>
   </si>
   <si>
     <t xml:space="preserve">2.13793063163757</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473509788513</t>
+    <t xml:space="preserve">2.14473533630371</t>
   </si>
   <si>
     <t xml:space="preserve">2.18061470985413</t>
@@ -1736,40 +1736,40 @@
     <t xml:space="preserve">2.20102906227112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09029698371887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916778564453</t>
+    <t xml:space="preserve">2.09029722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1243212223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699963569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916754722595</t>
   </si>
   <si>
     <t xml:space="preserve">2.1199905872345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07730603218079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07235717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11937212944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20474076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28392314910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23319673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19174981117249</t>
+    <t xml:space="preserve">2.07730650901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07235741615295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11937236785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20474052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28392338752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23319697380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19174957275391</t>
   </si>
   <si>
     <t xml:space="preserve">2.24309492111206</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">2.25299263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26969528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711844444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25608587265015</t>
+    <t xml:space="preserve">2.26969504356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25608563423157</t>
   </si>
   <si>
     <t xml:space="preserve">2.24185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19917273521423</t>
+    <t xml:space="preserve">2.19917321205139</t>
   </si>
   <si>
     <t xml:space="preserve">2.2220618724823</t>
@@ -1814,91 +1814,91 @@
     <t xml:space="preserve">2.3699107170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33712434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33836150169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3340311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3600127696991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40145993232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4163064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41445088386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42063665390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45589852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44352579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47012591362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48682904243469</t>
+    <t xml:space="preserve">2.33712387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33836126327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33403086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36001300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40145969390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41630673408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41445112228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42063689231873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45589804649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44352602958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47012615203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48682856559753</t>
   </si>
   <si>
     <t xml:space="preserve">2.50600600242615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37300372123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.367436170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30743074417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795281410217</t>
+    <t xml:space="preserve">2.37300395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36743640899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30743098258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37795305252075</t>
   </si>
   <si>
     <t xml:space="preserve">2.36496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27093243598938</t>
+    <t xml:space="preserve">2.27093267440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.28083038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19793605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1985547542572</t>
+    <t xml:space="preserve">2.19793581962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19855427742004</t>
   </si>
   <si>
     <t xml:space="preserve">2.20907115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1830894947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17504715919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19979166984558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16824245452881</t>
+    <t xml:space="preserve">2.18308925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17504739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16824269294739</t>
   </si>
   <si>
     <t xml:space="preserve">2.15648889541626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09772038459778</t>
+    <t xml:space="preserve">2.09772062301636</t>
   </si>
   <si>
     <t xml:space="preserve">2.13978624343872</t>
@@ -1907,25 +1907,25 @@
     <t xml:space="preserve">2.12184643745422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19669890403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17381024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21525692939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24247622489929</t>
+    <t xml:space="preserve">2.19669842720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17381000518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21525716781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.24433207511902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2474250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25979709625244</t>
+    <t xml:space="preserve">2.24742484092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25979733467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.33217525482178</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.26598358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26227211952209</t>
+    <t xml:space="preserve">2.26227164268494</t>
   </si>
   <si>
     <t xml:space="preserve">2.28825354576111</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">2.2041220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15834498405457</t>
+    <t xml:space="preserve">2.15834474563599</t>
   </si>
   <si>
     <t xml:space="preserve">2.13731169700623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23443460464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22639203071594</t>
+    <t xml:space="preserve">2.2344343662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22639226913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949069976807</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">2.23381567001343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15277719497681</t>
+    <t xml:space="preserve">2.15277695655823</t>
   </si>
   <si>
     <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15401434898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18556356430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21278238296509</t>
+    <t xml:space="preserve">2.15401458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18556380271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21278262138367</t>
   </si>
   <si>
     <t xml:space="preserve">2.19607996940613</t>
@@ -1997,19 +1997,19 @@
     <t xml:space="preserve">2.1762843132019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14040517807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27959299087524</t>
+    <t xml:space="preserve">2.14040493965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27959322929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.3241331577301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31794691085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35073351860046</t>
+    <t xml:space="preserve">2.31794714927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35073375701904</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846921920776</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">2.41012048721313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43053507804871</t>
+    <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
     <t xml:space="preserve">2.32227730751038</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">2.37424111366272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41259503364563</t>
+    <t xml:space="preserve">2.41259527206421</t>
   </si>
   <si>
     <t xml:space="preserve">2.43424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44971203804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55116486549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260612487793</t>
+    <t xml:space="preserve">2.44971179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342373847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930853843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55116438865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260636329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.47321915626526</t>
@@ -2057,55 +2057,55 @@
     <t xml:space="preserve">2.50043845176697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5152850151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52394556999207</t>
+    <t xml:space="preserve">2.51528525352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52394580841064</t>
   </si>
   <si>
     <t xml:space="preserve">2.46208429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32908225059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36124992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42620468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4410514831543</t>
+    <t xml:space="preserve">2.32908248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36125016212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42620444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44105124473572</t>
   </si>
   <si>
     <t xml:space="preserve">2.37609696388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45713520050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4509494304657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47507524490356</t>
+    <t xml:space="preserve">2.45713496208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45094895362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47507500648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46579599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47569370269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49054026603699</t>
+    <t xml:space="preserve">2.47569394111633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49054050445557</t>
   </si>
   <si>
     <t xml:space="preserve">2.4818799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47878670692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4954891204834</t>
+    <t xml:space="preserve">2.47878694534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49548888206482</t>
   </si>
   <si>
     <t xml:space="preserve">2.50662446022034</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">2.52889442443848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53446173667908</t>
+    <t xml:space="preserve">2.53446221351624</t>
   </si>
   <si>
     <t xml:space="preserve">2.50786161422729</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">2.55302023887634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601119041443</t>
+    <t xml:space="preserve">2.56601142883301</t>
   </si>
   <si>
     <t xml:space="preserve">2.58147668838501</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">2.68292951583862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69901347160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68231058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66870141029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179441452026</t>
+    <t xml:space="preserve">2.69901323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68231105804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66870164871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179417610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.69282746315002</t>
@@ -2156,46 +2156,46 @@
     <t xml:space="preserve">2.71014857292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74664664268494</t>
+    <t xml:space="preserve">2.74664688110352</t>
   </si>
   <si>
     <t xml:space="preserve">2.76396799087524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72994446754456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83696413040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83448958396912</t>
+    <t xml:space="preserve">2.7299439907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83696460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8344898223877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86109042167664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85057306289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79799199104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716280937195</t>
+    <t xml:space="preserve">2.85057377815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79799151420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716328620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.76025605201721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78500032424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78994989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82087993621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83943867683411</t>
+    <t xml:space="preserve">2.78500056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78994965553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82088017463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83943891525269</t>
   </si>
   <si>
     <t xml:space="preserve">2.83882021903992</t>
@@ -2204,31 +2204,31 @@
     <t xml:space="preserve">2.79737305641174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81160116195679</t>
+    <t xml:space="preserve">2.81160092353821</t>
   </si>
   <si>
     <t xml:space="preserve">2.78685665130615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79922866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80603337287903</t>
+    <t xml:space="preserve">2.79922890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80603361129761</t>
   </si>
   <si>
     <t xml:space="preserve">2.81778717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79551768302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7441725730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65694761276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014290809631</t>
+    <t xml:space="preserve">2.79551720619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74417209625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65694785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014314651489</t>
   </si>
   <si>
     <t xml:space="preserve">2.59137487411499</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">2.66560816764832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73056292533875</t>
+    <t xml:space="preserve">2.73056268692017</t>
   </si>
   <si>
     <t xml:space="preserve">2.79984736442566</t>
@@ -2249,19 +2249,19 @@
     <t xml:space="preserve">2.76334929466248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75045776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75625896453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79106664657593</t>
+    <t xml:space="preserve">2.7504575252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75625872612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79106616973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.68084192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79235553741455</t>
+    <t xml:space="preserve">2.79235577583313</t>
   </si>
   <si>
     <t xml:space="preserve">2.72596311569214</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">2.68148636817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62863039970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65892601013184</t>
+    <t xml:space="preserve">2.6286301612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65892577171326</t>
   </si>
   <si>
     <t xml:space="preserve">2.66279339790344</t>
@@ -2285,22 +2285,22 @@
     <t xml:space="preserve">2.68664360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66666078567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65183520317078</t>
+    <t xml:space="preserve">2.66666102409363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65183544158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.66472697257996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68857669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69437837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68986630439758</t>
+    <t xml:space="preserve">2.6885769367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6943781375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.689866065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72016167640686</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">2.69695663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65247988700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953536987305</t>
+    <t xml:space="preserve">2.65248012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953513145447</t>
   </si>
   <si>
     <t xml:space="preserve">2.75303602218628</t>
@@ -2327,100 +2327,100 @@
     <t xml:space="preserve">2.76205992698669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75883722305298</t>
+    <t xml:space="preserve">2.7588369846344</t>
   </si>
   <si>
     <t xml:space="preserve">2.79428958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76077103614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79944586753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.820072889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86197090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9116051197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90773677825928</t>
+    <t xml:space="preserve">2.76077079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79944610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82007312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86197137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91160464286804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90773701667786</t>
   </si>
   <si>
     <t xml:space="preserve">2.89162230491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8948450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97477412223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96832847595215</t>
+    <t xml:space="preserve">2.89484524726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414757728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97477388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96832823753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.97541904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98702096939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96897268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735238075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91805005073547</t>
+    <t xml:space="preserve">2.98702144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96897292137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735261917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91804981231689</t>
   </si>
   <si>
     <t xml:space="preserve">3.04181146621704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02118420600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0366542339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03923296928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04825735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829243659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9889554977417</t>
+    <t xml:space="preserve">3.02118396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03665447235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03923320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04825711250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155117988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98895502090454</t>
   </si>
   <si>
     <t xml:space="preserve">2.90902590751648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86003732681274</t>
+    <t xml:space="preserve">2.86003756523132</t>
   </si>
   <si>
     <t xml:space="preserve">2.84263348579407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78655433654785</t>
+    <t xml:space="preserve">2.78655409812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.7659273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83812165260315</t>
+    <t xml:space="preserve">2.83812117576599</t>
   </si>
   <si>
     <t xml:space="preserve">2.73434281349182</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">2.84843516349792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87421846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95608115196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94770121574402</t>
+    <t xml:space="preserve">2.87421822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95608139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9477014541626</t>
   </si>
   <si>
     <t xml:space="preserve">2.91869473457336</t>
@@ -2447,16 +2447,16 @@
     <t xml:space="preserve">2.91676115989685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94705700874329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9103147983551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96510577201843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94576787948608</t>
+    <t xml:space="preserve">2.94705677032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91031503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96510529518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94576811790466</t>
   </si>
   <si>
     <t xml:space="preserve">2.94125556945801</t>
@@ -2465,49 +2465,49 @@
     <t xml:space="preserve">2.94383382797241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97606348991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9547917842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95801496505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98959994316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05921506881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11013722419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10884809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.080486536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11464953422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10240244865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09853482246399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06372714042664</t>
+    <t xml:space="preserve">2.97606301307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95479226112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95801472663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98959922790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05921530723572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11013770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10884833335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08048629760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10240292549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09853529930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06372690200806</t>
   </si>
   <si>
     <t xml:space="preserve">3.10175776481628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12431883811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14945793151855</t>
+    <t xml:space="preserve">3.12431859970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14945769309998</t>
   </si>
   <si>
     <t xml:space="preserve">3.13592123985291</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">3.07661867141724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05663657188416</t>
+    <t xml:space="preserve">3.05663681030273</t>
   </si>
   <si>
     <t xml:space="preserve">3.02698612213135</t>
@@ -2525,85 +2525,85 @@
     <t xml:space="preserve">3.07275176048279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04696798324585</t>
+    <t xml:space="preserve">3.04696822166443</t>
   </si>
   <si>
     <t xml:space="preserve">3.0875768661499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12560749053955</t>
+    <t xml:space="preserve">3.12560796737671</t>
   </si>
   <si>
     <t xml:space="preserve">3.19071102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15396952629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15010261535645</t>
+    <t xml:space="preserve">3.15397000312805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15010213851929</t>
   </si>
   <si>
     <t xml:space="preserve">3.17781925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20553660392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22680807113647</t>
+    <t xml:space="preserve">3.20553684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22680759429932</t>
   </si>
   <si>
     <t xml:space="preserve">3.22165155410767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21262741088867</t>
+    <t xml:space="preserve">3.21262717247009</t>
   </si>
   <si>
     <t xml:space="preserve">3.23325395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25001311302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21391654014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23969960212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26548337936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24743461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229599952698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388073921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739953041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447196006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185813903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3995578289032</t>
+    <t xml:space="preserve">3.25001287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21391630172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23969984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26548361778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24743485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22229528427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388050079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739905357361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447243690491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39955806732178</t>
   </si>
   <si>
     <t xml:space="preserve">3.41116046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43307685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49108934402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304081916809</t>
+    <t xml:space="preserve">3.43307638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49108910560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304058074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.43823289871216</t>
@@ -2612,64 +2612,64 @@
     <t xml:space="preserve">3.45370268821716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39311218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41631722450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41502785682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41373896598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44596815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987110137939</t>
+    <t xml:space="preserve">3.39311170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600347518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41631698608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4150276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.413738489151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44596767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987062454224</t>
   </si>
   <si>
     <t xml:space="preserve">3.42920875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3454122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994222640991</t>
+    <t xml:space="preserve">3.34541249275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994198799133</t>
   </si>
   <si>
     <t xml:space="preserve">3.38924407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38795495033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34799027442932</t>
+    <t xml:space="preserve">3.38795566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3479905128479</t>
   </si>
   <si>
     <t xml:space="preserve">3.29126691818237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32865285873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36861729621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43049764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43694376945496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42405200004578</t>
+    <t xml:space="preserve">3.2719292640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32865262031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43049788475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43694353103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42405128479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.42147374153137</t>
@@ -2678,37 +2678,37 @@
     <t xml:space="preserve">3.4781973361969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45499229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37635183334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513478279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35572528839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22938632965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30544757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33252048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576108932495</t>
+    <t xml:space="preserve">3.45499205589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37635278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513430595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35572576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032686233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22938656806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30544781684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3325207233429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576132774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.23841071128845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14752316474915</t>
+    <t xml:space="preserve">3.14752340316772</t>
   </si>
   <si>
     <t xml:space="preserve">3.18490982055664</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">3.16815066337585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17395186424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09982395172119</t>
+    <t xml:space="preserve">3.17395162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205361366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09982419013977</t>
   </si>
   <si>
     <t xml:space="preserve">3.12238478660583</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">3.11593890190125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1462345123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02182936668396</t>
+    <t xml:space="preserve">3.14623475074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0218288898468</t>
   </si>
   <si>
     <t xml:space="preserve">2.96703934669495</t>
@@ -2750,43 +2750,43 @@
     <t xml:space="preserve">3.00958228111267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0431010723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09466743469238</t>
+    <t xml:space="preserve">3.04310059547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09466791152954</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848207473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18297600746155</t>
+    <t xml:space="preserve">3.15848159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18297624588013</t>
   </si>
   <si>
     <t xml:space="preserve">3.4008469581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854664802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54394602775574</t>
+    <t xml:space="preserve">3.44854640960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54394578933716</t>
   </si>
   <si>
     <t xml:space="preserve">3.47561931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39440059661865</t>
+    <t xml:space="preserve">3.39440083503723</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14236688613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01409435272217</t>
+    <t xml:space="preserve">3.1423671245575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01409411430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.88582110404968</t>
@@ -2807,25 +2807,25 @@
     <t xml:space="preserve">2.24896812438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15936994552612</t>
+    <t xml:space="preserve">2.1593701839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.17741870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646706581116</t>
+    <t xml:space="preserve">1.79646694660187</t>
   </si>
   <si>
     <t xml:space="preserve">1.88993239402771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76617133617401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68817591667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62500655651093</t>
+    <t xml:space="preserve">1.76617169380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68817639350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62500643730164</t>
   </si>
   <si>
     <t xml:space="preserve">1.91313743591309</t>
@@ -2840,31 +2840,31 @@
     <t xml:space="preserve">1.93827641010284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94149959087372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04141020774841</t>
+    <t xml:space="preserve">1.94149947166443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04141044616699</t>
   </si>
   <si>
     <t xml:space="preserve">1.90669167041779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923448562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02013897895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05236840248108</t>
+    <t xml:space="preserve">1.94923424720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02013921737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05236864089966</t>
   </si>
   <si>
     <t xml:space="preserve">1.98662054538727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11295986175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12327313423157</t>
+    <t xml:space="preserve">2.11295962333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12327337265015</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912779808044</t>
@@ -2873,28 +2873,28 @@
     <t xml:space="preserve">2.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09104371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92087280750275</t>
+    <t xml:space="preserve">2.0910439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278848171234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92087244987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.93892109394073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90282392501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83063018321991</t>
+    <t xml:space="preserve">1.9028240442276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">1.89766728878021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8938000202179</t>
+    <t xml:space="preserve">1.89379966259003</t>
   </si>
   <si>
     <t xml:space="preserve">1.99693393707275</t>
@@ -2903,37 +2903,37 @@
     <t xml:space="preserve">2.06010365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05623626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02658486366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02529573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04463362693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04721212387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05752491950989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01627159118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0175609588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790943622589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97243916988373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32651376724243</t>
+    <t xml:space="preserve">2.05623602867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02658534049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02529549598694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04463338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04721188545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05752515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0162718296051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01756072044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9724395275116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32651424407959</t>
   </si>
   <si>
     <t xml:space="preserve">2.22702980041504</t>
@@ -2948,31 +2948,31 @@
     <t xml:space="preserve">2.21992373466492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28387808799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27535033226013</t>
+    <t xml:space="preserve">2.28387784957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27535080909729</t>
   </si>
   <si>
     <t xml:space="preserve">2.26540231704712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31372356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24266314506531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25687527656555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39046835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52406191825867</t>
+    <t xml:space="preserve">2.31372332572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24266266822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25687503814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39046859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46863484382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52406167984009</t>
   </si>
   <si>
     <t xml:space="preserve">2.63633704185486</t>
@@ -2984,22 +2984,22 @@
     <t xml:space="preserve">2.56669807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48995304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37909913063049</t>
+    <t xml:space="preserve">2.48995280265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37909889221191</t>
   </si>
   <si>
     <t xml:space="preserve">2.38336253166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38762593269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47005605697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44873785972595</t>
+    <t xml:space="preserve">2.38762617111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44873809814453</t>
   </si>
   <si>
     <t xml:space="preserve">2.47574067115784</t>
@@ -3008,34 +3008,34 @@
     <t xml:space="preserve">2.451580286026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44021058082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40325903892517</t>
+    <t xml:space="preserve">2.44021081924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40325927734375</t>
   </si>
   <si>
     <t xml:space="preserve">2.41889262199402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42457699775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48284697532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46010756492615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43310475349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53258895874023</t>
+    <t xml:space="preserve">2.42457747459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48284649848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46010732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43310451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53258872032166</t>
   </si>
   <si>
     <t xml:space="preserve">2.53116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55817055702209</t>
+    <t xml:space="preserve">2.55817031860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.57238292694092</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">2.53685259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5652768611908</t>
+    <t xml:space="preserve">2.56527638435364</t>
   </si>
   <si>
     <t xml:space="preserve">2.60933423042297</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">2.63207364082336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6548125743866</t>
+    <t xml:space="preserve">2.65481305122375</t>
   </si>
   <si>
     <t xml:space="preserve">2.67755174636841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65907669067383</t>
+    <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
     <t xml:space="preserve">2.76424551010132</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">2.64770674705505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61501908302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60649156570435</t>
+    <t xml:space="preserve">2.61501884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60649180412292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4572651386261</t>
@@ -3089,91 +3089,91 @@
     <t xml:space="preserve">2.54680109024048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66049742698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68465828895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75287580490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89073276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768430709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89641785621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92199945449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86373019218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83388447761536</t>
+    <t xml:space="preserve">2.67186737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66049766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68465805053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7528760433197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89073252677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768406867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89641809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92199969291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86372995376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83388471603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.88931179046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84951853752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8409903049469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91773557662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93479037284851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95895075798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94615983963013</t>
+    <t xml:space="preserve">2.84951782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099078178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91773581504822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93479061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95895099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94616007804871</t>
   </si>
   <si>
     <t xml:space="preserve">2.94900226593018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87083578109741</t>
+    <t xml:space="preserve">2.87083601951599</t>
   </si>
   <si>
     <t xml:space="preserve">2.88789057731628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85378122329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81256675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78556394577026</t>
+    <t xml:space="preserve">2.8537814617157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81256651878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78556370735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.90068125724792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87794208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94189620018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95184469223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9575297832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93621158599854</t>
+    <t xml:space="preserve">2.87794232368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94189643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95184445381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95753002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93621134757996</t>
   </si>
   <si>
     <t xml:space="preserve">2.91489362716675</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">2.74861240386963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6960277557373</t>
+    <t xml:space="preserve">2.69602799415588</t>
   </si>
   <si>
     <t xml:space="preserve">2.70455503463745</t>
@@ -3200,55 +3200,55 @@
     <t xml:space="preserve">2.72729420661926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66902494430542</t>
+    <t xml:space="preserve">2.66902470588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.6505491733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64912819862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61075520515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68039464950562</t>
+    <t xml:space="preserve">2.6491277217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.610755443573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68039441108704</t>
   </si>
   <si>
     <t xml:space="preserve">2.62354612350464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63065195083618</t>
+    <t xml:space="preserve">2.63065218925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.61359786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56243419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45868635177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5027437210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48853182792664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49705910682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52690434455872</t>
+    <t xml:space="preserve">2.56243443489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45868611335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50274395942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48853158950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52690410614014</t>
   </si>
   <si>
     <t xml:space="preserve">2.48568916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42741966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3989953994751</t>
+    <t xml:space="preserve">2.42741990089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39899587631226</t>
   </si>
   <si>
     <t xml:space="preserve">2.37199258804321</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">2.25403261184692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23129367828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276616096497</t>
+    <t xml:space="preserve">2.23129320144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276639938354</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3947319984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56385540962219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52264046669006</t>
+    <t xml:space="preserve">2.39473176002502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56385564804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52264070510864</t>
   </si>
   <si>
     <t xml:space="preserve">2.52832531929016</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">2.93052673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90920877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81967258453369</t>
+    <t xml:space="preserve">2.90920853614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81967282295227</t>
   </si>
   <si>
     <t xml:space="preserve">2.80972409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78840613365173</t>
+    <t xml:space="preserve">2.78840589523315</t>
   </si>
   <si>
     <t xml:space="preserve">2.78130006790161</t>
@@ -3323,67 +3323,67 @@
     <t xml:space="preserve">2.78272128105164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77561497688293</t>
+    <t xml:space="preserve">2.77561473846436</t>
   </si>
   <si>
     <t xml:space="preserve">2.70597624778748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70739722251892</t>
+    <t xml:space="preserve">2.7073974609375</t>
   </si>
   <si>
     <t xml:space="preserve">2.7130823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75998210906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7983546257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72871518135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75429701805115</t>
+    <t xml:space="preserve">2.75998187065125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79835438728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72871541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75429725646973</t>
   </si>
   <si>
     <t xml:space="preserve">2.75571846961975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79266953468323</t>
+    <t xml:space="preserve">2.79266977310181</t>
   </si>
   <si>
     <t xml:space="preserve">2.77419424057007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77845764160156</t>
+    <t xml:space="preserve">2.77845788002014</t>
   </si>
   <si>
     <t xml:space="preserve">2.75713968276978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83246374130249</t>
+    <t xml:space="preserve">2.83246350288391</t>
   </si>
   <si>
     <t xml:space="preserve">2.8608877658844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85946655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91347217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88646936416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8424117565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76993012428284</t>
+    <t xml:space="preserve">2.85946679115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91347193717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88646912574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88362717628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84241199493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76993060112</t>
   </si>
   <si>
     <t xml:space="preserve">2.7471911907196</t>
@@ -3392,70 +3392,70 @@
     <t xml:space="preserve">2.79551219940186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67897319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68181538581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.745769739151</t>
+    <t xml:space="preserve">2.67897343635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68181562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74577021598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.64344310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57522511482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64486408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80546045303345</t>
+    <t xml:space="preserve">2.57522535324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.644864320755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80546069145203</t>
   </si>
   <si>
     <t xml:space="preserve">2.86657238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758105278015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13233780860901</t>
+    <t xml:space="preserve">2.94758129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13233828544617</t>
   </si>
   <si>
     <t xml:space="preserve">3.10533499717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18350124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13944411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15791916847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12665343284607</t>
+    <t xml:space="preserve">3.18350148200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14939260482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13944435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15791988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12665319442749</t>
   </si>
   <si>
     <t xml:space="preserve">3.03995943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742700576782</t>
+    <t xml:space="preserve">2.97742629051208</t>
   </si>
   <si>
     <t xml:space="preserve">3.01153540611267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03427481651306</t>
+    <t xml:space="preserve">3.03427505493164</t>
   </si>
   <si>
     <t xml:space="preserve">3.08259558677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13375902175903</t>
+    <t xml:space="preserve">3.13375926017761</t>
   </si>
   <si>
     <t xml:space="preserve">3.11812591552734</t>
@@ -3470,43 +3470,43 @@
     <t xml:space="preserve">3.16928935050964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21192574501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25171899795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479709148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30004000663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28867053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435563087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3014612197876</t>
+    <t xml:space="preserve">3.21192526817322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25171947479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14797067642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30004024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28867030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435586929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30146145820618</t>
   </si>
   <si>
     <t xml:space="preserve">3.32562184333801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30572533607483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41942119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36967921257019</t>
+    <t xml:space="preserve">3.30572557449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3526246547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110018730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41942143440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36967968940735</t>
   </si>
   <si>
     <t xml:space="preserve">3.26450991630554</t>
@@ -3518,22 +3518,22 @@
     <t xml:space="preserve">3.3085675239563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40947318077087</t>
+    <t xml:space="preserve">3.40947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.37962794303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38247060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40378832817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42013192176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32846450805664</t>
+    <t xml:space="preserve">3.38247036933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40378785133362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42013239860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32846474647522</t>
   </si>
   <si>
     <t xml:space="preserve">3.29790830612183</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">3.34978246688843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42723798751831</t>
+    <t xml:space="preserve">3.42723822593689</t>
   </si>
   <si>
     <t xml:space="preserve">3.44500327110291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32206916809082</t>
+    <t xml:space="preserve">3.32206869125366</t>
   </si>
   <si>
     <t xml:space="preserve">3.28014373779297</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">3.31567358970642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33201694488525</t>
+    <t xml:space="preserve">3.33201742172241</t>
   </si>
   <si>
     <t xml:space="preserve">3.3043041229248</t>
@@ -3578,22 +3578,22 @@
     <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28440713882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23679685592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31212043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27232694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31283116340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42226433753967</t>
+    <t xml:space="preserve">3.28440690040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23679637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31212019920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31283140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42226409912109</t>
   </si>
   <si>
     <t xml:space="preserve">3.48550748825073</t>
@@ -3602,13 +3602,13 @@
     <t xml:space="preserve">3.47555875778198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4954559803009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48124432563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57575416564941</t>
+    <t xml:space="preserve">3.49545645713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48124408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57575392723083</t>
   </si>
   <si>
     <t xml:space="preserve">3.58143901824951</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">3.53027582168579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49829864501953</t>
+    <t xml:space="preserve">3.49829792976379</t>
   </si>
   <si>
     <t xml:space="preserve">3.52459096908569</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">3.61421179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52383756637573</t>
+    <t xml:space="preserve">3.52383780479431</t>
   </si>
   <si>
     <t xml:space="preserve">3.38902974128723</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">3.43120408058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41614174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44927906990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48919415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46584820747375</t>
+    <t xml:space="preserve">3.41614198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44927930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48919439315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46584796905518</t>
   </si>
   <si>
     <t xml:space="preserve">3.47488498687744</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">3.45831632614136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.488440990448</t>
+    <t xml:space="preserve">3.48844122886658</t>
   </si>
   <si>
     <t xml:space="preserve">3.46132922172546</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">3.4507851600647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44626641273499</t>
+    <t xml:space="preserve">3.44626688957214</t>
   </si>
   <si>
     <t xml:space="preserve">3.44099473953247</t>
@@ -3671,49 +3671,49 @@
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752341270447</t>
+    <t xml:space="preserve">3.38752365112305</t>
   </si>
   <si>
     <t xml:space="preserve">3.36041116714478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32501459121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24744319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27229619026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23765277862549</t>
+    <t xml:space="preserve">3.32501482963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24744343757629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27229642868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23765301704407</t>
   </si>
   <si>
     <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28359317779541</t>
+    <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
     <t xml:space="preserve">3.21430635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24970269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279580116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37698006629944</t>
+    <t xml:space="preserve">3.24970293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279556274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062050819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37697982788086</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29488968849182</t>
+    <t xml:space="preserve">3.29489016532898</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731877326965</t>
@@ -3725,19 +3725,19 @@
     <t xml:space="preserve">3.316730260849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33329892158508</t>
+    <t xml:space="preserve">3.33329916000366</t>
   </si>
   <si>
     <t xml:space="preserve">3.32953333854675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112410545349</t>
+    <t xml:space="preserve">3.29112434387207</t>
   </si>
   <si>
     <t xml:space="preserve">3.28208661079407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14878511428833</t>
+    <t xml:space="preserve">3.14878535270691</t>
   </si>
   <si>
     <t xml:space="preserve">3.19999718666077</t>
@@ -3746,85 +3746,85 @@
     <t xml:space="preserve">3.32802724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33028674125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33480525016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38601684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37321400642395</t>
+    <t xml:space="preserve">3.33028650283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33480501174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3860170841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37321448326111</t>
   </si>
   <si>
     <t xml:space="preserve">3.4221670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4071044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38149785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42141366004944</t>
+    <t xml:space="preserve">3.40710425376892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38149833679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42141389846802</t>
   </si>
   <si>
     <t xml:space="preserve">3.37170791625977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36643624305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39204216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48994708061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61797761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60592794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647129058838</t>
+    <t xml:space="preserve">3.36643600463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39204239845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48994755744934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61797714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60592770576477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647081375122</t>
   </si>
   <si>
     <t xml:space="preserve">3.65337419509888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63981819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078045845032</t>
+    <t xml:space="preserve">3.63981795310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307806968689</t>
   </si>
   <si>
     <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72040152549744</t>
+    <t xml:space="preserve">3.72040176391602</t>
   </si>
   <si>
     <t xml:space="preserve">3.6752142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66542434692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75052618980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77462577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77311944961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79872560501099</t>
+    <t xml:space="preserve">3.66542387008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75052690505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7746262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77311992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79872608184814</t>
   </si>
   <si>
     <t xml:space="preserve">3.77613210678101</t>
@@ -3833,94 +3833,94 @@
     <t xml:space="preserve">3.7821569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76709461212158</t>
+    <t xml:space="preserve">3.76709413528442</t>
   </si>
   <si>
     <t xml:space="preserve">3.78667593002319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73696970939636</t>
+    <t xml:space="preserve">3.7369704246521</t>
   </si>
   <si>
     <t xml:space="preserve">3.77763843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71663618087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71588277816772</t>
+    <t xml:space="preserve">3.71663570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71588230133057</t>
   </si>
   <si>
     <t xml:space="preserve">3.70533895492554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63755869865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68726396560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699423789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638589859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72567343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67144870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258104324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429177284241</t>
+    <t xml:space="preserve">3.6375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68726420402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72567367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67144894599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258128166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6413242816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429153442383</t>
   </si>
   <si>
     <t xml:space="preserve">3.75203227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80926918983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450135231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80625700950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84541916847229</t>
+    <t xml:space="preserve">3.80926990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7445011138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80625677108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84541940689087</t>
   </si>
   <si>
     <t xml:space="preserve">3.83939409255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90717458724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006281852722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95386838912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97947430610657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9598925113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9448299407959</t>
+    <t xml:space="preserve">3.90717506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95386743545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97947359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483041763306</t>
   </si>
   <si>
     <t xml:space="preserve">3.89060592651367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88307476043701</t>
+    <t xml:space="preserve">3.88307523727417</t>
   </si>
   <si>
     <t xml:space="preserve">3.92976808547974</t>
@@ -3929,46 +3929,46 @@
     <t xml:space="preserve">3.95682597160339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99502563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01571655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96239686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95125555992126</t>
+    <t xml:space="preserve">3.99502515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01571702957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96239709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95125532150269</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97910928726196</t>
+    <t xml:space="preserve">3.9791088104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.98388361930847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95523428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00457572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98070096969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9735381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98706746101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807171821594</t>
+    <t xml:space="preserve">3.95523381233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00457525253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98070025444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01889991760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97353863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807243347168</t>
   </si>
   <si>
     <t xml:space="preserve">3.92340159416199</t>
@@ -3977,61 +3977,61 @@
     <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04277467727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98865914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97274231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90907692909241</t>
+    <t xml:space="preserve">4.04277515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98865938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9345428943634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97274279594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90907669067383</t>
   </si>
   <si>
     <t xml:space="preserve">3.89952707290649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83983969688416</t>
+    <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66078019142151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590117454529</t>
+    <t xml:space="preserve">3.67590093612671</t>
   </si>
   <si>
     <t xml:space="preserve">3.66316795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73638367652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72524213790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70057153701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76821637153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77219486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76264572143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74752497673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72922134399414</t>
+    <t xml:space="preserve">3.73638391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72524237632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70057129859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779858589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7721951007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76264595985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74752473831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72922086715698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73081278800964</t>
@@ -4043,22 +4043,22 @@
     <t xml:space="preserve">3.74513721466064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64565968513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74832081794739</t>
+    <t xml:space="preserve">3.64565944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74832105636597</t>
   </si>
   <si>
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77696990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83267760276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641579627991</t>
+    <t xml:space="preserve">3.77697038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641555786133</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
@@ -4076,52 +4076,52 @@
     <t xml:space="preserve">3.86212348937988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87008118629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554738998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146421432495</t>
+    <t xml:space="preserve">3.87008142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146469116211</t>
   </si>
   <si>
     <t xml:space="preserve">3.97115063667297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9639880657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95443820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99979996681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91942238807678</t>
+    <t xml:space="preserve">3.96398854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95443844795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91942262649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.76344132423401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80402827262878</t>
+    <t xml:space="preserve">3.80402851104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.90748476982117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95602989196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90430164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94409275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00775861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96796774864197</t>
+    <t xml:space="preserve">3.95603013038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90430188179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94409251213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96796751022339</t>
   </si>
   <si>
     <t xml:space="preserve">3.85575652122498</t>
@@ -4130,28 +4130,28 @@
     <t xml:space="preserve">3.82710719108582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03004169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01253318786621</t>
+    <t xml:space="preserve">4.03004121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01253366470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.00934982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99820923805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91623950004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85814380645752</t>
+    <t xml:space="preserve">3.99820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91623902320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8581440448761</t>
   </si>
   <si>
     <t xml:space="preserve">3.78094935417175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55414032936096</t>
+    <t xml:space="preserve">3.55414009094238</t>
   </si>
   <si>
     <t xml:space="preserve">3.69261288642883</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">3.60746026039124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42760443687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40293383598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34483933448792</t>
+    <t xml:space="preserve">3.42760491371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40293407440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34483909606934</t>
   </si>
   <si>
     <t xml:space="preserve">3.06948471069336</t>
@@ -4187,58 +4187,58 @@
     <t xml:space="preserve">3.51912403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5684654712677</t>
+    <t xml:space="preserve">3.56846499443054</t>
   </si>
   <si>
     <t xml:space="preserve">3.73797512054443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69022607803345</t>
+    <t xml:space="preserve">3.69022560119629</t>
   </si>
   <si>
     <t xml:space="preserve">3.68385934829712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70852947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354600906372</t>
+    <t xml:space="preserve">3.70852971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74036240577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354529380798</t>
   </si>
   <si>
     <t xml:space="preserve">3.90111827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92021822929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97194671630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9631929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693017959595</t>
+    <t xml:space="preserve">3.90668892860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9202184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97194647789001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693089485168</t>
   </si>
   <si>
     <t xml:space="preserve">4.03481674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06346607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02844953536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11758136749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09848260879517</t>
+    <t xml:space="preserve">4.06346654891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02845001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11758184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09848213195801</t>
   </si>
   <si>
     <t xml:space="preserve">4.12235689163208</t>
@@ -4247,22 +4247,22 @@
     <t xml:space="preserve">4.1334981918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16055631637573</t>
+    <t xml:space="preserve">4.16055679321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.16214799880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20193958282471</t>
+    <t xml:space="preserve">4.20193910598755</t>
   </si>
   <si>
     <t xml:space="preserve">4.21467208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1971640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15419006347656</t>
+    <t xml:space="preserve">4.19716501235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1541895866394</t>
   </si>
   <si>
     <t xml:space="preserve">4.11599016189575</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">4.14623165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24013900756836</t>
+    <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.19398069381714</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90509748458862</t>
+    <t xml:space="preserve">3.9050977230072</t>
   </si>
   <si>
     <t xml:space="preserve">4.00298404693604</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">4.00139188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12431669235229</t>
+    <t xml:space="preserve">4.12431621551514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">4.23011159896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24703931808472</t>
+    <t xml:space="preserve">4.24703884124756</t>
   </si>
   <si>
     <t xml:space="preserve">4.28597116470337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25042390823364</t>
+    <t xml:space="preserve">4.2504243850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.21487712860107</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">4.14124393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09723329544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19202566146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20810604095459</t>
+    <t xml:space="preserve">4.09723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19202518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20810651779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754560470581</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">4.10738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77053761482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383166313171</t>
+    <t xml:space="preserve">3.77053785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383142471313</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4370,28 +4370,28 @@
     <t xml:space="preserve">3.71213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77307677268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122736930847</t>
+    <t xml:space="preserve">3.7730770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122784614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65881824493408</t>
+    <t xml:space="preserve">3.6588180065155</t>
   </si>
   <si>
     <t xml:space="preserve">3.80100655555725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70198225975037</t>
+    <t xml:space="preserve">3.70198249816895</t>
   </si>
   <si>
     <t xml:space="preserve">3.71467781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71044611930847</t>
+    <t xml:space="preserve">3.71044564247131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66982078552246</t>
@@ -4403,25 +4403,25 @@
     <t xml:space="preserve">3.69690442085266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47177267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49123859405518</t>
+    <t xml:space="preserve">3.47177243232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4912383556366</t>
   </si>
   <si>
     <t xml:space="preserve">3.60634350776672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62919569015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53355669975281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51324415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48700666427612</t>
+    <t xml:space="preserve">3.62919545173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53355693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51324391365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48700642585754</t>
   </si>
   <si>
     <t xml:space="preserve">3.33381533622742</t>
@@ -4439,31 +4439,31 @@
     <t xml:space="preserve">3.38713598251343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26356720924377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25764274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29657554626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24325466156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2813413143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005258560181</t>
+    <t xml:space="preserve">3.26356744766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25764298439026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29657530784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24325489997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28134107589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005282402039</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860794067383</t>
+    <t xml:space="preserve">3.46415495872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860817909241</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">3.56741118431091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64358353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66135692596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64273715019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70875310897827</t>
+    <t xml:space="preserve">3.64358329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66135716438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64273691177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
     <t xml:space="preserve">3.70790696144104</t>
@@ -4499,37 +4499,37 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5597939491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46838665008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54625225067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50224113464355</t>
+    <t xml:space="preserve">3.55979347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46838688850403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54625201225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50224137306213</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50816583633423</t>
+    <t xml:space="preserve">3.50816559791565</t>
   </si>
   <si>
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61903882026672</t>
+    <t xml:space="preserve">3.54709839820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6190390586853</t>
   </si>
   <si>
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885582923889</t>
+    <t xml:space="preserve">3.49885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282864570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6791307926178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68336296081543</t>
+    <t xml:space="preserve">3.70282888412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67913103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
     <t xml:space="preserve">3.69351863861084</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">3.70706057548523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7002899646759</t>
+    <t xml:space="preserve">3.70029020309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010649681091</t>
+    <t xml:space="preserve">3.58010625839233</t>
   </si>
   <si>
     <t xml:space="preserve">3.47515749931335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44045686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38459706306458</t>
+    <t xml:space="preserve">3.4404571056366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38459730148315</t>
   </si>
   <si>
     <t xml:space="preserve">3.34735727310181</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38205814361572</t>
+    <t xml:space="preserve">3.38205790519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.3676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37613344192505</t>
+    <t xml:space="preserve">3.37613368034363</t>
   </si>
   <si>
     <t xml:space="preserve">3.31519556045532</t>
@@ -4610,19 +4610,19 @@
     <t xml:space="preserve">3.42437601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43114709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45315217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50647330284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48954582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471539497375</t>
+    <t xml:space="preserve">3.43114686012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4531524181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50647306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48954606056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471563339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4631,46 +4631,46 @@
     <t xml:space="preserve">3.58433842658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63173413276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7256805896759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370258331299</t>
+    <t xml:space="preserve">3.6317343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674778938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72568035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370210647583</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178828239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241337776184</t>
+    <t xml:space="preserve">3.85178852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241313934326</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366452217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06422519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01259660720825</t>
+    <t xml:space="preserve">3.97366428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06422472000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01259708404541</t>
   </si>
   <si>
     <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03037071228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04052639007568</t>
+    <t xml:space="preserve">4.03037023544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04052686691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.04899024963379</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391241073608</t>
+    <t xml:space="preserve">4.04391193389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">4.08623027801514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14209032058716</t>
+    <t xml:space="preserve">4.14208984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05322170257568</t>
+    <t xml:space="preserve">4.05322217941284</t>
   </si>
   <si>
     <t xml:space="preserve">4.00836515426636</t>
@@ -4718,22 +4718,22 @@
     <t xml:space="preserve">4.02359962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01344299316406</t>
+    <t xml:space="preserve">3.99990129470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01344347000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.96774005889893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00667285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.955890417099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84586381912231</t>
+    <t xml:space="preserve">4.00667238235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84586429595947</t>
   </si>
   <si>
     <t xml:space="preserve">3.78831100463867</t>
@@ -4748,64 +4748,64 @@
     <t xml:space="preserve">3.96096873283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9415020942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93219256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272592544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89325976371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96435451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03544902801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97958898544312</t>
+    <t xml:space="preserve">3.94150257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93219232559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272664070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865110397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85771298408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89326000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96435403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03544807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97958922386169</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0168285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99482297897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974537849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9973623752594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02529191970825</t>
+    <t xml:space="preserve">4.01682901382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99482321739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02529239654541</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04475831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05660772323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08792304992676</t>
+    <t xml:space="preserve">4.04475784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05660820007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0879225730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685537338257</t>
@@ -4814,28 +4814,28 @@
     <t xml:space="preserve">4.10992813110352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09638690948486</t>
+    <t xml:space="preserve">4.09638643264771</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1911792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13362646102905</t>
+    <t xml:space="preserve">4.19117879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13362598419189</t>
   </si>
   <si>
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732479095459</t>
+    <t xml:space="preserve">4.15732431411743</t>
   </si>
   <si>
     <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18271541595459</t>
+    <t xml:space="preserve">4.18271493911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4844,13 +4844,13 @@
     <t xml:space="preserve">4.19794988632202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20556735992432</t>
+    <t xml:space="preserve">4.20556688308716</t>
   </si>
   <si>
     <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21233797073364</t>
+    <t xml:space="preserve">4.2123384475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.17679071426392</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863964080811</t>
+    <t xml:space="preserve">4.18864011764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17932987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23349714279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24026823043823</t>
+    <t xml:space="preserve">4.17933034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23349666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24026775360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.27073669433594</t>
@@ -4880,37 +4880,37 @@
     <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33506059646606</t>
+    <t xml:space="preserve">4.33506011962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.29443454742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28427839279175</t>
+    <t xml:space="preserve">4.28427886962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09215497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8509418964386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784206390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85263466835022</t>
+    <t xml:space="preserve">4.09215450286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85094213485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87802505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784230232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8526349067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94658064842224</t>
+    <t xml:space="preserve">3.9465811252594</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93811702728271</t>
+    <t xml:space="preserve">3.93811678886414</t>
   </si>
   <si>
     <t xml:space="preserve">4.05491495132446</t>
@@ -4934,13 +4934,13 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29274225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32321071624756</t>
+    <t xml:space="preserve">4.28766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29274272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32321119308472</t>
   </si>
   <si>
     <t xml:space="preserve">4.3553729057312</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">4.25888776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045916557312</t>
+    <t xml:space="preserve">4.30459117889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.28258562088013</t>
@@ -4967,22 +4967,22 @@
     <t xml:space="preserve">4.23857498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32828950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938402175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37907075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34013795852661</t>
+    <t xml:space="preserve">4.32828903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37907123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34013843536377</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183120727539</t>
+    <t xml:space="preserve">4.34183168411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3398699760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072305679321</t>
+    <t xml:space="preserve">4.33531141281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33987045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072353363037</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266374588013</t>
+    <t xml:space="preserve">4.36266326904297</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369176864624</t>
+    <t xml:space="preserve">4.40369129180908</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081100463867</t>
+    <t xml:space="preserve">4.35081052780151</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5084,10 +5084,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292568206787</t>
+    <t xml:space="preserve">4.48757171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292520523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492404937744</t>
+    <t xml:space="preserve">4.43924903869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574781417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492357254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57692193984985</t>
+    <t xml:space="preserve">4.5769214630127</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59150981903076</t>
+    <t xml:space="preserve">4.5915093421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5132,7 +5132,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891935348511</t>
+    <t xml:space="preserve">4.63891983032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130603790283</t>
+    <t xml:space="preserve">4.52130556106567</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786296844482</t>
+    <t xml:space="preserve">4.58786249160767</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5168,22 +5168,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191690444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738765716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732902526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197553634644</t>
+    <t xml:space="preserve">4.73191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732950210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897798538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644662857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197505950928</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5192,10 +5192,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780481338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65533113479614</t>
+    <t xml:space="preserve">4.56780433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6553316116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5204,13 +5204,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792112350464</t>
+    <t xml:space="preserve">4.68268346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792064666748</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6845064163208</t>
+    <t xml:space="preserve">4.68450689315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5228,7 +5228,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009347915649</t>
+    <t xml:space="preserve">4.73009395599365</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174243927002</t>
+    <t xml:space="preserve">4.67174291610718</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5273,16 +5273,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70638847351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63709688186646</t>
+    <t xml:space="preserve">4.7063889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6370964050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080141067505</t>
+    <t xml:space="preserve">4.66080188751221</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903661727905</t>
+    <t xml:space="preserve">4.67903614044189</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050104141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88873624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403205871582</t>
+    <t xml:space="preserve">4.87050151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8887357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403158187866</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5318,10 +5318,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956048965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497261047363</t>
+    <t xml:space="preserve">4.85956001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497308731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5330,13 +5330,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491397857666</t>
+    <t xml:space="preserve">4.82491445541382</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756259918213</t>
+    <t xml:space="preserve">4.79756212234497</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5345,13 +5345,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932739257812</t>
+    <t xml:space="preserve">4.77932786941528</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6881537437439</t>
+    <t xml:space="preserve">4.68815422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5369,13 +5369,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714544296265</t>
+    <t xml:space="preserve">4.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602947235107</t>
+    <t xml:space="preserve">4.89602994918823</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079277038574</t>
+    <t xml:space="preserve">4.97079229354858</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23337268829346</t>
+    <t xml:space="preserve">5.2333722114563</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5429,13 +5429,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26072454452515</t>
+    <t xml:space="preserve">5.2607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078269958496</t>
+    <t xml:space="preserve">5.28078317642212</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5447,10 +5447,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216161727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709842681885</t>
+    <t xml:space="preserve">6.38216209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709890365601</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85626554489136</t>
+    <t xml:space="preserve">6.8562650680542</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5486,13 +5486,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655632019043</t>
+    <t xml:space="preserve">6.95655679702759</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632369995117</t>
+    <t xml:space="preserve">6.87632322311401</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5501,7 +5501,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86902952194214</t>
+    <t xml:space="preserve">6.8690299987793</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5522,13 +5522,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625595092773</t>
+    <t xml:space="preserve">7.16625642776489</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213474273682</t>
+    <t xml:space="preserve">7.31213426589966</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5537,13 +5537,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537355422974</t>
+    <t xml:space="preserve">7.21184301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566480636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537307739258</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5555,10 +5555,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51271629333496</t>
+    <t xml:space="preserve">7.41242551803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5127158164978</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5567,19 +5567,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5765380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580131530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.726975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682886123657</t>
+    <t xml:space="preserve">7.63124179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57653856277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72697448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682933807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5588,7 +5588,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67226982116699</t>
+    <t xml:space="preserve">7.67227029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5612,7 +5612,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2238712310791</t>
+    <t xml:space="preserve">8.22387218475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -6597,6 +6597,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.3600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3850002288818</t>
   </si>
 </sst>
 </file>
@@ -71987,7 +71990,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6910416667</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>1546443</v>
@@ -72008,6 +72011,32 @@
         <v>2194</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6910069444</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>1675314</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>19.4150009155273</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>18.8150005340576</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>19.1350002288818</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>19.3850002288818</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2195</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528841972351</t>
+    <t xml:space="preserve">2.44528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -47,103 +47,103 @@
     <t xml:space="preserve">2.50193190574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40895080566406</t>
+    <t xml:space="preserve">2.40895128250122</t>
   </si>
   <si>
     <t xml:space="preserve">2.3565821647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31490111351013</t>
+    <t xml:space="preserve">2.31490159034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.29780149459839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37261390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37795734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33413910865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2347457408905</t>
+    <t xml:space="preserve">2.37261366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3779571056366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33413887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23474550247192</t>
   </si>
   <si>
     <t xml:space="preserve">2.15458941459656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11184000968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99641573429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588387489319</t>
+    <t xml:space="preserve">2.11183977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964154958725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588411331177</t>
   </si>
   <si>
     <t xml:space="preserve">2.07977747917175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03489017486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03168392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90343475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00924038887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93549728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84037864208221</t>
+    <t xml:space="preserve">2.0348904132843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03168416023254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02954649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343463420868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00924015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93549680709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84037852287292</t>
   </si>
   <si>
     <t xml:space="preserve">1.74953544139862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75701701641083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792916297913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151142597198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6886168718338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823016166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60632348060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72922921180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899835109711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312317371368</t>
+    <t xml:space="preserve">1.75701653957367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792952060699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349858760834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151154518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861699104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55823028087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60632383823395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72922885417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67899799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312281608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.73350417613983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69396078586578</t>
+    <t xml:space="preserve">1.69396066665649</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419164657593</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">1.70571660995483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66296720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533560752869</t>
+    <t xml:space="preserve">1.66296696662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71533572673798</t>
   </si>
   <si>
     <t xml:space="preserve">1.82541632652283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82327878475189</t>
+    <t xml:space="preserve">1.82327890396118</t>
   </si>
   <si>
     <t xml:space="preserve">1.88099098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89381575584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86602878570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404150485992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556646823883</t>
+    <t xml:space="preserve">1.89381587505341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488446712494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86602854728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404138565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556658744812</t>
   </si>
   <si>
     <t xml:space="preserve">1.82648527622223</t>
@@ -188,37 +188,37 @@
     <t xml:space="preserve">1.79976618289948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053496837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442809581757</t>
+    <t xml:space="preserve">1.92053461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442821502686</t>
   </si>
   <si>
     <t xml:space="preserve">1.9322909116745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221578121185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96435296535492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183406352997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95580339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95259666442871</t>
+    <t xml:space="preserve">1.96221530437469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435308456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183430194855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95580303668976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95259702205658</t>
   </si>
   <si>
     <t xml:space="preserve">1.92374062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87564718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88312828540802</t>
+    <t xml:space="preserve">1.87564730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8831285238266</t>
   </si>
   <si>
     <t xml:space="preserve">1.91198480129242</t>
@@ -230,34 +230,34 @@
     <t xml:space="preserve">1.89167845249176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579756736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81793522834778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190396308899</t>
+    <t xml:space="preserve">1.81579780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81793487071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8019038438797</t>
   </si>
   <si>
     <t xml:space="preserve">1.87992227077484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90129709243774</t>
+    <t xml:space="preserve">1.90129733085632</t>
   </si>
   <si>
     <t xml:space="preserve">1.84465348720551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92587852478027</t>
+    <t xml:space="preserve">1.92587840557098</t>
   </si>
   <si>
     <t xml:space="preserve">1.92801594734192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9151908159256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01779055595398</t>
+    <t xml:space="preserve">1.91519093513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01779007911682</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626535415649</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">2.07443404197693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0616090297699</t>
+    <t xml:space="preserve">2.06160879135132</t>
   </si>
   <si>
     <t xml:space="preserve">2.07015919685364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02634024620056</t>
+    <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
     <t xml:space="preserve">2.0551962852478</t>
@@ -281,109 +281,109 @@
     <t xml:space="preserve">2.05092144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99855268001556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214053153992</t>
+    <t xml:space="preserve">1.99855303764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214041233063</t>
   </si>
   <si>
     <t xml:space="preserve">1.95045948028564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93977200984955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84999740123749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457895278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7912163734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73884797096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388541698456</t>
+    <t xml:space="preserve">1.93977236747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8499972820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457835674286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121625423431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73884785175323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388553619385</t>
   </si>
   <si>
     <t xml:space="preserve">1.69502925872803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70678544044495</t>
+    <t xml:space="preserve">1.70678555965424</t>
   </si>
   <si>
     <t xml:space="preserve">1.70785450935364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76235258579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700954914093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8777312040329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87546920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279733181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90601027011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451826572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80081236362457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80986130237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81438624858856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80646789073944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75104105472565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63113796710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54290676116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46711909770966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47390580177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42526614665985</t>
+    <t xml:space="preserve">1.76235294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700966835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87773144245148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87546896934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279745101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90601050853729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451814651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80081224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80986154079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81438612937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8064683675766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75104093551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6311377286911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54290688037872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46711897850037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47390592098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42526602745056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51689016819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61190795898438</t>
+    <t xml:space="preserve">1.61190783977509</t>
   </si>
   <si>
     <t xml:space="preserve">1.60059642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57684183120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69900739192963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38341307640076</t>
+    <t xml:space="preserve">1.57684195041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69900763034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38341283798218</t>
   </si>
   <si>
     <t xml:space="preserve">1.24201762676239</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">1.2725590467453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.213738322258</t>
+    <t xml:space="preserve">1.21373844146729</t>
   </si>
   <si>
     <t xml:space="preserve">1.19111502170563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23636186122894</t>
+    <t xml:space="preserve">1.23636174201965</t>
   </si>
   <si>
     <t xml:space="preserve">1.18545925617218</t>
@@ -410,100 +410,100 @@
     <t xml:space="preserve">1.0994907617569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722852706909</t>
+    <t xml:space="preserve">1.09722864627838</t>
   </si>
   <si>
     <t xml:space="preserve">1.23749279975891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28726422786713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36870789527893</t>
+    <t xml:space="preserve">1.28726410865784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36870777606964</t>
   </si>
   <si>
     <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39359354972839</t>
+    <t xml:space="preserve">1.3935934305191</t>
   </si>
   <si>
     <t xml:space="preserve">1.38454413414001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4003803730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36983895301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.398118019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37888813018799</t>
+    <t xml:space="preserve">1.40038061141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3698388338089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39811789989471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3788880109787</t>
   </si>
   <si>
     <t xml:space="preserve">1.37097024917603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37775707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42979061603546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4026426076889</t>
+    <t xml:space="preserve">1.37775719165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42979073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40264272689819</t>
   </si>
   <si>
     <t xml:space="preserve">1.38567519187927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26011598110199</t>
+    <t xml:space="preserve">1.2601158618927</t>
   </si>
   <si>
     <t xml:space="preserve">1.29631340503693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32233011722565</t>
+    <t xml:space="preserve">1.32233023643494</t>
   </si>
   <si>
     <t xml:space="preserve">1.37549471855164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43657779693604</t>
+    <t xml:space="preserve">1.43657755851746</t>
   </si>
   <si>
     <t xml:space="preserve">1.45354497432709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44788932800293</t>
+    <t xml:space="preserve">1.44788944721222</t>
   </si>
   <si>
     <t xml:space="preserve">1.47051227092743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45015168190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41961014270782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38001954555511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39698696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33137953281403</t>
+    <t xml:space="preserve">1.45015132427216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41961002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38001942634583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39698684215546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33137941360474</t>
   </si>
   <si>
     <t xml:space="preserve">1.33251047134399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38228178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3675764799118</t>
+    <t xml:space="preserve">1.38228166103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36757659912109</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816635608673</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">1.35400259494781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32798612117767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41056084632874</t>
+    <t xml:space="preserve">1.32798600196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41056060791016</t>
   </si>
   <si>
     <t xml:space="preserve">1.40377390384674</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">1.42413473129272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43883991241455</t>
+    <t xml:space="preserve">1.43884003162384</t>
   </si>
   <si>
     <t xml:space="preserve">1.45920097827911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.477299451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48748004436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48974215984344</t>
+    <t xml:space="preserve">1.47729969024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48748016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48974227905273</t>
   </si>
   <si>
     <t xml:space="preserve">1.39019989967346</t>
@@ -548,196 +548,196 @@
     <t xml:space="preserve">1.36078941822052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513377189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34947776794434</t>
+    <t xml:space="preserve">1.41282308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513389110565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34947788715363</t>
   </si>
   <si>
     <t xml:space="preserve">1.34269106388092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30536270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821469306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780540943146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28613293170929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28500163555145</t>
+    <t xml:space="preserve">1.30536282062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821457386017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780552864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28500175476074</t>
   </si>
   <si>
     <t xml:space="preserve">1.27934575080872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3517404794693</t>
+    <t xml:space="preserve">1.35174036026001</t>
   </si>
   <si>
     <t xml:space="preserve">1.35852718353271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37210130691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39472472667694</t>
+    <t xml:space="preserve">1.37210142612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39472460746765</t>
   </si>
   <si>
     <t xml:space="preserve">1.41621661186218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44110226631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49313592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52480816841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53159523010254</t>
+    <t xml:space="preserve">1.44110202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49313569068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52480852603912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53159546852112</t>
   </si>
   <si>
     <t xml:space="preserve">1.51575922966003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54856252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56553030014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61077690124512</t>
+    <t xml:space="preserve">1.54856276512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56553018093109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61077678203583</t>
   </si>
   <si>
     <t xml:space="preserve">1.63453125953674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59833407402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571089267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118618488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50444769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51802134513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47503709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6571546792984</t>
+    <t xml:space="preserve">1.59833383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50444757938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51802158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4750372171402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65715444087982</t>
   </si>
   <si>
     <t xml:space="preserve">1.69335162639618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66733503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6616792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63905596733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60172748565674</t>
+    <t xml:space="preserve">1.66733479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167914867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63905584812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60172724723816</t>
   </si>
   <si>
     <t xml:space="preserve">1.57457959651947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62661325931549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58475995063782</t>
+    <t xml:space="preserve">1.62661290168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58476006984711</t>
   </si>
   <si>
     <t xml:space="preserve">1.5610054731369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54064452648163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512089729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64923632144928</t>
+    <t xml:space="preserve">1.54064440727234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64923655986786</t>
   </si>
   <si>
     <t xml:space="preserve">1.6662038564682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049975395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741847515106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284566879272</t>
+    <t xml:space="preserve">1.62435066699982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049987316132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284614562988</t>
   </si>
   <si>
     <t xml:space="preserve">1.84492766857147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83022260665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86302626132965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85623919963837</t>
+    <t xml:space="preserve">1.83022248744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86302614212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85623931884766</t>
   </si>
   <si>
     <t xml:space="preserve">1.91053509712219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8992235660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91166627407074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92637097835541</t>
+    <t xml:space="preserve">1.89922380447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91166639328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92637133598328</t>
   </si>
   <si>
     <t xml:space="preserve">1.94560086727142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446969032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89696085453033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655180931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98066711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0134711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01573300361633</t>
+    <t xml:space="preserve">1.94446980953217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8969612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066759109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01347088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781512260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01573348045349</t>
   </si>
   <si>
     <t xml:space="preserve">2.01912665367126</t>
@@ -749,40 +749,40 @@
     <t xml:space="preserve">1.99876582622528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02025771141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727370262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007747650146</t>
+    <t xml:space="preserve">2.0202579498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727358341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007771492004</t>
   </si>
   <si>
     <t xml:space="preserve">1.9716180562973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94786310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953617572784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02252054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99084770679474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08247208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08699631690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05079936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193066596985</t>
+    <t xml:space="preserve">1.94786334037781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02252006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99084758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247137069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08699655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193042755127</t>
   </si>
   <si>
     <t xml:space="preserve">1.93542075157166</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">1.9320273399353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96709334850311</t>
+    <t xml:space="preserve">1.96709311008453</t>
   </si>
   <si>
     <t xml:space="preserve">2.00894641876221</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">1.90940392017365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89130532741547</t>
+    <t xml:space="preserve">1.89130520820618</t>
   </si>
   <si>
     <t xml:space="preserve">1.873206615448</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">1.87999367713928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85510766506195</t>
+    <t xml:space="preserve">1.85510790348053</t>
   </si>
   <si>
     <t xml:space="preserve">1.96596205234528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03609395027161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424111843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0021595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00329041481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478241920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01799559593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00442123413086</t>
+    <t xml:space="preserve">2.03609418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424159526825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00215911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00329113006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478289604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01799583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00442147254944</t>
   </si>
   <si>
     <t xml:space="preserve">1.95465052127838</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">2.02930736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02817606925964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13224339485168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432527542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12093162536621</t>
+    <t xml:space="preserve">2.02817630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09265232086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13224291801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12432503700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12093114852905</t>
   </si>
   <si>
     <t xml:space="preserve">2.15939116477966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15373516082764</t>
+    <t xml:space="preserve">2.15373492240906</t>
   </si>
   <si>
     <t xml:space="preserve">2.14016127586365</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">2.1084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07568502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14921045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19332575798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1786208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23291659355164</t>
+    <t xml:space="preserve">2.0756847858429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14921021461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19332599639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17862057685852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23291683197021</t>
   </si>
   <si>
     <t xml:space="preserve">2.19558835029602</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">2.20803093910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20576858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18314528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16617774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20350670814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19219493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15825963020325</t>
+    <t xml:space="preserve">2.20576882362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18314552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16617798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20350623130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19219446182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15825986862183</t>
   </si>
   <si>
     <t xml:space="preserve">2.20011305809021</t>
@@ -914,37 +914,37 @@
     <t xml:space="preserve">2.17522716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17748928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15599751472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14129209518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09378385543823</t>
+    <t xml:space="preserve">2.17748951911926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15599775314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14129257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09378337860107</t>
   </si>
   <si>
     <t xml:space="preserve">2.07907843589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08812785148621</t>
+    <t xml:space="preserve">2.08812761306763</t>
   </si>
   <si>
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10961985588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22273635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26232695579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26006436347961</t>
+    <t xml:space="preserve">2.10962009429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.222736120224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26232671737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26006460189819</t>
   </si>
   <si>
     <t xml:space="preserve">2.2578022480011</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">2.33132791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34716415405273</t>
+    <t xml:space="preserve">2.34716439247131</t>
   </si>
   <si>
     <t xml:space="preserve">2.40032863616943</t>
@@ -977,292 +977,292 @@
     <t xml:space="preserve">2.3256721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3867552280426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36300015449524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33585286140442</t>
+    <t xml:space="preserve">2.38675498962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3630006313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33585262298584</t>
   </si>
   <si>
     <t xml:space="preserve">2.25893330574036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24988389015198</t>
+    <t xml:space="preserve">2.24988412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27137613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33769369125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30216646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36137866973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35072040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30808806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926951408386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21097993850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18137431144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1458466053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13637280464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10913515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14110970497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14229393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16361021995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18611097335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13874125480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.119793176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14939975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13755679130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16597867012024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15532064437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2003219127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18374252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2382173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27374482154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39453744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3838791847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34835195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36848425865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37322092056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36966824531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37203693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38032627105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38861632347107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34361505508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30927181243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28913998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2938768863678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33058834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34953618049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36019444465637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31637787818909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34479904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31756162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34006214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40401148796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4099326133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37914228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3554573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25953388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27966594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2559814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23111200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22163820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19676923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18492650985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13163590431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058350563049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16834735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13045144081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12097764015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11031913757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08426594734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22400665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24295473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29624533653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28795576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25005984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24413871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22755908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22637510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23703336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24769115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2926926612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3211145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25716519355774</t>
   </si>
   <si>
     <t xml:space="preserve">2.27137637138367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.302166223526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36137866973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35072064399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30808782577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453261375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926927566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18137383460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14584684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13637256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.109135389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14110970497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14229369163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16361021995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18611097335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13874101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.119793176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14939951896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13755655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16597867012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15532040596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2003219127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27374482154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39453768730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3838791847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3483521938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36848425865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37322115898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36966824531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38032650947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38861608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34361505508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30927205085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28913998603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29387712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34953641891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36019420623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31637740135193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34479904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31756162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34006214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40401124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4099326133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37914204597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35545706748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25953388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27966594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25598120689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23111200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22163820266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19676876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18492650985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13163566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058350563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16834735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13045167922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12097764015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11031937599182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08426594734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22400689125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24295473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29624509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28795576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25005984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25834965705872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24413871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22755908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22637486457825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23703336715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24769115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29269242286682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32111406326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25716543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27137589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30453491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29742956161499</t>
+    <t xml:space="preserve">2.30453515052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29743003845215</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124406814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3187460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27848196029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26663947105408</t>
+    <t xml:space="preserve">2.31874632835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27848172187805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26663970947266</t>
   </si>
   <si>
     <t xml:space="preserve">2.28321862220764</t>
@@ -1271,70 +1271,70 @@
     <t xml:space="preserve">2.32703590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34598326683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30571937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27729725837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742726325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19203209877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14821529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19795322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2097954750061</t>
+    <t xml:space="preserve">2.34598350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30571961402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27729773521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19203233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1482150554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19795298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20979595184326</t>
   </si>
   <si>
     <t xml:space="preserve">2.19913768768311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23348045349121</t>
+    <t xml:space="preserve">2.23348069190979</t>
   </si>
   <si>
     <t xml:space="preserve">2.23584914207458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28085017204285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26900768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24177002906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27019214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26308631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28677129745483</t>
+    <t xml:space="preserve">2.28084993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26900792121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27256035804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24177050590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361275672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27019190788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26308655738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28677201271057</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3009819984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33177256584167</t>
+    <t xml:space="preserve">2.30098247528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33177280426025</t>
   </si>
   <si>
     <t xml:space="preserve">2.32821989059448</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">2.31519317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39098429679871</t>
+    <t xml:space="preserve">2.39098453521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.41585373878479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41940641403198</t>
+    <t xml:space="preserve">2.41940665245056</t>
   </si>
   <si>
     <t xml:space="preserve">2.4371702671051</t>
@@ -1358,22 +1358,22 @@
     <t xml:space="preserve">2.48098707199097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53309369087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56743717193604</t>
+    <t xml:space="preserve">2.53309345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56743669509888</t>
   </si>
   <si>
     <t xml:space="preserve">2.54612064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56151533126831</t>
+    <t xml:space="preserve">2.56151580810547</t>
   </si>
   <si>
     <t xml:space="preserve">2.57572650909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56862092018127</t>
+    <t xml:space="preserve">2.5686206817627</t>
   </si>
   <si>
     <t xml:space="preserve">2.57691073417664</t>
@@ -1382,22 +1382,22 @@
     <t xml:space="preserve">2.56980514526367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56625270843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6396758556366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65743923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66691327095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63671493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62960958480835</t>
+    <t xml:space="preserve">2.56625247001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63967561721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6574387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66691303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63671469688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62960910797119</t>
   </si>
   <si>
     <t xml:space="preserve">2.58105564117432</t>
@@ -1406,58 +1406,58 @@
     <t xml:space="preserve">2.57158160209656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56921339035034</t>
+    <t xml:space="preserve">2.56921315193176</t>
   </si>
   <si>
     <t xml:space="preserve">2.48039507865906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53013300895691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45611810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217129707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44605183601379</t>
+    <t xml:space="preserve">2.53013277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45611786842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44605207443237</t>
   </si>
   <si>
     <t xml:space="preserve">2.4069721698761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42236733436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4709210395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45552563667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723582267761</t>
+    <t xml:space="preserve">2.42236685752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47092080116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45552587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723606109619</t>
   </si>
   <si>
     <t xml:space="preserve">2.46559190750122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388124465942</t>
+    <t xml:space="preserve">2.473881483078</t>
   </si>
   <si>
     <t xml:space="preserve">2.41881442070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40934014320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43480157852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32644319534302</t>
+    <t xml:space="preserve">2.40934038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43480134010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40756392478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3264434337616</t>
   </si>
   <si>
     <t xml:space="preserve">2.33473324775696</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">2.35190486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39631390571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37440490722656</t>
+    <t xml:space="preserve">2.39631366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37440538406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.35782599449158</t>
@@ -1478,34 +1478,34 @@
     <t xml:space="preserve">2.42591977119446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38624811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39986634254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32881212234497</t>
+    <t xml:space="preserve">2.36611533164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38624787330627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39986658096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32881188392639</t>
   </si>
   <si>
     <t xml:space="preserve">2.35249710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302282333374</t>
+    <t xml:space="preserve">2.34302258491516</t>
   </si>
   <si>
     <t xml:space="preserve">2.37499737739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36374735832214</t>
+    <t xml:space="preserve">2.36374711990356</t>
   </si>
   <si>
     <t xml:space="preserve">2.39809012413025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38565540313721</t>
+    <t xml:space="preserve">2.38565564155579</t>
   </si>
   <si>
     <t xml:space="preserve">2.4123010635376</t>
@@ -1517,43 +1517,43 @@
     <t xml:space="preserve">2.45078897476196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51769828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51355361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54315996170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54079103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54375219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756899833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61066126823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58223986625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59408235549927</t>
+    <t xml:space="preserve">2.51769852638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51355338096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315972328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54079127311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54375195503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61066150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58224010467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59408211708069</t>
   </si>
   <si>
     <t xml:space="preserve">2.61480617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493871688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65803146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64204430580139</t>
+    <t xml:space="preserve">2.63493847846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65803122520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64204382896423</t>
   </si>
   <si>
     <t xml:space="preserve">2.67165017127991</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">2.6752028465271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58638477325439</t>
+    <t xml:space="preserve">2.58638453483582</t>
   </si>
   <si>
     <t xml:space="preserve">2.60177969932556</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">2.57039761543274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5934898853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59526658058167</t>
+    <t xml:space="preserve">2.59349012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
     <t xml:space="preserve">2.51059293746948</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">2.54967331886292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48868465423584</t>
+    <t xml:space="preserve">2.48868441581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.49672651290894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48620986938477</t>
+    <t xml:space="preserve">2.48621034622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.43548393249512</t>
@@ -1601,58 +1601,58 @@
     <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38785028457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37733387947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25917863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176090240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361132621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33464956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577947616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23752737045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22577381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23567152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020059585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2498996257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23195958137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23938274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20041036605835</t>
+    <t xml:space="preserve">2.38785099983215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773341178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25917887687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176114082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33464980125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577923774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23752760887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22577404975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23567175865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020083427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24989938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23196005821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23938298225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371314048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20041012763977</t>
   </si>
   <si>
     <t xml:space="preserve">2.20968961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22329926490784</t>
+    <t xml:space="preserve">2.22329950332642</t>
   </si>
   <si>
     <t xml:space="preserve">2.20721530914307</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19298696517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05812931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05874800682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379867553711</t>
+    <t xml:space="preserve">2.1929874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05812907218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0587477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379915237427</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843570709229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04699420928955</t>
+    <t xml:space="preserve">2.04699397087097</t>
   </si>
   <si>
     <t xml:space="preserve">2.04946851730347</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">2.0921528339386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11689758300781</t>
+    <t xml:space="preserve">2.11689734458923</t>
   </si>
   <si>
     <t xml:space="preserve">2.10143208503723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14102339744568</t>
+    <t xml:space="preserve">2.14102363586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813473701477</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">2.10638093948364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12679505348206</t>
+    <t xml:space="preserve">2.12679529190063</t>
   </si>
   <si>
     <t xml:space="preserve">2.14349770545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13793039321899</t>
+    <t xml:space="preserve">2.13793063163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.12122774124146</t>
@@ -1730,46 +1730,46 @@
     <t xml:space="preserve">2.14473509788513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18061470985413</t>
+    <t xml:space="preserve">2.18061494827271</t>
   </si>
   <si>
     <t xml:space="preserve">2.16514945030212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20102882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09029698371887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1199905872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07730650901794</t>
+    <t xml:space="preserve">2.20102906227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09029722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12432074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699963569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07730627059937</t>
   </si>
   <si>
     <t xml:space="preserve">2.07235741615295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11937189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20474076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28392338752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23319673538208</t>
+    <t xml:space="preserve">2.11937236785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20474052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28392314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23319697380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.19175004959106</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">2.24309468269348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26289033889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2529923915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26969504356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711892127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25608563423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2418577671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19917345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2220618724823</t>
+    <t xml:space="preserve">2.26289057731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25299263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26969528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25608587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24185752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19917321205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22206211090088</t>
   </si>
   <si>
     <t xml:space="preserve">2.2752628326416</t>
@@ -1811,70 +1811,70 @@
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3142352104187</t>
+    <t xml:space="preserve">2.31423568725586</t>
   </si>
   <si>
     <t xml:space="preserve">2.3699107170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33712434768677</t>
+    <t xml:space="preserve">2.33712410926819</t>
   </si>
   <si>
     <t xml:space="preserve">2.33836126327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33403086662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36001300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40146017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4163064956665</t>
+    <t xml:space="preserve">2.3340311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3600127696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40145993232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41630673408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.41445112228394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42063689231873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45589828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44352579116821</t>
+    <t xml:space="preserve">2.42063736915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45589804649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44352602958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.47012615203857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48682880401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50600600242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3730034828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.367436170578</t>
+    <t xml:space="preserve">2.48682856559753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50600576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37300372123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36743640899658</t>
   </si>
   <si>
     <t xml:space="preserve">2.30743074417114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37795281410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36496162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27093243598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28083038330078</t>
+    <t xml:space="preserve">2.37795305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36496186256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27093267440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808301448822</t>
   </si>
   <si>
     <t xml:space="preserve">2.19793581962585</t>
@@ -1883,46 +1883,46 @@
     <t xml:space="preserve">2.19855451583862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20907139778137</t>
+    <t xml:space="preserve">2.20907115936279</t>
   </si>
   <si>
     <t xml:space="preserve">2.1830894947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17504715919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19979166984558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16824269294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648865699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09772062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13978600502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12184619903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1966986656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17381000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21525740623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24247598648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2443323135376</t>
+    <t xml:space="preserve">2.17504739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16824245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15648913383484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09772038459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1397864818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1218466758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19669890403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380976676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21525716781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24247622489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24433207511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.24742484092712</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.26598358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26227211952209</t>
+    <t xml:space="preserve">2.26227188110352</t>
   </si>
   <si>
     <t xml:space="preserve">2.28825354576111</t>
@@ -1949,79 +1949,79 @@
     <t xml:space="preserve">2.22701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2041220664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15834474563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1373119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22639203071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28949093818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24680638313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23381543159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15277695655823</t>
+    <t xml:space="preserve">2.20412230491638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15834498405457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13731169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23443460464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2263925075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28949117660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24680685997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23381567001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15277743339539</t>
   </si>
   <si>
     <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15401458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18556356430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21278238296509</t>
+    <t xml:space="preserve">2.15401482582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18556380271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21278262138367</t>
   </si>
   <si>
     <t xml:space="preserve">2.19607996940613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504149436951</t>
+    <t xml:space="preserve">2.11504173278809</t>
   </si>
   <si>
     <t xml:space="preserve">2.13607454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1762843132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14040470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27959299087524</t>
+    <t xml:space="preserve">2.17628407478333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14040517807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27959322929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.32413339614868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31794714927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35073351860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38846945762634</t>
+    <t xml:space="preserve">2.31794738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35073375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38846921920776</t>
   </si>
   <si>
     <t xml:space="preserve">2.41012072563171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43053460121155</t>
+    <t xml:space="preserve">2.43053483963013</t>
   </si>
   <si>
     <t xml:space="preserve">2.32227754592896</t>
@@ -2030,43 +2030,43 @@
     <t xml:space="preserve">2.37424111366272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41259503364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43424677848816</t>
+    <t xml:space="preserve">2.41259527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43424654006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.44971179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45342373847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930901527405</t>
+    <t xml:space="preserve">2.45342397689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930877685547</t>
   </si>
   <si>
     <t xml:space="preserve">2.5511646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53260636329651</t>
+    <t xml:space="preserve">2.53260612487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.47321915626526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136354446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50043845176697</t>
+    <t xml:space="preserve">2.47136330604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50043821334839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5152850151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52394556999207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4620840549469</t>
+    <t xml:space="preserve">2.52394533157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46208429336548</t>
   </si>
   <si>
     <t xml:space="preserve">2.32908201217651</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">2.36125016212463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42620420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44105124473572</t>
+    <t xml:space="preserve">2.42620444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410514831543</t>
   </si>
   <si>
     <t xml:space="preserve">2.37609696388245</t>
@@ -2087,22 +2087,22 @@
     <t xml:space="preserve">2.45713543891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45094895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47507524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46579575538635</t>
+    <t xml:space="preserve">2.4509494304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47507500648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46579599380493</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49054050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48187971115112</t>
+    <t xml:space="preserve">2.49054026603699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4818799495697</t>
   </si>
   <si>
     <t xml:space="preserve">2.47878670692444</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">2.49548935890198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50662422180176</t>
+    <t xml:space="preserve">2.50662446022034</t>
   </si>
   <si>
     <t xml:space="preserve">2.52889442443848</t>
@@ -2120,31 +2120,31 @@
     <t xml:space="preserve">2.53446197509766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50786185264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55302047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58147668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64952397346497</t>
+    <t xml:space="preserve">2.50786161422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55302023887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601119041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58147644996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64952421188354</t>
   </si>
   <si>
     <t xml:space="preserve">2.68292927742004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69901323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68231129646301</t>
+    <t xml:space="preserve">2.69901347160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68231105804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.66870141029358</t>
@@ -2156,79 +2156,79 @@
     <t xml:space="preserve">2.69282746315002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71014857292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74664664268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76396775245667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7299439907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83696460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8344898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86108994483948</t>
+    <t xml:space="preserve">2.71014833450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74664688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76396799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72994375228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83696436882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83448958396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86109018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.85057377815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79799127578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716328620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76025652885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78500032424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78994989395142</t>
+    <t xml:space="preserve">2.79799175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716280937195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76025629043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78500056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78994965553284</t>
   </si>
   <si>
     <t xml:space="preserve">2.82088017463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83943867683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83881998062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79737329483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81160092353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78685712814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80603361129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81778740882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79551768302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74417233467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65694785118103</t>
+    <t xml:space="preserve">2.83943891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83882021903992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79737281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81160116195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78685688972473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80603337287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81778717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79551696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74417209625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65694761276245</t>
   </si>
   <si>
     <t xml:space="preserve">2.65014266967773</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">2.69097137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66560840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73056292533875</t>
+    <t xml:space="preserve">2.66560816764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73056268692017</t>
   </si>
   <si>
     <t xml:space="preserve">2.79984760284424</t>
@@ -2252,61 +2252,61 @@
     <t xml:space="preserve">2.76334929466248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75045776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75625872612</t>
+    <t xml:space="preserve">2.7504575252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75625848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.79106640815735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68084168434143</t>
+    <t xml:space="preserve">2.68084192276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.79235553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72596335411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68148636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62863063812256</t>
+    <t xml:space="preserve">2.72596311569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68148612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62863039970398</t>
   </si>
   <si>
     <t xml:space="preserve">2.65892601013184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66279363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6344313621521</t>
+    <t xml:space="preserve">2.66279339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63443160057068</t>
   </si>
   <si>
     <t xml:space="preserve">2.68664336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66666126251221</t>
+    <t xml:space="preserve">2.66666102409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.65183544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472721099854</t>
+    <t xml:space="preserve">2.66472697257996</t>
   </si>
   <si>
     <t xml:space="preserve">2.68857717514038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69437837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68986630439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72016191482544</t>
+    <t xml:space="preserve">2.6943781375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68986582756042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72016167640686</t>
   </si>
   <si>
     <t xml:space="preserve">2.69695663452148</t>
@@ -2315,40 +2315,40 @@
     <t xml:space="preserve">2.65248012542725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69953513145447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75303626060486</t>
+    <t xml:space="preserve">2.69953489303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7530357837677</t>
   </si>
   <si>
     <t xml:space="preserve">2.73563194274902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176455497742</t>
+    <t xml:space="preserve">2.73176431655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205992698669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7588369846344</t>
+    <t xml:space="preserve">2.75883722305298</t>
   </si>
   <si>
     <t xml:space="preserve">2.79428958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76077055931091</t>
+    <t xml:space="preserve">2.76077079772949</t>
   </si>
   <si>
     <t xml:space="preserve">2.79944634437561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82007312774658</t>
+    <t xml:space="preserve">2.820072889328</t>
   </si>
   <si>
     <t xml:space="preserve">2.86197137832642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91160440444946</t>
+    <t xml:space="preserve">2.91160464286804</t>
   </si>
   <si>
     <t xml:space="preserve">2.90773701667786</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">2.89162230491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89484524726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97477412223816</t>
+    <t xml:space="preserve">2.8948450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414757728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.974773645401</t>
   </si>
   <si>
     <t xml:space="preserve">2.96832823753357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97541904449463</t>
+    <t xml:space="preserve">2.97541880607605</t>
   </si>
   <si>
     <t xml:space="preserve">2.98702120780945</t>
@@ -2378,43 +2378,43 @@
     <t xml:space="preserve">2.96897292137146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97735261917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91805028915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04181122779846</t>
+    <t xml:space="preserve">2.97735238075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91805005073547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04181098937988</t>
   </si>
   <si>
     <t xml:space="preserve">3.02118444442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03665447235107</t>
+    <t xml:space="preserve">3.0366542339325</t>
   </si>
   <si>
     <t xml:space="preserve">3.03923296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04825687408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829291343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155094146729</t>
+    <t xml:space="preserve">3.04825735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155117988586</t>
   </si>
   <si>
     <t xml:space="preserve">2.98895502090454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90902614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86003708839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84263348579407</t>
+    <t xml:space="preserve">2.90902590751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86003756523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84263324737549</t>
   </si>
   <si>
     <t xml:space="preserve">2.78655409812927</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">2.7659273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83812141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7343430519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78010845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84843492507935</t>
+    <t xml:space="preserve">2.83812117576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73434257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78010869026184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84843516349792</t>
   </si>
   <si>
     <t xml:space="preserve">2.87421822547913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95608139038086</t>
+    <t xml:space="preserve">2.95608115196228</t>
   </si>
   <si>
     <t xml:space="preserve">2.9477014541626</t>
@@ -2447,58 +2447,58 @@
     <t xml:space="preserve">2.91869473457336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91676092147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94705677032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91031551361084</t>
+    <t xml:space="preserve">2.91676115989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94705653190613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91031527519226</t>
   </si>
   <si>
     <t xml:space="preserve">2.96510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94576811790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94125580787659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94383358955383</t>
+    <t xml:space="preserve">2.94576787948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94125556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94383382797241</t>
   </si>
   <si>
     <t xml:space="preserve">2.97606325149536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95479202270508</t>
+    <t xml:space="preserve">2.95479226112366</t>
   </si>
   <si>
     <t xml:space="preserve">2.95801496505737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98959970474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05921530723572</t>
+    <t xml:space="preserve">2.98959946632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05921506881714</t>
   </si>
   <si>
     <t xml:space="preserve">3.11013770103455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10884833335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08048629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11465001106262</t>
+    <t xml:space="preserve">3.10884809494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.080486536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11464977264404</t>
   </si>
   <si>
     <t xml:space="preserve">3.10240268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09853506088257</t>
+    <t xml:space="preserve">3.09853529930115</t>
   </si>
   <si>
     <t xml:space="preserve">3.06372690200806</t>
@@ -2507,106 +2507,106 @@
     <t xml:space="preserve">3.10175776481628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12431907653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1494574546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13592147827148</t>
+    <t xml:space="preserve">3.12431859970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14945769309998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13592123985291</t>
   </si>
   <si>
     <t xml:space="preserve">3.07661890983582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05663681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698588371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696822166443</t>
+    <t xml:space="preserve">3.05663704872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698636054993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696798324585</t>
   </si>
   <si>
     <t xml:space="preserve">3.08757662773132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12560796737671</t>
+    <t xml:space="preserve">3.12560772895813</t>
   </si>
   <si>
     <t xml:space="preserve">3.19071102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15396976470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15010190010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17781901359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20553660392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22680807113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22165107727051</t>
+    <t xml:space="preserve">3.15396952629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15010213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17781925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20553684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2268078327179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22165155410767</t>
   </si>
   <si>
     <t xml:space="preserve">3.21262693405151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23325347900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001311302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21391654014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23969984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26548337936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24743461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229599952698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388073921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739905357361</t>
+    <t xml:space="preserve">3.23325395584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21391630172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23970007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26548361778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24743485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2222957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388050079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739953041077</t>
   </si>
   <si>
     <t xml:space="preserve">3.31447243690491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35185790061951</t>
+    <t xml:space="preserve">3.35185813903809</t>
   </si>
   <si>
     <t xml:space="preserve">3.3995578289032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4111602306366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43307638168335</t>
+    <t xml:space="preserve">3.41115999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43307590484619</t>
   </si>
   <si>
     <t xml:space="preserve">3.49108910560608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47304058074951</t>
+    <t xml:space="preserve">3.47304081916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.43823313713074</t>
@@ -2615,40 +2615,40 @@
     <t xml:space="preserve">3.45370268821716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39311194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41631746292114</t>
+    <t xml:space="preserve">3.39311218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600371360779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41631698608398</t>
   </si>
   <si>
     <t xml:space="preserve">3.4150276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.413738489151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44596791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920899391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34541249275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994198799133</t>
+    <t xml:space="preserve">3.41373825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44596815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987086296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3454122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994222640991</t>
   </si>
   <si>
     <t xml:space="preserve">3.38924407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3879554271698</t>
+    <t xml:space="preserve">3.38795518875122</t>
   </si>
   <si>
     <t xml:space="preserve">3.3479905128479</t>
@@ -2660,28 +2660,28 @@
     <t xml:space="preserve">3.27192950248718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32865262031555</t>
+    <t xml:space="preserve">3.32865285873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.36861729621887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43049812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43694353103638</t>
+    <t xml:space="preserve">3.43049764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43694376945496</t>
   </si>
   <si>
     <t xml:space="preserve">3.42405200004578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42147350311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47819709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45499205589294</t>
+    <t xml:space="preserve">3.42147374153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4781973361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4549925327301</t>
   </si>
   <si>
     <t xml:space="preserve">3.37635278701782</t>
@@ -2693,46 +2693,46 @@
     <t xml:space="preserve">3.35572600364685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26032686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22938632965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30544757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3325207233429</t>
+    <t xml:space="preserve">3.26032662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22938656806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3054473400116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33252048492432</t>
   </si>
   <si>
     <t xml:space="preserve">3.31576108932495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23841094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1475236415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18490958213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006657600403</t>
+    <t xml:space="preserve">3.23841071128845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14752340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18490982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006609916687</t>
   </si>
   <si>
     <t xml:space="preserve">3.16815066337585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1739513874054</t>
+    <t xml:space="preserve">3.17395162582397</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205361366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09982419013977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12238454818726</t>
+    <t xml:space="preserve">3.09982442855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12238478660583</t>
   </si>
   <si>
     <t xml:space="preserve">3.04890179634094</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">3.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02182912826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96703934669495</t>
+    <t xml:space="preserve">3.0218288898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96703910827637</t>
   </si>
   <si>
     <t xml:space="preserve">3.00958204269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04310035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0946671962738</t>
+    <t xml:space="preserve">3.04310059547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09466743469238</t>
   </si>
   <si>
     <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15848159790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18297624588013</t>
+    <t xml:space="preserve">3.15848183631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18297648429871</t>
   </si>
   <si>
     <t xml:space="preserve">3.4008469581604</t>
@@ -2774,13 +2774,13 @@
     <t xml:space="preserve">3.44854640960693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54394555091858</t>
+    <t xml:space="preserve">3.54394578933716</t>
   </si>
   <si>
     <t xml:space="preserve">3.4756190776825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39440059661865</t>
+    <t xml:space="preserve">3.39440083503723</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459678649902</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">3.01409411430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8858208656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7427225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017981529236</t>
+    <t xml:space="preserve">2.88582110404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74272227287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017957687378</t>
   </si>
   <si>
     <t xml:space="preserve">2.56610536575317</t>
@@ -2807,46 +2807,46 @@
     <t xml:space="preserve">2.51969504356384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24896812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15936994552612</t>
+    <t xml:space="preserve">2.24896836280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1593701839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.17741847038269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646694660187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88993215560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7661714553833</t>
+    <t xml:space="preserve">1.79646682739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88993239402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76617169380188</t>
   </si>
   <si>
     <t xml:space="preserve">1.68817639350891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62500655651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91313743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77261734008789</t>
+    <t xml:space="preserve">1.62500643730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91313755512238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77261745929718</t>
   </si>
   <si>
     <t xml:space="preserve">1.83965456485748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93827664852142</t>
+    <t xml:space="preserve">1.93827641010284</t>
   </si>
   <si>
     <t xml:space="preserve">1.94149947166443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04141044616699</t>
+    <t xml:space="preserve">2.04141068458557</t>
   </si>
   <si>
     <t xml:space="preserve">1.90669167041779</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">1.94923436641693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02013897895813</t>
+    <t xml:space="preserve">2.02013921737671</t>
   </si>
   <si>
     <t xml:space="preserve">2.05236864089966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98662054538727</t>
+    <t xml:space="preserve">1.98662042617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.11295986175537</t>
@@ -2882,31 +2882,31 @@
     <t xml:space="preserve">1.94278848171234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92087244987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93892097473145</t>
+    <t xml:space="preserve">1.92087268829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93892121315002</t>
   </si>
   <si>
     <t xml:space="preserve">1.90282416343689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83063018321991</t>
+    <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">1.89766728878021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89379954338074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693405628204</t>
+    <t xml:space="preserve">1.89379966259003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693417549133</t>
   </si>
   <si>
     <t xml:space="preserve">2.06010365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05623579025269</t>
+    <t xml:space="preserve">2.05623602867126</t>
   </si>
   <si>
     <t xml:space="preserve">2.0265851020813</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">2.0252959728241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04463362693787</t>
+    <t xml:space="preserve">2.04463338851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.04721188545227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752515792847</t>
+    <t xml:space="preserve">2.05752539634705</t>
   </si>
   <si>
     <t xml:space="preserve">2.0162718296051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01756119728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790979385376</t>
+    <t xml:space="preserve">2.01756072044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790991306305</t>
   </si>
   <si>
     <t xml:space="preserve">1.97243940830231</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">2.22702980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21850275993347</t>
+    <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
     <t xml:space="preserve">2.17018151283264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21992373466492</t>
+    <t xml:space="preserve">2.21992349624634</t>
   </si>
   <si>
     <t xml:space="preserve">2.28387784957886</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">2.31372308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24266290664673</t>
+    <t xml:space="preserve">2.24266266822815</t>
   </si>
   <si>
     <t xml:space="preserve">2.25687503814697</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">2.39046859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46863484382629</t>
+    <t xml:space="preserve">2.46863460540771</t>
   </si>
   <si>
     <t xml:space="preserve">2.52406167984009</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">2.61644005775452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5666983127594</t>
+    <t xml:space="preserve">2.56669807434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.48995280265808</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">2.47574067115784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45158052444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44021081924438</t>
+    <t xml:space="preserve">2.451580286026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44021105766296</t>
   </si>
   <si>
     <t xml:space="preserve">2.40325951576233</t>
@@ -3023,37 +3023,37 @@
     <t xml:space="preserve">2.42457747459412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48284673690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46010732650757</t>
+    <t xml:space="preserve">2.48284649848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46010756492615</t>
   </si>
   <si>
     <t xml:space="preserve">2.43310451507568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53258895874023</t>
+    <t xml:space="preserve">2.53258872032166</t>
   </si>
   <si>
     <t xml:space="preserve">2.53116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55817055702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57238268852234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58091020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51127076148987</t>
+    <t xml:space="preserve">2.55817031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57238292694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58090996742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51127099990845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53685259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56527662277222</t>
+    <t xml:space="preserve">2.56527638435364</t>
   </si>
   <si>
     <t xml:space="preserve">2.60933423042297</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642457485199</t>
+    <t xml:space="preserve">2.76424551010132</t>
   </si>
   <si>
     <t xml:space="preserve">2.64770674705505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61501932144165</t>
+    <t xml:space="preserve">2.61501908302307</t>
   </si>
   <si>
     <t xml:space="preserve">2.60649180412292</t>
@@ -3092,37 +3092,37 @@
     <t xml:space="preserve">2.54680109024048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66049742698669</t>
+    <t xml:space="preserve">2.67186737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66049766540527</t>
   </si>
   <si>
     <t xml:space="preserve">2.68465805053711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7528760433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89073276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768406867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89641785621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92199945449829</t>
+    <t xml:space="preserve">2.75287580490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89073252677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89641809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92199969291687</t>
   </si>
   <si>
     <t xml:space="preserve">2.86373019218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83388447761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88931179046631</t>
+    <t xml:space="preserve">2.83388471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88931202888489</t>
   </si>
   <si>
     <t xml:space="preserve">2.84951782226562</t>
@@ -3134,16 +3134,16 @@
     <t xml:space="preserve">2.91773581504822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93479061126709</t>
+    <t xml:space="preserve">2.93479084968567</t>
   </si>
   <si>
     <t xml:space="preserve">2.95895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94900226593018</t>
+    <t xml:space="preserve">2.94616007804871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94900250434875</t>
   </si>
   <si>
     <t xml:space="preserve">2.87083601951599</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">2.81256651878357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78556346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90068101882935</t>
+    <t xml:space="preserve">2.78556370735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90068125724792</t>
   </si>
   <si>
     <t xml:space="preserve">2.87794232368469</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">2.94189643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95184445381165</t>
+    <t xml:space="preserve">2.95184469223022</t>
   </si>
   <si>
     <t xml:space="preserve">2.95753002166748</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">2.70313382148743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74861240386963</t>
+    <t xml:space="preserve">2.74861216545105</t>
   </si>
   <si>
     <t xml:space="preserve">2.69602799415588</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">2.65765523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72729444503784</t>
+    <t xml:space="preserve">2.72729420661926</t>
   </si>
   <si>
     <t xml:space="preserve">2.66902470588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6505491733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64912796020508</t>
+    <t xml:space="preserve">2.65054941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6491277217865</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075520515442</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">2.61359786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56243443489075</t>
+    <t xml:space="preserve">2.56243419647217</t>
   </si>
   <si>
     <t xml:space="preserve">2.45868611335754</t>
@@ -3239,37 +3239,37 @@
     <t xml:space="preserve">2.48853182792664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52690434455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48568940162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42741990089417</t>
+    <t xml:space="preserve">2.49705862998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52690410614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48568916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42742013931274</t>
   </si>
   <si>
     <t xml:space="preserve">2.39899587631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37199258804321</t>
+    <t xml:space="preserve">2.37199282646179</t>
   </si>
   <si>
     <t xml:space="preserve">2.25403261184692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23129343986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276639938354</t>
+    <t xml:space="preserve">2.23129320144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276616096497</t>
   </si>
   <si>
     <t xml:space="preserve">2.30235362052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37057185173035</t>
+    <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
     <t xml:space="preserve">2.3947319984436</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">2.56385564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52264022827148</t>
+    <t xml:space="preserve">2.52264046669006</t>
   </si>
   <si>
     <t xml:space="preserve">2.52832531929016</t>
@@ -3296,19 +3296,19 @@
     <t xml:space="preserve">2.7400848865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84383296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83672714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97174191474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93052649497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920877456665</t>
+    <t xml:space="preserve">2.84383320808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83672690391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97174167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920853614807</t>
   </si>
   <si>
     <t xml:space="preserve">2.81967282295227</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">2.78840589523315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78130030632019</t>
+    <t xml:space="preserve">2.78130006790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.78272128105164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77561521530151</t>
+    <t xml:space="preserve">2.77561497688293</t>
   </si>
   <si>
     <t xml:space="preserve">2.70597624778748</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">2.7130823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75998210906982</t>
+    <t xml:space="preserve">2.75998187065125</t>
   </si>
   <si>
     <t xml:space="preserve">2.79835438728333</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">2.77419400215149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77845811843872</t>
+    <t xml:space="preserve">2.77845788002014</t>
   </si>
   <si>
     <t xml:space="preserve">2.75713968276978</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">2.8608877658844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85946679115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91347217559814</t>
+    <t xml:space="preserve">2.85946655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91347193717957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88646912574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84241223335266</t>
+    <t xml:space="preserve">2.88362717628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84241199493408</t>
   </si>
   <si>
     <t xml:space="preserve">2.76993060112</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">2.67897343635559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68181586265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74577021598816</t>
+    <t xml:space="preserve">2.68181562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74576997756958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64344310760498</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">2.80546069145203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86657214164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758105278015</t>
+    <t xml:space="preserve">2.86657238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758129119873</t>
   </si>
   <si>
     <t xml:space="preserve">3.13233828544617</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">3.10533499717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18350148200989</t>
+    <t xml:space="preserve">3.18350172042847</t>
   </si>
   <si>
     <t xml:space="preserve">3.14939260482788</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">3.12665319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03995966911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742629051208</t>
+    <t xml:space="preserve">3.03995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742652893066</t>
   </si>
   <si>
     <t xml:space="preserve">3.01153540611267</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">3.03427481651306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08259534835815</t>
+    <t xml:space="preserve">3.08259558677673</t>
   </si>
   <si>
     <t xml:space="preserve">3.13375902175903</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">3.11812591552734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0584352016449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19344973564148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16928958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21192526817322</t>
+    <t xml:space="preserve">3.05843496322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19344997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16928935050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2119255065918</t>
   </si>
   <si>
     <t xml:space="preserve">3.25171947479248</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">3.30004024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28867030143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30146145820618</t>
+    <t xml:space="preserve">3.2886700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435563087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3014612197876</t>
   </si>
   <si>
     <t xml:space="preserve">3.32562184333801</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">3.30572533607483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110066413879</t>
+    <t xml:space="preserve">3.3526246547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110042572021</t>
   </si>
   <si>
     <t xml:space="preserve">3.41942143440247</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">3.3085675239563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40947294235229</t>
+    <t xml:space="preserve">3.40947318077087</t>
   </si>
   <si>
     <t xml:space="preserve">3.37962770462036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38247036933899</t>
+    <t xml:space="preserve">3.38247013092041</t>
   </si>
   <si>
     <t xml:space="preserve">3.40378785133362</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">3.42013239860535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32846450805664</t>
+    <t xml:space="preserve">3.32846474647522</t>
   </si>
   <si>
     <t xml:space="preserve">3.29790830612183</t>
@@ -3545,19 +3545,19 @@
     <t xml:space="preserve">3.33272790908813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35902047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36683678627014</t>
+    <t xml:space="preserve">3.35902070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36683702468872</t>
   </si>
   <si>
     <t xml:space="preserve">3.34978246688843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42723798751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500327110291</t>
+    <t xml:space="preserve">3.42723822593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500350952148</t>
   </si>
   <si>
     <t xml:space="preserve">3.32206869125366</t>
@@ -3575,40 +3575,40 @@
     <t xml:space="preserve">3.33201718330383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3043041229248</t>
+    <t xml:space="preserve">3.30430388450623</t>
   </si>
   <si>
     <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28440713882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23679614067078</t>
+    <t xml:space="preserve">3.28440690040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23679661750793</t>
   </si>
   <si>
     <t xml:space="preserve">3.31212019920349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27232670783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31283116340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42226409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48550748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47555875778198</t>
+    <t xml:space="preserve">3.27232646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31283140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42226433753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48550772666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47555899620056</t>
   </si>
   <si>
     <t xml:space="preserve">3.49545645713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48124408721924</t>
+    <t xml:space="preserve">3.48124432563782</t>
   </si>
   <si>
     <t xml:space="preserve">3.57575392723083</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">3.53027558326721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49829792976379</t>
+    <t xml:space="preserve">3.49829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">3.52459073066711</t>
@@ -3638,28 +3638,28 @@
     <t xml:space="preserve">3.43120408058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41614174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44927906990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48919415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46584820747375</t>
+    <t xml:space="preserve">3.41614198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44927930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48919439315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46584796905518</t>
   </si>
   <si>
     <t xml:space="preserve">3.47488498687744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831632614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844122886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46132922172546</t>
+    <t xml:space="preserve">3.45831608772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.488440990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46132898330688</t>
   </si>
   <si>
     <t xml:space="preserve">3.4507851600647</t>
@@ -3668,19 +3668,19 @@
     <t xml:space="preserve">3.44626665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44099497795105</t>
+    <t xml:space="preserve">3.44099473953247</t>
   </si>
   <si>
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752388954163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36041116714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32501459121704</t>
+    <t xml:space="preserve">3.38752365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3604109287262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32501482963562</t>
   </si>
   <si>
     <t xml:space="preserve">3.24744319915771</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21430635452271</t>
+    <t xml:space="preserve">3.21430611610413</t>
   </si>
   <si>
     <t xml:space="preserve">3.24970269203186</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">3.39279556274414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35062026977539</t>
+    <t xml:space="preserve">3.35062050819397</t>
   </si>
   <si>
     <t xml:space="preserve">3.37697982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29865527153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29489016532898</t>
+    <t xml:space="preserve">3.29865550994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2948899269104</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731853485107</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">3.30468034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31673002243042</t>
+    <t xml:space="preserve">3.316730260849</t>
   </si>
   <si>
     <t xml:space="preserve">3.33329916000366</t>
@@ -3788,52 +3788,52 @@
     <t xml:space="preserve">3.61797714233398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60592746734619</t>
+    <t xml:space="preserve">3.60592770576477</t>
   </si>
   <si>
     <t xml:space="preserve">3.6164710521698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65337371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078045845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63831186294556</t>
+    <t xml:space="preserve">3.65337419509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63981795310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6383113861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.72040152549744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67521405220032</t>
+    <t xml:space="preserve">3.6752142906189</t>
   </si>
   <si>
     <t xml:space="preserve">3.66542387008667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75052642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010703086853</t>
+    <t xml:space="preserve">3.75052666664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010679244995</t>
   </si>
   <si>
     <t xml:space="preserve">3.7746262550354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77311992645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79872608184814</t>
+    <t xml:space="preserve">3.77312016487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79872632026672</t>
   </si>
   <si>
     <t xml:space="preserve">3.77613210678101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78215718269348</t>
+    <t xml:space="preserve">3.78215670585632</t>
   </si>
   <si>
     <t xml:space="preserve">3.767094373703</t>
@@ -3842,19 +3842,19 @@
     <t xml:space="preserve">3.78667569160461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73697018623352</t>
+    <t xml:space="preserve">3.7369704246521</t>
   </si>
   <si>
     <t xml:space="preserve">3.77763819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71663594245911</t>
+    <t xml:space="preserve">3.71663546562195</t>
   </si>
   <si>
     <t xml:space="preserve">3.71588230133057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70533871650696</t>
+    <t xml:space="preserve">3.70533895492554</t>
   </si>
   <si>
     <t xml:space="preserve">3.63755822181702</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">3.65638613700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72567343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67144894599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258104324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132380485535</t>
+    <t xml:space="preserve">3.72567367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67144870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258128166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6413242816925</t>
   </si>
   <si>
     <t xml:space="preserve">3.75429177284241</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">3.75203204154968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80926942825317</t>
+    <t xml:space="preserve">3.80926966667175</t>
   </si>
   <si>
     <t xml:space="preserve">3.7445011138916</t>
@@ -3896,52 +3896,52 @@
     <t xml:space="preserve">3.80625677108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84541916847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83939409255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90717530250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006234169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95386791229248</t>
+    <t xml:space="preserve">3.84541940689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83939385414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90717458724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9538676738739</t>
   </si>
   <si>
     <t xml:space="preserve">3.97947359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95989298820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483041763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89060568809509</t>
+    <t xml:space="preserve">3.95989274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483065605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89060616493225</t>
   </si>
   <si>
     <t xml:space="preserve">3.88307523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92976808547974</t>
+    <t xml:space="preserve">3.92976784706116</t>
   </si>
   <si>
     <t xml:space="preserve">3.95682597160339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99502539634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01571655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96239686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95125555992126</t>
+    <t xml:space="preserve">3.99502515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01571702957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96239709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95125532150269</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025058746338</t>
@@ -3950,79 +3950,79 @@
     <t xml:space="preserve">3.9791088104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98388409614563</t>
+    <t xml:space="preserve">3.98388361930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.95523381233215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0045747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98070049285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9735381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98706746101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807195663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340135574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98229265213013</t>
+    <t xml:space="preserve">4.00457525253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98070025444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01889991760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97353863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340159416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
     <t xml:space="preserve">4.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98865914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93454313278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97274255752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90907692909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89952683448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83983993530273</t>
+    <t xml:space="preserve">3.98865938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9345428943634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97274279594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90907669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89952707290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66078019142151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590117454529</t>
+    <t xml:space="preserve">3.67590093612671</t>
   </si>
   <si>
     <t xml:space="preserve">3.66316795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73638367652893</t>
+    <t xml:space="preserve">3.73638391494751</t>
   </si>
   <si>
     <t xml:space="preserve">3.72524237632751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70057153701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76821637153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779834747314</t>
+    <t xml:space="preserve">3.70057129859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779858589172</t>
   </si>
   <si>
     <t xml:space="preserve">3.7721951007843</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">3.76264595985413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74752497673035</t>
+    <t xml:space="preserve">3.74752473831177</t>
   </si>
   <si>
     <t xml:space="preserve">3.72922086715698</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">3.74832105636597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75150394439697</t>
+    <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
     <t xml:space="preserve">3.77697038650513</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">3.83267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80641579627991</t>
+    <t xml:space="preserve">3.80641555786133</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
@@ -4076,25 +4076,25 @@
     <t xml:space="preserve">3.93613505363464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8621232509613</t>
+    <t xml:space="preserve">3.86212348937988</t>
   </si>
   <si>
     <t xml:space="preserve">3.87008142471313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89554786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146445274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97115087509155</t>
+    <t xml:space="preserve">3.89554762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146469116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97115063667297</t>
   </si>
   <si>
     <t xml:space="preserve">3.96398854255676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95443868637085</t>
+    <t xml:space="preserve">3.95443844795227</t>
   </si>
   <si>
     <t xml:space="preserve">3.99980068206787</t>
@@ -4112,40 +4112,40 @@
     <t xml:space="preserve">3.90748476982117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90430164337158</t>
+    <t xml:space="preserve">3.95603013038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90430188179016</t>
   </si>
   <si>
     <t xml:space="preserve">3.94409251213074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00775861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96796727180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85575675964355</t>
+    <t xml:space="preserve">4.00775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96796751022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85575652122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.82710719108582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03004169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01253318786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00935029983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99820876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9162392616272</t>
+    <t xml:space="preserve">4.03004121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01253366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00934982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91623902320862</t>
   </si>
   <si>
     <t xml:space="preserve">3.8581440448761</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">3.78094935417175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55414032936096</t>
+    <t xml:space="preserve">3.55414009094238</t>
   </si>
   <si>
     <t xml:space="preserve">3.69261288642883</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">2.94374465942383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14429211616516</t>
+    <t xml:space="preserve">3.14429187774658</t>
   </si>
   <si>
     <t xml:space="preserve">3.28913140296936</t>
@@ -4205,16 +4205,16 @@
     <t xml:space="preserve">3.70852971076965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354553222656</t>
+    <t xml:space="preserve">3.74036240577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354529380798</t>
   </si>
   <si>
     <t xml:space="preserve">3.90111827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668916702271</t>
+    <t xml:space="preserve">3.90668892860413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9202184677124</t>
@@ -4223,67 +4223,67 @@
     <t xml:space="preserve">3.97194647789001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9631929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693065643311</t>
+    <t xml:space="preserve">3.96319317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693089485168</t>
   </si>
   <si>
     <t xml:space="preserve">4.03481674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06346607208252</t>
+    <t xml:space="preserve">4.06346654891968</t>
   </si>
   <si>
     <t xml:space="preserve">4.02845001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11758232116699</t>
+    <t xml:space="preserve">4.11758184432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.09848213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12235641479492</t>
+    <t xml:space="preserve">4.12235689163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.1334981918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16055631637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16214752197266</t>
+    <t xml:space="preserve">4.16055679321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16214799880981</t>
   </si>
   <si>
     <t xml:space="preserve">4.20193910598755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21467256546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19716453552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599063873291</t>
+    <t xml:space="preserve">4.21467208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19716501235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1541895866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599016189575</t>
   </si>
   <si>
     <t xml:space="preserve">4.13668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14623212814331</t>
+    <t xml:space="preserve">4.14623165130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1939811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17488145828247</t>
+    <t xml:space="preserve">4.19398069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17488098144531</t>
   </si>
   <si>
     <t xml:space="preserve">4.12554025650024</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90509796142578</t>
+    <t xml:space="preserve">3.9050977230072</t>
   </si>
   <si>
     <t xml:space="preserve">4.00298404693604</t>
@@ -4319,16 +4319,16 @@
     <t xml:space="preserve">4.09469366073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011207580566</t>
+    <t xml:space="preserve">4.23011159896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.24703884124756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28597164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25042390823364</t>
+    <t xml:space="preserve">4.28597116470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2504243850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.21487712860107</t>
@@ -4376,13 +4376,13 @@
     <t xml:space="preserve">3.7730770111084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76122760772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73075890541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65881776809692</t>
+    <t xml:space="preserve">3.76122784614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73075866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6588180065155</t>
   </si>
   <si>
     <t xml:space="preserve">3.80100655555725</t>
@@ -4394,13 +4394,13 @@
     <t xml:space="preserve">3.71467781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71044588088989</t>
+    <t xml:space="preserve">3.71044564247131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66982078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68082356452942</t>
+    <t xml:space="preserve">3.68082332611084</t>
   </si>
   <si>
     <t xml:space="preserve">3.69690442085266</t>
@@ -4409,10 +4409,10 @@
     <t xml:space="preserve">3.47177243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49123859405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6063437461853</t>
+    <t xml:space="preserve">3.4912383556366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60634350776672</t>
   </si>
   <si>
     <t xml:space="preserve">3.62919545173645</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">3.51324391365051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48700666427612</t>
+    <t xml:space="preserve">3.48700642585754</t>
   </si>
   <si>
     <t xml:space="preserve">3.33381533622742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38290452957153</t>
+    <t xml:space="preserve">3.38290429115295</t>
   </si>
   <si>
     <t xml:space="preserve">3.40406322479248</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">3.25764298439026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29657554626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24325466156006</t>
+    <t xml:space="preserve">3.29657530784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24325489997864</t>
   </si>
   <si>
     <t xml:space="preserve">3.28134107589722</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">3.73922252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67659115791321</t>
+    <t xml:space="preserve">3.67659139633179</t>
   </si>
   <si>
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55979371070862</t>
+    <t xml:space="preserve">3.55979347229004</t>
   </si>
   <si>
     <t xml:space="preserve">3.46838688850403</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">3.54709839820862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61903882026672</t>
+    <t xml:space="preserve">3.6190390586853</t>
   </si>
   <si>
     <t xml:space="preserve">3.50901198387146</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">3.49885559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4980092048645</t>
+    <t xml:space="preserve">3.49800944328308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6105751991272</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">3.70282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6791307926178</t>
+    <t xml:space="preserve">3.67913103103638</t>
   </si>
   <si>
     <t xml:space="preserve">3.68336272239685</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">3.69351863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70706033706665</t>
+    <t xml:space="preserve">3.70706057548523</t>
   </si>
   <si>
     <t xml:space="preserve">3.70029020309448</t>
@@ -4565,19 +4565,19 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010649681091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47515773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44045686721802</t>
+    <t xml:space="preserve">3.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47515749931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4404571056366</t>
   </si>
   <si>
     <t xml:space="preserve">3.38459730148315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34735703468323</t>
+    <t xml:space="preserve">3.34735727310181</t>
   </si>
   <si>
     <t xml:space="preserve">3.38036513328552</t>
@@ -4586,22 +4586,22 @@
     <t xml:space="preserve">3.40829515457153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52678537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4743115901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34820342063904</t>
+    <t xml:space="preserve">3.52678561210632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47431135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38205790519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
     <t xml:space="preserve">3.3676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37613344192505</t>
+    <t xml:space="preserve">3.37613368034363</t>
   </si>
   <si>
     <t xml:space="preserve">3.31519556045532</t>
@@ -4610,13 +4610,13 @@
     <t xml:space="preserve">3.42014408111572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4243757724762</t>
+    <t xml:space="preserve">3.42437601089478</t>
   </si>
   <si>
     <t xml:space="preserve">3.43114686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45315217971802</t>
+    <t xml:space="preserve">3.4531524181366</t>
   </si>
   <si>
     <t xml:space="preserve">3.50647306442261</t>
@@ -4625,16 +4625,16 @@
     <t xml:space="preserve">3.48954606056213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55471539497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59618759155273</t>
+    <t xml:space="preserve">3.55471563339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59618735313416</t>
   </si>
   <si>
     <t xml:space="preserve">3.58433842658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63173413276672</t>
+    <t xml:space="preserve">3.6317343711853</t>
   </si>
   <si>
     <t xml:space="preserve">3.68674778938293</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">3.72568035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81370186805725</t>
+    <t xml:space="preserve">3.81370210647583</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
@@ -4658,16 +4658,16 @@
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366452217102</t>
+    <t xml:space="preserve">3.97366428375244</t>
   </si>
   <si>
     <t xml:space="preserve">4.06422472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01259660720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98466682434082</t>
+    <t xml:space="preserve">4.01259708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
     <t xml:space="preserve">4.03037023544312</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">4.06253242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04645109176636</t>
+    <t xml:space="preserve">4.04645156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
@@ -4706,16 +4706,16 @@
     <t xml:space="preserve">4.14208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09977149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0083646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98635959625244</t>
+    <t xml:space="preserve">4.09977197647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05322217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00836515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98635983467102</t>
   </si>
   <si>
     <t xml:space="preserve">4.02359962463379</t>
@@ -4733,52 +4733,52 @@
     <t xml:space="preserve">4.00667238235474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.955890417099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84586405754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78831124305725</t>
+    <t xml:space="preserve">3.95589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84586429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78831100463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.86702275276184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88818168640137</t>
+    <t xml:space="preserve">3.88818144798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.96096873283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94150233268738</t>
+    <t xml:space="preserve">3.94150257110596</t>
   </si>
   <si>
     <t xml:space="preserve">3.93219232559204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91272640228271</t>
+    <t xml:space="preserve">3.91272664070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.89579892158508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91865086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89325952529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96435451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03544855117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97958874702454</t>
+    <t xml:space="preserve">3.91865110397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85771298408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89326000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96435403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03544807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97958922386169</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
@@ -4790,31 +4790,31 @@
     <t xml:space="preserve">3.99482321739197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98974537849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9973623752594</t>
+    <t xml:space="preserve">3.98974514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.02529239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04306554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04475831985474</t>
+    <t xml:space="preserve">4.04306602478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04475784301758</t>
   </si>
   <si>
     <t xml:space="preserve">4.05660820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08792304992676</t>
+    <t xml:space="preserve">4.0879225730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685537338257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10992860794067</t>
+    <t xml:space="preserve">4.10992813110352</t>
   </si>
   <si>
     <t xml:space="preserve">4.09638643264771</t>
@@ -4835,10 +4835,10 @@
     <t xml:space="preserve">4.15732431411743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14462947845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18271541595459</t>
+    <t xml:space="preserve">4.14462900161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18271493911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4847,43 +4847,43 @@
     <t xml:space="preserve">4.19794988632202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20556735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22926568984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21233797073364</t>
+    <t xml:space="preserve">4.20556688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2292652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2123384475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.17679071426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16155576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18863964080811</t>
+    <t xml:space="preserve">4.16155624389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18864011764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17932987213135</t>
+    <t xml:space="preserve">4.17933034896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.23349666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24026823043823</t>
+    <t xml:space="preserve">4.24026775360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.27073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29612827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33506059646606</t>
+    <t xml:space="preserve">4.2961277961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33506011962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.29443454742432</t>
@@ -4892,19 +4892,19 @@
     <t xml:space="preserve">4.28427886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04560470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09215497970581</t>
+    <t xml:space="preserve">4.04560518264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09215450286865</t>
   </si>
   <si>
     <t xml:space="preserve">3.85094213485718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87802529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784254074097</t>
+    <t xml:space="preserve">3.87802505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784230232239</t>
   </si>
   <si>
     <t xml:space="preserve">3.8526349067688</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94658088684082</t>
+    <t xml:space="preserve">3.9465811252594</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92965364456177</t>
+    <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
     <t xml:space="preserve">3.93811678886414</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">4.05491495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06676340103149</t>
+    <t xml:space="preserve">4.06676387786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518991470337</t>
@@ -4937,10 +4937,10 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29274225234985</t>
+    <t xml:space="preserve">4.28766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29274272918701</t>
   </si>
   <si>
     <t xml:space="preserve">4.32321119308472</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">4.30289888381958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25888824462891</t>
+    <t xml:space="preserve">4.25888776779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.30459117889404</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">4.33336782455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31305456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23857545852661</t>
+    <t xml:space="preserve">4.31305503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23857498168945</t>
   </si>
   <si>
     <t xml:space="preserve">4.32828903198242</t>
@@ -4979,13 +4979,13 @@
     <t xml:space="preserve">4.37907123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34013795852661</t>
+    <t xml:space="preserve">4.34013843536377</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183120727539</t>
+    <t xml:space="preserve">4.34183168411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
@@ -6605,7 +6605,7 @@
     <t xml:space="preserve">19.3850002288818</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3999996185303</t>
+    <t xml:space="preserve">19.4150009155273</t>
   </si>
 </sst>
 </file>
@@ -72048,22 +72048,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6910532407</v>
+        <v>45967.6911805556</v>
       </c>
       <c r="B2505" t="n">
-        <v>1114155</v>
+        <v>1829620</v>
       </c>
       <c r="C2505" t="n">
-        <v>19.4099998474121</v>
+        <v>19.5849990844727</v>
       </c>
       <c r="D2505" t="n">
-        <v>19.125</v>
+        <v>19.2099990844727</v>
       </c>
       <c r="E2505" t="n">
-        <v>19.3649997711182</v>
+        <v>19.3999996185303</v>
       </c>
       <c r="F2505" t="n">
-        <v>19.3999996185303</v>
+        <v>19.4150009155273</v>
       </c>
       <c r="G2505" t="s">
         <v>2197</v>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="2200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="2201">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528841972351</t>
+    <t xml:space="preserve">2.44528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50193214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40895056724548</t>
+    <t xml:space="preserve">2.50193190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40895080566406</t>
   </si>
   <si>
     <t xml:space="preserve">2.35658240318298</t>
@@ -59,55 +59,55 @@
     <t xml:space="preserve">2.29780173301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37261366844177</t>
+    <t xml:space="preserve">2.37261343002319</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33413934707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2347457408905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15458965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11183953285217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9964154958725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588387489319</t>
+    <t xml:space="preserve">2.33413887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23474597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15458989143372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11184000968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99641537666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588363647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.07977747917175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03489017486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03168439865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90343475341797</t>
+    <t xml:space="preserve">2.03489065170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03168392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02954649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90343463420868</t>
   </si>
   <si>
     <t xml:space="preserve">2.00924038887024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93549728393555</t>
+    <t xml:space="preserve">1.93549692630768</t>
   </si>
   <si>
     <t xml:space="preserve">1.84037888050079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74953532218933</t>
+    <t xml:space="preserve">1.74953544139862</t>
   </si>
   <si>
     <t xml:space="preserve">1.75701665878296</t>
@@ -116,271 +116,271 @@
     <t xml:space="preserve">1.67792952060699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349882602692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151154518127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861699104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55823004245758</t>
+    <t xml:space="preserve">1.59349846839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151142597198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861711025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55823016166687</t>
   </si>
   <si>
     <t xml:space="preserve">1.60632359981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72922897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899811267853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7431229352951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73350405693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69396090507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419188499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70571660995483</t>
+    <t xml:space="preserve">1.72922921180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67899787425995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73350393772125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69396078586578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419176578522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70571672916412</t>
   </si>
   <si>
     <t xml:space="preserve">1.66296708583832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71533536911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82541608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8232786655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88099110126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381623268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89488470554352</t>
+    <t xml:space="preserve">1.71533584594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82541620731354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82327902317047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88099098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381587505341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89488506317139</t>
   </si>
   <si>
     <t xml:space="preserve">1.86602866649628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80404126644135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556670665741</t>
+    <t xml:space="preserve">1.80404150485992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556634902954</t>
   </si>
   <si>
     <t xml:space="preserve">1.82648503780365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79976630210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92053472995758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93442809581757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229079246521</t>
+    <t xml:space="preserve">1.79976642131805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92053461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93442821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93229067325592</t>
   </si>
   <si>
     <t xml:space="preserve">1.96221554279327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9643532037735</t>
+    <t xml:space="preserve">1.96435296535492</t>
   </si>
   <si>
     <t xml:space="preserve">1.97183430194855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95580351352692</t>
+    <t xml:space="preserve">1.95580327510834</t>
   </si>
   <si>
     <t xml:space="preserve">1.95259702205658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92374074459076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87564718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88312840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91198480129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90022850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89167833328247</t>
+    <t xml:space="preserve">1.92374086380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87564730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88312876224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91198468208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90022838115692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89167857170105</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579756736755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8179349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190420150757</t>
+    <t xml:space="preserve">1.81793475151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80190408229828</t>
   </si>
   <si>
     <t xml:space="preserve">1.87992215156555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90129733085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465336799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92587828636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92801582813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91519105434418</t>
+    <t xml:space="preserve">1.90129709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465348720551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92587864398956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92801594734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91519093513489</t>
   </si>
   <si>
     <t xml:space="preserve">2.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626559257507</t>
+    <t xml:space="preserve">2.05626511573792</t>
   </si>
   <si>
     <t xml:space="preserve">2.07443380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06160879135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07015895843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02634048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05519652366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05092144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99855268001556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99214041233063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95045924186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93977224826813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8499972820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457859516144</t>
+    <t xml:space="preserve">2.0616090297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07015919685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02634024620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0551962852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05092120170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855303764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99214065074921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95045971870422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93977200984955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84999740123749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457823753357</t>
   </si>
   <si>
     <t xml:space="preserve">1.79121625423431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73884797096252</t>
+    <t xml:space="preserve">1.73884773254395</t>
   </si>
   <si>
     <t xml:space="preserve">1.72388565540314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69502913951874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678567886353</t>
+    <t xml:space="preserve">1.69502949714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678555965424</t>
   </si>
   <si>
     <t xml:space="preserve">1.70785439014435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76235282421112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700954914093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87773132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8754688501358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279733181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.906010389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451814651489</t>
+    <t xml:space="preserve">1.76235258579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8777312040329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87546908855438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279721260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90601027011871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88451838493347</t>
   </si>
   <si>
     <t xml:space="preserve">1.80081212520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8098611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81438612937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80646812915802</t>
+    <t xml:space="preserve">1.80986154079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81438624858856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80646789073944</t>
   </si>
   <si>
     <t xml:space="preserve">1.75104117393494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63113749027252</t>
+    <t xml:space="preserve">1.63113784790039</t>
   </si>
   <si>
     <t xml:space="preserve">1.54290699958801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46711897850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47390604019165</t>
+    <t xml:space="preserve">1.46711909770966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47390592098236</t>
   </si>
   <si>
     <t xml:space="preserve">1.42526590824127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51688992977142</t>
+    <t xml:space="preserve">1.51689004898071</t>
   </si>
   <si>
     <t xml:space="preserve">1.61190783977509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60059630870819</t>
+    <t xml:space="preserve">1.6005961894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.57684195041656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69900751113892</t>
+    <t xml:space="preserve">1.69900739192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.38341295719147</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27255892753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213738322258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19111514091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23636198043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18545913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14021277427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09949088096619</t>
+    <t xml:space="preserve">1.27255880832672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21373844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19111502170563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23636174201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18545925617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14021289348602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09949100017548</t>
   </si>
   <si>
     <t xml:space="preserve">1.09722852706909</t>
@@ -416,55 +416,55 @@
     <t xml:space="preserve">1.2374929189682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28726398944855</t>
+    <t xml:space="preserve">1.28726410865784</t>
   </si>
   <si>
     <t xml:space="preserve">1.36870777606964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33477294445038</t>
+    <t xml:space="preserve">1.3347727060318</t>
   </si>
   <si>
     <t xml:space="preserve">1.39359331130981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38454413414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038061141968</t>
+    <t xml:space="preserve">1.3845442533493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4003803730011</t>
   </si>
   <si>
     <t xml:space="preserve">1.36983895301819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.398118019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3788880109787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37097012996674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37775707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42979073524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40264284610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38567531108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26011598110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29631316661835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32232999801636</t>
+    <t xml:space="preserve">1.39811789989471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37888824939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37097024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37775719165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42979061603546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40264272689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38567507266998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26011610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29631352424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32233011722565</t>
   </si>
   <si>
     <t xml:space="preserve">1.37549459934235</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">1.43657767772675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45354473590851</t>
+    <t xml:space="preserve">1.4535448551178</t>
   </si>
   <si>
     <t xml:space="preserve">1.44788920879364</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.47051239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45015144348145</t>
+    <t xml:space="preserve">1.45015132427216</t>
   </si>
   <si>
     <t xml:space="preserve">1.41961014270782</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">1.38001942634583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39698684215546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33137953281403</t>
+    <t xml:space="preserve">1.39698672294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33137929439545</t>
   </si>
   <si>
     <t xml:space="preserve">1.33251047134399</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">1.38228166103363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3675764799118</t>
+    <t xml:space="preserve">1.36757671833038</t>
   </si>
   <si>
     <t xml:space="preserve">1.33816635608673</t>
@@ -515,52 +515,52 @@
     <t xml:space="preserve">1.32798600196838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41056072711945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40377402305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42413473129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43883955478668</t>
+    <t xml:space="preserve">1.41056060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40377378463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42413485050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43883991241455</t>
   </si>
   <si>
     <t xml:space="preserve">1.45920073986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.477299451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48748004436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48974239826202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39019978046417</t>
+    <t xml:space="preserve">1.47729933261871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48748028278351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48974227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39019989967346</t>
   </si>
   <si>
     <t xml:space="preserve">1.40716731548309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3607896566391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282296180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513365268707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3494781255722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34269118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536270141602</t>
+    <t xml:space="preserve">1.36078953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513377189636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34947800636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34269094467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536282062531</t>
   </si>
   <si>
     <t xml:space="preserve">1.27821481227875</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">1.31780540943146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28613293170929</t>
+    <t xml:space="preserve">1.2861328125</t>
   </si>
   <si>
     <t xml:space="preserve">1.28500175476074</t>
@@ -578,40 +578,40 @@
     <t xml:space="preserve">1.27934587001801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35174036026001</t>
+    <t xml:space="preserve">1.3517404794693</t>
   </si>
   <si>
     <t xml:space="preserve">1.35852742195129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37210142612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39472496509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41621661186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44110226631165</t>
+    <t xml:space="preserve">1.37210130691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39472472667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41621673107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44110250473022</t>
   </si>
   <si>
     <t xml:space="preserve">1.49313580989838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52480828762054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53159534931183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51575934886932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54856252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5655300617218</t>
+    <t xml:space="preserve">1.52480852603912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53159523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51575922966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54856264591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56553018093109</t>
   </si>
   <si>
     <t xml:space="preserve">1.61077690124512</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">1.63453114032745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59833407402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571089267731</t>
+    <t xml:space="preserve">1.5983339548111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571077346802</t>
   </si>
   <si>
     <t xml:space="preserve">1.57118618488312</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">1.50444746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51802146434784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47503733634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6571546792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69335186481476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733491420746</t>
+    <t xml:space="preserve">1.51802134513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47503709793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65715444087982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69335162639618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733527183533</t>
   </si>
   <si>
     <t xml:space="preserve">1.66167914867401</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">1.63905584812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172748565674</t>
+    <t xml:space="preserve">1.60172736644745</t>
   </si>
   <si>
     <t xml:space="preserve">1.57457935810089</t>
@@ -662,40 +662,40 @@
     <t xml:space="preserve">1.62661278247833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58476006984711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5610054731369</t>
+    <t xml:space="preserve">1.58475983142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100571155548</t>
   </si>
   <si>
     <t xml:space="preserve">1.54064464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6051207780838</t>
+    <t xml:space="preserve">1.60512113571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.64923632144928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66620397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6243509054184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72049963474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79741871356964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284566879272</t>
+    <t xml:space="preserve">1.6662038564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62435078620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72049987316132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79741847515106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284578800201</t>
   </si>
   <si>
     <t xml:space="preserve">1.84492766857147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83022248744965</t>
+    <t xml:space="preserve">1.83022260665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.86302614212036</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">1.85623955726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91053509712219</t>
+    <t xml:space="preserve">1.91053521633148</t>
   </si>
   <si>
     <t xml:space="preserve">1.89922344684601</t>
@@ -713,28 +713,28 @@
     <t xml:space="preserve">1.91166639328003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92637157440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94560134410858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446992874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8969612121582</t>
+    <t xml:space="preserve">1.9263710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94560122489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446980953217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89696097373962</t>
   </si>
   <si>
     <t xml:space="preserve">1.93655169010162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98066735267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01347136497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781512260437</t>
+    <t xml:space="preserve">1.98066711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0134711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781536102295</t>
   </si>
   <si>
     <t xml:space="preserve">2.01573324203491</t>
@@ -743,118 +743,118 @@
     <t xml:space="preserve">2.01912665367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96483099460602</t>
+    <t xml:space="preserve">1.96483087539673</t>
   </si>
   <si>
     <t xml:space="preserve">1.99876570701599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02025818824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727382183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01007747650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97161817550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94786357879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953593730927</t>
+    <t xml:space="preserve">2.0202579498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01007771492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97161793708801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94786369800568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953581809998</t>
   </si>
   <si>
     <t xml:space="preserve">2.0225203037262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08247137069702</t>
+    <t xml:space="preserve">1.99084758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08247184753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.08699655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05079960823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93202710151672</t>
+    <t xml:space="preserve">2.05079889297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193090438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542075157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93202722072601</t>
   </si>
   <si>
     <t xml:space="preserve">1.96709334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894618034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90940380096436</t>
+    <t xml:space="preserve">2.00894641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90940415859222</t>
   </si>
   <si>
     <t xml:space="preserve">1.89130532741547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.873206615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999331951141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8551082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596217155457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03609395027161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424111843109</t>
+    <t xml:space="preserve">1.87320685386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8799934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510802268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96596193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03609418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424123764038</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215935707092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0032901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02478265762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01799583435059</t>
+    <t xml:space="preserve">2.00329065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02478241920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01799559593201</t>
   </si>
   <si>
     <t xml:space="preserve">2.00442171096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95465052127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02930760383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02817606925964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0926525592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13224315643311</t>
+    <t xml:space="preserve">1.9546502828598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02930736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02817583084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09265208244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13224339485168</t>
   </si>
   <si>
     <t xml:space="preserve">2.12432479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12093138694763</t>
+    <t xml:space="preserve">2.12093162536621</t>
   </si>
   <si>
     <t xml:space="preserve">2.15939092636108</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">2.14016103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10848879814148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0756847858429</t>
+    <t xml:space="preserve">2.1084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
     <t xml:space="preserve">2.14921045303345</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">2.1933262348175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17862057685852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23291683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1955885887146</t>
+    <t xml:space="preserve">2.17862105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23291659355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558835029602</t>
   </si>
   <si>
     <t xml:space="preserve">2.20803117752075</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">2.20576882362366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18314552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16617774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20350623130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19219470024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15825986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20011305809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17522716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17748975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15599751472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14129281044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09378337860107</t>
+    <t xml:space="preserve">2.18314528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16617798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2035059928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19219493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15825963020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20011329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17522764205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17748951911926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15599775314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14129209518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09378361701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.07907843589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08812737464905</t>
+    <t xml:space="preserve">2.08812761306763</t>
   </si>
   <si>
     <t xml:space="preserve">2.11188220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10962009429932</t>
+    <t xml:space="preserve">2.10961985588074</t>
   </si>
   <si>
     <t xml:space="preserve">2.222736120224</t>
@@ -950,28 +950,28 @@
     <t xml:space="preserve">2.25780200958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31436038017273</t>
+    <t xml:space="preserve">2.31436061859131</t>
   </si>
   <si>
     <t xml:space="preserve">2.33132791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34716439247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40032887458801</t>
+    <t xml:space="preserve">2.34716415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40032863616943</t>
   </si>
   <si>
     <t xml:space="preserve">2.41164064407349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43878817558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44557499885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127945899963</t>
+    <t xml:space="preserve">2.43878841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127993583679</t>
   </si>
   <si>
     <t xml:space="preserve">2.32567191123962</t>
@@ -980,73 +980,73 @@
     <t xml:space="preserve">2.38675498962402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3630006313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33585262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25893306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24988389015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27137589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33769392967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30216646194458</t>
+    <t xml:space="preserve">2.36300039291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33585238456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25893330574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24988436698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27137613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33769369125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30216670036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.36137866973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35072040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30808758735657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21453261375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21926951408386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18137407302856</t>
+    <t xml:space="preserve">2.35072064399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30808806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21453237533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21926927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558453559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2109797000885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18137335777283</t>
   </si>
   <si>
     <t xml:space="preserve">2.14584636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13637256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10913515090942</t>
+    <t xml:space="preserve">2.13637280464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10913491249084</t>
   </si>
   <si>
     <t xml:space="preserve">2.14110970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14229369163513</t>
+    <t xml:space="preserve">2.14229393005371</t>
   </si>
   <si>
     <t xml:space="preserve">2.16361021995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.186110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13874101638794</t>
+    <t xml:space="preserve">2.18611073493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13874125480652</t>
   </si>
   <si>
     <t xml:space="preserve">2.11979341506958</t>
@@ -1055,79 +1055,79 @@
     <t xml:space="preserve">2.1493992805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13755702972412</t>
+    <t xml:space="preserve">2.13755679130554</t>
   </si>
   <si>
     <t xml:space="preserve">2.16597867012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15532040596008</t>
+    <t xml:space="preserve">2.15532064437866</t>
   </si>
   <si>
     <t xml:space="preserve">2.20032167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1837420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23821759223938</t>
+    <t xml:space="preserve">2.18374228477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2382173538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.27374458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39453768730164</t>
+    <t xml:space="preserve">2.39453744888306</t>
   </si>
   <si>
     <t xml:space="preserve">2.3838791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34835171699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36848425865173</t>
+    <t xml:space="preserve">2.34835195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36848402023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.37322115898132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36966824531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37203645706177</t>
+    <t xml:space="preserve">2.36966800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37203669548035</t>
   </si>
   <si>
     <t xml:space="preserve">2.38032650947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38861632347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34361481666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30927205085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28913974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2938768863678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33058881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34953641891479</t>
+    <t xml:space="preserve">2.38861608505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34361529350281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30927181243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28913998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29387712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3305881023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34953594207764</t>
   </si>
   <si>
     <t xml:space="preserve">2.36019444465637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31637763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34479951858521</t>
+    <t xml:space="preserve">2.31637740135193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34479928016663</t>
   </si>
   <si>
     <t xml:space="preserve">2.31756162643433</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">2.40401148796082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40993285179138</t>
+    <t xml:space="preserve">2.40993237495422</t>
   </si>
   <si>
     <t xml:space="preserve">2.37914228439331</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">2.3554573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31045627593994</t>
+    <t xml:space="preserve">2.31045603752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25953388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27966594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25598096847534</t>
+    <t xml:space="preserve">2.27966570854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25598120689392</t>
   </si>
   <si>
     <t xml:space="preserve">2.23111200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22163820266724</t>
+    <t xml:space="preserve">2.22163796424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.19676899909973</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">2.19321608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18847942352295</t>
+    <t xml:space="preserve">2.18847918510437</t>
   </si>
   <si>
     <t xml:space="preserve">2.18492650985718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13163542747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005730628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058350563049</t>
+    <t xml:space="preserve">2.13163590431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058374404907</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13045167922974</t>
+    <t xml:space="preserve">2.13045144081116</t>
   </si>
   <si>
     <t xml:space="preserve">2.12097764015198</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">2.11031937599182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842661857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22400641441345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24295425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29624557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28795528411865</t>
+    <t xml:space="preserve">2.08426594734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22400665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24295473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29624533653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28795552253723</t>
   </si>
   <si>
     <t xml:space="preserve">2.25005984306335</t>
@@ -1223,64 +1223,64 @@
     <t xml:space="preserve">2.24413847923279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22755932807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22637510299683</t>
+    <t xml:space="preserve">2.22755908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22637534141541</t>
   </si>
   <si>
     <t xml:space="preserve">2.2370331287384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24769163131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2926926612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3211145401001</t>
+    <t xml:space="preserve">2.24769139289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29269242286682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32111430168152</t>
   </si>
   <si>
     <t xml:space="preserve">2.25716519355774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27137613296509</t>
+    <t xml:space="preserve">2.27137637138367</t>
   </si>
   <si>
     <t xml:space="preserve">2.30453491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29742956161499</t>
+    <t xml:space="preserve">2.29742980003357</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124406814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3187460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27848196029663</t>
+    <t xml:space="preserve">2.31874561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27848172187805</t>
   </si>
   <si>
     <t xml:space="preserve">2.2666392326355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28321838378906</t>
+    <t xml:space="preserve">2.28321886062622</t>
   </si>
   <si>
     <t xml:space="preserve">2.32703566551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34598350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30571961402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27729725837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20742726325989</t>
+    <t xml:space="preserve">2.3459837436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30571937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2772970199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20742702484131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19203186035156</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.1482150554657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19795322418213</t>
+    <t xml:space="preserve">2.19795298576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.20979571342468</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">2.19913721084595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23348045349121</t>
+    <t xml:space="preserve">2.23348069190979</t>
   </si>
   <si>
     <t xml:space="preserve">2.23584914207458</t>
@@ -1307,25 +1307,25 @@
     <t xml:space="preserve">2.28084993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26900768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24177050590515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27019214630127</t>
+    <t xml:space="preserve">2.26900792121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27256035804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24177002906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361275672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27019190788269</t>
   </si>
   <si>
     <t xml:space="preserve">2.26308631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28677129745483</t>
+    <t xml:space="preserve">2.28677153587341</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032421112061</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">2.30098223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3317723274231</t>
+    <t xml:space="preserve">2.33177256584167</t>
   </si>
   <si>
     <t xml:space="preserve">2.3282196521759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31519317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39098477363586</t>
+    <t xml:space="preserve">2.31519341468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39098453521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.41585373878479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41940641403198</t>
+    <t xml:space="preserve">2.41940665245056</t>
   </si>
   <si>
     <t xml:space="preserve">2.4371702671051</t>
@@ -1358,88 +1358,88 @@
     <t xml:space="preserve">2.48098707199097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53309345245361</t>
+    <t xml:space="preserve">2.53309369087219</t>
   </si>
   <si>
     <t xml:space="preserve">2.56743669509888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54612040519714</t>
+    <t xml:space="preserve">2.54612064361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.56151556968689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57572650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56862092018127</t>
+    <t xml:space="preserve">2.57572627067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56862115859985</t>
   </si>
   <si>
     <t xml:space="preserve">2.57691097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56980538368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56625247001648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63967561721802</t>
+    <t xml:space="preserve">2.56980514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56625270843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63967537879944</t>
   </si>
   <si>
     <t xml:space="preserve">2.65743899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6669135093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63671517372131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62960934638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58105540275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57158160209656</t>
+    <t xml:space="preserve">2.66691303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63671469688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62960958480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58105564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57158184051514</t>
   </si>
   <si>
     <t xml:space="preserve">2.56921315193176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48039507865906</t>
+    <t xml:space="preserve">2.48039531707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.53013300895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45611786842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48217105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44605183601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4069721698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236709594727</t>
+    <t xml:space="preserve">2.45611763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48217153549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40697193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236733436584</t>
   </si>
   <si>
     <t xml:space="preserve">2.4709210395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45552563667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44723606109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46559143066406</t>
+    <t xml:space="preserve">2.45552587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44723629951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46559190750122</t>
   </si>
   <si>
     <t xml:space="preserve">2.47388172149658</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">2.41881465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40934014320374</t>
+    <t xml:space="preserve">2.40934038162231</t>
   </si>
   <si>
     <t xml:space="preserve">2.43480157852173</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">2.33473324775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35190439224243</t>
+    <t xml:space="preserve">2.35190486907959</t>
   </si>
   <si>
     <t xml:space="preserve">2.39631390571594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3744056224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.357825756073</t>
+    <t xml:space="preserve">2.37440538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35782599449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.42592000961304</t>
@@ -1481,37 +1481,37 @@
     <t xml:space="preserve">2.36611557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38624811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39986681938171</t>
+    <t xml:space="preserve">2.38624787330627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39986634254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.32881212234497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3524968624115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302306175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37499761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36374688148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39809036254883</t>
+    <t xml:space="preserve">2.35249710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302282333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37499737739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36374735832214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39809012413025</t>
   </si>
   <si>
     <t xml:space="preserve">2.38565540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4123010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41822242736816</t>
+    <t xml:space="preserve">2.41230082511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41822218894958</t>
   </si>
   <si>
     <t xml:space="preserve">2.45078897476196</t>
@@ -1523,28 +1523,28 @@
     <t xml:space="preserve">2.51355361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54315948486328</t>
+    <t xml:space="preserve">2.54315996170044</t>
   </si>
   <si>
     <t xml:space="preserve">2.54079127311707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54375171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756875991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61066150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58223986625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59408211708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61480617523193</t>
+    <t xml:space="preserve">2.54375195503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756852149963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61066174507141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58224010467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59408235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61480665206909</t>
   </si>
   <si>
     <t xml:space="preserve">2.63493847846985</t>
@@ -1553,19 +1553,19 @@
     <t xml:space="preserve">2.65803098678589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64204406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67164993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67520260810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58638477325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60177993774414</t>
+    <t xml:space="preserve">2.64204382896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67165017127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6752028465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58638453483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60177969932556</t>
   </si>
   <si>
     <t xml:space="preserve">2.55855512619019</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">2.57039737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59349036216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59526658058167</t>
+    <t xml:space="preserve">2.59349012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59526610374451</t>
   </si>
   <si>
     <t xml:space="preserve">2.51059317588806</t>
@@ -1595,25 +1595,25 @@
     <t xml:space="preserve">2.48621010780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4354841709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38785028457642</t>
+    <t xml:space="preserve">2.43548393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888381004333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.387850522995</t>
   </si>
   <si>
     <t xml:space="preserve">2.3773341178894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25917863845825</t>
+    <t xml:space="preserve">2.25917887687683</t>
   </si>
   <si>
     <t xml:space="preserve">2.31176090240479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25361108779907</t>
+    <t xml:space="preserve">2.25361132621765</t>
   </si>
   <si>
     <t xml:space="preserve">2.33464980125427</t>
@@ -1628,37 +1628,37 @@
     <t xml:space="preserve">2.22577357292175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23567128181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16020035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24989938735962</t>
+    <t xml:space="preserve">2.23567152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16020059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2498996257782</t>
   </si>
   <si>
     <t xml:space="preserve">2.2319598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23938298225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24371337890625</t>
+    <t xml:space="preserve">2.23938322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24371361732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.20041036605835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20968985557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22329926490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20721530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15525126457214</t>
+    <t xml:space="preserve">2.2096893787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22329902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20721554756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298720359802</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">2.05812883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0587477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379891395569</t>
+    <t xml:space="preserve">2.05874800682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379843711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843570709229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04699373245239</t>
+    <t xml:space="preserve">2.04699397087097</t>
   </si>
   <si>
     <t xml:space="preserve">2.04946851730347</t>
@@ -1685,25 +1685,25 @@
     <t xml:space="preserve">2.0921528339386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10143232345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1410231590271</t>
+    <t xml:space="preserve">2.11689734458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10143208503723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14102339744568</t>
   </si>
   <si>
     <t xml:space="preserve">2.11813473701477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08906006813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0686457157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09091591835022</t>
+    <t xml:space="preserve">2.08905982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06864595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0909161567688</t>
   </si>
   <si>
     <t xml:space="preserve">2.10638117790222</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">2.14349770545959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13793063163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12122797966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09957647323608</t>
+    <t xml:space="preserve">2.13793039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12122774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0995762348175</t>
   </si>
   <si>
     <t xml:space="preserve">2.11380457878113</t>
@@ -1730,79 +1730,79 @@
     <t xml:space="preserve">2.14473509788513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18061470985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16514921188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20102882385254</t>
+    <t xml:space="preserve">2.18061494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16514945030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20102906227112</t>
   </si>
   <si>
     <t xml:space="preserve">2.09029722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1243212223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10699987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13916778564453</t>
+    <t xml:space="preserve">2.12432098388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10699963569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13916754722595</t>
   </si>
   <si>
     <t xml:space="preserve">2.1199905872345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07730603218079</t>
+    <t xml:space="preserve">2.07730627059937</t>
   </si>
   <si>
     <t xml:space="preserve">2.07235717773438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11937236785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20474028587341</t>
+    <t xml:space="preserve">2.11937189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20474052429199</t>
   </si>
   <si>
     <t xml:space="preserve">2.28392314910889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23319697380066</t>
+    <t xml:space="preserve">2.23319673538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.19175004959106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24309492111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26289057731628</t>
+    <t xml:space="preserve">2.24309420585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26289033889771</t>
   </si>
   <si>
     <t xml:space="preserve">2.25299263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26969480514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711844444275</t>
+    <t xml:space="preserve">2.26969504356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711892127991</t>
   </si>
   <si>
     <t xml:space="preserve">2.25608587265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24185729026794</t>
+    <t xml:space="preserve">2.2418577671051</t>
   </si>
   <si>
     <t xml:space="preserve">2.19917321205139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2220618724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27526259422302</t>
+    <t xml:space="preserve">2.22206234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2752628326416</t>
   </si>
   <si>
     <t xml:space="preserve">2.32846331596375</t>
@@ -1817,28 +1817,28 @@
     <t xml:space="preserve">2.3699107170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33712434768677</t>
+    <t xml:space="preserve">2.33712410926819</t>
   </si>
   <si>
     <t xml:space="preserve">2.33836126327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3340311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3600127696991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40146017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41630697250366</t>
+    <t xml:space="preserve">2.33403086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36001300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40145993232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41630673408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.41445112228394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4206371307373</t>
+    <t xml:space="preserve">2.42063736915588</t>
   </si>
   <si>
     <t xml:space="preserve">2.45589828491211</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">2.44352555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47012615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48682904243469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50600576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3730034828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.367436170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30743098258972</t>
+    <t xml:space="preserve">2.47012591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48682880401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50600600242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37300395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36743640899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30743074417114</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795281410217</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">2.36496186256409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27093267440796</t>
+    <t xml:space="preserve">2.27093243598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.2808301448822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19793629646301</t>
+    <t xml:space="preserve">2.19793581962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.1985547542572</t>
@@ -1886,31 +1886,31 @@
     <t xml:space="preserve">2.20907115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1830894947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17504715919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19979166984558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16824293136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648889541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09772038459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13978624343872</t>
+    <t xml:space="preserve">2.18308901786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17504739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16824269294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15648913383484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09772062301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1397864818573</t>
   </si>
   <si>
     <t xml:space="preserve">2.1218466758728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1966986656189</t>
+    <t xml:space="preserve">2.19669842720032</t>
   </si>
   <si>
     <t xml:space="preserve">2.17381000518799</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">2.21525716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24247598648071</t>
+    <t xml:space="preserve">2.24247622489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.24433207511902</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">2.2474250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25979733467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33217549324036</t>
+    <t xml:space="preserve">2.25979709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33217573165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.34949636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26598358154297</t>
+    <t xml:space="preserve">2.26598381996155</t>
   </si>
   <si>
     <t xml:space="preserve">2.26227188110352</t>
@@ -1946,73 +1946,73 @@
     <t xml:space="preserve">2.28825354576111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22701048851013</t>
+    <t xml:space="preserve">2.22701072692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.20412230491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15834474563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13731169700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443388938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22639203071594</t>
+    <t xml:space="preserve">2.15834450721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1373119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2344343662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22639226913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.28949069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24680638313293</t>
+    <t xml:space="preserve">2.24680662155151</t>
   </si>
   <si>
     <t xml:space="preserve">2.23381567001343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15277743339539</t>
+    <t xml:space="preserve">2.15277695655823</t>
   </si>
   <si>
     <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15401434898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18556356430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21278285980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19607973098755</t>
+    <t xml:space="preserve">2.15401458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18556380271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21278262138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19608020782471</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13607454299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1762843132019</t>
+    <t xml:space="preserve">2.13607430458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17628479003906</t>
   </si>
   <si>
     <t xml:space="preserve">2.14040493965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27959299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3241331577301</t>
+    <t xml:space="preserve">2.27959275245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32413339614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.31794714927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35073351860046</t>
+    <t xml:space="preserve">2.35073375701904</t>
   </si>
   <si>
     <t xml:space="preserve">2.38846898078918</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">2.41012048721313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43053507804871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32227778434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37424111366272</t>
+    <t xml:space="preserve">2.43053483963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32227730751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37424087524414</t>
   </si>
   <si>
     <t xml:space="preserve">2.41259503364563</t>
@@ -2036,28 +2036,28 @@
     <t xml:space="preserve">2.43424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44971203804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45342373847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5511646270752</t>
+    <t xml:space="preserve">2.44971179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45342350006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55116438865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.53260636329651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47321915626526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136330604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50043821334839</t>
+    <t xml:space="preserve">2.47321939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50043797492981</t>
   </si>
   <si>
     <t xml:space="preserve">2.5152850151062</t>
@@ -2069,22 +2069,22 @@
     <t xml:space="preserve">2.46208429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32908225059509</t>
+    <t xml:space="preserve">2.32908248901367</t>
   </si>
   <si>
     <t xml:space="preserve">2.36124992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42620444297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44105124473572</t>
+    <t xml:space="preserve">2.42620468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410514831543</t>
   </si>
   <si>
     <t xml:space="preserve">2.37609672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45713520050049</t>
+    <t xml:space="preserve">2.45713543891907</t>
   </si>
   <si>
     <t xml:space="preserve">2.4509494304657</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">2.47507500648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46579623222351</t>
+    <t xml:space="preserve">2.46579575538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.47569370269775</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">2.4818799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47878646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49548959732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50662422180176</t>
+    <t xml:space="preserve">2.47878694534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4954891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50662446022034</t>
   </si>
   <si>
     <t xml:space="preserve">2.52889442443848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53446221351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50786185264587</t>
+    <t xml:space="preserve">2.53446197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50786137580872</t>
   </si>
   <si>
     <t xml:space="preserve">2.55302023887634</t>
@@ -2129,22 +2129,22 @@
     <t xml:space="preserve">2.56601119041443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58147692680359</t>
+    <t xml:space="preserve">2.58147668838501</t>
   </si>
   <si>
     <t xml:space="preserve">2.64952421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6829297542572</t>
+    <t xml:space="preserve">2.68292927742004</t>
   </si>
   <si>
     <t xml:space="preserve">2.69901347160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69220876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68231105804443</t>
+    <t xml:space="preserve">2.69220900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68231081962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.66870164871216</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">2.67179417610168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69282722473145</t>
+    <t xml:space="preserve">2.69282746315002</t>
   </si>
   <si>
     <t xml:space="preserve">2.71014833450317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74664664268494</t>
+    <t xml:space="preserve">2.74664688110352</t>
   </si>
   <si>
     <t xml:space="preserve">2.76396775245667</t>
@@ -2168,19 +2168,19 @@
     <t xml:space="preserve">2.7299439907074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83696436882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8344898223877</t>
+    <t xml:space="preserve">2.83696413040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83448958396912</t>
   </si>
   <si>
     <t xml:space="preserve">2.86109018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85057401657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79799175262451</t>
+    <t xml:space="preserve">2.85057377815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79799151420593</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716304779053</t>
@@ -2192,61 +2192,61 @@
     <t xml:space="preserve">2.78500080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78994941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82088017463684</t>
+    <t xml:space="preserve">2.78994965553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.820880651474</t>
   </si>
   <si>
     <t xml:space="preserve">2.83943867683411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83881998062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79737329483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81160116195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78685712814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922890663147</t>
+    <t xml:space="preserve">2.83882021903992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79737305641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81160092353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78685617446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922914505005</t>
   </si>
   <si>
     <t xml:space="preserve">2.80603361129761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81778740882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7955174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74417209625244</t>
+    <t xml:space="preserve">2.81778717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79551720619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74417281150818</t>
   </si>
   <si>
     <t xml:space="preserve">2.65694761276245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65014266967773</t>
+    <t xml:space="preserve">2.65014290809631</t>
   </si>
   <si>
     <t xml:space="preserve">2.59137463569641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6909716129303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66560792922974</t>
+    <t xml:space="preserve">2.69097137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66560816764832</t>
   </si>
   <si>
     <t xml:space="preserve">2.73056292533875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79984736442566</t>
+    <t xml:space="preserve">2.79984784126282</t>
   </si>
   <si>
     <t xml:space="preserve">2.76334929466248</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">2.75625872612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79106640815735</t>
+    <t xml:space="preserve">2.79106664657593</t>
   </si>
   <si>
     <t xml:space="preserve">2.68084192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79235529899597</t>
+    <t xml:space="preserve">2.79235553741455</t>
   </si>
   <si>
     <t xml:space="preserve">2.72596311569214</t>
@@ -2273,40 +2273,40 @@
     <t xml:space="preserve">2.6814866065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62863039970398</t>
+    <t xml:space="preserve">2.6286301612854</t>
   </si>
   <si>
     <t xml:space="preserve">2.65892601013184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66279363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63443183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68664336204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66666102409363</t>
+    <t xml:space="preserve">2.66279339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6344313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68664312362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66666126251221</t>
   </si>
   <si>
     <t xml:space="preserve">2.65183520317078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472721099854</t>
+    <t xml:space="preserve">2.66472744941711</t>
   </si>
   <si>
     <t xml:space="preserve">2.68857717514038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6943781375885</t>
+    <t xml:space="preserve">2.69437789916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.68986630439758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72016215324402</t>
+    <t xml:space="preserve">2.72016191482544</t>
   </si>
   <si>
     <t xml:space="preserve">2.69695687294006</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">2.73563194274902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176431655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75883746147156</t>
+    <t xml:space="preserve">2.73176455497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76205992698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7588369846344</t>
   </si>
   <si>
     <t xml:space="preserve">2.79428935050964</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">2.79944634437561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.820072889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86197113990784</t>
+    <t xml:space="preserve">2.82007336616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86197137832642</t>
   </si>
   <si>
     <t xml:space="preserve">2.91160464286804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90773701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8916220664978</t>
+    <t xml:space="preserve">2.90773725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89162278175354</t>
   </si>
   <si>
     <t xml:space="preserve">2.89484524726868</t>
@@ -2363,43 +2363,43 @@
     <t xml:space="preserve">2.95414757728577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.974773645401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96832871437073</t>
+    <t xml:space="preserve">2.97477388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96832823753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.97541880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98702144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9689724445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97735261917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91805028915405</t>
+    <t xml:space="preserve">2.98702120780945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96897268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97735214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91805005073547</t>
   </si>
   <si>
     <t xml:space="preserve">3.04181146621704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02118468284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0366542339325</t>
+    <t xml:space="preserve">3.02118420600891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03665471076965</t>
   </si>
   <si>
     <t xml:space="preserve">3.03923296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04825711250305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829267501831</t>
+    <t xml:space="preserve">3.04825735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829243659973</t>
   </si>
   <si>
     <t xml:space="preserve">2.97155117988586</t>
@@ -2408,37 +2408,37 @@
     <t xml:space="preserve">2.98895525932312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90902590751648</t>
+    <t xml:space="preserve">2.90902614593506</t>
   </si>
   <si>
     <t xml:space="preserve">2.86003732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84263300895691</t>
+    <t xml:space="preserve">2.84263348579407</t>
   </si>
   <si>
     <t xml:space="preserve">2.78655433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76592707633972</t>
+    <t xml:space="preserve">2.7659273147583</t>
   </si>
   <si>
     <t xml:space="preserve">2.83812141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73434257507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78010869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84843516349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87421822547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9560809135437</t>
+    <t xml:space="preserve">2.73434281349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78010892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84843468666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87421846389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95608115196228</t>
   </si>
   <si>
     <t xml:space="preserve">2.9477014541626</t>
@@ -2450,31 +2450,31 @@
     <t xml:space="preserve">2.91676139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94705700874329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91031527519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96510553359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94576787948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94125556945801</t>
+    <t xml:space="preserve">2.94705677032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91031551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96510529518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94576740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94125580787659</t>
   </si>
   <si>
     <t xml:space="preserve">2.94383382797241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97606348991394</t>
+    <t xml:space="preserve">2.97606325149536</t>
   </si>
   <si>
     <t xml:space="preserve">2.95479202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801448822021</t>
+    <t xml:space="preserve">2.95801520347595</t>
   </si>
   <si>
     <t xml:space="preserve">2.98959946632385</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">3.05921483039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11013722419739</t>
+    <t xml:space="preserve">3.11013746261597</t>
   </si>
   <si>
     <t xml:space="preserve">3.10884833335876</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">3.080486536026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1024022102356</t>
+    <t xml:space="preserve">3.11464953422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10240268707275</t>
   </si>
   <si>
     <t xml:space="preserve">3.09853529930115</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">3.06372737884521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10175800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12431883811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14945769309998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13592076301575</t>
+    <t xml:space="preserve">3.10175776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12431836128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14945721626282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13592100143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.07661890983582</t>
@@ -2522,28 +2522,28 @@
     <t xml:space="preserve">3.05663681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02698588371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696774482727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0875768661499</t>
+    <t xml:space="preserve">3.02698564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696822166443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08757710456848</t>
   </si>
   <si>
     <t xml:space="preserve">3.12560796737671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19071102142334</t>
+    <t xml:space="preserve">3.19071125984192</t>
   </si>
   <si>
     <t xml:space="preserve">3.15396952629089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15010213851929</t>
+    <t xml:space="preserve">3.15010237693787</t>
   </si>
   <si>
     <t xml:space="preserve">3.17781949043274</t>
@@ -2552,46 +2552,46 @@
     <t xml:space="preserve">3.20553636550903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22680830955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22165131568909</t>
+    <t xml:space="preserve">3.22680807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22165155410767</t>
   </si>
   <si>
     <t xml:space="preserve">3.21262717247009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23325395584106</t>
+    <t xml:space="preserve">3.23325371742249</t>
   </si>
   <si>
     <t xml:space="preserve">3.25001287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21391630172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23969960212708</t>
+    <t xml:space="preserve">3.21391654014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23970007896423</t>
   </si>
   <si>
     <t xml:space="preserve">3.26548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24743437767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22229623794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447219848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185837745667</t>
+    <t xml:space="preserve">3.24743485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2222957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25388097763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739905357361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185813903809</t>
   </si>
   <si>
     <t xml:space="preserve">3.3995578289032</t>
@@ -2600,103 +2600,103 @@
     <t xml:space="preserve">3.4111602306366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43307662010193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4910888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4382336139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4537034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600347518921</t>
+    <t xml:space="preserve">3.43307685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49108910560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304034233093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823313713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600371360779</t>
   </si>
   <si>
     <t xml:space="preserve">3.41631722450256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41502809524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.413738489151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44596815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987086296082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920851707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34541249275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32994246482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38924431800842</t>
+    <t xml:space="preserve">3.4150276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41373896598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44596767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920899391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34541201591492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32994174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38924384117126</t>
   </si>
   <si>
     <t xml:space="preserve">3.38795495033264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34799027442932</t>
+    <t xml:space="preserve">3.34799075126648</t>
   </si>
   <si>
     <t xml:space="preserve">3.29126691818237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2719292640686</t>
+    <t xml:space="preserve">3.27192950248718</t>
   </si>
   <si>
     <t xml:space="preserve">3.32865309715271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43049788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43694376945496</t>
+    <t xml:space="preserve">3.36861777305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43049812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43694400787354</t>
   </si>
   <si>
     <t xml:space="preserve">3.42405200004578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42147374153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47819709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45499277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37635254859924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2951340675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26032686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22938680648804</t>
+    <t xml:space="preserve">3.42147397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4781973361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4549925327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37635207176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513382911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35572552680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26032662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22938632965088</t>
   </si>
   <si>
     <t xml:space="preserve">3.30544757843018</t>
@@ -2705,106 +2705,106 @@
     <t xml:space="preserve">3.33252048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31576132774353</t>
+    <t xml:space="preserve">3.31576108932495</t>
   </si>
   <si>
     <t xml:space="preserve">3.23841094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14752388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18490958213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006657600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815066337585</t>
+    <t xml:space="preserve">3.1475236415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18490982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815042495728</t>
   </si>
   <si>
     <t xml:space="preserve">3.17395162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13205361366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09982442855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12238454818726</t>
+    <t xml:space="preserve">3.1320538520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09982466697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12238478660583</t>
   </si>
   <si>
     <t xml:space="preserve">3.04890179634094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1159393787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14623498916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02182912826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96703934669495</t>
+    <t xml:space="preserve">3.11593866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14623475074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0218288898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96703910827637</t>
   </si>
   <si>
     <t xml:space="preserve">3.00958204269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0431010723114</t>
+    <t xml:space="preserve">3.04310083389282</t>
   </si>
   <si>
     <t xml:space="preserve">3.09466791152954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07017302513123</t>
+    <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
     <t xml:space="preserve">3.15848207473755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18297624588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40084671974182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854617118835</t>
+    <t xml:space="preserve">3.18297600746155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40084719657898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854664802551</t>
   </si>
   <si>
     <t xml:space="preserve">3.54394555091858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47561860084534</t>
+    <t xml:space="preserve">3.4756190776825</t>
   </si>
   <si>
     <t xml:space="preserve">3.39440059661865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17459678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1423671245575</t>
+    <t xml:space="preserve">3.17459607124329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14236688613892</t>
   </si>
   <si>
     <t xml:space="preserve">3.01409387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88582134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272227287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610512733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51969480514526</t>
+    <t xml:space="preserve">2.88582110404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7427225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017981529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610536575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51969528198242</t>
   </si>
   <si>
     <t xml:space="preserve">2.24896812438965</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">2.15936994552612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17741847038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646682739258</t>
+    <t xml:space="preserve">2.17741870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646694660187</t>
   </si>
   <si>
     <t xml:space="preserve">1.88993239402771</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">1.76617157459259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68817627429962</t>
+    <t xml:space="preserve">1.68817603588104</t>
   </si>
   <si>
     <t xml:space="preserve">1.62500643730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9131373167038</t>
+    <t xml:space="preserve">1.91313743591309</t>
   </si>
   <si>
     <t xml:space="preserve">1.77261734008789</t>
@@ -2840,28 +2840,28 @@
     <t xml:space="preserve">1.83965456485748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93827664852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94149923324585</t>
+    <t xml:space="preserve">1.93827652931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94149935245514</t>
   </si>
   <si>
     <t xml:space="preserve">2.04141044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90669143199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923436641693</t>
+    <t xml:space="preserve">1.9066915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923412799835</t>
   </si>
   <si>
     <t xml:space="preserve">2.02013921737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05236864089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98662066459656</t>
+    <t xml:space="preserve">2.05236840248108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98662042617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.11295986175537</t>
@@ -2870,46 +2870,46 @@
     <t xml:space="preserve">2.12327337265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06912755966187</t>
+    <t xml:space="preserve">2.06912779808044</t>
   </si>
   <si>
     <t xml:space="preserve">2.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0910439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94278848171234</t>
+    <t xml:space="preserve">2.09104371070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94278860092163</t>
   </si>
   <si>
     <t xml:space="preserve">1.92087268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93892121315002</t>
+    <t xml:space="preserve">1.93892085552216</t>
   </si>
   <si>
     <t xml:space="preserve">1.90282416343689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83063018321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89766728878021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89379966259003</t>
+    <t xml:space="preserve">1.83063006401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8976674079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89379978179932</t>
   </si>
   <si>
     <t xml:space="preserve">1.99693393707275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06010389328003</t>
+    <t xml:space="preserve">2.06010365486145</t>
   </si>
   <si>
     <t xml:space="preserve">2.05623602867126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02658486366272</t>
+    <t xml:space="preserve">2.02658534049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.02529573440552</t>
@@ -2918,31 +2918,31 @@
     <t xml:space="preserve">2.04463338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04721164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05752515792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0162718296051</t>
+    <t xml:space="preserve">2.04721188545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05752539634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01627159118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.01756072044373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98790943622589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97243940830231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32651400566101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22702980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21850252151489</t>
+    <t xml:space="preserve">1.98790991306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97243964672089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32651424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22702956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21850228309631</t>
   </si>
   <si>
     <t xml:space="preserve">2.17018151283264</t>
@@ -2957,16 +2957,16 @@
     <t xml:space="preserve">2.27535057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26540207862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31372356414795</t>
+    <t xml:space="preserve">2.26540231704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31372332572937</t>
   </si>
   <si>
     <t xml:space="preserve">2.24266290664673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25687479972839</t>
+    <t xml:space="preserve">2.25687527656555</t>
   </si>
   <si>
     <t xml:space="preserve">2.39046835899353</t>
@@ -2975,31 +2975,31 @@
     <t xml:space="preserve">2.46863460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52406144142151</t>
+    <t xml:space="preserve">2.52406167984009</t>
   </si>
   <si>
     <t xml:space="preserve">2.63633704185486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61644005775452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56669783592224</t>
+    <t xml:space="preserve">2.6164402961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56669807434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.48995280265808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37909889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38336277008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38762617111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47005581855774</t>
+    <t xml:space="preserve">2.37909865379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38336229324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38762593269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47005605697632</t>
   </si>
   <si>
     <t xml:space="preserve">2.44873809814453</t>
@@ -3017,16 +3017,16 @@
     <t xml:space="preserve">2.40325927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41889262199402</t>
+    <t xml:space="preserve">2.4188928604126</t>
   </si>
   <si>
     <t xml:space="preserve">2.42457723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48284673690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46010756492615</t>
+    <t xml:space="preserve">2.48284721374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46010732650757</t>
   </si>
   <si>
     <t xml:space="preserve">2.43310451507568</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">2.57238292694092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58090996742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51127076148987</t>
+    <t xml:space="preserve">2.58091020584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51127099990845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53685259819031</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">2.56527662277222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60933423042297</t>
+    <t xml:space="preserve">2.60933399200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.64202189445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63207340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65481305122375</t>
+    <t xml:space="preserve">2.63207316398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65481281280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.67755198478699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65907669067383</t>
+    <t xml:space="preserve">2.65907645225525</t>
   </si>
   <si>
     <t xml:space="preserve">2.76424551010132</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">2.64770674705505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61501908302307</t>
+    <t xml:space="preserve">2.61501884460449</t>
   </si>
   <si>
     <t xml:space="preserve">2.60649180412292</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">2.54680132865906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186760902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66049766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68465828895569</t>
+    <t xml:space="preserve">2.67186737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66049742698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68465805053711</t>
   </si>
   <si>
     <t xml:space="preserve">2.7528760433197</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">2.89073300361633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92768454551697</t>
+    <t xml:space="preserve">2.92768406867981</t>
   </si>
   <si>
     <t xml:space="preserve">2.89641809463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92199969291687</t>
+    <t xml:space="preserve">2.92199921607971</t>
   </si>
   <si>
     <t xml:space="preserve">2.86372995376587</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">2.88931155204773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84951829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84099054336548</t>
+    <t xml:space="preserve">2.8495180606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84099078178406</t>
   </si>
   <si>
     <t xml:space="preserve">2.91773581504822</t>
@@ -3137,43 +3137,43 @@
     <t xml:space="preserve">2.93479037284851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95895075798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94900274276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87083601951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88789057731628</t>
+    <t xml:space="preserve">2.95895099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94616007804871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94900250434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87083578109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88789081573486</t>
   </si>
   <si>
     <t xml:space="preserve">2.8537814617157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81256651878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78556394577026</t>
+    <t xml:space="preserve">2.81256675720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78556370735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.90068125724792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87794232368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94189620018005</t>
+    <t xml:space="preserve">2.87794208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94189643859863</t>
   </si>
   <si>
     <t xml:space="preserve">2.95184469223022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95753002166748</t>
+    <t xml:space="preserve">2.95752954483032</t>
   </si>
   <si>
     <t xml:space="preserve">2.93621158599854</t>
@@ -3182,19 +3182,19 @@
     <t xml:space="preserve">2.91489362716675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85662436485291</t>
+    <t xml:space="preserve">2.85662412643433</t>
   </si>
   <si>
     <t xml:space="preserve">2.70313382148743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74861216545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6960277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70455503463745</t>
+    <t xml:space="preserve">2.74861264228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69602751731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70455479621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.65765500068665</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">2.66902494430542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65054941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64912796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.610755443573</t>
+    <t xml:space="preserve">2.6505491733551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6491277217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61075520515442</t>
   </si>
   <si>
     <t xml:space="preserve">2.68039464950562</t>
@@ -3242,31 +3242,31 @@
     <t xml:space="preserve">2.4970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52690434455872</t>
+    <t xml:space="preserve">2.52690410614014</t>
   </si>
   <si>
     <t xml:space="preserve">2.48568916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42741966247559</t>
+    <t xml:space="preserve">2.42741990089417</t>
   </si>
   <si>
     <t xml:space="preserve">2.3989953994751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37199282646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25403237342834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23129343986511</t>
+    <t xml:space="preserve">2.37199258804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25403261184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23129367828369</t>
   </si>
   <si>
     <t xml:space="preserve">2.22276616096497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30235385894775</t>
+    <t xml:space="preserve">2.30235362052917</t>
   </si>
   <si>
     <t xml:space="preserve">2.37057161331177</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">2.3947319984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56385564804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52264022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52832531929016</t>
+    <t xml:space="preserve">2.56385588645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52264070510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52832555770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.55532836914062</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">2.71450352668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76850914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7400848865509</t>
+    <t xml:space="preserve">2.76850891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74008512496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.84383320808411</t>
@@ -3302,25 +3302,25 @@
     <t xml:space="preserve">2.83672714233398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97174167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93052697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81967258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8097243309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78840613365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78129982948303</t>
+    <t xml:space="preserve">2.97174191474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93052649497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920853614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81967234611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80972409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78840589523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78130006790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.78272104263306</t>
@@ -3329,25 +3329,25 @@
     <t xml:space="preserve">2.77561521530151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70597624778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7073974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7130823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75998187065125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79835414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72871518135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75429701805115</t>
+    <t xml:space="preserve">2.70597648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70739722251892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71308207511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75998210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7983546257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72871541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75429725646973</t>
   </si>
   <si>
     <t xml:space="preserve">2.75571823120117</t>
@@ -3359,10 +3359,10 @@
     <t xml:space="preserve">2.77419400215149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77845764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7571394443512</t>
+    <t xml:space="preserve">2.77845788002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75713992118835</t>
   </si>
   <si>
     <t xml:space="preserve">2.83246350288391</t>
@@ -3377,55 +3377,55 @@
     <t xml:space="preserve">2.91347241401672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88646936416626</t>
+    <t xml:space="preserve">2.88646912574768</t>
   </si>
   <si>
     <t xml:space="preserve">2.88362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84241199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76993012428284</t>
+    <t xml:space="preserve">2.8424117565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76993083953857</t>
   </si>
   <si>
     <t xml:space="preserve">2.74719095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79551219940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67897319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68181586265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.745769739151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64344334602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57522487640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.644864320755</t>
+    <t xml:space="preserve">2.79551243782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67897343635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68181562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74577021598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64344310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57522535324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64486408233643</t>
   </si>
   <si>
     <t xml:space="preserve">2.80546069145203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8665726184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13233804702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10533499717712</t>
+    <t xml:space="preserve">2.86657238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758081436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13233780860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10533475875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.18350148200989</t>
@@ -3443,52 +3443,52 @@
     <t xml:space="preserve">3.12665319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.039959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742652893066</t>
+    <t xml:space="preserve">3.03995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742676734924</t>
   </si>
   <si>
     <t xml:space="preserve">3.01153540611267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03427481651306</t>
+    <t xml:space="preserve">3.03427457809448</t>
   </si>
   <si>
     <t xml:space="preserve">3.08259582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13375878334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11812591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05843496322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19344997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16928911209106</t>
+    <t xml:space="preserve">3.13375902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11812615394592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0584352016449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19344973564148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16928935050964</t>
   </si>
   <si>
     <t xml:space="preserve">3.2119255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2517192363739</t>
+    <t xml:space="preserve">3.25171971321106</t>
   </si>
   <si>
     <t xml:space="preserve">3.14797115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30004000663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28867053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435539245605</t>
+    <t xml:space="preserve">3.30004024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28867030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435563087463</t>
   </si>
   <si>
     <t xml:space="preserve">3.3014612197876</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">3.30572509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37110066413879</t>
+    <t xml:space="preserve">3.35262441635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37110042572021</t>
   </si>
   <si>
     <t xml:space="preserve">3.41942143440247</t>
@@ -3512,19 +3512,19 @@
     <t xml:space="preserve">3.36967945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26450967788696</t>
+    <t xml:space="preserve">3.26451015472412</t>
   </si>
   <si>
     <t xml:space="preserve">3.27587962150574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3085675239563</t>
+    <t xml:space="preserve">3.30856776237488</t>
   </si>
   <si>
     <t xml:space="preserve">3.40947318077087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37962770462036</t>
+    <t xml:space="preserve">3.37962794303894</t>
   </si>
   <si>
     <t xml:space="preserve">3.38247036933899</t>
@@ -3533,19 +3533,19 @@
     <t xml:space="preserve">3.40378832817078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42013192176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32846474647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29790782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272767066956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3590202331543</t>
+    <t xml:space="preserve">3.42013239860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32846450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29790830612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35902047157288</t>
   </si>
   <si>
     <t xml:space="preserve">3.36683702468872</t>
@@ -3554,52 +3554,52 @@
     <t xml:space="preserve">3.34978270530701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42723822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500327110291</t>
+    <t xml:space="preserve">3.42723798751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500350952148</t>
   </si>
   <si>
     <t xml:space="preserve">3.32206892967224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28014349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29719758033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31567311286926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33201718330383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430388450623</t>
+    <t xml:space="preserve">3.28014373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29719805717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31567358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33201766014099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430436134338</t>
   </si>
   <si>
     <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28440737724304</t>
+    <t xml:space="preserve">3.28440690040588</t>
   </si>
   <si>
     <t xml:space="preserve">3.23679661750793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31211996078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27232718467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31283092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42226409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48550748825073</t>
+    <t xml:space="preserve">3.31212067604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232694625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31283140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42226362228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48550772666931</t>
   </si>
   <si>
     <t xml:space="preserve">3.47555899620056</t>
@@ -3611,19 +3611,19 @@
     <t xml:space="preserve">3.48124408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57575464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143854141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53027534484863</t>
+    <t xml:space="preserve">3.57575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143877983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53027558326721</t>
   </si>
   <si>
     <t xml:space="preserve">3.49829840660095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52459096908569</t>
+    <t xml:space="preserve">3.52459073066711</t>
   </si>
   <si>
     <t xml:space="preserve">3.61421179771423</t>
@@ -3632,28 +3632,28 @@
     <t xml:space="preserve">3.52383756637573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38902974128723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43120431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41614174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44927930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48919463157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46584796905518</t>
+    <t xml:space="preserve">3.38902950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43120408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41614198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44927883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48919415473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4658477306366</t>
   </si>
   <si>
     <t xml:space="preserve">3.47488498687744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45831608772278</t>
+    <t xml:space="preserve">3.45831680297852</t>
   </si>
   <si>
     <t xml:space="preserve">3.48844122886658</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">3.46132898330688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45078539848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44626665115356</t>
+    <t xml:space="preserve">3.4507851600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44626688957214</t>
   </si>
   <si>
     <t xml:space="preserve">3.44099450111389</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">3.41764831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38752341270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3604109287262</t>
+    <t xml:space="preserve">3.38752365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36041116714478</t>
   </si>
   <si>
     <t xml:space="preserve">3.32501459121704</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">3.27229619026184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23765301704407</t>
+    <t xml:space="preserve">3.23765277862549</t>
   </si>
   <si>
     <t xml:space="preserve">3.21129393577576</t>
@@ -3701,22 +3701,22 @@
     <t xml:space="preserve">3.21430635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24970269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062050819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37697982788086</t>
+    <t xml:space="preserve">3.24970293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279532432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37697958946228</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865574836731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29488968849182</t>
+    <t xml:space="preserve">3.29489016532898</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731877326965</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">3.33329892158508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32953357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29112434387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28208637237549</t>
+    <t xml:space="preserve">3.32953310012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29112410545349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28208684921265</t>
   </si>
   <si>
     <t xml:space="preserve">3.14878511428833</t>
@@ -3749,61 +3749,61 @@
     <t xml:space="preserve">3.32802724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33028674125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33480525016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38601684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37321424484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42216682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4071044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38149785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42141366004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37170815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36643600463867</t>
+    <t xml:space="preserve">3.33028626441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33480548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3860170841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37321400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4221670627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40710425376892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38149833679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4214141368866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37170791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36643624305725</t>
   </si>
   <si>
     <t xml:space="preserve">3.39204239845276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48994779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61797761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60592770576477</t>
+    <t xml:space="preserve">3.48994708061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61797738075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60592794418335</t>
   </si>
   <si>
     <t xml:space="preserve">3.6164710521698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65337419509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63981819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6307806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6383113861084</t>
+    <t xml:space="preserve">3.65337371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6398184299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63078045845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63831162452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.72040104866028</t>
@@ -3815,40 +3815,40 @@
     <t xml:space="preserve">3.66542387008667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75052618980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77462601661682</t>
+    <t xml:space="preserve">3.75052571296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7746262550354</t>
   </si>
   <si>
     <t xml:space="preserve">3.77312016487122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79872584342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77613186836243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78215670585632</t>
+    <t xml:space="preserve">3.79872560501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77613210678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7821569442749</t>
   </si>
   <si>
     <t xml:space="preserve">3.76709461212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78667569160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73696947097778</t>
+    <t xml:space="preserve">3.78667545318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73696970939636</t>
   </si>
   <si>
     <t xml:space="preserve">3.77763819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71663594245911</t>
+    <t xml:space="preserve">3.71663570404053</t>
   </si>
   <si>
     <t xml:space="preserve">3.71588277816772</t>
@@ -3857,37 +3857,37 @@
     <t xml:space="preserve">3.7053394317627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63755822181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68726420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699423789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65638613700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72567319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67144870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258080482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132475852966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429201126099</t>
+    <t xml:space="preserve">3.6375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68726396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65638661384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72567343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67144894599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6413242816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429153442383</t>
   </si>
   <si>
     <t xml:space="preserve">3.75203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80926966667175</t>
+    <t xml:space="preserve">3.80926942825317</t>
   </si>
   <si>
     <t xml:space="preserve">3.7445011138916</t>
@@ -3896,46 +3896,46 @@
     <t xml:space="preserve">3.80625677108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84541893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83939433097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90717458724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95386815071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97947382926941</t>
+    <t xml:space="preserve">3.84541916847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83939409255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90717506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9538676738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97947406768799</t>
   </si>
   <si>
     <t xml:space="preserve">3.95989274978638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94483065605164</t>
+    <t xml:space="preserve">3.94483041763306</t>
   </si>
   <si>
     <t xml:space="preserve">3.89060616493225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92976832389832</t>
+    <t xml:space="preserve">3.88307499885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92976856231689</t>
   </si>
   <si>
     <t xml:space="preserve">3.95682597160339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99502539634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01571702957153</t>
+    <t xml:space="preserve">3.99502563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01571655273438</t>
   </si>
   <si>
     <t xml:space="preserve">3.96239686012268</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">3.95125532150269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9902503490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97910928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98388409614563</t>
+    <t xml:space="preserve">3.99025058746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97910904884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98388361930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.95523428916931</t>
@@ -3959,73 +3959,73 @@
     <t xml:space="preserve">4.00457572937012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98070049285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0189003944397</t>
+    <t xml:space="preserve">3.98070025444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01889991760254</t>
   </si>
   <si>
     <t xml:space="preserve">3.9735381603241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98706769943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92340159416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98229241371155</t>
+    <t xml:space="preserve">3.98706746101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92340135574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98229193687439</t>
   </si>
   <si>
     <t xml:space="preserve">4.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9345428943634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97274231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90907669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89952707290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83983969688416</t>
+    <t xml:space="preserve">3.98865914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93454313278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97274279594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90907692909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89952683448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66078042984009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66316819190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73638343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72524237632751</t>
+    <t xml:space="preserve">3.67590045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66316771507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73638367652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72524213790894</t>
   </si>
   <si>
     <t xml:space="preserve">3.70057153701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76821613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779906272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77219462394714</t>
+    <t xml:space="preserve">3.76821637153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779858589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7721951007843</t>
   </si>
   <si>
     <t xml:space="preserve">3.76264548301697</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">3.72922086715698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73081278800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77856206893921</t>
+    <t xml:space="preserve">3.73081254959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77856230735779</t>
   </si>
   <si>
     <t xml:space="preserve">3.74513721466064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64565968513489</t>
+    <t xml:space="preserve">3.64565992355347</t>
   </si>
   <si>
     <t xml:space="preserve">3.74832057952881</t>
@@ -4055,25 +4055,25 @@
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77696990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641603469849</t>
+    <t xml:space="preserve">3.77697062492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8326780796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641555786133</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85177755355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85973572731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93613457679749</t>
+    <t xml:space="preserve">3.85177779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8597354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93613481521606</t>
   </si>
   <si>
     <t xml:space="preserve">3.86212348937988</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">3.89554762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91146421432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97115063667297</t>
+    <t xml:space="preserve">3.91146397590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97115111351013</t>
   </si>
   <si>
     <t xml:space="preserve">3.96398854255676</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">3.99980020523071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91942262649536</t>
+    <t xml:space="preserve">3.91942238807678</t>
   </si>
   <si>
     <t xml:space="preserve">3.76344132423401</t>
@@ -4109,28 +4109,28 @@
     <t xml:space="preserve">3.80402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748476982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603013038635</t>
+    <t xml:space="preserve">3.90748524665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603036880493</t>
   </si>
   <si>
     <t xml:space="preserve">3.90430188179016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94409251213074</t>
+    <t xml:space="preserve">3.94409227371216</t>
   </si>
   <si>
     <t xml:space="preserve">4.00775861740112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96796751022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85575652122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82710719108582</t>
+    <t xml:space="preserve">3.96796774864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8557562828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82710766792297</t>
   </si>
   <si>
     <t xml:space="preserve">4.03004169464111</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">4.01253318786621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00934982299805</t>
+    <t xml:space="preserve">4.00935029983521</t>
   </si>
   <si>
     <t xml:space="preserve">3.99820899963379</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.91623950004578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8581440448761</t>
+    <t xml:space="preserve">3.85814428329468</t>
   </si>
   <si>
     <t xml:space="preserve">3.78094935417175</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">3.55414009094238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69261288642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60746049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42760443687439</t>
+    <t xml:space="preserve">3.69261336326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60746002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42760467529297</t>
   </si>
   <si>
     <t xml:space="preserve">3.40293407440186</t>
@@ -4172,34 +4172,34 @@
     <t xml:space="preserve">3.34483909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06948494911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94374489784241</t>
+    <t xml:space="preserve">3.06948471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94374465942383</t>
   </si>
   <si>
     <t xml:space="preserve">3.14429187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28913140296936</t>
+    <t xml:space="preserve">3.28913164138794</t>
   </si>
   <si>
     <t xml:space="preserve">3.39338421821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51912426948547</t>
+    <t xml:space="preserve">3.51912379264832</t>
   </si>
   <si>
     <t xml:space="preserve">3.56846499443054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73797512054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69022583961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68385934829712</t>
+    <t xml:space="preserve">3.73797488212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69022607803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6838595867157</t>
   </si>
   <si>
     <t xml:space="preserve">3.70852971076965</t>
@@ -4208,37 +4208,37 @@
     <t xml:space="preserve">3.74036240577698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7435462474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90111875534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90668940544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9202184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97194647789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96319270133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693041801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03481674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06346607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02845001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11758136749268</t>
+    <t xml:space="preserve">3.74354553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.901118516922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90668892860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92021870613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97194695472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319222450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693065643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0348162651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06346654891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02844953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11758184432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.09848213195801</t>
@@ -4247,10 +4247,10 @@
     <t xml:space="preserve">4.12235689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1334981918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16055679321289</t>
+    <t xml:space="preserve">4.13349866867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16055631637573</t>
   </si>
   <si>
     <t xml:space="preserve">4.16214799880981</t>
@@ -4262,19 +4262,19 @@
     <t xml:space="preserve">4.21467208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716453552246</t>
+    <t xml:space="preserve">4.1971640586853</t>
   </si>
   <si>
     <t xml:space="preserve">4.1541895866394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11599016189575</t>
+    <t xml:space="preserve">4.11599063873291</t>
   </si>
   <si>
     <t xml:space="preserve">4.13668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14623165130615</t>
+    <t xml:space="preserve">4.14623212814331</t>
   </si>
   <si>
     <t xml:space="preserve">4.2401385307312</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">4.17488098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12554025650024</t>
+    <t xml:space="preserve">4.12553977966309</t>
   </si>
   <si>
     <t xml:space="preserve">4.0650577545166</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">4.1637396812439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26719665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28470468521118</t>
+    <t xml:space="preserve">4.26719617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28470420837402</t>
   </si>
   <si>
     <t xml:space="preserve">3.93135929107666</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">3.9050977230072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00298404693604</t>
+    <t xml:space="preserve">4.00298357009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.00139188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12431621551514</t>
+    <t xml:space="preserve">4.12431669235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
@@ -4325,13 +4325,13 @@
     <t xml:space="preserve">4.24703884124756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28597116470337</t>
+    <t xml:space="preserve">4.28597164154053</t>
   </si>
   <si>
     <t xml:space="preserve">4.25042390823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21487712860107</t>
+    <t xml:space="preserve">4.21487665176392</t>
   </si>
   <si>
     <t xml:space="preserve">4.14547538757324</t>
@@ -4340,58 +4340,58 @@
     <t xml:space="preserve">4.14124345779419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09723281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19202566146851</t>
+    <t xml:space="preserve">4.09723329544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19202518463135</t>
   </si>
   <si>
     <t xml:space="preserve">4.20810604095459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754512786865</t>
+    <t xml:space="preserve">4.11754560470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.10738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77053785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383142471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71975588798523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82301211357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69944334030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71213912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7730770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122736930847</t>
+    <t xml:space="preserve">3.77053737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383166313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71975612640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82301235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69944310188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71213865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77307677268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122760772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65881824493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80100655555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70198225975037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71467781066895</t>
+    <t xml:space="preserve">3.65881776809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80100679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70198249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71467757225037</t>
   </si>
   <si>
     <t xml:space="preserve">3.71044588088989</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">3.68082332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69690442085266</t>
+    <t xml:space="preserve">3.69690418243408</t>
   </si>
   <si>
     <t xml:space="preserve">3.47177243232727</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">3.6063437461853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62919569015503</t>
+    <t xml:space="preserve">3.62919545173645</t>
   </si>
   <si>
     <t xml:space="preserve">3.53355669975281</t>
@@ -4424,19 +4424,19 @@
     <t xml:space="preserve">3.51324391365051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48700666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33381509780884</t>
+    <t xml:space="preserve">3.48700642585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33381533622742</t>
   </si>
   <si>
     <t xml:space="preserve">3.38290429115295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40406322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44892048835754</t>
+    <t xml:space="preserve">3.4040629863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44892024993896</t>
   </si>
   <si>
     <t xml:space="preserve">3.38713598251343</t>
@@ -4460,10 +4460,10 @@
     <t xml:space="preserve">3.36005282402039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45738434791565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46415495872498</t>
+    <t xml:space="preserve">3.45738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46415519714355</t>
   </si>
   <si>
     <t xml:space="preserve">3.42860794067383</t>
@@ -4472,13 +4472,13 @@
     <t xml:space="preserve">3.48362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56741118431091</t>
+    <t xml:space="preserve">3.56741142272949</t>
   </si>
   <si>
     <t xml:space="preserve">3.64358353614807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66135716438293</t>
+    <t xml:space="preserve">3.66135740280151</t>
   </si>
   <si>
     <t xml:space="preserve">3.64273715019226</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">3.70790696144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74176144599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73922252655029</t>
+    <t xml:space="preserve">3.74176120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73922228813171</t>
   </si>
   <si>
     <t xml:space="preserve">3.67659139633179</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">3.46838688850403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54625225067139</t>
+    <t xml:space="preserve">3.54625201225281</t>
   </si>
   <si>
     <t xml:space="preserve">3.50224137306213</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709815979004</t>
+    <t xml:space="preserve">3.54709839820862</t>
   </si>
   <si>
     <t xml:space="preserve">3.6190390586853</t>
@@ -4541,19 +4541,19 @@
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282864570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6791307926178</t>
+    <t xml:space="preserve">3.70282888412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67913055419922</t>
   </si>
   <si>
     <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69351863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706057548523</t>
+    <t xml:space="preserve">3.69351887702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706081390381</t>
   </si>
   <si>
     <t xml:space="preserve">3.70029020309448</t>
@@ -4568,13 +4568,13 @@
     <t xml:space="preserve">3.58010625839233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47515749931335</t>
+    <t xml:space="preserve">3.47515773773193</t>
   </si>
   <si>
     <t xml:space="preserve">3.44045686721802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38459730148315</t>
+    <t xml:space="preserve">3.38459706306458</t>
   </si>
   <si>
     <t xml:space="preserve">3.34735703468323</t>
@@ -4583,28 +4583,28 @@
     <t xml:space="preserve">3.3803653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40829515457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52678561210632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47431135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38205790519714</t>
+    <t xml:space="preserve">3.40829539299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52678537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4743115901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3676700592041</t>
+    <t xml:space="preserve">3.36766982078552</t>
   </si>
   <si>
     <t xml:space="preserve">3.37613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31519556045532</t>
+    <t xml:space="preserve">3.3151957988739</t>
   </si>
   <si>
     <t xml:space="preserve">3.42014408111572</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">3.45315217971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50647330284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48954606056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471563339233</t>
+    <t xml:space="preserve">3.50647306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48954582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471539497375</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4640,10 +4640,10 @@
     <t xml:space="preserve">3.68674802780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7256805896759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370258331299</t>
+    <t xml:space="preserve">3.72568011283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370210647583</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
@@ -4658,25 +4658,25 @@
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366428375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06422519683838</t>
+    <t xml:space="preserve">3.97366452217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06422472000122</t>
   </si>
   <si>
     <t xml:space="preserve">4.01259660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9846670627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03037023544312</t>
+    <t xml:space="preserve">3.98466730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03037071228027</t>
   </si>
   <si>
     <t xml:space="preserve">4.04052686691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04899072647095</t>
+    <t xml:space="preserve">4.04898977279663</t>
   </si>
   <si>
     <t xml:space="preserve">4.06845664978027</t>
@@ -4685,16 +4685,16 @@
     <t xml:space="preserve">4.05576086044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06253242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04645156860352</t>
+    <t xml:space="preserve">4.0625319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04645109176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391193389893</t>
+    <t xml:space="preserve">4.04391241073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
@@ -4709,13 +4709,13 @@
     <t xml:space="preserve">4.09977197647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05322170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00836515426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98635983467102</t>
+    <t xml:space="preserve">4.05322217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0083646774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98635959625244</t>
   </si>
   <si>
     <t xml:space="preserve">4.02360010147095</t>
@@ -4724,49 +4724,49 @@
     <t xml:space="preserve">3.99990129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01344299316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96774005889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00667285919189</t>
+    <t xml:space="preserve">4.01344347000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96773958206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00667238235474</t>
   </si>
   <si>
     <t xml:space="preserve">3.955890417099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84586381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78831100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86702275276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88818144798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96096873283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94150257110596</t>
+    <t xml:space="preserve">3.84586405754089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78831076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86702251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88818168640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96096849441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94150233268738</t>
   </si>
   <si>
     <t xml:space="preserve">3.93219232559204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91272616386414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579939842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85771298408508</t>
+    <t xml:space="preserve">3.91272640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8577127456665</t>
   </si>
   <si>
     <t xml:space="preserve">3.89326000213623</t>
@@ -4778,22 +4778,22 @@
     <t xml:space="preserve">4.03544855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97958922386169</t>
+    <t xml:space="preserve">3.97958874702454</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0168285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99482321739197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99736213684082</t>
+    <t xml:space="preserve">4.01682901382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99482274055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974537849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9973623752594</t>
   </si>
   <si>
     <t xml:space="preserve">4.02529239654541</t>
@@ -4805,19 +4805,19 @@
     <t xml:space="preserve">4.04475831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05660772323608</t>
+    <t xml:space="preserve">4.05660820007324</t>
   </si>
   <si>
     <t xml:space="preserve">4.08792304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12685537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638643264771</t>
+    <t xml:space="preserve">4.12685585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10992860794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
@@ -4832,16 +4832,16 @@
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732431411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14462900161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18271493911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18948602676392</t>
+    <t xml:space="preserve">4.15732479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14462947845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18948650360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.19794988632202</t>
@@ -4850,19 +4850,19 @@
     <t xml:space="preserve">4.20556688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2123384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17679119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16155624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18864011764526</t>
+    <t xml:space="preserve">4.22926568984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21233797073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17679071426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16155576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18863964080811</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">4.17932987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23349714279175</t>
+    <t xml:space="preserve">4.23349666595459</t>
   </si>
   <si>
     <t xml:space="preserve">4.24026823043823</t>
@@ -4880,16 +4880,16 @@
     <t xml:space="preserve">4.27073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2961277961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33506011962891</t>
+    <t xml:space="preserve">4.29612827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33506107330322</t>
   </si>
   <si>
     <t xml:space="preserve">4.29443454742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28427886962891</t>
+    <t xml:space="preserve">4.28427839279175</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">3.85094213485718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8780255317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784206390381</t>
+    <t xml:space="preserve">3.87802529335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784230232239</t>
   </si>
   <si>
     <t xml:space="preserve">3.8526349067688</t>
@@ -4913,25 +4913,25 @@
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94658064842224</t>
+    <t xml:space="preserve">3.94658088684082</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92965340614319</t>
+    <t xml:space="preserve">3.92965316772461</t>
   </si>
   <si>
     <t xml:space="preserve">3.93811726570129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0549144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06676435470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518991470337</t>
+    <t xml:space="preserve">4.05491495132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06676340103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518943786621</t>
   </si>
   <si>
     <t xml:space="preserve">4.25550222396851</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">4.32321119308472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3553729057312</t>
+    <t xml:space="preserve">4.35537338256836</t>
   </si>
   <si>
     <t xml:space="preserve">4.30289888381958</t>
@@ -4955,22 +4955,22 @@
     <t xml:space="preserve">4.25888824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045916557312</t>
+    <t xml:space="preserve">4.30459117889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.28258609771729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33336782455444</t>
+    <t xml:space="preserve">4.33336734771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.31305503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23857498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32828903198242</t>
+    <t xml:space="preserve">4.23857545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32828950881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.39938354492188</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">4.37907075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34013843536377</t>
+    <t xml:space="preserve">4.34013795852661</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">4.31644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36722183227539</t>
+    <t xml:space="preserve">4.36722135543823</t>
   </si>
   <si>
     <t xml:space="preserve">4.37269258499146</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3398699760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072305679321</t>
+    <t xml:space="preserve">4.33531141281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33987045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072353363037</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266374588013</t>
+    <t xml:space="preserve">4.36266326904297</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369176864624</t>
+    <t xml:space="preserve">4.40369129180908</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081100463867</t>
+    <t xml:space="preserve">4.35081052780151</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292568206787</t>
+    <t xml:space="preserve">4.48757171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292520523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492404937744</t>
+    <t xml:space="preserve">4.43924903869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574781417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492357254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57692193984985</t>
+    <t xml:space="preserve">4.5769214630127</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59150981903076</t>
+    <t xml:space="preserve">4.5915093421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891935348511</t>
+    <t xml:space="preserve">4.63891983032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130603790283</t>
+    <t xml:space="preserve">4.52130556106567</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5159,7 +5159,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786296844482</t>
+    <t xml:space="preserve">4.58786249160767</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5171,22 +5171,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191690444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738765716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732902526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197553634644</t>
+    <t xml:space="preserve">4.73191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732950210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897798538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644662857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197505950928</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780481338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65533113479614</t>
+    <t xml:space="preserve">4.56780433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6553316116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792112350464</t>
+    <t xml:space="preserve">4.68268346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792064666748</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6845064163208</t>
+    <t xml:space="preserve">4.68450689315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009347915649</t>
+    <t xml:space="preserve">4.73009395599365</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174243927002</t>
+    <t xml:space="preserve">4.67174291610718</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70638847351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63709688186646</t>
+    <t xml:space="preserve">4.7063889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6370964050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080141067505</t>
+    <t xml:space="preserve">4.66080188751221</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903661727905</t>
+    <t xml:space="preserve">4.67903614044189</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050104141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88873624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403205871582</t>
+    <t xml:space="preserve">4.87050151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8887357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403158187866</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956048965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497261047363</t>
+    <t xml:space="preserve">4.85956001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497308731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491397857666</t>
+    <t xml:space="preserve">4.82491445541382</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756259918213</t>
+    <t xml:space="preserve">4.79756212234497</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5348,13 +5348,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932739257812</t>
+    <t xml:space="preserve">4.77932786941528</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6881537437439</t>
+    <t xml:space="preserve">4.68815422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714544296265</t>
+    <t xml:space="preserve">4.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602947235107</t>
+    <t xml:space="preserve">4.89602994918823</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079277038574</t>
+    <t xml:space="preserve">4.97079229354858</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5423,7 +5423,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23337268829346</t>
+    <t xml:space="preserve">5.2333722114563</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5432,13 +5432,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26072454452515</t>
+    <t xml:space="preserve">5.2607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078269958496</t>
+    <t xml:space="preserve">5.28078317642212</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5450,10 +5450,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216161727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709842681885</t>
+    <t xml:space="preserve">6.38216209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709890365601</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85626554489136</t>
+    <t xml:space="preserve">6.8562650680542</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5489,13 +5489,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655632019043</t>
+    <t xml:space="preserve">6.95655679702759</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632369995117</t>
+    <t xml:space="preserve">6.87632322311401</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86902952194214</t>
+    <t xml:space="preserve">6.8690299987793</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5525,13 +5525,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625595092773</t>
+    <t xml:space="preserve">7.16625642776489</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213474273682</t>
+    <t xml:space="preserve">7.31213426589966</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537355422974</t>
+    <t xml:space="preserve">7.21184301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566480636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537307739258</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5558,10 +5558,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51271629333496</t>
+    <t xml:space="preserve">7.41242551803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5127158164978</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5570,19 +5570,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5765380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580131530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.726975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682886123657</t>
+    <t xml:space="preserve">7.63124179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57653856277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72697448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682933807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5591,7 +5591,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67226982116699</t>
+    <t xml:space="preserve">7.67227029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2238712310791</t>
+    <t xml:space="preserve">8.22387218475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -6612,6 +6612,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.6700000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1450004577637</t>
   </si>
 </sst>
 </file>
@@ -72132,7 +72135,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6910416667</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>1965242</v>
@@ -72153,6 +72156,32 @@
         <v>2190</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6929398148</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>1720440</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>19.2649993896484</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>18.9249992370605</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>19.0750007629395</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>19.1450004577637</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>2200</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UNI.MI.xlsx
+++ b/data/UNI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44528841972351</t>
+    <t xml:space="preserve">2.44528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">UNI.MI</t>
@@ -50,22 +50,22 @@
     <t xml:space="preserve">2.40895104408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3565821647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31490135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29780173301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37261343002319</t>
+    <t xml:space="preserve">2.35658240318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31490159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29780197143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37261366844177</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33413887023926</t>
+    <t xml:space="preserve">2.3341383934021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2347457408905</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">2.11183977127075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99641537666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06588363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07977771759033</t>
+    <t xml:space="preserve">1.99641561508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06588387489319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07977747917175</t>
   </si>
   <si>
     <t xml:space="preserve">2.03489017486572</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.03168392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02954649925232</t>
+    <t xml:space="preserve">2.0295467376709</t>
   </si>
   <si>
     <t xml:space="preserve">1.90343487262726</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">1.93549728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84037864208221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74953544139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75701677799225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67792952060699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53151154518127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861699104309</t>
+    <t xml:space="preserve">1.84037888050079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74953496456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75701653957367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67792928218842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349846839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53151142597198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6886168718338</t>
   </si>
   <si>
     <t xml:space="preserve">1.55823004245758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60632383823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72922956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67899811267853</t>
+    <t xml:space="preserve">1.60632359981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72922945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67899823188782</t>
   </si>
   <si>
     <t xml:space="preserve">1.7431229352951</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">1.73350441455841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69396078586578</t>
+    <t xml:space="preserve">1.69396066665649</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419176578522</t>
@@ -152,37 +152,37 @@
     <t xml:space="preserve">1.70571672916412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66296720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71533572673798</t>
+    <t xml:space="preserve">1.66296708583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7153354883194</t>
   </si>
   <si>
     <t xml:space="preserve">1.82541596889496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8232786655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88099110126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89381587505341</t>
+    <t xml:space="preserve">1.82327890396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88099145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89381611347198</t>
   </si>
   <si>
     <t xml:space="preserve">1.89488482475281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86602854728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80404126644135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76556658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82648515701294</t>
+    <t xml:space="preserve">1.86602866649628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80404114723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76556622982025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82648527622223</t>
   </si>
   <si>
     <t xml:space="preserve">1.79976654052734</t>
@@ -191,61 +191,61 @@
     <t xml:space="preserve">1.92053472995758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93442821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93229067325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221566200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9643532037735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97183406352997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95580315589905</t>
+    <t xml:space="preserve">1.93442797660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9322909116745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96435296535492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97183454036713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95580303668976</t>
   </si>
   <si>
     <t xml:space="preserve">1.95259714126587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92374110221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87564718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8831285238266</t>
+    <t xml:space="preserve">1.92374062538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87564730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88312840461731</t>
   </si>
   <si>
     <t xml:space="preserve">1.91198468208313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90022873878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89167833328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579732894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80190408229828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87992203235626</t>
+    <t xml:space="preserve">1.90022826194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89167845249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579768657684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81793475151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80190432071686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87992227077484</t>
   </si>
   <si>
     <t xml:space="preserve">1.90129733085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84465360641479</t>
+    <t xml:space="preserve">1.84465336799622</t>
   </si>
   <si>
     <t xml:space="preserve">1.9258781671524</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">2.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626487731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07443404197693</t>
+    <t xml:space="preserve">2.05626511573792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07443380355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.06160879135132</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">2.07015895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02634024620056</t>
+    <t xml:space="preserve">2.02634048461914</t>
   </si>
   <si>
     <t xml:space="preserve">2.0551962852478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05092191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99855268001556</t>
+    <t xml:space="preserve">2.05092120170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99855291843414</t>
   </si>
   <si>
     <t xml:space="preserve">1.99214065074921</t>
@@ -290,46 +290,46 @@
     <t xml:space="preserve">1.95045948028564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93977236747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84999716281891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87457847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79121649265289</t>
+    <t xml:space="preserve">1.93977165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84999740123749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87457859516144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79121661186218</t>
   </si>
   <si>
     <t xml:space="preserve">1.73884797096252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388565540314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69502925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678544044495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70785439014435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76235282421112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700954914093</t>
+    <t xml:space="preserve">1.72388601303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69502937793732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678555965424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70785450935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76235258579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700942993164</t>
   </si>
   <si>
     <t xml:space="preserve">1.87773108482361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87546908855438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91279721260071</t>
+    <t xml:space="preserve">1.87546920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91279745101929</t>
   </si>
   <si>
     <t xml:space="preserve">1.90601050853729</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">1.81438612937927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80646789073944</t>
+    <t xml:space="preserve">1.80646777153015</t>
   </si>
   <si>
     <t xml:space="preserve">1.75104117393494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63113760948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54290676116943</t>
+    <t xml:space="preserve">1.63113796710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54290699958801</t>
   </si>
   <si>
     <t xml:space="preserve">1.46711909770966</t>
@@ -365,28 +365,28 @@
     <t xml:space="preserve">1.47390604019165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42526614665985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51689004898071</t>
+    <t xml:space="preserve">1.42526602745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51689028739929</t>
   </si>
   <si>
     <t xml:space="preserve">1.61190795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60059630870819</t>
+    <t xml:space="preserve">1.60059642791748</t>
   </si>
   <si>
     <t xml:space="preserve">1.57684195041656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69900727272034</t>
+    <t xml:space="preserve">1.69900739192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.38341307640076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24201738834381</t>
+    <t xml:space="preserve">1.2420175075531</t>
   </si>
   <si>
     <t xml:space="preserve">1.27255892753601</t>
@@ -401,67 +401,67 @@
     <t xml:space="preserve">1.23636174201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18545913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14021277427673</t>
+    <t xml:space="preserve">1.18545937538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14021289348602</t>
   </si>
   <si>
     <t xml:space="preserve">1.09949088096619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0972284078598</t>
+    <t xml:space="preserve">1.09722864627838</t>
   </si>
   <si>
     <t xml:space="preserve">1.23749279975891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28726410865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36870765686035</t>
+    <t xml:space="preserve">1.28726387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36870789527893</t>
   </si>
   <si>
     <t xml:space="preserve">1.33477282524109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39359331130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38454401493073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40038061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3698388338089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39811789989471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37888824939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37097012996674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37775719165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42979061603546</t>
+    <t xml:space="preserve">1.39359319210052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38454413414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40038049221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.398118019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37888836860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37097024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37775707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42979073524475</t>
   </si>
   <si>
     <t xml:space="preserve">1.40264272689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38567531108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26011610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29631340503693</t>
+    <t xml:space="preserve">1.38567507266998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26011621952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29631328582764</t>
   </si>
   <si>
     <t xml:space="preserve">1.32233011722565</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">1.37549471855164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43657767772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4535448551178</t>
+    <t xml:space="preserve">1.43657755851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45354497432709</t>
   </si>
   <si>
     <t xml:space="preserve">1.44788920879364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47051239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45015156269073</t>
+    <t xml:space="preserve">1.47051250934601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45015144348145</t>
   </si>
   <si>
     <t xml:space="preserve">1.41961002349854</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">1.36757659912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33816623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3540027141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32798588275909</t>
+    <t xml:space="preserve">1.33816635608673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35400283336639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3279857635498</t>
   </si>
   <si>
     <t xml:space="preserve">1.41056072711945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40377414226532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42413473129272</t>
+    <t xml:space="preserve">1.40377378463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42413485050201</t>
   </si>
   <si>
     <t xml:space="preserve">1.43883967399597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45920085906982</t>
+    <t xml:space="preserve">1.4592010974884</t>
   </si>
   <si>
     <t xml:space="preserve">1.47729933261871</t>
@@ -539,94 +539,94 @@
     <t xml:space="preserve">1.48974227905273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39020001888275</t>
+    <t xml:space="preserve">1.39019989967346</t>
   </si>
   <si>
     <t xml:space="preserve">1.4071671962738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36078941822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513377189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34947788715363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34269106388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30536282062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27821469306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31780529022217</t>
+    <t xml:space="preserve">1.36078953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41282308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513389110565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34947800636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34269118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30536258220673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27821457386017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31780564785004</t>
   </si>
   <si>
     <t xml:space="preserve">1.2861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28500175476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27934587001801</t>
+    <t xml:space="preserve">1.28500151634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27934598922729</t>
   </si>
   <si>
     <t xml:space="preserve">1.35174024105072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35852742195129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37210130691528</t>
+    <t xml:space="preserve">1.35852718353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37210118770599</t>
   </si>
   <si>
     <t xml:space="preserve">1.39472448825836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41621661186218</t>
+    <t xml:space="preserve">1.41621673107147</t>
   </si>
   <si>
     <t xml:space="preserve">1.44110226631165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49313592910767</t>
+    <t xml:space="preserve">1.4931355714798</t>
   </si>
   <si>
     <t xml:space="preserve">1.52480840682983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53159558773041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51575899124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54856276512146</t>
+    <t xml:space="preserve">1.53159546852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51575911045074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54856264591217</t>
   </si>
   <si>
     <t xml:space="preserve">1.5655300617218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61077690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63453125953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5983339548111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57571041584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57118594646454</t>
+    <t xml:space="preserve">1.61077666282654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63453102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59833407402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57571077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57118630409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.50444734096527</t>
@@ -635,64 +635,64 @@
     <t xml:space="preserve">1.51802134513855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4750372171402</t>
+    <t xml:space="preserve">1.47503709793091</t>
   </si>
   <si>
     <t xml:space="preserve">1.6571546792984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69335126876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167938709259</t>
+    <t xml:space="preserve">1.69335174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733491420746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167914867401</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905584812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60172772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57457947731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62661290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5847601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5610054731369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064452648163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60512089729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64923655986786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6662038564682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62435078620911</t>
+    <t xml:space="preserve">1.60172748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57457959651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62661278247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58475995063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60512101650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64923632144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66620409488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62435102462769</t>
   </si>
   <si>
     <t xml:space="preserve">1.72049951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79741847515106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85284578800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84492766857147</t>
+    <t xml:space="preserve">1.79741883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85284566879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84492778778076</t>
   </si>
   <si>
     <t xml:space="preserve">1.83022260665894</t>
@@ -701,49 +701,49 @@
     <t xml:space="preserve">1.86302614212036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85623955726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91053485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89922320842743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91166639328003</t>
+    <t xml:space="preserve">1.85623919963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91053533554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89922368526459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91166615486145</t>
   </si>
   <si>
     <t xml:space="preserve">1.92637133598328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94560086727142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446969032288</t>
+    <t xml:space="preserve">1.94560110569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446992874146</t>
   </si>
   <si>
     <t xml:space="preserve">1.8969612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655157089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98066747188568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01347064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00781536102295</t>
+    <t xml:space="preserve">1.93655180931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98066711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0134711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00781512260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.01573324203491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01912689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96483063697815</t>
+    <t xml:space="preserve">2.01912713050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96483087539673</t>
   </si>
   <si>
     <t xml:space="preserve">1.99876594543457</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">1.97727382183075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01007747650146</t>
+    <t xml:space="preserve">2.01007723808289</t>
   </si>
   <si>
     <t xml:space="preserve">1.9716180562973</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">1.97953593730927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02252054214478</t>
+    <t xml:space="preserve">2.0225203037262</t>
   </si>
   <si>
     <t xml:space="preserve">1.99084782600403</t>
@@ -779,40 +779,40 @@
     <t xml:space="preserve">2.08699631690979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05079936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05193066596985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542051315308</t>
+    <t xml:space="preserve">2.05079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9354202747345</t>
   </si>
   <si>
     <t xml:space="preserve">1.93202698230743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96709299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894641876221</t>
+    <t xml:space="preserve">1.96709322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894618034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.90940380096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89130532741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.873206615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87999355792999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8551082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96596193313599</t>
+    <t xml:space="preserve">1.89130556583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87320649623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87999367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85510802268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96596240997314</t>
   </si>
   <si>
     <t xml:space="preserve">2.03609442710876</t>
@@ -824,85 +824,85 @@
     <t xml:space="preserve">2.00215935707092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329065322876</t>
+    <t xml:space="preserve">2.00329041481018</t>
   </si>
   <si>
     <t xml:space="preserve">2.02478265762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01799583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00442147254944</t>
+    <t xml:space="preserve">2.01799559593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00442171096802</t>
   </si>
   <si>
     <t xml:space="preserve">1.95465052127838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02930736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02817630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09265232086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13224315643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12432479858398</t>
+    <t xml:space="preserve">2.0293071269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02817606925964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09265208244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13224291801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12432503700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.12093162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15939140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15373516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14016151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1084885597229</t>
+    <t xml:space="preserve">2.15939092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15373492240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14016127586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10848879814148</t>
   </si>
   <si>
     <t xml:space="preserve">2.07568502426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14921069145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19332575798035</t>
+    <t xml:space="preserve">2.14921045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19332599639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.17862105369568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23291659355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558835029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20803093910217</t>
+    <t xml:space="preserve">2.23291683197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20803141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.20576882362366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18314552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16617798805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20350646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19219470024109</t>
+    <t xml:space="preserve">2.18314576148987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16617822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2035059928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19219493865967</t>
   </si>
   <si>
     <t xml:space="preserve">2.15825986862183</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">2.15599751472473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14129257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09378385543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07907819747925</t>
+    <t xml:space="preserve">2.14129209518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09378361701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07907843589783</t>
   </si>
   <si>
     <t xml:space="preserve">2.08812761306763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11188220977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10961985588074</t>
+    <t xml:space="preserve">2.11188197135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10961961746216</t>
   </si>
   <si>
     <t xml:space="preserve">2.222736120224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26232719421387</t>
+    <t xml:space="preserve">2.26232671737671</t>
   </si>
   <si>
     <t xml:space="preserve">2.26006460189819</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">2.2578022480011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31436014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33132791519165</t>
+    <t xml:space="preserve">2.31436038017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33132815361023</t>
   </si>
   <si>
     <t xml:space="preserve">2.34716439247131</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">2.40032863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41164040565491</t>
+    <t xml:space="preserve">2.41164064407349</t>
   </si>
   <si>
     <t xml:space="preserve">2.43878817558289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39127922058105</t>
+    <t xml:space="preserve">2.44557499885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39127969741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3256721496582</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">2.3630006313324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33585238456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25893330574036</t>
+    <t xml:space="preserve">2.33585262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25893354415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.24988436698914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27137637138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30216646194458</t>
+    <t xml:space="preserve">2.27137613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33769345283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.302166223526</t>
   </si>
   <si>
     <t xml:space="preserve">2.36137866973877</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">2.21453261375427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21926951408386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19558477401733</t>
+    <t xml:space="preserve">2.21926975250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19558453559875</t>
   </si>
   <si>
     <t xml:space="preserve">2.21097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18137359619141</t>
+    <t xml:space="preserve">2.18137383460999</t>
   </si>
   <si>
     <t xml:space="preserve">2.1458466053009</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">2.13637280464172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.109135389328</t>
+    <t xml:space="preserve">2.10913515090942</t>
   </si>
   <si>
     <t xml:space="preserve">2.14110946655273</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">2.16361021995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18611097335815</t>
+    <t xml:space="preserve">2.18611073493958</t>
   </si>
   <si>
     <t xml:space="preserve">2.13874125480652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.119793176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14939951896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13755679130554</t>
+    <t xml:space="preserve">2.11979341506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1493992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13755702972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.16597867012024</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">2.15532040596008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20032167434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18374276161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23821783065796</t>
+    <t xml:space="preserve">2.20032143592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18374252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821759223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.27374482154846</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">2.3838791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34835195541382</t>
+    <t xml:space="preserve">2.3483521938324</t>
   </si>
   <si>
     <t xml:space="preserve">2.36848425865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37322115898132</t>
+    <t xml:space="preserve">2.37322092056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.36966824531555</t>
@@ -1097,76 +1097,76 @@
     <t xml:space="preserve">2.37203669548035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38032650947571</t>
+    <t xml:space="preserve">2.38032674789429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38861608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34361505508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30927205085754</t>
+    <t xml:space="preserve">2.34361481666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30927228927612</t>
   </si>
   <si>
     <t xml:space="preserve">2.28913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2938768863678</t>
+    <t xml:space="preserve">2.29387712478638</t>
   </si>
   <si>
     <t xml:space="preserve">2.33058834075928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34953618049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36019468307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31637763977051</t>
+    <t xml:space="preserve">2.34953594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36019444465637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31637716293335</t>
   </si>
   <si>
     <t xml:space="preserve">2.34479928016663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31756186485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34006237983704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40401148796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40993285179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37914228439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3554573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31045603752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25953388214111</t>
+    <t xml:space="preserve">2.31756162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34006214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40401124954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40993237495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37914252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35545754432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31045651435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25953412055969</t>
   </si>
   <si>
     <t xml:space="preserve">2.27966570854187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25598120689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23111200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22163820266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19676923751831</t>
+    <t xml:space="preserve">2.25598096847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23111176490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22163796424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19676899909973</t>
   </si>
   <si>
     <t xml:space="preserve">2.19321632385254</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">2.13163566589355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16005706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15058374404907</t>
+    <t xml:space="preserve">2.16005730628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15058350563049</t>
   </si>
   <si>
     <t xml:space="preserve">2.16834712028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13045144081116</t>
+    <t xml:space="preserve">2.13045120239258</t>
   </si>
   <si>
     <t xml:space="preserve">2.12097716331482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1103196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08426642417908</t>
+    <t xml:space="preserve">2.11031937599182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08426594734192</t>
   </si>
   <si>
     <t xml:space="preserve">2.22400665283203</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.24295449256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29624509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28795576095581</t>
+    <t xml:space="preserve">2.29624533653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28795552253723</t>
   </si>
   <si>
     <t xml:space="preserve">2.25006008148193</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">2.25834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24413824081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2275595664978</t>
+    <t xml:space="preserve">2.24413847923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22755908966064</t>
   </si>
   <si>
     <t xml:space="preserve">2.22637510299683</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">2.2926926612854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3211145401001</t>
+    <t xml:space="preserve">2.32111430168152</t>
   </si>
   <si>
     <t xml:space="preserve">2.25716543197632</t>
@@ -1250,31 +1250,31 @@
     <t xml:space="preserve">2.29742956161499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124382972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31874561309814</t>
+    <t xml:space="preserve">2.25124430656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3187460899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.27848172187805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2666392326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28321886062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32703566551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34598326683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30571937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27729749679565</t>
+    <t xml:space="preserve">2.26663947105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28321862220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32703590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34598350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30571961402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27729725837708</t>
   </si>
   <si>
     <t xml:space="preserve">2.20742702484131</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">2.20979571342468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19913744926453</t>
+    <t xml:space="preserve">2.19913768768311</t>
   </si>
   <si>
     <t xml:space="preserve">2.23348045349121</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">2.26900768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27256083488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24177002906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361275672913</t>
+    <t xml:space="preserve">2.27256059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24177050590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361251831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.27019190788269</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">2.33177256584167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3282196521759</t>
+    <t xml:space="preserve">2.32821989059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.31519317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41585373878479</t>
+    <t xml:space="preserve">2.39098477363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41585397720337</t>
   </si>
   <si>
     <t xml:space="preserve">2.41940641403198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4371702671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48098731040955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53309321403503</t>
+    <t xml:space="preserve">2.43717002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48098754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53309369087219</t>
   </si>
   <si>
     <t xml:space="preserve">2.56743693351746</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">2.54612064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56151533126831</t>
+    <t xml:space="preserve">2.56151604652405</t>
   </si>
   <si>
     <t xml:space="preserve">2.57572650909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56862092018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57691073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56980538368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5662522315979</t>
+    <t xml:space="preserve">2.56862115859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57691097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56980514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56625294685364</t>
   </si>
   <si>
     <t xml:space="preserve">2.63967537879944</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">2.63671493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62960934638977</t>
+    <t xml:space="preserve">2.62960910797119</t>
   </si>
   <si>
     <t xml:space="preserve">2.58105564117432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57158160209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56921339035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48039531707764</t>
+    <t xml:space="preserve">2.57158136367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56921315193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48039484024048</t>
   </si>
   <si>
     <t xml:space="preserve">2.53013324737549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45611786842346</t>
+    <t xml:space="preserve">2.45611810684204</t>
   </si>
   <si>
     <t xml:space="preserve">2.48217129707336</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">2.44605207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40697169303894</t>
+    <t xml:space="preserve">2.40697193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47092127799988</t>
+    <t xml:space="preserve">2.47092056274414</t>
   </si>
   <si>
     <t xml:space="preserve">2.45552563667297</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.44723606109619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4655921459198</t>
+    <t xml:space="preserve">2.46559190750122</t>
   </si>
   <si>
     <t xml:space="preserve">2.473881483078</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">2.43480181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40756368637085</t>
+    <t xml:space="preserve">2.40756416320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.3264434337616</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">2.3744056224823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.357825756073</t>
+    <t xml:space="preserve">2.35782623291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.42592000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36611580848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38624811172485</t>
+    <t xml:space="preserve">2.36611557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3862476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.39986658096313</t>
@@ -1496,40 +1496,40 @@
     <t xml:space="preserve">2.37499737739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36374688148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39809012413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38565564155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41230082511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41822242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45078873634338</t>
+    <t xml:space="preserve">2.36374711990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39809036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38565540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4123010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41822218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45078897476196</t>
   </si>
   <si>
     <t xml:space="preserve">2.51769852638245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51355385780334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54315948486328</t>
+    <t xml:space="preserve">2.51355361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54315972328186</t>
   </si>
   <si>
     <t xml:space="preserve">2.54079127311707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54375171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58756852149963</t>
+    <t xml:space="preserve">2.54375195503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58756875991821</t>
   </si>
   <si>
     <t xml:space="preserve">2.61066150665283</t>
@@ -1541,25 +1541,25 @@
     <t xml:space="preserve">2.59408235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61480641365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63493847846985</t>
+    <t xml:space="preserve">2.61480617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63493871688843</t>
   </si>
   <si>
     <t xml:space="preserve">2.65803122520447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64204406738281</t>
+    <t xml:space="preserve">2.64204382896423</t>
   </si>
   <si>
     <t xml:space="preserve">2.67165017127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6752028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58638477325439</t>
+    <t xml:space="preserve">2.67520236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58638453483582</t>
   </si>
   <si>
     <t xml:space="preserve">2.60177969932556</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.55855536460876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57039713859558</t>
+    <t xml:space="preserve">2.57039737701416</t>
   </si>
   <si>
     <t xml:space="preserve">2.59349036216736</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">2.59526634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51059293746948</t>
+    <t xml:space="preserve">2.51059317588806</t>
   </si>
   <si>
     <t xml:space="preserve">2.54967355728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48868465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49672627449036</t>
+    <t xml:space="preserve">2.48868489265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49672651290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.48621010780334</t>
@@ -1598,19 +1598,19 @@
     <t xml:space="preserve">2.40888357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.387850522995</t>
+    <t xml:space="preserve">2.38785076141357</t>
   </si>
   <si>
     <t xml:space="preserve">2.3773341178894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25917887687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31176090240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25361156463623</t>
+    <t xml:space="preserve">2.25917863845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176114082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25361108779907</t>
   </si>
   <si>
     <t xml:space="preserve">2.33464956283569</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">2.24371337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20041012763977</t>
+    <t xml:space="preserve">2.20041036605835</t>
   </si>
   <si>
     <t xml:space="preserve">2.20968985557556</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">2.22329902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20721530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15525126457214</t>
+    <t xml:space="preserve">2.20721507072449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15525150299072</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298696517944</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">2.05812907218933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05874752998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05379891395569</t>
+    <t xml:space="preserve">2.0587477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05379843711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.02843594551086</t>
@@ -1679,58 +1679,58 @@
     <t xml:space="preserve">2.04946875572205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09215307235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11689758300781</t>
+    <t xml:space="preserve">2.09215259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11689710617065</t>
   </si>
   <si>
     <t xml:space="preserve">2.10143232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14102339744568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11813473701477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08905982971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06864547729492</t>
+    <t xml:space="preserve">2.14102363586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11813449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08906006813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0686457157135</t>
   </si>
   <si>
     <t xml:space="preserve">2.09091591835022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1063814163208</t>
+    <t xml:space="preserve">2.10638093948364</t>
   </si>
   <si>
     <t xml:space="preserve">2.12679553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14349794387817</t>
+    <t xml:space="preserve">2.14349770545959</t>
   </si>
   <si>
     <t xml:space="preserve">2.13793039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12122774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0995762348175</t>
+    <t xml:space="preserve">2.12122750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09957671165466</t>
   </si>
   <si>
     <t xml:space="preserve">2.11380457878113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14473533630371</t>
+    <t xml:space="preserve">2.14473509788513</t>
   </si>
   <si>
     <t xml:space="preserve">2.18061494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16514945030212</t>
+    <t xml:space="preserve">2.1651496887207</t>
   </si>
   <si>
     <t xml:space="preserve">2.20102906227112</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">2.12432074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10699987411499</t>
+    <t xml:space="preserve">2.10699963569641</t>
   </si>
   <si>
     <t xml:space="preserve">2.13916754722595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1199905872345</t>
+    <t xml:space="preserve">2.11999082565308</t>
   </si>
   <si>
     <t xml:space="preserve">2.07730627059937</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">2.20474076271057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28392314910889</t>
+    <t xml:space="preserve">2.28392338752747</t>
   </si>
   <si>
     <t xml:space="preserve">2.23319697380066</t>
@@ -1772,31 +1772,31 @@
     <t xml:space="preserve">2.19174981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24309468269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26289057731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2529923915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26969504356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27711868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25608587265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24185729026794</t>
+    <t xml:space="preserve">2.2430944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26289033889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25299263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26969528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27711844444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25608563423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2418577671051</t>
   </si>
   <si>
     <t xml:space="preserve">2.19917345046997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22206211090088</t>
+    <t xml:space="preserve">2.2220618724823</t>
   </si>
   <si>
     <t xml:space="preserve">2.27526259422302</t>
@@ -1808,46 +1808,46 @@
     <t xml:space="preserve">2.31485414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31423568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991095542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33712410926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33836150169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33403086662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3600127696991</t>
+    <t xml:space="preserve">2.31423544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3699107170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33712434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33836126327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3340311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36001300811768</t>
   </si>
   <si>
     <t xml:space="preserve">2.40146017074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41630697250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41445088386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42063689231873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45589804649353</t>
+    <t xml:space="preserve">2.41630673408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41445112228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4206371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45589828491211</t>
   </si>
   <si>
     <t xml:space="preserve">2.44352579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47012615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48682880401611</t>
+    <t xml:space="preserve">2.47012591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48682904243469</t>
   </si>
   <si>
     <t xml:space="preserve">2.50600576400757</t>
@@ -1859,16 +1859,16 @@
     <t xml:space="preserve">2.367436170578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30743074417114</t>
+    <t xml:space="preserve">2.30743050575256</t>
   </si>
   <si>
     <t xml:space="preserve">2.37795281410217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36496186256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27093243598938</t>
+    <t xml:space="preserve">2.36496162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2709321975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.28083038330078</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">2.20907115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18308925628662</t>
+    <t xml:space="preserve">2.1830894947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.17504715919495</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">2.19979166984558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16824245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648865699768</t>
+    <t xml:space="preserve">2.16824269294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15648889541626</t>
   </si>
   <si>
     <t xml:space="preserve">2.09772038459778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13978624343872</t>
+    <t xml:space="preserve">2.1397864818573</t>
   </si>
   <si>
     <t xml:space="preserve">2.1218466758728</t>
@@ -1910,28 +1910,28 @@
     <t xml:space="preserve">2.19669890403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17381024360657</t>
+    <t xml:space="preserve">2.17381000518799</t>
   </si>
   <si>
     <t xml:space="preserve">2.21525716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24247598648071</t>
+    <t xml:space="preserve">2.24247622489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.24433183670044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24742484092712</t>
+    <t xml:space="preserve">2.2474250793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.2597975730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33217549324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34949636459351</t>
+    <t xml:space="preserve">2.33217525482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34949660301208</t>
   </si>
   <si>
     <t xml:space="preserve">2.26598358154297</t>
@@ -1943,49 +1943,49 @@
     <t xml:space="preserve">2.28825354576111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22701048851013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2041220664978</t>
+    <t xml:space="preserve">2.22701072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20412230491638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15834474563599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1373119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23443388938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22639203071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28949069976807</t>
+    <t xml:space="preserve">2.13731169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2344343662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22639226913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28949093818665</t>
   </si>
   <si>
     <t xml:space="preserve">2.24680638313293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23381543159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15277719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16947937011719</t>
+    <t xml:space="preserve">2.23381519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15277695655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16947960853577</t>
   </si>
   <si>
     <t xml:space="preserve">2.15401434898376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18556380271912</t>
+    <t xml:space="preserve">2.18556356430054</t>
   </si>
   <si>
     <t xml:space="preserve">2.21278238296509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19608020782471</t>
+    <t xml:space="preserve">2.19607996940613</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504173278809</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">2.1762843132019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14040470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27959322929382</t>
+    <t xml:space="preserve">2.14040493965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27959299087524</t>
   </si>
   <si>
     <t xml:space="preserve">2.3241331577301</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">2.41012048721313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43053483963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32227754592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3742413520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41259503364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43424677848816</t>
+    <t xml:space="preserve">2.43053507804871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32227730751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37424111366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41259527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.434246301651</t>
   </si>
   <si>
     <t xml:space="preserve">2.44971203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45342373847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54930853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55116438865662</t>
+    <t xml:space="preserve">2.45342350006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54930830001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55116486549377</t>
   </si>
   <si>
     <t xml:space="preserve">2.53260612487793</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">2.47321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136330604553</t>
+    <t xml:space="preserve">2.47136306762695</t>
   </si>
   <si>
     <t xml:space="preserve">2.50043821334839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51528477668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52394533157349</t>
+    <t xml:space="preserve">2.5152850151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52394580841064</t>
   </si>
   <si>
     <t xml:space="preserve">2.4620840549469</t>
@@ -2069,25 +2069,25 @@
     <t xml:space="preserve">2.32908201217651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36125016212463</t>
+    <t xml:space="preserve">2.36124992370605</t>
   </si>
   <si>
     <t xml:space="preserve">2.42620444297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44105100631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45713496208191</t>
+    <t xml:space="preserve">2.4410514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609696388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45713520050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.45094919204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47507524490356</t>
+    <t xml:space="preserve">2.47507500648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46579599380493</t>
@@ -2102,34 +2102,34 @@
     <t xml:space="preserve">2.4818799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47878670692444</t>
+    <t xml:space="preserve">2.47878694534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.49548935890198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50662422180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5288941860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53446221351624</t>
+    <t xml:space="preserve">2.50662446022034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52889442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53446197509766</t>
   </si>
   <si>
     <t xml:space="preserve">2.50786161422729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55302047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58147692680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64952445030212</t>
+    <t xml:space="preserve">2.5530207157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58147668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64952421188354</t>
   </si>
   <si>
     <t xml:space="preserve">2.68292927742004</t>
@@ -2144,22 +2144,22 @@
     <t xml:space="preserve">2.68231081962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66870164871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179417610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69282746315002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71014857292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74664640426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76396775245667</t>
+    <t xml:space="preserve">2.66870141029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179441452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69282722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71014881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74664688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76396751403809</t>
   </si>
   <si>
     <t xml:space="preserve">2.7299439907074</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">2.83696436882019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8344898223877</t>
+    <t xml:space="preserve">2.83448958396912</t>
   </si>
   <si>
     <t xml:space="preserve">2.86109018325806</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">2.75716280937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76025629043579</t>
+    <t xml:space="preserve">2.76025605201721</t>
   </si>
   <si>
     <t xml:space="preserve">2.78500056266785</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.78994965553284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82088017463684</t>
+    <t xml:space="preserve">2.82088088989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.83943867683411</t>
@@ -2201,37 +2201,37 @@
     <t xml:space="preserve">2.83882021903992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79737329483032</t>
+    <t xml:space="preserve">2.79737305641174</t>
   </si>
   <si>
     <t xml:space="preserve">2.81160116195679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78685688972473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79922866821289</t>
+    <t xml:space="preserve">2.78685665130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79922914505005</t>
   </si>
   <si>
     <t xml:space="preserve">2.80603337287903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81778764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79551696777344</t>
+    <t xml:space="preserve">2.81778717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79551720619202</t>
   </si>
   <si>
     <t xml:space="preserve">2.74417209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65694761276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014290809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59137487411499</t>
+    <t xml:space="preserve">2.65694737434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59137439727783</t>
   </si>
   <si>
     <t xml:space="preserve">2.69097137451172</t>
@@ -2240,43 +2240,43 @@
     <t xml:space="preserve">2.66560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73056292533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79984760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76334929466248</t>
+    <t xml:space="preserve">2.73056268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79984784126282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76334953308105</t>
   </si>
   <si>
     <t xml:space="preserve">2.75045776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75625872612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79106616973877</t>
+    <t xml:space="preserve">2.75625896453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79106664657593</t>
   </si>
   <si>
     <t xml:space="preserve">2.68084192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79235553741455</t>
+    <t xml:space="preserve">2.79235577583313</t>
   </si>
   <si>
     <t xml:space="preserve">2.72596311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68148636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62863039970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65892577171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66279315948486</t>
+    <t xml:space="preserve">2.68148612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62863063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65892601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66279339790344</t>
   </si>
   <si>
     <t xml:space="preserve">2.6344313621521</t>
@@ -2285,43 +2285,43 @@
     <t xml:space="preserve">2.68664336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66666102409363</t>
+    <t xml:space="preserve">2.66666126251221</t>
   </si>
   <si>
     <t xml:space="preserve">2.65183544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66472721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6885769367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6943781375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68986630439758</t>
+    <t xml:space="preserve">2.66472697257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68857717514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69437837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.689866065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72016167640686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69695639610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65247988700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69953536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75303602218628</t>
+    <t xml:space="preserve">2.69695663452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65247964859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69953513145447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7530357837677</t>
   </si>
   <si>
     <t xml:space="preserve">2.73563170433044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176455497742</t>
+    <t xml:space="preserve">2.73176431655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205992698669</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">2.75883722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79428958892822</t>
+    <t xml:space="preserve">2.79428935050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.76077103614807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79944610595703</t>
+    <t xml:space="preserve">2.79944634437561</t>
   </si>
   <si>
     <t xml:space="preserve">2.820072889328</t>
@@ -2345,67 +2345,67 @@
     <t xml:space="preserve">2.86197113990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91160440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90773701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89162254333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89484548568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95414733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.974773645401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96832847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97541904449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98702144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9689724445343</t>
+    <t xml:space="preserve">2.91160488128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90773725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89162230491638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89484524726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95414781570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97477388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96832823753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97541880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98702096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96897268295288</t>
   </si>
   <si>
     <t xml:space="preserve">2.97735238075256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91805028915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04181122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02118468284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03665447235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03923296928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04825735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00829243659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97155117988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98895502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90902614593506</t>
+    <t xml:space="preserve">2.91805052757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04181146621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02118396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0366542339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03923273086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04825711250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97155141830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98895525932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90902590751648</t>
   </si>
   <si>
     <t xml:space="preserve">2.86003732681274</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">2.78655433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76592755317688</t>
+    <t xml:space="preserve">2.76592779159546</t>
   </si>
   <si>
     <t xml:space="preserve">2.83812141418457</t>
@@ -2429,31 +2429,31 @@
     <t xml:space="preserve">2.78010869026184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84843516349792</t>
+    <t xml:space="preserve">2.84843468666077</t>
   </si>
   <si>
     <t xml:space="preserve">2.87421846389771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95608115196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9477014541626</t>
+    <t xml:space="preserve">2.9560809135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94770121574402</t>
   </si>
   <si>
     <t xml:space="preserve">2.91869473457336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91676115989685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94705677032471</t>
+    <t xml:space="preserve">2.91676139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94705724716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.91031527519226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96510529518127</t>
+    <t xml:space="preserve">2.96510553359985</t>
   </si>
   <si>
     <t xml:space="preserve">2.9457676410675</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">2.94125556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94383406639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97606348991394</t>
+    <t xml:space="preserve">2.94383358955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97606372833252</t>
   </si>
   <si>
     <t xml:space="preserve">2.95479202270508</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">3.05921530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11013722419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10884833335876</t>
+    <t xml:space="preserve">3.11013746261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10884857177734</t>
   </si>
   <si>
     <t xml:space="preserve">3.08048629760742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11464953422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10240268707275</t>
+    <t xml:space="preserve">3.11464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10240244865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.09853506088257</t>
@@ -2504,28 +2504,28 @@
     <t xml:space="preserve">3.10175776481628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12431859970093</t>
+    <t xml:space="preserve">3.12431836128235</t>
   </si>
   <si>
     <t xml:space="preserve">3.1494574546814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13592100143433</t>
+    <t xml:space="preserve">3.13592076301575</t>
   </si>
   <si>
     <t xml:space="preserve">3.07661867141724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05663704872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02698564529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04696798324585</t>
+    <t xml:space="preserve">3.05663728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02698540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04696822166443</t>
   </si>
   <si>
     <t xml:space="preserve">3.0875768661499</t>
@@ -2537,34 +2537,34 @@
     <t xml:space="preserve">3.19071102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15397000312805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15010261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17781901359558</t>
+    <t xml:space="preserve">3.15396976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15010213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17781925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.20553660392761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2268078327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22165179252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21262741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23325419425964</t>
+    <t xml:space="preserve">3.22680807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22165155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21262717247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23325347900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.25001311302185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21391630172729</t>
+    <t xml:space="preserve">3.21391654014587</t>
   </si>
   <si>
     <t xml:space="preserve">3.23970007896423</t>
@@ -2576,73 +2576,73 @@
     <t xml:space="preserve">3.24743485450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22229623794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25388050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28739976882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31447243690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35185790061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39955735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116046905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43307614326477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49108934402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47304058074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43823313713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45370268821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39311194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40600323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41631722450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41502785682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.413738489151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44596815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40987086296082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42920851707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3454122543335</t>
+    <t xml:space="preserve">3.22229599952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2538800239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28739905357361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31447172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35185813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3995578289032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41115999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43307685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4910888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47304081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43823289871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39311146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40600371360779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41631746292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4150276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41373872756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44596791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40987110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42920899391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34541273117065</t>
   </si>
   <si>
     <t xml:space="preserve">3.32994198799133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38924407958984</t>
+    <t xml:space="preserve">3.38924431800842</t>
   </si>
   <si>
     <t xml:space="preserve">3.38795471191406</t>
@@ -2654,43 +2654,43 @@
     <t xml:space="preserve">3.29126667976379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192950248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32865309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43049788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4369432926178</t>
+    <t xml:space="preserve">3.27192974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32865285873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36861729621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43049764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43694376945496</t>
   </si>
   <si>
     <t xml:space="preserve">3.4240517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42147350311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4781973361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45499205589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37635207176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29513478279114</t>
+    <t xml:space="preserve">3.42147397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45499277114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37635278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29513430595398</t>
   </si>
   <si>
     <t xml:space="preserve">3.35572552680969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26032686233521</t>
+    <t xml:space="preserve">3.26032662391663</t>
   </si>
   <si>
     <t xml:space="preserve">3.22938680648804</t>
@@ -2699,49 +2699,49 @@
     <t xml:space="preserve">3.30544805526733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3325207233429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31576132774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23841071128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1475236415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18490982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19006657600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1681501865387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17395162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205361366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09982395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12238454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04890203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1159393787384</t>
+    <t xml:space="preserve">3.33252048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23841094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14752316474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18491005897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19006609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815042495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17395210266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09982419013977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12238502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04890155792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11593914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.14623498916626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02182936668396</t>
+    <t xml:space="preserve">3.02182912826538</t>
   </si>
   <si>
     <t xml:space="preserve">2.96703910827637</t>
@@ -2753,58 +2753,58 @@
     <t xml:space="preserve">3.04310035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09466767311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07017350196838</t>
+    <t xml:space="preserve">3.09466743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0701732635498</t>
   </si>
   <si>
     <t xml:space="preserve">3.15848183631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18297600746155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4008469581604</t>
+    <t xml:space="preserve">3.18297576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40084719657898</t>
   </si>
   <si>
     <t xml:space="preserve">3.44854617118835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54394555091858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4756190776825</t>
+    <t xml:space="preserve">3.54394578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47561955451965</t>
   </si>
   <si>
     <t xml:space="preserve">3.39440083503723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17459654808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14236688613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01409387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88582110404968</t>
+    <t xml:space="preserve">3.17459678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14236736297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01409411430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8858208656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.74272274971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70017981529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56610512733459</t>
+    <t xml:space="preserve">2.70017957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56610536575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.51969480514526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24896812438965</t>
+    <t xml:space="preserve">2.24896788597107</t>
   </si>
   <si>
     <t xml:space="preserve">2.15936994552612</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">2.17741870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646730422974</t>
+    <t xml:space="preserve">1.79646694660187</t>
   </si>
   <si>
     <t xml:space="preserve">1.88993239402771</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">1.76617133617401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68817603588104</t>
+    <t xml:space="preserve">1.68817639350891</t>
   </si>
   <si>
     <t xml:space="preserve">1.62500655651093</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">1.91313743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77261734008789</t>
+    <t xml:space="preserve">1.7726172208786</t>
   </si>
   <si>
     <t xml:space="preserve">1.83965456485748</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">1.94149935245514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04141092300415</t>
+    <t xml:space="preserve">2.04141068458557</t>
   </si>
   <si>
     <t xml:space="preserve">1.90669167041779</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">2.05236864089966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98662090301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11295986175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12327313423157</t>
+    <t xml:space="preserve">1.98662042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11295962333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12327289581299</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912755966187</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">2.09104371070862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94278836250305</t>
+    <t xml:space="preserve">1.94278860092163</t>
   </si>
   <si>
     <t xml:space="preserve">1.92087244987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93892085552216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90282416343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83063042163849</t>
+    <t xml:space="preserve">1.93892109394073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90282392501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">1.8976674079895</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">2.05623602867126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02658534049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0252959728241</t>
+    <t xml:space="preserve">2.0265851020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02529573440552</t>
   </si>
   <si>
     <t xml:space="preserve">2.04463338851929</t>
@@ -2918,40 +2918,40 @@
     <t xml:space="preserve">2.04721188545227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752515792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01627135276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01756119728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98790967464447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97243940830231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32651424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22702980041504</t>
+    <t xml:space="preserve">2.05752539634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01627159118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01756072044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98790991306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97243964672089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32651400566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22702956199646</t>
   </si>
   <si>
     <t xml:space="preserve">2.21850252151489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17018151283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2199239730835</t>
+    <t xml:space="preserve">2.17018127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21992373466492</t>
   </si>
   <si>
     <t xml:space="preserve">2.28387808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27535080909729</t>
+    <t xml:space="preserve">2.27535057067871</t>
   </si>
   <si>
     <t xml:space="preserve">2.26540231704712</t>
@@ -2960,25 +2960,25 @@
     <t xml:space="preserve">2.31372332572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24266290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25687503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46863460540771</t>
+    <t xml:space="preserve">2.24266266822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25687527656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39046835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46863484382629</t>
   </si>
   <si>
     <t xml:space="preserve">2.52406191825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63633704185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61644005775452</t>
+    <t xml:space="preserve">2.63633680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6164402961731</t>
   </si>
   <si>
     <t xml:space="preserve">2.56669783592224</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">2.48995280265808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37909889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38336277008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38762593269348</t>
+    <t xml:space="preserve">2.37909865379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38336253166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38762617111206</t>
   </si>
   <si>
     <t xml:space="preserve">2.47005605697632</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">2.47574067115784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45158052444458</t>
+    <t xml:space="preserve">2.45158004760742</t>
   </si>
   <si>
     <t xml:space="preserve">2.44021034240723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40325927734375</t>
+    <t xml:space="preserve">2.40325903892517</t>
   </si>
   <si>
     <t xml:space="preserve">2.4188928604126</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">2.42457723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48284697532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46010732650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43310475349426</t>
+    <t xml:space="preserve">2.48284649848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46010756492615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43310451507568</t>
   </si>
   <si>
     <t xml:space="preserve">2.53258895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53116798400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55817055702209</t>
+    <t xml:space="preserve">2.53116774559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55817031860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.57238268852234</t>
@@ -3044,25 +3044,25 @@
     <t xml:space="preserve">2.58090972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51127076148987</t>
+    <t xml:space="preserve">2.51127099990845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53685259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56527662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60933423042297</t>
+    <t xml:space="preserve">2.5652768611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60933375358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.64202189445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63207364082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65481281280518</t>
+    <t xml:space="preserve">2.63207316398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6548125743866</t>
   </si>
   <si>
     <t xml:space="preserve">2.67755198478699</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">2.76424551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64770650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61501908302307</t>
+    <t xml:space="preserve">2.64770698547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61501932144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.60649180412292</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">2.4572651386261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5468008518219</t>
+    <t xml:space="preserve">2.54680109024048</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186713218689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66049742698669</t>
+    <t xml:space="preserve">2.66049718856812</t>
   </si>
   <si>
     <t xml:space="preserve">2.68465805053711</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">2.89641785621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92199969291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86373019218445</t>
+    <t xml:space="preserve">2.92199945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86372995376587</t>
   </si>
   <si>
     <t xml:space="preserve">2.83388447761536</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">2.88931155204773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84951829910278</t>
+    <t xml:space="preserve">2.8495180606842</t>
   </si>
   <si>
     <t xml:space="preserve">2.84099054336548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9177360534668</t>
+    <t xml:space="preserve">2.91773581504822</t>
   </si>
   <si>
     <t xml:space="preserve">2.93479037284851</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">2.87083601951599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88789057731628</t>
+    <t xml:space="preserve">2.88789033889771</t>
   </si>
   <si>
     <t xml:space="preserve">2.85378122329712</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">2.81256651878357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78556370735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90068125724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87794232368469</t>
+    <t xml:space="preserve">2.78556346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90068101882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87794208526611</t>
   </si>
   <si>
     <t xml:space="preserve">2.94189643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95184445381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95752954483032</t>
+    <t xml:space="preserve">2.95184469223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9575297832489</t>
   </si>
   <si>
     <t xml:space="preserve">2.93621134757996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91489362716675</t>
+    <t xml:space="preserve">2.91489338874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.85662412643433</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">2.70455479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6576554775238</t>
+    <t xml:space="preserve">2.65765523910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.72729420661926</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">2.66902470588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65054965019226</t>
+    <t xml:space="preserve">2.65054893493652</t>
   </si>
   <si>
     <t xml:space="preserve">2.6491277217865</t>
@@ -3212,25 +3212,25 @@
     <t xml:space="preserve">2.610755443573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68039441108704</t>
+    <t xml:space="preserve">2.68039417266846</t>
   </si>
   <si>
     <t xml:space="preserve">2.62354612350464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63065242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61359786987305</t>
+    <t xml:space="preserve">2.63065195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61359763145447</t>
   </si>
   <si>
     <t xml:space="preserve">2.56243419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45868635177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5027437210083</t>
+    <t xml:space="preserve">2.45868611335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50274348258972</t>
   </si>
   <si>
     <t xml:space="preserve">2.48853182792664</t>
@@ -3239,34 +3239,34 @@
     <t xml:space="preserve">2.4970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52690434455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48568940162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42741966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39899563789368</t>
+    <t xml:space="preserve">2.52690386772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48568916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42741942405701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3989953994751</t>
   </si>
   <si>
     <t xml:space="preserve">2.37199258804321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25403261184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23129343986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30235385894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37057185173035</t>
+    <t xml:space="preserve">2.25403237342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23129320144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276616096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30235362052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37057161331177</t>
   </si>
   <si>
     <t xml:space="preserve">2.3947319984436</t>
@@ -3278,16 +3278,16 @@
     <t xml:space="preserve">2.52264046669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52832531929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5553286075592</t>
+    <t xml:space="preserve">2.52832555770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">2.71450328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76850938796997</t>
+    <t xml:space="preserve">2.76850914955139</t>
   </si>
   <si>
     <t xml:space="preserve">2.74008512496948</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">2.84383320808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83672738075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97174167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93052673339844</t>
+    <t xml:space="preserve">2.83672714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97174191474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93052697181702</t>
   </si>
   <si>
     <t xml:space="preserve">2.90920829772949</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">2.81967258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8097243309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78840637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78130030632019</t>
+    <t xml:space="preserve">2.80972385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78840613365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78130006790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.78272104263306</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">2.77561521530151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70597648620605</t>
+    <t xml:space="preserve">2.70597624778748</t>
   </si>
   <si>
     <t xml:space="preserve">2.70739722251892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71308255195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75998210906982</t>
+    <t xml:space="preserve">2.71308207511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75998187065125</t>
   </si>
   <si>
     <t xml:space="preserve">2.79835438728333</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">2.72871541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75429725646973</t>
+    <t xml:space="preserve">2.75429677963257</t>
   </si>
   <si>
     <t xml:space="preserve">2.75571823120117</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">2.79266977310181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77419424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77845764160156</t>
+    <t xml:space="preserve">2.77419400215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77845740318298</t>
   </si>
   <si>
     <t xml:space="preserve">2.75713968276978</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">2.86088752746582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85946655273438</t>
+    <t xml:space="preserve">2.8594663143158</t>
   </si>
   <si>
     <t xml:space="preserve">2.91347217559814</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">2.88646936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84241199493408</t>
+    <t xml:space="preserve">2.88362669944763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8424117565155</t>
   </si>
   <si>
     <t xml:space="preserve">2.76993060112</t>
@@ -3392,37 +3392,37 @@
     <t xml:space="preserve">2.79551219940186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67897343635559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68181562423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.745769739151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64344334602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57522559165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.644864320755</t>
+    <t xml:space="preserve">2.67897319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68181538581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74576997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64344310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57522535324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64486408233643</t>
   </si>
   <si>
     <t xml:space="preserve">2.80546045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8665726184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758081436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13233780860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1053352355957</t>
+    <t xml:space="preserve">2.86657238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758105278015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13233804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10533475875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.18350124359131</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">3.13944435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15791940689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12665319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.039959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742676734924</t>
+    <t xml:space="preserve">3.15791988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12665343284607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03995966911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742652893066</t>
   </si>
   <si>
     <t xml:space="preserve">3.01153540611267</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">3.03427481651306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08259558677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13375878334045</t>
+    <t xml:space="preserve">3.08259582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13375902175903</t>
   </si>
   <si>
     <t xml:space="preserve">3.11812591552734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05843496322632</t>
+    <t xml:space="preserve">3.0584352016449</t>
   </si>
   <si>
     <t xml:space="preserve">3.19344997406006</t>
@@ -3470,28 +3470,28 @@
     <t xml:space="preserve">3.16928911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21192526817322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25171899795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479709148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30004024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28867053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435539245605</t>
+    <t xml:space="preserve">3.2119255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2517192363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14797115325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30004048347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28867077827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435563087463</t>
   </si>
   <si>
     <t xml:space="preserve">3.3014612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32562160491943</t>
+    <t xml:space="preserve">3.32562184333801</t>
   </si>
   <si>
     <t xml:space="preserve">3.30572533607483</t>
@@ -3503,31 +3503,31 @@
     <t xml:space="preserve">3.37110090255737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41942167282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36967921257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26450991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27587962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30856728553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947294235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37962746620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38247013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4037880897522</t>
+    <t xml:space="preserve">3.41942119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36967968940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2645103931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27587985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856800079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947270393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37962794303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38247036933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40378832817078</t>
   </si>
   <si>
     <t xml:space="preserve">3.42013216018677</t>
@@ -3536,103 +3536,103 @@
     <t xml:space="preserve">3.32846450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29790830612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33272767066956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35902047157288</t>
+    <t xml:space="preserve">3.29790854454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33272838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35902070999146</t>
   </si>
   <si>
     <t xml:space="preserve">3.3668372631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34978246688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42723798751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44500303268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32206916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28014373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29719758033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31567335128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33201694488525</t>
+    <t xml:space="preserve">3.34978270530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42723846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44500350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3220694065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28014349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2971978187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31567358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33201766014099</t>
   </si>
   <si>
     <t xml:space="preserve">3.3043041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31780576705933</t>
+    <t xml:space="preserve">3.31780552864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.28440737724304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23679661750793</t>
+    <t xml:space="preserve">3.23679637908936</t>
   </si>
   <si>
     <t xml:space="preserve">3.31212019920349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27232694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31283116340637</t>
+    <t xml:space="preserve">3.27232670783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31283092498779</t>
   </si>
   <si>
     <t xml:space="preserve">3.42226386070251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48550724983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47555875778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49545645713806</t>
+    <t xml:space="preserve">3.48550796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47555923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4954559803009</t>
   </si>
   <si>
     <t xml:space="preserve">3.48124432563782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57575464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58143854141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53027582168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49829840660095</t>
+    <t xml:space="preserve">3.57575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58143925666809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">3.52459073066711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61421203613281</t>
+    <t xml:space="preserve">3.61421179771423</t>
   </si>
   <si>
     <t xml:space="preserve">3.52383756637573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38902950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43120408058167</t>
+    <t xml:space="preserve">3.38902974128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43120431900024</t>
   </si>
   <si>
     <t xml:space="preserve">3.41614174842834</t>
@@ -3641,49 +3641,49 @@
     <t xml:space="preserve">3.44927906990051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48919415473938</t>
+    <t xml:space="preserve">3.48919439315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.46584796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47488474845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45831632614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48844146728516</t>
+    <t xml:space="preserve">3.47488498687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45831656455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48844170570374</t>
   </si>
   <si>
     <t xml:space="preserve">3.46132922172546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4507851600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44626641273499</t>
+    <t xml:space="preserve">3.45078492164612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44626665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.44099473953247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41764831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38752317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3604109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32501482963562</t>
+    <t xml:space="preserve">3.41764855384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38752341270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36041116714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32501459121704</t>
   </si>
   <si>
     <t xml:space="preserve">3.24744319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27229619026184</t>
+    <t xml:space="preserve">3.272296667099</t>
   </si>
   <si>
     <t xml:space="preserve">3.23765277862549</t>
@@ -3692,28 +3692,28 @@
     <t xml:space="preserve">3.21129393577576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28359317779541</t>
+    <t xml:space="preserve">3.28359341621399</t>
   </si>
   <si>
     <t xml:space="preserve">3.21430635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24970269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39279556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35062074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37698030471802</t>
+    <t xml:space="preserve">3.24970293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39279532432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35062050819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37698006629944</t>
   </si>
   <si>
     <t xml:space="preserve">3.29865574836731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29488968849182</t>
+    <t xml:space="preserve">3.2948899269104</t>
   </si>
   <si>
     <t xml:space="preserve">3.21731877326965</t>
@@ -3722,19 +3722,19 @@
     <t xml:space="preserve">3.30468058586121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.316730260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329892158508</t>
+    <t xml:space="preserve">3.31673002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329916000366</t>
   </si>
   <si>
     <t xml:space="preserve">3.32953357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112458229065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28208661079407</t>
+    <t xml:space="preserve">3.29112410545349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28208708763123</t>
   </si>
   <si>
     <t xml:space="preserve">3.14878511428833</t>
@@ -3752,46 +3752,46 @@
     <t xml:space="preserve">3.33480501174927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3860170841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37321400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42216682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40710425376892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38149785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42141366004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37170791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36643600463867</t>
+    <t xml:space="preserve">3.38601732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37321424484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42216658592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4071044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38149809837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4214141368866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37170815467834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36643624305725</t>
   </si>
   <si>
     <t xml:space="preserve">3.39204239845276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48994731903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61797761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60592794418335</t>
+    <t xml:space="preserve">3.48994708061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61797738075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60592770576477</t>
   </si>
   <si>
     <t xml:space="preserve">3.61647129058838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65337419509888</t>
+    <t xml:space="preserve">3.6533739566803</t>
   </si>
   <si>
     <t xml:space="preserve">3.63981819152832</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">3.6307806968689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6383113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72040152549744</t>
+    <t xml:space="preserve">3.63831114768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72040176391602</t>
   </si>
   <si>
     <t xml:space="preserve">3.6752142906189</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">3.66542410850525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75052642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77010679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77462601661682</t>
+    <t xml:space="preserve">3.7505259513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77010726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7746262550354</t>
   </si>
   <si>
     <t xml:space="preserve">3.77311992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79872584342957</t>
+    <t xml:space="preserve">3.79872560501099</t>
   </si>
   <si>
     <t xml:space="preserve">3.77613210678101</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">3.7821569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76709508895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78667569160461</t>
+    <t xml:space="preserve">3.76709461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78667593002319</t>
   </si>
   <si>
     <t xml:space="preserve">3.73696994781494</t>
@@ -3851,124 +3851,124 @@
     <t xml:space="preserve">3.71588277816772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70533919334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6375584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68726420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66994261741638</t>
+    <t xml:space="preserve">3.7053394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63755869865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68726444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994285583496</t>
   </si>
   <si>
     <t xml:space="preserve">3.65638613700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72567296028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67144846916199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58258056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64132404327393</t>
+    <t xml:space="preserve">3.72567319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67144918441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58258128166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6413242816925</t>
   </si>
   <si>
     <t xml:space="preserve">3.75429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75203227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80926918983459</t>
+    <t xml:space="preserve">3.75203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80926942825317</t>
   </si>
   <si>
     <t xml:space="preserve">3.7445011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8062572479248</t>
+    <t xml:space="preserve">3.80625677108765</t>
   </si>
   <si>
     <t xml:space="preserve">3.84541893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83939433097839</t>
+    <t xml:space="preserve">3.83939456939697</t>
   </si>
   <si>
     <t xml:space="preserve">3.90717458724976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88006234169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9538676738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97947382926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9598925113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94483017921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89060616493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92976784706116</t>
+    <t xml:space="preserve">3.88006210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95386791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97947406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95989274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94483089447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89060592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88307523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92976808547974</t>
   </si>
   <si>
     <t xml:space="preserve">3.95682597160339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99502563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01571655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96239686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95125555992126</t>
+    <t xml:space="preserve">3.99502515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01571702957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96239709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95125532150269</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97910928726196</t>
+    <t xml:space="preserve">3.9791088104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.98388361930847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95523428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00457572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98070096969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9735381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98706746101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94807171821594</t>
+    <t xml:space="preserve">3.95523381233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00457525253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98070025444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01889991760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97353863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94807243347168</t>
   </si>
   <si>
     <t xml:space="preserve">3.92340159416199</t>
@@ -3977,61 +3977,61 @@
     <t xml:space="preserve">3.98229241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04277467727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98865914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97274231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90907692909241</t>
+    <t xml:space="preserve">4.04277515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98865938186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9345428943634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97274279594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90907669067383</t>
   </si>
   <si>
     <t xml:space="preserve">3.89952707290649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83983969688416</t>
+    <t xml:space="preserve">3.83984017372131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66078019142151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590117454529</t>
+    <t xml:space="preserve">3.67590093612671</t>
   </si>
   <si>
     <t xml:space="preserve">3.66316795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73638367652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72524213790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70057153701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76821637153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77219486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76264572143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74752497673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72922134399414</t>
+    <t xml:space="preserve">3.73638391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72524237632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70057129859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779858589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7721951007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76264595985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74752473831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72922086715698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73081278800964</t>
@@ -4043,22 +4043,22 @@
     <t xml:space="preserve">3.74513721466064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64565968513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74832081794739</t>
+    <t xml:space="preserve">3.64565944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74832105636597</t>
   </si>
   <si>
     <t xml:space="preserve">3.75150418281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77696990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83267760276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80641579627991</t>
+    <t xml:space="preserve">3.77697038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80641555786133</t>
   </si>
   <si>
     <t xml:space="preserve">3.80323219299316</t>
@@ -4076,52 +4076,52 @@
     <t xml:space="preserve">3.86212348937988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87008118629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89554738998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91146421432495</t>
+    <t xml:space="preserve">3.87008142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89554762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91146469116211</t>
   </si>
   <si>
     <t xml:space="preserve">3.97115063667297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9639880657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95443820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99979996681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91942238807678</t>
+    <t xml:space="preserve">3.96398854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95443844795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99980068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91942262649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.76344132423401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80402827262878</t>
+    <t xml:space="preserve">3.80402851104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.90748476982117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95602989196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90430164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94409275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00775861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96796774864197</t>
+    <t xml:space="preserve">3.95603013038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90430188179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94409251213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96796751022339</t>
   </si>
   <si>
     <t xml:space="preserve">3.85575652122498</t>
@@ -4130,28 +4130,28 @@
     <t xml:space="preserve">3.82710719108582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03004169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01253318786621</t>
+    <t xml:space="preserve">4.03004121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01253366470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.00934982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99820923805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91623950004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85814380645752</t>
+    <t xml:space="preserve">3.99820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91623902320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8581440448761</t>
   </si>
   <si>
     <t xml:space="preserve">3.78094935417175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55414032936096</t>
+    <t xml:space="preserve">3.55414009094238</t>
   </si>
   <si>
     <t xml:space="preserve">3.69261288642883</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">3.60746026039124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42760443687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40293383598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34483933448792</t>
+    <t xml:space="preserve">3.42760491371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40293407440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34483909606934</t>
   </si>
   <si>
     <t xml:space="preserve">3.06948471069336</t>
@@ -4187,58 +4187,58 @@
     <t xml:space="preserve">3.51912403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5684654712677</t>
+    <t xml:space="preserve">3.56846499443054</t>
   </si>
   <si>
     <t xml:space="preserve">3.73797512054443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69022607803345</t>
+    <t xml:space="preserve">3.69022560119629</t>
   </si>
   <si>
     <t xml:space="preserve">3.68385934829712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70852947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74354600906372</t>
+    <t xml:space="preserve">3.70852971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74036240577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74354529380798</t>
   </si>
   <si>
     <t xml:space="preserve">3.90111827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92021822929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97194671630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9631929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693017959595</t>
+    <t xml:space="preserve">3.90668892860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9202184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97194647789001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96319317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693089485168</t>
   </si>
   <si>
     <t xml:space="preserve">4.03481674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06346607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02844953536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11758136749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09848260879517</t>
+    <t xml:space="preserve">4.06346654891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02845001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11758184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09848213195801</t>
   </si>
   <si>
     <t xml:space="preserve">4.12235689163208</t>
@@ -4247,22 +4247,22 @@
     <t xml:space="preserve">4.1334981918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16055631637573</t>
+    <t xml:space="preserve">4.16055679321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.16214799880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20193958282471</t>
+    <t xml:space="preserve">4.20193910598755</t>
   </si>
   <si>
     <t xml:space="preserve">4.21467208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1971640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15419006347656</t>
+    <t xml:space="preserve">4.19716501235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1541895866394</t>
   </si>
   <si>
     <t xml:space="preserve">4.11599016189575</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">4.14623165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24013900756836</t>
+    <t xml:space="preserve">4.2401385307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.19398069381714</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">3.93135976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90509748458862</t>
+    <t xml:space="preserve">3.9050977230072</t>
   </si>
   <si>
     <t xml:space="preserve">4.00298404693604</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">4.00139188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12431669235229</t>
+    <t xml:space="preserve">4.12431621551514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09469366073608</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">4.23011159896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24703931808472</t>
+    <t xml:space="preserve">4.24703884124756</t>
   </si>
   <si>
     <t xml:space="preserve">4.28597116470337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25042390823364</t>
+    <t xml:space="preserve">4.2504243850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.21487712860107</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">4.14124393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09723329544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19202566146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20810604095459</t>
+    <t xml:space="preserve">4.09723281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19202518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20810651779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754560470581</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">4.10738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77053761482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71383166313171</t>
+    <t xml:space="preserve">3.77053785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71383142471313</t>
   </si>
   <si>
     <t xml:space="preserve">3.71975588798523</t>
@@ -4370,28 +4370,28 @@
     <t xml:space="preserve">3.71213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77307677268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76122736930847</t>
+    <t xml:space="preserve">3.7730770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76122784614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.73075866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65881824493408</t>
+    <t xml:space="preserve">3.6588180065155</t>
   </si>
   <si>
     <t xml:space="preserve">3.80100655555725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70198225975037</t>
+    <t xml:space="preserve">3.70198249816895</t>
   </si>
   <si>
     <t xml:space="preserve">3.71467781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71044611930847</t>
+    <t xml:space="preserve">3.71044564247131</t>
   </si>
   <si>
     <t xml:space="preserve">3.66982078552246</t>
@@ -4403,25 +4403,25 @@
     <t xml:space="preserve">3.69690442085266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47177267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49123859405518</t>
+    <t xml:space="preserve">3.47177243232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4912383556366</t>
   </si>
   <si>
     <t xml:space="preserve">3.60634350776672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62919569015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53355669975281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51324415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48700666427612</t>
+    <t xml:space="preserve">3.62919545173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53355693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51324391365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48700642585754</t>
   </si>
   <si>
     <t xml:space="preserve">3.33381533622742</t>
@@ -4439,31 +4439,31 @@
     <t xml:space="preserve">3.38713598251343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26356720924377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25764274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29657554626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24325466156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2813413143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36005258560181</t>
+    <t xml:space="preserve">3.26356744766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25764298439026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29657530784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24325489997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28134107589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36005282402039</t>
   </si>
   <si>
     <t xml:space="preserve">3.45738434791565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46415519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860794067383</t>
+    <t xml:space="preserve">3.46415495872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860817909241</t>
   </si>
   <si>
     <t xml:space="preserve">3.48362135887146</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">3.56741118431091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64358353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66135692596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64273715019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70875310897827</t>
+    <t xml:space="preserve">3.64358329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66135716438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64273691177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70875334739685</t>
   </si>
   <si>
     <t xml:space="preserve">3.70790696144104</t>
@@ -4499,37 +4499,37 @@
     <t xml:space="preserve">3.6520471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5597939491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46838665008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54625225067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50224113464355</t>
+    <t xml:space="preserve">3.55979347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46838688850403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54625201225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50224137306213</t>
   </si>
   <si>
     <t xml:space="preserve">3.50562691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50816583633423</t>
+    <t xml:space="preserve">3.50816559791565</t>
   </si>
   <si>
     <t xml:space="preserve">3.54117393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54709815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61903882026672</t>
+    <t xml:space="preserve">3.54709839820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6190390586853</t>
   </si>
   <si>
     <t xml:space="preserve">3.50901198387146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49885582923889</t>
+    <t xml:space="preserve">3.49885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">3.49800944328308</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">3.6105751991272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70282864570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6791307926178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68336296081543</t>
+    <t xml:space="preserve">3.70282888412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67913103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68336272239685</t>
   </si>
   <si>
     <t xml:space="preserve">3.69351863861084</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">3.70706057548523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7002899646759</t>
+    <t xml:space="preserve">3.70029020309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.59534120559692</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">3.59872627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58010649681091</t>
+    <t xml:space="preserve">3.58010625839233</t>
   </si>
   <si>
     <t xml:space="preserve">3.47515749931335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44045686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38459706306458</t>
+    <t xml:space="preserve">3.4404571056366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38459730148315</t>
   </si>
   <si>
     <t xml:space="preserve">3.34735727310181</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.47431135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38205814361572</t>
+    <t xml:space="preserve">3.38205790519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.34820365905762</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.3676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37613344192505</t>
+    <t xml:space="preserve">3.37613368034363</t>
   </si>
   <si>
     <t xml:space="preserve">3.31519556045532</t>
@@ -4610,19 +4610,19 @@
     <t xml:space="preserve">3.42437601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43114709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45315217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50647330284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48954582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55471539497375</t>
+    <t xml:space="preserve">3.43114686012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4531524181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50647306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48954606056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55471563339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.59618735313416</t>
@@ -4631,46 +4631,46 @@
     <t xml:space="preserve">3.58433842658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63173413276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7256805896759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81370258331299</t>
+    <t xml:space="preserve">3.6317343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674778938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72568035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81370210647583</t>
   </si>
   <si>
     <t xml:space="preserve">3.80523824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85178828239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89241337776184</t>
+    <t xml:space="preserve">3.85178852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89241313934326</t>
   </si>
   <si>
     <t xml:space="preserve">3.91949725151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366452217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06422519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01259660720825</t>
+    <t xml:space="preserve">3.97366428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06422472000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01259708404541</t>
   </si>
   <si>
     <t xml:space="preserve">3.9846670627594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03037071228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04052639007568</t>
+    <t xml:space="preserve">4.03037023544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04052686691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.04899024963379</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">4.0041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04391241073608</t>
+    <t xml:space="preserve">4.04391193389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.03460264205933</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">4.08623027801514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14209032058716</t>
+    <t xml:space="preserve">4.14208984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.09977197647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05322170257568</t>
+    <t xml:space="preserve">4.05322217941284</t>
   </si>
   <si>
     <t xml:space="preserve">4.00836515426636</t>
@@ -4718,22 +4718,22 @@
     <t xml:space="preserve">4.02359962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01344299316406</t>
+    <t xml:space="preserve">3.99990129470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01344347000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.96774005889893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00667285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.955890417099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84586381912231</t>
+    <t xml:space="preserve">4.00667238235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84586429595947</t>
   </si>
   <si>
     <t xml:space="preserve">3.78831100463867</t>
@@ -4748,64 +4748,64 @@
     <t xml:space="preserve">3.96096873283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9415020942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93219256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91272592544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91865086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89325976371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96435451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03544902801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97958898544312</t>
+    <t xml:space="preserve">3.94150257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93219232559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91272664070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91865110397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85771298408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89326000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96435403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03544807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97958922386169</t>
   </si>
   <si>
     <t xml:space="preserve">4.03629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0168285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99482297897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98974537849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9973623752594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02529191970825</t>
+    <t xml:space="preserve">4.01682901382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99482321739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98974514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02529239654541</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04475831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05660772323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08792304992676</t>
+    <t xml:space="preserve">4.04475784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05660820007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0879225730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685537338257</t>
@@ -4814,28 +4814,28 @@
     <t xml:space="preserve">4.10992813110352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09638690948486</t>
+    <t xml:space="preserve">4.09638643264771</t>
   </si>
   <si>
     <t xml:space="preserve">4.15901708602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1911792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13362646102905</t>
+    <t xml:space="preserve">4.19117879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13362598419189</t>
   </si>
   <si>
     <t xml:space="preserve">4.17763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732479095459</t>
+    <t xml:space="preserve">4.15732431411743</t>
   </si>
   <si>
     <t xml:space="preserve">4.14462900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18271541595459</t>
+    <t xml:space="preserve">4.18271493911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.18948602676392</t>
@@ -4844,13 +4844,13 @@
     <t xml:space="preserve">4.19794988632202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20556735992432</t>
+    <t xml:space="preserve">4.20556688308716</t>
   </si>
   <si>
     <t xml:space="preserve">4.2292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21233797073364</t>
+    <t xml:space="preserve">4.2123384475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.17679071426392</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">4.16155624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863964080811</t>
+    <t xml:space="preserve">4.18864011764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17932987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23349714279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24026823043823</t>
+    <t xml:space="preserve">4.17933034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23349666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24026775360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.27073669433594</t>
@@ -4880,37 +4880,37 @@
     <t xml:space="preserve">4.2961277961731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33506059646606</t>
+    <t xml:space="preserve">4.33506011962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.29443454742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28427839279175</t>
+    <t xml:space="preserve">4.28427886962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.04560518264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09215497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8509418964386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87802529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784206390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85263466835022</t>
+    <t xml:space="preserve">4.09215450286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85094213485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87802505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784230232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8526349067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.96604681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94658064842224</t>
+    <t xml:space="preserve">3.9465811252594</t>
   </si>
   <si>
     <t xml:space="preserve">3.88056445121765</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">3.92965340614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93811702728271</t>
+    <t xml:space="preserve">3.93811678886414</t>
   </si>
   <si>
     <t xml:space="preserve">4.05491495132446</t>
@@ -4934,13 +4934,13 @@
     <t xml:space="preserve">4.25550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28766441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29274225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32321071624756</t>
+    <t xml:space="preserve">4.28766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29274272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32321119308472</t>
   </si>
   <si>
     <t xml:space="preserve">4.3553729057312</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">4.25888776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045916557312</t>
+    <t xml:space="preserve">4.30459117889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.28258562088013</t>
@@ -4967,22 +4967,22 @@
     <t xml:space="preserve">4.23857498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32828950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39938402175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37907075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34013795852661</t>
+    <t xml:space="preserve">4.32828903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39938354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37907123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34013843536377</t>
   </si>
   <si>
     <t xml:space="preserve">4.35706567764282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34183120727539</t>
+    <t xml:space="preserve">4.34183168411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.31644058227539</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">4.3216347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33531188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3398699760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32072305679321</t>
+    <t xml:space="preserve">4.33531141281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33987045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32072353363037</t>
   </si>
   <si>
     <t xml:space="preserve">4.29519462585449</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">4.38363361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36266374588013</t>
+    <t xml:space="preserve">4.36266326904297</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945746421814</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">4.38545703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40369176864624</t>
+    <t xml:space="preserve">4.40369129180908</t>
   </si>
   <si>
     <t xml:space="preserve">4.37451601028442</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">4.4000449180603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081100463867</t>
+    <t xml:space="preserve">4.35081052780151</t>
   </si>
   <si>
     <t xml:space="preserve">4.42830848693848</t>
@@ -5084,10 +5084,10 @@
     <t xml:space="preserve">4.49760103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45292568206787</t>
+    <t xml:space="preserve">4.48757171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45292520523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.40551519393921</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">4.4328670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43924951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50762939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51492404937744</t>
+    <t xml:space="preserve">4.43924903869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48574781417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51492357254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.51948213577271</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">4.54318761825562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57692193984985</t>
+    <t xml:space="preserve">4.5769214630127</t>
   </si>
   <si>
     <t xml:space="preserve">4.52859973907471</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">4.56233406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59150981903076</t>
+    <t xml:space="preserve">4.5915093421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.60974454879761</t>
@@ -5132,7 +5132,7 @@
     <t xml:space="preserve">4.61156797409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63891935348511</t>
+    <t xml:space="preserve">4.63891983032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.6425666809082</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">4.58239221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52130603790283</t>
+    <t xml:space="preserve">4.52130556106567</t>
   </si>
   <si>
     <t xml:space="preserve">4.51218843460083</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">4.55595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58786296844482</t>
+    <t xml:space="preserve">4.58786249160767</t>
   </si>
   <si>
     <t xml:space="preserve">4.67721319198608</t>
@@ -5168,22 +5168,22 @@
     <t xml:space="preserve">4.65350770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73191690444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73738765716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71732902526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65897846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75197553634644</t>
+    <t xml:space="preserve">4.73191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71732950210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65897798538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72644662857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75197505950928</t>
   </si>
   <si>
     <t xml:space="preserve">4.55686378479004</t>
@@ -5192,10 +5192,10 @@
     <t xml:space="preserve">4.55503988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56780481338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65533113479614</t>
+    <t xml:space="preserve">4.56780433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6553316116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.66627216339111</t>
@@ -5204,13 +5204,13 @@
     <t xml:space="preserve">4.68997716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68268394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64074325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60792112350464</t>
+    <t xml:space="preserve">4.68268346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60792064666748</t>
   </si>
   <si>
     <t xml:space="preserve">4.62615537643433</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">4.64803743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6845064163208</t>
+    <t xml:space="preserve">4.68450689315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.72279977798462</t>
@@ -5228,7 +5228,7 @@
     <t xml:space="preserve">4.76473951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73009347915649</t>
+    <t xml:space="preserve">4.73009395599365</t>
   </si>
   <si>
     <t xml:space="preserve">4.78115081787109</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">4.7392110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67174243927002</t>
+    <t xml:space="preserve">4.67174291610718</t>
   </si>
   <si>
     <t xml:space="preserve">4.66991901397705</t>
@@ -5273,16 +5273,16 @@
     <t xml:space="preserve">4.74285840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70638847351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63709688186646</t>
+    <t xml:space="preserve">4.7063889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6370964050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.57509851455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66080141067505</t>
+    <t xml:space="preserve">4.66080188751221</t>
   </si>
   <si>
     <t xml:space="preserve">4.71003532409668</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">4.7027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67903661727905</t>
+    <t xml:space="preserve">4.67903614044189</t>
   </si>
   <si>
     <t xml:space="preserve">4.65715456008911</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">4.92155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87050104141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88873624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83403205871582</t>
+    <t xml:space="preserve">4.87050151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8887357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83403158187866</t>
   </si>
   <si>
     <t xml:space="preserve">4.87414836883545</t>
@@ -5318,10 +5318,10 @@
     <t xml:space="preserve">4.81397390365601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85956048965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84497261047363</t>
+    <t xml:space="preserve">4.85956001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84497308731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.78844499588013</t>
@@ -5330,13 +5330,13 @@
     <t xml:space="preserve">4.79573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82491397857666</t>
+    <t xml:space="preserve">4.82491445541382</t>
   </si>
   <si>
     <t xml:space="preserve">4.78297424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79756259918213</t>
+    <t xml:space="preserve">4.79756212234497</t>
   </si>
   <si>
     <t xml:space="preserve">4.78479814529419</t>
@@ -5345,13 +5345,13 @@
     <t xml:space="preserve">4.7902684211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77932739257812</t>
+    <t xml:space="preserve">4.77932786941528</t>
   </si>
   <si>
     <t xml:space="preserve">4.74650478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6881537437439</t>
+    <t xml:space="preserve">4.68815422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.66262483596802</t>
@@ -5369,13 +5369,13 @@
     <t xml:space="preserve">4.89238309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96714544296265</t>
+    <t xml:space="preserve">4.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">4.94161653518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89602947235107</t>
+    <t xml:space="preserve">4.89602994918823</t>
   </si>
   <si>
     <t xml:space="preserve">4.8559136390686</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">4.93796968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97079277038574</t>
+    <t xml:space="preserve">4.97079229354858</t>
   </si>
   <si>
     <t xml:space="preserve">5.07655382156372</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">5.22060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23337268829346</t>
+    <t xml:space="preserve">5.2333722114563</t>
   </si>
   <si>
     <t xml:space="preserve">5.28807735443115</t>
@@ -5429,13 +5429,13 @@
     <t xml:space="preserve">5.25707769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26072454452515</t>
+    <t xml:space="preserve">5.2607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">5.24978399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28078269958496</t>
+    <t xml:space="preserve">5.28078317642212</t>
   </si>
   <si>
     <t xml:space="preserve">5.21696138381958</t>
@@ -5447,10 +5447,10 @@
     <t xml:space="preserve">6.33839845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38216161727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51709842681885</t>
+    <t xml:space="preserve">6.38216209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51709890365601</t>
   </si>
   <si>
     <t xml:space="preserve">6.6100959777832</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">6.85261821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85626554489136</t>
+    <t xml:space="preserve">6.8562650680542</t>
   </si>
   <si>
     <t xml:space="preserve">6.87997055053711</t>
@@ -5486,13 +5486,13 @@
     <t xml:space="preserve">6.94561576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95655632019043</t>
+    <t xml:space="preserve">6.95655679702759</t>
   </si>
   <si>
     <t xml:space="preserve">6.90002870559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87632369995117</t>
+    <t xml:space="preserve">6.87632322311401</t>
   </si>
   <si>
     <t xml:space="preserve">6.92373371124268</t>
@@ -5501,7 +5501,7 @@
     <t xml:space="preserve">6.93832159042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86902952194214</t>
+    <t xml:space="preserve">6.8690299987793</t>
   </si>
   <si>
     <t xml:space="preserve">6.96202707290649</t>
@@ -5522,13 +5522,13 @@
     <t xml:space="preserve">7.08055257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16625595092773</t>
+    <t xml:space="preserve">7.16625642776489</t>
   </si>
   <si>
     <t xml:space="preserve">7.33492755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31213474273682</t>
+    <t xml:space="preserve">7.31213426589966</t>
   </si>
   <si>
     <t xml:space="preserve">7.2437539100647</t>
@@ -5537,13 +5537,13 @@
     <t xml:space="preserve">7.37139701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21184253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27566432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17537355422974</t>
+    <t xml:space="preserve">7.21184301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27566480636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17537307739258</t>
   </si>
   <si>
     <t xml:space="preserve">7.23919534683228</t>
@@ -5555,10 +5555,10 @@
     <t xml:space="preserve">7.29389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41242504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51271629333496</t>
+    <t xml:space="preserve">7.41242551803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5127158164978</t>
   </si>
   <si>
     <t xml:space="preserve">7.53551006317139</t>
@@ -5567,19 +5567,19 @@
     <t xml:space="preserve">7.59933137893677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63124227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5765380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63580131530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.726975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67682886123657</t>
+    <t xml:space="preserve">7.63124179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57653856277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63580083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72697448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67682933807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.68594646453857</t>
@@ -5588,7 +5588,7 @@
     <t xml:space="preserve">7.59477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67226982116699</t>
+    <t xml:space="preserve">7.67227029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.78167867660522</t>
@@ -5612,7 +5612,7 @@
     <t xml:space="preserve">8.11902141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2238712310791</t>
+    <t xml:space="preserve">8.22387218475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.44268894195557</t>
@@ -72187,7 +72187,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.691087963</v>
+     